--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA137"/>
+  <dimension ref="A1:AA145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12614,7 +12614,7 @@
         <v>100</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>45828.89427865107</v>
+        <v>45828.89427864584</v>
       </c>
       <c r="O130" t="n">
         <v>1</v>
@@ -12705,7 +12705,7 @@
         <v>12.02781891822815</v>
       </c>
       <c r="N131" s="2" t="n">
-        <v>45828.89427865107</v>
+        <v>45828.89427864584</v>
       </c>
       <c r="O131" t="n">
         <v>37.45</v>
@@ -12796,7 +12796,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N132" s="2" t="n">
-        <v>45828.89427865107</v>
+        <v>45828.89427864584</v>
       </c>
       <c r="O132" t="n">
         <v>380</v>
@@ -12891,7 +12891,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N133" s="2" t="n">
-        <v>45828.89427865107</v>
+        <v>45828.89427864584</v>
       </c>
       <c r="O133" t="n">
         <v>0.725</v>
@@ -12982,7 +12982,7 @@
         <v>11.4948091506958</v>
       </c>
       <c r="N134" s="2" t="n">
-        <v>45828.89427865107</v>
+        <v>45828.89427864584</v>
       </c>
       <c r="O134" t="n">
         <v>89.90000000000001</v>
@@ -13077,7 +13077,7 @@
         <v>13.05655670166016</v>
       </c>
       <c r="N135" s="2" t="n">
-        <v>45828.89427865107</v>
+        <v>45828.89427864584</v>
       </c>
       <c r="O135" t="n">
         <v>43.6</v>
@@ -13172,7 +13172,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N136" s="2" t="n">
-        <v>45828.89427865107</v>
+        <v>45828.89427864584</v>
       </c>
       <c r="O136" t="n">
         <v>25.2</v>
@@ -13267,7 +13267,7 @@
         <v>12.30872821807861</v>
       </c>
       <c r="N137" s="2" t="n">
-        <v>45828.89427865107</v>
+        <v>45828.89427864584</v>
       </c>
       <c r="O137" t="n">
         <v>55</v>
@@ -13309,6 +13309,756 @@
       </c>
       <c r="AA137" t="n">
         <v>12.30872821807861</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
+        <v>1</v>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H138" t="n">
+        <v>1</v>
+      </c>
+      <c r="I138" t="n">
+        <v>1</v>
+      </c>
+      <c r="J138" t="n">
+        <v>1</v>
+      </c>
+      <c r="K138" t="n">
+        <v>100</v>
+      </c>
+      <c r="L138" t="n">
+        <v>100</v>
+      </c>
+      <c r="M138" t="n">
+        <v>100</v>
+      </c>
+      <c r="N138" s="2" t="n">
+        <v>45831.31329159903</v>
+      </c>
+      <c r="O138" t="n">
+        <v>1</v>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>1</v>
+      </c>
+      <c r="R138" t="n">
+        <v>1</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0</v>
+      </c>
+      <c r="T138" t="n">
+        <v>16.03601332880703</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V138" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W138" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>DE000A0XYG76</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>DR0.DE</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>DT.ROHSTOFF AG NA O.N.</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F139" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H139" t="n">
+        <v>1</v>
+      </c>
+      <c r="I139" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="J139" t="n">
+        <v>39</v>
+      </c>
+      <c r="K139" t="n">
+        <v>11</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.4329348504543304</v>
+      </c>
+      <c r="M139" t="n">
+        <v>12.02781891822815</v>
+      </c>
+      <c r="N139" s="2" t="n">
+        <v>45831.31329159903</v>
+      </c>
+      <c r="O139" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>1</v>
+      </c>
+      <c r="R139" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="S139" t="n">
+        <v>1513.2</v>
+      </c>
+      <c r="T139" t="n">
+        <v>1513.2</v>
+      </c>
+      <c r="U139" t="n">
+        <v>34.92</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.029177718832891</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.029177718832891</v>
+      </c>
+      <c r="X139" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.4742938280105591</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>12.61593472957611</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F140" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H140" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I140" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J140" t="n">
+        <v>3</v>
+      </c>
+      <c r="K140" t="n">
+        <v>10</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M140" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N140" s="2" t="n">
+        <v>45831.31329159903</v>
+      </c>
+      <c r="O140" t="n">
+        <v>380</v>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.85553</v>
+      </c>
+      <c r="R140" t="n">
+        <v>444.1691115448903</v>
+      </c>
+      <c r="S140" t="n">
+        <v>1140</v>
+      </c>
+      <c r="T140" t="n">
+        <v>1332.507334634671</v>
+      </c>
+      <c r="U140" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.0335467516713539</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.03129972706893347</v>
+      </c>
+      <c r="X140" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.5007368326187134</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>12.07941150665283</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H141" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J141" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K141" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M141" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N141" s="2" t="n">
+        <v>45831.31329159903</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>1.78991</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.4050482985178026</v>
+      </c>
+      <c r="S141" t="n">
+        <v>2656.4</v>
+      </c>
+      <c r="T141" t="n">
+        <v>1484.096965769229</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.3678646934460888</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0</v>
+      </c>
+      <c r="W141" t="n">
+        <v>-0.008570263309328308</v>
+      </c>
+      <c r="X141" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.5391064286231995</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>12.27176785469055</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>NO0012851874</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>DOFG.OL</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>DOF GROUP ASA  NK 2,50</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F142" t="n">
+        <v>90.45</v>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="H142" t="n">
+        <v>11.53806</v>
+      </c>
+      <c r="I142" t="n">
+        <v>7.839272806693673</v>
+      </c>
+      <c r="J142" t="n">
+        <v>160</v>
+      </c>
+      <c r="K142" t="n">
+        <v>9</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.5388140678405762</v>
+      </c>
+      <c r="M142" t="n">
+        <v>11.4948091506958</v>
+      </c>
+      <c r="N142" s="2" t="n">
+        <v>45831.31329159903</v>
+      </c>
+      <c r="O142" t="n">
+        <v>90</v>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>11.63899</v>
+      </c>
+      <c r="R142" t="n">
+        <v>7.732629721307434</v>
+      </c>
+      <c r="S142" t="n">
+        <v>14400</v>
+      </c>
+      <c r="T142" t="n">
+        <v>1237.220755409189</v>
+      </c>
+      <c r="U142" t="n">
+        <v>7.055345526024306</v>
+      </c>
+      <c r="V142" t="n">
+        <v>-0.00497512437810943</v>
+      </c>
+      <c r="W142" t="n">
+        <v>-0.01360369616110069</v>
+      </c>
+      <c r="X142" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.5161983370780945</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>10.16883182525635</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F143" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H143" t="n">
+        <v>1</v>
+      </c>
+      <c r="I143" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="J143" t="n">
+        <v>34</v>
+      </c>
+      <c r="K143" t="n">
+        <v>9</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.6616257429122925</v>
+      </c>
+      <c r="M143" t="n">
+        <v>13.05655670166016</v>
+      </c>
+      <c r="N143" s="2" t="n">
+        <v>45831.31329159903</v>
+      </c>
+      <c r="O143" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>1</v>
+      </c>
+      <c r="R143" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="S143" t="n">
+        <v>1482.4</v>
+      </c>
+      <c r="T143" t="n">
+        <v>1482.4</v>
+      </c>
+      <c r="U143" t="n">
+        <v>39.24</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.01869158878504673</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.01869158878504673</v>
+      </c>
+      <c r="X143" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.6566609740257263</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>12.99397349357605</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F144" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H144" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I144" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J144" t="n">
+        <v>537</v>
+      </c>
+      <c r="K144" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L144" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M144" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N144" s="2" t="n">
+        <v>45831.31329159903</v>
+      </c>
+      <c r="O144" t="n">
+        <v>25.85</v>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>9.028740000000001</v>
+      </c>
+      <c r="R144" t="n">
+        <v>2.863079455162071</v>
+      </c>
+      <c r="S144" t="n">
+        <v>13881.45</v>
+      </c>
+      <c r="T144" t="n">
+        <v>1537.473667422032</v>
+      </c>
+      <c r="U144" t="n">
+        <v>2.576771509645864</v>
+      </c>
+      <c r="V144" t="n">
+        <v>0.02579365079365092</v>
+      </c>
+      <c r="W144" t="n">
+        <v>0.02713429910995679</v>
+      </c>
+      <c r="X144" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y144" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z144" t="n">
+        <v>0.5859425067901611</v>
+      </c>
+      <c r="AA144" t="n">
+        <v>12.04357481002808</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="n">
+        <v>45831.31329159903</v>
+      </c>
+      <c r="F145" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H145" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I145" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J145" t="n">
+        <v>121</v>
+      </c>
+      <c r="K145" t="n">
+        <v>12</v>
+      </c>
+      <c r="L145" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M145" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N145" s="2" t="n">
+        <v>45831.31329159903</v>
+      </c>
+      <c r="O145" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="R145" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="S145" t="n">
+        <v>1715.78</v>
+      </c>
+      <c r="T145" t="n">
+        <v>1491.527627920109</v>
+      </c>
+      <c r="U145" t="n">
+        <v>11.09400714981899</v>
+      </c>
+      <c r="V145" t="n">
+        <v>0</v>
+      </c>
+      <c r="W145" t="n">
+        <v>0</v>
+      </c>
+      <c r="X145" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y145" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z145" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="AA145" t="n">
+        <v>14.27337956428528</v>
       </c>
     </row>
   </sheetData>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA145"/>
+  <dimension ref="A1:AA153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13364,7 +13364,7 @@
         <v>100</v>
       </c>
       <c r="N138" s="2" t="n">
-        <v>45831.31329159903</v>
+        <v>45831.31329159722</v>
       </c>
       <c r="O138" t="n">
         <v>1</v>
@@ -13455,7 +13455,7 @@
         <v>12.02781891822815</v>
       </c>
       <c r="N139" s="2" t="n">
-        <v>45831.31329159903</v>
+        <v>45831.31329159722</v>
       </c>
       <c r="O139" t="n">
         <v>38.8</v>
@@ -13546,7 +13546,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N140" s="2" t="n">
-        <v>45831.31329159903</v>
+        <v>45831.31329159722</v>
       </c>
       <c r="O140" t="n">
         <v>380</v>
@@ -13641,7 +13641,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N141" s="2" t="n">
-        <v>45831.31329159903</v>
+        <v>45831.31329159722</v>
       </c>
       <c r="O141" t="n">
         <v>0.725</v>
@@ -13732,7 +13732,7 @@
         <v>11.4948091506958</v>
       </c>
       <c r="N142" s="2" t="n">
-        <v>45831.31329159903</v>
+        <v>45831.31329159722</v>
       </c>
       <c r="O142" t="n">
         <v>90</v>
@@ -13827,7 +13827,7 @@
         <v>13.05655670166016</v>
       </c>
       <c r="N143" s="2" t="n">
-        <v>45831.31329159903</v>
+        <v>45831.31329159722</v>
       </c>
       <c r="O143" t="n">
         <v>43.6</v>
@@ -13922,7 +13922,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N144" s="2" t="n">
-        <v>45831.31329159903</v>
+        <v>45831.31329159722</v>
       </c>
       <c r="O144" t="n">
         <v>25.85</v>
@@ -13988,7 +13988,7 @@
         </is>
       </c>
       <c r="E145" s="2" t="n">
-        <v>45831.31329159903</v>
+        <v>45831.31329159722</v>
       </c>
       <c r="F145" t="n">
         <v>14.18</v>
@@ -14017,7 +14017,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N145" s="2" t="n">
-        <v>45831.31329159903</v>
+        <v>45831.31329159722</v>
       </c>
       <c r="O145" t="n">
         <v>14.18</v>
@@ -14058,6 +14058,756 @@
         <v>0.540931224822998</v>
       </c>
       <c r="AA145" t="n">
+        <v>14.27337956428528</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
+        <v>1</v>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H146" t="n">
+        <v>1</v>
+      </c>
+      <c r="I146" t="n">
+        <v>1</v>
+      </c>
+      <c r="J146" t="n">
+        <v>1</v>
+      </c>
+      <c r="K146" t="n">
+        <v>100</v>
+      </c>
+      <c r="L146" t="n">
+        <v>100</v>
+      </c>
+      <c r="M146" t="n">
+        <v>100</v>
+      </c>
+      <c r="N146" s="2" t="n">
+        <v>45831.36153190835</v>
+      </c>
+      <c r="O146" t="n">
+        <v>1</v>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q146" t="n">
+        <v>1</v>
+      </c>
+      <c r="R146" t="n">
+        <v>1</v>
+      </c>
+      <c r="S146" t="n">
+        <v>0</v>
+      </c>
+      <c r="T146" t="n">
+        <v>16.03601332880703</v>
+      </c>
+      <c r="U146" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V146" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W146" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X146" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y146" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z146" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA146" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>DE000A0XYG76</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>DR0.DE</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>DT.ROHSTOFF AG NA O.N.</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F147" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H147" t="n">
+        <v>1</v>
+      </c>
+      <c r="I147" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="J147" t="n">
+        <v>39</v>
+      </c>
+      <c r="K147" t="n">
+        <v>11</v>
+      </c>
+      <c r="L147" t="n">
+        <v>0.4329348504543304</v>
+      </c>
+      <c r="M147" t="n">
+        <v>12.02781891822815</v>
+      </c>
+      <c r="N147" s="2" t="n">
+        <v>45831.36153190835</v>
+      </c>
+      <c r="O147" t="n">
+        <v>38.25</v>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>1</v>
+      </c>
+      <c r="R147" t="n">
+        <v>38.25</v>
+      </c>
+      <c r="S147" t="n">
+        <v>1491.75</v>
+      </c>
+      <c r="T147" t="n">
+        <v>1491.75</v>
+      </c>
+      <c r="U147" t="n">
+        <v>34.92</v>
+      </c>
+      <c r="V147" t="n">
+        <v>0.01458885941644561</v>
+      </c>
+      <c r="W147" t="n">
+        <v>0.01458885941644561</v>
+      </c>
+      <c r="X147" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y147" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z147" t="n">
+        <v>0.4742938280105591</v>
+      </c>
+      <c r="AA147" t="n">
+        <v>12.61593472957611</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F148" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H148" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I148" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J148" t="n">
+        <v>3</v>
+      </c>
+      <c r="K148" t="n">
+        <v>10</v>
+      </c>
+      <c r="L148" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M148" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N148" s="2" t="n">
+        <v>45831.36153190835</v>
+      </c>
+      <c r="O148" t="n">
+        <v>380</v>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>0.8552999999999999</v>
+      </c>
+      <c r="R148" t="n">
+        <v>444.2885537238396</v>
+      </c>
+      <c r="S148" t="n">
+        <v>1140</v>
+      </c>
+      <c r="T148" t="n">
+        <v>1332.865661171519</v>
+      </c>
+      <c r="U148" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V148" t="n">
+        <v>0.0335467516713539</v>
+      </c>
+      <c r="W148" t="n">
+        <v>0.03157705541831501</v>
+      </c>
+      <c r="X148" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y148" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z148" t="n">
+        <v>0.5007368326187134</v>
+      </c>
+      <c r="AA148" t="n">
+        <v>12.07941150665283</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F149" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H149" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I149" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J149" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K149" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L149" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M149" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N149" s="2" t="n">
+        <v>45831.36153190835</v>
+      </c>
+      <c r="O149" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q149" t="n">
+        <v>1.79089</v>
+      </c>
+      <c r="R149" t="n">
+        <v>0.4048266504363752</v>
+      </c>
+      <c r="S149" t="n">
+        <v>2656.4</v>
+      </c>
+      <c r="T149" t="n">
+        <v>1483.284847198879</v>
+      </c>
+      <c r="U149" t="n">
+        <v>0.3678646934460888</v>
+      </c>
+      <c r="V149" t="n">
+        <v>0</v>
+      </c>
+      <c r="W149" t="n">
+        <v>-0.009112787496719621</v>
+      </c>
+      <c r="X149" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y149" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z149" t="n">
+        <v>0.5391064286231995</v>
+      </c>
+      <c r="AA149" t="n">
+        <v>12.27176785469055</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>NO0012851874</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>DOFG.OL</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>DOF GROUP ASA  NK 2,50</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F150" t="n">
+        <v>90.45</v>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="H150" t="n">
+        <v>11.53806</v>
+      </c>
+      <c r="I150" t="n">
+        <v>7.839272806693673</v>
+      </c>
+      <c r="J150" t="n">
+        <v>160</v>
+      </c>
+      <c r="K150" t="n">
+        <v>9</v>
+      </c>
+      <c r="L150" t="n">
+        <v>0.5388140678405762</v>
+      </c>
+      <c r="M150" t="n">
+        <v>11.4948091506958</v>
+      </c>
+      <c r="N150" s="2" t="n">
+        <v>45831.36153190835</v>
+      </c>
+      <c r="O150" t="n">
+        <v>90.15000000000001</v>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="Q150" t="n">
+        <v>11.67971</v>
+      </c>
+      <c r="R150" t="n">
+        <v>7.718513558983914</v>
+      </c>
+      <c r="S150" t="n">
+        <v>14424</v>
+      </c>
+      <c r="T150" t="n">
+        <v>1234.962169437426</v>
+      </c>
+      <c r="U150" t="n">
+        <v>7.055345526024306</v>
+      </c>
+      <c r="V150" t="n">
+        <v>-0.003316749585406287</v>
+      </c>
+      <c r="W150" t="n">
+        <v>-0.01540439409209571</v>
+      </c>
+      <c r="X150" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y150" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z150" t="n">
+        <v>0.5161983370780945</v>
+      </c>
+      <c r="AA150" t="n">
+        <v>10.16883182525635</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F151" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H151" t="n">
+        <v>1</v>
+      </c>
+      <c r="I151" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="J151" t="n">
+        <v>34</v>
+      </c>
+      <c r="K151" t="n">
+        <v>9</v>
+      </c>
+      <c r="L151" t="n">
+        <v>0.6616257429122925</v>
+      </c>
+      <c r="M151" t="n">
+        <v>13.05655670166016</v>
+      </c>
+      <c r="N151" s="2" t="n">
+        <v>45831.36153190835</v>
+      </c>
+      <c r="O151" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q151" t="n">
+        <v>1</v>
+      </c>
+      <c r="R151" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="S151" t="n">
+        <v>1489.2</v>
+      </c>
+      <c r="T151" t="n">
+        <v>1489.2</v>
+      </c>
+      <c r="U151" t="n">
+        <v>39.42</v>
+      </c>
+      <c r="V151" t="n">
+        <v>0.02336448598130847</v>
+      </c>
+      <c r="W151" t="n">
+        <v>0.02336448598130847</v>
+      </c>
+      <c r="X151" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y151" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z151" t="n">
+        <v>0.6566609740257263</v>
+      </c>
+      <c r="AA151" t="n">
+        <v>12.99397349357605</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F152" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H152" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I152" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J152" t="n">
+        <v>537</v>
+      </c>
+      <c r="K152" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L152" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M152" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N152" s="2" t="n">
+        <v>45831.36153190835</v>
+      </c>
+      <c r="O152" t="n">
+        <v>26.05</v>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q152" t="n">
+        <v>9.01972</v>
+      </c>
+      <c r="R152" t="n">
+        <v>2.888116260815192</v>
+      </c>
+      <c r="S152" t="n">
+        <v>13988.85</v>
+      </c>
+      <c r="T152" t="n">
+        <v>1550.918432057758</v>
+      </c>
+      <c r="U152" t="n">
+        <v>2.599304634733673</v>
+      </c>
+      <c r="V152" t="n">
+        <v>0.03373015873015883</v>
+      </c>
+      <c r="W152" t="n">
+        <v>0.03611629287897511</v>
+      </c>
+      <c r="X152" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y152" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z152" t="n">
+        <v>0.5859425067901611</v>
+      </c>
+      <c r="AA152" t="n">
+        <v>12.04357481002808</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F153" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H153" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I153" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J153" t="n">
+        <v>121</v>
+      </c>
+      <c r="K153" t="n">
+        <v>12</v>
+      </c>
+      <c r="L153" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M153" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N153" s="2" t="n">
+        <v>45831.36153190835</v>
+      </c>
+      <c r="O153" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q153" t="n">
+        <v>1.1494253</v>
+      </c>
+      <c r="R153" t="n">
+        <v>12.3365998642974</v>
+      </c>
+      <c r="S153" t="n">
+        <v>1715.78</v>
+      </c>
+      <c r="T153" t="n">
+        <v>1492.728583579986</v>
+      </c>
+      <c r="U153" t="n">
+        <v>11.10293987786766</v>
+      </c>
+      <c r="V153" t="n">
+        <v>0</v>
+      </c>
+      <c r="W153" t="n">
+        <v>0.0008051849911427933</v>
+      </c>
+      <c r="X153" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y153" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z153" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="AA153" t="n">
         <v>14.27337956428528</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA153"/>
+  <dimension ref="A1:AA161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14114,7 +14114,7 @@
         <v>100</v>
       </c>
       <c r="N146" s="2" t="n">
-        <v>45831.36153190835</v>
+        <v>45831.36153190972</v>
       </c>
       <c r="O146" t="n">
         <v>1</v>
@@ -14205,7 +14205,7 @@
         <v>12.02781891822815</v>
       </c>
       <c r="N147" s="2" t="n">
-        <v>45831.36153190835</v>
+        <v>45831.36153190972</v>
       </c>
       <c r="O147" t="n">
         <v>38.25</v>
@@ -14296,7 +14296,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N148" s="2" t="n">
-        <v>45831.36153190835</v>
+        <v>45831.36153190972</v>
       </c>
       <c r="O148" t="n">
         <v>380</v>
@@ -14391,7 +14391,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N149" s="2" t="n">
-        <v>45831.36153190835</v>
+        <v>45831.36153190972</v>
       </c>
       <c r="O149" t="n">
         <v>0.725</v>
@@ -14482,7 +14482,7 @@
         <v>11.4948091506958</v>
       </c>
       <c r="N150" s="2" t="n">
-        <v>45831.36153190835</v>
+        <v>45831.36153190972</v>
       </c>
       <c r="O150" t="n">
         <v>90.15000000000001</v>
@@ -14577,7 +14577,7 @@
         <v>13.05655670166016</v>
       </c>
       <c r="N151" s="2" t="n">
-        <v>45831.36153190835</v>
+        <v>45831.36153190972</v>
       </c>
       <c r="O151" t="n">
         <v>43.8</v>
@@ -14672,7 +14672,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N152" s="2" t="n">
-        <v>45831.36153190835</v>
+        <v>45831.36153190972</v>
       </c>
       <c r="O152" t="n">
         <v>26.05</v>
@@ -14767,7 +14767,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N153" s="2" t="n">
-        <v>45831.36153190835</v>
+        <v>45831.36153190972</v>
       </c>
       <c r="O153" t="n">
         <v>14.18</v>
@@ -14808,6 +14808,756 @@
         <v>0.540931224822998</v>
       </c>
       <c r="AA153" t="n">
+        <v>14.27337956428528</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F154" t="n">
+        <v>1</v>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H154" t="n">
+        <v>1</v>
+      </c>
+      <c r="I154" t="n">
+        <v>1</v>
+      </c>
+      <c r="J154" t="n">
+        <v>1</v>
+      </c>
+      <c r="K154" t="n">
+        <v>100</v>
+      </c>
+      <c r="L154" t="n">
+        <v>100</v>
+      </c>
+      <c r="M154" t="n">
+        <v>100</v>
+      </c>
+      <c r="N154" s="2" t="n">
+        <v>45831.39935006046</v>
+      </c>
+      <c r="O154" t="n">
+        <v>1</v>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q154" t="n">
+        <v>1</v>
+      </c>
+      <c r="R154" t="n">
+        <v>1</v>
+      </c>
+      <c r="S154" t="n">
+        <v>0</v>
+      </c>
+      <c r="T154" t="n">
+        <v>16.03601332880703</v>
+      </c>
+      <c r="U154" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V154" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W154" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X154" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y154" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z154" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA154" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>DE000A0XYG76</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>DR0.DE</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>DT.ROHSTOFF AG NA O.N.</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F155" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H155" t="n">
+        <v>1</v>
+      </c>
+      <c r="I155" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="J155" t="n">
+        <v>39</v>
+      </c>
+      <c r="K155" t="n">
+        <v>11</v>
+      </c>
+      <c r="L155" t="n">
+        <v>0.4329348504543304</v>
+      </c>
+      <c r="M155" t="n">
+        <v>12.02781891822815</v>
+      </c>
+      <c r="N155" s="2" t="n">
+        <v>45831.39935006046</v>
+      </c>
+      <c r="O155" t="n">
+        <v>38.45</v>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q155" t="n">
+        <v>1</v>
+      </c>
+      <c r="R155" t="n">
+        <v>38.45</v>
+      </c>
+      <c r="S155" t="n">
+        <v>1499.55</v>
+      </c>
+      <c r="T155" t="n">
+        <v>1499.55</v>
+      </c>
+      <c r="U155" t="n">
+        <v>34.92</v>
+      </c>
+      <c r="V155" t="n">
+        <v>0.01989389920424411</v>
+      </c>
+      <c r="W155" t="n">
+        <v>0.01989389920424411</v>
+      </c>
+      <c r="X155" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y155" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z155" t="n">
+        <v>0.4742938280105591</v>
+      </c>
+      <c r="AA155" t="n">
+        <v>12.61593472957611</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F156" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H156" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I156" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J156" t="n">
+        <v>3</v>
+      </c>
+      <c r="K156" t="n">
+        <v>10</v>
+      </c>
+      <c r="L156" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M156" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N156" s="2" t="n">
+        <v>45831.39935006046</v>
+      </c>
+      <c r="O156" t="n">
+        <v>377.26</v>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q156" t="n">
+        <v>0.85654</v>
+      </c>
+      <c r="R156" t="n">
+        <v>440.4464473346254</v>
+      </c>
+      <c r="S156" t="n">
+        <v>1131.78</v>
+      </c>
+      <c r="T156" t="n">
+        <v>1321.339342003876</v>
+      </c>
+      <c r="U156" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V156" t="n">
+        <v>0.02609433561982888</v>
+      </c>
+      <c r="W156" t="n">
+        <v>0.02265621160550513</v>
+      </c>
+      <c r="X156" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y156" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z156" t="n">
+        <v>0.5007368326187134</v>
+      </c>
+      <c r="AA156" t="n">
+        <v>12.07941150665283</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F157" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H157" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I157" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J157" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K157" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L157" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M157" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N157" s="2" t="n">
+        <v>45831.39935006046</v>
+      </c>
+      <c r="O157" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q157" t="n">
+        <v>1.7951</v>
+      </c>
+      <c r="R157" t="n">
+        <v>0.4038772213247173</v>
+      </c>
+      <c r="S157" t="n">
+        <v>2656.4</v>
+      </c>
+      <c r="T157" t="n">
+        <v>1479.806138933764</v>
+      </c>
+      <c r="U157" t="n">
+        <v>0.3678646934460888</v>
+      </c>
+      <c r="V157" t="n">
+        <v>0</v>
+      </c>
+      <c r="W157" t="n">
+        <v>-0.01143668876385706</v>
+      </c>
+      <c r="X157" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y157" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z157" t="n">
+        <v>0.5391064286231995</v>
+      </c>
+      <c r="AA157" t="n">
+        <v>12.27176785469055</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>NO0012851874</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>DOFG.OL</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>DOF GROUP ASA  NK 2,50</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F158" t="n">
+        <v>90.45</v>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="H158" t="n">
+        <v>11.53806</v>
+      </c>
+      <c r="I158" t="n">
+        <v>7.839272806693673</v>
+      </c>
+      <c r="J158" t="n">
+        <v>160</v>
+      </c>
+      <c r="K158" t="n">
+        <v>9</v>
+      </c>
+      <c r="L158" t="n">
+        <v>0.5388140678405762</v>
+      </c>
+      <c r="M158" t="n">
+        <v>11.4948091506958</v>
+      </c>
+      <c r="N158" s="2" t="n">
+        <v>45831.39935006046</v>
+      </c>
+      <c r="O158" t="n">
+        <v>90.45</v>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="Q158" t="n">
+        <v>11.68601</v>
+      </c>
+      <c r="R158" t="n">
+        <v>7.740024182762124</v>
+      </c>
+      <c r="S158" t="n">
+        <v>14472</v>
+      </c>
+      <c r="T158" t="n">
+        <v>1238.40386924194</v>
+      </c>
+      <c r="U158" t="n">
+        <v>7.055345526024306</v>
+      </c>
+      <c r="V158" t="n">
+        <v>0</v>
+      </c>
+      <c r="W158" t="n">
+        <v>-0.01266043756594415</v>
+      </c>
+      <c r="X158" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y158" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z158" t="n">
+        <v>0.5161983370780945</v>
+      </c>
+      <c r="AA158" t="n">
+        <v>10.16883182525635</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F159" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H159" t="n">
+        <v>1</v>
+      </c>
+      <c r="I159" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="J159" t="n">
+        <v>34</v>
+      </c>
+      <c r="K159" t="n">
+        <v>9</v>
+      </c>
+      <c r="L159" t="n">
+        <v>0.6616257429122925</v>
+      </c>
+      <c r="M159" t="n">
+        <v>13.05655670166016</v>
+      </c>
+      <c r="N159" s="2" t="n">
+        <v>45831.39935006046</v>
+      </c>
+      <c r="O159" t="n">
+        <v>43.78</v>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q159" t="n">
+        <v>1</v>
+      </c>
+      <c r="R159" t="n">
+        <v>43.78</v>
+      </c>
+      <c r="S159" t="n">
+        <v>1488.52</v>
+      </c>
+      <c r="T159" t="n">
+        <v>1488.52</v>
+      </c>
+      <c r="U159" t="n">
+        <v>39.42</v>
+      </c>
+      <c r="V159" t="n">
+        <v>0.02289719626168241</v>
+      </c>
+      <c r="W159" t="n">
+        <v>0.02289719626168241</v>
+      </c>
+      <c r="X159" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y159" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z159" t="n">
+        <v>0.6566609740257263</v>
+      </c>
+      <c r="AA159" t="n">
+        <v>12.99397349357605</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F160" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H160" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I160" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J160" t="n">
+        <v>537</v>
+      </c>
+      <c r="K160" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L160" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M160" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N160" s="2" t="n">
+        <v>45831.39935006046</v>
+      </c>
+      <c r="O160" t="n">
+        <v>26.05</v>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q160" t="n">
+        <v>8.996029999999999</v>
+      </c>
+      <c r="R160" t="n">
+        <v>2.895721779496067</v>
+      </c>
+      <c r="S160" t="n">
+        <v>13988.85</v>
+      </c>
+      <c r="T160" t="n">
+        <v>1555.002595589388</v>
+      </c>
+      <c r="U160" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V160" t="n">
+        <v>0.03373015873015883</v>
+      </c>
+      <c r="W160" t="n">
+        <v>0.03884478477799092</v>
+      </c>
+      <c r="X160" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y160" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z160" t="n">
+        <v>0.5859425067901611</v>
+      </c>
+      <c r="AA160" t="n">
+        <v>12.04357481002808</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F161" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H161" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I161" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J161" t="n">
+        <v>121</v>
+      </c>
+      <c r="K161" t="n">
+        <v>12</v>
+      </c>
+      <c r="L161" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M161" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N161" s="2" t="n">
+        <v>45831.39935006046</v>
+      </c>
+      <c r="O161" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q161" t="n">
+        <v>1.1463946</v>
+      </c>
+      <c r="R161" t="n">
+        <v>12.36921388150293</v>
+      </c>
+      <c r="S161" t="n">
+        <v>1715.78</v>
+      </c>
+      <c r="T161" t="n">
+        <v>1496.674879661855</v>
+      </c>
+      <c r="U161" t="n">
+        <v>11.13229249335264</v>
+      </c>
+      <c r="V161" t="n">
+        <v>0</v>
+      </c>
+      <c r="W161" t="n">
+        <v>0.003450993226939314</v>
+      </c>
+      <c r="X161" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y161" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z161" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="AA161" t="n">
         <v>14.27337956428528</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA161"/>
+  <dimension ref="A1:AA169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14864,7 +14864,7 @@
         <v>100</v>
       </c>
       <c r="N154" s="2" t="n">
-        <v>45831.39935006046</v>
+        <v>45831.39935005787</v>
       </c>
       <c r="O154" t="n">
         <v>1</v>
@@ -14955,7 +14955,7 @@
         <v>12.02781891822815</v>
       </c>
       <c r="N155" s="2" t="n">
-        <v>45831.39935006046</v>
+        <v>45831.39935005787</v>
       </c>
       <c r="O155" t="n">
         <v>38.45</v>
@@ -15046,7 +15046,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N156" s="2" t="n">
-        <v>45831.39935006046</v>
+        <v>45831.39935005787</v>
       </c>
       <c r="O156" t="n">
         <v>377.26</v>
@@ -15141,7 +15141,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N157" s="2" t="n">
-        <v>45831.39935006046</v>
+        <v>45831.39935005787</v>
       </c>
       <c r="O157" t="n">
         <v>0.725</v>
@@ -15232,7 +15232,7 @@
         <v>11.4948091506958</v>
       </c>
       <c r="N158" s="2" t="n">
-        <v>45831.39935006046</v>
+        <v>45831.39935005787</v>
       </c>
       <c r="O158" t="n">
         <v>90.45</v>
@@ -15327,7 +15327,7 @@
         <v>13.05655670166016</v>
       </c>
       <c r="N159" s="2" t="n">
-        <v>45831.39935006046</v>
+        <v>45831.39935005787</v>
       </c>
       <c r="O159" t="n">
         <v>43.78</v>
@@ -15422,7 +15422,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N160" s="2" t="n">
-        <v>45831.39935006046</v>
+        <v>45831.39935005787</v>
       </c>
       <c r="O160" t="n">
         <v>26.05</v>
@@ -15517,7 +15517,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N161" s="2" t="n">
-        <v>45831.39935006046</v>
+        <v>45831.39935005787</v>
       </c>
       <c r="O161" t="n">
         <v>14.18</v>
@@ -15558,6 +15558,756 @@
         <v>0.540931224822998</v>
       </c>
       <c r="AA161" t="n">
+        <v>14.27337956428528</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F162" t="n">
+        <v>1</v>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H162" t="n">
+        <v>1</v>
+      </c>
+      <c r="I162" t="n">
+        <v>1</v>
+      </c>
+      <c r="J162" t="n">
+        <v>1</v>
+      </c>
+      <c r="K162" t="n">
+        <v>100</v>
+      </c>
+      <c r="L162" t="n">
+        <v>100</v>
+      </c>
+      <c r="M162" t="n">
+        <v>100</v>
+      </c>
+      <c r="N162" s="2" t="n">
+        <v>45831.44249482949</v>
+      </c>
+      <c r="O162" t="n">
+        <v>1</v>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q162" t="n">
+        <v>1</v>
+      </c>
+      <c r="R162" t="n">
+        <v>1</v>
+      </c>
+      <c r="S162" t="n">
+        <v>0</v>
+      </c>
+      <c r="T162" t="n">
+        <v>16.03601332880703</v>
+      </c>
+      <c r="U162" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V162" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W162" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X162" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y162" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z162" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA162" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>DE000A0XYG76</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>DR0.DE</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>DT.ROHSTOFF AG NA O.N.</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F163" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H163" t="n">
+        <v>1</v>
+      </c>
+      <c r="I163" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="J163" t="n">
+        <v>39</v>
+      </c>
+      <c r="K163" t="n">
+        <v>11</v>
+      </c>
+      <c r="L163" t="n">
+        <v>0.4329348504543304</v>
+      </c>
+      <c r="M163" t="n">
+        <v>12.02781891822815</v>
+      </c>
+      <c r="N163" s="2" t="n">
+        <v>45831.44249482949</v>
+      </c>
+      <c r="O163" t="n">
+        <v>38.45</v>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q163" t="n">
+        <v>1</v>
+      </c>
+      <c r="R163" t="n">
+        <v>38.45</v>
+      </c>
+      <c r="S163" t="n">
+        <v>1499.55</v>
+      </c>
+      <c r="T163" t="n">
+        <v>1499.55</v>
+      </c>
+      <c r="U163" t="n">
+        <v>34.92</v>
+      </c>
+      <c r="V163" t="n">
+        <v>0.01989389920424411</v>
+      </c>
+      <c r="W163" t="n">
+        <v>0.01989389920424411</v>
+      </c>
+      <c r="X163" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y163" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z163" t="n">
+        <v>0.4742938280105591</v>
+      </c>
+      <c r="AA163" t="n">
+        <v>12.61593472957611</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F164" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H164" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I164" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J164" t="n">
+        <v>3</v>
+      </c>
+      <c r="K164" t="n">
+        <v>10</v>
+      </c>
+      <c r="L164" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M164" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N164" s="2" t="n">
+        <v>45831.44249482949</v>
+      </c>
+      <c r="O164" t="n">
+        <v>377.26</v>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q164" t="n">
+        <v>0.85669</v>
+      </c>
+      <c r="R164" t="n">
+        <v>440.3693284618707</v>
+      </c>
+      <c r="S164" t="n">
+        <v>1131.78</v>
+      </c>
+      <c r="T164" t="n">
+        <v>1321.107985385612</v>
+      </c>
+      <c r="U164" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V164" t="n">
+        <v>0.02609433561982888</v>
+      </c>
+      <c r="W164" t="n">
+        <v>0.02247715216540325</v>
+      </c>
+      <c r="X164" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y164" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z164" t="n">
+        <v>0.5007368326187134</v>
+      </c>
+      <c r="AA164" t="n">
+        <v>12.07941150665283</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F165" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H165" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I165" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J165" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K165" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L165" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M165" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N165" s="2" t="n">
+        <v>45831.44249482949</v>
+      </c>
+      <c r="O165" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q165" t="n">
+        <v>1.79611</v>
+      </c>
+      <c r="R165" t="n">
+        <v>0.4036501105166164</v>
+      </c>
+      <c r="S165" t="n">
+        <v>2656.4</v>
+      </c>
+      <c r="T165" t="n">
+        <v>1478.974004932883</v>
+      </c>
+      <c r="U165" t="n">
+        <v>0.3678646934460888</v>
+      </c>
+      <c r="V165" t="n">
+        <v>0</v>
+      </c>
+      <c r="W165" t="n">
+        <v>-0.01199258397314207</v>
+      </c>
+      <c r="X165" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y165" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z165" t="n">
+        <v>0.5391064286231995</v>
+      </c>
+      <c r="AA165" t="n">
+        <v>12.27176785469055</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>NO0012851874</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>DOFG.OL</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>DOF GROUP ASA  NK 2,50</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F166" t="n">
+        <v>90.45</v>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="H166" t="n">
+        <v>11.53806</v>
+      </c>
+      <c r="I166" t="n">
+        <v>7.839272806693673</v>
+      </c>
+      <c r="J166" t="n">
+        <v>160</v>
+      </c>
+      <c r="K166" t="n">
+        <v>9</v>
+      </c>
+      <c r="L166" t="n">
+        <v>0.5388140678405762</v>
+      </c>
+      <c r="M166" t="n">
+        <v>11.4948091506958</v>
+      </c>
+      <c r="N166" s="2" t="n">
+        <v>45831.44249482949</v>
+      </c>
+      <c r="O166" t="n">
+        <v>90.25</v>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="Q166" t="n">
+        <v>11.6831</v>
+      </c>
+      <c r="R166" t="n">
+        <v>7.724833306228655</v>
+      </c>
+      <c r="S166" t="n">
+        <v>14440</v>
+      </c>
+      <c r="T166" t="n">
+        <v>1235.973328996585</v>
+      </c>
+      <c r="U166" t="n">
+        <v>7.055345526024306</v>
+      </c>
+      <c r="V166" t="n">
+        <v>-0.002211166390270858</v>
+      </c>
+      <c r="W166" t="n">
+        <v>-0.0145982291070802</v>
+      </c>
+      <c r="X166" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y166" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z166" t="n">
+        <v>0.5161983370780945</v>
+      </c>
+      <c r="AA166" t="n">
+        <v>10.16883182525635</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F167" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H167" t="n">
+        <v>1</v>
+      </c>
+      <c r="I167" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="J167" t="n">
+        <v>34</v>
+      </c>
+      <c r="K167" t="n">
+        <v>9</v>
+      </c>
+      <c r="L167" t="n">
+        <v>0.6616257429122925</v>
+      </c>
+      <c r="M167" t="n">
+        <v>13.05655670166016</v>
+      </c>
+      <c r="N167" s="2" t="n">
+        <v>45831.44249482949</v>
+      </c>
+      <c r="O167" t="n">
+        <v>43.76</v>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q167" t="n">
+        <v>1</v>
+      </c>
+      <c r="R167" t="n">
+        <v>43.76</v>
+      </c>
+      <c r="S167" t="n">
+        <v>1487.84</v>
+      </c>
+      <c r="T167" t="n">
+        <v>1487.84</v>
+      </c>
+      <c r="U167" t="n">
+        <v>39.42</v>
+      </c>
+      <c r="V167" t="n">
+        <v>0.02242990654205612</v>
+      </c>
+      <c r="W167" t="n">
+        <v>0.02242990654205612</v>
+      </c>
+      <c r="X167" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y167" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z167" t="n">
+        <v>0.6566609740257263</v>
+      </c>
+      <c r="AA167" t="n">
+        <v>12.99397349357605</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F168" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H168" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I168" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J168" t="n">
+        <v>537</v>
+      </c>
+      <c r="K168" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L168" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M168" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N168" s="2" t="n">
+        <v>45831.44249482949</v>
+      </c>
+      <c r="O168" t="n">
+        <v>26.05</v>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q168" t="n">
+        <v>8.99869</v>
+      </c>
+      <c r="R168" t="n">
+        <v>2.894865808245422</v>
+      </c>
+      <c r="S168" t="n">
+        <v>13988.85</v>
+      </c>
+      <c r="T168" t="n">
+        <v>1554.542939027792</v>
+      </c>
+      <c r="U168" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V168" t="n">
+        <v>0.03373015873015883</v>
+      </c>
+      <c r="W168" t="n">
+        <v>0.03853770373313781</v>
+      </c>
+      <c r="X168" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y168" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z168" t="n">
+        <v>0.5859425067901611</v>
+      </c>
+      <c r="AA168" t="n">
+        <v>12.04357481002808</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F169" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H169" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I169" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J169" t="n">
+        <v>121</v>
+      </c>
+      <c r="K169" t="n">
+        <v>12</v>
+      </c>
+      <c r="L169" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M169" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N169" s="2" t="n">
+        <v>45831.44249482949</v>
+      </c>
+      <c r="O169" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q169" t="n">
+        <v>1.1466575</v>
+      </c>
+      <c r="R169" t="n">
+        <v>12.36637792889332</v>
+      </c>
+      <c r="S169" t="n">
+        <v>1715.78</v>
+      </c>
+      <c r="T169" t="n">
+        <v>1496.331729396092</v>
+      </c>
+      <c r="U169" t="n">
+        <v>11.13229249335264</v>
+      </c>
+      <c r="V169" t="n">
+        <v>0</v>
+      </c>
+      <c r="W169" t="n">
+        <v>0.003220926911479571</v>
+      </c>
+      <c r="X169" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y169" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z169" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="AA169" t="n">
         <v>14.27337956428528</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA169"/>
+  <dimension ref="A1:AA177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15614,7 +15614,7 @@
         <v>100</v>
       </c>
       <c r="N162" s="2" t="n">
-        <v>45831.44249482949</v>
+        <v>45831.44249482639</v>
       </c>
       <c r="O162" t="n">
         <v>1</v>
@@ -15705,7 +15705,7 @@
         <v>12.02781891822815</v>
       </c>
       <c r="N163" s="2" t="n">
-        <v>45831.44249482949</v>
+        <v>45831.44249482639</v>
       </c>
       <c r="O163" t="n">
         <v>38.45</v>
@@ -15796,7 +15796,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N164" s="2" t="n">
-        <v>45831.44249482949</v>
+        <v>45831.44249482639</v>
       </c>
       <c r="O164" t="n">
         <v>377.26</v>
@@ -15891,7 +15891,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N165" s="2" t="n">
-        <v>45831.44249482949</v>
+        <v>45831.44249482639</v>
       </c>
       <c r="O165" t="n">
         <v>0.725</v>
@@ -15982,7 +15982,7 @@
         <v>11.4948091506958</v>
       </c>
       <c r="N166" s="2" t="n">
-        <v>45831.44249482949</v>
+        <v>45831.44249482639</v>
       </c>
       <c r="O166" t="n">
         <v>90.25</v>
@@ -16077,7 +16077,7 @@
         <v>13.05655670166016</v>
       </c>
       <c r="N167" s="2" t="n">
-        <v>45831.44249482949</v>
+        <v>45831.44249482639</v>
       </c>
       <c r="O167" t="n">
         <v>43.76</v>
@@ -16172,7 +16172,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N168" s="2" t="n">
-        <v>45831.44249482949</v>
+        <v>45831.44249482639</v>
       </c>
       <c r="O168" t="n">
         <v>26.05</v>
@@ -16267,7 +16267,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N169" s="2" t="n">
-        <v>45831.44249482949</v>
+        <v>45831.44249482639</v>
       </c>
       <c r="O169" t="n">
         <v>14.18</v>
@@ -16308,6 +16308,756 @@
         <v>0.540931224822998</v>
       </c>
       <c r="AA169" t="n">
+        <v>14.27337956428528</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F170" t="n">
+        <v>1</v>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H170" t="n">
+        <v>1</v>
+      </c>
+      <c r="I170" t="n">
+        <v>1</v>
+      </c>
+      <c r="J170" t="n">
+        <v>1</v>
+      </c>
+      <c r="K170" t="n">
+        <v>100</v>
+      </c>
+      <c r="L170" t="n">
+        <v>100</v>
+      </c>
+      <c r="M170" t="n">
+        <v>100</v>
+      </c>
+      <c r="N170" s="2" t="n">
+        <v>45831.47715674101</v>
+      </c>
+      <c r="O170" t="n">
+        <v>1</v>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q170" t="n">
+        <v>1</v>
+      </c>
+      <c r="R170" t="n">
+        <v>1</v>
+      </c>
+      <c r="S170" t="n">
+        <v>0</v>
+      </c>
+      <c r="T170" t="n">
+        <v>16.03601332880703</v>
+      </c>
+      <c r="U170" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V170" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W170" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X170" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y170" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z170" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA170" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>DE000A0XYG76</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>DR0.DE</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>DT.ROHSTOFF AG NA O.N.</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F171" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H171" t="n">
+        <v>1</v>
+      </c>
+      <c r="I171" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="J171" t="n">
+        <v>39</v>
+      </c>
+      <c r="K171" t="n">
+        <v>11</v>
+      </c>
+      <c r="L171" t="n">
+        <v>0.4329348504543304</v>
+      </c>
+      <c r="M171" t="n">
+        <v>12.02781891822815</v>
+      </c>
+      <c r="N171" s="2" t="n">
+        <v>45831.47715674101</v>
+      </c>
+      <c r="O171" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q171" t="n">
+        <v>1</v>
+      </c>
+      <c r="R171" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="S171" t="n">
+        <v>1489.8</v>
+      </c>
+      <c r="T171" t="n">
+        <v>1489.8</v>
+      </c>
+      <c r="U171" t="n">
+        <v>34.92</v>
+      </c>
+      <c r="V171" t="n">
+        <v>0.01326259946949593</v>
+      </c>
+      <c r="W171" t="n">
+        <v>0.01326259946949593</v>
+      </c>
+      <c r="X171" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y171" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z171" t="n">
+        <v>0.4742938280105591</v>
+      </c>
+      <c r="AA171" t="n">
+        <v>12.61593472957611</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F172" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H172" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I172" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J172" t="n">
+        <v>3</v>
+      </c>
+      <c r="K172" t="n">
+        <v>10</v>
+      </c>
+      <c r="L172" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M172" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N172" s="2" t="n">
+        <v>45831.47715674101</v>
+      </c>
+      <c r="O172" t="n">
+        <v>375.256</v>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q172" t="n">
+        <v>0.85715</v>
+      </c>
+      <c r="R172" t="n">
+        <v>437.7950183748468</v>
+      </c>
+      <c r="S172" t="n">
+        <v>1125.768</v>
+      </c>
+      <c r="T172" t="n">
+        <v>1313.385055124541</v>
+      </c>
+      <c r="U172" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V172" t="n">
+        <v>0.02064373643469875</v>
+      </c>
+      <c r="W172" t="n">
+        <v>0.01649995739626609</v>
+      </c>
+      <c r="X172" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y172" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z172" t="n">
+        <v>0.5007368326187134</v>
+      </c>
+      <c r="AA172" t="n">
+        <v>12.07941150665283</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F173" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H173" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I173" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J173" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K173" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L173" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M173" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N173" s="2" t="n">
+        <v>45831.47715674101</v>
+      </c>
+      <c r="O173" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q173" t="n">
+        <v>1.79724</v>
+      </c>
+      <c r="R173" t="n">
+        <v>0.4033963187999377</v>
+      </c>
+      <c r="S173" t="n">
+        <v>2656.4</v>
+      </c>
+      <c r="T173" t="n">
+        <v>1478.044112082972</v>
+      </c>
+      <c r="U173" t="n">
+        <v>0.3678646934460888</v>
+      </c>
+      <c r="V173" t="n">
+        <v>0</v>
+      </c>
+      <c r="W173" t="n">
+        <v>-0.01261378558233728</v>
+      </c>
+      <c r="X173" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y173" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z173" t="n">
+        <v>0.5391064286231995</v>
+      </c>
+      <c r="AA173" t="n">
+        <v>12.27176785469055</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>NO0012851874</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>DOFG.OL</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>DOF GROUP ASA  NK 2,50</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F174" t="n">
+        <v>90.45</v>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="H174" t="n">
+        <v>11.53806</v>
+      </c>
+      <c r="I174" t="n">
+        <v>7.839272806693673</v>
+      </c>
+      <c r="J174" t="n">
+        <v>160</v>
+      </c>
+      <c r="K174" t="n">
+        <v>9</v>
+      </c>
+      <c r="L174" t="n">
+        <v>0.5388140678405762</v>
+      </c>
+      <c r="M174" t="n">
+        <v>11.4948091506958</v>
+      </c>
+      <c r="N174" s="2" t="n">
+        <v>45831.47715674101</v>
+      </c>
+      <c r="O174" t="n">
+        <v>90.09999999999999</v>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="Q174" t="n">
+        <v>11.66341</v>
+      </c>
+      <c r="R174" t="n">
+        <v>7.725013525204035</v>
+      </c>
+      <c r="S174" t="n">
+        <v>14416</v>
+      </c>
+      <c r="T174" t="n">
+        <v>1236.002164032646</v>
+      </c>
+      <c r="U174" t="n">
+        <v>7.055345526024306</v>
+      </c>
+      <c r="V174" t="n">
+        <v>-0.003869541182974112</v>
+      </c>
+      <c r="W174" t="n">
+        <v>-0.01457523986052334</v>
+      </c>
+      <c r="X174" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y174" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z174" t="n">
+        <v>0.5161983370780945</v>
+      </c>
+      <c r="AA174" t="n">
+        <v>10.16883182525635</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F175" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H175" t="n">
+        <v>1</v>
+      </c>
+      <c r="I175" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="J175" t="n">
+        <v>34</v>
+      </c>
+      <c r="K175" t="n">
+        <v>9</v>
+      </c>
+      <c r="L175" t="n">
+        <v>0.6616257429122925</v>
+      </c>
+      <c r="M175" t="n">
+        <v>13.05655670166016</v>
+      </c>
+      <c r="N175" s="2" t="n">
+        <v>45831.47715674101</v>
+      </c>
+      <c r="O175" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q175" t="n">
+        <v>1</v>
+      </c>
+      <c r="R175" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="S175" t="n">
+        <v>1492.6</v>
+      </c>
+      <c r="T175" t="n">
+        <v>1492.6</v>
+      </c>
+      <c r="U175" t="n">
+        <v>39.51</v>
+      </c>
+      <c r="V175" t="n">
+        <v>0.02570093457943923</v>
+      </c>
+      <c r="W175" t="n">
+        <v>0.02570093457943923</v>
+      </c>
+      <c r="X175" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y175" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z175" t="n">
+        <v>0.6566609740257263</v>
+      </c>
+      <c r="AA175" t="n">
+        <v>12.99397349357605</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F176" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H176" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I176" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J176" t="n">
+        <v>537</v>
+      </c>
+      <c r="K176" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L176" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M176" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N176" s="2" t="n">
+        <v>45831.47715674101</v>
+      </c>
+      <c r="O176" t="n">
+        <v>26.05</v>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q176" t="n">
+        <v>9.0006</v>
+      </c>
+      <c r="R176" t="n">
+        <v>2.894251494344821</v>
+      </c>
+      <c r="S176" t="n">
+        <v>13988.85</v>
+      </c>
+      <c r="T176" t="n">
+        <v>1554.213052463169</v>
+      </c>
+      <c r="U176" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V176" t="n">
+        <v>0.03373015873015883</v>
+      </c>
+      <c r="W176" t="n">
+        <v>0.0383173176461955</v>
+      </c>
+      <c r="X176" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y176" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z176" t="n">
+        <v>0.5859425067901611</v>
+      </c>
+      <c r="AA176" t="n">
+        <v>12.04357481002808</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F177" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H177" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I177" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J177" t="n">
+        <v>121</v>
+      </c>
+      <c r="K177" t="n">
+        <v>12</v>
+      </c>
+      <c r="L177" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M177" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N177" s="2" t="n">
+        <v>45831.47715674101</v>
+      </c>
+      <c r="O177" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q177" t="n">
+        <v>1.147052</v>
+      </c>
+      <c r="R177" t="n">
+        <v>12.36212482084509</v>
+      </c>
+      <c r="S177" t="n">
+        <v>1715.78</v>
+      </c>
+      <c r="T177" t="n">
+        <v>1495.817103322256</v>
+      </c>
+      <c r="U177" t="n">
+        <v>11.13229249335264</v>
+      </c>
+      <c r="V177" t="n">
+        <v>0</v>
+      </c>
+      <c r="W177" t="n">
+        <v>0.002875894030959447</v>
+      </c>
+      <c r="X177" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y177" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z177" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="AA177" t="n">
         <v>14.27337956428528</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA177"/>
+  <dimension ref="A1:AA185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16364,7 +16364,7 @@
         <v>100</v>
       </c>
       <c r="N170" s="2" t="n">
-        <v>45831.47715674101</v>
+        <v>45831.47715673611</v>
       </c>
       <c r="O170" t="n">
         <v>1</v>
@@ -16455,7 +16455,7 @@
         <v>12.02781891822815</v>
       </c>
       <c r="N171" s="2" t="n">
-        <v>45831.47715674101</v>
+        <v>45831.47715673611</v>
       </c>
       <c r="O171" t="n">
         <v>38.2</v>
@@ -16546,7 +16546,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N172" s="2" t="n">
-        <v>45831.47715674101</v>
+        <v>45831.47715673611</v>
       </c>
       <c r="O172" t="n">
         <v>375.256</v>
@@ -16641,7 +16641,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N173" s="2" t="n">
-        <v>45831.47715674101</v>
+        <v>45831.47715673611</v>
       </c>
       <c r="O173" t="n">
         <v>0.725</v>
@@ -16732,7 +16732,7 @@
         <v>11.4948091506958</v>
       </c>
       <c r="N174" s="2" t="n">
-        <v>45831.47715674101</v>
+        <v>45831.47715673611</v>
       </c>
       <c r="O174" t="n">
         <v>90.09999999999999</v>
@@ -16827,7 +16827,7 @@
         <v>13.05655670166016</v>
       </c>
       <c r="N175" s="2" t="n">
-        <v>45831.47715674101</v>
+        <v>45831.47715673611</v>
       </c>
       <c r="O175" t="n">
         <v>43.9</v>
@@ -16922,7 +16922,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N176" s="2" t="n">
-        <v>45831.47715674101</v>
+        <v>45831.47715673611</v>
       </c>
       <c r="O176" t="n">
         <v>26.05</v>
@@ -17017,7 +17017,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N177" s="2" t="n">
-        <v>45831.47715674101</v>
+        <v>45831.47715673611</v>
       </c>
       <c r="O177" t="n">
         <v>14.18</v>
@@ -17058,6 +17058,756 @@
         <v>0.540931224822998</v>
       </c>
       <c r="AA177" t="n">
+        <v>14.27337956428528</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F178" t="n">
+        <v>1</v>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H178" t="n">
+        <v>1</v>
+      </c>
+      <c r="I178" t="n">
+        <v>1</v>
+      </c>
+      <c r="J178" t="n">
+        <v>1</v>
+      </c>
+      <c r="K178" t="n">
+        <v>100</v>
+      </c>
+      <c r="L178" t="n">
+        <v>100</v>
+      </c>
+      <c r="M178" t="n">
+        <v>100</v>
+      </c>
+      <c r="N178" s="2" t="n">
+        <v>45831.54217408504</v>
+      </c>
+      <c r="O178" t="n">
+        <v>1</v>
+      </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q178" t="n">
+        <v>1</v>
+      </c>
+      <c r="R178" t="n">
+        <v>1</v>
+      </c>
+      <c r="S178" t="n">
+        <v>0</v>
+      </c>
+      <c r="T178" t="n">
+        <v>16.03601332880703</v>
+      </c>
+      <c r="U178" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V178" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W178" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X178" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y178" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z178" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA178" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>DE000A0XYG76</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>DR0.DE</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>DT.ROHSTOFF AG NA O.N.</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F179" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H179" t="n">
+        <v>1</v>
+      </c>
+      <c r="I179" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="J179" t="n">
+        <v>39</v>
+      </c>
+      <c r="K179" t="n">
+        <v>11</v>
+      </c>
+      <c r="L179" t="n">
+        <v>0.4329348504543304</v>
+      </c>
+      <c r="M179" t="n">
+        <v>12.02781891822815</v>
+      </c>
+      <c r="N179" s="2" t="n">
+        <v>45831.54217408504</v>
+      </c>
+      <c r="O179" t="n">
+        <v>38</v>
+      </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q179" t="n">
+        <v>1</v>
+      </c>
+      <c r="R179" t="n">
+        <v>38</v>
+      </c>
+      <c r="S179" t="n">
+        <v>1482</v>
+      </c>
+      <c r="T179" t="n">
+        <v>1482</v>
+      </c>
+      <c r="U179" t="n">
+        <v>34.92</v>
+      </c>
+      <c r="V179" t="n">
+        <v>0.007957559681697646</v>
+      </c>
+      <c r="W179" t="n">
+        <v>0.007957559681697646</v>
+      </c>
+      <c r="X179" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y179" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z179" t="n">
+        <v>0.4742938280105591</v>
+      </c>
+      <c r="AA179" t="n">
+        <v>12.61593472957611</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F180" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H180" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I180" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J180" t="n">
+        <v>3</v>
+      </c>
+      <c r="K180" t="n">
+        <v>10</v>
+      </c>
+      <c r="L180" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M180" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N180" s="2" t="n">
+        <v>45831.54217408504</v>
+      </c>
+      <c r="O180" t="n">
+        <v>379.4</v>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q180" t="n">
+        <v>0.8562</v>
+      </c>
+      <c r="R180" t="n">
+        <v>443.1207661761271</v>
+      </c>
+      <c r="S180" t="n">
+        <v>1138.2</v>
+      </c>
+      <c r="T180" t="n">
+        <v>1329.362298528381</v>
+      </c>
+      <c r="U180" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V180" t="n">
+        <v>0.03191483574766218</v>
+      </c>
+      <c r="W180" t="n">
+        <v>0.02886561297910162</v>
+      </c>
+      <c r="X180" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y180" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z180" t="n">
+        <v>0.5007368326187134</v>
+      </c>
+      <c r="AA180" t="n">
+        <v>12.07941150665283</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F181" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H181" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I181" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J181" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K181" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L181" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M181" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N181" s="2" t="n">
+        <v>45831.54217408504</v>
+      </c>
+      <c r="O181" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q181" t="n">
+        <v>1.79425</v>
+      </c>
+      <c r="R181" t="n">
+        <v>0.4040685523199108</v>
+      </c>
+      <c r="S181" t="n">
+        <v>2656.4</v>
+      </c>
+      <c r="T181" t="n">
+        <v>1480.507175700153</v>
+      </c>
+      <c r="U181" t="n">
+        <v>0.3678646934460888</v>
+      </c>
+      <c r="V181" t="n">
+        <v>0</v>
+      </c>
+      <c r="W181" t="n">
+        <v>-0.01096837118573213</v>
+      </c>
+      <c r="X181" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y181" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z181" t="n">
+        <v>0.5391064286231995</v>
+      </c>
+      <c r="AA181" t="n">
+        <v>12.27176785469055</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>NO0012851874</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>DOFG.OL</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr"/>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>DOF GROUP ASA  NK 2,50</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F182" t="n">
+        <v>90.45</v>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="H182" t="n">
+        <v>11.53806</v>
+      </c>
+      <c r="I182" t="n">
+        <v>7.839272806693673</v>
+      </c>
+      <c r="J182" t="n">
+        <v>160</v>
+      </c>
+      <c r="K182" t="n">
+        <v>9</v>
+      </c>
+      <c r="L182" t="n">
+        <v>0.5388140678405762</v>
+      </c>
+      <c r="M182" t="n">
+        <v>11.4948091506958</v>
+      </c>
+      <c r="N182" s="2" t="n">
+        <v>45831.54217408504</v>
+      </c>
+      <c r="O182" t="n">
+        <v>90.05</v>
+      </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="Q182" t="n">
+        <v>11.65452</v>
+      </c>
+      <c r="R182" t="n">
+        <v>7.726615939566795</v>
+      </c>
+      <c r="S182" t="n">
+        <v>14408</v>
+      </c>
+      <c r="T182" t="n">
+        <v>1236.258550330687</v>
+      </c>
+      <c r="U182" t="n">
+        <v>7.055345526024306</v>
+      </c>
+      <c r="V182" t="n">
+        <v>-0.004422332780541827</v>
+      </c>
+      <c r="W182" t="n">
+        <v>-0.01437083131367545</v>
+      </c>
+      <c r="X182" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y182" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z182" t="n">
+        <v>0.5161983370780945</v>
+      </c>
+      <c r="AA182" t="n">
+        <v>10.16883182525635</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F183" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H183" t="n">
+        <v>1</v>
+      </c>
+      <c r="I183" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="J183" t="n">
+        <v>34</v>
+      </c>
+      <c r="K183" t="n">
+        <v>9</v>
+      </c>
+      <c r="L183" t="n">
+        <v>0.6616257429122925</v>
+      </c>
+      <c r="M183" t="n">
+        <v>13.05655670166016</v>
+      </c>
+      <c r="N183" s="2" t="n">
+        <v>45831.54217408504</v>
+      </c>
+      <c r="O183" t="n">
+        <v>43.66</v>
+      </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q183" t="n">
+        <v>1</v>
+      </c>
+      <c r="R183" t="n">
+        <v>43.66</v>
+      </c>
+      <c r="S183" t="n">
+        <v>1484.44</v>
+      </c>
+      <c r="T183" t="n">
+        <v>1484.44</v>
+      </c>
+      <c r="U183" t="n">
+        <v>39.51</v>
+      </c>
+      <c r="V183" t="n">
+        <v>0.02009345794392514</v>
+      </c>
+      <c r="W183" t="n">
+        <v>0.02009345794392514</v>
+      </c>
+      <c r="X183" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y183" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z183" t="n">
+        <v>0.6566609740257263</v>
+      </c>
+      <c r="AA183" t="n">
+        <v>12.99397349357605</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F184" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H184" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I184" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J184" t="n">
+        <v>537</v>
+      </c>
+      <c r="K184" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L184" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M184" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N184" s="2" t="n">
+        <v>45831.54217408504</v>
+      </c>
+      <c r="O184" t="n">
+        <v>26.05</v>
+      </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q184" t="n">
+        <v>9.00014</v>
+      </c>
+      <c r="R184" t="n">
+        <v>2.89439942045346</v>
+      </c>
+      <c r="S184" t="n">
+        <v>13988.85</v>
+      </c>
+      <c r="T184" t="n">
+        <v>1554.292488783508</v>
+      </c>
+      <c r="U184" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V184" t="n">
+        <v>0.03373015873015883</v>
+      </c>
+      <c r="W184" t="n">
+        <v>0.03837038637247292</v>
+      </c>
+      <c r="X184" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y184" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z184" t="n">
+        <v>0.5859425067901611</v>
+      </c>
+      <c r="AA184" t="n">
+        <v>12.04357481002808</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F185" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H185" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I185" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J185" t="n">
+        <v>121</v>
+      </c>
+      <c r="K185" t="n">
+        <v>12</v>
+      </c>
+      <c r="L185" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M185" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N185" s="2" t="n">
+        <v>45831.54217408504</v>
+      </c>
+      <c r="O185" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q185" t="n">
+        <v>1.147052</v>
+      </c>
+      <c r="R185" t="n">
+        <v>12.36212482084509</v>
+      </c>
+      <c r="S185" t="n">
+        <v>1715.78</v>
+      </c>
+      <c r="T185" t="n">
+        <v>1495.817103322256</v>
+      </c>
+      <c r="U185" t="n">
+        <v>11.13229249335264</v>
+      </c>
+      <c r="V185" t="n">
+        <v>0</v>
+      </c>
+      <c r="W185" t="n">
+        <v>0.002875894030959447</v>
+      </c>
+      <c r="X185" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y185" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z185" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="AA185" t="n">
         <v>14.27337956428528</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA185"/>
+  <dimension ref="A1:AA193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17114,7 +17114,7 @@
         <v>100</v>
       </c>
       <c r="N178" s="2" t="n">
-        <v>45831.54217408504</v>
+        <v>45831.54217408565</v>
       </c>
       <c r="O178" t="n">
         <v>1</v>
@@ -17205,7 +17205,7 @@
         <v>12.02781891822815</v>
       </c>
       <c r="N179" s="2" t="n">
-        <v>45831.54217408504</v>
+        <v>45831.54217408565</v>
       </c>
       <c r="O179" t="n">
         <v>38</v>
@@ -17296,7 +17296,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N180" s="2" t="n">
-        <v>45831.54217408504</v>
+        <v>45831.54217408565</v>
       </c>
       <c r="O180" t="n">
         <v>379.4</v>
@@ -17391,7 +17391,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N181" s="2" t="n">
-        <v>45831.54217408504</v>
+        <v>45831.54217408565</v>
       </c>
       <c r="O181" t="n">
         <v>0.725</v>
@@ -17482,7 +17482,7 @@
         <v>11.4948091506958</v>
       </c>
       <c r="N182" s="2" t="n">
-        <v>45831.54217408504</v>
+        <v>45831.54217408565</v>
       </c>
       <c r="O182" t="n">
         <v>90.05</v>
@@ -17577,7 +17577,7 @@
         <v>13.05655670166016</v>
       </c>
       <c r="N183" s="2" t="n">
-        <v>45831.54217408504</v>
+        <v>45831.54217408565</v>
       </c>
       <c r="O183" t="n">
         <v>43.66</v>
@@ -17672,7 +17672,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N184" s="2" t="n">
-        <v>45831.54217408504</v>
+        <v>45831.54217408565</v>
       </c>
       <c r="O184" t="n">
         <v>26.05</v>
@@ -17767,7 +17767,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N185" s="2" t="n">
-        <v>45831.54217408504</v>
+        <v>45831.54217408565</v>
       </c>
       <c r="O185" t="n">
         <v>14.18</v>
@@ -17808,6 +17808,756 @@
         <v>0.540931224822998</v>
       </c>
       <c r="AA185" t="n">
+        <v>14.27337956428528</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F186" t="n">
+        <v>1</v>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H186" t="n">
+        <v>1</v>
+      </c>
+      <c r="I186" t="n">
+        <v>1</v>
+      </c>
+      <c r="J186" t="n">
+        <v>1</v>
+      </c>
+      <c r="K186" t="n">
+        <v>100</v>
+      </c>
+      <c r="L186" t="n">
+        <v>100</v>
+      </c>
+      <c r="M186" t="n">
+        <v>100</v>
+      </c>
+      <c r="N186" s="2" t="n">
+        <v>45831.57300043706</v>
+      </c>
+      <c r="O186" t="n">
+        <v>1</v>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q186" t="n">
+        <v>1</v>
+      </c>
+      <c r="R186" t="n">
+        <v>1</v>
+      </c>
+      <c r="S186" t="n">
+        <v>0</v>
+      </c>
+      <c r="T186" t="n">
+        <v>16.03601332880703</v>
+      </c>
+      <c r="U186" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V186" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W186" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X186" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y186" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z186" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA186" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>DE000A0XYG76</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>DR0.DE</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>DT.ROHSTOFF AG NA O.N.</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F187" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H187" t="n">
+        <v>1</v>
+      </c>
+      <c r="I187" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="J187" t="n">
+        <v>39</v>
+      </c>
+      <c r="K187" t="n">
+        <v>11</v>
+      </c>
+      <c r="L187" t="n">
+        <v>0.4329348504543304</v>
+      </c>
+      <c r="M187" t="n">
+        <v>12.02781891822815</v>
+      </c>
+      <c r="N187" s="2" t="n">
+        <v>45831.57300043706</v>
+      </c>
+      <c r="O187" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q187" t="n">
+        <v>1</v>
+      </c>
+      <c r="R187" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="S187" t="n">
+        <v>1489.8</v>
+      </c>
+      <c r="T187" t="n">
+        <v>1489.8</v>
+      </c>
+      <c r="U187" t="n">
+        <v>34.92</v>
+      </c>
+      <c r="V187" t="n">
+        <v>0.01326259946949593</v>
+      </c>
+      <c r="W187" t="n">
+        <v>0.01326259946949593</v>
+      </c>
+      <c r="X187" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y187" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z187" t="n">
+        <v>0.4742938280105591</v>
+      </c>
+      <c r="AA187" t="n">
+        <v>12.61593472957611</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F188" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H188" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I188" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J188" t="n">
+        <v>3</v>
+      </c>
+      <c r="K188" t="n">
+        <v>10</v>
+      </c>
+      <c r="L188" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M188" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N188" s="2" t="n">
+        <v>45831.57300043706</v>
+      </c>
+      <c r="O188" t="n">
+        <v>374</v>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q188" t="n">
+        <v>0.85567</v>
+      </c>
+      <c r="R188" t="n">
+        <v>437.0843900101675</v>
+      </c>
+      <c r="S188" t="n">
+        <v>1122</v>
+      </c>
+      <c r="T188" t="n">
+        <v>1311.253170030502</v>
+      </c>
+      <c r="U188" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V188" t="n">
+        <v>0.01722759243443783</v>
+      </c>
+      <c r="W188" t="n">
+        <v>0.01484997584758907</v>
+      </c>
+      <c r="X188" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y188" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z188" t="n">
+        <v>0.5007368326187134</v>
+      </c>
+      <c r="AA188" t="n">
+        <v>12.07941150665283</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F189" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H189" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I189" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J189" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K189" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L189" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M189" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N189" s="2" t="n">
+        <v>45831.57300043706</v>
+      </c>
+      <c r="O189" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q189" t="n">
+        <v>1.79561</v>
+      </c>
+      <c r="R189" t="n">
+        <v>0.4037625096763774</v>
+      </c>
+      <c r="S189" t="n">
+        <v>2656.4</v>
+      </c>
+      <c r="T189" t="n">
+        <v>1479.385835454247</v>
+      </c>
+      <c r="U189" t="n">
+        <v>0.3678646934460888</v>
+      </c>
+      <c r="V189" t="n">
+        <v>0</v>
+      </c>
+      <c r="W189" t="n">
+        <v>-0.01171746648771166</v>
+      </c>
+      <c r="X189" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y189" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z189" t="n">
+        <v>0.5391064286231995</v>
+      </c>
+      <c r="AA189" t="n">
+        <v>12.27176785469055</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>NO0012851874</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>DOFG.OL</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>DOF GROUP ASA  NK 2,50</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F190" t="n">
+        <v>90.45</v>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="H190" t="n">
+        <v>11.53806</v>
+      </c>
+      <c r="I190" t="n">
+        <v>7.839272806693673</v>
+      </c>
+      <c r="J190" t="n">
+        <v>160</v>
+      </c>
+      <c r="K190" t="n">
+        <v>9</v>
+      </c>
+      <c r="L190" t="n">
+        <v>0.5388140678405762</v>
+      </c>
+      <c r="M190" t="n">
+        <v>11.4948091506958</v>
+      </c>
+      <c r="N190" s="2" t="n">
+        <v>45831.57300043706</v>
+      </c>
+      <c r="O190" t="n">
+        <v>90.05</v>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="Q190" t="n">
+        <v>11.64535</v>
+      </c>
+      <c r="R190" t="n">
+        <v>7.732700176465284</v>
+      </c>
+      <c r="S190" t="n">
+        <v>14408</v>
+      </c>
+      <c r="T190" t="n">
+        <v>1237.232028234445</v>
+      </c>
+      <c r="U190" t="n">
+        <v>7.055345526024306</v>
+      </c>
+      <c r="V190" t="n">
+        <v>-0.004422332780541827</v>
+      </c>
+      <c r="W190" t="n">
+        <v>-0.01359470870019863</v>
+      </c>
+      <c r="X190" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y190" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z190" t="n">
+        <v>0.5161983370780945</v>
+      </c>
+      <c r="AA190" t="n">
+        <v>10.16883182525635</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F191" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H191" t="n">
+        <v>1</v>
+      </c>
+      <c r="I191" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="J191" t="n">
+        <v>34</v>
+      </c>
+      <c r="K191" t="n">
+        <v>9</v>
+      </c>
+      <c r="L191" t="n">
+        <v>0.6616257429122925</v>
+      </c>
+      <c r="M191" t="n">
+        <v>13.05655670166016</v>
+      </c>
+      <c r="N191" s="2" t="n">
+        <v>45831.57300043706</v>
+      </c>
+      <c r="O191" t="n">
+        <v>43.76</v>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q191" t="n">
+        <v>1</v>
+      </c>
+      <c r="R191" t="n">
+        <v>43.76</v>
+      </c>
+      <c r="S191" t="n">
+        <v>1487.84</v>
+      </c>
+      <c r="T191" t="n">
+        <v>1487.84</v>
+      </c>
+      <c r="U191" t="n">
+        <v>39.51</v>
+      </c>
+      <c r="V191" t="n">
+        <v>0.02242990654205612</v>
+      </c>
+      <c r="W191" t="n">
+        <v>0.02242990654205612</v>
+      </c>
+      <c r="X191" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y191" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z191" t="n">
+        <v>0.6566609740257263</v>
+      </c>
+      <c r="AA191" t="n">
+        <v>12.99397349357605</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F192" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H192" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I192" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J192" t="n">
+        <v>537</v>
+      </c>
+      <c r="K192" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L192" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M192" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N192" s="2" t="n">
+        <v>45831.57300043706</v>
+      </c>
+      <c r="O192" t="n">
+        <v>26.05</v>
+      </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q192" t="n">
+        <v>9.01634</v>
+      </c>
+      <c r="R192" t="n">
+        <v>2.889198943251918</v>
+      </c>
+      <c r="S192" t="n">
+        <v>13988.85</v>
+      </c>
+      <c r="T192" t="n">
+        <v>1551.49983252628</v>
+      </c>
+      <c r="U192" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V192" t="n">
+        <v>0.03373015873015883</v>
+      </c>
+      <c r="W192" t="n">
+        <v>0.03650470692169439</v>
+      </c>
+      <c r="X192" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y192" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z192" t="n">
+        <v>0.5859425067901611</v>
+      </c>
+      <c r="AA192" t="n">
+        <v>12.04357481002808</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F193" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H193" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I193" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J193" t="n">
+        <v>121</v>
+      </c>
+      <c r="K193" t="n">
+        <v>12</v>
+      </c>
+      <c r="L193" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M193" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N193" s="2" t="n">
+        <v>45831.57300043706</v>
+      </c>
+      <c r="O193" t="n">
+        <v>14.58</v>
+      </c>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q193" t="n">
+        <v>1.1491611</v>
+      </c>
+      <c r="R193" t="n">
+        <v>12.68751613677142</v>
+      </c>
+      <c r="S193" t="n">
+        <v>1764.18</v>
+      </c>
+      <c r="T193" t="n">
+        <v>1535.189452549342</v>
+      </c>
+      <c r="U193" t="n">
+        <v>11.41876452309428</v>
+      </c>
+      <c r="V193" t="n">
+        <v>0.02820874471086032</v>
+      </c>
+      <c r="W193" t="n">
+        <v>0.02927322552524103</v>
+      </c>
+      <c r="X193" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y193" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z193" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="AA193" t="n">
         <v>14.27337956428528</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA193"/>
+  <dimension ref="A1:AA201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17864,7 +17864,7 @@
         <v>100</v>
       </c>
       <c r="N186" s="2" t="n">
-        <v>45831.57300043706</v>
+        <v>45831.57300043981</v>
       </c>
       <c r="O186" t="n">
         <v>1</v>
@@ -17955,7 +17955,7 @@
         <v>12.02781891822815</v>
       </c>
       <c r="N187" s="2" t="n">
-        <v>45831.57300043706</v>
+        <v>45831.57300043981</v>
       </c>
       <c r="O187" t="n">
         <v>38.2</v>
@@ -18046,7 +18046,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N188" s="2" t="n">
-        <v>45831.57300043706</v>
+        <v>45831.57300043981</v>
       </c>
       <c r="O188" t="n">
         <v>374</v>
@@ -18141,7 +18141,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N189" s="2" t="n">
-        <v>45831.57300043706</v>
+        <v>45831.57300043981</v>
       </c>
       <c r="O189" t="n">
         <v>0.725</v>
@@ -18232,7 +18232,7 @@
         <v>11.4948091506958</v>
       </c>
       <c r="N190" s="2" t="n">
-        <v>45831.57300043706</v>
+        <v>45831.57300043981</v>
       </c>
       <c r="O190" t="n">
         <v>90.05</v>
@@ -18327,7 +18327,7 @@
         <v>13.05655670166016</v>
       </c>
       <c r="N191" s="2" t="n">
-        <v>45831.57300043706</v>
+        <v>45831.57300043981</v>
       </c>
       <c r="O191" t="n">
         <v>43.76</v>
@@ -18422,7 +18422,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N192" s="2" t="n">
-        <v>45831.57300043706</v>
+        <v>45831.57300043981</v>
       </c>
       <c r="O192" t="n">
         <v>26.05</v>
@@ -18517,7 +18517,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N193" s="2" t="n">
-        <v>45831.57300043706</v>
+        <v>45831.57300043981</v>
       </c>
       <c r="O193" t="n">
         <v>14.58</v>
@@ -18558,6 +18558,756 @@
         <v>0.540931224822998</v>
       </c>
       <c r="AA193" t="n">
+        <v>14.27337956428528</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F194" t="n">
+        <v>1</v>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H194" t="n">
+        <v>1</v>
+      </c>
+      <c r="I194" t="n">
+        <v>1</v>
+      </c>
+      <c r="J194" t="n">
+        <v>1</v>
+      </c>
+      <c r="K194" t="n">
+        <v>100</v>
+      </c>
+      <c r="L194" t="n">
+        <v>100</v>
+      </c>
+      <c r="M194" t="n">
+        <v>100</v>
+      </c>
+      <c r="N194" s="2" t="n">
+        <v>45831.60812513205</v>
+      </c>
+      <c r="O194" t="n">
+        <v>1</v>
+      </c>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q194" t="n">
+        <v>1</v>
+      </c>
+      <c r="R194" t="n">
+        <v>1</v>
+      </c>
+      <c r="S194" t="n">
+        <v>0</v>
+      </c>
+      <c r="T194" t="n">
+        <v>16.03601332880703</v>
+      </c>
+      <c r="U194" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V194" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W194" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X194" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y194" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z194" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA194" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>DE000A0XYG76</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>DR0.DE</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>DT.ROHSTOFF AG NA O.N.</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F195" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H195" t="n">
+        <v>1</v>
+      </c>
+      <c r="I195" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="J195" t="n">
+        <v>39</v>
+      </c>
+      <c r="K195" t="n">
+        <v>11</v>
+      </c>
+      <c r="L195" t="n">
+        <v>0.4329348504543304</v>
+      </c>
+      <c r="M195" t="n">
+        <v>12.02781891822815</v>
+      </c>
+      <c r="N195" s="2" t="n">
+        <v>45831.60812513205</v>
+      </c>
+      <c r="O195" t="n">
+        <v>38.25</v>
+      </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q195" t="n">
+        <v>1</v>
+      </c>
+      <c r="R195" t="n">
+        <v>38.25</v>
+      </c>
+      <c r="S195" t="n">
+        <v>1491.75</v>
+      </c>
+      <c r="T195" t="n">
+        <v>1491.75</v>
+      </c>
+      <c r="U195" t="n">
+        <v>34.92</v>
+      </c>
+      <c r="V195" t="n">
+        <v>0.01458885941644561</v>
+      </c>
+      <c r="W195" t="n">
+        <v>0.01458885941644561</v>
+      </c>
+      <c r="X195" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y195" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z195" t="n">
+        <v>0.4742938280105591</v>
+      </c>
+      <c r="AA195" t="n">
+        <v>12.61593472957611</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr"/>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F196" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H196" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I196" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J196" t="n">
+        <v>3</v>
+      </c>
+      <c r="K196" t="n">
+        <v>10</v>
+      </c>
+      <c r="L196" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M196" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N196" s="2" t="n">
+        <v>45831.60812513205</v>
+      </c>
+      <c r="O196" t="n">
+        <v>379.4</v>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q196" t="n">
+        <v>0.85567</v>
+      </c>
+      <c r="R196" t="n">
+        <v>443.3952341440041</v>
+      </c>
+      <c r="S196" t="n">
+        <v>1138.2</v>
+      </c>
+      <c r="T196" t="n">
+        <v>1330.185702432012</v>
+      </c>
+      <c r="U196" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V196" t="n">
+        <v>0.03191483574766218</v>
+      </c>
+      <c r="W196" t="n">
+        <v>0.02950288993736705</v>
+      </c>
+      <c r="X196" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y196" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z196" t="n">
+        <v>0.5007368326187134</v>
+      </c>
+      <c r="AA196" t="n">
+        <v>12.07941150665283</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F197" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H197" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I197" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J197" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K197" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L197" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M197" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N197" s="2" t="n">
+        <v>45831.60812513205</v>
+      </c>
+      <c r="O197" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q197" t="n">
+        <v>1.79435</v>
+      </c>
+      <c r="R197" t="n">
+        <v>0.404046033382562</v>
+      </c>
+      <c r="S197" t="n">
+        <v>2656.4</v>
+      </c>
+      <c r="T197" t="n">
+        <v>1480.424666313707</v>
+      </c>
+      <c r="U197" t="n">
+        <v>0.3678646934460888</v>
+      </c>
+      <c r="V197" t="n">
+        <v>0</v>
+      </c>
+      <c r="W197" t="n">
+        <v>-0.0110234904004235</v>
+      </c>
+      <c r="X197" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y197" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z197" t="n">
+        <v>0.5391064286231995</v>
+      </c>
+      <c r="AA197" t="n">
+        <v>12.27176785469055</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>NO0012851874</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>DOFG.OL</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr"/>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>DOF GROUP ASA  NK 2,50</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F198" t="n">
+        <v>90.45</v>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="H198" t="n">
+        <v>11.53806</v>
+      </c>
+      <c r="I198" t="n">
+        <v>7.839272806693673</v>
+      </c>
+      <c r="J198" t="n">
+        <v>160</v>
+      </c>
+      <c r="K198" t="n">
+        <v>9</v>
+      </c>
+      <c r="L198" t="n">
+        <v>0.5388140678405762</v>
+      </c>
+      <c r="M198" t="n">
+        <v>11.4948091506958</v>
+      </c>
+      <c r="N198" s="2" t="n">
+        <v>45831.60812513205</v>
+      </c>
+      <c r="O198" t="n">
+        <v>89.95</v>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="Q198" t="n">
+        <v>11.65001</v>
+      </c>
+      <c r="R198" t="n">
+        <v>7.721023415430545</v>
+      </c>
+      <c r="S198" t="n">
+        <v>14392</v>
+      </c>
+      <c r="T198" t="n">
+        <v>1235.363746468887</v>
+      </c>
+      <c r="U198" t="n">
+        <v>7.055345526024306</v>
+      </c>
+      <c r="V198" t="n">
+        <v>-0.005527915975677145</v>
+      </c>
+      <c r="W198" t="n">
+        <v>-0.0150842296446374</v>
+      </c>
+      <c r="X198" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y198" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z198" t="n">
+        <v>0.5161983370780945</v>
+      </c>
+      <c r="AA198" t="n">
+        <v>10.16883182525635</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F199" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H199" t="n">
+        <v>1</v>
+      </c>
+      <c r="I199" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="J199" t="n">
+        <v>34</v>
+      </c>
+      <c r="K199" t="n">
+        <v>9</v>
+      </c>
+      <c r="L199" t="n">
+        <v>0.6616257429122925</v>
+      </c>
+      <c r="M199" t="n">
+        <v>13.05655670166016</v>
+      </c>
+      <c r="N199" s="2" t="n">
+        <v>45831.60812513205</v>
+      </c>
+      <c r="O199" t="n">
+        <v>43.98</v>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q199" t="n">
+        <v>1</v>
+      </c>
+      <c r="R199" t="n">
+        <v>43.98</v>
+      </c>
+      <c r="S199" t="n">
+        <v>1495.32</v>
+      </c>
+      <c r="T199" t="n">
+        <v>1495.32</v>
+      </c>
+      <c r="U199" t="n">
+        <v>39.582</v>
+      </c>
+      <c r="V199" t="n">
+        <v>0.02757009345794392</v>
+      </c>
+      <c r="W199" t="n">
+        <v>0.02757009345794392</v>
+      </c>
+      <c r="X199" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y199" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z199" t="n">
+        <v>0.6566609740257263</v>
+      </c>
+      <c r="AA199" t="n">
+        <v>12.99397349357605</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F200" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H200" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I200" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J200" t="n">
+        <v>537</v>
+      </c>
+      <c r="K200" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L200" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M200" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N200" s="2" t="n">
+        <v>45831.60812513205</v>
+      </c>
+      <c r="O200" t="n">
+        <v>26.05</v>
+      </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q200" t="n">
+        <v>9.050509999999999</v>
+      </c>
+      <c r="R200" t="n">
+        <v>2.878290836648985</v>
+      </c>
+      <c r="S200" t="n">
+        <v>13988.85</v>
+      </c>
+      <c r="T200" t="n">
+        <v>1545.642179280505</v>
+      </c>
+      <c r="U200" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V200" t="n">
+        <v>0.03373015873015883</v>
+      </c>
+      <c r="W200" t="n">
+        <v>0.03259140636343694</v>
+      </c>
+      <c r="X200" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y200" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z200" t="n">
+        <v>0.5859425067901611</v>
+      </c>
+      <c r="AA200" t="n">
+        <v>12.04357481002808</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F201" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H201" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I201" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J201" t="n">
+        <v>121</v>
+      </c>
+      <c r="K201" t="n">
+        <v>12</v>
+      </c>
+      <c r="L201" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M201" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N201" s="2" t="n">
+        <v>45831.60812513205</v>
+      </c>
+      <c r="O201" t="n">
+        <v>14.62</v>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q201" t="n">
+        <v>1.1535356</v>
+      </c>
+      <c r="R201" t="n">
+        <v>12.67407785247373</v>
+      </c>
+      <c r="S201" t="n">
+        <v>1769.02</v>
+      </c>
+      <c r="T201" t="n">
+        <v>1533.563420149322</v>
+      </c>
+      <c r="U201" t="n">
+        <v>11.41876452309428</v>
+      </c>
+      <c r="V201" t="n">
+        <v>0.03102961918194636</v>
+      </c>
+      <c r="W201" t="n">
+        <v>0.02818304632266844</v>
+      </c>
+      <c r="X201" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y201" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z201" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="AA201" t="n">
         <v>14.27337956428528</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA201"/>
+  <dimension ref="A1:AA209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18614,7 +18614,7 @@
         <v>100</v>
       </c>
       <c r="N194" s="2" t="n">
-        <v>45831.60812513205</v>
+        <v>45831.60812512731</v>
       </c>
       <c r="O194" t="n">
         <v>1</v>
@@ -18705,7 +18705,7 @@
         <v>12.02781891822815</v>
       </c>
       <c r="N195" s="2" t="n">
-        <v>45831.60812513205</v>
+        <v>45831.60812512731</v>
       </c>
       <c r="O195" t="n">
         <v>38.25</v>
@@ -18796,7 +18796,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N196" s="2" t="n">
-        <v>45831.60812513205</v>
+        <v>45831.60812512731</v>
       </c>
       <c r="O196" t="n">
         <v>379.4</v>
@@ -18891,7 +18891,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N197" s="2" t="n">
-        <v>45831.60812513205</v>
+        <v>45831.60812512731</v>
       </c>
       <c r="O197" t="n">
         <v>0.725</v>
@@ -18982,7 +18982,7 @@
         <v>11.4948091506958</v>
       </c>
       <c r="N198" s="2" t="n">
-        <v>45831.60812513205</v>
+        <v>45831.60812512731</v>
       </c>
       <c r="O198" t="n">
         <v>89.95</v>
@@ -19077,7 +19077,7 @@
         <v>13.05655670166016</v>
       </c>
       <c r="N199" s="2" t="n">
-        <v>45831.60812513205</v>
+        <v>45831.60812512731</v>
       </c>
       <c r="O199" t="n">
         <v>43.98</v>
@@ -19172,7 +19172,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N200" s="2" t="n">
-        <v>45831.60812513205</v>
+        <v>45831.60812512731</v>
       </c>
       <c r="O200" t="n">
         <v>26.05</v>
@@ -19267,7 +19267,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N201" s="2" t="n">
-        <v>45831.60812513205</v>
+        <v>45831.60812512731</v>
       </c>
       <c r="O201" t="n">
         <v>14.62</v>
@@ -19308,6 +19308,756 @@
         <v>0.540931224822998</v>
       </c>
       <c r="AA201" t="n">
+        <v>14.27337956428528</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F202" t="n">
+        <v>1</v>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H202" t="n">
+        <v>1</v>
+      </c>
+      <c r="I202" t="n">
+        <v>1</v>
+      </c>
+      <c r="J202" t="n">
+        <v>1</v>
+      </c>
+      <c r="K202" t="n">
+        <v>100</v>
+      </c>
+      <c r="L202" t="n">
+        <v>100</v>
+      </c>
+      <c r="M202" t="n">
+        <v>100</v>
+      </c>
+      <c r="N202" s="2" t="n">
+        <v>45831.64798667824</v>
+      </c>
+      <c r="O202" t="n">
+        <v>1</v>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q202" t="n">
+        <v>1</v>
+      </c>
+      <c r="R202" t="n">
+        <v>1</v>
+      </c>
+      <c r="S202" t="n">
+        <v>0</v>
+      </c>
+      <c r="T202" t="n">
+        <v>16.03601332880703</v>
+      </c>
+      <c r="U202" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V202" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W202" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X202" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y202" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z202" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA202" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>DE000A0XYG76</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>DR0.DE</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>DT.ROHSTOFF AG NA O.N.</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F203" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H203" t="n">
+        <v>1</v>
+      </c>
+      <c r="I203" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="J203" t="n">
+        <v>39</v>
+      </c>
+      <c r="K203" t="n">
+        <v>11</v>
+      </c>
+      <c r="L203" t="n">
+        <v>0.4329348504543304</v>
+      </c>
+      <c r="M203" t="n">
+        <v>12.02781891822815</v>
+      </c>
+      <c r="N203" s="2" t="n">
+        <v>45831.64798667824</v>
+      </c>
+      <c r="O203" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q203" t="n">
+        <v>1</v>
+      </c>
+      <c r="R203" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="S203" t="n">
+        <v>1478.1</v>
+      </c>
+      <c r="T203" t="n">
+        <v>1478.1</v>
+      </c>
+      <c r="U203" t="n">
+        <v>34.92</v>
+      </c>
+      <c r="V203" t="n">
+        <v>0.005305039787798282</v>
+      </c>
+      <c r="W203" t="n">
+        <v>0.005305039787798282</v>
+      </c>
+      <c r="X203" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y203" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z203" t="n">
+        <v>0.4742938280105591</v>
+      </c>
+      <c r="AA203" t="n">
+        <v>12.61593472957611</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F204" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H204" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I204" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J204" t="n">
+        <v>3</v>
+      </c>
+      <c r="K204" t="n">
+        <v>10</v>
+      </c>
+      <c r="L204" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M204" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N204" s="2" t="n">
+        <v>45831.64798667824</v>
+      </c>
+      <c r="O204" t="n">
+        <v>379.4</v>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q204" t="n">
+        <v>0.85524</v>
+      </c>
+      <c r="R204" t="n">
+        <v>443.6181656611009</v>
+      </c>
+      <c r="S204" t="n">
+        <v>1138.2</v>
+      </c>
+      <c r="T204" t="n">
+        <v>1330.854496983303</v>
+      </c>
+      <c r="U204" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V204" t="n">
+        <v>0.03191483574766218</v>
+      </c>
+      <c r="W204" t="n">
+        <v>0.03002050632887476</v>
+      </c>
+      <c r="X204" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y204" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z204" t="n">
+        <v>0.5007368326187134</v>
+      </c>
+      <c r="AA204" t="n">
+        <v>12.07941150665283</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F205" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H205" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I205" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J205" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K205" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L205" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M205" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N205" s="2" t="n">
+        <v>45831.64798667824</v>
+      </c>
+      <c r="O205" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q205" t="n">
+        <v>1.79373</v>
+      </c>
+      <c r="R205" t="n">
+        <v>0.4041856912690315</v>
+      </c>
+      <c r="S205" t="n">
+        <v>2656.4</v>
+      </c>
+      <c r="T205" t="n">
+        <v>1480.936372809732</v>
+      </c>
+      <c r="U205" t="n">
+        <v>0.3678646934460888</v>
+      </c>
+      <c r="V205" t="n">
+        <v>0</v>
+      </c>
+      <c r="W205" t="n">
+        <v>-0.01068165219960648</v>
+      </c>
+      <c r="X205" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y205" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z205" t="n">
+        <v>0.5391064286231995</v>
+      </c>
+      <c r="AA205" t="n">
+        <v>12.27176785469055</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>NO0012851874</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>DOFG.OL</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr"/>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>DOF GROUP ASA  NK 2,50</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F206" t="n">
+        <v>90.45</v>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="H206" t="n">
+        <v>11.53806</v>
+      </c>
+      <c r="I206" t="n">
+        <v>7.839272806693673</v>
+      </c>
+      <c r="J206" t="n">
+        <v>160</v>
+      </c>
+      <c r="K206" t="n">
+        <v>9</v>
+      </c>
+      <c r="L206" t="n">
+        <v>0.5388140678405762</v>
+      </c>
+      <c r="M206" t="n">
+        <v>11.4948091506958</v>
+      </c>
+      <c r="N206" s="2" t="n">
+        <v>45831.64798667824</v>
+      </c>
+      <c r="O206" t="n">
+        <v>90</v>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="Q206" t="n">
+        <v>11.6442</v>
+      </c>
+      <c r="R206" t="n">
+        <v>7.72916988715412</v>
+      </c>
+      <c r="S206" t="n">
+        <v>14400</v>
+      </c>
+      <c r="T206" t="n">
+        <v>1236.667181944659</v>
+      </c>
+      <c r="U206" t="n">
+        <v>7.055345526024306</v>
+      </c>
+      <c r="V206" t="n">
+        <v>-0.00497512437810943</v>
+      </c>
+      <c r="W206" t="n">
+        <v>-0.01404504247454441</v>
+      </c>
+      <c r="X206" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y206" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z206" t="n">
+        <v>0.5161983370780945</v>
+      </c>
+      <c r="AA206" t="n">
+        <v>10.16883182525635</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F207" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H207" t="n">
+        <v>1</v>
+      </c>
+      <c r="I207" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="J207" t="n">
+        <v>34</v>
+      </c>
+      <c r="K207" t="n">
+        <v>9</v>
+      </c>
+      <c r="L207" t="n">
+        <v>0.6616257429122925</v>
+      </c>
+      <c r="M207" t="n">
+        <v>13.05655670166016</v>
+      </c>
+      <c r="N207" s="2" t="n">
+        <v>45831.64798667824</v>
+      </c>
+      <c r="O207" t="n">
+        <v>43.98</v>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q207" t="n">
+        <v>1</v>
+      </c>
+      <c r="R207" t="n">
+        <v>43.98</v>
+      </c>
+      <c r="S207" t="n">
+        <v>1495.32</v>
+      </c>
+      <c r="T207" t="n">
+        <v>1495.32</v>
+      </c>
+      <c r="U207" t="n">
+        <v>39.582</v>
+      </c>
+      <c r="V207" t="n">
+        <v>0.02757009345794392</v>
+      </c>
+      <c r="W207" t="n">
+        <v>0.02757009345794392</v>
+      </c>
+      <c r="X207" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y207" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z207" t="n">
+        <v>0.6566609740257263</v>
+      </c>
+      <c r="AA207" t="n">
+        <v>12.99397349357605</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F208" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H208" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I208" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J208" t="n">
+        <v>537</v>
+      </c>
+      <c r="K208" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L208" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M208" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N208" s="2" t="n">
+        <v>45831.64798667824</v>
+      </c>
+      <c r="O208" t="n">
+        <v>26.05</v>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q208" t="n">
+        <v>9.061859999999999</v>
+      </c>
+      <c r="R208" t="n">
+        <v>2.874685770912374</v>
+      </c>
+      <c r="S208" t="n">
+        <v>13988.85</v>
+      </c>
+      <c r="T208" t="n">
+        <v>1543.706258979945</v>
+      </c>
+      <c r="U208" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V208" t="n">
+        <v>0.03373015873015883</v>
+      </c>
+      <c r="W208" t="n">
+        <v>0.03129808330810135</v>
+      </c>
+      <c r="X208" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y208" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z208" t="n">
+        <v>0.5859425067901611</v>
+      </c>
+      <c r="AA208" t="n">
+        <v>12.04357481002808</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F209" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H209" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I209" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J209" t="n">
+        <v>121</v>
+      </c>
+      <c r="K209" t="n">
+        <v>12</v>
+      </c>
+      <c r="L209" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M209" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N209" s="2" t="n">
+        <v>45831.64798667824</v>
+      </c>
+      <c r="O209" t="n">
+        <v>14.755</v>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q209" t="n">
+        <v>1.1552681</v>
+      </c>
+      <c r="R209" t="n">
+        <v>12.77192713968299</v>
+      </c>
+      <c r="S209" t="n">
+        <v>1785.355</v>
+      </c>
+      <c r="T209" t="n">
+        <v>1545.403183901642</v>
+      </c>
+      <c r="U209" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V209" t="n">
+        <v>0.04055007052186177</v>
+      </c>
+      <c r="W209" t="n">
+        <v>0.03612105801664578</v>
+      </c>
+      <c r="X209" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y209" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z209" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="AA209" t="n">
         <v>14.27337956428528</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA209"/>
+  <dimension ref="A1:AA217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20061,6 +20061,756 @@
         <v>14.27337956428528</v>
       </c>
     </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F210" t="n">
+        <v>1</v>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H210" t="n">
+        <v>1</v>
+      </c>
+      <c r="I210" t="n">
+        <v>1</v>
+      </c>
+      <c r="J210" t="n">
+        <v>1</v>
+      </c>
+      <c r="K210" t="n">
+        <v>100</v>
+      </c>
+      <c r="L210" t="n">
+        <v>100</v>
+      </c>
+      <c r="M210" t="n">
+        <v>100</v>
+      </c>
+      <c r="N210" s="2" t="n">
+        <v>45831.69371380457</v>
+      </c>
+      <c r="O210" t="n">
+        <v>1</v>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q210" t="n">
+        <v>1</v>
+      </c>
+      <c r="R210" t="n">
+        <v>1</v>
+      </c>
+      <c r="S210" t="n">
+        <v>0</v>
+      </c>
+      <c r="T210" t="n">
+        <v>16.03601332880703</v>
+      </c>
+      <c r="U210" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V210" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W210" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X210" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y210" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z210" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA210" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>DE000A0XYG76</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>DR0.DE</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr"/>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>DT.ROHSTOFF AG NA O.N.</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F211" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H211" t="n">
+        <v>1</v>
+      </c>
+      <c r="I211" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="J211" t="n">
+        <v>39</v>
+      </c>
+      <c r="K211" t="n">
+        <v>11</v>
+      </c>
+      <c r="L211" t="n">
+        <v>0.4329348504543304</v>
+      </c>
+      <c r="M211" t="n">
+        <v>12.02781891822815</v>
+      </c>
+      <c r="N211" s="2" t="n">
+        <v>45831.69371380457</v>
+      </c>
+      <c r="O211" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q211" t="n">
+        <v>1</v>
+      </c>
+      <c r="R211" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="S211" t="n">
+        <v>1478.1</v>
+      </c>
+      <c r="T211" t="n">
+        <v>1478.1</v>
+      </c>
+      <c r="U211" t="n">
+        <v>34.92</v>
+      </c>
+      <c r="V211" t="n">
+        <v>0.005305039787798282</v>
+      </c>
+      <c r="W211" t="n">
+        <v>0.005305039787798282</v>
+      </c>
+      <c r="X211" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y211" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z211" t="n">
+        <v>0.4742938280105591</v>
+      </c>
+      <c r="AA211" t="n">
+        <v>12.61593472957611</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr"/>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F212" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H212" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I212" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J212" t="n">
+        <v>3</v>
+      </c>
+      <c r="K212" t="n">
+        <v>10</v>
+      </c>
+      <c r="L212" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M212" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N212" s="2" t="n">
+        <v>45831.69371380457</v>
+      </c>
+      <c r="O212" t="n">
+        <v>375</v>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q212" t="n">
+        <v>0.85511</v>
+      </c>
+      <c r="R212" t="n">
+        <v>438.5400708680754</v>
+      </c>
+      <c r="S212" t="n">
+        <v>1125</v>
+      </c>
+      <c r="T212" t="n">
+        <v>1315.620212604226</v>
+      </c>
+      <c r="U212" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V212" t="n">
+        <v>0.01994745230725714</v>
+      </c>
+      <c r="W212" t="n">
+        <v>0.01822986704767349</v>
+      </c>
+      <c r="X212" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y212" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z212" t="n">
+        <v>0.5007368326187134</v>
+      </c>
+      <c r="AA212" t="n">
+        <v>12.07941150665283</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F213" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H213" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I213" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J213" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K213" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L213" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M213" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N213" s="2" t="n">
+        <v>45831.69371380457</v>
+      </c>
+      <c r="O213" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q213" t="n">
+        <v>1.79737</v>
+      </c>
+      <c r="R213" t="n">
+        <v>0.4033671419907977</v>
+      </c>
+      <c r="S213" t="n">
+        <v>2656.4</v>
+      </c>
+      <c r="T213" t="n">
+        <v>1477.937208254283</v>
+      </c>
+      <c r="U213" t="n">
+        <v>0.3678646934460888</v>
+      </c>
+      <c r="V213" t="n">
+        <v>0</v>
+      </c>
+      <c r="W213" t="n">
+        <v>-0.01268520115502103</v>
+      </c>
+      <c r="X213" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y213" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z213" t="n">
+        <v>0.5391064286231995</v>
+      </c>
+      <c r="AA213" t="n">
+        <v>12.27176785469055</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>NO0012851874</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>DOFG.OL</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>DOF GROUP ASA  NK 2,50</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F214" t="n">
+        <v>90.45</v>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="H214" t="n">
+        <v>11.53806</v>
+      </c>
+      <c r="I214" t="n">
+        <v>7.839272806693673</v>
+      </c>
+      <c r="J214" t="n">
+        <v>160</v>
+      </c>
+      <c r="K214" t="n">
+        <v>9</v>
+      </c>
+      <c r="L214" t="n">
+        <v>0.5388140678405762</v>
+      </c>
+      <c r="M214" t="n">
+        <v>11.4948091506958</v>
+      </c>
+      <c r="N214" s="2" t="n">
+        <v>45831.69371380457</v>
+      </c>
+      <c r="O214" t="n">
+        <v>90</v>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="Q214" t="n">
+        <v>11.6522</v>
+      </c>
+      <c r="R214" t="n">
+        <v>7.723863304783646</v>
+      </c>
+      <c r="S214" t="n">
+        <v>14400</v>
+      </c>
+      <c r="T214" t="n">
+        <v>1235.818128765383</v>
+      </c>
+      <c r="U214" t="n">
+        <v>7.055345526024306</v>
+      </c>
+      <c r="V214" t="n">
+        <v>-0.00497512437810943</v>
+      </c>
+      <c r="W214" t="n">
+        <v>-0.01472196525824221</v>
+      </c>
+      <c r="X214" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y214" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z214" t="n">
+        <v>0.5161983370780945</v>
+      </c>
+      <c r="AA214" t="n">
+        <v>10.16883182525635</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F215" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H215" t="n">
+        <v>1</v>
+      </c>
+      <c r="I215" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="J215" t="n">
+        <v>34</v>
+      </c>
+      <c r="K215" t="n">
+        <v>9</v>
+      </c>
+      <c r="L215" t="n">
+        <v>0.6616257429122925</v>
+      </c>
+      <c r="M215" t="n">
+        <v>13.05655670166016</v>
+      </c>
+      <c r="N215" s="2" t="n">
+        <v>45831.69371380457</v>
+      </c>
+      <c r="O215" t="n">
+        <v>43.98</v>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q215" t="n">
+        <v>1</v>
+      </c>
+      <c r="R215" t="n">
+        <v>43.98</v>
+      </c>
+      <c r="S215" t="n">
+        <v>1495.32</v>
+      </c>
+      <c r="T215" t="n">
+        <v>1495.32</v>
+      </c>
+      <c r="U215" t="n">
+        <v>39.582</v>
+      </c>
+      <c r="V215" t="n">
+        <v>0.02757009345794392</v>
+      </c>
+      <c r="W215" t="n">
+        <v>0.02757009345794392</v>
+      </c>
+      <c r="X215" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y215" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z215" t="n">
+        <v>0.6566609740257263</v>
+      </c>
+      <c r="AA215" t="n">
+        <v>12.99397349357605</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F216" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H216" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I216" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J216" t="n">
+        <v>537</v>
+      </c>
+      <c r="K216" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L216" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M216" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N216" s="2" t="n">
+        <v>45831.69371380457</v>
+      </c>
+      <c r="O216" t="n">
+        <v>26.05</v>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q216" t="n">
+        <v>9.047829999999999</v>
+      </c>
+      <c r="R216" t="n">
+        <v>2.879143396814485</v>
+      </c>
+      <c r="S216" t="n">
+        <v>13988.85</v>
+      </c>
+      <c r="T216" t="n">
+        <v>1546.100004089378</v>
+      </c>
+      <c r="U216" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V216" t="n">
+        <v>0.03373015873015883</v>
+      </c>
+      <c r="W216" t="n">
+        <v>0.03289726367608048</v>
+      </c>
+      <c r="X216" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y216" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z216" t="n">
+        <v>0.5859425067901611</v>
+      </c>
+      <c r="AA216" t="n">
+        <v>12.04357481002808</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F217" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H217" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I217" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J217" t="n">
+        <v>121</v>
+      </c>
+      <c r="K217" t="n">
+        <v>12</v>
+      </c>
+      <c r="L217" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M217" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N217" s="2" t="n">
+        <v>45831.69371380457</v>
+      </c>
+      <c r="O217" t="n">
+        <v>14.59</v>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q217" t="n">
+        <v>1.1527377</v>
+      </c>
+      <c r="R217" t="n">
+        <v>12.65682557272136</v>
+      </c>
+      <c r="S217" t="n">
+        <v>1765.39</v>
+      </c>
+      <c r="T217" t="n">
+        <v>1531.475894299284</v>
+      </c>
+      <c r="U217" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V217" t="n">
+        <v>0.02891396332863194</v>
+      </c>
+      <c r="W217" t="n">
+        <v>0.02678345719608388</v>
+      </c>
+      <c r="X217" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y217" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z217" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="AA217" t="n">
+        <v>14.27337956428528</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA217"/>
+  <dimension ref="A1:AA225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20114,7 +20114,7 @@
         <v>100</v>
       </c>
       <c r="N210" s="2" t="n">
-        <v>45831.69371380457</v>
+        <v>45831.69371380787</v>
       </c>
       <c r="O210" t="n">
         <v>1</v>
@@ -20205,7 +20205,7 @@
         <v>12.02781891822815</v>
       </c>
       <c r="N211" s="2" t="n">
-        <v>45831.69371380457</v>
+        <v>45831.69371380787</v>
       </c>
       <c r="O211" t="n">
         <v>37.9</v>
@@ -20296,7 +20296,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N212" s="2" t="n">
-        <v>45831.69371380457</v>
+        <v>45831.69371380787</v>
       </c>
       <c r="O212" t="n">
         <v>375</v>
@@ -20391,7 +20391,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N213" s="2" t="n">
-        <v>45831.69371380457</v>
+        <v>45831.69371380787</v>
       </c>
       <c r="O213" t="n">
         <v>0.725</v>
@@ -20482,7 +20482,7 @@
         <v>11.4948091506958</v>
       </c>
       <c r="N214" s="2" t="n">
-        <v>45831.69371380457</v>
+        <v>45831.69371380787</v>
       </c>
       <c r="O214" t="n">
         <v>90</v>
@@ -20577,7 +20577,7 @@
         <v>13.05655670166016</v>
       </c>
       <c r="N215" s="2" t="n">
-        <v>45831.69371380457</v>
+        <v>45831.69371380787</v>
       </c>
       <c r="O215" t="n">
         <v>43.98</v>
@@ -20672,7 +20672,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N216" s="2" t="n">
-        <v>45831.69371380457</v>
+        <v>45831.69371380787</v>
       </c>
       <c r="O216" t="n">
         <v>26.05</v>
@@ -20767,7 +20767,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N217" s="2" t="n">
-        <v>45831.69371380457</v>
+        <v>45831.69371380787</v>
       </c>
       <c r="O217" t="n">
         <v>14.59</v>
@@ -20808,6 +20808,756 @@
         <v>0.540931224822998</v>
       </c>
       <c r="AA217" t="n">
+        <v>14.27337956428528</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F218" t="n">
+        <v>1</v>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H218" t="n">
+        <v>1</v>
+      </c>
+      <c r="I218" t="n">
+        <v>1</v>
+      </c>
+      <c r="J218" t="n">
+        <v>1</v>
+      </c>
+      <c r="K218" t="n">
+        <v>100</v>
+      </c>
+      <c r="L218" t="n">
+        <v>100</v>
+      </c>
+      <c r="M218" t="n">
+        <v>100</v>
+      </c>
+      <c r="N218" s="2" t="n">
+        <v>45831.73073729732</v>
+      </c>
+      <c r="O218" t="n">
+        <v>1</v>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q218" t="n">
+        <v>1</v>
+      </c>
+      <c r="R218" t="n">
+        <v>1</v>
+      </c>
+      <c r="S218" t="n">
+        <v>0</v>
+      </c>
+      <c r="T218" t="n">
+        <v>16.03601332880703</v>
+      </c>
+      <c r="U218" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V218" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W218" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X218" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y218" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z218" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA218" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>DE000A0XYG76</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>DR0.DE</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>DT.ROHSTOFF AG NA O.N.</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F219" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H219" t="n">
+        <v>1</v>
+      </c>
+      <c r="I219" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="J219" t="n">
+        <v>39</v>
+      </c>
+      <c r="K219" t="n">
+        <v>11</v>
+      </c>
+      <c r="L219" t="n">
+        <v>0.4329348504543304</v>
+      </c>
+      <c r="M219" t="n">
+        <v>12.02781891822815</v>
+      </c>
+      <c r="N219" s="2" t="n">
+        <v>45831.73073729732</v>
+      </c>
+      <c r="O219" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q219" t="n">
+        <v>1</v>
+      </c>
+      <c r="R219" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="S219" t="n">
+        <v>1478.1</v>
+      </c>
+      <c r="T219" t="n">
+        <v>1478.1</v>
+      </c>
+      <c r="U219" t="n">
+        <v>34.92</v>
+      </c>
+      <c r="V219" t="n">
+        <v>0.005305039787798282</v>
+      </c>
+      <c r="W219" t="n">
+        <v>0.005305039787798282</v>
+      </c>
+      <c r="X219" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y219" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z219" t="n">
+        <v>0.4742938280105591</v>
+      </c>
+      <c r="AA219" t="n">
+        <v>12.61593472957611</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F220" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H220" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I220" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J220" t="n">
+        <v>3</v>
+      </c>
+      <c r="K220" t="n">
+        <v>10</v>
+      </c>
+      <c r="L220" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M220" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N220" s="2" t="n">
+        <v>45831.73073729732</v>
+      </c>
+      <c r="O220" t="n">
+        <v>375</v>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q220" t="n">
+        <v>0.85538</v>
+      </c>
+      <c r="R220" t="n">
+        <v>438.4016460520471</v>
+      </c>
+      <c r="S220" t="n">
+        <v>1125</v>
+      </c>
+      <c r="T220" t="n">
+        <v>1315.204938156141</v>
+      </c>
+      <c r="U220" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V220" t="n">
+        <v>0.01994745230725714</v>
+      </c>
+      <c r="W220" t="n">
+        <v>0.017908463619837</v>
+      </c>
+      <c r="X220" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y220" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z220" t="n">
+        <v>0.5007368326187134</v>
+      </c>
+      <c r="AA220" t="n">
+        <v>12.07941150665283</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F221" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H221" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I221" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J221" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K221" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L221" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M221" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N221" s="2" t="n">
+        <v>45831.73073729732</v>
+      </c>
+      <c r="O221" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q221" t="n">
+        <v>1.79308</v>
+      </c>
+      <c r="R221" t="n">
+        <v>0.4043322104981373</v>
+      </c>
+      <c r="S221" t="n">
+        <v>2656.4</v>
+      </c>
+      <c r="T221" t="n">
+        <v>1481.473219265175</v>
+      </c>
+      <c r="U221" t="n">
+        <v>0.3678646934460888</v>
+      </c>
+      <c r="V221" t="n">
+        <v>0</v>
+      </c>
+      <c r="W221" t="n">
+        <v>-0.01032301960871795</v>
+      </c>
+      <c r="X221" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y221" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z221" t="n">
+        <v>0.5391064286231995</v>
+      </c>
+      <c r="AA221" t="n">
+        <v>12.27176785469055</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>NO0012851874</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>DOFG.OL</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr"/>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>DOF GROUP ASA  NK 2,50</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F222" t="n">
+        <v>90.45</v>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="H222" t="n">
+        <v>11.53806</v>
+      </c>
+      <c r="I222" t="n">
+        <v>7.839272806693673</v>
+      </c>
+      <c r="J222" t="n">
+        <v>160</v>
+      </c>
+      <c r="K222" t="n">
+        <v>9</v>
+      </c>
+      <c r="L222" t="n">
+        <v>0.5388140678405762</v>
+      </c>
+      <c r="M222" t="n">
+        <v>11.4948091506958</v>
+      </c>
+      <c r="N222" s="2" t="n">
+        <v>45831.73073729732</v>
+      </c>
+      <c r="O222" t="n">
+        <v>90</v>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="Q222" t="n">
+        <v>11.66664</v>
+      </c>
+      <c r="R222" t="n">
+        <v>7.714303346979079</v>
+      </c>
+      <c r="S222" t="n">
+        <v>14400</v>
+      </c>
+      <c r="T222" t="n">
+        <v>1234.288535516653</v>
+      </c>
+      <c r="U222" t="n">
+        <v>7.055345526024306</v>
+      </c>
+      <c r="V222" t="n">
+        <v>-0.00497512437810943</v>
+      </c>
+      <c r="W222" t="n">
+        <v>-0.01594146074466074</v>
+      </c>
+      <c r="X222" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y222" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z222" t="n">
+        <v>0.5161983370780945</v>
+      </c>
+      <c r="AA222" t="n">
+        <v>10.16883182525635</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F223" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H223" t="n">
+        <v>1</v>
+      </c>
+      <c r="I223" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="J223" t="n">
+        <v>34</v>
+      </c>
+      <c r="K223" t="n">
+        <v>9</v>
+      </c>
+      <c r="L223" t="n">
+        <v>0.6616257429122925</v>
+      </c>
+      <c r="M223" t="n">
+        <v>13.05655670166016</v>
+      </c>
+      <c r="N223" s="2" t="n">
+        <v>45831.73073729732</v>
+      </c>
+      <c r="O223" t="n">
+        <v>43.98</v>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q223" t="n">
+        <v>1</v>
+      </c>
+      <c r="R223" t="n">
+        <v>43.98</v>
+      </c>
+      <c r="S223" t="n">
+        <v>1495.32</v>
+      </c>
+      <c r="T223" t="n">
+        <v>1495.32</v>
+      </c>
+      <c r="U223" t="n">
+        <v>39.582</v>
+      </c>
+      <c r="V223" t="n">
+        <v>0.02757009345794392</v>
+      </c>
+      <c r="W223" t="n">
+        <v>0.02757009345794392</v>
+      </c>
+      <c r="X223" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y223" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z223" t="n">
+        <v>0.6566609740257263</v>
+      </c>
+      <c r="AA223" t="n">
+        <v>12.99397349357605</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F224" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H224" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I224" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J224" t="n">
+        <v>537</v>
+      </c>
+      <c r="K224" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L224" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M224" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N224" s="2" t="n">
+        <v>45831.73073729732</v>
+      </c>
+      <c r="O224" t="n">
+        <v>26.05</v>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q224" t="n">
+        <v>9.076840000000001</v>
+      </c>
+      <c r="R224" t="n">
+        <v>2.869941521498671</v>
+      </c>
+      <c r="S224" t="n">
+        <v>13988.85</v>
+      </c>
+      <c r="T224" t="n">
+        <v>1541.158597044786</v>
+      </c>
+      <c r="U224" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V224" t="n">
+        <v>0.03373015873015883</v>
+      </c>
+      <c r="W224" t="n">
+        <v>0.02959607630038086</v>
+      </c>
+      <c r="X224" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y224" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z224" t="n">
+        <v>0.5859425067901611</v>
+      </c>
+      <c r="AA224" t="n">
+        <v>12.04357481002808</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F225" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H225" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I225" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J225" t="n">
+        <v>121</v>
+      </c>
+      <c r="K225" t="n">
+        <v>12</v>
+      </c>
+      <c r="L225" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M225" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N225" s="2" t="n">
+        <v>45831.73073729732</v>
+      </c>
+      <c r="O225" t="n">
+        <v>14.595</v>
+      </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q225" t="n">
+        <v>1.156738</v>
+      </c>
+      <c r="R225" t="n">
+        <v>12.61737748738262</v>
+      </c>
+      <c r="S225" t="n">
+        <v>1765.995</v>
+      </c>
+      <c r="T225" t="n">
+        <v>1526.702675973297</v>
+      </c>
+      <c r="U225" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V225" t="n">
+        <v>0.02926657263751764</v>
+      </c>
+      <c r="W225" t="n">
+        <v>0.02358323600229828</v>
+      </c>
+      <c r="X225" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y225" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z225" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="AA225" t="n">
         <v>14.27337956428528</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA225"/>
+  <dimension ref="A1:AA233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20864,7 +20864,7 @@
         <v>100</v>
       </c>
       <c r="N218" s="2" t="n">
-        <v>45831.73073729732</v>
+        <v>45831.73073729167</v>
       </c>
       <c r="O218" t="n">
         <v>1</v>
@@ -20955,7 +20955,7 @@
         <v>12.02781891822815</v>
       </c>
       <c r="N219" s="2" t="n">
-        <v>45831.73073729732</v>
+        <v>45831.73073729167</v>
       </c>
       <c r="O219" t="n">
         <v>37.9</v>
@@ -21046,7 +21046,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N220" s="2" t="n">
-        <v>45831.73073729732</v>
+        <v>45831.73073729167</v>
       </c>
       <c r="O220" t="n">
         <v>375</v>
@@ -21141,7 +21141,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N221" s="2" t="n">
-        <v>45831.73073729732</v>
+        <v>45831.73073729167</v>
       </c>
       <c r="O221" t="n">
         <v>0.725</v>
@@ -21232,7 +21232,7 @@
         <v>11.4948091506958</v>
       </c>
       <c r="N222" s="2" t="n">
-        <v>45831.73073729732</v>
+        <v>45831.73073729167</v>
       </c>
       <c r="O222" t="n">
         <v>90</v>
@@ -21327,7 +21327,7 @@
         <v>13.05655670166016</v>
       </c>
       <c r="N223" s="2" t="n">
-        <v>45831.73073729732</v>
+        <v>45831.73073729167</v>
       </c>
       <c r="O223" t="n">
         <v>43.98</v>
@@ -21422,7 +21422,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N224" s="2" t="n">
-        <v>45831.73073729732</v>
+        <v>45831.73073729167</v>
       </c>
       <c r="O224" t="n">
         <v>26.05</v>
@@ -21517,7 +21517,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N225" s="2" t="n">
-        <v>45831.73073729732</v>
+        <v>45831.73073729167</v>
       </c>
       <c r="O225" t="n">
         <v>14.595</v>
@@ -21558,6 +21558,756 @@
         <v>0.540931224822998</v>
       </c>
       <c r="AA225" t="n">
+        <v>14.27337956428528</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F226" t="n">
+        <v>1</v>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H226" t="n">
+        <v>1</v>
+      </c>
+      <c r="I226" t="n">
+        <v>1</v>
+      </c>
+      <c r="J226" t="n">
+        <v>1</v>
+      </c>
+      <c r="K226" t="n">
+        <v>100</v>
+      </c>
+      <c r="L226" t="n">
+        <v>100</v>
+      </c>
+      <c r="M226" t="n">
+        <v>100</v>
+      </c>
+      <c r="N226" s="2" t="n">
+        <v>45831.77951203917</v>
+      </c>
+      <c r="O226" t="n">
+        <v>1</v>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q226" t="n">
+        <v>1</v>
+      </c>
+      <c r="R226" t="n">
+        <v>1</v>
+      </c>
+      <c r="S226" t="n">
+        <v>0</v>
+      </c>
+      <c r="T226" t="n">
+        <v>16.03601332880703</v>
+      </c>
+      <c r="U226" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V226" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W226" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X226" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y226" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z226" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA226" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>DE000A0XYG76</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>DR0.DE</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>DT.ROHSTOFF AG NA O.N.</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F227" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H227" t="n">
+        <v>1</v>
+      </c>
+      <c r="I227" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="J227" t="n">
+        <v>39</v>
+      </c>
+      <c r="K227" t="n">
+        <v>11</v>
+      </c>
+      <c r="L227" t="n">
+        <v>0.4329348504543304</v>
+      </c>
+      <c r="M227" t="n">
+        <v>12.02781891822815</v>
+      </c>
+      <c r="N227" s="2" t="n">
+        <v>45831.77951203917</v>
+      </c>
+      <c r="O227" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q227" t="n">
+        <v>1</v>
+      </c>
+      <c r="R227" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="S227" t="n">
+        <v>1478.1</v>
+      </c>
+      <c r="T227" t="n">
+        <v>1478.1</v>
+      </c>
+      <c r="U227" t="n">
+        <v>34.92</v>
+      </c>
+      <c r="V227" t="n">
+        <v>0.005305039787798282</v>
+      </c>
+      <c r="W227" t="n">
+        <v>0.005305039787798282</v>
+      </c>
+      <c r="X227" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y227" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z227" t="n">
+        <v>0.4742938280105591</v>
+      </c>
+      <c r="AA227" t="n">
+        <v>12.61593472957611</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr"/>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F228" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H228" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I228" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J228" t="n">
+        <v>3</v>
+      </c>
+      <c r="K228" t="n">
+        <v>10</v>
+      </c>
+      <c r="L228" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M228" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N228" s="2" t="n">
+        <v>45831.77951203917</v>
+      </c>
+      <c r="O228" t="n">
+        <v>375</v>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q228" t="n">
+        <v>0.85569</v>
+      </c>
+      <c r="R228" t="n">
+        <v>438.2428215825825</v>
+      </c>
+      <c r="S228" t="n">
+        <v>1125</v>
+      </c>
+      <c r="T228" t="n">
+        <v>1314.728464747747</v>
+      </c>
+      <c r="U228" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V228" t="n">
+        <v>0.01994745230725714</v>
+      </c>
+      <c r="W228" t="n">
+        <v>0.01753969499601049</v>
+      </c>
+      <c r="X228" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y228" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z228" t="n">
+        <v>0.5007368326187134</v>
+      </c>
+      <c r="AA228" t="n">
+        <v>12.07941150665283</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F229" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H229" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I229" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J229" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K229" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L229" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M229" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N229" s="2" t="n">
+        <v>45831.77951203917</v>
+      </c>
+      <c r="O229" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q229" t="n">
+        <v>1.79304</v>
+      </c>
+      <c r="R229" t="n">
+        <v>0.4043412305358497</v>
+      </c>
+      <c r="S229" t="n">
+        <v>2656.4</v>
+      </c>
+      <c r="T229" t="n">
+        <v>1481.506268683353</v>
+      </c>
+      <c r="U229" t="n">
+        <v>0.3678646934460888</v>
+      </c>
+      <c r="V229" t="n">
+        <v>0</v>
+      </c>
+      <c r="W229" t="n">
+        <v>-0.01030094141792703</v>
+      </c>
+      <c r="X229" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y229" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z229" t="n">
+        <v>0.5391064286231995</v>
+      </c>
+      <c r="AA229" t="n">
+        <v>12.27176785469055</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>NO0012851874</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>DOFG.OL</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>DOF GROUP ASA  NK 2,50</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F230" t="n">
+        <v>90.45</v>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="H230" t="n">
+        <v>11.53806</v>
+      </c>
+      <c r="I230" t="n">
+        <v>7.839272806693673</v>
+      </c>
+      <c r="J230" t="n">
+        <v>160</v>
+      </c>
+      <c r="K230" t="n">
+        <v>9</v>
+      </c>
+      <c r="L230" t="n">
+        <v>0.5388140678405762</v>
+      </c>
+      <c r="M230" t="n">
+        <v>11.4948091506958</v>
+      </c>
+      <c r="N230" s="2" t="n">
+        <v>45831.77951203917</v>
+      </c>
+      <c r="O230" t="n">
+        <v>90</v>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="Q230" t="n">
+        <v>11.67781</v>
+      </c>
+      <c r="R230" t="n">
+        <v>7.70692450039862</v>
+      </c>
+      <c r="S230" t="n">
+        <v>14400</v>
+      </c>
+      <c r="T230" t="n">
+        <v>1233.107920063779</v>
+      </c>
+      <c r="U230" t="n">
+        <v>7.055345526024306</v>
+      </c>
+      <c r="V230" t="n">
+        <v>-0.00497512437810943</v>
+      </c>
+      <c r="W230" t="n">
+        <v>-0.01688272746192032</v>
+      </c>
+      <c r="X230" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y230" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z230" t="n">
+        <v>0.5161983370780945</v>
+      </c>
+      <c r="AA230" t="n">
+        <v>10.16883182525635</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F231" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H231" t="n">
+        <v>1</v>
+      </c>
+      <c r="I231" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="J231" t="n">
+        <v>34</v>
+      </c>
+      <c r="K231" t="n">
+        <v>9</v>
+      </c>
+      <c r="L231" t="n">
+        <v>0.6616257429122925</v>
+      </c>
+      <c r="M231" t="n">
+        <v>13.05655670166016</v>
+      </c>
+      <c r="N231" s="2" t="n">
+        <v>45831.77951203917</v>
+      </c>
+      <c r="O231" t="n">
+        <v>43.98</v>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q231" t="n">
+        <v>1</v>
+      </c>
+      <c r="R231" t="n">
+        <v>43.98</v>
+      </c>
+      <c r="S231" t="n">
+        <v>1495.32</v>
+      </c>
+      <c r="T231" t="n">
+        <v>1495.32</v>
+      </c>
+      <c r="U231" t="n">
+        <v>39.582</v>
+      </c>
+      <c r="V231" t="n">
+        <v>0.02757009345794392</v>
+      </c>
+      <c r="W231" t="n">
+        <v>0.02757009345794392</v>
+      </c>
+      <c r="X231" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y231" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z231" t="n">
+        <v>0.6566609740257263</v>
+      </c>
+      <c r="AA231" t="n">
+        <v>12.99397349357605</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F232" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H232" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I232" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J232" t="n">
+        <v>537</v>
+      </c>
+      <c r="K232" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L232" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M232" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N232" s="2" t="n">
+        <v>45831.77951203917</v>
+      </c>
+      <c r="O232" t="n">
+        <v>26.05</v>
+      </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q232" t="n">
+        <v>9.082879999999999</v>
+      </c>
+      <c r="R232" t="n">
+        <v>2.868033046786922</v>
+      </c>
+      <c r="S232" t="n">
+        <v>13988.85</v>
+      </c>
+      <c r="T232" t="n">
+        <v>1540.133746124577</v>
+      </c>
+      <c r="U232" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V232" t="n">
+        <v>0.03373015873015883</v>
+      </c>
+      <c r="W232" t="n">
+        <v>0.02891140796821601</v>
+      </c>
+      <c r="X232" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y232" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z232" t="n">
+        <v>0.5859425067901611</v>
+      </c>
+      <c r="AA232" t="n">
+        <v>12.04357481002808</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F233" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H233" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I233" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J233" t="n">
+        <v>121</v>
+      </c>
+      <c r="K233" t="n">
+        <v>12</v>
+      </c>
+      <c r="L233" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M233" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N233" s="2" t="n">
+        <v>45831.77951203917</v>
+      </c>
+      <c r="O233" t="n">
+        <v>14.595</v>
+      </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q233" t="n">
+        <v>1.1572735</v>
+      </c>
+      <c r="R233" t="n">
+        <v>12.61153910462825</v>
+      </c>
+      <c r="S233" t="n">
+        <v>1765.995</v>
+      </c>
+      <c r="T233" t="n">
+        <v>1525.996231660018</v>
+      </c>
+      <c r="U233" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V233" t="n">
+        <v>0.02926657263751764</v>
+      </c>
+      <c r="W233" t="n">
+        <v>0.02310959790129696</v>
+      </c>
+      <c r="X233" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y233" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z233" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="AA233" t="n">
         <v>14.27337956428528</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA233"/>
+  <dimension ref="A1:AA241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21614,7 +21614,7 @@
         <v>100</v>
       </c>
       <c r="N226" s="2" t="n">
-        <v>45831.77951203917</v>
+        <v>45831.77951203704</v>
       </c>
       <c r="O226" t="n">
         <v>1</v>
@@ -21705,7 +21705,7 @@
         <v>12.02781891822815</v>
       </c>
       <c r="N227" s="2" t="n">
-        <v>45831.77951203917</v>
+        <v>45831.77951203704</v>
       </c>
       <c r="O227" t="n">
         <v>37.9</v>
@@ -21796,7 +21796,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N228" s="2" t="n">
-        <v>45831.77951203917</v>
+        <v>45831.77951203704</v>
       </c>
       <c r="O228" t="n">
         <v>375</v>
@@ -21891,7 +21891,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N229" s="2" t="n">
-        <v>45831.77951203917</v>
+        <v>45831.77951203704</v>
       </c>
       <c r="O229" t="n">
         <v>0.725</v>
@@ -21982,7 +21982,7 @@
         <v>11.4948091506958</v>
       </c>
       <c r="N230" s="2" t="n">
-        <v>45831.77951203917</v>
+        <v>45831.77951203704</v>
       </c>
       <c r="O230" t="n">
         <v>90</v>
@@ -22077,7 +22077,7 @@
         <v>13.05655670166016</v>
       </c>
       <c r="N231" s="2" t="n">
-        <v>45831.77951203917</v>
+        <v>45831.77951203704</v>
       </c>
       <c r="O231" t="n">
         <v>43.98</v>
@@ -22172,7 +22172,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N232" s="2" t="n">
-        <v>45831.77951203917</v>
+        <v>45831.77951203704</v>
       </c>
       <c r="O232" t="n">
         <v>26.05</v>
@@ -22267,7 +22267,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N233" s="2" t="n">
-        <v>45831.77951203917</v>
+        <v>45831.77951203704</v>
       </c>
       <c r="O233" t="n">
         <v>14.595</v>
@@ -22308,6 +22308,756 @@
         <v>0.540931224822998</v>
       </c>
       <c r="AA233" t="n">
+        <v>14.27337956428528</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F234" t="n">
+        <v>1</v>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H234" t="n">
+        <v>1</v>
+      </c>
+      <c r="I234" t="n">
+        <v>1</v>
+      </c>
+      <c r="J234" t="n">
+        <v>1</v>
+      </c>
+      <c r="K234" t="n">
+        <v>100</v>
+      </c>
+      <c r="L234" t="n">
+        <v>100</v>
+      </c>
+      <c r="M234" t="n">
+        <v>100</v>
+      </c>
+      <c r="N234" s="2" t="n">
+        <v>45831.80908497843</v>
+      </c>
+      <c r="O234" t="n">
+        <v>1</v>
+      </c>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q234" t="n">
+        <v>1</v>
+      </c>
+      <c r="R234" t="n">
+        <v>1</v>
+      </c>
+      <c r="S234" t="n">
+        <v>0</v>
+      </c>
+      <c r="T234" t="n">
+        <v>16.03601332880703</v>
+      </c>
+      <c r="U234" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V234" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W234" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X234" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y234" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z234" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA234" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>DE000A0XYG76</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>DR0.DE</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>DT.ROHSTOFF AG NA O.N.</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F235" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H235" t="n">
+        <v>1</v>
+      </c>
+      <c r="I235" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="J235" t="n">
+        <v>39</v>
+      </c>
+      <c r="K235" t="n">
+        <v>11</v>
+      </c>
+      <c r="L235" t="n">
+        <v>0.4329348504543304</v>
+      </c>
+      <c r="M235" t="n">
+        <v>12.02781891822815</v>
+      </c>
+      <c r="N235" s="2" t="n">
+        <v>45831.80908497843</v>
+      </c>
+      <c r="O235" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q235" t="n">
+        <v>1</v>
+      </c>
+      <c r="R235" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="S235" t="n">
+        <v>1478.1</v>
+      </c>
+      <c r="T235" t="n">
+        <v>1478.1</v>
+      </c>
+      <c r="U235" t="n">
+        <v>34.92</v>
+      </c>
+      <c r="V235" t="n">
+        <v>0.005305039787798282</v>
+      </c>
+      <c r="W235" t="n">
+        <v>0.005305039787798282</v>
+      </c>
+      <c r="X235" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y235" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z235" t="n">
+        <v>0.4742938280105591</v>
+      </c>
+      <c r="AA235" t="n">
+        <v>12.61593472957611</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F236" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H236" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I236" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J236" t="n">
+        <v>3</v>
+      </c>
+      <c r="K236" t="n">
+        <v>10</v>
+      </c>
+      <c r="L236" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M236" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N236" s="2" t="n">
+        <v>45831.80908497843</v>
+      </c>
+      <c r="O236" t="n">
+        <v>375</v>
+      </c>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q236" t="n">
+        <v>0.8556</v>
+      </c>
+      <c r="R236" t="n">
+        <v>438.2889200561009</v>
+      </c>
+      <c r="S236" t="n">
+        <v>1125</v>
+      </c>
+      <c r="T236" t="n">
+        <v>1314.866760168303</v>
+      </c>
+      <c r="U236" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V236" t="n">
+        <v>0.01994745230725714</v>
+      </c>
+      <c r="W236" t="n">
+        <v>0.01764672932577871</v>
+      </c>
+      <c r="X236" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y236" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z236" t="n">
+        <v>0.5007368326187134</v>
+      </c>
+      <c r="AA236" t="n">
+        <v>12.07941150665283</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F237" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H237" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I237" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J237" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K237" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L237" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M237" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N237" s="2" t="n">
+        <v>45831.80908497843</v>
+      </c>
+      <c r="O237" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q237" t="n">
+        <v>1.79281</v>
+      </c>
+      <c r="R237" t="n">
+        <v>0.4043931035636794</v>
+      </c>
+      <c r="S237" t="n">
+        <v>2656.4</v>
+      </c>
+      <c r="T237" t="n">
+        <v>1481.696331457321</v>
+      </c>
+      <c r="U237" t="n">
+        <v>0.3678646934460888</v>
+      </c>
+      <c r="V237" t="n">
+        <v>0</v>
+      </c>
+      <c r="W237" t="n">
+        <v>-0.0101739727020711</v>
+      </c>
+      <c r="X237" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y237" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z237" t="n">
+        <v>0.5391064286231995</v>
+      </c>
+      <c r="AA237" t="n">
+        <v>12.27176785469055</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>NO0012851874</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>DOFG.OL</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr"/>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>DOF GROUP ASA  NK 2,50</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F238" t="n">
+        <v>90.45</v>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="H238" t="n">
+        <v>11.53806</v>
+      </c>
+      <c r="I238" t="n">
+        <v>7.839272806693673</v>
+      </c>
+      <c r="J238" t="n">
+        <v>160</v>
+      </c>
+      <c r="K238" t="n">
+        <v>9</v>
+      </c>
+      <c r="L238" t="n">
+        <v>0.5388140678405762</v>
+      </c>
+      <c r="M238" t="n">
+        <v>11.4948091506958</v>
+      </c>
+      <c r="N238" s="2" t="n">
+        <v>45831.80908497843</v>
+      </c>
+      <c r="O238" t="n">
+        <v>90</v>
+      </c>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="Q238" t="n">
+        <v>11.67485</v>
+      </c>
+      <c r="R238" t="n">
+        <v>7.708878486661499</v>
+      </c>
+      <c r="S238" t="n">
+        <v>14400</v>
+      </c>
+      <c r="T238" t="n">
+        <v>1233.42055786584</v>
+      </c>
+      <c r="U238" t="n">
+        <v>7.055345526024306</v>
+      </c>
+      <c r="V238" t="n">
+        <v>-0.00497512437810943</v>
+      </c>
+      <c r="W238" t="n">
+        <v>-0.01663347140066807</v>
+      </c>
+      <c r="X238" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y238" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z238" t="n">
+        <v>0.5161983370780945</v>
+      </c>
+      <c r="AA238" t="n">
+        <v>10.16883182525635</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F239" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H239" t="n">
+        <v>1</v>
+      </c>
+      <c r="I239" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="J239" t="n">
+        <v>34</v>
+      </c>
+      <c r="K239" t="n">
+        <v>9</v>
+      </c>
+      <c r="L239" t="n">
+        <v>0.6616257429122925</v>
+      </c>
+      <c r="M239" t="n">
+        <v>13.05655670166016</v>
+      </c>
+      <c r="N239" s="2" t="n">
+        <v>45831.80908497843</v>
+      </c>
+      <c r="O239" t="n">
+        <v>43.98</v>
+      </c>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q239" t="n">
+        <v>1</v>
+      </c>
+      <c r="R239" t="n">
+        <v>43.98</v>
+      </c>
+      <c r="S239" t="n">
+        <v>1495.32</v>
+      </c>
+      <c r="T239" t="n">
+        <v>1495.32</v>
+      </c>
+      <c r="U239" t="n">
+        <v>39.582</v>
+      </c>
+      <c r="V239" t="n">
+        <v>0.02757009345794392</v>
+      </c>
+      <c r="W239" t="n">
+        <v>0.02757009345794392</v>
+      </c>
+      <c r="X239" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y239" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z239" t="n">
+        <v>0.6566609740257263</v>
+      </c>
+      <c r="AA239" t="n">
+        <v>12.99397349357605</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F240" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H240" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I240" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J240" t="n">
+        <v>537</v>
+      </c>
+      <c r="K240" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L240" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M240" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N240" s="2" t="n">
+        <v>45831.80908497843</v>
+      </c>
+      <c r="O240" t="n">
+        <v>26.05</v>
+      </c>
+      <c r="P240" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q240" t="n">
+        <v>9.08306</v>
+      </c>
+      <c r="R240" t="n">
+        <v>2.867976210660284</v>
+      </c>
+      <c r="S240" t="n">
+        <v>13988.85</v>
+      </c>
+      <c r="T240" t="n">
+        <v>1540.103225124573</v>
+      </c>
+      <c r="U240" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V240" t="n">
+        <v>0.03373015873015883</v>
+      </c>
+      <c r="W240" t="n">
+        <v>0.02889101791756854</v>
+      </c>
+      <c r="X240" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y240" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z240" t="n">
+        <v>0.5859425067901611</v>
+      </c>
+      <c r="AA240" t="n">
+        <v>12.04357481002808</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F241" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H241" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I241" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J241" t="n">
+        <v>121</v>
+      </c>
+      <c r="K241" t="n">
+        <v>12</v>
+      </c>
+      <c r="L241" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M241" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N241" s="2" t="n">
+        <v>45831.80908497843</v>
+      </c>
+      <c r="O241" t="n">
+        <v>14.575</v>
+      </c>
+      <c r="P241" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q241" t="n">
+        <v>1.1575414</v>
+      </c>
+      <c r="R241" t="n">
+        <v>12.59134230533785</v>
+      </c>
+      <c r="S241" t="n">
+        <v>1763.575</v>
+      </c>
+      <c r="T241" t="n">
+        <v>1523.552418945879</v>
+      </c>
+      <c r="U241" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V241" t="n">
+        <v>0.02785613540197462</v>
+      </c>
+      <c r="W241" t="n">
+        <v>0.02147113498020015</v>
+      </c>
+      <c r="X241" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y241" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z241" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="AA241" t="n">
         <v>14.27337956428528</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA241"/>
+  <dimension ref="A1:AA249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22364,7 +22364,7 @@
         <v>100</v>
       </c>
       <c r="N234" s="2" t="n">
-        <v>45831.80908497843</v>
+        <v>45831.80908497685</v>
       </c>
       <c r="O234" t="n">
         <v>1</v>
@@ -22455,7 +22455,7 @@
         <v>12.02781891822815</v>
       </c>
       <c r="N235" s="2" t="n">
-        <v>45831.80908497843</v>
+        <v>45831.80908497685</v>
       </c>
       <c r="O235" t="n">
         <v>37.9</v>
@@ -22546,7 +22546,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N236" s="2" t="n">
-        <v>45831.80908497843</v>
+        <v>45831.80908497685</v>
       </c>
       <c r="O236" t="n">
         <v>375</v>
@@ -22641,7 +22641,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N237" s="2" t="n">
-        <v>45831.80908497843</v>
+        <v>45831.80908497685</v>
       </c>
       <c r="O237" t="n">
         <v>0.725</v>
@@ -22732,7 +22732,7 @@
         <v>11.4948091506958</v>
       </c>
       <c r="N238" s="2" t="n">
-        <v>45831.80908497843</v>
+        <v>45831.80908497685</v>
       </c>
       <c r="O238" t="n">
         <v>90</v>
@@ -22827,7 +22827,7 @@
         <v>13.05655670166016</v>
       </c>
       <c r="N239" s="2" t="n">
-        <v>45831.80908497843</v>
+        <v>45831.80908497685</v>
       </c>
       <c r="O239" t="n">
         <v>43.98</v>
@@ -22922,7 +22922,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N240" s="2" t="n">
-        <v>45831.80908497843</v>
+        <v>45831.80908497685</v>
       </c>
       <c r="O240" t="n">
         <v>26.05</v>
@@ -23017,7 +23017,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N241" s="2" t="n">
-        <v>45831.80908497843</v>
+        <v>45831.80908497685</v>
       </c>
       <c r="O241" t="n">
         <v>14.575</v>
@@ -23058,6 +23058,756 @@
         <v>0.540931224822998</v>
       </c>
       <c r="AA241" t="n">
+        <v>14.27337956428528</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F242" t="n">
+        <v>1</v>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H242" t="n">
+        <v>1</v>
+      </c>
+      <c r="I242" t="n">
+        <v>1</v>
+      </c>
+      <c r="J242" t="n">
+        <v>1</v>
+      </c>
+      <c r="K242" t="n">
+        <v>100</v>
+      </c>
+      <c r="L242" t="n">
+        <v>100</v>
+      </c>
+      <c r="M242" t="n">
+        <v>100</v>
+      </c>
+      <c r="N242" s="2" t="n">
+        <v>45831.85611282686</v>
+      </c>
+      <c r="O242" t="n">
+        <v>1</v>
+      </c>
+      <c r="P242" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q242" t="n">
+        <v>1</v>
+      </c>
+      <c r="R242" t="n">
+        <v>1</v>
+      </c>
+      <c r="S242" t="n">
+        <v>0</v>
+      </c>
+      <c r="T242" t="n">
+        <v>16.03601332880703</v>
+      </c>
+      <c r="U242" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V242" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W242" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X242" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y242" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z242" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA242" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>DE000A0XYG76</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>DR0.DE</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>DT.ROHSTOFF AG NA O.N.</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F243" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H243" t="n">
+        <v>1</v>
+      </c>
+      <c r="I243" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="J243" t="n">
+        <v>39</v>
+      </c>
+      <c r="K243" t="n">
+        <v>11</v>
+      </c>
+      <c r="L243" t="n">
+        <v>0.4329348504543304</v>
+      </c>
+      <c r="M243" t="n">
+        <v>12.02781891822815</v>
+      </c>
+      <c r="N243" s="2" t="n">
+        <v>45831.85611282686</v>
+      </c>
+      <c r="O243" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="P243" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q243" t="n">
+        <v>1</v>
+      </c>
+      <c r="R243" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="S243" t="n">
+        <v>1478.1</v>
+      </c>
+      <c r="T243" t="n">
+        <v>1478.1</v>
+      </c>
+      <c r="U243" t="n">
+        <v>34.92</v>
+      </c>
+      <c r="V243" t="n">
+        <v>0.005305039787798282</v>
+      </c>
+      <c r="W243" t="n">
+        <v>0.005305039787798282</v>
+      </c>
+      <c r="X243" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y243" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z243" t="n">
+        <v>0.4742938280105591</v>
+      </c>
+      <c r="AA243" t="n">
+        <v>12.61593472957611</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F244" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H244" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I244" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J244" t="n">
+        <v>3</v>
+      </c>
+      <c r="K244" t="n">
+        <v>10</v>
+      </c>
+      <c r="L244" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M244" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N244" s="2" t="n">
+        <v>45831.85611282686</v>
+      </c>
+      <c r="O244" t="n">
+        <v>375</v>
+      </c>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q244" t="n">
+        <v>0.8559</v>
+      </c>
+      <c r="R244" t="n">
+        <v>438.1352961794602</v>
+      </c>
+      <c r="S244" t="n">
+        <v>1125</v>
+      </c>
+      <c r="T244" t="n">
+        <v>1314.405888538381</v>
+      </c>
+      <c r="U244" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V244" t="n">
+        <v>0.01994745230725714</v>
+      </c>
+      <c r="W244" t="n">
+        <v>0.01729003576485133</v>
+      </c>
+      <c r="X244" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y244" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z244" t="n">
+        <v>0.5007368326187134</v>
+      </c>
+      <c r="AA244" t="n">
+        <v>12.07941150665283</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F245" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H245" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I245" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J245" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K245" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L245" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M245" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N245" s="2" t="n">
+        <v>45831.85611282686</v>
+      </c>
+      <c r="O245" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q245" t="n">
+        <v>1.79183</v>
+      </c>
+      <c r="R245" t="n">
+        <v>0.404614277024048</v>
+      </c>
+      <c r="S245" t="n">
+        <v>2656.4</v>
+      </c>
+      <c r="T245" t="n">
+        <v>1482.506711016112</v>
+      </c>
+      <c r="U245" t="n">
+        <v>0.3678646934460888</v>
+      </c>
+      <c r="V245" t="n">
+        <v>0</v>
+      </c>
+      <c r="W245" t="n">
+        <v>-0.009632610236462225</v>
+      </c>
+      <c r="X245" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y245" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z245" t="n">
+        <v>0.5391064286231995</v>
+      </c>
+      <c r="AA245" t="n">
+        <v>12.27176785469055</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>NO0012851874</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>DOFG.OL</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr"/>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>DOF GROUP ASA  NK 2,50</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F246" t="n">
+        <v>90.45</v>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="H246" t="n">
+        <v>11.53806</v>
+      </c>
+      <c r="I246" t="n">
+        <v>7.839272806693673</v>
+      </c>
+      <c r="J246" t="n">
+        <v>160</v>
+      </c>
+      <c r="K246" t="n">
+        <v>9</v>
+      </c>
+      <c r="L246" t="n">
+        <v>0.5388140678405762</v>
+      </c>
+      <c r="M246" t="n">
+        <v>11.4948091506958</v>
+      </c>
+      <c r="N246" s="2" t="n">
+        <v>45831.85611282686</v>
+      </c>
+      <c r="O246" t="n">
+        <v>90</v>
+      </c>
+      <c r="P246" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="Q246" t="n">
+        <v>11.6793</v>
+      </c>
+      <c r="R246" t="n">
+        <v>7.705941280727441</v>
+      </c>
+      <c r="S246" t="n">
+        <v>14400</v>
+      </c>
+      <c r="T246" t="n">
+        <v>1232.950604916391</v>
+      </c>
+      <c r="U246" t="n">
+        <v>7.055345526024306</v>
+      </c>
+      <c r="V246" t="n">
+        <v>-0.00497512437810943</v>
+      </c>
+      <c r="W246" t="n">
+        <v>-0.01700814976771625</v>
+      </c>
+      <c r="X246" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y246" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z246" t="n">
+        <v>0.5161983370780945</v>
+      </c>
+      <c r="AA246" t="n">
+        <v>10.16883182525635</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F247" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H247" t="n">
+        <v>1</v>
+      </c>
+      <c r="I247" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="J247" t="n">
+        <v>34</v>
+      </c>
+      <c r="K247" t="n">
+        <v>9</v>
+      </c>
+      <c r="L247" t="n">
+        <v>0.6616257429122925</v>
+      </c>
+      <c r="M247" t="n">
+        <v>13.05655670166016</v>
+      </c>
+      <c r="N247" s="2" t="n">
+        <v>45831.85611282686</v>
+      </c>
+      <c r="O247" t="n">
+        <v>43.98</v>
+      </c>
+      <c r="P247" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q247" t="n">
+        <v>1</v>
+      </c>
+      <c r="R247" t="n">
+        <v>43.98</v>
+      </c>
+      <c r="S247" t="n">
+        <v>1495.32</v>
+      </c>
+      <c r="T247" t="n">
+        <v>1495.32</v>
+      </c>
+      <c r="U247" t="n">
+        <v>39.582</v>
+      </c>
+      <c r="V247" t="n">
+        <v>0.02757009345794392</v>
+      </c>
+      <c r="W247" t="n">
+        <v>0.02757009345794392</v>
+      </c>
+      <c r="X247" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y247" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z247" t="n">
+        <v>0.6566609740257263</v>
+      </c>
+      <c r="AA247" t="n">
+        <v>12.99397349357605</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F248" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H248" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I248" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J248" t="n">
+        <v>537</v>
+      </c>
+      <c r="K248" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L248" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M248" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N248" s="2" t="n">
+        <v>45831.85611282686</v>
+      </c>
+      <c r="O248" t="n">
+        <v>26.05</v>
+      </c>
+      <c r="P248" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q248" t="n">
+        <v>9.0899</v>
+      </c>
+      <c r="R248" t="n">
+        <v>2.865818105809745</v>
+      </c>
+      <c r="S248" t="n">
+        <v>13988.85</v>
+      </c>
+      <c r="T248" t="n">
+        <v>1538.944322819833</v>
+      </c>
+      <c r="U248" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V248" t="n">
+        <v>0.03373015873015883</v>
+      </c>
+      <c r="W248" t="n">
+        <v>0.02811679437687431</v>
+      </c>
+      <c r="X248" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y248" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z248" t="n">
+        <v>0.5859425067901611</v>
+      </c>
+      <c r="AA248" t="n">
+        <v>12.04357481002808</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F249" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H249" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I249" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J249" t="n">
+        <v>121</v>
+      </c>
+      <c r="K249" t="n">
+        <v>12</v>
+      </c>
+      <c r="L249" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M249" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N249" s="2" t="n">
+        <v>45831.85611282686</v>
+      </c>
+      <c r="O249" t="n">
+        <v>14.56</v>
+      </c>
+      <c r="P249" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q249" t="n">
+        <v>1.1583458</v>
+      </c>
+      <c r="R249" t="n">
+        <v>12.56964889068532</v>
+      </c>
+      <c r="S249" t="n">
+        <v>1761.76</v>
+      </c>
+      <c r="T249" t="n">
+        <v>1520.927515772924</v>
+      </c>
+      <c r="U249" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V249" t="n">
+        <v>0.02679830747531731</v>
+      </c>
+      <c r="W249" t="n">
+        <v>0.01971125931727591</v>
+      </c>
+      <c r="X249" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y249" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z249" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="AA249" t="n">
         <v>14.27337956428528</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA249"/>
+  <dimension ref="A1:AA257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23114,7 +23114,7 @@
         <v>100</v>
       </c>
       <c r="N242" s="2" t="n">
-        <v>45831.85611282686</v>
+        <v>45831.85611282408</v>
       </c>
       <c r="O242" t="n">
         <v>1</v>
@@ -23205,7 +23205,7 @@
         <v>12.02781891822815</v>
       </c>
       <c r="N243" s="2" t="n">
-        <v>45831.85611282686</v>
+        <v>45831.85611282408</v>
       </c>
       <c r="O243" t="n">
         <v>37.9</v>
@@ -23296,7 +23296,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N244" s="2" t="n">
-        <v>45831.85611282686</v>
+        <v>45831.85611282408</v>
       </c>
       <c r="O244" t="n">
         <v>375</v>
@@ -23391,7 +23391,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N245" s="2" t="n">
-        <v>45831.85611282686</v>
+        <v>45831.85611282408</v>
       </c>
       <c r="O245" t="n">
         <v>0.725</v>
@@ -23482,7 +23482,7 @@
         <v>11.4948091506958</v>
       </c>
       <c r="N246" s="2" t="n">
-        <v>45831.85611282686</v>
+        <v>45831.85611282408</v>
       </c>
       <c r="O246" t="n">
         <v>90</v>
@@ -23577,7 +23577,7 @@
         <v>13.05655670166016</v>
       </c>
       <c r="N247" s="2" t="n">
-        <v>45831.85611282686</v>
+        <v>45831.85611282408</v>
       </c>
       <c r="O247" t="n">
         <v>43.98</v>
@@ -23672,7 +23672,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N248" s="2" t="n">
-        <v>45831.85611282686</v>
+        <v>45831.85611282408</v>
       </c>
       <c r="O248" t="n">
         <v>26.05</v>
@@ -23767,7 +23767,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N249" s="2" t="n">
-        <v>45831.85611282686</v>
+        <v>45831.85611282408</v>
       </c>
       <c r="O249" t="n">
         <v>14.56</v>
@@ -23808,6 +23808,756 @@
         <v>0.540931224822998</v>
       </c>
       <c r="AA249" t="n">
+        <v>14.27337956428528</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F250" t="n">
+        <v>1</v>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H250" t="n">
+        <v>1</v>
+      </c>
+      <c r="I250" t="n">
+        <v>1</v>
+      </c>
+      <c r="J250" t="n">
+        <v>1</v>
+      </c>
+      <c r="K250" t="n">
+        <v>100</v>
+      </c>
+      <c r="L250" t="n">
+        <v>100</v>
+      </c>
+      <c r="M250" t="n">
+        <v>100</v>
+      </c>
+      <c r="N250" s="2" t="n">
+        <v>45831.89516832597</v>
+      </c>
+      <c r="O250" t="n">
+        <v>1</v>
+      </c>
+      <c r="P250" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q250" t="n">
+        <v>1</v>
+      </c>
+      <c r="R250" t="n">
+        <v>1</v>
+      </c>
+      <c r="S250" t="n">
+        <v>0</v>
+      </c>
+      <c r="T250" t="n">
+        <v>16.03601332880703</v>
+      </c>
+      <c r="U250" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V250" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W250" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X250" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y250" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z250" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA250" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>DE000A0XYG76</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>DR0.DE</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr"/>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>DT.ROHSTOFF AG NA O.N.</t>
+        </is>
+      </c>
+      <c r="E251" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F251" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H251" t="n">
+        <v>1</v>
+      </c>
+      <c r="I251" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="J251" t="n">
+        <v>39</v>
+      </c>
+      <c r="K251" t="n">
+        <v>11</v>
+      </c>
+      <c r="L251" t="n">
+        <v>0.4329348504543304</v>
+      </c>
+      <c r="M251" t="n">
+        <v>12.02781891822815</v>
+      </c>
+      <c r="N251" s="2" t="n">
+        <v>45831.89516832597</v>
+      </c>
+      <c r="O251" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q251" t="n">
+        <v>1</v>
+      </c>
+      <c r="R251" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="S251" t="n">
+        <v>1478.1</v>
+      </c>
+      <c r="T251" t="n">
+        <v>1478.1</v>
+      </c>
+      <c r="U251" t="n">
+        <v>34.92</v>
+      </c>
+      <c r="V251" t="n">
+        <v>0.005305039787798282</v>
+      </c>
+      <c r="W251" t="n">
+        <v>0.005305039787798282</v>
+      </c>
+      <c r="X251" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y251" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z251" t="n">
+        <v>0.4742938280105591</v>
+      </c>
+      <c r="AA251" t="n">
+        <v>12.61593472957611</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F252" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H252" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I252" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J252" t="n">
+        <v>3</v>
+      </c>
+      <c r="K252" t="n">
+        <v>10</v>
+      </c>
+      <c r="L252" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M252" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N252" s="2" t="n">
+        <v>45831.89516832597</v>
+      </c>
+      <c r="O252" t="n">
+        <v>375</v>
+      </c>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q252" t="n">
+        <v>0.8562</v>
+      </c>
+      <c r="R252" t="n">
+        <v>437.9817799579538</v>
+      </c>
+      <c r="S252" t="n">
+        <v>1125</v>
+      </c>
+      <c r="T252" t="n">
+        <v>1313.945339873861</v>
+      </c>
+      <c r="U252" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V252" t="n">
+        <v>0.01994745230725714</v>
+      </c>
+      <c r="W252" t="n">
+        <v>0.01693359216437318</v>
+      </c>
+      <c r="X252" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y252" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z252" t="n">
+        <v>0.5007368326187134</v>
+      </c>
+      <c r="AA252" t="n">
+        <v>12.07941150665283</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E253" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F253" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H253" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I253" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J253" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K253" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L253" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M253" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N253" s="2" t="n">
+        <v>45831.89516832597</v>
+      </c>
+      <c r="O253" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="P253" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q253" t="n">
+        <v>1.79207</v>
+      </c>
+      <c r="R253" t="n">
+        <v>0.4045600897286378</v>
+      </c>
+      <c r="S253" t="n">
+        <v>2656.4</v>
+      </c>
+      <c r="T253" t="n">
+        <v>1482.308168765729</v>
+      </c>
+      <c r="U253" t="n">
+        <v>0.3678646934460888</v>
+      </c>
+      <c r="V253" t="n">
+        <v>0</v>
+      </c>
+      <c r="W253" t="n">
+        <v>-0.009765243545174052</v>
+      </c>
+      <c r="X253" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y253" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z253" t="n">
+        <v>0.5391064286231995</v>
+      </c>
+      <c r="AA253" t="n">
+        <v>12.27176785469055</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>NO0012851874</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>DOFG.OL</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr"/>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>DOF GROUP ASA  NK 2,50</t>
+        </is>
+      </c>
+      <c r="E254" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F254" t="n">
+        <v>90.45</v>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="H254" t="n">
+        <v>11.53806</v>
+      </c>
+      <c r="I254" t="n">
+        <v>7.839272806693673</v>
+      </c>
+      <c r="J254" t="n">
+        <v>160</v>
+      </c>
+      <c r="K254" t="n">
+        <v>9</v>
+      </c>
+      <c r="L254" t="n">
+        <v>0.5388140678405762</v>
+      </c>
+      <c r="M254" t="n">
+        <v>11.4948091506958</v>
+      </c>
+      <c r="N254" s="2" t="n">
+        <v>45831.89516832597</v>
+      </c>
+      <c r="O254" t="n">
+        <v>90</v>
+      </c>
+      <c r="P254" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="Q254" t="n">
+        <v>11.67581</v>
+      </c>
+      <c r="R254" t="n">
+        <v>7.708244652833508</v>
+      </c>
+      <c r="S254" t="n">
+        <v>14400</v>
+      </c>
+      <c r="T254" t="n">
+        <v>1233.319144453361</v>
+      </c>
+      <c r="U254" t="n">
+        <v>7.055345526024306</v>
+      </c>
+      <c r="V254" t="n">
+        <v>-0.00497512437810943</v>
+      </c>
+      <c r="W254" t="n">
+        <v>-0.01671432505171722</v>
+      </c>
+      <c r="X254" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y254" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z254" t="n">
+        <v>0.5161983370780945</v>
+      </c>
+      <c r="AA254" t="n">
+        <v>10.16883182525635</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E255" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F255" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H255" t="n">
+        <v>1</v>
+      </c>
+      <c r="I255" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="J255" t="n">
+        <v>34</v>
+      </c>
+      <c r="K255" t="n">
+        <v>9</v>
+      </c>
+      <c r="L255" t="n">
+        <v>0.6616257429122925</v>
+      </c>
+      <c r="M255" t="n">
+        <v>13.05655670166016</v>
+      </c>
+      <c r="N255" s="2" t="n">
+        <v>45831.89516832597</v>
+      </c>
+      <c r="O255" t="n">
+        <v>43.98</v>
+      </c>
+      <c r="P255" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q255" t="n">
+        <v>1</v>
+      </c>
+      <c r="R255" t="n">
+        <v>43.98</v>
+      </c>
+      <c r="S255" t="n">
+        <v>1495.32</v>
+      </c>
+      <c r="T255" t="n">
+        <v>1495.32</v>
+      </c>
+      <c r="U255" t="n">
+        <v>39.582</v>
+      </c>
+      <c r="V255" t="n">
+        <v>0.02757009345794392</v>
+      </c>
+      <c r="W255" t="n">
+        <v>0.02757009345794392</v>
+      </c>
+      <c r="X255" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y255" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z255" t="n">
+        <v>0.6566609740257263</v>
+      </c>
+      <c r="AA255" t="n">
+        <v>12.99397349357605</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F256" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H256" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I256" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J256" t="n">
+        <v>537</v>
+      </c>
+      <c r="K256" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L256" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M256" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N256" s="2" t="n">
+        <v>45831.89516832597</v>
+      </c>
+      <c r="O256" t="n">
+        <v>26.05</v>
+      </c>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q256" t="n">
+        <v>9.086370000000001</v>
+      </c>
+      <c r="R256" t="n">
+        <v>2.866931458877418</v>
+      </c>
+      <c r="S256" t="n">
+        <v>13988.85</v>
+      </c>
+      <c r="T256" t="n">
+        <v>1539.542193417173</v>
+      </c>
+      <c r="U256" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V256" t="n">
+        <v>0.03373015873015883</v>
+      </c>
+      <c r="W256" t="n">
+        <v>0.02851621155712891</v>
+      </c>
+      <c r="X256" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y256" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z256" t="n">
+        <v>0.5859425067901611</v>
+      </c>
+      <c r="AA256" t="n">
+        <v>12.04357481002808</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E257" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F257" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H257" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I257" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J257" t="n">
+        <v>121</v>
+      </c>
+      <c r="K257" t="n">
+        <v>12</v>
+      </c>
+      <c r="L257" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M257" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N257" s="2" t="n">
+        <v>45831.89516832597</v>
+      </c>
+      <c r="O257" t="n">
+        <v>14.56</v>
+      </c>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q257" t="n">
+        <v>1.1580776</v>
+      </c>
+      <c r="R257" t="n">
+        <v>12.57255990444855</v>
+      </c>
+      <c r="S257" t="n">
+        <v>1761.76</v>
+      </c>
+      <c r="T257" t="n">
+        <v>1521.279748438274</v>
+      </c>
+      <c r="U257" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V257" t="n">
+        <v>0.02679830747531731</v>
+      </c>
+      <c r="W257" t="n">
+        <v>0.01994741495982444</v>
+      </c>
+      <c r="X257" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y257" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z257" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="AA257" t="n">
         <v>14.27337956428528</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA257"/>
+  <dimension ref="A1:AA265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23864,7 +23864,7 @@
         <v>100</v>
       </c>
       <c r="N250" s="2" t="n">
-        <v>45831.89516832597</v>
+        <v>45831.89516832176</v>
       </c>
       <c r="O250" t="n">
         <v>1</v>
@@ -23955,7 +23955,7 @@
         <v>12.02781891822815</v>
       </c>
       <c r="N251" s="2" t="n">
-        <v>45831.89516832597</v>
+        <v>45831.89516832176</v>
       </c>
       <c r="O251" t="n">
         <v>37.9</v>
@@ -24046,7 +24046,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N252" s="2" t="n">
-        <v>45831.89516832597</v>
+        <v>45831.89516832176</v>
       </c>
       <c r="O252" t="n">
         <v>375</v>
@@ -24141,7 +24141,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N253" s="2" t="n">
-        <v>45831.89516832597</v>
+        <v>45831.89516832176</v>
       </c>
       <c r="O253" t="n">
         <v>0.725</v>
@@ -24232,7 +24232,7 @@
         <v>11.4948091506958</v>
       </c>
       <c r="N254" s="2" t="n">
-        <v>45831.89516832597</v>
+        <v>45831.89516832176</v>
       </c>
       <c r="O254" t="n">
         <v>90</v>
@@ -24327,7 +24327,7 @@
         <v>13.05655670166016</v>
       </c>
       <c r="N255" s="2" t="n">
-        <v>45831.89516832597</v>
+        <v>45831.89516832176</v>
       </c>
       <c r="O255" t="n">
         <v>43.98</v>
@@ -24422,7 +24422,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N256" s="2" t="n">
-        <v>45831.89516832597</v>
+        <v>45831.89516832176</v>
       </c>
       <c r="O256" t="n">
         <v>26.05</v>
@@ -24517,7 +24517,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N257" s="2" t="n">
-        <v>45831.89516832597</v>
+        <v>45831.89516832176</v>
       </c>
       <c r="O257" t="n">
         <v>14.56</v>
@@ -24559,6 +24559,756 @@
       </c>
       <c r="AA257" t="n">
         <v>14.27337956428528</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F258" t="n">
+        <v>1</v>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H258" t="n">
+        <v>1</v>
+      </c>
+      <c r="I258" t="n">
+        <v>1</v>
+      </c>
+      <c r="J258" t="n">
+        <v>1</v>
+      </c>
+      <c r="K258" t="n">
+        <v>100</v>
+      </c>
+      <c r="L258" t="n">
+        <v>100</v>
+      </c>
+      <c r="M258" t="n">
+        <v>100</v>
+      </c>
+      <c r="N258" s="2" t="n">
+        <v>45832.31308749835</v>
+      </c>
+      <c r="O258" t="n">
+        <v>1</v>
+      </c>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q258" t="n">
+        <v>1</v>
+      </c>
+      <c r="R258" t="n">
+        <v>1</v>
+      </c>
+      <c r="S258" t="n">
+        <v>0</v>
+      </c>
+      <c r="T258" t="n">
+        <v>0.2858026033402439</v>
+      </c>
+      <c r="U258" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V258" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W258" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X258" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y258" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z258" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA258" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>DE000A0XYG76</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>DR0.DE</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr"/>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>DT.ROHSTOFF AG NA O.N.</t>
+        </is>
+      </c>
+      <c r="E259" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F259" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H259" t="n">
+        <v>1</v>
+      </c>
+      <c r="I259" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="J259" t="n">
+        <v>39</v>
+      </c>
+      <c r="K259" t="n">
+        <v>11</v>
+      </c>
+      <c r="L259" t="n">
+        <v>0.4329348504543304</v>
+      </c>
+      <c r="M259" t="n">
+        <v>12.02781891822815</v>
+      </c>
+      <c r="N259" s="2" t="n">
+        <v>45832.31308749835</v>
+      </c>
+      <c r="O259" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="P259" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q259" t="n">
+        <v>1</v>
+      </c>
+      <c r="R259" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="S259" t="n">
+        <v>1450.8</v>
+      </c>
+      <c r="T259" t="n">
+        <v>1450.8</v>
+      </c>
+      <c r="U259" t="n">
+        <v>34.92</v>
+      </c>
+      <c r="V259" t="n">
+        <v>-0.01326259946949604</v>
+      </c>
+      <c r="W259" t="n">
+        <v>-0.01326259946949604</v>
+      </c>
+      <c r="X259" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y259" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z259" t="n">
+        <v>0.4433653950691223</v>
+      </c>
+      <c r="AA259" t="n">
+        <v>12.17899870872498</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr"/>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F260" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H260" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I260" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J260" t="n">
+        <v>3</v>
+      </c>
+      <c r="K260" t="n">
+        <v>10</v>
+      </c>
+      <c r="L260" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M260" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N260" s="2" t="n">
+        <v>45832.31308749835</v>
+      </c>
+      <c r="O260" t="n">
+        <v>375</v>
+      </c>
+      <c r="P260" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q260" t="n">
+        <v>0.85407</v>
+      </c>
+      <c r="R260" t="n">
+        <v>439.0740805788753</v>
+      </c>
+      <c r="S260" t="n">
+        <v>1125</v>
+      </c>
+      <c r="T260" t="n">
+        <v>1317.222241736626</v>
+      </c>
+      <c r="U260" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V260" t="n">
+        <v>0.01994745230725714</v>
+      </c>
+      <c r="W260" t="n">
+        <v>0.01946976431807257</v>
+      </c>
+      <c r="X260" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y260" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z260" t="n">
+        <v>0.5300061702728271</v>
+      </c>
+      <c r="AA260" t="n">
+        <v>12.44775533676147</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F261" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H261" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I261" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J261" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K261" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L261" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M261" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N261" s="2" t="n">
+        <v>45832.31308749835</v>
+      </c>
+      <c r="O261" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P261" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q261" t="n">
+        <v>1.7834</v>
+      </c>
+      <c r="R261" t="n">
+        <v>0.420545026354155</v>
+      </c>
+      <c r="S261" t="n">
+        <v>2748</v>
+      </c>
+      <c r="T261" t="n">
+        <v>1540.876976561624</v>
+      </c>
+      <c r="U261" t="n">
+        <v>0.3784905237187395</v>
+      </c>
+      <c r="V261" t="n">
+        <v>0.03448275862068972</v>
+      </c>
+      <c r="W261" t="n">
+        <v>0.02936081023074877</v>
+      </c>
+      <c r="X261" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y261" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z261" t="n">
+        <v>0.4560990333557129</v>
+      </c>
+      <c r="AA261" t="n">
+        <v>11.05002820491791</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F262" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H262" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I262" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J262" t="n">
+        <v>537</v>
+      </c>
+      <c r="K262" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L262" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M262" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N262" s="2" t="n">
+        <v>45832.31308749835</v>
+      </c>
+      <c r="O262" t="n">
+        <v>25.65</v>
+      </c>
+      <c r="P262" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q262" t="n">
+        <v>9.10005</v>
+      </c>
+      <c r="R262" t="n">
+        <v>2.81866583150642</v>
+      </c>
+      <c r="S262" t="n">
+        <v>13774.05</v>
+      </c>
+      <c r="T262" t="n">
+        <v>1513.623551518948</v>
+      </c>
+      <c r="U262" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V262" t="n">
+        <v>0.01785714285714279</v>
+      </c>
+      <c r="W262" t="n">
+        <v>0.01120084112567676</v>
+      </c>
+      <c r="X262" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y262" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z262" t="n">
+        <v>0.5799588561058044</v>
+      </c>
+      <c r="AA262" t="n">
+        <v>12.64349049758911</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E263" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F263" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H263" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I263" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J263" t="n">
+        <v>121</v>
+      </c>
+      <c r="K263" t="n">
+        <v>12</v>
+      </c>
+      <c r="L263" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M263" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N263" s="2" t="n">
+        <v>45832.31308749835</v>
+      </c>
+      <c r="O263" t="n">
+        <v>14.56</v>
+      </c>
+      <c r="P263" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q263" t="n">
+        <v>1.1599582</v>
+      </c>
+      <c r="R263" t="n">
+        <v>12.55217644911687</v>
+      </c>
+      <c r="S263" t="n">
+        <v>1761.76</v>
+      </c>
+      <c r="T263" t="n">
+        <v>1518.813350343142</v>
+      </c>
+      <c r="U263" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V263" t="n">
+        <v>0.02679830747531731</v>
+      </c>
+      <c r="W263" t="n">
+        <v>0.01829380958975713</v>
+      </c>
+      <c r="X263" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y263" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z263" t="n">
+        <v>0.4978975057601929</v>
+      </c>
+      <c r="AA263" t="n">
+        <v>13.57315373420715</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr"/>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E264" s="2" t="n">
+        <v>45832.31308749835</v>
+      </c>
+      <c r="F264" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H264" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I264" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J264" t="n">
+        <v>162</v>
+      </c>
+      <c r="K264" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L264" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M264" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N264" s="2" t="n">
+        <v>45832.31308749835</v>
+      </c>
+      <c r="O264" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="P264" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q264" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="R264" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="S264" t="n">
+        <v>6350.400000000001</v>
+      </c>
+      <c r="T264" t="n">
+        <v>1489.057872633778</v>
+      </c>
+      <c r="U264" t="n">
+        <v>8.272543736854324</v>
+      </c>
+      <c r="V264" t="n">
+        <v>0</v>
+      </c>
+      <c r="W264" t="n">
+        <v>0</v>
+      </c>
+      <c r="X264" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y264" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z264" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="AA264" t="n">
+        <v>12.85747975540161</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E265" s="2" t="n">
+        <v>45832.31308749835</v>
+      </c>
+      <c r="F265" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H265" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I265" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J265" t="n">
+        <v>101</v>
+      </c>
+      <c r="K265" t="n">
+        <v>11</v>
+      </c>
+      <c r="L265" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M265" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N265" s="2" t="n">
+        <v>45832.31308749835</v>
+      </c>
+      <c r="O265" t="n">
+        <v>24528</v>
+      </c>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q265" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="R265" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="S265" t="n">
+        <v>2477328</v>
+      </c>
+      <c r="T265" t="n">
+        <v>1204.761997393351</v>
+      </c>
+      <c r="U265" t="n">
+        <v>10.73550294706946</v>
+      </c>
+      <c r="V265" t="n">
+        <v>0</v>
+      </c>
+      <c r="W265" t="n">
+        <v>0</v>
+      </c>
+      <c r="X265" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y265" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z265" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="AA265" t="n">
+        <v>12.66160106658936</v>
       </c>
     </row>
   </sheetData>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA265"/>
+  <dimension ref="A1:AA273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24614,7 +24614,7 @@
         <v>100</v>
       </c>
       <c r="N258" s="2" t="n">
-        <v>45832.31308749835</v>
+        <v>45832.3130875</v>
       </c>
       <c r="O258" t="n">
         <v>1</v>
@@ -24705,7 +24705,7 @@
         <v>12.02781891822815</v>
       </c>
       <c r="N259" s="2" t="n">
-        <v>45832.31308749835</v>
+        <v>45832.3130875</v>
       </c>
       <c r="O259" t="n">
         <v>37.2</v>
@@ -24796,7 +24796,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N260" s="2" t="n">
-        <v>45832.31308749835</v>
+        <v>45832.3130875</v>
       </c>
       <c r="O260" t="n">
         <v>375</v>
@@ -24891,7 +24891,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N261" s="2" t="n">
-        <v>45832.31308749835</v>
+        <v>45832.3130875</v>
       </c>
       <c r="O261" t="n">
         <v>0.75</v>
@@ -24986,7 +24986,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N262" s="2" t="n">
-        <v>45832.31308749835</v>
+        <v>45832.3130875</v>
       </c>
       <c r="O262" t="n">
         <v>25.65</v>
@@ -25081,7 +25081,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N263" s="2" t="n">
-        <v>45832.31308749835</v>
+        <v>45832.3130875</v>
       </c>
       <c r="O263" t="n">
         <v>14.56</v>
@@ -25143,7 +25143,7 @@
         </is>
       </c>
       <c r="E264" s="2" t="n">
-        <v>45832.31308749835</v>
+        <v>45832.3130875</v>
       </c>
       <c r="F264" t="n">
         <v>39.2</v>
@@ -25172,7 +25172,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N264" s="2" t="n">
-        <v>45832.31308749835</v>
+        <v>45832.3130875</v>
       </c>
       <c r="O264" t="n">
         <v>39.2</v>
@@ -25238,7 +25238,7 @@
         </is>
       </c>
       <c r="E265" s="2" t="n">
-        <v>45832.31308749835</v>
+        <v>45832.3130875</v>
       </c>
       <c r="F265" t="n">
         <v>24528</v>
@@ -25267,7 +25267,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N265" s="2" t="n">
-        <v>45832.31308749835</v>
+        <v>45832.3130875</v>
       </c>
       <c r="O265" t="n">
         <v>24528</v>
@@ -25308,6 +25308,756 @@
         <v>0.4939931035041809</v>
       </c>
       <c r="AA265" t="n">
+        <v>12.66160106658936</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F266" t="n">
+        <v>1</v>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H266" t="n">
+        <v>1</v>
+      </c>
+      <c r="I266" t="n">
+        <v>1</v>
+      </c>
+      <c r="J266" t="n">
+        <v>1</v>
+      </c>
+      <c r="K266" t="n">
+        <v>100</v>
+      </c>
+      <c r="L266" t="n">
+        <v>100</v>
+      </c>
+      <c r="M266" t="n">
+        <v>100</v>
+      </c>
+      <c r="N266" s="2" t="n">
+        <v>45832.36102698342</v>
+      </c>
+      <c r="O266" t="n">
+        <v>1</v>
+      </c>
+      <c r="P266" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q266" t="n">
+        <v>1</v>
+      </c>
+      <c r="R266" t="n">
+        <v>1</v>
+      </c>
+      <c r="S266" t="n">
+        <v>0</v>
+      </c>
+      <c r="T266" t="n">
+        <v>0.2858026033402439</v>
+      </c>
+      <c r="U266" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V266" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W266" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X266" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y266" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z266" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA266" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>DE000A0XYG76</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>DR0.DE</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>DT.ROHSTOFF AG NA O.N.</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F267" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H267" t="n">
+        <v>1</v>
+      </c>
+      <c r="I267" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="J267" t="n">
+        <v>39</v>
+      </c>
+      <c r="K267" t="n">
+        <v>11</v>
+      </c>
+      <c r="L267" t="n">
+        <v>0.4329348504543304</v>
+      </c>
+      <c r="M267" t="n">
+        <v>12.02781891822815</v>
+      </c>
+      <c r="N267" s="2" t="n">
+        <v>45832.36102698342</v>
+      </c>
+      <c r="O267" t="n">
+        <v>36.65</v>
+      </c>
+      <c r="P267" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q267" t="n">
+        <v>1</v>
+      </c>
+      <c r="R267" t="n">
+        <v>36.65</v>
+      </c>
+      <c r="S267" t="n">
+        <v>1429.35</v>
+      </c>
+      <c r="T267" t="n">
+        <v>1429.35</v>
+      </c>
+      <c r="U267" t="n">
+        <v>34.92</v>
+      </c>
+      <c r="V267" t="n">
+        <v>-0.02785145888594176</v>
+      </c>
+      <c r="W267" t="n">
+        <v>-0.02785145888594176</v>
+      </c>
+      <c r="X267" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y267" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z267" t="n">
+        <v>0.4433653950691223</v>
+      </c>
+      <c r="AA267" t="n">
+        <v>12.17899870872498</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr"/>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F268" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H268" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I268" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J268" t="n">
+        <v>3</v>
+      </c>
+      <c r="K268" t="n">
+        <v>10</v>
+      </c>
+      <c r="L268" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M268" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N268" s="2" t="n">
+        <v>45832.36102698342</v>
+      </c>
+      <c r="O268" t="n">
+        <v>374.266</v>
+      </c>
+      <c r="P268" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q268" t="n">
+        <v>0.85254</v>
+      </c>
+      <c r="R268" t="n">
+        <v>439.0011025875619</v>
+      </c>
+      <c r="S268" t="n">
+        <v>1122.798</v>
+      </c>
+      <c r="T268" t="n">
+        <v>1317.003307762686</v>
+      </c>
+      <c r="U268" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V268" t="n">
+        <v>0.01795107516060779</v>
+      </c>
+      <c r="W268" t="n">
+        <v>0.01930031943645583</v>
+      </c>
+      <c r="X268" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y268" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z268" t="n">
+        <v>0.5300061702728271</v>
+      </c>
+      <c r="AA268" t="n">
+        <v>12.44775533676147</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F269" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H269" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I269" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J269" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K269" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L269" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M269" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N269" s="2" t="n">
+        <v>45832.36102698342</v>
+      </c>
+      <c r="O269" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P269" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q269" t="n">
+        <v>1.783</v>
+      </c>
+      <c r="R269" t="n">
+        <v>0.4206393718452047</v>
+      </c>
+      <c r="S269" t="n">
+        <v>2748</v>
+      </c>
+      <c r="T269" t="n">
+        <v>1541.22265844083</v>
+      </c>
+      <c r="U269" t="n">
+        <v>0.3785754346606843</v>
+      </c>
+      <c r="V269" t="n">
+        <v>0.03448275862068972</v>
+      </c>
+      <c r="W269" t="n">
+        <v>0.02959173806254478</v>
+      </c>
+      <c r="X269" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y269" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z269" t="n">
+        <v>0.4560990333557129</v>
+      </c>
+      <c r="AA269" t="n">
+        <v>11.05002820491791</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F270" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H270" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I270" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J270" t="n">
+        <v>537</v>
+      </c>
+      <c r="K270" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L270" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M270" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N270" s="2" t="n">
+        <v>45832.36102698342</v>
+      </c>
+      <c r="O270" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="P270" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q270" t="n">
+        <v>9.098409999999999</v>
+      </c>
+      <c r="R270" t="n">
+        <v>2.824669365306685</v>
+      </c>
+      <c r="S270" t="n">
+        <v>13800.9</v>
+      </c>
+      <c r="T270" t="n">
+        <v>1516.84744916969</v>
+      </c>
+      <c r="U270" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V270" t="n">
+        <v>0.01984126984126977</v>
+      </c>
+      <c r="W270" t="n">
+        <v>0.01335461840594054</v>
+      </c>
+      <c r="X270" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y270" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z270" t="n">
+        <v>0.5799588561058044</v>
+      </c>
+      <c r="AA270" t="n">
+        <v>12.64349049758911</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F271" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H271" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I271" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J271" t="n">
+        <v>121</v>
+      </c>
+      <c r="K271" t="n">
+        <v>12</v>
+      </c>
+      <c r="L271" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M271" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N271" s="2" t="n">
+        <v>45832.36102698342</v>
+      </c>
+      <c r="O271" t="n">
+        <v>14.56</v>
+      </c>
+      <c r="P271" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q271" t="n">
+        <v>1.1594203</v>
+      </c>
+      <c r="R271" t="n">
+        <v>12.5579998901175</v>
+      </c>
+      <c r="S271" t="n">
+        <v>1761.76</v>
+      </c>
+      <c r="T271" t="n">
+        <v>1519.517986704217</v>
+      </c>
+      <c r="U271" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V271" t="n">
+        <v>0.02679830747531731</v>
+      </c>
+      <c r="W271" t="n">
+        <v>0.01876623554277712</v>
+      </c>
+      <c r="X271" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y271" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z271" t="n">
+        <v>0.4978975057601929</v>
+      </c>
+      <c r="AA271" t="n">
+        <v>13.57315373420715</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr"/>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E272" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F272" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H272" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I272" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J272" t="n">
+        <v>162</v>
+      </c>
+      <c r="K272" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L272" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M272" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N272" s="2" t="n">
+        <v>45832.36102698342</v>
+      </c>
+      <c r="O272" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="P272" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q272" t="n">
+        <v>4.26078</v>
+      </c>
+      <c r="R272" t="n">
+        <v>9.059374105210784</v>
+      </c>
+      <c r="S272" t="n">
+        <v>6253.2</v>
+      </c>
+      <c r="T272" t="n">
+        <v>1467.618605044147</v>
+      </c>
+      <c r="U272" t="n">
+        <v>8.272543736854324</v>
+      </c>
+      <c r="V272" t="n">
+        <v>-0.01530612244897966</v>
+      </c>
+      <c r="W272" t="n">
+        <v>-0.01439787397363568</v>
+      </c>
+      <c r="X272" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y272" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z272" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="AA272" t="n">
+        <v>12.85747975540161</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E273" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F273" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H273" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I273" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J273" t="n">
+        <v>101</v>
+      </c>
+      <c r="K273" t="n">
+        <v>11</v>
+      </c>
+      <c r="L273" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M273" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N273" s="2" t="n">
+        <v>45832.36102698342</v>
+      </c>
+      <c r="O273" t="n">
+        <v>25052</v>
+      </c>
+      <c r="P273" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q273" t="n">
+        <v>2054.71</v>
+      </c>
+      <c r="R273" t="n">
+        <v>12.19247485046552</v>
+      </c>
+      <c r="S273" t="n">
+        <v>2530252</v>
+      </c>
+      <c r="T273" t="n">
+        <v>1231.439959897017</v>
+      </c>
+      <c r="U273" t="n">
+        <v>10.97322736541896</v>
+      </c>
+      <c r="V273" t="n">
+        <v>0.02136333985649053</v>
+      </c>
+      <c r="W273" t="n">
+        <v>0.02214376164037968</v>
+      </c>
+      <c r="X273" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y273" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z273" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="AA273" t="n">
         <v>12.66160106658936</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA273"/>
+  <dimension ref="A1:AA281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25364,7 +25364,7 @@
         <v>100</v>
       </c>
       <c r="N266" s="2" t="n">
-        <v>45832.36102698342</v>
+        <v>45832.36102697917</v>
       </c>
       <c r="O266" t="n">
         <v>1</v>
@@ -25455,7 +25455,7 @@
         <v>12.02781891822815</v>
       </c>
       <c r="N267" s="2" t="n">
-        <v>45832.36102698342</v>
+        <v>45832.36102697917</v>
       </c>
       <c r="O267" t="n">
         <v>36.65</v>
@@ -25546,7 +25546,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N268" s="2" t="n">
-        <v>45832.36102698342</v>
+        <v>45832.36102697917</v>
       </c>
       <c r="O268" t="n">
         <v>374.266</v>
@@ -25641,7 +25641,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N269" s="2" t="n">
-        <v>45832.36102698342</v>
+        <v>45832.36102697917</v>
       </c>
       <c r="O269" t="n">
         <v>0.75</v>
@@ -25736,7 +25736,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N270" s="2" t="n">
-        <v>45832.36102698342</v>
+        <v>45832.36102697917</v>
       </c>
       <c r="O270" t="n">
         <v>25.7</v>
@@ -25831,7 +25831,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N271" s="2" t="n">
-        <v>45832.36102698342</v>
+        <v>45832.36102697917</v>
       </c>
       <c r="O271" t="n">
         <v>14.56</v>
@@ -25922,7 +25922,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N272" s="2" t="n">
-        <v>45832.36102698342</v>
+        <v>45832.36102697917</v>
       </c>
       <c r="O272" t="n">
         <v>38.6</v>
@@ -26017,7 +26017,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N273" s="2" t="n">
-        <v>45832.36102698342</v>
+        <v>45832.36102697917</v>
       </c>
       <c r="O273" t="n">
         <v>25052</v>
@@ -26058,6 +26058,756 @@
         <v>0.4939931035041809</v>
       </c>
       <c r="AA273" t="n">
+        <v>12.66160106658936</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F274" t="n">
+        <v>1</v>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H274" t="n">
+        <v>1</v>
+      </c>
+      <c r="I274" t="n">
+        <v>1</v>
+      </c>
+      <c r="J274" t="n">
+        <v>1</v>
+      </c>
+      <c r="K274" t="n">
+        <v>100</v>
+      </c>
+      <c r="L274" t="n">
+        <v>100</v>
+      </c>
+      <c r="M274" t="n">
+        <v>100</v>
+      </c>
+      <c r="N274" s="2" t="n">
+        <v>45832.39878708099</v>
+      </c>
+      <c r="O274" t="n">
+        <v>1</v>
+      </c>
+      <c r="P274" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q274" t="n">
+        <v>1</v>
+      </c>
+      <c r="R274" t="n">
+        <v>1</v>
+      </c>
+      <c r="S274" t="n">
+        <v>0</v>
+      </c>
+      <c r="T274" t="n">
+        <v>0.2858026033402439</v>
+      </c>
+      <c r="U274" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V274" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W274" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X274" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y274" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z274" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA274" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>DE000A0XYG76</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>DR0.DE</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr"/>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>DT.ROHSTOFF AG NA O.N.</t>
+        </is>
+      </c>
+      <c r="E275" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F275" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H275" t="n">
+        <v>1</v>
+      </c>
+      <c r="I275" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="J275" t="n">
+        <v>39</v>
+      </c>
+      <c r="K275" t="n">
+        <v>11</v>
+      </c>
+      <c r="L275" t="n">
+        <v>0.4329348504543304</v>
+      </c>
+      <c r="M275" t="n">
+        <v>12.02781891822815</v>
+      </c>
+      <c r="N275" s="2" t="n">
+        <v>45832.39878708099</v>
+      </c>
+      <c r="O275" t="n">
+        <v>36.45</v>
+      </c>
+      <c r="P275" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q275" t="n">
+        <v>1</v>
+      </c>
+      <c r="R275" t="n">
+        <v>36.45</v>
+      </c>
+      <c r="S275" t="n">
+        <v>1421.55</v>
+      </c>
+      <c r="T275" t="n">
+        <v>1421.55</v>
+      </c>
+      <c r="U275" t="n">
+        <v>34.92</v>
+      </c>
+      <c r="V275" t="n">
+        <v>-0.03315649867374004</v>
+      </c>
+      <c r="W275" t="n">
+        <v>-0.03315649867374004</v>
+      </c>
+      <c r="X275" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y275" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z275" t="n">
+        <v>0.4433653950691223</v>
+      </c>
+      <c r="AA275" t="n">
+        <v>12.17899870872498</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr"/>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E276" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F276" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H276" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I276" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J276" t="n">
+        <v>3</v>
+      </c>
+      <c r="K276" t="n">
+        <v>10</v>
+      </c>
+      <c r="L276" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M276" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N276" s="2" t="n">
+        <v>45832.39878708099</v>
+      </c>
+      <c r="O276" t="n">
+        <v>374.555</v>
+      </c>
+      <c r="P276" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q276" t="n">
+        <v>0.85275</v>
+      </c>
+      <c r="R276" t="n">
+        <v>439.2318968044562</v>
+      </c>
+      <c r="S276" t="n">
+        <v>1123.665</v>
+      </c>
+      <c r="T276" t="n">
+        <v>1317.695690413369</v>
+      </c>
+      <c r="U276" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V276" t="n">
+        <v>0.01873711466385264</v>
+      </c>
+      <c r="W276" t="n">
+        <v>0.01983619193795505</v>
+      </c>
+      <c r="X276" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y276" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z276" t="n">
+        <v>0.5300061702728271</v>
+      </c>
+      <c r="AA276" t="n">
+        <v>12.44775533676147</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E277" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F277" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H277" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I277" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J277" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K277" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L277" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M277" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N277" s="2" t="n">
+        <v>45832.39878708099</v>
+      </c>
+      <c r="O277" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P277" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q277" t="n">
+        <v>1.78261</v>
+      </c>
+      <c r="R277" t="n">
+        <v>0.4207313994648297</v>
+      </c>
+      <c r="S277" t="n">
+        <v>2748</v>
+      </c>
+      <c r="T277" t="n">
+        <v>1541.559847639136</v>
+      </c>
+      <c r="U277" t="n">
+        <v>0.3786582595183467</v>
+      </c>
+      <c r="V277" t="n">
+        <v>0.03448275862068972</v>
+      </c>
+      <c r="W277" t="n">
+        <v>0.02981699248041769</v>
+      </c>
+      <c r="X277" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y277" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z277" t="n">
+        <v>0.4560990333557129</v>
+      </c>
+      <c r="AA277" t="n">
+        <v>11.05002820491791</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E278" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F278" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H278" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I278" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J278" t="n">
+        <v>537</v>
+      </c>
+      <c r="K278" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L278" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M278" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N278" s="2" t="n">
+        <v>45832.39878708099</v>
+      </c>
+      <c r="O278" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="P278" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q278" t="n">
+        <v>9.11388</v>
+      </c>
+      <c r="R278" t="n">
+        <v>2.81987474050569</v>
+      </c>
+      <c r="S278" t="n">
+        <v>13800.9</v>
+      </c>
+      <c r="T278" t="n">
+        <v>1514.272735651556</v>
+      </c>
+      <c r="U278" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V278" t="n">
+        <v>0.01984126984126977</v>
+      </c>
+      <c r="W278" t="n">
+        <v>0.01163453914806789</v>
+      </c>
+      <c r="X278" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y278" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z278" t="n">
+        <v>0.5799588561058044</v>
+      </c>
+      <c r="AA278" t="n">
+        <v>12.64349049758911</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E279" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F279" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H279" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I279" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J279" t="n">
+        <v>121</v>
+      </c>
+      <c r="K279" t="n">
+        <v>12</v>
+      </c>
+      <c r="L279" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M279" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N279" s="2" t="n">
+        <v>45832.39878708099</v>
+      </c>
+      <c r="O279" t="n">
+        <v>14.56</v>
+      </c>
+      <c r="P279" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q279" t="n">
+        <v>1.1614401</v>
+      </c>
+      <c r="R279" t="n">
+        <v>12.53616092642229</v>
+      </c>
+      <c r="S279" t="n">
+        <v>1761.76</v>
+      </c>
+      <c r="T279" t="n">
+        <v>1516.875472097097</v>
+      </c>
+      <c r="U279" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V279" t="n">
+        <v>0.02679830747531731</v>
+      </c>
+      <c r="W279" t="n">
+        <v>0.01699455223121471</v>
+      </c>
+      <c r="X279" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y279" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z279" t="n">
+        <v>0.4978975057601929</v>
+      </c>
+      <c r="AA279" t="n">
+        <v>13.57315373420715</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr"/>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E280" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F280" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H280" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I280" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J280" t="n">
+        <v>162</v>
+      </c>
+      <c r="K280" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L280" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M280" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N280" s="2" t="n">
+        <v>45832.39878708099</v>
+      </c>
+      <c r="O280" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="P280" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q280" t="n">
+        <v>4.25658</v>
+      </c>
+      <c r="R280" t="n">
+        <v>9.138792175878288</v>
+      </c>
+      <c r="S280" t="n">
+        <v>6301.8</v>
+      </c>
+      <c r="T280" t="n">
+        <v>1480.484332492283</v>
+      </c>
+      <c r="U280" t="n">
+        <v>8.272543736854324</v>
+      </c>
+      <c r="V280" t="n">
+        <v>-0.007653061224489943</v>
+      </c>
+      <c r="W280" t="n">
+        <v>-0.00575769437780882</v>
+      </c>
+      <c r="X280" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y280" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z280" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="AA280" t="n">
+        <v>12.85747975540161</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E281" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F281" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H281" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I281" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J281" t="n">
+        <v>101</v>
+      </c>
+      <c r="K281" t="n">
+        <v>11</v>
+      </c>
+      <c r="L281" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M281" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N281" s="2" t="n">
+        <v>45832.39878708099</v>
+      </c>
+      <c r="O281" t="n">
+        <v>25113</v>
+      </c>
+      <c r="P281" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q281" t="n">
+        <v>2054.07</v>
+      </c>
+      <c r="R281" t="n">
+        <v>12.22597087733135</v>
+      </c>
+      <c r="S281" t="n">
+        <v>2536413</v>
+      </c>
+      <c r="T281" t="n">
+        <v>1234.823058610466</v>
+      </c>
+      <c r="U281" t="n">
+        <v>11.00337378959821</v>
+      </c>
+      <c r="V281" t="n">
+        <v>0.02385029354207435</v>
+      </c>
+      <c r="W281" t="n">
+        <v>0.02495186707594987</v>
+      </c>
+      <c r="X281" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y281" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z281" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="AA281" t="n">
         <v>12.66160106658936</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA281"/>
+  <dimension ref="A1:AA289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26114,7 +26114,7 @@
         <v>100</v>
       </c>
       <c r="N274" s="2" t="n">
-        <v>45832.39878708099</v>
+        <v>45832.39878708333</v>
       </c>
       <c r="O274" t="n">
         <v>1</v>
@@ -26205,7 +26205,7 @@
         <v>12.02781891822815</v>
       </c>
       <c r="N275" s="2" t="n">
-        <v>45832.39878708099</v>
+        <v>45832.39878708333</v>
       </c>
       <c r="O275" t="n">
         <v>36.45</v>
@@ -26296,7 +26296,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N276" s="2" t="n">
-        <v>45832.39878708099</v>
+        <v>45832.39878708333</v>
       </c>
       <c r="O276" t="n">
         <v>374.555</v>
@@ -26391,7 +26391,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N277" s="2" t="n">
-        <v>45832.39878708099</v>
+        <v>45832.39878708333</v>
       </c>
       <c r="O277" t="n">
         <v>0.75</v>
@@ -26486,7 +26486,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N278" s="2" t="n">
-        <v>45832.39878708099</v>
+        <v>45832.39878708333</v>
       </c>
       <c r="O278" t="n">
         <v>25.7</v>
@@ -26581,7 +26581,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N279" s="2" t="n">
-        <v>45832.39878708099</v>
+        <v>45832.39878708333</v>
       </c>
       <c r="O279" t="n">
         <v>14.56</v>
@@ -26672,7 +26672,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N280" s="2" t="n">
-        <v>45832.39878708099</v>
+        <v>45832.39878708333</v>
       </c>
       <c r="O280" t="n">
         <v>38.9</v>
@@ -26767,7 +26767,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N281" s="2" t="n">
-        <v>45832.39878708099</v>
+        <v>45832.39878708333</v>
       </c>
       <c r="O281" t="n">
         <v>25113</v>
@@ -26808,6 +26808,756 @@
         <v>0.4939931035041809</v>
       </c>
       <c r="AA281" t="n">
+        <v>12.66160106658936</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F282" t="n">
+        <v>1</v>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H282" t="n">
+        <v>1</v>
+      </c>
+      <c r="I282" t="n">
+        <v>1</v>
+      </c>
+      <c r="J282" t="n">
+        <v>1</v>
+      </c>
+      <c r="K282" t="n">
+        <v>100</v>
+      </c>
+      <c r="L282" t="n">
+        <v>100</v>
+      </c>
+      <c r="M282" t="n">
+        <v>100</v>
+      </c>
+      <c r="N282" s="2" t="n">
+        <v>45832.44248545185</v>
+      </c>
+      <c r="O282" t="n">
+        <v>1</v>
+      </c>
+      <c r="P282" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q282" t="n">
+        <v>1</v>
+      </c>
+      <c r="R282" t="n">
+        <v>1</v>
+      </c>
+      <c r="S282" t="n">
+        <v>0</v>
+      </c>
+      <c r="T282" t="n">
+        <v>0.2858026033402439</v>
+      </c>
+      <c r="U282" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V282" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W282" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X282" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y282" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z282" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA282" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>DE000A0XYG76</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>DR0.DE</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr"/>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>DT.ROHSTOFF AG NA O.N.</t>
+        </is>
+      </c>
+      <c r="E283" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F283" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H283" t="n">
+        <v>1</v>
+      </c>
+      <c r="I283" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="J283" t="n">
+        <v>39</v>
+      </c>
+      <c r="K283" t="n">
+        <v>11</v>
+      </c>
+      <c r="L283" t="n">
+        <v>0.4329348504543304</v>
+      </c>
+      <c r="M283" t="n">
+        <v>12.02781891822815</v>
+      </c>
+      <c r="N283" s="2" t="n">
+        <v>45832.44248545185</v>
+      </c>
+      <c r="O283" t="n">
+        <v>36.45</v>
+      </c>
+      <c r="P283" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q283" t="n">
+        <v>1</v>
+      </c>
+      <c r="R283" t="n">
+        <v>36.45</v>
+      </c>
+      <c r="S283" t="n">
+        <v>1421.55</v>
+      </c>
+      <c r="T283" t="n">
+        <v>1421.55</v>
+      </c>
+      <c r="U283" t="n">
+        <v>34.92</v>
+      </c>
+      <c r="V283" t="n">
+        <v>-0.03315649867374004</v>
+      </c>
+      <c r="W283" t="n">
+        <v>-0.03315649867374004</v>
+      </c>
+      <c r="X283" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y283" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z283" t="n">
+        <v>0.4433653950691223</v>
+      </c>
+      <c r="AA283" t="n">
+        <v>12.17899870872498</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr"/>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E284" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F284" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H284" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I284" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J284" t="n">
+        <v>3</v>
+      </c>
+      <c r="K284" t="n">
+        <v>10</v>
+      </c>
+      <c r="L284" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M284" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N284" s="2" t="n">
+        <v>45832.44248545185</v>
+      </c>
+      <c r="O284" t="n">
+        <v>374.35</v>
+      </c>
+      <c r="P284" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q284" t="n">
+        <v>0.85209</v>
+      </c>
+      <c r="R284" t="n">
+        <v>439.3315260125104</v>
+      </c>
+      <c r="S284" t="n">
+        <v>1123.05</v>
+      </c>
+      <c r="T284" t="n">
+        <v>1317.994578037531</v>
+      </c>
+      <c r="U284" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V284" t="n">
+        <v>0.01817954338992456</v>
+      </c>
+      <c r="W284" t="n">
+        <v>0.02006751728770073</v>
+      </c>
+      <c r="X284" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y284" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z284" t="n">
+        <v>0.5300061702728271</v>
+      </c>
+      <c r="AA284" t="n">
+        <v>12.44775533676147</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E285" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F285" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H285" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I285" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J285" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K285" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L285" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M285" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N285" s="2" t="n">
+        <v>45832.44248545185</v>
+      </c>
+      <c r="O285" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P285" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q285" t="n">
+        <v>1.78144</v>
+      </c>
+      <c r="R285" t="n">
+        <v>0.4210077240883779</v>
+      </c>
+      <c r="S285" t="n">
+        <v>2748</v>
+      </c>
+      <c r="T285" t="n">
+        <v>1542.572301059817</v>
+      </c>
+      <c r="U285" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="V285" t="n">
+        <v>0.03448275862068972</v>
+      </c>
+      <c r="W285" t="n">
+        <v>0.03049334749725907</v>
+      </c>
+      <c r="X285" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y285" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z285" t="n">
+        <v>0.4560990333557129</v>
+      </c>
+      <c r="AA285" t="n">
+        <v>11.05002820491791</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E286" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F286" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H286" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I286" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J286" t="n">
+        <v>537</v>
+      </c>
+      <c r="K286" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L286" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M286" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N286" s="2" t="n">
+        <v>45832.44248545185</v>
+      </c>
+      <c r="O286" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="P286" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q286" t="n">
+        <v>9.102650000000001</v>
+      </c>
+      <c r="R286" t="n">
+        <v>2.823353638775521</v>
+      </c>
+      <c r="S286" t="n">
+        <v>13800.9</v>
+      </c>
+      <c r="T286" t="n">
+        <v>1516.140904022455</v>
+      </c>
+      <c r="U286" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V286" t="n">
+        <v>0.01984126984126977</v>
+      </c>
+      <c r="W286" t="n">
+        <v>0.0128825994244306</v>
+      </c>
+      <c r="X286" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y286" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z286" t="n">
+        <v>0.5799588561058044</v>
+      </c>
+      <c r="AA286" t="n">
+        <v>12.64349049758911</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E287" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F287" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H287" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I287" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J287" t="n">
+        <v>121</v>
+      </c>
+      <c r="K287" t="n">
+        <v>12</v>
+      </c>
+      <c r="L287" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M287" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N287" s="2" t="n">
+        <v>45832.44248545185</v>
+      </c>
+      <c r="O287" t="n">
+        <v>14.56</v>
+      </c>
+      <c r="P287" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q287" t="n">
+        <v>1.1599582</v>
+      </c>
+      <c r="R287" t="n">
+        <v>12.55217644911687</v>
+      </c>
+      <c r="S287" t="n">
+        <v>1761.76</v>
+      </c>
+      <c r="T287" t="n">
+        <v>1518.813350343142</v>
+      </c>
+      <c r="U287" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V287" t="n">
+        <v>0.02679830747531731</v>
+      </c>
+      <c r="W287" t="n">
+        <v>0.01829380958975713</v>
+      </c>
+      <c r="X287" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y287" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z287" t="n">
+        <v>0.4978975057601929</v>
+      </c>
+      <c r="AA287" t="n">
+        <v>13.57315373420715</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr"/>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E288" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F288" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H288" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I288" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J288" t="n">
+        <v>162</v>
+      </c>
+      <c r="K288" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L288" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M288" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N288" s="2" t="n">
+        <v>45832.44248545185</v>
+      </c>
+      <c r="O288" t="n">
+        <v>38.95</v>
+      </c>
+      <c r="P288" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q288" t="n">
+        <v>4.25755</v>
+      </c>
+      <c r="R288" t="n">
+        <v>9.148453923030852</v>
+      </c>
+      <c r="S288" t="n">
+        <v>6309.900000000001</v>
+      </c>
+      <c r="T288" t="n">
+        <v>1482.049535530998</v>
+      </c>
+      <c r="U288" t="n">
+        <v>8.272543736854324</v>
+      </c>
+      <c r="V288" t="n">
+        <v>-0.006377551020408156</v>
+      </c>
+      <c r="W288" t="n">
+        <v>-0.004706557905895359</v>
+      </c>
+      <c r="X288" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y288" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z288" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="AA288" t="n">
+        <v>12.85747975540161</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E289" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F289" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H289" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I289" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J289" t="n">
+        <v>101</v>
+      </c>
+      <c r="K289" t="n">
+        <v>11</v>
+      </c>
+      <c r="L289" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M289" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N289" s="2" t="n">
+        <v>45832.44248545185</v>
+      </c>
+      <c r="O289" t="n">
+        <v>24995</v>
+      </c>
+      <c r="P289" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q289" t="n">
+        <v>2054.49</v>
+      </c>
+      <c r="R289" t="n">
+        <v>12.16603633991891</v>
+      </c>
+      <c r="S289" t="n">
+        <v>2524495</v>
+      </c>
+      <c r="T289" t="n">
+        <v>1228.76967033181</v>
+      </c>
+      <c r="U289" t="n">
+        <v>11.00337378959821</v>
+      </c>
+      <c r="V289" t="n">
+        <v>0.01903946510110899</v>
+      </c>
+      <c r="W289" t="n">
+        <v>0.0199273159266331</v>
+      </c>
+      <c r="X289" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y289" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z289" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="AA289" t="n">
         <v>12.66160106658936</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA289"/>
+  <dimension ref="A1:AA297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26864,7 +26864,7 @@
         <v>100</v>
       </c>
       <c r="N282" s="2" t="n">
-        <v>45832.44248545185</v>
+        <v>45832.44248545139</v>
       </c>
       <c r="O282" t="n">
         <v>1</v>
@@ -26955,7 +26955,7 @@
         <v>12.02781891822815</v>
       </c>
       <c r="N283" s="2" t="n">
-        <v>45832.44248545185</v>
+        <v>45832.44248545139</v>
       </c>
       <c r="O283" t="n">
         <v>36.45</v>
@@ -27046,7 +27046,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N284" s="2" t="n">
-        <v>45832.44248545185</v>
+        <v>45832.44248545139</v>
       </c>
       <c r="O284" t="n">
         <v>374.35</v>
@@ -27141,7 +27141,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N285" s="2" t="n">
-        <v>45832.44248545185</v>
+        <v>45832.44248545139</v>
       </c>
       <c r="O285" t="n">
         <v>0.75</v>
@@ -27236,7 +27236,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N286" s="2" t="n">
-        <v>45832.44248545185</v>
+        <v>45832.44248545139</v>
       </c>
       <c r="O286" t="n">
         <v>25.7</v>
@@ -27331,7 +27331,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N287" s="2" t="n">
-        <v>45832.44248545185</v>
+        <v>45832.44248545139</v>
       </c>
       <c r="O287" t="n">
         <v>14.56</v>
@@ -27422,7 +27422,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N288" s="2" t="n">
-        <v>45832.44248545185</v>
+        <v>45832.44248545139</v>
       </c>
       <c r="O288" t="n">
         <v>38.95</v>
@@ -27517,7 +27517,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N289" s="2" t="n">
-        <v>45832.44248545185</v>
+        <v>45832.44248545139</v>
       </c>
       <c r="O289" t="n">
         <v>24995</v>
@@ -27558,6 +27558,756 @@
         <v>0.4939931035041809</v>
       </c>
       <c r="AA289" t="n">
+        <v>12.66160106658936</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F290" t="n">
+        <v>1</v>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H290" t="n">
+        <v>1</v>
+      </c>
+      <c r="I290" t="n">
+        <v>1</v>
+      </c>
+      <c r="J290" t="n">
+        <v>1</v>
+      </c>
+      <c r="K290" t="n">
+        <v>100</v>
+      </c>
+      <c r="L290" t="n">
+        <v>100</v>
+      </c>
+      <c r="M290" t="n">
+        <v>100</v>
+      </c>
+      <c r="N290" s="2" t="n">
+        <v>45832.47712098862</v>
+      </c>
+      <c r="O290" t="n">
+        <v>1</v>
+      </c>
+      <c r="P290" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q290" t="n">
+        <v>1</v>
+      </c>
+      <c r="R290" t="n">
+        <v>1</v>
+      </c>
+      <c r="S290" t="n">
+        <v>0</v>
+      </c>
+      <c r="T290" t="n">
+        <v>0.2858026033402439</v>
+      </c>
+      <c r="U290" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V290" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W290" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X290" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y290" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z290" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA290" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>DE000A0XYG76</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>DR0.DE</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr"/>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>DT.ROHSTOFF AG NA O.N.</t>
+        </is>
+      </c>
+      <c r="E291" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F291" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H291" t="n">
+        <v>1</v>
+      </c>
+      <c r="I291" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="J291" t="n">
+        <v>39</v>
+      </c>
+      <c r="K291" t="n">
+        <v>11</v>
+      </c>
+      <c r="L291" t="n">
+        <v>0.4329348504543304</v>
+      </c>
+      <c r="M291" t="n">
+        <v>12.02781891822815</v>
+      </c>
+      <c r="N291" s="2" t="n">
+        <v>45832.47712098862</v>
+      </c>
+      <c r="O291" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="P291" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q291" t="n">
+        <v>1</v>
+      </c>
+      <c r="R291" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="S291" t="n">
+        <v>1419.6</v>
+      </c>
+      <c r="T291" t="n">
+        <v>1419.6</v>
+      </c>
+      <c r="U291" t="n">
+        <v>34.92</v>
+      </c>
+      <c r="V291" t="n">
+        <v>-0.03448275862068972</v>
+      </c>
+      <c r="W291" t="n">
+        <v>-0.03448275862068972</v>
+      </c>
+      <c r="X291" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y291" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z291" t="n">
+        <v>0.4433653950691223</v>
+      </c>
+      <c r="AA291" t="n">
+        <v>12.17899870872498</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr"/>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E292" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F292" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H292" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I292" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J292" t="n">
+        <v>3</v>
+      </c>
+      <c r="K292" t="n">
+        <v>10</v>
+      </c>
+      <c r="L292" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M292" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N292" s="2" t="n">
+        <v>45832.47712098862</v>
+      </c>
+      <c r="O292" t="n">
+        <v>374.35</v>
+      </c>
+      <c r="P292" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q292" t="n">
+        <v>0.85248</v>
+      </c>
+      <c r="R292" t="n">
+        <v>439.1305367867868</v>
+      </c>
+      <c r="S292" t="n">
+        <v>1123.05</v>
+      </c>
+      <c r="T292" t="n">
+        <v>1317.391610360361</v>
+      </c>
+      <c r="U292" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V292" t="n">
+        <v>0.01817954338992456</v>
+      </c>
+      <c r="W292" t="n">
+        <v>0.01960084788578853</v>
+      </c>
+      <c r="X292" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y292" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z292" t="n">
+        <v>0.5300061702728271</v>
+      </c>
+      <c r="AA292" t="n">
+        <v>12.44775533676147</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E293" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F293" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H293" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I293" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J293" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K293" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L293" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M293" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N293" s="2" t="n">
+        <v>45832.47712098862</v>
+      </c>
+      <c r="O293" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P293" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q293" t="n">
+        <v>1.78285</v>
+      </c>
+      <c r="R293" t="n">
+        <v>0.4206747623187593</v>
+      </c>
+      <c r="S293" t="n">
+        <v>2748</v>
+      </c>
+      <c r="T293" t="n">
+        <v>1541.352329135934</v>
+      </c>
+      <c r="U293" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="V293" t="n">
+        <v>0.03448275862068972</v>
+      </c>
+      <c r="W293" t="n">
+        <v>0.02967836271448365</v>
+      </c>
+      <c r="X293" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y293" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z293" t="n">
+        <v>0.4560990333557129</v>
+      </c>
+      <c r="AA293" t="n">
+        <v>11.05002820491791</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E294" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F294" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H294" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I294" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J294" t="n">
+        <v>537</v>
+      </c>
+      <c r="K294" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L294" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M294" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N294" s="2" t="n">
+        <v>45832.47712098862</v>
+      </c>
+      <c r="O294" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="P294" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q294" t="n">
+        <v>9.110659999999999</v>
+      </c>
+      <c r="R294" t="n">
+        <v>2.820871374850999</v>
+      </c>
+      <c r="S294" t="n">
+        <v>13800.9</v>
+      </c>
+      <c r="T294" t="n">
+        <v>1514.807928294986</v>
+      </c>
+      <c r="U294" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V294" t="n">
+        <v>0.01984126984126977</v>
+      </c>
+      <c r="W294" t="n">
+        <v>0.01199208330140666</v>
+      </c>
+      <c r="X294" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y294" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z294" t="n">
+        <v>0.5799588561058044</v>
+      </c>
+      <c r="AA294" t="n">
+        <v>12.64349049758911</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E295" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F295" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H295" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I295" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J295" t="n">
+        <v>121</v>
+      </c>
+      <c r="K295" t="n">
+        <v>12</v>
+      </c>
+      <c r="L295" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M295" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N295" s="2" t="n">
+        <v>45832.47712098862</v>
+      </c>
+      <c r="O295" t="n">
+        <v>14.56</v>
+      </c>
+      <c r="P295" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q295" t="n">
+        <v>1.1610357</v>
+      </c>
+      <c r="R295" t="n">
+        <v>12.54052739291307</v>
+      </c>
+      <c r="S295" t="n">
+        <v>1761.76</v>
+      </c>
+      <c r="T295" t="n">
+        <v>1517.403814542481</v>
+      </c>
+      <c r="U295" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V295" t="n">
+        <v>0.02679830747531731</v>
+      </c>
+      <c r="W295" t="n">
+        <v>0.01734878130179585</v>
+      </c>
+      <c r="X295" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y295" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z295" t="n">
+        <v>0.4978975057601929</v>
+      </c>
+      <c r="AA295" t="n">
+        <v>13.57315373420715</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr"/>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E296" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F296" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H296" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I296" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J296" t="n">
+        <v>162</v>
+      </c>
+      <c r="K296" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L296" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M296" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N296" s="2" t="n">
+        <v>45832.47712098862</v>
+      </c>
+      <c r="O296" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="P296" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q296" t="n">
+        <v>4.2551</v>
+      </c>
+      <c r="R296" t="n">
+        <v>9.118469601184461</v>
+      </c>
+      <c r="S296" t="n">
+        <v>6285.599999999999</v>
+      </c>
+      <c r="T296" t="n">
+        <v>1477.192075391883</v>
+      </c>
+      <c r="U296" t="n">
+        <v>8.272543736854324</v>
+      </c>
+      <c r="V296" t="n">
+        <v>-0.01020408163265318</v>
+      </c>
+      <c r="W296" t="n">
+        <v>-0.007968660896240265</v>
+      </c>
+      <c r="X296" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y296" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z296" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="AA296" t="n">
+        <v>12.85747975540161</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E297" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F297" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H297" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I297" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J297" t="n">
+        <v>101</v>
+      </c>
+      <c r="K297" t="n">
+        <v>11</v>
+      </c>
+      <c r="L297" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M297" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N297" s="2" t="n">
+        <v>45832.47712098862</v>
+      </c>
+      <c r="O297" t="n">
+        <v>25054</v>
+      </c>
+      <c r="P297" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q297" t="n">
+        <v>2058.27</v>
+      </c>
+      <c r="R297" t="n">
+        <v>12.17235833977078</v>
+      </c>
+      <c r="S297" t="n">
+        <v>2530454</v>
+      </c>
+      <c r="T297" t="n">
+        <v>1229.408192316849</v>
+      </c>
+      <c r="U297" t="n">
+        <v>11.00337378959821</v>
+      </c>
+      <c r="V297" t="n">
+        <v>0.02144487932159156</v>
+      </c>
+      <c r="W297" t="n">
+        <v>0.0204573143714879</v>
+      </c>
+      <c r="X297" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y297" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z297" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="AA297" t="n">
         <v>12.66160106658936</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA297"/>
+  <dimension ref="A1:AA305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27614,7 +27614,7 @@
         <v>100</v>
       </c>
       <c r="N290" s="2" t="n">
-        <v>45832.47712098862</v>
+        <v>45832.47712098379</v>
       </c>
       <c r="O290" t="n">
         <v>1</v>
@@ -27705,7 +27705,7 @@
         <v>12.02781891822815</v>
       </c>
       <c r="N291" s="2" t="n">
-        <v>45832.47712098862</v>
+        <v>45832.47712098379</v>
       </c>
       <c r="O291" t="n">
         <v>36.4</v>
@@ -27796,7 +27796,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N292" s="2" t="n">
-        <v>45832.47712098862</v>
+        <v>45832.47712098379</v>
       </c>
       <c r="O292" t="n">
         <v>374.35</v>
@@ -27891,7 +27891,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N293" s="2" t="n">
-        <v>45832.47712098862</v>
+        <v>45832.47712098379</v>
       </c>
       <c r="O293" t="n">
         <v>0.75</v>
@@ -27986,7 +27986,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N294" s="2" t="n">
-        <v>45832.47712098862</v>
+        <v>45832.47712098379</v>
       </c>
       <c r="O294" t="n">
         <v>25.7</v>
@@ -28081,7 +28081,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N295" s="2" t="n">
-        <v>45832.47712098862</v>
+        <v>45832.47712098379</v>
       </c>
       <c r="O295" t="n">
         <v>14.56</v>
@@ -28172,7 +28172,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N296" s="2" t="n">
-        <v>45832.47712098862</v>
+        <v>45832.47712098379</v>
       </c>
       <c r="O296" t="n">
         <v>38.8</v>
@@ -28267,7 +28267,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N297" s="2" t="n">
-        <v>45832.47712098862</v>
+        <v>45832.47712098379</v>
       </c>
       <c r="O297" t="n">
         <v>25054</v>
@@ -28308,6 +28308,756 @@
         <v>0.4939931035041809</v>
       </c>
       <c r="AA297" t="n">
+        <v>12.66160106658936</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F298" t="n">
+        <v>1</v>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H298" t="n">
+        <v>1</v>
+      </c>
+      <c r="I298" t="n">
+        <v>1</v>
+      </c>
+      <c r="J298" t="n">
+        <v>1</v>
+      </c>
+      <c r="K298" t="n">
+        <v>100</v>
+      </c>
+      <c r="L298" t="n">
+        <v>100</v>
+      </c>
+      <c r="M298" t="n">
+        <v>100</v>
+      </c>
+      <c r="N298" s="2" t="n">
+        <v>45832.54173486812</v>
+      </c>
+      <c r="O298" t="n">
+        <v>1</v>
+      </c>
+      <c r="P298" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q298" t="n">
+        <v>1</v>
+      </c>
+      <c r="R298" t="n">
+        <v>1</v>
+      </c>
+      <c r="S298" t="n">
+        <v>0</v>
+      </c>
+      <c r="T298" t="n">
+        <v>0.2858026033402439</v>
+      </c>
+      <c r="U298" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V298" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W298" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X298" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y298" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z298" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA298" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>DE000A0XYG76</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>DR0.DE</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr"/>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>DT.ROHSTOFF AG NA O.N.</t>
+        </is>
+      </c>
+      <c r="E299" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F299" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H299" t="n">
+        <v>1</v>
+      </c>
+      <c r="I299" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="J299" t="n">
+        <v>39</v>
+      </c>
+      <c r="K299" t="n">
+        <v>11</v>
+      </c>
+      <c r="L299" t="n">
+        <v>0.4329348504543304</v>
+      </c>
+      <c r="M299" t="n">
+        <v>12.02781891822815</v>
+      </c>
+      <c r="N299" s="2" t="n">
+        <v>45832.54173486812</v>
+      </c>
+      <c r="O299" t="n">
+        <v>36.35</v>
+      </c>
+      <c r="P299" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q299" t="n">
+        <v>1</v>
+      </c>
+      <c r="R299" t="n">
+        <v>36.35</v>
+      </c>
+      <c r="S299" t="n">
+        <v>1417.65</v>
+      </c>
+      <c r="T299" t="n">
+        <v>1417.65</v>
+      </c>
+      <c r="U299" t="n">
+        <v>34.92</v>
+      </c>
+      <c r="V299" t="n">
+        <v>-0.03580901856763929</v>
+      </c>
+      <c r="W299" t="n">
+        <v>-0.03580901856763929</v>
+      </c>
+      <c r="X299" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y299" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z299" t="n">
+        <v>0.4433653950691223</v>
+      </c>
+      <c r="AA299" t="n">
+        <v>12.17899870872498</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr"/>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E300" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F300" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H300" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I300" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J300" t="n">
+        <v>3</v>
+      </c>
+      <c r="K300" t="n">
+        <v>10</v>
+      </c>
+      <c r="L300" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M300" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N300" s="2" t="n">
+        <v>45832.54173486812</v>
+      </c>
+      <c r="O300" t="n">
+        <v>374.35</v>
+      </c>
+      <c r="P300" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q300" t="n">
+        <v>0.85281</v>
+      </c>
+      <c r="R300" t="n">
+        <v>438.9606125631736</v>
+      </c>
+      <c r="S300" t="n">
+        <v>1123.05</v>
+      </c>
+      <c r="T300" t="n">
+        <v>1316.881837689521</v>
+      </c>
+      <c r="U300" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V300" t="n">
+        <v>0.01817954338992456</v>
+      </c>
+      <c r="W300" t="n">
+        <v>0.01920630715596339</v>
+      </c>
+      <c r="X300" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y300" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z300" t="n">
+        <v>0.5300061702728271</v>
+      </c>
+      <c r="AA300" t="n">
+        <v>12.44775533676147</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E301" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F301" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H301" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I301" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J301" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K301" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L301" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M301" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N301" s="2" t="n">
+        <v>45832.54173486812</v>
+      </c>
+      <c r="O301" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P301" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q301" t="n">
+        <v>1.78352</v>
+      </c>
+      <c r="R301" t="n">
+        <v>0.4205167309590024</v>
+      </c>
+      <c r="S301" t="n">
+        <v>2748</v>
+      </c>
+      <c r="T301" t="n">
+        <v>1540.773302233785</v>
+      </c>
+      <c r="U301" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="V301" t="n">
+        <v>0.03448275862068972</v>
+      </c>
+      <c r="W301" t="n">
+        <v>0.02929155207988554</v>
+      </c>
+      <c r="X301" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y301" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z301" t="n">
+        <v>0.4560990333557129</v>
+      </c>
+      <c r="AA301" t="n">
+        <v>11.05002820491791</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E302" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F302" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H302" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I302" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J302" t="n">
+        <v>537</v>
+      </c>
+      <c r="K302" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L302" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M302" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N302" s="2" t="n">
+        <v>45832.54173486812</v>
+      </c>
+      <c r="O302" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="P302" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q302" t="n">
+        <v>9.10595</v>
+      </c>
+      <c r="R302" t="n">
+        <v>2.822330454263421</v>
+      </c>
+      <c r="S302" t="n">
+        <v>13800.9</v>
+      </c>
+      <c r="T302" t="n">
+        <v>1515.591453939457</v>
+      </c>
+      <c r="U302" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V302" t="n">
+        <v>0.01984126984126977</v>
+      </c>
+      <c r="W302" t="n">
+        <v>0.01251553035661224</v>
+      </c>
+      <c r="X302" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y302" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z302" t="n">
+        <v>0.5799588561058044</v>
+      </c>
+      <c r="AA302" t="n">
+        <v>12.64349049758911</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E303" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F303" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H303" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I303" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J303" t="n">
+        <v>121</v>
+      </c>
+      <c r="K303" t="n">
+        <v>12</v>
+      </c>
+      <c r="L303" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M303" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N303" s="2" t="n">
+        <v>45832.54173486812</v>
+      </c>
+      <c r="O303" t="n">
+        <v>14.56</v>
+      </c>
+      <c r="P303" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q303" t="n">
+        <v>1.160362</v>
+      </c>
+      <c r="R303" t="n">
+        <v>12.54780835635776</v>
+      </c>
+      <c r="S303" t="n">
+        <v>1761.76</v>
+      </c>
+      <c r="T303" t="n">
+        <v>1518.284811119289</v>
+      </c>
+      <c r="U303" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V303" t="n">
+        <v>0.02679830747531731</v>
+      </c>
+      <c r="W303" t="n">
+        <v>0.01793944858835217</v>
+      </c>
+      <c r="X303" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y303" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z303" t="n">
+        <v>0.4978975057601929</v>
+      </c>
+      <c r="AA303" t="n">
+        <v>13.57315373420715</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr"/>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E304" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F304" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H304" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I304" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J304" t="n">
+        <v>162</v>
+      </c>
+      <c r="K304" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L304" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M304" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N304" s="2" t="n">
+        <v>45832.54173486812</v>
+      </c>
+      <c r="O304" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="P304" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q304" t="n">
+        <v>4.25187</v>
+      </c>
+      <c r="R304" t="n">
+        <v>9.05483940007573</v>
+      </c>
+      <c r="S304" t="n">
+        <v>6237</v>
+      </c>
+      <c r="T304" t="n">
+        <v>1466.883982812268</v>
+      </c>
+      <c r="U304" t="n">
+        <v>8.272543736854324</v>
+      </c>
+      <c r="V304" t="n">
+        <v>-0.0178571428571429</v>
+      </c>
+      <c r="W304" t="n">
+        <v>-0.01489122097201623</v>
+      </c>
+      <c r="X304" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y304" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z304" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="AA304" t="n">
+        <v>12.85747975540161</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E305" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F305" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H305" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I305" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J305" t="n">
+        <v>101</v>
+      </c>
+      <c r="K305" t="n">
+        <v>11</v>
+      </c>
+      <c r="L305" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M305" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N305" s="2" t="n">
+        <v>45832.54173486812</v>
+      </c>
+      <c r="O305" t="n">
+        <v>24601</v>
+      </c>
+      <c r="P305" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q305" t="n">
+        <v>2057.12</v>
+      </c>
+      <c r="R305" t="n">
+        <v>11.95895232169246</v>
+      </c>
+      <c r="S305" t="n">
+        <v>2484701</v>
+      </c>
+      <c r="T305" t="n">
+        <v>1207.854184490939</v>
+      </c>
+      <c r="U305" t="n">
+        <v>11.00337378959821</v>
+      </c>
+      <c r="V305" t="n">
+        <v>0.002976190476190466</v>
+      </c>
+      <c r="W305" t="n">
+        <v>0.002566637314488807</v>
+      </c>
+      <c r="X305" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y305" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z305" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="AA305" t="n">
         <v>12.66160106658936</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA305"/>
+  <dimension ref="A1:AA313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28364,7 +28364,7 @@
         <v>100</v>
       </c>
       <c r="N298" s="2" t="n">
-        <v>45832.54173486812</v>
+        <v>45832.54173487268</v>
       </c>
       <c r="O298" t="n">
         <v>1</v>
@@ -28455,7 +28455,7 @@
         <v>12.02781891822815</v>
       </c>
       <c r="N299" s="2" t="n">
-        <v>45832.54173486812</v>
+        <v>45832.54173487268</v>
       </c>
       <c r="O299" t="n">
         <v>36.35</v>
@@ -28546,7 +28546,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N300" s="2" t="n">
-        <v>45832.54173486812</v>
+        <v>45832.54173487268</v>
       </c>
       <c r="O300" t="n">
         <v>374.35</v>
@@ -28641,7 +28641,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N301" s="2" t="n">
-        <v>45832.54173486812</v>
+        <v>45832.54173487268</v>
       </c>
       <c r="O301" t="n">
         <v>0.75</v>
@@ -28736,7 +28736,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N302" s="2" t="n">
-        <v>45832.54173486812</v>
+        <v>45832.54173487268</v>
       </c>
       <c r="O302" t="n">
         <v>25.7</v>
@@ -28831,7 +28831,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N303" s="2" t="n">
-        <v>45832.54173486812</v>
+        <v>45832.54173487268</v>
       </c>
       <c r="O303" t="n">
         <v>14.56</v>
@@ -28922,7 +28922,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N304" s="2" t="n">
-        <v>45832.54173486812</v>
+        <v>45832.54173487268</v>
       </c>
       <c r="O304" t="n">
         <v>38.5</v>
@@ -29017,7 +29017,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N305" s="2" t="n">
-        <v>45832.54173486812</v>
+        <v>45832.54173487268</v>
       </c>
       <c r="O305" t="n">
         <v>24601</v>
@@ -29058,6 +29058,756 @@
         <v>0.4939931035041809</v>
       </c>
       <c r="AA305" t="n">
+        <v>12.66160106658936</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F306" t="n">
+        <v>1</v>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H306" t="n">
+        <v>1</v>
+      </c>
+      <c r="I306" t="n">
+        <v>1</v>
+      </c>
+      <c r="J306" t="n">
+        <v>1</v>
+      </c>
+      <c r="K306" t="n">
+        <v>100</v>
+      </c>
+      <c r="L306" t="n">
+        <v>100</v>
+      </c>
+      <c r="M306" t="n">
+        <v>100</v>
+      </c>
+      <c r="N306" s="2" t="n">
+        <v>45832.57249423649</v>
+      </c>
+      <c r="O306" t="n">
+        <v>1</v>
+      </c>
+      <c r="P306" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q306" t="n">
+        <v>1</v>
+      </c>
+      <c r="R306" t="n">
+        <v>1</v>
+      </c>
+      <c r="S306" t="n">
+        <v>0</v>
+      </c>
+      <c r="T306" t="n">
+        <v>0.2858026033402439</v>
+      </c>
+      <c r="U306" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V306" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W306" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X306" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y306" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z306" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA306" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>DE000A0XYG76</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>DR0.DE</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr"/>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>DT.ROHSTOFF AG NA O.N.</t>
+        </is>
+      </c>
+      <c r="E307" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F307" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H307" t="n">
+        <v>1</v>
+      </c>
+      <c r="I307" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="J307" t="n">
+        <v>39</v>
+      </c>
+      <c r="K307" t="n">
+        <v>11</v>
+      </c>
+      <c r="L307" t="n">
+        <v>0.4329348504543304</v>
+      </c>
+      <c r="M307" t="n">
+        <v>12.02781891822815</v>
+      </c>
+      <c r="N307" s="2" t="n">
+        <v>45832.57249423649</v>
+      </c>
+      <c r="O307" t="n">
+        <v>36.05</v>
+      </c>
+      <c r="P307" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q307" t="n">
+        <v>1</v>
+      </c>
+      <c r="R307" t="n">
+        <v>36.05</v>
+      </c>
+      <c r="S307" t="n">
+        <v>1405.95</v>
+      </c>
+      <c r="T307" t="n">
+        <v>1405.95</v>
+      </c>
+      <c r="U307" t="n">
+        <v>34.92</v>
+      </c>
+      <c r="V307" t="n">
+        <v>-0.04376657824933705</v>
+      </c>
+      <c r="W307" t="n">
+        <v>-0.04376657824933705</v>
+      </c>
+      <c r="X307" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y307" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z307" t="n">
+        <v>0.4433653950691223</v>
+      </c>
+      <c r="AA307" t="n">
+        <v>12.17899870872498</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr"/>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E308" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F308" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H308" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I308" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J308" t="n">
+        <v>3</v>
+      </c>
+      <c r="K308" t="n">
+        <v>10</v>
+      </c>
+      <c r="L308" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M308" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N308" s="2" t="n">
+        <v>45832.57249423649</v>
+      </c>
+      <c r="O308" t="n">
+        <v>374.575</v>
+      </c>
+      <c r="P308" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q308" t="n">
+        <v>0.85209</v>
+      </c>
+      <c r="R308" t="n">
+        <v>439.5955826262484</v>
+      </c>
+      <c r="S308" t="n">
+        <v>1123.725</v>
+      </c>
+      <c r="T308" t="n">
+        <v>1318.786747878745</v>
+      </c>
+      <c r="U308" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V308" t="n">
+        <v>0.0187915118613089</v>
+      </c>
+      <c r="W308" t="n">
+        <v>0.02068062051032582</v>
+      </c>
+      <c r="X308" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y308" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z308" t="n">
+        <v>0.5300061702728271</v>
+      </c>
+      <c r="AA308" t="n">
+        <v>12.44775533676147</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E309" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F309" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H309" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I309" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J309" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K309" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L309" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M309" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N309" s="2" t="n">
+        <v>45832.57249423649</v>
+      </c>
+      <c r="O309" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P309" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q309" t="n">
+        <v>1.7851</v>
+      </c>
+      <c r="R309" t="n">
+        <v>0.4201445297182231</v>
+      </c>
+      <c r="S309" t="n">
+        <v>2748</v>
+      </c>
+      <c r="T309" t="n">
+        <v>1539.409556887569</v>
+      </c>
+      <c r="U309" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="V309" t="n">
+        <v>0.03448275862068972</v>
+      </c>
+      <c r="W309" t="n">
+        <v>0.02838052152009252</v>
+      </c>
+      <c r="X309" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y309" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z309" t="n">
+        <v>0.4560990333557129</v>
+      </c>
+      <c r="AA309" t="n">
+        <v>11.05002820491791</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E310" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F310" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H310" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I310" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J310" t="n">
+        <v>537</v>
+      </c>
+      <c r="K310" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L310" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M310" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N310" s="2" t="n">
+        <v>45832.57249423649</v>
+      </c>
+      <c r="O310" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="P310" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q310" t="n">
+        <v>9.09332</v>
+      </c>
+      <c r="R310" t="n">
+        <v>2.826250478373135</v>
+      </c>
+      <c r="S310" t="n">
+        <v>13800.9</v>
+      </c>
+      <c r="T310" t="n">
+        <v>1517.696506886374</v>
+      </c>
+      <c r="U310" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V310" t="n">
+        <v>0.01984126984126977</v>
+      </c>
+      <c r="W310" t="n">
+        <v>0.01392184522823259</v>
+      </c>
+      <c r="X310" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y310" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z310" t="n">
+        <v>0.5799588561058044</v>
+      </c>
+      <c r="AA310" t="n">
+        <v>12.64349049758911</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E311" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F311" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H311" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I311" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J311" t="n">
+        <v>121</v>
+      </c>
+      <c r="K311" t="n">
+        <v>12</v>
+      </c>
+      <c r="L311" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M311" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N311" s="2" t="n">
+        <v>45832.57249423649</v>
+      </c>
+      <c r="O311" t="n">
+        <v>13.685</v>
+      </c>
+      <c r="P311" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q311" t="n">
+        <v>1.1588829</v>
+      </c>
+      <c r="R311" t="n">
+        <v>11.80878585748396</v>
+      </c>
+      <c r="S311" t="n">
+        <v>1655.885</v>
+      </c>
+      <c r="T311" t="n">
+        <v>1428.863088755559</v>
+      </c>
+      <c r="U311" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V311" t="n">
+        <v>-0.03490832157968959</v>
+      </c>
+      <c r="W311" t="n">
+        <v>-0.04201366303347243</v>
+      </c>
+      <c r="X311" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y311" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z311" t="n">
+        <v>0.4978975057601929</v>
+      </c>
+      <c r="AA311" t="n">
+        <v>13.57315373420715</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr"/>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E312" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F312" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H312" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I312" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J312" t="n">
+        <v>162</v>
+      </c>
+      <c r="K312" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L312" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M312" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N312" s="2" t="n">
+        <v>45832.57249423649</v>
+      </c>
+      <c r="O312" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="P312" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q312" t="n">
+        <v>4.2504</v>
+      </c>
+      <c r="R312" t="n">
+        <v>9.105025409373237</v>
+      </c>
+      <c r="S312" t="n">
+        <v>6269.400000000001</v>
+      </c>
+      <c r="T312" t="n">
+        <v>1475.014116318464</v>
+      </c>
+      <c r="U312" t="n">
+        <v>8.272543736854324</v>
+      </c>
+      <c r="V312" t="n">
+        <v>-0.01275510204081631</v>
+      </c>
+      <c r="W312" t="n">
+        <v>-0.009431303224282317</v>
+      </c>
+      <c r="X312" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y312" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z312" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="AA312" t="n">
+        <v>12.85747975540161</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E313" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F313" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H313" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I313" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J313" t="n">
+        <v>101</v>
+      </c>
+      <c r="K313" t="n">
+        <v>11</v>
+      </c>
+      <c r="L313" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M313" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N313" s="2" t="n">
+        <v>45832.57249423649</v>
+      </c>
+      <c r="O313" t="n">
+        <v>24616</v>
+      </c>
+      <c r="P313" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q313" t="n">
+        <v>2058.06</v>
+      </c>
+      <c r="R313" t="n">
+        <v>11.96077859731981</v>
+      </c>
+      <c r="S313" t="n">
+        <v>2486216</v>
+      </c>
+      <c r="T313" t="n">
+        <v>1208.038638329301</v>
+      </c>
+      <c r="U313" t="n">
+        <v>11.00337378959821</v>
+      </c>
+      <c r="V313" t="n">
+        <v>0.003587736464448765</v>
+      </c>
+      <c r="W313" t="n">
+        <v>0.002719741279222587</v>
+      </c>
+      <c r="X313" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y313" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z313" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="AA313" t="n">
         <v>12.66160106658936</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA313"/>
+  <dimension ref="A1:AA321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29114,7 +29114,7 @@
         <v>100</v>
       </c>
       <c r="N306" s="2" t="n">
-        <v>45832.57249423649</v>
+        <v>45832.57249423611</v>
       </c>
       <c r="O306" t="n">
         <v>1</v>
@@ -29205,7 +29205,7 @@
         <v>12.02781891822815</v>
       </c>
       <c r="N307" s="2" t="n">
-        <v>45832.57249423649</v>
+        <v>45832.57249423611</v>
       </c>
       <c r="O307" t="n">
         <v>36.05</v>
@@ -29296,7 +29296,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N308" s="2" t="n">
-        <v>45832.57249423649</v>
+        <v>45832.57249423611</v>
       </c>
       <c r="O308" t="n">
         <v>374.575</v>
@@ -29391,7 +29391,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N309" s="2" t="n">
-        <v>45832.57249423649</v>
+        <v>45832.57249423611</v>
       </c>
       <c r="O309" t="n">
         <v>0.75</v>
@@ -29486,7 +29486,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N310" s="2" t="n">
-        <v>45832.57249423649</v>
+        <v>45832.57249423611</v>
       </c>
       <c r="O310" t="n">
         <v>25.7</v>
@@ -29581,7 +29581,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N311" s="2" t="n">
-        <v>45832.57249423649</v>
+        <v>45832.57249423611</v>
       </c>
       <c r="O311" t="n">
         <v>13.685</v>
@@ -29672,7 +29672,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N312" s="2" t="n">
-        <v>45832.57249423649</v>
+        <v>45832.57249423611</v>
       </c>
       <c r="O312" t="n">
         <v>38.7</v>
@@ -29767,7 +29767,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N313" s="2" t="n">
-        <v>45832.57249423649</v>
+        <v>45832.57249423611</v>
       </c>
       <c r="O313" t="n">
         <v>24616</v>
@@ -29808,6 +29808,756 @@
         <v>0.4939931035041809</v>
       </c>
       <c r="AA313" t="n">
+        <v>12.66160106658936</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F314" t="n">
+        <v>1</v>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H314" t="n">
+        <v>1</v>
+      </c>
+      <c r="I314" t="n">
+        <v>1</v>
+      </c>
+      <c r="J314" t="n">
+        <v>1</v>
+      </c>
+      <c r="K314" t="n">
+        <v>100</v>
+      </c>
+      <c r="L314" t="n">
+        <v>100</v>
+      </c>
+      <c r="M314" t="n">
+        <v>100</v>
+      </c>
+      <c r="N314" s="2" t="n">
+        <v>45832.60774948669</v>
+      </c>
+      <c r="O314" t="n">
+        <v>1</v>
+      </c>
+      <c r="P314" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q314" t="n">
+        <v>1</v>
+      </c>
+      <c r="R314" t="n">
+        <v>1</v>
+      </c>
+      <c r="S314" t="n">
+        <v>0</v>
+      </c>
+      <c r="T314" t="n">
+        <v>0.2858026033402439</v>
+      </c>
+      <c r="U314" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V314" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W314" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X314" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y314" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z314" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA314" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>DE000A0XYG76</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>DR0.DE</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr"/>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>DT.ROHSTOFF AG NA O.N.</t>
+        </is>
+      </c>
+      <c r="E315" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F315" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H315" t="n">
+        <v>1</v>
+      </c>
+      <c r="I315" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="J315" t="n">
+        <v>39</v>
+      </c>
+      <c r="K315" t="n">
+        <v>11</v>
+      </c>
+      <c r="L315" t="n">
+        <v>0.4329348504543304</v>
+      </c>
+      <c r="M315" t="n">
+        <v>12.02781891822815</v>
+      </c>
+      <c r="N315" s="2" t="n">
+        <v>45832.60774948669</v>
+      </c>
+      <c r="O315" t="n">
+        <v>36.05</v>
+      </c>
+      <c r="P315" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q315" t="n">
+        <v>1</v>
+      </c>
+      <c r="R315" t="n">
+        <v>36.05</v>
+      </c>
+      <c r="S315" t="n">
+        <v>1405.95</v>
+      </c>
+      <c r="T315" t="n">
+        <v>1405.95</v>
+      </c>
+      <c r="U315" t="n">
+        <v>34.92</v>
+      </c>
+      <c r="V315" t="n">
+        <v>-0.04376657824933705</v>
+      </c>
+      <c r="W315" t="n">
+        <v>-0.04376657824933705</v>
+      </c>
+      <c r="X315" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y315" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z315" t="n">
+        <v>0.4433653950691223</v>
+      </c>
+      <c r="AA315" t="n">
+        <v>12.17899870872498</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr"/>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E316" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F316" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H316" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I316" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J316" t="n">
+        <v>3</v>
+      </c>
+      <c r="K316" t="n">
+        <v>10</v>
+      </c>
+      <c r="L316" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M316" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N316" s="2" t="n">
+        <v>45832.60774948669</v>
+      </c>
+      <c r="O316" t="n">
+        <v>375</v>
+      </c>
+      <c r="P316" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q316" t="n">
+        <v>0.85309</v>
+      </c>
+      <c r="R316" t="n">
+        <v>439.578473549098</v>
+      </c>
+      <c r="S316" t="n">
+        <v>1125</v>
+      </c>
+      <c r="T316" t="n">
+        <v>1318.735420647294</v>
+      </c>
+      <c r="U316" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V316" t="n">
+        <v>0.01994745230725714</v>
+      </c>
+      <c r="W316" t="n">
+        <v>0.02064089558093074</v>
+      </c>
+      <c r="X316" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y316" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z316" t="n">
+        <v>0.5300061702728271</v>
+      </c>
+      <c r="AA316" t="n">
+        <v>12.44775533676147</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E317" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F317" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H317" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I317" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J317" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K317" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L317" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M317" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N317" s="2" t="n">
+        <v>45832.60774948669</v>
+      </c>
+      <c r="O317" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P317" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q317" t="n">
+        <v>1.78525</v>
+      </c>
+      <c r="R317" t="n">
+        <v>0.4201092283993839</v>
+      </c>
+      <c r="S317" t="n">
+        <v>2748</v>
+      </c>
+      <c r="T317" t="n">
+        <v>1539.280212855342</v>
+      </c>
+      <c r="U317" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="V317" t="n">
+        <v>0.03448275862068972</v>
+      </c>
+      <c r="W317" t="n">
+        <v>0.0282941150906133</v>
+      </c>
+      <c r="X317" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y317" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z317" t="n">
+        <v>0.4560990333557129</v>
+      </c>
+      <c r="AA317" t="n">
+        <v>11.05002820491791</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E318" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F318" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H318" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I318" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J318" t="n">
+        <v>537</v>
+      </c>
+      <c r="K318" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L318" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M318" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N318" s="2" t="n">
+        <v>45832.60774948669</v>
+      </c>
+      <c r="O318" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="P318" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q318" t="n">
+        <v>9.1327</v>
+      </c>
+      <c r="R318" t="n">
+        <v>2.814063748946095</v>
+      </c>
+      <c r="S318" t="n">
+        <v>13800.9</v>
+      </c>
+      <c r="T318" t="n">
+        <v>1511.152233184053</v>
+      </c>
+      <c r="U318" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V318" t="n">
+        <v>0.01984126984126977</v>
+      </c>
+      <c r="W318" t="n">
+        <v>0.009549836702267056</v>
+      </c>
+      <c r="X318" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y318" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z318" t="n">
+        <v>0.5799588561058044</v>
+      </c>
+      <c r="AA318" t="n">
+        <v>12.64349049758911</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E319" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F319" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H319" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I319" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J319" t="n">
+        <v>121</v>
+      </c>
+      <c r="K319" t="n">
+        <v>12</v>
+      </c>
+      <c r="L319" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M319" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N319" s="2" t="n">
+        <v>45832.60774948669</v>
+      </c>
+      <c r="O319" t="n">
+        <v>14.035</v>
+      </c>
+      <c r="P319" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q319" t="n">
+        <v>1.1636026</v>
+      </c>
+      <c r="R319" t="n">
+        <v>12.06167810212868</v>
+      </c>
+      <c r="S319" t="n">
+        <v>1698.235</v>
+      </c>
+      <c r="T319" t="n">
+        <v>1459.463050357571</v>
+      </c>
+      <c r="U319" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V319" t="n">
+        <v>-0.01022566995768681</v>
+      </c>
+      <c r="W319" t="n">
+        <v>-0.02149781000520368</v>
+      </c>
+      <c r="X319" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y319" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z319" t="n">
+        <v>0.4978975057601929</v>
+      </c>
+      <c r="AA319" t="n">
+        <v>13.57315373420715</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr"/>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E320" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F320" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H320" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I320" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J320" t="n">
+        <v>162</v>
+      </c>
+      <c r="K320" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L320" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M320" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N320" s="2" t="n">
+        <v>45832.60774948669</v>
+      </c>
+      <c r="O320" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="P320" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q320" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="R320" t="n">
+        <v>9.129411764705882</v>
+      </c>
+      <c r="S320" t="n">
+        <v>6285.599999999999</v>
+      </c>
+      <c r="T320" t="n">
+        <v>1478.964705882353</v>
+      </c>
+      <c r="U320" t="n">
+        <v>8.272543736854324</v>
+      </c>
+      <c r="V320" t="n">
+        <v>-0.01020408163265318</v>
+      </c>
+      <c r="W320" t="n">
+        <v>-0.006778223289315877</v>
+      </c>
+      <c r="X320" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y320" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z320" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="AA320" t="n">
+        <v>12.85747975540161</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E321" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F321" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H321" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I321" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J321" t="n">
+        <v>101</v>
+      </c>
+      <c r="K321" t="n">
+        <v>11</v>
+      </c>
+      <c r="L321" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M321" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N321" s="2" t="n">
+        <v>45832.60774948669</v>
+      </c>
+      <c r="O321" t="n">
+        <v>24653</v>
+      </c>
+      <c r="P321" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q321" t="n">
+        <v>2059.96</v>
+      </c>
+      <c r="R321" t="n">
+        <v>11.9677081108371</v>
+      </c>
+      <c r="S321" t="n">
+        <v>2489953</v>
+      </c>
+      <c r="T321" t="n">
+        <v>1208.738519194548</v>
+      </c>
+      <c r="U321" t="n">
+        <v>11.00337378959821</v>
+      </c>
+      <c r="V321" t="n">
+        <v>0.005096216568819312</v>
+      </c>
+      <c r="W321" t="n">
+        <v>0.003300670015986551</v>
+      </c>
+      <c r="X321" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y321" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z321" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="AA321" t="n">
         <v>12.66160106658936</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA321"/>
+  <dimension ref="A1:AA329"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29864,7 +29864,7 @@
         <v>100</v>
       </c>
       <c r="N314" s="2" t="n">
-        <v>45832.60774948669</v>
+        <v>45832.60774949074</v>
       </c>
       <c r="O314" t="n">
         <v>1</v>
@@ -29955,7 +29955,7 @@
         <v>12.02781891822815</v>
       </c>
       <c r="N315" s="2" t="n">
-        <v>45832.60774948669</v>
+        <v>45832.60774949074</v>
       </c>
       <c r="O315" t="n">
         <v>36.05</v>
@@ -30046,7 +30046,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N316" s="2" t="n">
-        <v>45832.60774948669</v>
+        <v>45832.60774949074</v>
       </c>
       <c r="O316" t="n">
         <v>375</v>
@@ -30141,7 +30141,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N317" s="2" t="n">
-        <v>45832.60774948669</v>
+        <v>45832.60774949074</v>
       </c>
       <c r="O317" t="n">
         <v>0.75</v>
@@ -30236,7 +30236,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N318" s="2" t="n">
-        <v>45832.60774948669</v>
+        <v>45832.60774949074</v>
       </c>
       <c r="O318" t="n">
         <v>25.7</v>
@@ -30331,7 +30331,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N319" s="2" t="n">
-        <v>45832.60774948669</v>
+        <v>45832.60774949074</v>
       </c>
       <c r="O319" t="n">
         <v>14.035</v>
@@ -30422,7 +30422,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N320" s="2" t="n">
-        <v>45832.60774948669</v>
+        <v>45832.60774949074</v>
       </c>
       <c r="O320" t="n">
         <v>38.8</v>
@@ -30517,7 +30517,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N321" s="2" t="n">
-        <v>45832.60774948669</v>
+        <v>45832.60774949074</v>
       </c>
       <c r="O321" t="n">
         <v>24653</v>
@@ -30558,6 +30558,756 @@
         <v>0.4939931035041809</v>
       </c>
       <c r="AA321" t="n">
+        <v>12.66160106658936</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F322" t="n">
+        <v>1</v>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H322" t="n">
+        <v>1</v>
+      </c>
+      <c r="I322" t="n">
+        <v>1</v>
+      </c>
+      <c r="J322" t="n">
+        <v>1</v>
+      </c>
+      <c r="K322" t="n">
+        <v>100</v>
+      </c>
+      <c r="L322" t="n">
+        <v>100</v>
+      </c>
+      <c r="M322" t="n">
+        <v>100</v>
+      </c>
+      <c r="N322" s="2" t="n">
+        <v>45832.64840297784</v>
+      </c>
+      <c r="O322" t="n">
+        <v>1</v>
+      </c>
+      <c r="P322" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q322" t="n">
+        <v>1</v>
+      </c>
+      <c r="R322" t="n">
+        <v>1</v>
+      </c>
+      <c r="S322" t="n">
+        <v>0</v>
+      </c>
+      <c r="T322" t="n">
+        <v>0.2858026033402439</v>
+      </c>
+      <c r="U322" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V322" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W322" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X322" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y322" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z322" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA322" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>DE000A0XYG76</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>DR0.DE</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr"/>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>DT.ROHSTOFF AG NA O.N.</t>
+        </is>
+      </c>
+      <c r="E323" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F323" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H323" t="n">
+        <v>1</v>
+      </c>
+      <c r="I323" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="J323" t="n">
+        <v>39</v>
+      </c>
+      <c r="K323" t="n">
+        <v>11</v>
+      </c>
+      <c r="L323" t="n">
+        <v>0.4329348504543304</v>
+      </c>
+      <c r="M323" t="n">
+        <v>12.02781891822815</v>
+      </c>
+      <c r="N323" s="2" t="n">
+        <v>45832.64840297784</v>
+      </c>
+      <c r="O323" t="n">
+        <v>36.05</v>
+      </c>
+      <c r="P323" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q323" t="n">
+        <v>1</v>
+      </c>
+      <c r="R323" t="n">
+        <v>36.05</v>
+      </c>
+      <c r="S323" t="n">
+        <v>1405.95</v>
+      </c>
+      <c r="T323" t="n">
+        <v>1405.95</v>
+      </c>
+      <c r="U323" t="n">
+        <v>34.92</v>
+      </c>
+      <c r="V323" t="n">
+        <v>-0.04376657824933705</v>
+      </c>
+      <c r="W323" t="n">
+        <v>-0.04376657824933705</v>
+      </c>
+      <c r="X323" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y323" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z323" t="n">
+        <v>0.4433653950691223</v>
+      </c>
+      <c r="AA323" t="n">
+        <v>12.17899870872498</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr"/>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E324" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F324" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H324" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I324" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J324" t="n">
+        <v>3</v>
+      </c>
+      <c r="K324" t="n">
+        <v>10</v>
+      </c>
+      <c r="L324" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M324" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N324" s="2" t="n">
+        <v>45832.64840297784</v>
+      </c>
+      <c r="O324" t="n">
+        <v>374.51</v>
+      </c>
+      <c r="P324" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q324" t="n">
+        <v>0.85317</v>
+      </c>
+      <c r="R324" t="n">
+        <v>438.96292649765</v>
+      </c>
+      <c r="S324" t="n">
+        <v>1123.53</v>
+      </c>
+      <c r="T324" t="n">
+        <v>1316.88877949295</v>
+      </c>
+      <c r="U324" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V324" t="n">
+        <v>0.01861472096957573</v>
+      </c>
+      <c r="W324" t="n">
+        <v>0.01921167979429383</v>
+      </c>
+      <c r="X324" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y324" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z324" t="n">
+        <v>0.5300061702728271</v>
+      </c>
+      <c r="AA324" t="n">
+        <v>12.44775533676147</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E325" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F325" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H325" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I325" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J325" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K325" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L325" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M325" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N325" s="2" t="n">
+        <v>45832.64840297784</v>
+      </c>
+      <c r="O325" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P325" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q325" t="n">
+        <v>1.78628</v>
+      </c>
+      <c r="R325" t="n">
+        <v>0.4198669861387912</v>
+      </c>
+      <c r="S325" t="n">
+        <v>2748</v>
+      </c>
+      <c r="T325" t="n">
+        <v>1538.392637212531</v>
+      </c>
+      <c r="U325" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="V325" t="n">
+        <v>0.03448275862068972</v>
+      </c>
+      <c r="W325" t="n">
+        <v>0.02770118288595125</v>
+      </c>
+      <c r="X325" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y325" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z325" t="n">
+        <v>0.4560990333557129</v>
+      </c>
+      <c r="AA325" t="n">
+        <v>11.05002820491791</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E326" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F326" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H326" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I326" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J326" t="n">
+        <v>537</v>
+      </c>
+      <c r="K326" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L326" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M326" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N326" s="2" t="n">
+        <v>45832.64840297784</v>
+      </c>
+      <c r="O326" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="P326" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q326" t="n">
+        <v>9.124510000000001</v>
+      </c>
+      <c r="R326" t="n">
+        <v>2.816589603167731</v>
+      </c>
+      <c r="S326" t="n">
+        <v>13800.9</v>
+      </c>
+      <c r="T326" t="n">
+        <v>1512.508616901072</v>
+      </c>
+      <c r="U326" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V326" t="n">
+        <v>0.01984126984126977</v>
+      </c>
+      <c r="W326" t="n">
+        <v>0.01045599091357152</v>
+      </c>
+      <c r="X326" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y326" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z326" t="n">
+        <v>0.5799588561058044</v>
+      </c>
+      <c r="AA326" t="n">
+        <v>12.64349049758911</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E327" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F327" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H327" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I327" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J327" t="n">
+        <v>121</v>
+      </c>
+      <c r="K327" t="n">
+        <v>12</v>
+      </c>
+      <c r="L327" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M327" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N327" s="2" t="n">
+        <v>45832.64840297784</v>
+      </c>
+      <c r="O327" t="n">
+        <v>14.105</v>
+      </c>
+      <c r="P327" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q327" t="n">
+        <v>1.1627907</v>
+      </c>
+      <c r="R327" t="n">
+        <v>12.1302999757394</v>
+      </c>
+      <c r="S327" t="n">
+        <v>1706.705</v>
+      </c>
+      <c r="T327" t="n">
+        <v>1467.766297064468</v>
+      </c>
+      <c r="U327" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V327" t="n">
+        <v>-0.005289139633286255</v>
+      </c>
+      <c r="W327" t="n">
+        <v>-0.01593086873541605</v>
+      </c>
+      <c r="X327" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y327" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z327" t="n">
+        <v>0.4978975057601929</v>
+      </c>
+      <c r="AA327" t="n">
+        <v>13.57315373420715</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr"/>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E328" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F328" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H328" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I328" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J328" t="n">
+        <v>162</v>
+      </c>
+      <c r="K328" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L328" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M328" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N328" s="2" t="n">
+        <v>45832.64840297784</v>
+      </c>
+      <c r="O328" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="P328" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q328" t="n">
+        <v>4.25243</v>
+      </c>
+      <c r="R328" t="n">
+        <v>9.100678905943189</v>
+      </c>
+      <c r="S328" t="n">
+        <v>6269.400000000001</v>
+      </c>
+      <c r="T328" t="n">
+        <v>1474.309982762797</v>
+      </c>
+      <c r="U328" t="n">
+        <v>8.272543736854324</v>
+      </c>
+      <c r="V328" t="n">
+        <v>-0.01275510204081631</v>
+      </c>
+      <c r="W328" t="n">
+        <v>-0.009904175077424138</v>
+      </c>
+      <c r="X328" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y328" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z328" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="AA328" t="n">
+        <v>12.85747975540161</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E329" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F329" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H329" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I329" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J329" t="n">
+        <v>101</v>
+      </c>
+      <c r="K329" t="n">
+        <v>11</v>
+      </c>
+      <c r="L329" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M329" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N329" s="2" t="n">
+        <v>45832.64840297784</v>
+      </c>
+      <c r="O329" t="n">
+        <v>24700</v>
+      </c>
+      <c r="P329" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q329" t="n">
+        <v>2064.76</v>
+      </c>
+      <c r="R329" t="n">
+        <v>11.9626494120382</v>
+      </c>
+      <c r="S329" t="n">
+        <v>2494700</v>
+      </c>
+      <c r="T329" t="n">
+        <v>1208.227590615858</v>
+      </c>
+      <c r="U329" t="n">
+        <v>11.00337378959821</v>
+      </c>
+      <c r="V329" t="n">
+        <v>0.007012393998695465</v>
+      </c>
+      <c r="W329" t="n">
+        <v>0.002876579133476609</v>
+      </c>
+      <c r="X329" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y329" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z329" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="AA329" t="n">
         <v>12.66160106658936</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA329"/>
+  <dimension ref="A1:AA337"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30614,7 +30614,7 @@
         <v>100</v>
       </c>
       <c r="N322" s="2" t="n">
-        <v>45832.64840297784</v>
+        <v>45832.64840297454</v>
       </c>
       <c r="O322" t="n">
         <v>1</v>
@@ -30705,7 +30705,7 @@
         <v>12.02781891822815</v>
       </c>
       <c r="N323" s="2" t="n">
-        <v>45832.64840297784</v>
+        <v>45832.64840297454</v>
       </c>
       <c r="O323" t="n">
         <v>36.05</v>
@@ -30796,7 +30796,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N324" s="2" t="n">
-        <v>45832.64840297784</v>
+        <v>45832.64840297454</v>
       </c>
       <c r="O324" t="n">
         <v>374.51</v>
@@ -30891,7 +30891,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N325" s="2" t="n">
-        <v>45832.64840297784</v>
+        <v>45832.64840297454</v>
       </c>
       <c r="O325" t="n">
         <v>0.75</v>
@@ -30986,7 +30986,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N326" s="2" t="n">
-        <v>45832.64840297784</v>
+        <v>45832.64840297454</v>
       </c>
       <c r="O326" t="n">
         <v>25.7</v>
@@ -31081,7 +31081,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N327" s="2" t="n">
-        <v>45832.64840297784</v>
+        <v>45832.64840297454</v>
       </c>
       <c r="O327" t="n">
         <v>14.105</v>
@@ -31172,7 +31172,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N328" s="2" t="n">
-        <v>45832.64840297784</v>
+        <v>45832.64840297454</v>
       </c>
       <c r="O328" t="n">
         <v>38.7</v>
@@ -31267,7 +31267,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N329" s="2" t="n">
-        <v>45832.64840297784</v>
+        <v>45832.64840297454</v>
       </c>
       <c r="O329" t="n">
         <v>24700</v>
@@ -31308,6 +31308,756 @@
         <v>0.4939931035041809</v>
       </c>
       <c r="AA329" t="n">
+        <v>12.66160106658936</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F330" t="n">
+        <v>1</v>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H330" t="n">
+        <v>1</v>
+      </c>
+      <c r="I330" t="n">
+        <v>1</v>
+      </c>
+      <c r="J330" t="n">
+        <v>1</v>
+      </c>
+      <c r="K330" t="n">
+        <v>100</v>
+      </c>
+      <c r="L330" t="n">
+        <v>100</v>
+      </c>
+      <c r="M330" t="n">
+        <v>100</v>
+      </c>
+      <c r="N330" s="2" t="n">
+        <v>45832.69357599643</v>
+      </c>
+      <c r="O330" t="n">
+        <v>1</v>
+      </c>
+      <c r="P330" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q330" t="n">
+        <v>1</v>
+      </c>
+      <c r="R330" t="n">
+        <v>1</v>
+      </c>
+      <c r="S330" t="n">
+        <v>0</v>
+      </c>
+      <c r="T330" t="n">
+        <v>0.2858026033402439</v>
+      </c>
+      <c r="U330" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V330" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W330" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X330" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y330" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z330" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA330" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>DE000A0XYG76</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>DR0.DE</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr"/>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>DT.ROHSTOFF AG NA O.N.</t>
+        </is>
+      </c>
+      <c r="E331" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F331" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H331" t="n">
+        <v>1</v>
+      </c>
+      <c r="I331" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="J331" t="n">
+        <v>39</v>
+      </c>
+      <c r="K331" t="n">
+        <v>11</v>
+      </c>
+      <c r="L331" t="n">
+        <v>0.4329348504543304</v>
+      </c>
+      <c r="M331" t="n">
+        <v>12.02781891822815</v>
+      </c>
+      <c r="N331" s="2" t="n">
+        <v>45832.69357599643</v>
+      </c>
+      <c r="O331" t="n">
+        <v>36.15</v>
+      </c>
+      <c r="P331" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q331" t="n">
+        <v>1</v>
+      </c>
+      <c r="R331" t="n">
+        <v>36.15</v>
+      </c>
+      <c r="S331" t="n">
+        <v>1409.85</v>
+      </c>
+      <c r="T331" t="n">
+        <v>1409.85</v>
+      </c>
+      <c r="U331" t="n">
+        <v>34.92</v>
+      </c>
+      <c r="V331" t="n">
+        <v>-0.0411140583554378</v>
+      </c>
+      <c r="W331" t="n">
+        <v>-0.0411140583554378</v>
+      </c>
+      <c r="X331" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y331" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z331" t="n">
+        <v>0.4433653950691223</v>
+      </c>
+      <c r="AA331" t="n">
+        <v>12.17899870872498</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr"/>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E332" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F332" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H332" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I332" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J332" t="n">
+        <v>3</v>
+      </c>
+      <c r="K332" t="n">
+        <v>10</v>
+      </c>
+      <c r="L332" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M332" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N332" s="2" t="n">
+        <v>45832.69357599643</v>
+      </c>
+      <c r="O332" t="n">
+        <v>375</v>
+      </c>
+      <c r="P332" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q332" t="n">
+        <v>0.8528</v>
+      </c>
+      <c r="R332" t="n">
+        <v>439.7279549718574</v>
+      </c>
+      <c r="S332" t="n">
+        <v>1125</v>
+      </c>
+      <c r="T332" t="n">
+        <v>1319.183864915572</v>
+      </c>
+      <c r="U332" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V332" t="n">
+        <v>0.01994745230725714</v>
+      </c>
+      <c r="W332" t="n">
+        <v>0.02098797093238303</v>
+      </c>
+      <c r="X332" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y332" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z332" t="n">
+        <v>0.5300061702728271</v>
+      </c>
+      <c r="AA332" t="n">
+        <v>12.44775533676147</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E333" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F333" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H333" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I333" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J333" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K333" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L333" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M333" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N333" s="2" t="n">
+        <v>45832.69357599643</v>
+      </c>
+      <c r="O333" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P333" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q333" t="n">
+        <v>1.7868</v>
+      </c>
+      <c r="R333" t="n">
+        <v>0.41974479516454</v>
+      </c>
+      <c r="S333" t="n">
+        <v>2748</v>
+      </c>
+      <c r="T333" t="n">
+        <v>1537.944929482874</v>
+      </c>
+      <c r="U333" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="V333" t="n">
+        <v>0.03448275862068972</v>
+      </c>
+      <c r="W333" t="n">
+        <v>0.02740209814501759</v>
+      </c>
+      <c r="X333" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y333" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z333" t="n">
+        <v>0.4560990333557129</v>
+      </c>
+      <c r="AA333" t="n">
+        <v>11.05002820491791</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E334" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F334" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H334" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I334" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J334" t="n">
+        <v>537</v>
+      </c>
+      <c r="K334" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L334" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M334" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N334" s="2" t="n">
+        <v>45832.69357599643</v>
+      </c>
+      <c r="O334" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="P334" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q334" t="n">
+        <v>9.12016</v>
+      </c>
+      <c r="R334" t="n">
+        <v>2.81793301871897</v>
+      </c>
+      <c r="S334" t="n">
+        <v>13800.9</v>
+      </c>
+      <c r="T334" t="n">
+        <v>1513.230031052087</v>
+      </c>
+      <c r="U334" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V334" t="n">
+        <v>0.01984126984126977</v>
+      </c>
+      <c r="W334" t="n">
+        <v>0.01093794337498388</v>
+      </c>
+      <c r="X334" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y334" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z334" t="n">
+        <v>0.5799588561058044</v>
+      </c>
+      <c r="AA334" t="n">
+        <v>12.64349049758911</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E335" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F335" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H335" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I335" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J335" t="n">
+        <v>121</v>
+      </c>
+      <c r="K335" t="n">
+        <v>12</v>
+      </c>
+      <c r="L335" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M335" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N335" s="2" t="n">
+        <v>45832.69357599643</v>
+      </c>
+      <c r="O335" t="n">
+        <v>14.16</v>
+      </c>
+      <c r="P335" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q335" t="n">
+        <v>1.16225</v>
+      </c>
+      <c r="R335" t="n">
+        <v>12.18326521832652</v>
+      </c>
+      <c r="S335" t="n">
+        <v>1713.36</v>
+      </c>
+      <c r="T335" t="n">
+        <v>1474.175091417509</v>
+      </c>
+      <c r="U335" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V335" t="n">
+        <v>-0.001410437235543016</v>
+      </c>
+      <c r="W335" t="n">
+        <v>-0.01163406978038861</v>
+      </c>
+      <c r="X335" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y335" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z335" t="n">
+        <v>0.4978975057601929</v>
+      </c>
+      <c r="AA335" t="n">
+        <v>13.57315373420715</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr"/>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E336" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F336" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H336" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I336" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J336" t="n">
+        <v>162</v>
+      </c>
+      <c r="K336" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L336" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M336" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N336" s="2" t="n">
+        <v>45832.69357599643</v>
+      </c>
+      <c r="O336" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="P336" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q336" t="n">
+        <v>4.24939</v>
+      </c>
+      <c r="R336" t="n">
+        <v>9.1071895024933</v>
+      </c>
+      <c r="S336" t="n">
+        <v>6269.400000000001</v>
+      </c>
+      <c r="T336" t="n">
+        <v>1475.364699403915</v>
+      </c>
+      <c r="U336" t="n">
+        <v>8.272543736854324</v>
+      </c>
+      <c r="V336" t="n">
+        <v>-0.01275510204081631</v>
+      </c>
+      <c r="W336" t="n">
+        <v>-0.009195863694433704</v>
+      </c>
+      <c r="X336" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y336" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z336" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="AA336" t="n">
+        <v>12.85747975540161</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E337" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F337" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H337" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I337" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J337" t="n">
+        <v>101</v>
+      </c>
+      <c r="K337" t="n">
+        <v>11</v>
+      </c>
+      <c r="L337" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M337" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N337" s="2" t="n">
+        <v>45832.69357599643</v>
+      </c>
+      <c r="O337" t="n">
+        <v>24700</v>
+      </c>
+      <c r="P337" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q337" t="n">
+        <v>2061.17</v>
+      </c>
+      <c r="R337" t="n">
+        <v>11.98348510797266</v>
+      </c>
+      <c r="S337" t="n">
+        <v>2494700</v>
+      </c>
+      <c r="T337" t="n">
+        <v>1210.331995905238</v>
+      </c>
+      <c r="U337" t="n">
+        <v>11.00337378959821</v>
+      </c>
+      <c r="V337" t="n">
+        <v>0.007012393998695465</v>
+      </c>
+      <c r="W337" t="n">
+        <v>0.00462331856743381</v>
+      </c>
+      <c r="X337" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y337" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z337" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="AA337" t="n">
         <v>12.66160106658936</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA337"/>
+  <dimension ref="A1:AA345"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31364,7 +31364,7 @@
         <v>100</v>
       </c>
       <c r="N330" s="2" t="n">
-        <v>45832.69357599643</v>
+        <v>45832.69357599537</v>
       </c>
       <c r="O330" t="n">
         <v>1</v>
@@ -31455,7 +31455,7 @@
         <v>12.02781891822815</v>
       </c>
       <c r="N331" s="2" t="n">
-        <v>45832.69357599643</v>
+        <v>45832.69357599537</v>
       </c>
       <c r="O331" t="n">
         <v>36.15</v>
@@ -31546,7 +31546,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N332" s="2" t="n">
-        <v>45832.69357599643</v>
+        <v>45832.69357599537</v>
       </c>
       <c r="O332" t="n">
         <v>375</v>
@@ -31641,7 +31641,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N333" s="2" t="n">
-        <v>45832.69357599643</v>
+        <v>45832.69357599537</v>
       </c>
       <c r="O333" t="n">
         <v>0.75</v>
@@ -31736,7 +31736,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N334" s="2" t="n">
-        <v>45832.69357599643</v>
+        <v>45832.69357599537</v>
       </c>
       <c r="O334" t="n">
         <v>25.7</v>
@@ -31831,7 +31831,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N335" s="2" t="n">
-        <v>45832.69357599643</v>
+        <v>45832.69357599537</v>
       </c>
       <c r="O335" t="n">
         <v>14.16</v>
@@ -31922,7 +31922,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N336" s="2" t="n">
-        <v>45832.69357599643</v>
+        <v>45832.69357599537</v>
       </c>
       <c r="O336" t="n">
         <v>38.7</v>
@@ -32017,7 +32017,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N337" s="2" t="n">
-        <v>45832.69357599643</v>
+        <v>45832.69357599537</v>
       </c>
       <c r="O337" t="n">
         <v>24700</v>
@@ -32058,6 +32058,756 @@
         <v>0.4939931035041809</v>
       </c>
       <c r="AA337" t="n">
+        <v>12.66160106658936</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F338" t="n">
+        <v>1</v>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H338" t="n">
+        <v>1</v>
+      </c>
+      <c r="I338" t="n">
+        <v>1</v>
+      </c>
+      <c r="J338" t="n">
+        <v>1</v>
+      </c>
+      <c r="K338" t="n">
+        <v>100</v>
+      </c>
+      <c r="L338" t="n">
+        <v>100</v>
+      </c>
+      <c r="M338" t="n">
+        <v>100</v>
+      </c>
+      <c r="N338" s="2" t="n">
+        <v>45832.73136576778</v>
+      </c>
+      <c r="O338" t="n">
+        <v>1</v>
+      </c>
+      <c r="P338" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q338" t="n">
+        <v>1</v>
+      </c>
+      <c r="R338" t="n">
+        <v>1</v>
+      </c>
+      <c r="S338" t="n">
+        <v>0</v>
+      </c>
+      <c r="T338" t="n">
+        <v>0.2858026033402439</v>
+      </c>
+      <c r="U338" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V338" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W338" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X338" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y338" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z338" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA338" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>DE000A0XYG76</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>DR0.DE</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr"/>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>DT.ROHSTOFF AG NA O.N.</t>
+        </is>
+      </c>
+      <c r="E339" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F339" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H339" t="n">
+        <v>1</v>
+      </c>
+      <c r="I339" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="J339" t="n">
+        <v>39</v>
+      </c>
+      <c r="K339" t="n">
+        <v>11</v>
+      </c>
+      <c r="L339" t="n">
+        <v>0.4329348504543304</v>
+      </c>
+      <c r="M339" t="n">
+        <v>12.02781891822815</v>
+      </c>
+      <c r="N339" s="2" t="n">
+        <v>45832.73136576778</v>
+      </c>
+      <c r="O339" t="n">
+        <v>36.15</v>
+      </c>
+      <c r="P339" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q339" t="n">
+        <v>1</v>
+      </c>
+      <c r="R339" t="n">
+        <v>36.15</v>
+      </c>
+      <c r="S339" t="n">
+        <v>1409.85</v>
+      </c>
+      <c r="T339" t="n">
+        <v>1409.85</v>
+      </c>
+      <c r="U339" t="n">
+        <v>34.92</v>
+      </c>
+      <c r="V339" t="n">
+        <v>-0.0411140583554378</v>
+      </c>
+      <c r="W339" t="n">
+        <v>-0.0411140583554378</v>
+      </c>
+      <c r="X339" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y339" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z339" t="n">
+        <v>0.4433653950691223</v>
+      </c>
+      <c r="AA339" t="n">
+        <v>12.17899870872498</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr"/>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E340" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F340" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H340" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I340" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J340" t="n">
+        <v>3</v>
+      </c>
+      <c r="K340" t="n">
+        <v>10</v>
+      </c>
+      <c r="L340" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M340" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N340" s="2" t="n">
+        <v>45832.73136576778</v>
+      </c>
+      <c r="O340" t="n">
+        <v>375</v>
+      </c>
+      <c r="P340" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q340" t="n">
+        <v>0.85279</v>
+      </c>
+      <c r="R340" t="n">
+        <v>439.7331113169713</v>
+      </c>
+      <c r="S340" t="n">
+        <v>1125</v>
+      </c>
+      <c r="T340" t="n">
+        <v>1319.199333950914</v>
+      </c>
+      <c r="U340" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V340" t="n">
+        <v>0.01994745230725714</v>
+      </c>
+      <c r="W340" t="n">
+        <v>0.02099994325817156</v>
+      </c>
+      <c r="X340" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y340" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z340" t="n">
+        <v>0.5300061702728271</v>
+      </c>
+      <c r="AA340" t="n">
+        <v>12.44775533676147</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E341" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F341" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H341" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I341" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J341" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K341" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L341" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M341" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N341" s="2" t="n">
+        <v>45832.73136576778</v>
+      </c>
+      <c r="O341" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P341" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q341" t="n">
+        <v>1.78687</v>
+      </c>
+      <c r="R341" t="n">
+        <v>0.4197283518107081</v>
+      </c>
+      <c r="S341" t="n">
+        <v>2748</v>
+      </c>
+      <c r="T341" t="n">
+        <v>1537.884681034435</v>
+      </c>
+      <c r="U341" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="V341" t="n">
+        <v>0.03448275862068972</v>
+      </c>
+      <c r="W341" t="n">
+        <v>0.02736185003134928</v>
+      </c>
+      <c r="X341" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y341" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z341" t="n">
+        <v>0.4560990333557129</v>
+      </c>
+      <c r="AA341" t="n">
+        <v>11.05002820491791</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E342" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F342" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H342" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I342" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J342" t="n">
+        <v>537</v>
+      </c>
+      <c r="K342" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L342" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M342" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N342" s="2" t="n">
+        <v>45832.73136576778</v>
+      </c>
+      <c r="O342" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="P342" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q342" t="n">
+        <v>9.127000000000001</v>
+      </c>
+      <c r="R342" t="n">
+        <v>2.815821189876191</v>
+      </c>
+      <c r="S342" t="n">
+        <v>13800.9</v>
+      </c>
+      <c r="T342" t="n">
+        <v>1512.095978963515</v>
+      </c>
+      <c r="U342" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V342" t="n">
+        <v>0.01984126984126977</v>
+      </c>
+      <c r="W342" t="n">
+        <v>0.01018032142552783</v>
+      </c>
+      <c r="X342" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y342" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z342" t="n">
+        <v>0.5799588561058044</v>
+      </c>
+      <c r="AA342" t="n">
+        <v>12.64349049758911</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E343" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F343" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H343" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I343" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J343" t="n">
+        <v>121</v>
+      </c>
+      <c r="K343" t="n">
+        <v>12</v>
+      </c>
+      <c r="L343" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M343" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N343" s="2" t="n">
+        <v>45832.73136576778</v>
+      </c>
+      <c r="O343" t="n">
+        <v>14.19</v>
+      </c>
+      <c r="P343" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q343" t="n">
+        <v>1.1631964</v>
+      </c>
+      <c r="R343" t="n">
+        <v>12.19914366997697</v>
+      </c>
+      <c r="S343" t="n">
+        <v>1716.99</v>
+      </c>
+      <c r="T343" t="n">
+        <v>1476.096384067214</v>
+      </c>
+      <c r="U343" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V343" t="n">
+        <v>0.000705218617771397</v>
+      </c>
+      <c r="W343" t="n">
+        <v>-0.01034593229386849</v>
+      </c>
+      <c r="X343" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y343" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z343" t="n">
+        <v>0.4978975057601929</v>
+      </c>
+      <c r="AA343" t="n">
+        <v>13.57315373420715</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr"/>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E344" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F344" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H344" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I344" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J344" t="n">
+        <v>162</v>
+      </c>
+      <c r="K344" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L344" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M344" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N344" s="2" t="n">
+        <v>45832.73136576778</v>
+      </c>
+      <c r="O344" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="P344" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q344" t="n">
+        <v>4.25177</v>
+      </c>
+      <c r="R344" t="n">
+        <v>9.102091599498563</v>
+      </c>
+      <c r="S344" t="n">
+        <v>6269.400000000001</v>
+      </c>
+      <c r="T344" t="n">
+        <v>1474.538839118767</v>
+      </c>
+      <c r="U344" t="n">
+        <v>8.272543736854324</v>
+      </c>
+      <c r="V344" t="n">
+        <v>-0.01275510204081631</v>
+      </c>
+      <c r="W344" t="n">
+        <v>-0.009750483028124646</v>
+      </c>
+      <c r="X344" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y344" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z344" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="AA344" t="n">
+        <v>12.85747975540161</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E345" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F345" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H345" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I345" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J345" t="n">
+        <v>101</v>
+      </c>
+      <c r="K345" t="n">
+        <v>11</v>
+      </c>
+      <c r="L345" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M345" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N345" s="2" t="n">
+        <v>45832.73136576778</v>
+      </c>
+      <c r="O345" t="n">
+        <v>24700</v>
+      </c>
+      <c r="P345" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q345" t="n">
+        <v>2059.68</v>
+      </c>
+      <c r="R345" t="n">
+        <v>11.99215412102851</v>
+      </c>
+      <c r="S345" t="n">
+        <v>2494700</v>
+      </c>
+      <c r="T345" t="n">
+        <v>1211.207566223879</v>
+      </c>
+      <c r="U345" t="n">
+        <v>11.00337378959821</v>
+      </c>
+      <c r="V345" t="n">
+        <v>0.007012393998695465</v>
+      </c>
+      <c r="W345" t="n">
+        <v>0.005350076483549682</v>
+      </c>
+      <c r="X345" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y345" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z345" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="AA345" t="n">
         <v>12.66160106658936</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA345"/>
+  <dimension ref="A1:AA353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32114,7 +32114,7 @@
         <v>100</v>
       </c>
       <c r="N338" s="2" t="n">
-        <v>45832.73136576778</v>
+        <v>45832.73136576389</v>
       </c>
       <c r="O338" t="n">
         <v>1</v>
@@ -32205,7 +32205,7 @@
         <v>12.02781891822815</v>
       </c>
       <c r="N339" s="2" t="n">
-        <v>45832.73136576778</v>
+        <v>45832.73136576389</v>
       </c>
       <c r="O339" t="n">
         <v>36.15</v>
@@ -32296,7 +32296,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N340" s="2" t="n">
-        <v>45832.73136576778</v>
+        <v>45832.73136576389</v>
       </c>
       <c r="O340" t="n">
         <v>375</v>
@@ -32391,7 +32391,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N341" s="2" t="n">
-        <v>45832.73136576778</v>
+        <v>45832.73136576389</v>
       </c>
       <c r="O341" t="n">
         <v>0.75</v>
@@ -32486,7 +32486,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N342" s="2" t="n">
-        <v>45832.73136576778</v>
+        <v>45832.73136576389</v>
       </c>
       <c r="O342" t="n">
         <v>25.7</v>
@@ -32581,7 +32581,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N343" s="2" t="n">
-        <v>45832.73136576778</v>
+        <v>45832.73136576389</v>
       </c>
       <c r="O343" t="n">
         <v>14.19</v>
@@ -32672,7 +32672,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N344" s="2" t="n">
-        <v>45832.73136576778</v>
+        <v>45832.73136576389</v>
       </c>
       <c r="O344" t="n">
         <v>38.7</v>
@@ -32767,7 +32767,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N345" s="2" t="n">
-        <v>45832.73136576778</v>
+        <v>45832.73136576389</v>
       </c>
       <c r="O345" t="n">
         <v>24700</v>
@@ -32808,6 +32808,756 @@
         <v>0.4939931035041809</v>
       </c>
       <c r="AA345" t="n">
+        <v>12.66160106658936</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F346" t="n">
+        <v>1</v>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H346" t="n">
+        <v>1</v>
+      </c>
+      <c r="I346" t="n">
+        <v>1</v>
+      </c>
+      <c r="J346" t="n">
+        <v>1</v>
+      </c>
+      <c r="K346" t="n">
+        <v>100</v>
+      </c>
+      <c r="L346" t="n">
+        <v>100</v>
+      </c>
+      <c r="M346" t="n">
+        <v>100</v>
+      </c>
+      <c r="N346" s="2" t="n">
+        <v>45832.77938498239</v>
+      </c>
+      <c r="O346" t="n">
+        <v>1</v>
+      </c>
+      <c r="P346" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q346" t="n">
+        <v>1</v>
+      </c>
+      <c r="R346" t="n">
+        <v>1</v>
+      </c>
+      <c r="S346" t="n">
+        <v>0</v>
+      </c>
+      <c r="T346" t="n">
+        <v>0.2858026033402439</v>
+      </c>
+      <c r="U346" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V346" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W346" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X346" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y346" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z346" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA346" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>DE000A0XYG76</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>DR0.DE</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr"/>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>DT.ROHSTOFF AG NA O.N.</t>
+        </is>
+      </c>
+      <c r="E347" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F347" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H347" t="n">
+        <v>1</v>
+      </c>
+      <c r="I347" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="J347" t="n">
+        <v>39</v>
+      </c>
+      <c r="K347" t="n">
+        <v>11</v>
+      </c>
+      <c r="L347" t="n">
+        <v>0.4329348504543304</v>
+      </c>
+      <c r="M347" t="n">
+        <v>12.02781891822815</v>
+      </c>
+      <c r="N347" s="2" t="n">
+        <v>45832.77938498239</v>
+      </c>
+      <c r="O347" t="n">
+        <v>36.15</v>
+      </c>
+      <c r="P347" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q347" t="n">
+        <v>1</v>
+      </c>
+      <c r="R347" t="n">
+        <v>36.15</v>
+      </c>
+      <c r="S347" t="n">
+        <v>1409.85</v>
+      </c>
+      <c r="T347" t="n">
+        <v>1409.85</v>
+      </c>
+      <c r="U347" t="n">
+        <v>34.92</v>
+      </c>
+      <c r="V347" t="n">
+        <v>-0.0411140583554378</v>
+      </c>
+      <c r="W347" t="n">
+        <v>-0.0411140583554378</v>
+      </c>
+      <c r="X347" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y347" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z347" t="n">
+        <v>0.4433653950691223</v>
+      </c>
+      <c r="AA347" t="n">
+        <v>12.17899870872498</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr"/>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E348" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F348" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H348" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I348" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J348" t="n">
+        <v>3</v>
+      </c>
+      <c r="K348" t="n">
+        <v>10</v>
+      </c>
+      <c r="L348" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M348" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N348" s="2" t="n">
+        <v>45832.77938498239</v>
+      </c>
+      <c r="O348" t="n">
+        <v>375</v>
+      </c>
+      <c r="P348" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q348" t="n">
+        <v>0.85276</v>
+      </c>
+      <c r="R348" t="n">
+        <v>439.7485810779118</v>
+      </c>
+      <c r="S348" t="n">
+        <v>1125</v>
+      </c>
+      <c r="T348" t="n">
+        <v>1319.245743233735</v>
+      </c>
+      <c r="U348" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V348" t="n">
+        <v>0.01994745230725714</v>
+      </c>
+      <c r="W348" t="n">
+        <v>0.02103586192027795</v>
+      </c>
+      <c r="X348" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y348" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z348" t="n">
+        <v>0.5300061702728271</v>
+      </c>
+      <c r="AA348" t="n">
+        <v>12.44775533676147</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E349" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F349" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H349" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I349" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J349" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K349" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L349" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M349" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N349" s="2" t="n">
+        <v>45832.77938498239</v>
+      </c>
+      <c r="O349" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P349" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q349" t="n">
+        <v>1.78662</v>
+      </c>
+      <c r="R349" t="n">
+        <v>0.4197870839909997</v>
+      </c>
+      <c r="S349" t="n">
+        <v>2748</v>
+      </c>
+      <c r="T349" t="n">
+        <v>1538.099875743023</v>
+      </c>
+      <c r="U349" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="V349" t="n">
+        <v>0.03448275862068972</v>
+      </c>
+      <c r="W349" t="n">
+        <v>0.0275056077764253</v>
+      </c>
+      <c r="X349" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y349" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z349" t="n">
+        <v>0.4560990333557129</v>
+      </c>
+      <c r="AA349" t="n">
+        <v>11.05002820491791</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E350" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F350" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H350" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I350" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J350" t="n">
+        <v>537</v>
+      </c>
+      <c r="K350" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L350" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M350" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N350" s="2" t="n">
+        <v>45832.77938498239</v>
+      </c>
+      <c r="O350" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="P350" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q350" t="n">
+        <v>9.121420000000001</v>
+      </c>
+      <c r="R350" t="n">
+        <v>2.817543759633916</v>
+      </c>
+      <c r="S350" t="n">
+        <v>13800.9</v>
+      </c>
+      <c r="T350" t="n">
+        <v>1513.020998923413</v>
+      </c>
+      <c r="U350" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V350" t="n">
+        <v>0.01984126984126977</v>
+      </c>
+      <c r="W350" t="n">
+        <v>0.01079829606034943</v>
+      </c>
+      <c r="X350" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y350" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z350" t="n">
+        <v>0.5799588561058044</v>
+      </c>
+      <c r="AA350" t="n">
+        <v>12.64349049758911</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E351" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F351" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H351" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I351" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J351" t="n">
+        <v>121</v>
+      </c>
+      <c r="K351" t="n">
+        <v>12</v>
+      </c>
+      <c r="L351" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M351" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N351" s="2" t="n">
+        <v>45832.77938498239</v>
+      </c>
+      <c r="O351" t="n">
+        <v>14.125</v>
+      </c>
+      <c r="P351" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q351" t="n">
+        <v>1.1623852</v>
+      </c>
+      <c r="R351" t="n">
+        <v>12.15173765116762</v>
+      </c>
+      <c r="S351" t="n">
+        <v>1709.125</v>
+      </c>
+      <c r="T351" t="n">
+        <v>1470.360255791282</v>
+      </c>
+      <c r="U351" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V351" t="n">
+        <v>-0.003878702397743239</v>
+      </c>
+      <c r="W351" t="n">
+        <v>-0.01419173988640399</v>
+      </c>
+      <c r="X351" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y351" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z351" t="n">
+        <v>0.4978975057601929</v>
+      </c>
+      <c r="AA351" t="n">
+        <v>13.57315373420715</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr"/>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E352" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F352" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H352" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I352" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J352" t="n">
+        <v>162</v>
+      </c>
+      <c r="K352" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L352" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M352" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N352" s="2" t="n">
+        <v>45832.77938498239</v>
+      </c>
+      <c r="O352" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="P352" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q352" t="n">
+        <v>4.25197</v>
+      </c>
+      <c r="R352" t="n">
+        <v>9.101663464229523</v>
+      </c>
+      <c r="S352" t="n">
+        <v>6269.400000000001</v>
+      </c>
+      <c r="T352" t="n">
+        <v>1474.469481205183</v>
+      </c>
+      <c r="U352" t="n">
+        <v>8.272543736854324</v>
+      </c>
+      <c r="V352" t="n">
+        <v>-0.01275510204081631</v>
+      </c>
+      <c r="W352" t="n">
+        <v>-0.009797061414941743</v>
+      </c>
+      <c r="X352" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y352" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z352" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="AA352" t="n">
+        <v>12.85747975540161</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E353" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F353" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H353" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I353" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J353" t="n">
+        <v>101</v>
+      </c>
+      <c r="K353" t="n">
+        <v>11</v>
+      </c>
+      <c r="L353" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M353" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N353" s="2" t="n">
+        <v>45832.77938498239</v>
+      </c>
+      <c r="O353" t="n">
+        <v>24700</v>
+      </c>
+      <c r="P353" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q353" t="n">
+        <v>2060.49</v>
+      </c>
+      <c r="R353" t="n">
+        <v>11.98743988080505</v>
+      </c>
+      <c r="S353" t="n">
+        <v>2494700</v>
+      </c>
+      <c r="T353" t="n">
+        <v>1210.73142796131</v>
+      </c>
+      <c r="U353" t="n">
+        <v>11.00337378959821</v>
+      </c>
+      <c r="V353" t="n">
+        <v>0.007012393998695465</v>
+      </c>
+      <c r="W353" t="n">
+        <v>0.004954862936310089</v>
+      </c>
+      <c r="X353" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y353" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z353" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="AA353" t="n">
         <v>12.66160106658936</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA353"/>
+  <dimension ref="A1:AA361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32864,7 +32864,7 @@
         <v>100</v>
       </c>
       <c r="N346" s="2" t="n">
-        <v>45832.77938498239</v>
+        <v>45832.77938497685</v>
       </c>
       <c r="O346" t="n">
         <v>1</v>
@@ -32955,7 +32955,7 @@
         <v>12.02781891822815</v>
       </c>
       <c r="N347" s="2" t="n">
-        <v>45832.77938498239</v>
+        <v>45832.77938497685</v>
       </c>
       <c r="O347" t="n">
         <v>36.15</v>
@@ -33046,7 +33046,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N348" s="2" t="n">
-        <v>45832.77938498239</v>
+        <v>45832.77938497685</v>
       </c>
       <c r="O348" t="n">
         <v>375</v>
@@ -33141,7 +33141,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N349" s="2" t="n">
-        <v>45832.77938498239</v>
+        <v>45832.77938497685</v>
       </c>
       <c r="O349" t="n">
         <v>0.75</v>
@@ -33236,7 +33236,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N350" s="2" t="n">
-        <v>45832.77938498239</v>
+        <v>45832.77938497685</v>
       </c>
       <c r="O350" t="n">
         <v>25.7</v>
@@ -33331,7 +33331,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N351" s="2" t="n">
-        <v>45832.77938498239</v>
+        <v>45832.77938497685</v>
       </c>
       <c r="O351" t="n">
         <v>14.125</v>
@@ -33422,7 +33422,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N352" s="2" t="n">
-        <v>45832.77938498239</v>
+        <v>45832.77938497685</v>
       </c>
       <c r="O352" t="n">
         <v>38.7</v>
@@ -33517,7 +33517,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N353" s="2" t="n">
-        <v>45832.77938498239</v>
+        <v>45832.77938497685</v>
       </c>
       <c r="O353" t="n">
         <v>24700</v>
@@ -33558,6 +33558,756 @@
         <v>0.4939931035041809</v>
       </c>
       <c r="AA353" t="n">
+        <v>12.66160106658936</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F354" t="n">
+        <v>1</v>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H354" t="n">
+        <v>1</v>
+      </c>
+      <c r="I354" t="n">
+        <v>1</v>
+      </c>
+      <c r="J354" t="n">
+        <v>1</v>
+      </c>
+      <c r="K354" t="n">
+        <v>100</v>
+      </c>
+      <c r="L354" t="n">
+        <v>100</v>
+      </c>
+      <c r="M354" t="n">
+        <v>100</v>
+      </c>
+      <c r="N354" s="2" t="n">
+        <v>45832.80917448101</v>
+      </c>
+      <c r="O354" t="n">
+        <v>1</v>
+      </c>
+      <c r="P354" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q354" t="n">
+        <v>1</v>
+      </c>
+      <c r="R354" t="n">
+        <v>1</v>
+      </c>
+      <c r="S354" t="n">
+        <v>0</v>
+      </c>
+      <c r="T354" t="n">
+        <v>0.2858026033402439</v>
+      </c>
+      <c r="U354" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V354" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W354" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X354" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y354" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z354" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA354" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>DE000A0XYG76</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>DR0.DE</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr"/>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>DT.ROHSTOFF AG NA O.N.</t>
+        </is>
+      </c>
+      <c r="E355" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F355" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H355" t="n">
+        <v>1</v>
+      </c>
+      <c r="I355" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="J355" t="n">
+        <v>39</v>
+      </c>
+      <c r="K355" t="n">
+        <v>11</v>
+      </c>
+      <c r="L355" t="n">
+        <v>0.4329348504543304</v>
+      </c>
+      <c r="M355" t="n">
+        <v>12.02781891822815</v>
+      </c>
+      <c r="N355" s="2" t="n">
+        <v>45832.80917448101</v>
+      </c>
+      <c r="O355" t="n">
+        <v>36.15</v>
+      </c>
+      <c r="P355" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q355" t="n">
+        <v>1</v>
+      </c>
+      <c r="R355" t="n">
+        <v>36.15</v>
+      </c>
+      <c r="S355" t="n">
+        <v>1409.85</v>
+      </c>
+      <c r="T355" t="n">
+        <v>1409.85</v>
+      </c>
+      <c r="U355" t="n">
+        <v>34.92</v>
+      </c>
+      <c r="V355" t="n">
+        <v>-0.0411140583554378</v>
+      </c>
+      <c r="W355" t="n">
+        <v>-0.0411140583554378</v>
+      </c>
+      <c r="X355" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y355" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z355" t="n">
+        <v>0.4433653950691223</v>
+      </c>
+      <c r="AA355" t="n">
+        <v>12.17899870872498</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr"/>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E356" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F356" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H356" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I356" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J356" t="n">
+        <v>3</v>
+      </c>
+      <c r="K356" t="n">
+        <v>10</v>
+      </c>
+      <c r="L356" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M356" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N356" s="2" t="n">
+        <v>45832.80917448101</v>
+      </c>
+      <c r="O356" t="n">
+        <v>375</v>
+      </c>
+      <c r="P356" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q356" t="n">
+        <v>0.85265</v>
+      </c>
+      <c r="R356" t="n">
+        <v>439.8053128481792</v>
+      </c>
+      <c r="S356" t="n">
+        <v>1125</v>
+      </c>
+      <c r="T356" t="n">
+        <v>1319.415938544538</v>
+      </c>
+      <c r="U356" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V356" t="n">
+        <v>0.01994745230725714</v>
+      </c>
+      <c r="W356" t="n">
+        <v>0.02116758530597096</v>
+      </c>
+      <c r="X356" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y356" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z356" t="n">
+        <v>0.5300061702728271</v>
+      </c>
+      <c r="AA356" t="n">
+        <v>12.44775533676147</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E357" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F357" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H357" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I357" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J357" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K357" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L357" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M357" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N357" s="2" t="n">
+        <v>45832.80917448101</v>
+      </c>
+      <c r="O357" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P357" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q357" t="n">
+        <v>1.78639</v>
+      </c>
+      <c r="R357" t="n">
+        <v>0.4198411321156075</v>
+      </c>
+      <c r="S357" t="n">
+        <v>2748</v>
+      </c>
+      <c r="T357" t="n">
+        <v>1538.297908071586</v>
+      </c>
+      <c r="U357" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="V357" t="n">
+        <v>0.03448275862068972</v>
+      </c>
+      <c r="W357" t="n">
+        <v>0.02763790043916359</v>
+      </c>
+      <c r="X357" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y357" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z357" t="n">
+        <v>0.4560990333557129</v>
+      </c>
+      <c r="AA357" t="n">
+        <v>11.05002820491791</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E358" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F358" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H358" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I358" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J358" t="n">
+        <v>537</v>
+      </c>
+      <c r="K358" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L358" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M358" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N358" s="2" t="n">
+        <v>45832.80917448101</v>
+      </c>
+      <c r="O358" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="P358" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q358" t="n">
+        <v>9.123200000000001</v>
+      </c>
+      <c r="R358" t="n">
+        <v>2.816994037179937</v>
+      </c>
+      <c r="S358" t="n">
+        <v>13800.9</v>
+      </c>
+      <c r="T358" t="n">
+        <v>1512.725797965626</v>
+      </c>
+      <c r="U358" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V358" t="n">
+        <v>0.01984126984126977</v>
+      </c>
+      <c r="W358" t="n">
+        <v>0.01060108225740897</v>
+      </c>
+      <c r="X358" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y358" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z358" t="n">
+        <v>0.5799588561058044</v>
+      </c>
+      <c r="AA358" t="n">
+        <v>12.64349049758911</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E359" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F359" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H359" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I359" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J359" t="n">
+        <v>121</v>
+      </c>
+      <c r="K359" t="n">
+        <v>12</v>
+      </c>
+      <c r="L359" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M359" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N359" s="2" t="n">
+        <v>45832.80917448101</v>
+      </c>
+      <c r="O359" t="n">
+        <v>14.135</v>
+      </c>
+      <c r="P359" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q359" t="n">
+        <v>1.1626556</v>
+      </c>
+      <c r="R359" t="n">
+        <v>12.15751250843328</v>
+      </c>
+      <c r="S359" t="n">
+        <v>1710.335</v>
+      </c>
+      <c r="T359" t="n">
+        <v>1471.059013520427</v>
+      </c>
+      <c r="U359" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V359" t="n">
+        <v>-0.003173483779971731</v>
+      </c>
+      <c r="W359" t="n">
+        <v>-0.01372325528305851</v>
+      </c>
+      <c r="X359" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y359" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z359" t="n">
+        <v>0.4978975057601929</v>
+      </c>
+      <c r="AA359" t="n">
+        <v>13.57315373420715</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr"/>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E360" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F360" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H360" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I360" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J360" t="n">
+        <v>162</v>
+      </c>
+      <c r="K360" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L360" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M360" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N360" s="2" t="n">
+        <v>45832.80917448101</v>
+      </c>
+      <c r="O360" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="P360" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q360" t="n">
+        <v>4.24972</v>
+      </c>
+      <c r="R360" t="n">
+        <v>9.10648230942274</v>
+      </c>
+      <c r="S360" t="n">
+        <v>6269.400000000001</v>
+      </c>
+      <c r="T360" t="n">
+        <v>1475.250134126484</v>
+      </c>
+      <c r="U360" t="n">
+        <v>8.272543736854324</v>
+      </c>
+      <c r="V360" t="n">
+        <v>-0.01275510204081631</v>
+      </c>
+      <c r="W360" t="n">
+        <v>-0.009272801790350838</v>
+      </c>
+      <c r="X360" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y360" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z360" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="AA360" t="n">
+        <v>12.85747975540161</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E361" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F361" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H361" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I361" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J361" t="n">
+        <v>101</v>
+      </c>
+      <c r="K361" t="n">
+        <v>11</v>
+      </c>
+      <c r="L361" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M361" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N361" s="2" t="n">
+        <v>45832.80917448101</v>
+      </c>
+      <c r="O361" t="n">
+        <v>24700</v>
+      </c>
+      <c r="P361" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q361" t="n">
+        <v>2060.9</v>
+      </c>
+      <c r="R361" t="n">
+        <v>11.98505507302635</v>
+      </c>
+      <c r="S361" t="n">
+        <v>2494700</v>
+      </c>
+      <c r="T361" t="n">
+        <v>1210.490562375661</v>
+      </c>
+      <c r="U361" t="n">
+        <v>11.00337378959821</v>
+      </c>
+      <c r="V361" t="n">
+        <v>0.007012393998695465</v>
+      </c>
+      <c r="W361" t="n">
+        <v>0.004754934995214288</v>
+      </c>
+      <c r="X361" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y361" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z361" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="AA361" t="n">
         <v>12.66160106658936</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA361"/>
+  <dimension ref="A1:AA369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33614,7 +33614,7 @@
         <v>100</v>
       </c>
       <c r="N354" s="2" t="n">
-        <v>45832.80917448101</v>
+        <v>45832.80917447917</v>
       </c>
       <c r="O354" t="n">
         <v>1</v>
@@ -33705,7 +33705,7 @@
         <v>12.02781891822815</v>
       </c>
       <c r="N355" s="2" t="n">
-        <v>45832.80917448101</v>
+        <v>45832.80917447917</v>
       </c>
       <c r="O355" t="n">
         <v>36.15</v>
@@ -33796,7 +33796,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N356" s="2" t="n">
-        <v>45832.80917448101</v>
+        <v>45832.80917447917</v>
       </c>
       <c r="O356" t="n">
         <v>375</v>
@@ -33891,7 +33891,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N357" s="2" t="n">
-        <v>45832.80917448101</v>
+        <v>45832.80917447917</v>
       </c>
       <c r="O357" t="n">
         <v>0.75</v>
@@ -33986,7 +33986,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N358" s="2" t="n">
-        <v>45832.80917448101</v>
+        <v>45832.80917447917</v>
       </c>
       <c r="O358" t="n">
         <v>25.7</v>
@@ -34081,7 +34081,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N359" s="2" t="n">
-        <v>45832.80917448101</v>
+        <v>45832.80917447917</v>
       </c>
       <c r="O359" t="n">
         <v>14.135</v>
@@ -34172,7 +34172,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N360" s="2" t="n">
-        <v>45832.80917448101</v>
+        <v>45832.80917447917</v>
       </c>
       <c r="O360" t="n">
         <v>38.7</v>
@@ -34267,7 +34267,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N361" s="2" t="n">
-        <v>45832.80917448101</v>
+        <v>45832.80917447917</v>
       </c>
       <c r="O361" t="n">
         <v>24700</v>
@@ -34308,6 +34308,756 @@
         <v>0.4939931035041809</v>
       </c>
       <c r="AA361" t="n">
+        <v>12.66160106658936</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F362" t="n">
+        <v>1</v>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H362" t="n">
+        <v>1</v>
+      </c>
+      <c r="I362" t="n">
+        <v>1</v>
+      </c>
+      <c r="J362" t="n">
+        <v>1</v>
+      </c>
+      <c r="K362" t="n">
+        <v>100</v>
+      </c>
+      <c r="L362" t="n">
+        <v>100</v>
+      </c>
+      <c r="M362" t="n">
+        <v>100</v>
+      </c>
+      <c r="N362" s="2" t="n">
+        <v>45832.85631708262</v>
+      </c>
+      <c r="O362" t="n">
+        <v>1</v>
+      </c>
+      <c r="P362" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q362" t="n">
+        <v>1</v>
+      </c>
+      <c r="R362" t="n">
+        <v>1</v>
+      </c>
+      <c r="S362" t="n">
+        <v>0</v>
+      </c>
+      <c r="T362" t="n">
+        <v>0.2858026033402439</v>
+      </c>
+      <c r="U362" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V362" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W362" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X362" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y362" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z362" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA362" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>DE000A0XYG76</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>DR0.DE</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr"/>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>DT.ROHSTOFF AG NA O.N.</t>
+        </is>
+      </c>
+      <c r="E363" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F363" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H363" t="n">
+        <v>1</v>
+      </c>
+      <c r="I363" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="J363" t="n">
+        <v>39</v>
+      </c>
+      <c r="K363" t="n">
+        <v>11</v>
+      </c>
+      <c r="L363" t="n">
+        <v>0.4329348504543304</v>
+      </c>
+      <c r="M363" t="n">
+        <v>12.02781891822815</v>
+      </c>
+      <c r="N363" s="2" t="n">
+        <v>45832.85631708262</v>
+      </c>
+      <c r="O363" t="n">
+        <v>36.15</v>
+      </c>
+      <c r="P363" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q363" t="n">
+        <v>1</v>
+      </c>
+      <c r="R363" t="n">
+        <v>36.15</v>
+      </c>
+      <c r="S363" t="n">
+        <v>1409.85</v>
+      </c>
+      <c r="T363" t="n">
+        <v>1409.85</v>
+      </c>
+      <c r="U363" t="n">
+        <v>34.92</v>
+      </c>
+      <c r="V363" t="n">
+        <v>-0.0411140583554378</v>
+      </c>
+      <c r="W363" t="n">
+        <v>-0.0411140583554378</v>
+      </c>
+      <c r="X363" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y363" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z363" t="n">
+        <v>0.4433653950691223</v>
+      </c>
+      <c r="AA363" t="n">
+        <v>12.17899870872498</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr"/>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E364" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F364" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H364" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I364" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J364" t="n">
+        <v>3</v>
+      </c>
+      <c r="K364" t="n">
+        <v>10</v>
+      </c>
+      <c r="L364" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M364" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N364" s="2" t="n">
+        <v>45832.85631708262</v>
+      </c>
+      <c r="O364" t="n">
+        <v>375</v>
+      </c>
+      <c r="P364" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q364" t="n">
+        <v>0.85277</v>
+      </c>
+      <c r="R364" t="n">
+        <v>439.7434243699942</v>
+      </c>
+      <c r="S364" t="n">
+        <v>1125</v>
+      </c>
+      <c r="T364" t="n">
+        <v>1319.230273109983</v>
+      </c>
+      <c r="U364" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V364" t="n">
+        <v>0.01994745230725714</v>
+      </c>
+      <c r="W364" t="n">
+        <v>0.02102388875210925</v>
+      </c>
+      <c r="X364" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y364" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z364" t="n">
+        <v>0.5300061702728271</v>
+      </c>
+      <c r="AA364" t="n">
+        <v>12.44775533676147</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E365" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F365" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H365" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I365" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J365" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K365" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L365" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M365" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N365" s="2" t="n">
+        <v>45832.85631708262</v>
+      </c>
+      <c r="O365" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P365" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q365" t="n">
+        <v>1.78878</v>
+      </c>
+      <c r="R365" t="n">
+        <v>0.4192801797873411</v>
+      </c>
+      <c r="S365" t="n">
+        <v>2748</v>
+      </c>
+      <c r="T365" t="n">
+        <v>1536.242578740818</v>
+      </c>
+      <c r="U365" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="V365" t="n">
+        <v>0.03448275862068972</v>
+      </c>
+      <c r="W365" t="n">
+        <v>0.02626486709685771</v>
+      </c>
+      <c r="X365" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y365" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z365" t="n">
+        <v>0.4560990333557129</v>
+      </c>
+      <c r="AA365" t="n">
+        <v>11.05002820491791</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E366" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F366" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H366" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I366" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J366" t="n">
+        <v>537</v>
+      </c>
+      <c r="K366" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L366" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M366" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N366" s="2" t="n">
+        <v>45832.85631708262</v>
+      </c>
+      <c r="O366" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="P366" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q366" t="n">
+        <v>9.11459</v>
+      </c>
+      <c r="R366" t="n">
+        <v>2.819655080480855</v>
+      </c>
+      <c r="S366" t="n">
+        <v>13800.9</v>
+      </c>
+      <c r="T366" t="n">
+        <v>1514.154778218219</v>
+      </c>
+      <c r="U366" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V366" t="n">
+        <v>0.01984126984126977</v>
+      </c>
+      <c r="W366" t="n">
+        <v>0.01155573576549163</v>
+      </c>
+      <c r="X366" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y366" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z366" t="n">
+        <v>0.5799588561058044</v>
+      </c>
+      <c r="AA366" t="n">
+        <v>12.64349049758911</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E367" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F367" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H367" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I367" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J367" t="n">
+        <v>121</v>
+      </c>
+      <c r="K367" t="n">
+        <v>12</v>
+      </c>
+      <c r="L367" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M367" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N367" s="2" t="n">
+        <v>45832.85631708262</v>
+      </c>
+      <c r="O367" t="n">
+        <v>14.09</v>
+      </c>
+      <c r="P367" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q367" t="n">
+        <v>1.1615751</v>
+      </c>
+      <c r="R367" t="n">
+        <v>12.13008095645301</v>
+      </c>
+      <c r="S367" t="n">
+        <v>1704.89</v>
+      </c>
+      <c r="T367" t="n">
+        <v>1467.739795730814</v>
+      </c>
+      <c r="U367" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V367" t="n">
+        <v>-0.006346967559943573</v>
+      </c>
+      <c r="W367" t="n">
+        <v>-0.015948636648767</v>
+      </c>
+      <c r="X367" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y367" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z367" t="n">
+        <v>0.4978975057601929</v>
+      </c>
+      <c r="AA367" t="n">
+        <v>13.57315373420715</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr"/>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E368" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F368" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H368" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I368" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J368" t="n">
+        <v>162</v>
+      </c>
+      <c r="K368" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L368" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M368" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N368" s="2" t="n">
+        <v>45832.85631708262</v>
+      </c>
+      <c r="O368" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="P368" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q368" t="n">
+        <v>4.25185</v>
+      </c>
+      <c r="R368" t="n">
+        <v>9.101920340557641</v>
+      </c>
+      <c r="S368" t="n">
+        <v>6269.400000000001</v>
+      </c>
+      <c r="T368" t="n">
+        <v>1474.511095170338</v>
+      </c>
+      <c r="U368" t="n">
+        <v>8.272543736854324</v>
+      </c>
+      <c r="V368" t="n">
+        <v>-0.01275510204081631</v>
+      </c>
+      <c r="W368" t="n">
+        <v>-0.009769114908684373</v>
+      </c>
+      <c r="X368" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y368" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z368" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="AA368" t="n">
+        <v>12.85747975540161</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E369" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F369" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H369" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I369" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J369" t="n">
+        <v>101</v>
+      </c>
+      <c r="K369" t="n">
+        <v>11</v>
+      </c>
+      <c r="L369" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M369" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N369" s="2" t="n">
+        <v>45832.85631708262</v>
+      </c>
+      <c r="O369" t="n">
+        <v>24700</v>
+      </c>
+      <c r="P369" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q369" t="n">
+        <v>2062.1</v>
+      </c>
+      <c r="R369" t="n">
+        <v>11.9780805974492</v>
+      </c>
+      <c r="S369" t="n">
+        <v>2494700</v>
+      </c>
+      <c r="T369" t="n">
+        <v>1209.786140342369</v>
+      </c>
+      <c r="U369" t="n">
+        <v>11.00337378959821</v>
+      </c>
+      <c r="V369" t="n">
+        <v>0.007012393998695465</v>
+      </c>
+      <c r="W369" t="n">
+        <v>0.004170236909770475</v>
+      </c>
+      <c r="X369" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y369" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z369" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="AA369" t="n">
         <v>12.66160106658936</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA369"/>
+  <dimension ref="A1:AA377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34364,7 +34364,7 @@
         <v>100</v>
       </c>
       <c r="N362" s="2" t="n">
-        <v>45832.85631708262</v>
+        <v>45832.85631708334</v>
       </c>
       <c r="O362" t="n">
         <v>1</v>
@@ -34455,7 +34455,7 @@
         <v>12.02781891822815</v>
       </c>
       <c r="N363" s="2" t="n">
-        <v>45832.85631708262</v>
+        <v>45832.85631708334</v>
       </c>
       <c r="O363" t="n">
         <v>36.15</v>
@@ -34546,7 +34546,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N364" s="2" t="n">
-        <v>45832.85631708262</v>
+        <v>45832.85631708334</v>
       </c>
       <c r="O364" t="n">
         <v>375</v>
@@ -34641,7 +34641,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N365" s="2" t="n">
-        <v>45832.85631708262</v>
+        <v>45832.85631708334</v>
       </c>
       <c r="O365" t="n">
         <v>0.75</v>
@@ -34736,7 +34736,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N366" s="2" t="n">
-        <v>45832.85631708262</v>
+        <v>45832.85631708334</v>
       </c>
       <c r="O366" t="n">
         <v>25.7</v>
@@ -34831,7 +34831,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N367" s="2" t="n">
-        <v>45832.85631708262</v>
+        <v>45832.85631708334</v>
       </c>
       <c r="O367" t="n">
         <v>14.09</v>
@@ -34922,7 +34922,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N368" s="2" t="n">
-        <v>45832.85631708262</v>
+        <v>45832.85631708334</v>
       </c>
       <c r="O368" t="n">
         <v>38.7</v>
@@ -35017,7 +35017,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N369" s="2" t="n">
-        <v>45832.85631708262</v>
+        <v>45832.85631708334</v>
       </c>
       <c r="O369" t="n">
         <v>24700</v>
@@ -35058,6 +35058,756 @@
         <v>0.4939931035041809</v>
       </c>
       <c r="AA369" t="n">
+        <v>12.66160106658936</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F370" t="n">
+        <v>1</v>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H370" t="n">
+        <v>1</v>
+      </c>
+      <c r="I370" t="n">
+        <v>1</v>
+      </c>
+      <c r="J370" t="n">
+        <v>1</v>
+      </c>
+      <c r="K370" t="n">
+        <v>100</v>
+      </c>
+      <c r="L370" t="n">
+        <v>100</v>
+      </c>
+      <c r="M370" t="n">
+        <v>100</v>
+      </c>
+      <c r="N370" s="2" t="n">
+        <v>45832.89540211859</v>
+      </c>
+      <c r="O370" t="n">
+        <v>1</v>
+      </c>
+      <c r="P370" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q370" t="n">
+        <v>1</v>
+      </c>
+      <c r="R370" t="n">
+        <v>1</v>
+      </c>
+      <c r="S370" t="n">
+        <v>0</v>
+      </c>
+      <c r="T370" t="n">
+        <v>0.2858026033402439</v>
+      </c>
+      <c r="U370" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V370" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W370" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X370" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y370" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z370" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA370" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>DE000A0XYG76</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>DR0.DE</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr"/>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>DT.ROHSTOFF AG NA O.N.</t>
+        </is>
+      </c>
+      <c r="E371" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F371" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H371" t="n">
+        <v>1</v>
+      </c>
+      <c r="I371" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="J371" t="n">
+        <v>39</v>
+      </c>
+      <c r="K371" t="n">
+        <v>11</v>
+      </c>
+      <c r="L371" t="n">
+        <v>0.4329348504543304</v>
+      </c>
+      <c r="M371" t="n">
+        <v>12.02781891822815</v>
+      </c>
+      <c r="N371" s="2" t="n">
+        <v>45832.89540211859</v>
+      </c>
+      <c r="O371" t="n">
+        <v>36.15</v>
+      </c>
+      <c r="P371" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q371" t="n">
+        <v>1</v>
+      </c>
+      <c r="R371" t="n">
+        <v>36.15</v>
+      </c>
+      <c r="S371" t="n">
+        <v>1409.85</v>
+      </c>
+      <c r="T371" t="n">
+        <v>1409.85</v>
+      </c>
+      <c r="U371" t="n">
+        <v>34.92</v>
+      </c>
+      <c r="V371" t="n">
+        <v>-0.0411140583554378</v>
+      </c>
+      <c r="W371" t="n">
+        <v>-0.0411140583554378</v>
+      </c>
+      <c r="X371" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y371" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z371" t="n">
+        <v>0.4433653950691223</v>
+      </c>
+      <c r="AA371" t="n">
+        <v>12.17899870872498</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr"/>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E372" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F372" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H372" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I372" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J372" t="n">
+        <v>3</v>
+      </c>
+      <c r="K372" t="n">
+        <v>10</v>
+      </c>
+      <c r="L372" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M372" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N372" s="2" t="n">
+        <v>45832.89540211859</v>
+      </c>
+      <c r="O372" t="n">
+        <v>375</v>
+      </c>
+      <c r="P372" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q372" t="n">
+        <v>0.85206</v>
+      </c>
+      <c r="R372" t="n">
+        <v>440.1098514189142</v>
+      </c>
+      <c r="S372" t="n">
+        <v>1125</v>
+      </c>
+      <c r="T372" t="n">
+        <v>1320.329554256742</v>
+      </c>
+      <c r="U372" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V372" t="n">
+        <v>0.01994745230725714</v>
+      </c>
+      <c r="W372" t="n">
+        <v>0.02187468207771315</v>
+      </c>
+      <c r="X372" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y372" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z372" t="n">
+        <v>0.5300061702728271</v>
+      </c>
+      <c r="AA372" t="n">
+        <v>12.44775533676147</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E373" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F373" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H373" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I373" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J373" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K373" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L373" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M373" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N373" s="2" t="n">
+        <v>45832.89540211859</v>
+      </c>
+      <c r="O373" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P373" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q373" t="n">
+        <v>1.7874</v>
+      </c>
+      <c r="R373" t="n">
+        <v>0.4196038939241356</v>
+      </c>
+      <c r="S373" t="n">
+        <v>2748</v>
+      </c>
+      <c r="T373" t="n">
+        <v>1537.428667338033</v>
+      </c>
+      <c r="U373" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="V373" t="n">
+        <v>0.03448275862068972</v>
+      </c>
+      <c r="W373" t="n">
+        <v>0.02705721660821148</v>
+      </c>
+      <c r="X373" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y373" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z373" t="n">
+        <v>0.4560990333557129</v>
+      </c>
+      <c r="AA373" t="n">
+        <v>11.05002820491791</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E374" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F374" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H374" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I374" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J374" t="n">
+        <v>537</v>
+      </c>
+      <c r="K374" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L374" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M374" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N374" s="2" t="n">
+        <v>45832.89540211859</v>
+      </c>
+      <c r="O374" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="P374" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q374" t="n">
+        <v>9.10852</v>
+      </c>
+      <c r="R374" t="n">
+        <v>2.821534124094804</v>
+      </c>
+      <c r="S374" t="n">
+        <v>13800.9</v>
+      </c>
+      <c r="T374" t="n">
+        <v>1515.163824638909</v>
+      </c>
+      <c r="U374" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V374" t="n">
+        <v>0.01984126984126977</v>
+      </c>
+      <c r="W374" t="n">
+        <v>0.01222984564460461</v>
+      </c>
+      <c r="X374" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y374" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z374" t="n">
+        <v>0.5799588561058044</v>
+      </c>
+      <c r="AA374" t="n">
+        <v>12.64349049758911</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E375" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F375" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H375" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I375" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J375" t="n">
+        <v>121</v>
+      </c>
+      <c r="K375" t="n">
+        <v>12</v>
+      </c>
+      <c r="L375" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M375" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N375" s="2" t="n">
+        <v>45832.89540211859</v>
+      </c>
+      <c r="O375" t="n">
+        <v>14.09</v>
+      </c>
+      <c r="P375" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q375" t="n">
+        <v>1.1614401</v>
+      </c>
+      <c r="R375" t="n">
+        <v>12.13149089651718</v>
+      </c>
+      <c r="S375" t="n">
+        <v>1704.89</v>
+      </c>
+      <c r="T375" t="n">
+        <v>1467.910398478578</v>
+      </c>
+      <c r="U375" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V375" t="n">
+        <v>-0.006346967559943573</v>
+      </c>
+      <c r="W375" t="n">
+        <v>-0.01583425543009509</v>
+      </c>
+      <c r="X375" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y375" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z375" t="n">
+        <v>0.4978975057601929</v>
+      </c>
+      <c r="AA375" t="n">
+        <v>13.57315373420715</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr"/>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E376" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F376" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H376" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I376" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J376" t="n">
+        <v>162</v>
+      </c>
+      <c r="K376" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L376" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M376" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N376" s="2" t="n">
+        <v>45832.89540211859</v>
+      </c>
+      <c r="O376" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="P376" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q376" t="n">
+        <v>4.2505</v>
+      </c>
+      <c r="R376" t="n">
+        <v>9.104811198682508</v>
+      </c>
+      <c r="S376" t="n">
+        <v>6269.400000000001</v>
+      </c>
+      <c r="T376" t="n">
+        <v>1474.979414186567</v>
+      </c>
+      <c r="U376" t="n">
+        <v>8.272543736854324</v>
+      </c>
+      <c r="V376" t="n">
+        <v>-0.01275510204081631</v>
+      </c>
+      <c r="W376" t="n">
+        <v>-0.009454607981293939</v>
+      </c>
+      <c r="X376" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y376" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z376" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="AA376" t="n">
+        <v>12.85747975540161</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E377" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F377" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H377" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I377" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J377" t="n">
+        <v>101</v>
+      </c>
+      <c r="K377" t="n">
+        <v>11</v>
+      </c>
+      <c r="L377" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M377" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N377" s="2" t="n">
+        <v>45832.89540211859</v>
+      </c>
+      <c r="O377" t="n">
+        <v>24700</v>
+      </c>
+      <c r="P377" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q377" t="n">
+        <v>2062.53</v>
+      </c>
+      <c r="R377" t="n">
+        <v>11.97558338545379</v>
+      </c>
+      <c r="S377" t="n">
+        <v>2494700</v>
+      </c>
+      <c r="T377" t="n">
+        <v>1209.533921930832</v>
+      </c>
+      <c r="U377" t="n">
+        <v>11.00337378959821</v>
+      </c>
+      <c r="V377" t="n">
+        <v>0.007012393998695465</v>
+      </c>
+      <c r="W377" t="n">
+        <v>0.003960885675184045</v>
+      </c>
+      <c r="X377" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y377" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z377" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="AA377" t="n">
         <v>12.66160106658936</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA377"/>
+  <dimension ref="A1:AA385"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35114,7 +35114,7 @@
         <v>100</v>
       </c>
       <c r="N370" s="2" t="n">
-        <v>45832.89540211859</v>
+        <v>45832.89540211805</v>
       </c>
       <c r="O370" t="n">
         <v>1</v>
@@ -35205,7 +35205,7 @@
         <v>12.02781891822815</v>
       </c>
       <c r="N371" s="2" t="n">
-        <v>45832.89540211859</v>
+        <v>45832.89540211805</v>
       </c>
       <c r="O371" t="n">
         <v>36.15</v>
@@ -35296,7 +35296,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N372" s="2" t="n">
-        <v>45832.89540211859</v>
+        <v>45832.89540211805</v>
       </c>
       <c r="O372" t="n">
         <v>375</v>
@@ -35391,7 +35391,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N373" s="2" t="n">
-        <v>45832.89540211859</v>
+        <v>45832.89540211805</v>
       </c>
       <c r="O373" t="n">
         <v>0.75</v>
@@ -35486,7 +35486,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N374" s="2" t="n">
-        <v>45832.89540211859</v>
+        <v>45832.89540211805</v>
       </c>
       <c r="O374" t="n">
         <v>25.7</v>
@@ -35581,7 +35581,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N375" s="2" t="n">
-        <v>45832.89540211859</v>
+        <v>45832.89540211805</v>
       </c>
       <c r="O375" t="n">
         <v>14.09</v>
@@ -35672,7 +35672,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N376" s="2" t="n">
-        <v>45832.89540211859</v>
+        <v>45832.89540211805</v>
       </c>
       <c r="O376" t="n">
         <v>38.7</v>
@@ -35767,7 +35767,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N377" s="2" t="n">
-        <v>45832.89540211859</v>
+        <v>45832.89540211805</v>
       </c>
       <c r="O377" t="n">
         <v>24700</v>
@@ -35809,6 +35809,760 @@
       </c>
       <c r="AA377" t="n">
         <v>12.66160106658936</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F378" t="n">
+        <v>1</v>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H378" t="n">
+        <v>1</v>
+      </c>
+      <c r="I378" t="n">
+        <v>1</v>
+      </c>
+      <c r="J378" t="n">
+        <v>1</v>
+      </c>
+      <c r="K378" t="n">
+        <v>100</v>
+      </c>
+      <c r="L378" t="n">
+        <v>100</v>
+      </c>
+      <c r="M378" t="n">
+        <v>100</v>
+      </c>
+      <c r="N378" s="2" t="n">
+        <v>45833.31316271198</v>
+      </c>
+      <c r="O378" t="n">
+        <v>1</v>
+      </c>
+      <c r="P378" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q378" t="n">
+        <v>1</v>
+      </c>
+      <c r="R378" t="n">
+        <v>1</v>
+      </c>
+      <c r="S378" t="n">
+        <v>0</v>
+      </c>
+      <c r="T378" t="n">
+        <v>45.43580260334033</v>
+      </c>
+      <c r="U378" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V378" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W378" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X378" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y378" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z378" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA378" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr"/>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E379" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F379" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H379" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I379" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J379" t="n">
+        <v>3</v>
+      </c>
+      <c r="K379" t="n">
+        <v>10</v>
+      </c>
+      <c r="L379" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M379" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N379" s="2" t="n">
+        <v>45833.31316271198</v>
+      </c>
+      <c r="O379" t="n">
+        <v>375</v>
+      </c>
+      <c r="P379" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q379" t="n">
+        <v>0.85195</v>
+      </c>
+      <c r="R379" t="n">
+        <v>440.1666764481484</v>
+      </c>
+      <c r="S379" t="n">
+        <v>1125</v>
+      </c>
+      <c r="T379" t="n">
+        <v>1320.500029344445</v>
+      </c>
+      <c r="U379" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V379" t="n">
+        <v>0.01994745230725714</v>
+      </c>
+      <c r="W379" t="n">
+        <v>0.0220066219979298</v>
+      </c>
+      <c r="X379" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y379" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z379" t="n">
+        <v>0.5092240571975708</v>
+      </c>
+      <c r="AA379" t="n">
+        <v>12.11775493621826</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E380" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F380" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H380" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I380" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J380" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K380" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L380" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M380" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N380" s="2" t="n">
+        <v>45833.31316271198</v>
+      </c>
+      <c r="O380" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="P380" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q380" t="n">
+        <v>1.78498</v>
+      </c>
+      <c r="R380" t="n">
+        <v>0.4089681677105625</v>
+      </c>
+      <c r="S380" t="n">
+        <v>2674.72</v>
+      </c>
+      <c r="T380" t="n">
+        <v>1498.459366491501</v>
+      </c>
+      <c r="U380" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="V380" t="n">
+        <v>0.006896551724137945</v>
+      </c>
+      <c r="W380" t="n">
+        <v>0.001024332929838501</v>
+      </c>
+      <c r="X380" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y380" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z380" t="n">
+        <v>0.5095238089561462</v>
+      </c>
+      <c r="AA380" t="n">
+        <v>11.94347476959229</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E381" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F381" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H381" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I381" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J381" t="n">
+        <v>537</v>
+      </c>
+      <c r="K381" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L381" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M381" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N381" s="2" t="n">
+        <v>45833.31316271198</v>
+      </c>
+      <c r="O381" t="n">
+        <v>25</v>
+      </c>
+      <c r="P381" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q381" t="n">
+        <v>9.109970000000001</v>
+      </c>
+      <c r="R381" t="n">
+        <v>2.744246139120107</v>
+      </c>
+      <c r="S381" t="n">
+        <v>13425</v>
+      </c>
+      <c r="T381" t="n">
+        <v>1473.660176707497</v>
+      </c>
+      <c r="U381" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V381" t="n">
+        <v>-0.007936507936507908</v>
+      </c>
+      <c r="W381" t="n">
+        <v>-0.0154973416444093</v>
+      </c>
+      <c r="X381" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y381" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z381" t="n">
+        <v>0.5673728585243225</v>
+      </c>
+      <c r="AA381" t="n">
+        <v>11.78222894668579</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E382" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F382" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H382" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I382" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J382" t="n">
+        <v>121</v>
+      </c>
+      <c r="K382" t="n">
+        <v>12</v>
+      </c>
+      <c r="L382" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M382" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N382" s="2" t="n">
+        <v>45833.31316271198</v>
+      </c>
+      <c r="O382" t="n">
+        <v>14.09</v>
+      </c>
+      <c r="P382" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q382" t="n">
+        <v>1.1609008</v>
+      </c>
+      <c r="R382" t="n">
+        <v>12.137126617537</v>
+      </c>
+      <c r="S382" t="n">
+        <v>1704.89</v>
+      </c>
+      <c r="T382" t="n">
+        <v>1468.592320721977</v>
+      </c>
+      <c r="U382" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V382" t="n">
+        <v>-0.006346967559943573</v>
+      </c>
+      <c r="W382" t="n">
+        <v>-0.01537705823801239</v>
+      </c>
+      <c r="X382" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y382" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z382" t="n">
+        <v>0.5561246275901794</v>
+      </c>
+      <c r="AA382" t="n">
+        <v>14.51355290412903</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr"/>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E383" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F383" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H383" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I383" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J383" t="n">
+        <v>162</v>
+      </c>
+      <c r="K383" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L383" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M383" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N383" s="2" t="n">
+        <v>45833.31316271198</v>
+      </c>
+      <c r="O383" t="n">
+        <v>38.65</v>
+      </c>
+      <c r="P383" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q383" t="n">
+        <v>4.25118</v>
+      </c>
+      <c r="R383" t="n">
+        <v>9.091593392893268</v>
+      </c>
+      <c r="S383" t="n">
+        <v>6261.3</v>
+      </c>
+      <c r="T383" t="n">
+        <v>1472.838129648709</v>
+      </c>
+      <c r="U383" t="n">
+        <v>8.272543736854324</v>
+      </c>
+      <c r="V383" t="n">
+        <v>-0.0140306122448981</v>
+      </c>
+      <c r="W383" t="n">
+        <v>-0.01089262095393251</v>
+      </c>
+      <c r="X383" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y383" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z383" t="n">
+        <v>0.6009591817855835</v>
+      </c>
+      <c r="AA383" t="n">
+        <v>12.92029732894897</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E384" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F384" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H384" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I384" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J384" t="n">
+        <v>101</v>
+      </c>
+      <c r="K384" t="n">
+        <v>11</v>
+      </c>
+      <c r="L384" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M384" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N384" s="2" t="n">
+        <v>45833.31316271198</v>
+      </c>
+      <c r="O384" t="n">
+        <v>25334</v>
+      </c>
+      <c r="P384" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q384" t="n">
+        <v>2056.88</v>
+      </c>
+      <c r="R384" t="n">
+        <v>12.31671269106608</v>
+      </c>
+      <c r="S384" t="n">
+        <v>2558734</v>
+      </c>
+      <c r="T384" t="n">
+        <v>1243.987981797674</v>
+      </c>
+      <c r="U384" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V384" t="n">
+        <v>0.032860404435747</v>
+      </c>
+      <c r="W384" t="n">
+        <v>0.03255911498635689</v>
+      </c>
+      <c r="X384" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y384" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z384" t="n">
+        <v>0.4206280708312988</v>
+      </c>
+      <c r="AA384" t="n">
+        <v>10.58742851018906</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E385" s="2" t="n">
+        <v>45833.31316271198</v>
+      </c>
+      <c r="F385" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H385" t="n">
+        <v>1</v>
+      </c>
+      <c r="I385" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J385" t="n">
+        <v>30</v>
+      </c>
+      <c r="K385" t="n">
+        <v>9</v>
+      </c>
+      <c r="L385" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M385" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N385" s="2" t="n">
+        <v>45833.31316271198</v>
+      </c>
+      <c r="O385" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="P385" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q385" t="n">
+        <v>1</v>
+      </c>
+      <c r="R385" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="S385" t="n">
+        <v>1370.4</v>
+      </c>
+      <c r="T385" t="n">
+        <v>1370.4</v>
+      </c>
+      <c r="U385" t="n">
+        <v>41.112</v>
+      </c>
+      <c r="V385" t="n">
+        <v>0</v>
+      </c>
+      <c r="W385" t="n">
+        <v>0</v>
+      </c>
+      <c r="X385" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y385" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z385" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="AA385" t="n">
+        <v>12.81225872039795</v>
       </c>
     </row>
   </sheetData>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA385"/>
+  <dimension ref="A1:AA393"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35864,7 +35864,7 @@
         <v>100</v>
       </c>
       <c r="N378" s="2" t="n">
-        <v>45833.31316271198</v>
+        <v>45833.31316270833</v>
       </c>
       <c r="O378" t="n">
         <v>1</v>
@@ -35955,7 +35955,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N379" s="2" t="n">
-        <v>45833.31316271198</v>
+        <v>45833.31316270833</v>
       </c>
       <c r="O379" t="n">
         <v>375</v>
@@ -36050,7 +36050,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N380" s="2" t="n">
-        <v>45833.31316271198</v>
+        <v>45833.31316270833</v>
       </c>
       <c r="O380" t="n">
         <v>0.73</v>
@@ -36145,7 +36145,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N381" s="2" t="n">
-        <v>45833.31316271198</v>
+        <v>45833.31316270833</v>
       </c>
       <c r="O381" t="n">
         <v>25</v>
@@ -36240,7 +36240,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N382" s="2" t="n">
-        <v>45833.31316271198</v>
+        <v>45833.31316270833</v>
       </c>
       <c r="O382" t="n">
         <v>14.09</v>
@@ -36331,7 +36331,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N383" s="2" t="n">
-        <v>45833.31316271198</v>
+        <v>45833.31316270833</v>
       </c>
       <c r="O383" t="n">
         <v>38.65</v>
@@ -36426,7 +36426,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N384" s="2" t="n">
-        <v>45833.31316271198</v>
+        <v>45833.31316270833</v>
       </c>
       <c r="O384" t="n">
         <v>25334</v>
@@ -36492,7 +36492,7 @@
         </is>
       </c>
       <c r="E385" s="2" t="n">
-        <v>45833.31316271198</v>
+        <v>45833.31316270833</v>
       </c>
       <c r="F385" t="n">
         <v>45.68</v>
@@ -36521,7 +36521,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N385" s="2" t="n">
-        <v>45833.31316271198</v>
+        <v>45833.31316270833</v>
       </c>
       <c r="O385" t="n">
         <v>45.68</v>
@@ -36562,6 +36562,760 @@
         <v>0.6434202790260315</v>
       </c>
       <c r="AA385" t="n">
+        <v>12.81225872039795</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F386" t="n">
+        <v>1</v>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H386" t="n">
+        <v>1</v>
+      </c>
+      <c r="I386" t="n">
+        <v>1</v>
+      </c>
+      <c r="J386" t="n">
+        <v>1</v>
+      </c>
+      <c r="K386" t="n">
+        <v>100</v>
+      </c>
+      <c r="L386" t="n">
+        <v>100</v>
+      </c>
+      <c r="M386" t="n">
+        <v>100</v>
+      </c>
+      <c r="N386" s="2" t="n">
+        <v>45833.36154284501</v>
+      </c>
+      <c r="O386" t="n">
+        <v>1</v>
+      </c>
+      <c r="P386" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q386" t="n">
+        <v>1</v>
+      </c>
+      <c r="R386" t="n">
+        <v>1</v>
+      </c>
+      <c r="S386" t="n">
+        <v>0</v>
+      </c>
+      <c r="T386" t="n">
+        <v>45.43580260334033</v>
+      </c>
+      <c r="U386" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V386" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W386" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X386" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y386" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z386" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA386" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr"/>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E387" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F387" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H387" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I387" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J387" t="n">
+        <v>3</v>
+      </c>
+      <c r="K387" t="n">
+        <v>10</v>
+      </c>
+      <c r="L387" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M387" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N387" s="2" t="n">
+        <v>45833.36154284501</v>
+      </c>
+      <c r="O387" t="n">
+        <v>375</v>
+      </c>
+      <c r="P387" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q387" t="n">
+        <v>0.85206</v>
+      </c>
+      <c r="R387" t="n">
+        <v>440.1098514189142</v>
+      </c>
+      <c r="S387" t="n">
+        <v>1125</v>
+      </c>
+      <c r="T387" t="n">
+        <v>1320.329554256742</v>
+      </c>
+      <c r="U387" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V387" t="n">
+        <v>0.01994745230725714</v>
+      </c>
+      <c r="W387" t="n">
+        <v>0.02187468207771315</v>
+      </c>
+      <c r="X387" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y387" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z387" t="n">
+        <v>0.5092240571975708</v>
+      </c>
+      <c r="AA387" t="n">
+        <v>12.11775493621826</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E388" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F388" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H388" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I388" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J388" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K388" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L388" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M388" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N388" s="2" t="n">
+        <v>45833.36154284501</v>
+      </c>
+      <c r="O388" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="P388" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q388" t="n">
+        <v>1.78608</v>
+      </c>
+      <c r="R388" t="n">
+        <v>0.4087162949028039</v>
+      </c>
+      <c r="S388" t="n">
+        <v>2674.72</v>
+      </c>
+      <c r="T388" t="n">
+        <v>1497.536504523873</v>
+      </c>
+      <c r="U388" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="V388" t="n">
+        <v>0.006896551724137945</v>
+      </c>
+      <c r="W388" t="n">
+        <v>0.0004078282009223333</v>
+      </c>
+      <c r="X388" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y388" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z388" t="n">
+        <v>0.5095238089561462</v>
+      </c>
+      <c r="AA388" t="n">
+        <v>11.94347476959229</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E389" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F389" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H389" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I389" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J389" t="n">
+        <v>537</v>
+      </c>
+      <c r="K389" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L389" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M389" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N389" s="2" t="n">
+        <v>45833.36154284501</v>
+      </c>
+      <c r="O389" t="n">
+        <v>24.95</v>
+      </c>
+      <c r="P389" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q389" t="n">
+        <v>9.10872</v>
+      </c>
+      <c r="R389" t="n">
+        <v>2.739133489667044</v>
+      </c>
+      <c r="S389" t="n">
+        <v>13398.15</v>
+      </c>
+      <c r="T389" t="n">
+        <v>1470.914683951203</v>
+      </c>
+      <c r="U389" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V389" t="n">
+        <v>-0.009920634920634885</v>
+      </c>
+      <c r="W389" t="n">
+        <v>-0.01733151275101197</v>
+      </c>
+      <c r="X389" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y389" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z389" t="n">
+        <v>0.5673728585243225</v>
+      </c>
+      <c r="AA389" t="n">
+        <v>11.78222894668579</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E390" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F390" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H390" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I390" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J390" t="n">
+        <v>121</v>
+      </c>
+      <c r="K390" t="n">
+        <v>12</v>
+      </c>
+      <c r="L390" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M390" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N390" s="2" t="n">
+        <v>45833.36154284501</v>
+      </c>
+      <c r="O390" t="n">
+        <v>14.09</v>
+      </c>
+      <c r="P390" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q390" t="n">
+        <v>1.1607661</v>
+      </c>
+      <c r="R390" t="n">
+        <v>12.13853505887189</v>
+      </c>
+      <c r="S390" t="n">
+        <v>1704.89</v>
+      </c>
+      <c r="T390" t="n">
+        <v>1468.762742123499</v>
+      </c>
+      <c r="U390" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V390" t="n">
+        <v>-0.006346967559943573</v>
+      </c>
+      <c r="W390" t="n">
+        <v>-0.01526279860357316</v>
+      </c>
+      <c r="X390" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y390" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z390" t="n">
+        <v>0.5561246275901794</v>
+      </c>
+      <c r="AA390" t="n">
+        <v>14.51355290412903</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr"/>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E391" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F391" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H391" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I391" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J391" t="n">
+        <v>162</v>
+      </c>
+      <c r="K391" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L391" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M391" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N391" s="2" t="n">
+        <v>45833.36154284501</v>
+      </c>
+      <c r="O391" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="P391" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q391" t="n">
+        <v>4.25065</v>
+      </c>
+      <c r="R391" t="n">
+        <v>9.033912460447224</v>
+      </c>
+      <c r="S391" t="n">
+        <v>6220.8</v>
+      </c>
+      <c r="T391" t="n">
+        <v>1463.49381859245</v>
+      </c>
+      <c r="U391" t="n">
+        <v>8.272543736854324</v>
+      </c>
+      <c r="V391" t="n">
+        <v>-0.02040816326530626</v>
+      </c>
+      <c r="W391" t="n">
+        <v>-0.01716793854097243</v>
+      </c>
+      <c r="X391" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y391" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z391" t="n">
+        <v>0.6009591817855835</v>
+      </c>
+      <c r="AA391" t="n">
+        <v>12.92029732894897</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E392" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F392" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H392" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I392" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J392" t="n">
+        <v>101</v>
+      </c>
+      <c r="K392" t="n">
+        <v>11</v>
+      </c>
+      <c r="L392" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M392" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N392" s="2" t="n">
+        <v>45833.36154284501</v>
+      </c>
+      <c r="O392" t="n">
+        <v>24845</v>
+      </c>
+      <c r="P392" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q392" t="n">
+        <v>2055.69</v>
+      </c>
+      <c r="R392" t="n">
+        <v>12.0859662692332</v>
+      </c>
+      <c r="S392" t="n">
+        <v>2509345</v>
+      </c>
+      <c r="T392" t="n">
+        <v>1220.682593192553</v>
+      </c>
+      <c r="U392" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V392" t="n">
+        <v>0.01292400521852577</v>
+      </c>
+      <c r="W392" t="n">
+        <v>0.0132147227698487</v>
+      </c>
+      <c r="X392" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y392" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z392" t="n">
+        <v>0.4206280708312988</v>
+      </c>
+      <c r="AA392" t="n">
+        <v>10.58742851018906</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E393" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F393" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H393" t="n">
+        <v>1</v>
+      </c>
+      <c r="I393" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J393" t="n">
+        <v>30</v>
+      </c>
+      <c r="K393" t="n">
+        <v>9</v>
+      </c>
+      <c r="L393" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M393" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N393" s="2" t="n">
+        <v>45833.36154284501</v>
+      </c>
+      <c r="O393" t="n">
+        <v>45.88</v>
+      </c>
+      <c r="P393" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q393" t="n">
+        <v>1</v>
+      </c>
+      <c r="R393" t="n">
+        <v>45.88</v>
+      </c>
+      <c r="S393" t="n">
+        <v>1376.4</v>
+      </c>
+      <c r="T393" t="n">
+        <v>1376.4</v>
+      </c>
+      <c r="U393" t="n">
+        <v>41.292</v>
+      </c>
+      <c r="V393" t="n">
+        <v>0.004378283712784592</v>
+      </c>
+      <c r="W393" t="n">
+        <v>0.004378283712784592</v>
+      </c>
+      <c r="X393" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y393" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z393" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="AA393" t="n">
         <v>12.81225872039795</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA393"/>
+  <dimension ref="A1:AA401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36618,7 +36618,7 @@
         <v>100</v>
       </c>
       <c r="N386" s="2" t="n">
-        <v>45833.36154284501</v>
+        <v>45833.36154284723</v>
       </c>
       <c r="O386" t="n">
         <v>1</v>
@@ -36709,7 +36709,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N387" s="2" t="n">
-        <v>45833.36154284501</v>
+        <v>45833.36154284723</v>
       </c>
       <c r="O387" t="n">
         <v>375</v>
@@ -36804,7 +36804,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N388" s="2" t="n">
-        <v>45833.36154284501</v>
+        <v>45833.36154284723</v>
       </c>
       <c r="O388" t="n">
         <v>0.73</v>
@@ -36899,7 +36899,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N389" s="2" t="n">
-        <v>45833.36154284501</v>
+        <v>45833.36154284723</v>
       </c>
       <c r="O389" t="n">
         <v>24.95</v>
@@ -36994,7 +36994,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N390" s="2" t="n">
-        <v>45833.36154284501</v>
+        <v>45833.36154284723</v>
       </c>
       <c r="O390" t="n">
         <v>14.09</v>
@@ -37085,7 +37085,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N391" s="2" t="n">
-        <v>45833.36154284501</v>
+        <v>45833.36154284723</v>
       </c>
       <c r="O391" t="n">
         <v>38.4</v>
@@ -37180,7 +37180,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N392" s="2" t="n">
-        <v>45833.36154284501</v>
+        <v>45833.36154284723</v>
       </c>
       <c r="O392" t="n">
         <v>24845</v>
@@ -37275,7 +37275,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N393" s="2" t="n">
-        <v>45833.36154284501</v>
+        <v>45833.36154284723</v>
       </c>
       <c r="O393" t="n">
         <v>45.88</v>
@@ -37316,6 +37316,760 @@
         <v>0.6434202790260315</v>
       </c>
       <c r="AA393" t="n">
+        <v>12.81225872039795</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F394" t="n">
+        <v>1</v>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H394" t="n">
+        <v>1</v>
+      </c>
+      <c r="I394" t="n">
+        <v>1</v>
+      </c>
+      <c r="J394" t="n">
+        <v>1</v>
+      </c>
+      <c r="K394" t="n">
+        <v>100</v>
+      </c>
+      <c r="L394" t="n">
+        <v>100</v>
+      </c>
+      <c r="M394" t="n">
+        <v>100</v>
+      </c>
+      <c r="N394" s="2" t="n">
+        <v>45833.39956027412</v>
+      </c>
+      <c r="O394" t="n">
+        <v>1</v>
+      </c>
+      <c r="P394" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q394" t="n">
+        <v>1</v>
+      </c>
+      <c r="R394" t="n">
+        <v>1</v>
+      </c>
+      <c r="S394" t="n">
+        <v>0</v>
+      </c>
+      <c r="T394" t="n">
+        <v>45.43580260334033</v>
+      </c>
+      <c r="U394" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V394" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W394" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X394" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y394" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z394" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA394" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr"/>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E395" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F395" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H395" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I395" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J395" t="n">
+        <v>3</v>
+      </c>
+      <c r="K395" t="n">
+        <v>10</v>
+      </c>
+      <c r="L395" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M395" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N395" s="2" t="n">
+        <v>45833.39956027412</v>
+      </c>
+      <c r="O395" t="n">
+        <v>373.1</v>
+      </c>
+      <c r="P395" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q395" t="n">
+        <v>0.85204</v>
+      </c>
+      <c r="R395" t="n">
+        <v>437.8902398948406</v>
+      </c>
+      <c r="S395" t="n">
+        <v>1119.3</v>
+      </c>
+      <c r="T395" t="n">
+        <v>1313.670719684522</v>
+      </c>
+      <c r="U395" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V395" t="n">
+        <v>0.01477971854890048</v>
+      </c>
+      <c r="W395" t="n">
+        <v>0.01672104869916891</v>
+      </c>
+      <c r="X395" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y395" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z395" t="n">
+        <v>0.5092240571975708</v>
+      </c>
+      <c r="AA395" t="n">
+        <v>12.11775493621826</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E396" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F396" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H396" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I396" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J396" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K396" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L396" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M396" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N396" s="2" t="n">
+        <v>45833.39956027412</v>
+      </c>
+      <c r="O396" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="P396" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q396" t="n">
+        <v>1.78605</v>
+      </c>
+      <c r="R396" t="n">
+        <v>0.4087231600459114</v>
+      </c>
+      <c r="S396" t="n">
+        <v>2674.72</v>
+      </c>
+      <c r="T396" t="n">
+        <v>1497.561658408219</v>
+      </c>
+      <c r="U396" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="V396" t="n">
+        <v>0.006896551724137945</v>
+      </c>
+      <c r="W396" t="n">
+        <v>0.0004246318933418536</v>
+      </c>
+      <c r="X396" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y396" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z396" t="n">
+        <v>0.5095238089561462</v>
+      </c>
+      <c r="AA396" t="n">
+        <v>11.94347476959229</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E397" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F397" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H397" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I397" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J397" t="n">
+        <v>537</v>
+      </c>
+      <c r="K397" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L397" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M397" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N397" s="2" t="n">
+        <v>45833.39956027412</v>
+      </c>
+      <c r="O397" t="n">
+        <v>24.95</v>
+      </c>
+      <c r="P397" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q397" t="n">
+        <v>9.10136</v>
+      </c>
+      <c r="R397" t="n">
+        <v>2.74134854571185</v>
+      </c>
+      <c r="S397" t="n">
+        <v>13398.15</v>
+      </c>
+      <c r="T397" t="n">
+        <v>1472.104169047263</v>
+      </c>
+      <c r="U397" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V397" t="n">
+        <v>-0.009920634920634885</v>
+      </c>
+      <c r="W397" t="n">
+        <v>-0.01653685787897596</v>
+      </c>
+      <c r="X397" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y397" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z397" t="n">
+        <v>0.5673728585243225</v>
+      </c>
+      <c r="AA397" t="n">
+        <v>11.78222894668579</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E398" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F398" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H398" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I398" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J398" t="n">
+        <v>121</v>
+      </c>
+      <c r="K398" t="n">
+        <v>12</v>
+      </c>
+      <c r="L398" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M398" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N398" s="2" t="n">
+        <v>45833.39956027412</v>
+      </c>
+      <c r="O398" t="n">
+        <v>14.09</v>
+      </c>
+      <c r="P398" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q398" t="n">
+        <v>1.1598237</v>
+      </c>
+      <c r="R398" t="n">
+        <v>12.14839807118961</v>
+      </c>
+      <c r="S398" t="n">
+        <v>1704.89</v>
+      </c>
+      <c r="T398" t="n">
+        <v>1469.956166613943</v>
+      </c>
+      <c r="U398" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V398" t="n">
+        <v>-0.006346967559943573</v>
+      </c>
+      <c r="W398" t="n">
+        <v>-0.01446266291174692</v>
+      </c>
+      <c r="X398" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y398" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z398" t="n">
+        <v>0.5561246275901794</v>
+      </c>
+      <c r="AA398" t="n">
+        <v>14.51355290412903</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr"/>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E399" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F399" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H399" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I399" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J399" t="n">
+        <v>162</v>
+      </c>
+      <c r="K399" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L399" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M399" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N399" s="2" t="n">
+        <v>45833.39956027412</v>
+      </c>
+      <c r="O399" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="P399" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q399" t="n">
+        <v>4.24851</v>
+      </c>
+      <c r="R399" t="n">
+        <v>9.085538223989117</v>
+      </c>
+      <c r="S399" t="n">
+        <v>6253.2</v>
+      </c>
+      <c r="T399" t="n">
+        <v>1471.857192286237</v>
+      </c>
+      <c r="U399" t="n">
+        <v>8.272543736854324</v>
+      </c>
+      <c r="V399" t="n">
+        <v>-0.01530612244897966</v>
+      </c>
+      <c r="W399" t="n">
+        <v>-0.01155138471355555</v>
+      </c>
+      <c r="X399" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y399" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z399" t="n">
+        <v>0.6009591817855835</v>
+      </c>
+      <c r="AA399" t="n">
+        <v>12.92029732894897</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E400" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F400" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H400" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I400" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J400" t="n">
+        <v>101</v>
+      </c>
+      <c r="K400" t="n">
+        <v>11</v>
+      </c>
+      <c r="L400" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M400" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N400" s="2" t="n">
+        <v>45833.39956027412</v>
+      </c>
+      <c r="O400" t="n">
+        <v>24726</v>
+      </c>
+      <c r="P400" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q400" t="n">
+        <v>2056.79</v>
+      </c>
+      <c r="R400" t="n">
+        <v>12.0216453794505</v>
+      </c>
+      <c r="S400" t="n">
+        <v>2497326</v>
+      </c>
+      <c r="T400" t="n">
+        <v>1214.186183324501</v>
+      </c>
+      <c r="U400" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V400" t="n">
+        <v>0.008072407045009777</v>
+      </c>
+      <c r="W400" t="n">
+        <v>0.007822446218871404</v>
+      </c>
+      <c r="X400" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y400" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z400" t="n">
+        <v>0.4206280708312988</v>
+      </c>
+      <c r="AA400" t="n">
+        <v>10.58742851018906</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E401" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F401" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H401" t="n">
+        <v>1</v>
+      </c>
+      <c r="I401" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J401" t="n">
+        <v>30</v>
+      </c>
+      <c r="K401" t="n">
+        <v>9</v>
+      </c>
+      <c r="L401" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M401" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N401" s="2" t="n">
+        <v>45833.39956027412</v>
+      </c>
+      <c r="O401" t="n">
+        <v>46</v>
+      </c>
+      <c r="P401" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q401" t="n">
+        <v>1</v>
+      </c>
+      <c r="R401" t="n">
+        <v>46</v>
+      </c>
+      <c r="S401" t="n">
+        <v>1380</v>
+      </c>
+      <c r="T401" t="n">
+        <v>1380</v>
+      </c>
+      <c r="U401" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="V401" t="n">
+        <v>0.007005253940455258</v>
+      </c>
+      <c r="W401" t="n">
+        <v>0.007005253940455258</v>
+      </c>
+      <c r="X401" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y401" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z401" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="AA401" t="n">
         <v>12.81225872039795</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA401"/>
+  <dimension ref="A1:AA409"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37372,7 +37372,7 @@
         <v>100</v>
       </c>
       <c r="N394" s="2" t="n">
-        <v>45833.39956027412</v>
+        <v>45833.39956027778</v>
       </c>
       <c r="O394" t="n">
         <v>1</v>
@@ -37463,7 +37463,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N395" s="2" t="n">
-        <v>45833.39956027412</v>
+        <v>45833.39956027778</v>
       </c>
       <c r="O395" t="n">
         <v>373.1</v>
@@ -37558,7 +37558,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N396" s="2" t="n">
-        <v>45833.39956027412</v>
+        <v>45833.39956027778</v>
       </c>
       <c r="O396" t="n">
         <v>0.73</v>
@@ -37653,7 +37653,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N397" s="2" t="n">
-        <v>45833.39956027412</v>
+        <v>45833.39956027778</v>
       </c>
       <c r="O397" t="n">
         <v>24.95</v>
@@ -37748,7 +37748,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N398" s="2" t="n">
-        <v>45833.39956027412</v>
+        <v>45833.39956027778</v>
       </c>
       <c r="O398" t="n">
         <v>14.09</v>
@@ -37839,7 +37839,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N399" s="2" t="n">
-        <v>45833.39956027412</v>
+        <v>45833.39956027778</v>
       </c>
       <c r="O399" t="n">
         <v>38.6</v>
@@ -37934,7 +37934,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N400" s="2" t="n">
-        <v>45833.39956027412</v>
+        <v>45833.39956027778</v>
       </c>
       <c r="O400" t="n">
         <v>24726</v>
@@ -38029,7 +38029,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N401" s="2" t="n">
-        <v>45833.39956027412</v>
+        <v>45833.39956027778</v>
       </c>
       <c r="O401" t="n">
         <v>46</v>
@@ -38070,6 +38070,760 @@
         <v>0.6434202790260315</v>
       </c>
       <c r="AA401" t="n">
+        <v>12.81225872039795</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F402" t="n">
+        <v>1</v>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H402" t="n">
+        <v>1</v>
+      </c>
+      <c r="I402" t="n">
+        <v>1</v>
+      </c>
+      <c r="J402" t="n">
+        <v>1</v>
+      </c>
+      <c r="K402" t="n">
+        <v>100</v>
+      </c>
+      <c r="L402" t="n">
+        <v>100</v>
+      </c>
+      <c r="M402" t="n">
+        <v>100</v>
+      </c>
+      <c r="N402" s="2" t="n">
+        <v>45833.44239746398</v>
+      </c>
+      <c r="O402" t="n">
+        <v>1</v>
+      </c>
+      <c r="P402" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q402" t="n">
+        <v>1</v>
+      </c>
+      <c r="R402" t="n">
+        <v>1</v>
+      </c>
+      <c r="S402" t="n">
+        <v>0</v>
+      </c>
+      <c r="T402" t="n">
+        <v>45.43580260334033</v>
+      </c>
+      <c r="U402" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V402" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W402" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X402" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y402" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z402" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA402" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr"/>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E403" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F403" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H403" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I403" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J403" t="n">
+        <v>3</v>
+      </c>
+      <c r="K403" t="n">
+        <v>10</v>
+      </c>
+      <c r="L403" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M403" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N403" s="2" t="n">
+        <v>45833.44239746398</v>
+      </c>
+      <c r="O403" t="n">
+        <v>373.5</v>
+      </c>
+      <c r="P403" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q403" t="n">
+        <v>0.85263</v>
+      </c>
+      <c r="R403" t="n">
+        <v>438.0563667710496</v>
+      </c>
+      <c r="S403" t="n">
+        <v>1120.5</v>
+      </c>
+      <c r="T403" t="n">
+        <v>1314.169100313149</v>
+      </c>
+      <c r="U403" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V403" t="n">
+        <v>0.01586766249802807</v>
+      </c>
+      <c r="W403" t="n">
+        <v>0.01710677250940229</v>
+      </c>
+      <c r="X403" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y403" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z403" t="n">
+        <v>0.5092240571975708</v>
+      </c>
+      <c r="AA403" t="n">
+        <v>12.11775493621826</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E404" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F404" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H404" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I404" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J404" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K404" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L404" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M404" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N404" s="2" t="n">
+        <v>45833.44239746398</v>
+      </c>
+      <c r="O404" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="P404" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q404" t="n">
+        <v>1.78637</v>
+      </c>
+      <c r="R404" t="n">
+        <v>0.4086499437406584</v>
+      </c>
+      <c r="S404" t="n">
+        <v>2674.72</v>
+      </c>
+      <c r="T404" t="n">
+        <v>1497.293393865772</v>
+      </c>
+      <c r="U404" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="V404" t="n">
+        <v>0.006896551724137945</v>
+      </c>
+      <c r="W404" t="n">
+        <v>0.0002454216053244807</v>
+      </c>
+      <c r="X404" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y404" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z404" t="n">
+        <v>0.5095238089561462</v>
+      </c>
+      <c r="AA404" t="n">
+        <v>11.94347476959229</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E405" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F405" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H405" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I405" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J405" t="n">
+        <v>537</v>
+      </c>
+      <c r="K405" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L405" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M405" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N405" s="2" t="n">
+        <v>45833.44239746398</v>
+      </c>
+      <c r="O405" t="n">
+        <v>24.95</v>
+      </c>
+      <c r="P405" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q405" t="n">
+        <v>9.10688</v>
+      </c>
+      <c r="R405" t="n">
+        <v>2.739686918022418</v>
+      </c>
+      <c r="S405" t="n">
+        <v>13398.15</v>
+      </c>
+      <c r="T405" t="n">
+        <v>1471.211874978038</v>
+      </c>
+      <c r="U405" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V405" t="n">
+        <v>-0.009920634920634885</v>
+      </c>
+      <c r="W405" t="n">
+        <v>-0.01713296945006393</v>
+      </c>
+      <c r="X405" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y405" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z405" t="n">
+        <v>0.5673728585243225</v>
+      </c>
+      <c r="AA405" t="n">
+        <v>11.78222894668579</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E406" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F406" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H406" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I406" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J406" t="n">
+        <v>121</v>
+      </c>
+      <c r="K406" t="n">
+        <v>12</v>
+      </c>
+      <c r="L406" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M406" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N406" s="2" t="n">
+        <v>45833.44239746398</v>
+      </c>
+      <c r="O406" t="n">
+        <v>14.09</v>
+      </c>
+      <c r="P406" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q406" t="n">
+        <v>1.1606314</v>
+      </c>
+      <c r="R406" t="n">
+        <v>12.1399438271272</v>
+      </c>
+      <c r="S406" t="n">
+        <v>1704.89</v>
+      </c>
+      <c r="T406" t="n">
+        <v>1468.933203082391</v>
+      </c>
+      <c r="U406" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V406" t="n">
+        <v>-0.006346967559943573</v>
+      </c>
+      <c r="W406" t="n">
+        <v>-0.01514851244775484</v>
+      </c>
+      <c r="X406" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y406" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z406" t="n">
+        <v>0.5561246275901794</v>
+      </c>
+      <c r="AA406" t="n">
+        <v>14.51355290412903</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr"/>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E407" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F407" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H407" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I407" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J407" t="n">
+        <v>162</v>
+      </c>
+      <c r="K407" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L407" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M407" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N407" s="2" t="n">
+        <v>45833.44239746398</v>
+      </c>
+      <c r="O407" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="P407" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q407" t="n">
+        <v>4.2482</v>
+      </c>
+      <c r="R407" t="n">
+        <v>9.08620121463208</v>
+      </c>
+      <c r="S407" t="n">
+        <v>6253.2</v>
+      </c>
+      <c r="T407" t="n">
+        <v>1471.964596770397</v>
+      </c>
+      <c r="U407" t="n">
+        <v>8.272543736854324</v>
+      </c>
+      <c r="V407" t="n">
+        <v>-0.01530612244897966</v>
+      </c>
+      <c r="W407" t="n">
+        <v>-0.01147925555985774</v>
+      </c>
+      <c r="X407" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y407" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z407" t="n">
+        <v>0.6009591817855835</v>
+      </c>
+      <c r="AA407" t="n">
+        <v>12.92029732894897</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E408" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F408" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H408" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I408" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J408" t="n">
+        <v>101</v>
+      </c>
+      <c r="K408" t="n">
+        <v>11</v>
+      </c>
+      <c r="L408" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M408" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N408" s="2" t="n">
+        <v>45833.44239746398</v>
+      </c>
+      <c r="O408" t="n">
+        <v>24659</v>
+      </c>
+      <c r="P408" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q408" t="n">
+        <v>2060.41</v>
+      </c>
+      <c r="R408" t="n">
+        <v>11.96800636766469</v>
+      </c>
+      <c r="S408" t="n">
+        <v>2490559</v>
+      </c>
+      <c r="T408" t="n">
+        <v>1208.768643134134</v>
+      </c>
+      <c r="U408" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V408" t="n">
+        <v>0.005340834964122632</v>
+      </c>
+      <c r="W408" t="n">
+        <v>0.003325674074590168</v>
+      </c>
+      <c r="X408" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y408" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z408" t="n">
+        <v>0.4206280708312988</v>
+      </c>
+      <c r="AA408" t="n">
+        <v>10.58742851018906</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E409" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F409" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H409" t="n">
+        <v>1</v>
+      </c>
+      <c r="I409" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J409" t="n">
+        <v>30</v>
+      </c>
+      <c r="K409" t="n">
+        <v>9</v>
+      </c>
+      <c r="L409" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M409" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N409" s="2" t="n">
+        <v>45833.44239746398</v>
+      </c>
+      <c r="O409" t="n">
+        <v>46.08</v>
+      </c>
+      <c r="P409" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q409" t="n">
+        <v>1</v>
+      </c>
+      <c r="R409" t="n">
+        <v>46.08</v>
+      </c>
+      <c r="S409" t="n">
+        <v>1382.4</v>
+      </c>
+      <c r="T409" t="n">
+        <v>1382.4</v>
+      </c>
+      <c r="U409" t="n">
+        <v>41.472</v>
+      </c>
+      <c r="V409" t="n">
+        <v>0.008756567425569184</v>
+      </c>
+      <c r="W409" t="n">
+        <v>0.008756567425569184</v>
+      </c>
+      <c r="X409" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y409" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z409" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="AA409" t="n">
         <v>12.81225872039795</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA409"/>
+  <dimension ref="A1:AA417"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38126,7 +38126,7 @@
         <v>100</v>
       </c>
       <c r="N402" s="2" t="n">
-        <v>45833.44239746398</v>
+        <v>45833.44239746527</v>
       </c>
       <c r="O402" t="n">
         <v>1</v>
@@ -38217,7 +38217,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N403" s="2" t="n">
-        <v>45833.44239746398</v>
+        <v>45833.44239746527</v>
       </c>
       <c r="O403" t="n">
         <v>373.5</v>
@@ -38312,7 +38312,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N404" s="2" t="n">
-        <v>45833.44239746398</v>
+        <v>45833.44239746527</v>
       </c>
       <c r="O404" t="n">
         <v>0.73</v>
@@ -38407,7 +38407,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N405" s="2" t="n">
-        <v>45833.44239746398</v>
+        <v>45833.44239746527</v>
       </c>
       <c r="O405" t="n">
         <v>24.95</v>
@@ -38502,7 +38502,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N406" s="2" t="n">
-        <v>45833.44239746398</v>
+        <v>45833.44239746527</v>
       </c>
       <c r="O406" t="n">
         <v>14.09</v>
@@ -38593,7 +38593,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N407" s="2" t="n">
-        <v>45833.44239746398</v>
+        <v>45833.44239746527</v>
       </c>
       <c r="O407" t="n">
         <v>38.6</v>
@@ -38688,7 +38688,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N408" s="2" t="n">
-        <v>45833.44239746398</v>
+        <v>45833.44239746527</v>
       </c>
       <c r="O408" t="n">
         <v>24659</v>
@@ -38783,7 +38783,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N409" s="2" t="n">
-        <v>45833.44239746398</v>
+        <v>45833.44239746527</v>
       </c>
       <c r="O409" t="n">
         <v>46.08</v>
@@ -38824,6 +38824,760 @@
         <v>0.6434202790260315</v>
       </c>
       <c r="AA409" t="n">
+        <v>12.81225872039795</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F410" t="n">
+        <v>1</v>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H410" t="n">
+        <v>1</v>
+      </c>
+      <c r="I410" t="n">
+        <v>1</v>
+      </c>
+      <c r="J410" t="n">
+        <v>1</v>
+      </c>
+      <c r="K410" t="n">
+        <v>100</v>
+      </c>
+      <c r="L410" t="n">
+        <v>100</v>
+      </c>
+      <c r="M410" t="n">
+        <v>100</v>
+      </c>
+      <c r="N410" s="2" t="n">
+        <v>45833.47729447171</v>
+      </c>
+      <c r="O410" t="n">
+        <v>1</v>
+      </c>
+      <c r="P410" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q410" t="n">
+        <v>1</v>
+      </c>
+      <c r="R410" t="n">
+        <v>1</v>
+      </c>
+      <c r="S410" t="n">
+        <v>0</v>
+      </c>
+      <c r="T410" t="n">
+        <v>45.43580260334033</v>
+      </c>
+      <c r="U410" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V410" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W410" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X410" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y410" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z410" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA410" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr"/>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E411" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F411" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H411" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I411" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J411" t="n">
+        <v>3</v>
+      </c>
+      <c r="K411" t="n">
+        <v>10</v>
+      </c>
+      <c r="L411" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M411" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N411" s="2" t="n">
+        <v>45833.47729447171</v>
+      </c>
+      <c r="O411" t="n">
+        <v>373.5</v>
+      </c>
+      <c r="P411" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q411" t="n">
+        <v>0.85281</v>
+      </c>
+      <c r="R411" t="n">
+        <v>437.9639075526788</v>
+      </c>
+      <c r="S411" t="n">
+        <v>1120.5</v>
+      </c>
+      <c r="T411" t="n">
+        <v>1313.891722658037</v>
+      </c>
+      <c r="U411" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V411" t="n">
+        <v>0.01586766249802807</v>
+      </c>
+      <c r="W411" t="n">
+        <v>0.01689209489181853</v>
+      </c>
+      <c r="X411" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y411" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z411" t="n">
+        <v>0.5092240571975708</v>
+      </c>
+      <c r="AA411" t="n">
+        <v>12.11775493621826</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E412" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F412" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H412" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I412" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J412" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K412" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L412" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M412" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N412" s="2" t="n">
+        <v>45833.47729447171</v>
+      </c>
+      <c r="O412" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="P412" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q412" t="n">
+        <v>1.78645</v>
+      </c>
+      <c r="R412" t="n">
+        <v>0.4086316437627697</v>
+      </c>
+      <c r="S412" t="n">
+        <v>2674.72</v>
+      </c>
+      <c r="T412" t="n">
+        <v>1497.226342746788</v>
+      </c>
+      <c r="U412" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="V412" t="n">
+        <v>0.006896551724137945</v>
+      </c>
+      <c r="W412" t="n">
+        <v>0.0002006290649632092</v>
+      </c>
+      <c r="X412" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y412" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z412" t="n">
+        <v>0.5095238089561462</v>
+      </c>
+      <c r="AA412" t="n">
+        <v>11.94347476959229</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E413" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F413" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H413" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I413" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J413" t="n">
+        <v>537</v>
+      </c>
+      <c r="K413" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L413" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M413" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>45833.47729447171</v>
+      </c>
+      <c r="O413" t="n">
+        <v>24.95</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q413" t="n">
+        <v>9.108409999999999</v>
+      </c>
+      <c r="R413" t="n">
+        <v>2.739226714651624</v>
+      </c>
+      <c r="S413" t="n">
+        <v>13398.15</v>
+      </c>
+      <c r="T413" t="n">
+        <v>1470.964745767922</v>
+      </c>
+      <c r="U413" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V413" t="n">
+        <v>-0.009920634920634885</v>
+      </c>
+      <c r="W413" t="n">
+        <v>-0.0172980681398176</v>
+      </c>
+      <c r="X413" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y413" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z413" t="n">
+        <v>0.5673728585243225</v>
+      </c>
+      <c r="AA413" t="n">
+        <v>11.78222894668579</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E414" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F414" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H414" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I414" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J414" t="n">
+        <v>121</v>
+      </c>
+      <c r="K414" t="n">
+        <v>12</v>
+      </c>
+      <c r="L414" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M414" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>45833.47729447171</v>
+      </c>
+      <c r="O414" t="n">
+        <v>14.09</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q414" t="n">
+        <v>1.1606314</v>
+      </c>
+      <c r="R414" t="n">
+        <v>12.1399438271272</v>
+      </c>
+      <c r="S414" t="n">
+        <v>1704.89</v>
+      </c>
+      <c r="T414" t="n">
+        <v>1468.933203082391</v>
+      </c>
+      <c r="U414" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V414" t="n">
+        <v>-0.006346967559943573</v>
+      </c>
+      <c r="W414" t="n">
+        <v>-0.01514851244775484</v>
+      </c>
+      <c r="X414" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y414" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z414" t="n">
+        <v>0.5561246275901794</v>
+      </c>
+      <c r="AA414" t="n">
+        <v>14.51355290412903</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr"/>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E415" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F415" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H415" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I415" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J415" t="n">
+        <v>162</v>
+      </c>
+      <c r="K415" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L415" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M415" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N415" s="2" t="n">
+        <v>45833.47729447171</v>
+      </c>
+      <c r="O415" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q415" t="n">
+        <v>4.24652</v>
+      </c>
+      <c r="R415" t="n">
+        <v>9.066247185931068</v>
+      </c>
+      <c r="S415" t="n">
+        <v>6237</v>
+      </c>
+      <c r="T415" t="n">
+        <v>1468.732044120833</v>
+      </c>
+      <c r="U415" t="n">
+        <v>8.272543736854324</v>
+      </c>
+      <c r="V415" t="n">
+        <v>-0.0178571428571429</v>
+      </c>
+      <c r="W415" t="n">
+        <v>-0.01365012662469167</v>
+      </c>
+      <c r="X415" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y415" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z415" t="n">
+        <v>0.6009591817855835</v>
+      </c>
+      <c r="AA415" t="n">
+        <v>12.92029732894897</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E416" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F416" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H416" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I416" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J416" t="n">
+        <v>101</v>
+      </c>
+      <c r="K416" t="n">
+        <v>11</v>
+      </c>
+      <c r="L416" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M416" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N416" s="2" t="n">
+        <v>45833.47729447171</v>
+      </c>
+      <c r="O416" t="n">
+        <v>24537</v>
+      </c>
+      <c r="P416" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q416" t="n">
+        <v>2063.71</v>
+      </c>
+      <c r="R416" t="n">
+        <v>11.88975195158234</v>
+      </c>
+      <c r="S416" t="n">
+        <v>2478237</v>
+      </c>
+      <c r="T416" t="n">
+        <v>1200.864947109817</v>
+      </c>
+      <c r="U416" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V416" t="n">
+        <v>0.0003669275929549798</v>
+      </c>
+      <c r="W416" t="n">
+        <v>-0.003234705520232195</v>
+      </c>
+      <c r="X416" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y416" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z416" t="n">
+        <v>0.4206280708312988</v>
+      </c>
+      <c r="AA416" t="n">
+        <v>10.58742851018906</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E417" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F417" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H417" t="n">
+        <v>1</v>
+      </c>
+      <c r="I417" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J417" t="n">
+        <v>30</v>
+      </c>
+      <c r="K417" t="n">
+        <v>9</v>
+      </c>
+      <c r="L417" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M417" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N417" s="2" t="n">
+        <v>45833.47729447171</v>
+      </c>
+      <c r="O417" t="n">
+        <v>46.08</v>
+      </c>
+      <c r="P417" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q417" t="n">
+        <v>1</v>
+      </c>
+      <c r="R417" t="n">
+        <v>46.08</v>
+      </c>
+      <c r="S417" t="n">
+        <v>1382.4</v>
+      </c>
+      <c r="T417" t="n">
+        <v>1382.4</v>
+      </c>
+      <c r="U417" t="n">
+        <v>41.472</v>
+      </c>
+      <c r="V417" t="n">
+        <v>0.008756567425569184</v>
+      </c>
+      <c r="W417" t="n">
+        <v>0.008756567425569184</v>
+      </c>
+      <c r="X417" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y417" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z417" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="AA417" t="n">
         <v>12.81225872039795</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA417"/>
+  <dimension ref="A1:AA425"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38880,7 +38880,7 @@
         <v>100</v>
       </c>
       <c r="N410" s="2" t="n">
-        <v>45833.47729447171</v>
+        <v>45833.47729446759</v>
       </c>
       <c r="O410" t="n">
         <v>1</v>
@@ -38971,7 +38971,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N411" s="2" t="n">
-        <v>45833.47729447171</v>
+        <v>45833.47729446759</v>
       </c>
       <c r="O411" t="n">
         <v>373.5</v>
@@ -39066,7 +39066,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N412" s="2" t="n">
-        <v>45833.47729447171</v>
+        <v>45833.47729446759</v>
       </c>
       <c r="O412" t="n">
         <v>0.73</v>
@@ -39161,7 +39161,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>45833.47729447171</v>
+        <v>45833.47729446759</v>
       </c>
       <c r="O413" t="n">
         <v>24.95</v>
@@ -39256,7 +39256,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>45833.47729447171</v>
+        <v>45833.47729446759</v>
       </c>
       <c r="O414" t="n">
         <v>14.09</v>
@@ -39347,7 +39347,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N415" s="2" t="n">
-        <v>45833.47729447171</v>
+        <v>45833.47729446759</v>
       </c>
       <c r="O415" t="n">
         <v>38.5</v>
@@ -39442,7 +39442,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N416" s="2" t="n">
-        <v>45833.47729447171</v>
+        <v>45833.47729446759</v>
       </c>
       <c r="O416" t="n">
         <v>24537</v>
@@ -39537,7 +39537,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N417" s="2" t="n">
-        <v>45833.47729447171</v>
+        <v>45833.47729446759</v>
       </c>
       <c r="O417" t="n">
         <v>46.08</v>
@@ -39578,6 +39578,760 @@
         <v>0.6434202790260315</v>
       </c>
       <c r="AA417" t="n">
+        <v>12.81225872039795</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F418" t="n">
+        <v>1</v>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H418" t="n">
+        <v>1</v>
+      </c>
+      <c r="I418" t="n">
+        <v>1</v>
+      </c>
+      <c r="J418" t="n">
+        <v>1</v>
+      </c>
+      <c r="K418" t="n">
+        <v>100</v>
+      </c>
+      <c r="L418" t="n">
+        <v>100</v>
+      </c>
+      <c r="M418" t="n">
+        <v>100</v>
+      </c>
+      <c r="N418" s="2" t="n">
+        <v>45833.54234937639</v>
+      </c>
+      <c r="O418" t="n">
+        <v>1</v>
+      </c>
+      <c r="P418" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q418" t="n">
+        <v>1</v>
+      </c>
+      <c r="R418" t="n">
+        <v>1</v>
+      </c>
+      <c r="S418" t="n">
+        <v>0</v>
+      </c>
+      <c r="T418" t="n">
+        <v>45.43580260334033</v>
+      </c>
+      <c r="U418" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V418" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W418" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X418" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y418" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z418" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA418" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr"/>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E419" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F419" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H419" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I419" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J419" t="n">
+        <v>3</v>
+      </c>
+      <c r="K419" t="n">
+        <v>10</v>
+      </c>
+      <c r="L419" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M419" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N419" s="2" t="n">
+        <v>45833.54234937639</v>
+      </c>
+      <c r="O419" t="n">
+        <v>377.48</v>
+      </c>
+      <c r="P419" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q419" t="n">
+        <v>0.85254</v>
+      </c>
+      <c r="R419" t="n">
+        <v>442.7710136767777</v>
+      </c>
+      <c r="S419" t="n">
+        <v>1132.44</v>
+      </c>
+      <c r="T419" t="n">
+        <v>1328.313041030333</v>
+      </c>
+      <c r="U419" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V419" t="n">
+        <v>0.02669270479184926</v>
+      </c>
+      <c r="W419" t="n">
+        <v>0.02805353566947932</v>
+      </c>
+      <c r="X419" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y419" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z419" t="n">
+        <v>0.5092240571975708</v>
+      </c>
+      <c r="AA419" t="n">
+        <v>12.11775493621826</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E420" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F420" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H420" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I420" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J420" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K420" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L420" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M420" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N420" s="2" t="n">
+        <v>45833.54234937639</v>
+      </c>
+      <c r="O420" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="P420" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q420" t="n">
+        <v>1.78543</v>
+      </c>
+      <c r="R420" t="n">
+        <v>0.4088650913225385</v>
+      </c>
+      <c r="S420" t="n">
+        <v>2674.72</v>
+      </c>
+      <c r="T420" t="n">
+        <v>1498.081694605781</v>
+      </c>
+      <c r="U420" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="V420" t="n">
+        <v>0.006896551724137945</v>
+      </c>
+      <c r="W420" t="n">
+        <v>0.0007720346320512217</v>
+      </c>
+      <c r="X420" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y420" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z420" t="n">
+        <v>0.5095238089561462</v>
+      </c>
+      <c r="AA420" t="n">
+        <v>11.94347476959229</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E421" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F421" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H421" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I421" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J421" t="n">
+        <v>537</v>
+      </c>
+      <c r="K421" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L421" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M421" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N421" s="2" t="n">
+        <v>45833.54234937639</v>
+      </c>
+      <c r="O421" t="n">
+        <v>24.95</v>
+      </c>
+      <c r="P421" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q421" t="n">
+        <v>9.09914</v>
+      </c>
+      <c r="R421" t="n">
+        <v>2.742017377466442</v>
+      </c>
+      <c r="S421" t="n">
+        <v>13398.15</v>
+      </c>
+      <c r="T421" t="n">
+        <v>1472.463331699479</v>
+      </c>
+      <c r="U421" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V421" t="n">
+        <v>-0.009920634920634885</v>
+      </c>
+      <c r="W421" t="n">
+        <v>-0.01629691342537842</v>
+      </c>
+      <c r="X421" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y421" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z421" t="n">
+        <v>0.5673728585243225</v>
+      </c>
+      <c r="AA421" t="n">
+        <v>11.78222894668579</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E422" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F422" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H422" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I422" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J422" t="n">
+        <v>121</v>
+      </c>
+      <c r="K422" t="n">
+        <v>12</v>
+      </c>
+      <c r="L422" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M422" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N422" s="2" t="n">
+        <v>45833.54234937639</v>
+      </c>
+      <c r="O422" t="n">
+        <v>14.09</v>
+      </c>
+      <c r="P422" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q422" t="n">
+        <v>1.1595547</v>
+      </c>
+      <c r="R422" t="n">
+        <v>12.1512163246805</v>
+      </c>
+      <c r="S422" t="n">
+        <v>1704.89</v>
+      </c>
+      <c r="T422" t="n">
+        <v>1470.29717528634</v>
+      </c>
+      <c r="U422" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V422" t="n">
+        <v>-0.006346967559943573</v>
+      </c>
+      <c r="W422" t="n">
+        <v>-0.01423403243517107</v>
+      </c>
+      <c r="X422" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y422" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z422" t="n">
+        <v>0.5561246275901794</v>
+      </c>
+      <c r="AA422" t="n">
+        <v>14.51355290412903</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr"/>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E423" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F423" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H423" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I423" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J423" t="n">
+        <v>162</v>
+      </c>
+      <c r="K423" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L423" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M423" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N423" s="2" t="n">
+        <v>45833.54234937639</v>
+      </c>
+      <c r="O423" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="P423" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q423" t="n">
+        <v>4.24701</v>
+      </c>
+      <c r="R423" t="n">
+        <v>9.065201165054944</v>
+      </c>
+      <c r="S423" t="n">
+        <v>6237</v>
+      </c>
+      <c r="T423" t="n">
+        <v>1468.562588738901</v>
+      </c>
+      <c r="U423" t="n">
+        <v>8.272543736854324</v>
+      </c>
+      <c r="V423" t="n">
+        <v>-0.0178571428571429</v>
+      </c>
+      <c r="W423" t="n">
+        <v>-0.01376392702496254</v>
+      </c>
+      <c r="X423" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y423" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z423" t="n">
+        <v>0.6009591817855835</v>
+      </c>
+      <c r="AA423" t="n">
+        <v>12.92029732894897</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E424" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F424" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H424" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I424" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J424" t="n">
+        <v>101</v>
+      </c>
+      <c r="K424" t="n">
+        <v>11</v>
+      </c>
+      <c r="L424" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M424" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N424" s="2" t="n">
+        <v>45833.54234937639</v>
+      </c>
+      <c r="O424" t="n">
+        <v>24614</v>
+      </c>
+      <c r="P424" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q424" t="n">
+        <v>2065.82</v>
+      </c>
+      <c r="R424" t="n">
+        <v>11.91488125780562</v>
+      </c>
+      <c r="S424" t="n">
+        <v>2486014</v>
+      </c>
+      <c r="T424" t="n">
+        <v>1203.403007038367</v>
+      </c>
+      <c r="U424" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V424" t="n">
+        <v>0.003506196999347733</v>
+      </c>
+      <c r="W424" t="n">
+        <v>-0.001128015622939738</v>
+      </c>
+      <c r="X424" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y424" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z424" t="n">
+        <v>0.4206280708312988</v>
+      </c>
+      <c r="AA424" t="n">
+        <v>10.58742851018906</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E425" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F425" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H425" t="n">
+        <v>1</v>
+      </c>
+      <c r="I425" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J425" t="n">
+        <v>30</v>
+      </c>
+      <c r="K425" t="n">
+        <v>9</v>
+      </c>
+      <c r="L425" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M425" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N425" s="2" t="n">
+        <v>45833.54234937639</v>
+      </c>
+      <c r="O425" t="n">
+        <v>46.18</v>
+      </c>
+      <c r="P425" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q425" t="n">
+        <v>1</v>
+      </c>
+      <c r="R425" t="n">
+        <v>46.18</v>
+      </c>
+      <c r="S425" t="n">
+        <v>1385.4</v>
+      </c>
+      <c r="T425" t="n">
+        <v>1385.4</v>
+      </c>
+      <c r="U425" t="n">
+        <v>41.562</v>
+      </c>
+      <c r="V425" t="n">
+        <v>0.01094570928196137</v>
+      </c>
+      <c r="W425" t="n">
+        <v>0.01094570928196137</v>
+      </c>
+      <c r="X425" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y425" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z425" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="AA425" t="n">
         <v>12.81225872039795</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA425"/>
+  <dimension ref="A1:AA433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39634,7 +39634,7 @@
         <v>100</v>
       </c>
       <c r="N418" s="2" t="n">
-        <v>45833.54234937639</v>
+        <v>45833.542349375</v>
       </c>
       <c r="O418" t="n">
         <v>1</v>
@@ -39725,7 +39725,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N419" s="2" t="n">
-        <v>45833.54234937639</v>
+        <v>45833.542349375</v>
       </c>
       <c r="O419" t="n">
         <v>377.48</v>
@@ -39820,7 +39820,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N420" s="2" t="n">
-        <v>45833.54234937639</v>
+        <v>45833.542349375</v>
       </c>
       <c r="O420" t="n">
         <v>0.73</v>
@@ -39915,7 +39915,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N421" s="2" t="n">
-        <v>45833.54234937639</v>
+        <v>45833.542349375</v>
       </c>
       <c r="O421" t="n">
         <v>24.95</v>
@@ -40010,7 +40010,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N422" s="2" t="n">
-        <v>45833.54234937639</v>
+        <v>45833.542349375</v>
       </c>
       <c r="O422" t="n">
         <v>14.09</v>
@@ -40101,7 +40101,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N423" s="2" t="n">
-        <v>45833.54234937639</v>
+        <v>45833.542349375</v>
       </c>
       <c r="O423" t="n">
         <v>38.5</v>
@@ -40196,7 +40196,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N424" s="2" t="n">
-        <v>45833.54234937639</v>
+        <v>45833.542349375</v>
       </c>
       <c r="O424" t="n">
         <v>24614</v>
@@ -40291,7 +40291,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N425" s="2" t="n">
-        <v>45833.54234937639</v>
+        <v>45833.542349375</v>
       </c>
       <c r="O425" t="n">
         <v>46.18</v>
@@ -40332,6 +40332,760 @@
         <v>0.6434202790260315</v>
       </c>
       <c r="AA425" t="n">
+        <v>12.81225872039795</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F426" t="n">
+        <v>1</v>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H426" t="n">
+        <v>1</v>
+      </c>
+      <c r="I426" t="n">
+        <v>1</v>
+      </c>
+      <c r="J426" t="n">
+        <v>1</v>
+      </c>
+      <c r="K426" t="n">
+        <v>100</v>
+      </c>
+      <c r="L426" t="n">
+        <v>100</v>
+      </c>
+      <c r="M426" t="n">
+        <v>100</v>
+      </c>
+      <c r="N426" s="2" t="n">
+        <v>45833.57324664685</v>
+      </c>
+      <c r="O426" t="n">
+        <v>1</v>
+      </c>
+      <c r="P426" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q426" t="n">
+        <v>1</v>
+      </c>
+      <c r="R426" t="n">
+        <v>1</v>
+      </c>
+      <c r="S426" t="n">
+        <v>0</v>
+      </c>
+      <c r="T426" t="n">
+        <v>45.43580260334033</v>
+      </c>
+      <c r="U426" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V426" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W426" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X426" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y426" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z426" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA426" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr"/>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E427" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F427" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H427" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I427" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J427" t="n">
+        <v>3</v>
+      </c>
+      <c r="K427" t="n">
+        <v>10</v>
+      </c>
+      <c r="L427" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M427" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N427" s="2" t="n">
+        <v>45833.57324664685</v>
+      </c>
+      <c r="O427" t="n">
+        <v>373.61</v>
+      </c>
+      <c r="P427" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q427" t="n">
+        <v>0.85231</v>
+      </c>
+      <c r="R427" t="n">
+        <v>438.3498961645411</v>
+      </c>
+      <c r="S427" t="n">
+        <v>1120.83</v>
+      </c>
+      <c r="T427" t="n">
+        <v>1315.049688493623</v>
+      </c>
+      <c r="U427" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V427" t="n">
+        <v>0.01616684708403837</v>
+      </c>
+      <c r="W427" t="n">
+        <v>0.01778830748229043</v>
+      </c>
+      <c r="X427" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y427" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z427" t="n">
+        <v>0.5092240571975708</v>
+      </c>
+      <c r="AA427" t="n">
+        <v>12.11775493621826</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E428" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F428" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H428" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I428" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J428" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K428" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L428" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M428" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N428" s="2" t="n">
+        <v>45833.57324664685</v>
+      </c>
+      <c r="O428" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="P428" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q428" t="n">
+        <v>1.78744</v>
+      </c>
+      <c r="R428" t="n">
+        <v>0.4084053171015531</v>
+      </c>
+      <c r="S428" t="n">
+        <v>2674.72</v>
+      </c>
+      <c r="T428" t="n">
+        <v>1496.39708186009</v>
+      </c>
+      <c r="U428" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="V428" t="n">
+        <v>0.006896551724137945</v>
+      </c>
+      <c r="W428" t="n">
+        <v>-0.0003533468015129992</v>
+      </c>
+      <c r="X428" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y428" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z428" t="n">
+        <v>0.5095238089561462</v>
+      </c>
+      <c r="AA428" t="n">
+        <v>11.94347476959229</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E429" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F429" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H429" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I429" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J429" t="n">
+        <v>537</v>
+      </c>
+      <c r="K429" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L429" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M429" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N429" s="2" t="n">
+        <v>45833.57324664685</v>
+      </c>
+      <c r="O429" t="n">
+        <v>24.95</v>
+      </c>
+      <c r="P429" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q429" t="n">
+        <v>9.108890000000001</v>
+      </c>
+      <c r="R429" t="n">
+        <v>2.739082368982389</v>
+      </c>
+      <c r="S429" t="n">
+        <v>13398.15</v>
+      </c>
+      <c r="T429" t="n">
+        <v>1470.887232143543</v>
+      </c>
+      <c r="U429" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V429" t="n">
+        <v>-0.009920634920634885</v>
+      </c>
+      <c r="W429" t="n">
+        <v>-0.01734985237777587</v>
+      </c>
+      <c r="X429" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y429" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z429" t="n">
+        <v>0.5673728585243225</v>
+      </c>
+      <c r="AA429" t="n">
+        <v>11.78222894668579</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E430" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F430" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H430" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I430" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J430" t="n">
+        <v>121</v>
+      </c>
+      <c r="K430" t="n">
+        <v>12</v>
+      </c>
+      <c r="L430" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M430" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N430" s="2" t="n">
+        <v>45833.57324664685</v>
+      </c>
+      <c r="O430" t="n">
+        <v>13.867</v>
+      </c>
+      <c r="P430" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q430" t="n">
+        <v>1.1606314</v>
+      </c>
+      <c r="R430" t="n">
+        <v>11.94780702986323</v>
+      </c>
+      <c r="S430" t="n">
+        <v>1677.907</v>
+      </c>
+      <c r="T430" t="n">
+        <v>1445.684650613451</v>
+      </c>
+      <c r="U430" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V430" t="n">
+        <v>-0.02207334273624817</v>
+      </c>
+      <c r="W430" t="n">
+        <v>-0.0307355870910585</v>
+      </c>
+      <c r="X430" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y430" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z430" t="n">
+        <v>0.5561246275901794</v>
+      </c>
+      <c r="AA430" t="n">
+        <v>14.51355290412903</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr"/>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E431" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F431" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H431" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I431" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J431" t="n">
+        <v>162</v>
+      </c>
+      <c r="K431" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L431" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M431" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N431" s="2" t="n">
+        <v>45833.57324664685</v>
+      </c>
+      <c r="O431" t="n">
+        <v>38.45</v>
+      </c>
+      <c r="P431" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q431" t="n">
+        <v>4.24843</v>
+      </c>
+      <c r="R431" t="n">
+        <v>9.05040214855841</v>
+      </c>
+      <c r="S431" t="n">
+        <v>6228.900000000001</v>
+      </c>
+      <c r="T431" t="n">
+        <v>1466.165148066462</v>
+      </c>
+      <c r="U431" t="n">
+        <v>8.272543736854324</v>
+      </c>
+      <c r="V431" t="n">
+        <v>-0.01913265306122447</v>
+      </c>
+      <c r="W431" t="n">
+        <v>-0.01537396563830273</v>
+      </c>
+      <c r="X431" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y431" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z431" t="n">
+        <v>0.6009591817855835</v>
+      </c>
+      <c r="AA431" t="n">
+        <v>12.92029732894897</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E432" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F432" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H432" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I432" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J432" t="n">
+        <v>101</v>
+      </c>
+      <c r="K432" t="n">
+        <v>11</v>
+      </c>
+      <c r="L432" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M432" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N432" s="2" t="n">
+        <v>45833.57324664685</v>
+      </c>
+      <c r="O432" t="n">
+        <v>24595</v>
+      </c>
+      <c r="P432" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q432" t="n">
+        <v>2070.52</v>
+      </c>
+      <c r="R432" t="n">
+        <v>11.87865850124606</v>
+      </c>
+      <c r="S432" t="n">
+        <v>2484095</v>
+      </c>
+      <c r="T432" t="n">
+        <v>1199.744508625852</v>
+      </c>
+      <c r="U432" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V432" t="n">
+        <v>0.002731572080887146</v>
+      </c>
+      <c r="W432" t="n">
+        <v>-0.004164713676522491</v>
+      </c>
+      <c r="X432" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y432" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z432" t="n">
+        <v>0.4206280708312988</v>
+      </c>
+      <c r="AA432" t="n">
+        <v>10.58742851018906</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E433" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F433" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H433" t="n">
+        <v>1</v>
+      </c>
+      <c r="I433" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J433" t="n">
+        <v>30</v>
+      </c>
+      <c r="K433" t="n">
+        <v>9</v>
+      </c>
+      <c r="L433" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M433" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N433" s="2" t="n">
+        <v>45833.57324664685</v>
+      </c>
+      <c r="O433" t="n">
+        <v>46.32</v>
+      </c>
+      <c r="P433" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q433" t="n">
+        <v>1</v>
+      </c>
+      <c r="R433" t="n">
+        <v>46.32</v>
+      </c>
+      <c r="S433" t="n">
+        <v>1389.6</v>
+      </c>
+      <c r="T433" t="n">
+        <v>1389.6</v>
+      </c>
+      <c r="U433" t="n">
+        <v>41.688</v>
+      </c>
+      <c r="V433" t="n">
+        <v>0.01401050788091074</v>
+      </c>
+      <c r="W433" t="n">
+        <v>0.01401050788091074</v>
+      </c>
+      <c r="X433" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y433" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z433" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="AA433" t="n">
         <v>12.81225872039795</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA433"/>
+  <dimension ref="A1:AA441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40388,7 +40388,7 @@
         <v>100</v>
       </c>
       <c r="N426" s="2" t="n">
-        <v>45833.57324664685</v>
+        <v>45833.57324664352</v>
       </c>
       <c r="O426" t="n">
         <v>1</v>
@@ -40479,7 +40479,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N427" s="2" t="n">
-        <v>45833.57324664685</v>
+        <v>45833.57324664352</v>
       </c>
       <c r="O427" t="n">
         <v>373.61</v>
@@ -40574,7 +40574,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N428" s="2" t="n">
-        <v>45833.57324664685</v>
+        <v>45833.57324664352</v>
       </c>
       <c r="O428" t="n">
         <v>0.73</v>
@@ -40669,7 +40669,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N429" s="2" t="n">
-        <v>45833.57324664685</v>
+        <v>45833.57324664352</v>
       </c>
       <c r="O429" t="n">
         <v>24.95</v>
@@ -40764,7 +40764,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N430" s="2" t="n">
-        <v>45833.57324664685</v>
+        <v>45833.57324664352</v>
       </c>
       <c r="O430" t="n">
         <v>13.867</v>
@@ -40855,7 +40855,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N431" s="2" t="n">
-        <v>45833.57324664685</v>
+        <v>45833.57324664352</v>
       </c>
       <c r="O431" t="n">
         <v>38.45</v>
@@ -40950,7 +40950,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N432" s="2" t="n">
-        <v>45833.57324664685</v>
+        <v>45833.57324664352</v>
       </c>
       <c r="O432" t="n">
         <v>24595</v>
@@ -41045,7 +41045,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N433" s="2" t="n">
-        <v>45833.57324664685</v>
+        <v>45833.57324664352</v>
       </c>
       <c r="O433" t="n">
         <v>46.32</v>
@@ -41086,6 +41086,760 @@
         <v>0.6434202790260315</v>
       </c>
       <c r="AA433" t="n">
+        <v>12.81225872039795</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F434" t="n">
+        <v>1</v>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H434" t="n">
+        <v>1</v>
+      </c>
+      <c r="I434" t="n">
+        <v>1</v>
+      </c>
+      <c r="J434" t="n">
+        <v>1</v>
+      </c>
+      <c r="K434" t="n">
+        <v>100</v>
+      </c>
+      <c r="L434" t="n">
+        <v>100</v>
+      </c>
+      <c r="M434" t="n">
+        <v>100</v>
+      </c>
+      <c r="N434" s="2" t="n">
+        <v>45833.6078551254</v>
+      </c>
+      <c r="O434" t="n">
+        <v>1</v>
+      </c>
+      <c r="P434" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q434" t="n">
+        <v>1</v>
+      </c>
+      <c r="R434" t="n">
+        <v>1</v>
+      </c>
+      <c r="S434" t="n">
+        <v>0</v>
+      </c>
+      <c r="T434" t="n">
+        <v>45.43580260334033</v>
+      </c>
+      <c r="U434" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V434" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W434" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X434" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y434" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z434" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA434" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr"/>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E435" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F435" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H435" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I435" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J435" t="n">
+        <v>3</v>
+      </c>
+      <c r="K435" t="n">
+        <v>10</v>
+      </c>
+      <c r="L435" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M435" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N435" s="2" t="n">
+        <v>45833.6078551254</v>
+      </c>
+      <c r="O435" t="n">
+        <v>373.61</v>
+      </c>
+      <c r="P435" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q435" t="n">
+        <v>0.85297</v>
+      </c>
+      <c r="R435" t="n">
+        <v>438.010715499959</v>
+      </c>
+      <c r="S435" t="n">
+        <v>1120.83</v>
+      </c>
+      <c r="T435" t="n">
+        <v>1314.032146499877</v>
+      </c>
+      <c r="U435" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V435" t="n">
+        <v>0.01616684708403837</v>
+      </c>
+      <c r="W435" t="n">
+        <v>0.01700077652230547</v>
+      </c>
+      <c r="X435" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y435" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z435" t="n">
+        <v>0.5092240571975708</v>
+      </c>
+      <c r="AA435" t="n">
+        <v>12.11775493621826</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E436" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F436" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H436" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I436" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J436" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K436" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L436" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M436" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N436" s="2" t="n">
+        <v>45833.6078551254</v>
+      </c>
+      <c r="O436" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="P436" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q436" t="n">
+        <v>1.78927</v>
+      </c>
+      <c r="R436" t="n">
+        <v>0.4079876150608908</v>
+      </c>
+      <c r="S436" t="n">
+        <v>2674.72</v>
+      </c>
+      <c r="T436" t="n">
+        <v>1494.866621583104</v>
+      </c>
+      <c r="U436" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="V436" t="n">
+        <v>0.006896551724137945</v>
+      </c>
+      <c r="W436" t="n">
+        <v>-0.001375748884682837</v>
+      </c>
+      <c r="X436" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y436" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z436" t="n">
+        <v>0.5095238089561462</v>
+      </c>
+      <c r="AA436" t="n">
+        <v>11.94347476959229</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E437" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F437" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H437" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I437" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J437" t="n">
+        <v>537</v>
+      </c>
+      <c r="K437" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L437" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M437" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N437" s="2" t="n">
+        <v>45833.6078551254</v>
+      </c>
+      <c r="O437" t="n">
+        <v>24.95</v>
+      </c>
+      <c r="P437" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q437" t="n">
+        <v>9.11702</v>
+      </c>
+      <c r="R437" t="n">
+        <v>2.736639823100092</v>
+      </c>
+      <c r="S437" t="n">
+        <v>13398.15</v>
+      </c>
+      <c r="T437" t="n">
+        <v>1469.575585004749</v>
+      </c>
+      <c r="U437" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V437" t="n">
+        <v>-0.009920634920634885</v>
+      </c>
+      <c r="W437" t="n">
+        <v>-0.018226119590107</v>
+      </c>
+      <c r="X437" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y437" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z437" t="n">
+        <v>0.5673728585243225</v>
+      </c>
+      <c r="AA437" t="n">
+        <v>11.78222894668579</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E438" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F438" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H438" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I438" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J438" t="n">
+        <v>121</v>
+      </c>
+      <c r="K438" t="n">
+        <v>12</v>
+      </c>
+      <c r="L438" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M438" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N438" s="2" t="n">
+        <v>45833.6078551254</v>
+      </c>
+      <c r="O438" t="n">
+        <v>14.025</v>
+      </c>
+      <c r="P438" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q438" t="n">
+        <v>1.161845</v>
+      </c>
+      <c r="R438" t="n">
+        <v>12.0713176026062</v>
+      </c>
+      <c r="S438" t="n">
+        <v>1697.025</v>
+      </c>
+      <c r="T438" t="n">
+        <v>1460.62942991535</v>
+      </c>
+      <c r="U438" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V438" t="n">
+        <v>-0.01093088857545832</v>
+      </c>
+      <c r="W438" t="n">
+        <v>-0.02071580668461748</v>
+      </c>
+      <c r="X438" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y438" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z438" t="n">
+        <v>0.5561246275901794</v>
+      </c>
+      <c r="AA438" t="n">
+        <v>14.51355290412903</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr"/>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E439" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F439" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H439" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I439" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J439" t="n">
+        <v>162</v>
+      </c>
+      <c r="K439" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L439" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M439" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N439" s="2" t="n">
+        <v>45833.6078551254</v>
+      </c>
+      <c r="O439" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="P439" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q439" t="n">
+        <v>4.24833</v>
+      </c>
+      <c r="R439" t="n">
+        <v>9.062384513444107</v>
+      </c>
+      <c r="S439" t="n">
+        <v>6237</v>
+      </c>
+      <c r="T439" t="n">
+        <v>1468.106291177945</v>
+      </c>
+      <c r="U439" t="n">
+        <v>8.272543736854324</v>
+      </c>
+      <c r="V439" t="n">
+        <v>-0.0178571428571429</v>
+      </c>
+      <c r="W439" t="n">
+        <v>-0.01407036075688228</v>
+      </c>
+      <c r="X439" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y439" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z439" t="n">
+        <v>0.6009591817855835</v>
+      </c>
+      <c r="AA439" t="n">
+        <v>12.92029732894897</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E440" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F440" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H440" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I440" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J440" t="n">
+        <v>101</v>
+      </c>
+      <c r="K440" t="n">
+        <v>11</v>
+      </c>
+      <c r="L440" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M440" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N440" s="2" t="n">
+        <v>45833.6078551254</v>
+      </c>
+      <c r="O440" t="n">
+        <v>24759</v>
+      </c>
+      <c r="P440" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q440" t="n">
+        <v>2066.22</v>
+      </c>
+      <c r="R440" t="n">
+        <v>11.98275111072393</v>
+      </c>
+      <c r="S440" t="n">
+        <v>2500659</v>
+      </c>
+      <c r="T440" t="n">
+        <v>1210.257862183117</v>
+      </c>
+      <c r="U440" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V440" t="n">
+        <v>0.009417808219178037</v>
+      </c>
+      <c r="W440" t="n">
+        <v>0.004561784652617806</v>
+      </c>
+      <c r="X440" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y440" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z440" t="n">
+        <v>0.4206280708312988</v>
+      </c>
+      <c r="AA440" t="n">
+        <v>10.58742851018906</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E441" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F441" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H441" t="n">
+        <v>1</v>
+      </c>
+      <c r="I441" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J441" t="n">
+        <v>30</v>
+      </c>
+      <c r="K441" t="n">
+        <v>9</v>
+      </c>
+      <c r="L441" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M441" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N441" s="2" t="n">
+        <v>45833.6078551254</v>
+      </c>
+      <c r="O441" t="n">
+        <v>46.14</v>
+      </c>
+      <c r="P441" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q441" t="n">
+        <v>1</v>
+      </c>
+      <c r="R441" t="n">
+        <v>46.14</v>
+      </c>
+      <c r="S441" t="n">
+        <v>1384.2</v>
+      </c>
+      <c r="T441" t="n">
+        <v>1384.2</v>
+      </c>
+      <c r="U441" t="n">
+        <v>41.688</v>
+      </c>
+      <c r="V441" t="n">
+        <v>0.01007005253940463</v>
+      </c>
+      <c r="W441" t="n">
+        <v>0.01007005253940463</v>
+      </c>
+      <c r="X441" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y441" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z441" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="AA441" t="n">
         <v>12.81225872039795</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA441"/>
+  <dimension ref="A1:AA449"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41142,7 +41142,7 @@
         <v>100</v>
       </c>
       <c r="N434" s="2" t="n">
-        <v>45833.6078551254</v>
+        <v>45833.60785512732</v>
       </c>
       <c r="O434" t="n">
         <v>1</v>
@@ -41233,7 +41233,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N435" s="2" t="n">
-        <v>45833.6078551254</v>
+        <v>45833.60785512732</v>
       </c>
       <c r="O435" t="n">
         <v>373.61</v>
@@ -41328,7 +41328,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N436" s="2" t="n">
-        <v>45833.6078551254</v>
+        <v>45833.60785512732</v>
       </c>
       <c r="O436" t="n">
         <v>0.73</v>
@@ -41423,7 +41423,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N437" s="2" t="n">
-        <v>45833.6078551254</v>
+        <v>45833.60785512732</v>
       </c>
       <c r="O437" t="n">
         <v>24.95</v>
@@ -41518,7 +41518,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N438" s="2" t="n">
-        <v>45833.6078551254</v>
+        <v>45833.60785512732</v>
       </c>
       <c r="O438" t="n">
         <v>14.025</v>
@@ -41609,7 +41609,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N439" s="2" t="n">
-        <v>45833.6078551254</v>
+        <v>45833.60785512732</v>
       </c>
       <c r="O439" t="n">
         <v>38.5</v>
@@ -41704,7 +41704,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N440" s="2" t="n">
-        <v>45833.6078551254</v>
+        <v>45833.60785512732</v>
       </c>
       <c r="O440" t="n">
         <v>24759</v>
@@ -41799,7 +41799,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N441" s="2" t="n">
-        <v>45833.6078551254</v>
+        <v>45833.60785512732</v>
       </c>
       <c r="O441" t="n">
         <v>46.14</v>
@@ -41840,6 +41840,760 @@
         <v>0.6434202790260315</v>
       </c>
       <c r="AA441" t="n">
+        <v>12.81225872039795</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F442" t="n">
+        <v>1</v>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H442" t="n">
+        <v>1</v>
+      </c>
+      <c r="I442" t="n">
+        <v>1</v>
+      </c>
+      <c r="J442" t="n">
+        <v>1</v>
+      </c>
+      <c r="K442" t="n">
+        <v>100</v>
+      </c>
+      <c r="L442" t="n">
+        <v>100</v>
+      </c>
+      <c r="M442" t="n">
+        <v>100</v>
+      </c>
+      <c r="N442" s="2" t="n">
+        <v>45833.64895553317</v>
+      </c>
+      <c r="O442" t="n">
+        <v>1</v>
+      </c>
+      <c r="P442" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q442" t="n">
+        <v>1</v>
+      </c>
+      <c r="R442" t="n">
+        <v>1</v>
+      </c>
+      <c r="S442" t="n">
+        <v>0</v>
+      </c>
+      <c r="T442" t="n">
+        <v>45.43580260334033</v>
+      </c>
+      <c r="U442" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V442" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W442" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X442" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y442" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z442" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA442" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr"/>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E443" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F443" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H443" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I443" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J443" t="n">
+        <v>3</v>
+      </c>
+      <c r="K443" t="n">
+        <v>10</v>
+      </c>
+      <c r="L443" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M443" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N443" s="2" t="n">
+        <v>45833.64895553317</v>
+      </c>
+      <c r="O443" t="n">
+        <v>373.61</v>
+      </c>
+      <c r="P443" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q443" t="n">
+        <v>0.85348</v>
+      </c>
+      <c r="R443" t="n">
+        <v>437.7489806439518</v>
+      </c>
+      <c r="S443" t="n">
+        <v>1120.83</v>
+      </c>
+      <c r="T443" t="n">
+        <v>1313.246941931855</v>
+      </c>
+      <c r="U443" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V443" t="n">
+        <v>0.01616684708403837</v>
+      </c>
+      <c r="W443" t="n">
+        <v>0.01639306410253427</v>
+      </c>
+      <c r="X443" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y443" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z443" t="n">
+        <v>0.5092240571975708</v>
+      </c>
+      <c r="AA443" t="n">
+        <v>12.11775493621826</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E444" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F444" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H444" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I444" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J444" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K444" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L444" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M444" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N444" s="2" t="n">
+        <v>45833.64895553317</v>
+      </c>
+      <c r="O444" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="P444" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q444" t="n">
+        <v>1.7914</v>
+      </c>
+      <c r="R444" t="n">
+        <v>0.4075025120017863</v>
+      </c>
+      <c r="S444" t="n">
+        <v>2674.72</v>
+      </c>
+      <c r="T444" t="n">
+        <v>1493.089203974545</v>
+      </c>
+      <c r="U444" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="V444" t="n">
+        <v>0.006896551724137945</v>
+      </c>
+      <c r="W444" t="n">
+        <v>-0.00256312727860708</v>
+      </c>
+      <c r="X444" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y444" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z444" t="n">
+        <v>0.5095238089561462</v>
+      </c>
+      <c r="AA444" t="n">
+        <v>11.94347476959229</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E445" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F445" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H445" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I445" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J445" t="n">
+        <v>537</v>
+      </c>
+      <c r="K445" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L445" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M445" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N445" s="2" t="n">
+        <v>45833.64895553317</v>
+      </c>
+      <c r="O445" t="n">
+        <v>24.95</v>
+      </c>
+      <c r="P445" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q445" t="n">
+        <v>9.12542</v>
+      </c>
+      <c r="R445" t="n">
+        <v>2.734120730881428</v>
+      </c>
+      <c r="S445" t="n">
+        <v>13398.15</v>
+      </c>
+      <c r="T445" t="n">
+        <v>1468.222832483327</v>
+      </c>
+      <c r="U445" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V445" t="n">
+        <v>-0.009920634920634885</v>
+      </c>
+      <c r="W445" t="n">
+        <v>-0.01912984792211181</v>
+      </c>
+      <c r="X445" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y445" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z445" t="n">
+        <v>0.5673728585243225</v>
+      </c>
+      <c r="AA445" t="n">
+        <v>11.78222894668579</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E446" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F446" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H446" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I446" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J446" t="n">
+        <v>121</v>
+      </c>
+      <c r="K446" t="n">
+        <v>12</v>
+      </c>
+      <c r="L446" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M446" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N446" s="2" t="n">
+        <v>45833.64895553317</v>
+      </c>
+      <c r="O446" t="n">
+        <v>13.995</v>
+      </c>
+      <c r="P446" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q446" t="n">
+        <v>1.162926</v>
+      </c>
+      <c r="R446" t="n">
+        <v>12.0342996888882</v>
+      </c>
+      <c r="S446" t="n">
+        <v>1693.395</v>
+      </c>
+      <c r="T446" t="n">
+        <v>1456.150262355472</v>
+      </c>
+      <c r="U446" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V446" t="n">
+        <v>-0.01304654442877295</v>
+      </c>
+      <c r="W446" t="n">
+        <v>-0.02371888049701742</v>
+      </c>
+      <c r="X446" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y446" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z446" t="n">
+        <v>0.5561246275901794</v>
+      </c>
+      <c r="AA446" t="n">
+        <v>14.51355290412903</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr"/>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E447" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F447" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H447" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I447" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J447" t="n">
+        <v>162</v>
+      </c>
+      <c r="K447" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L447" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M447" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N447" s="2" t="n">
+        <v>45833.64895553317</v>
+      </c>
+      <c r="O447" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="P447" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q447" t="n">
+        <v>4.24661</v>
+      </c>
+      <c r="R447" t="n">
+        <v>9.066055041550788</v>
+      </c>
+      <c r="S447" t="n">
+        <v>6237</v>
+      </c>
+      <c r="T447" t="n">
+        <v>1468.700916731228</v>
+      </c>
+      <c r="U447" t="n">
+        <v>8.272543736854324</v>
+      </c>
+      <c r="V447" t="n">
+        <v>-0.0178571428571429</v>
+      </c>
+      <c r="W447" t="n">
+        <v>-0.01367103070785569</v>
+      </c>
+      <c r="X447" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y447" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z447" t="n">
+        <v>0.6009591817855835</v>
+      </c>
+      <c r="AA447" t="n">
+        <v>12.92029732894897</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E448" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F448" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H448" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I448" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J448" t="n">
+        <v>101</v>
+      </c>
+      <c r="K448" t="n">
+        <v>11</v>
+      </c>
+      <c r="L448" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M448" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N448" s="2" t="n">
+        <v>45833.64895553317</v>
+      </c>
+      <c r="O448" t="n">
+        <v>24830</v>
+      </c>
+      <c r="P448" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q448" t="n">
+        <v>2067.21</v>
+      </c>
+      <c r="R448" t="n">
+        <v>12.01135830418777</v>
+      </c>
+      <c r="S448" t="n">
+        <v>2507830</v>
+      </c>
+      <c r="T448" t="n">
+        <v>1213.147188722965</v>
+      </c>
+      <c r="U448" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V448" t="n">
+        <v>0.01231245923026747</v>
+      </c>
+      <c r="W448" t="n">
+        <v>0.006960039698924891</v>
+      </c>
+      <c r="X448" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y448" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z448" t="n">
+        <v>0.4206280708312988</v>
+      </c>
+      <c r="AA448" t="n">
+        <v>10.58742851018906</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E449" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F449" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H449" t="n">
+        <v>1</v>
+      </c>
+      <c r="I449" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J449" t="n">
+        <v>30</v>
+      </c>
+      <c r="K449" t="n">
+        <v>9</v>
+      </c>
+      <c r="L449" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M449" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N449" s="2" t="n">
+        <v>45833.64895553317</v>
+      </c>
+      <c r="O449" t="n">
+        <v>46.14</v>
+      </c>
+      <c r="P449" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q449" t="n">
+        <v>1</v>
+      </c>
+      <c r="R449" t="n">
+        <v>46.14</v>
+      </c>
+      <c r="S449" t="n">
+        <v>1384.2</v>
+      </c>
+      <c r="T449" t="n">
+        <v>1384.2</v>
+      </c>
+      <c r="U449" t="n">
+        <v>41.688</v>
+      </c>
+      <c r="V449" t="n">
+        <v>0.01007005253940463</v>
+      </c>
+      <c r="W449" t="n">
+        <v>0.01007005253940463</v>
+      </c>
+      <c r="X449" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y449" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z449" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="AA449" t="n">
         <v>12.81225872039795</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA449"/>
+  <dimension ref="A1:AA457"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41896,7 +41896,7 @@
         <v>100</v>
       </c>
       <c r="N442" s="2" t="n">
-        <v>45833.64895553317</v>
+        <v>45833.64895553241</v>
       </c>
       <c r="O442" t="n">
         <v>1</v>
@@ -41987,7 +41987,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N443" s="2" t="n">
-        <v>45833.64895553317</v>
+        <v>45833.64895553241</v>
       </c>
       <c r="O443" t="n">
         <v>373.61</v>
@@ -42082,7 +42082,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N444" s="2" t="n">
-        <v>45833.64895553317</v>
+        <v>45833.64895553241</v>
       </c>
       <c r="O444" t="n">
         <v>0.73</v>
@@ -42177,7 +42177,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N445" s="2" t="n">
-        <v>45833.64895553317</v>
+        <v>45833.64895553241</v>
       </c>
       <c r="O445" t="n">
         <v>24.95</v>
@@ -42272,7 +42272,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N446" s="2" t="n">
-        <v>45833.64895553317</v>
+        <v>45833.64895553241</v>
       </c>
       <c r="O446" t="n">
         <v>13.995</v>
@@ -42363,7 +42363,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N447" s="2" t="n">
-        <v>45833.64895553317</v>
+        <v>45833.64895553241</v>
       </c>
       <c r="O447" t="n">
         <v>38.5</v>
@@ -42458,7 +42458,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N448" s="2" t="n">
-        <v>45833.64895553317</v>
+        <v>45833.64895553241</v>
       </c>
       <c r="O448" t="n">
         <v>24830</v>
@@ -42553,7 +42553,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N449" s="2" t="n">
-        <v>45833.64895553317</v>
+        <v>45833.64895553241</v>
       </c>
       <c r="O449" t="n">
         <v>46.14</v>
@@ -42594,6 +42594,760 @@
         <v>0.6434202790260315</v>
       </c>
       <c r="AA449" t="n">
+        <v>12.81225872039795</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F450" t="n">
+        <v>1</v>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H450" t="n">
+        <v>1</v>
+      </c>
+      <c r="I450" t="n">
+        <v>1</v>
+      </c>
+      <c r="J450" t="n">
+        <v>1</v>
+      </c>
+      <c r="K450" t="n">
+        <v>100</v>
+      </c>
+      <c r="L450" t="n">
+        <v>100</v>
+      </c>
+      <c r="M450" t="n">
+        <v>100</v>
+      </c>
+      <c r="N450" s="2" t="n">
+        <v>45833.69416259341</v>
+      </c>
+      <c r="O450" t="n">
+        <v>1</v>
+      </c>
+      <c r="P450" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q450" t="n">
+        <v>1</v>
+      </c>
+      <c r="R450" t="n">
+        <v>1</v>
+      </c>
+      <c r="S450" t="n">
+        <v>0</v>
+      </c>
+      <c r="T450" t="n">
+        <v>45.43580260334033</v>
+      </c>
+      <c r="U450" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V450" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W450" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X450" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y450" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z450" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA450" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr"/>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E451" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F451" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H451" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I451" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J451" t="n">
+        <v>3</v>
+      </c>
+      <c r="K451" t="n">
+        <v>10</v>
+      </c>
+      <c r="L451" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M451" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N451" s="2" t="n">
+        <v>45833.69416259341</v>
+      </c>
+      <c r="O451" t="n">
+        <v>373.61</v>
+      </c>
+      <c r="P451" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q451" t="n">
+        <v>0.85271</v>
+      </c>
+      <c r="R451" t="n">
+        <v>438.1442694468225</v>
+      </c>
+      <c r="S451" t="n">
+        <v>1120.83</v>
+      </c>
+      <c r="T451" t="n">
+        <v>1314.432808340467</v>
+      </c>
+      <c r="U451" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V451" t="n">
+        <v>0.01616684708403837</v>
+      </c>
+      <c r="W451" t="n">
+        <v>0.01731087046033353</v>
+      </c>
+      <c r="X451" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y451" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z451" t="n">
+        <v>0.5092240571975708</v>
+      </c>
+      <c r="AA451" t="n">
+        <v>12.11775493621826</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E452" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F452" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H452" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I452" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J452" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K452" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L452" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M452" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N452" s="2" t="n">
+        <v>45833.69416259341</v>
+      </c>
+      <c r="O452" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="P452" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q452" t="n">
+        <v>1.78894</v>
+      </c>
+      <c r="R452" t="n">
+        <v>0.4080628752221986</v>
+      </c>
+      <c r="S452" t="n">
+        <v>2674.72</v>
+      </c>
+      <c r="T452" t="n">
+        <v>1495.142374814136</v>
+      </c>
+      <c r="U452" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="V452" t="n">
+        <v>0.006896551724137945</v>
+      </c>
+      <c r="W452" t="n">
+        <v>-0.001191535885438522</v>
+      </c>
+      <c r="X452" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y452" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z452" t="n">
+        <v>0.5095238089561462</v>
+      </c>
+      <c r="AA452" t="n">
+        <v>11.94347476959229</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E453" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F453" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H453" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I453" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J453" t="n">
+        <v>537</v>
+      </c>
+      <c r="K453" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L453" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M453" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N453" s="2" t="n">
+        <v>45833.69416259341</v>
+      </c>
+      <c r="O453" t="n">
+        <v>24.95</v>
+      </c>
+      <c r="P453" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q453" t="n">
+        <v>9.13162</v>
+      </c>
+      <c r="R453" t="n">
+        <v>2.732264373681778</v>
+      </c>
+      <c r="S453" t="n">
+        <v>13398.15</v>
+      </c>
+      <c r="T453" t="n">
+        <v>1467.225968667115</v>
+      </c>
+      <c r="U453" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V453" t="n">
+        <v>-0.009920634920634885</v>
+      </c>
+      <c r="W453" t="n">
+        <v>-0.01979581901408478</v>
+      </c>
+      <c r="X453" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y453" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z453" t="n">
+        <v>0.5673728585243225</v>
+      </c>
+      <c r="AA453" t="n">
+        <v>11.78222894668579</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E454" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F454" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H454" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I454" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J454" t="n">
+        <v>121</v>
+      </c>
+      <c r="K454" t="n">
+        <v>12</v>
+      </c>
+      <c r="L454" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M454" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N454" s="2" t="n">
+        <v>45833.69416259341</v>
+      </c>
+      <c r="O454" t="n">
+        <v>14.125</v>
+      </c>
+      <c r="P454" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q454" t="n">
+        <v>1.1637379</v>
+      </c>
+      <c r="R454" t="n">
+        <v>12.13761277346041</v>
+      </c>
+      <c r="S454" t="n">
+        <v>1709.125</v>
+      </c>
+      <c r="T454" t="n">
+        <v>1468.65114558871</v>
+      </c>
+      <c r="U454" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V454" t="n">
+        <v>-0.003878702397743239</v>
+      </c>
+      <c r="W454" t="n">
+        <v>-0.01533761889700935</v>
+      </c>
+      <c r="X454" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y454" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z454" t="n">
+        <v>0.5561246275901794</v>
+      </c>
+      <c r="AA454" t="n">
+        <v>14.51355290412903</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr"/>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E455" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F455" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H455" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I455" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J455" t="n">
+        <v>162</v>
+      </c>
+      <c r="K455" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L455" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M455" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N455" s="2" t="n">
+        <v>45833.69416259341</v>
+      </c>
+      <c r="O455" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="P455" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q455" t="n">
+        <v>4.24814</v>
+      </c>
+      <c r="R455" t="n">
+        <v>9.062789832726793</v>
+      </c>
+      <c r="S455" t="n">
+        <v>6237</v>
+      </c>
+      <c r="T455" t="n">
+        <v>1468.17195290174</v>
+      </c>
+      <c r="U455" t="n">
+        <v>8.272543736854324</v>
+      </c>
+      <c r="V455" t="n">
+        <v>-0.0178571428571429</v>
+      </c>
+      <c r="W455" t="n">
+        <v>-0.01402626460387046</v>
+      </c>
+      <c r="X455" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y455" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z455" t="n">
+        <v>0.6009591817855835</v>
+      </c>
+      <c r="AA455" t="n">
+        <v>12.92029732894897</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E456" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F456" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H456" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I456" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J456" t="n">
+        <v>101</v>
+      </c>
+      <c r="K456" t="n">
+        <v>11</v>
+      </c>
+      <c r="L456" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M456" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N456" s="2" t="n">
+        <v>45833.69416259341</v>
+      </c>
+      <c r="O456" t="n">
+        <v>24830</v>
+      </c>
+      <c r="P456" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q456" t="n">
+        <v>2067.32</v>
+      </c>
+      <c r="R456" t="n">
+        <v>12.01071919199737</v>
+      </c>
+      <c r="S456" t="n">
+        <v>2507830</v>
+      </c>
+      <c r="T456" t="n">
+        <v>1213.082638391734</v>
+      </c>
+      <c r="U456" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V456" t="n">
+        <v>0.01231245923026747</v>
+      </c>
+      <c r="W456" t="n">
+        <v>0.006906460376726598</v>
+      </c>
+      <c r="X456" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y456" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z456" t="n">
+        <v>0.4206280708312988</v>
+      </c>
+      <c r="AA456" t="n">
+        <v>10.58742851018906</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E457" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F457" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H457" t="n">
+        <v>1</v>
+      </c>
+      <c r="I457" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J457" t="n">
+        <v>30</v>
+      </c>
+      <c r="K457" t="n">
+        <v>9</v>
+      </c>
+      <c r="L457" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M457" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N457" s="2" t="n">
+        <v>45833.69416259341</v>
+      </c>
+      <c r="O457" t="n">
+        <v>46.14</v>
+      </c>
+      <c r="P457" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q457" t="n">
+        <v>1</v>
+      </c>
+      <c r="R457" t="n">
+        <v>46.14</v>
+      </c>
+      <c r="S457" t="n">
+        <v>1384.2</v>
+      </c>
+      <c r="T457" t="n">
+        <v>1384.2</v>
+      </c>
+      <c r="U457" t="n">
+        <v>41.688</v>
+      </c>
+      <c r="V457" t="n">
+        <v>0.01007005253940463</v>
+      </c>
+      <c r="W457" t="n">
+        <v>0.01007005253940463</v>
+      </c>
+      <c r="X457" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y457" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z457" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="AA457" t="n">
         <v>12.81225872039795</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA457"/>
+  <dimension ref="A1:AA465"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42650,7 +42650,7 @@
         <v>100</v>
       </c>
       <c r="N450" s="2" t="n">
-        <v>45833.69416259341</v>
+        <v>45833.69416259259</v>
       </c>
       <c r="O450" t="n">
         <v>1</v>
@@ -42741,7 +42741,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N451" s="2" t="n">
-        <v>45833.69416259341</v>
+        <v>45833.69416259259</v>
       </c>
       <c r="O451" t="n">
         <v>373.61</v>
@@ -42836,7 +42836,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N452" s="2" t="n">
-        <v>45833.69416259341</v>
+        <v>45833.69416259259</v>
       </c>
       <c r="O452" t="n">
         <v>0.73</v>
@@ -42931,7 +42931,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N453" s="2" t="n">
-        <v>45833.69416259341</v>
+        <v>45833.69416259259</v>
       </c>
       <c r="O453" t="n">
         <v>24.95</v>
@@ -43026,7 +43026,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N454" s="2" t="n">
-        <v>45833.69416259341</v>
+        <v>45833.69416259259</v>
       </c>
       <c r="O454" t="n">
         <v>14.125</v>
@@ -43117,7 +43117,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N455" s="2" t="n">
-        <v>45833.69416259341</v>
+        <v>45833.69416259259</v>
       </c>
       <c r="O455" t="n">
         <v>38.5</v>
@@ -43212,7 +43212,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N456" s="2" t="n">
-        <v>45833.69416259341</v>
+        <v>45833.69416259259</v>
       </c>
       <c r="O456" t="n">
         <v>24830</v>
@@ -43307,7 +43307,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N457" s="2" t="n">
-        <v>45833.69416259341</v>
+        <v>45833.69416259259</v>
       </c>
       <c r="O457" t="n">
         <v>46.14</v>
@@ -43348,6 +43348,760 @@
         <v>0.6434202790260315</v>
       </c>
       <c r="AA457" t="n">
+        <v>12.81225872039795</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F458" t="n">
+        <v>1</v>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H458" t="n">
+        <v>1</v>
+      </c>
+      <c r="I458" t="n">
+        <v>1</v>
+      </c>
+      <c r="J458" t="n">
+        <v>1</v>
+      </c>
+      <c r="K458" t="n">
+        <v>100</v>
+      </c>
+      <c r="L458" t="n">
+        <v>100</v>
+      </c>
+      <c r="M458" t="n">
+        <v>100</v>
+      </c>
+      <c r="N458" s="2" t="n">
+        <v>45833.73103450242</v>
+      </c>
+      <c r="O458" t="n">
+        <v>1</v>
+      </c>
+      <c r="P458" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q458" t="n">
+        <v>1</v>
+      </c>
+      <c r="R458" t="n">
+        <v>1</v>
+      </c>
+      <c r="S458" t="n">
+        <v>0</v>
+      </c>
+      <c r="T458" t="n">
+        <v>45.43580260334033</v>
+      </c>
+      <c r="U458" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V458" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W458" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X458" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y458" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z458" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA458" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr"/>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E459" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F459" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H459" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I459" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J459" t="n">
+        <v>3</v>
+      </c>
+      <c r="K459" t="n">
+        <v>10</v>
+      </c>
+      <c r="L459" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M459" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N459" s="2" t="n">
+        <v>45833.73103450242</v>
+      </c>
+      <c r="O459" t="n">
+        <v>373.61</v>
+      </c>
+      <c r="P459" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q459" t="n">
+        <v>0.8529099999999999</v>
+      </c>
+      <c r="R459" t="n">
+        <v>438.0415284144869</v>
+      </c>
+      <c r="S459" t="n">
+        <v>1120.83</v>
+      </c>
+      <c r="T459" t="n">
+        <v>1314.124585243461</v>
+      </c>
+      <c r="U459" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V459" t="n">
+        <v>0.01616684708403837</v>
+      </c>
+      <c r="W459" t="n">
+        <v>0.01707231988161828</v>
+      </c>
+      <c r="X459" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y459" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z459" t="n">
+        <v>0.5092240571975708</v>
+      </c>
+      <c r="AA459" t="n">
+        <v>12.11775493621826</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E460" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F460" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H460" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I460" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J460" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K460" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L460" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M460" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N460" s="2" t="n">
+        <v>45833.73103450242</v>
+      </c>
+      <c r="O460" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="P460" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q460" t="n">
+        <v>1.78918</v>
+      </c>
+      <c r="R460" t="n">
+        <v>0.4080081378061458</v>
+      </c>
+      <c r="S460" t="n">
+        <v>2674.72</v>
+      </c>
+      <c r="T460" t="n">
+        <v>1494.941816921718</v>
+      </c>
+      <c r="U460" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="V460" t="n">
+        <v>0.006896551724137945</v>
+      </c>
+      <c r="W460" t="n">
+        <v>-0.001325515714962533</v>
+      </c>
+      <c r="X460" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y460" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z460" t="n">
+        <v>0.5095238089561462</v>
+      </c>
+      <c r="AA460" t="n">
+        <v>11.94347476959229</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E461" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F461" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H461" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I461" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J461" t="n">
+        <v>537</v>
+      </c>
+      <c r="K461" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L461" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M461" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N461" s="2" t="n">
+        <v>45833.73103450242</v>
+      </c>
+      <c r="O461" t="n">
+        <v>24.95</v>
+      </c>
+      <c r="P461" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q461" t="n">
+        <v>9.13377</v>
+      </c>
+      <c r="R461" t="n">
+        <v>2.731621225408566</v>
+      </c>
+      <c r="S461" t="n">
+        <v>13398.15</v>
+      </c>
+      <c r="T461" t="n">
+        <v>1466.8805980444</v>
+      </c>
+      <c r="U461" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V461" t="n">
+        <v>-0.009920634920634885</v>
+      </c>
+      <c r="W461" t="n">
+        <v>-0.02002654947797</v>
+      </c>
+      <c r="X461" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y461" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z461" t="n">
+        <v>0.5673728585243225</v>
+      </c>
+      <c r="AA461" t="n">
+        <v>11.78222894668579</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E462" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F462" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H462" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I462" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J462" t="n">
+        <v>121</v>
+      </c>
+      <c r="K462" t="n">
+        <v>12</v>
+      </c>
+      <c r="L462" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M462" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N462" s="2" t="n">
+        <v>45833.73103450242</v>
+      </c>
+      <c r="O462" t="n">
+        <v>14.07</v>
+      </c>
+      <c r="P462" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q462" t="n">
+        <v>1.1638733</v>
+      </c>
+      <c r="R462" t="n">
+        <v>12.08894473307361</v>
+      </c>
+      <c r="S462" t="n">
+        <v>1702.47</v>
+      </c>
+      <c r="T462" t="n">
+        <v>1462.762312701906</v>
+      </c>
+      <c r="U462" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V462" t="n">
+        <v>-0.007757404795486589</v>
+      </c>
+      <c r="W462" t="n">
+        <v>-0.01928580783871581</v>
+      </c>
+      <c r="X462" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y462" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z462" t="n">
+        <v>0.5561246275901794</v>
+      </c>
+      <c r="AA462" t="n">
+        <v>14.51355290412903</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr"/>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E463" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F463" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H463" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I463" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J463" t="n">
+        <v>162</v>
+      </c>
+      <c r="K463" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L463" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M463" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N463" s="2" t="n">
+        <v>45833.73103450242</v>
+      </c>
+      <c r="O463" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="P463" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q463" t="n">
+        <v>4.24819</v>
+      </c>
+      <c r="R463" t="n">
+        <v>9.062683166242564</v>
+      </c>
+      <c r="S463" t="n">
+        <v>6237</v>
+      </c>
+      <c r="T463" t="n">
+        <v>1468.154672931295</v>
+      </c>
+      <c r="U463" t="n">
+        <v>8.272543736854324</v>
+      </c>
+      <c r="V463" t="n">
+        <v>-0.0178571428571429</v>
+      </c>
+      <c r="W463" t="n">
+        <v>-0.01403786923708361</v>
+      </c>
+      <c r="X463" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y463" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z463" t="n">
+        <v>0.6009591817855835</v>
+      </c>
+      <c r="AA463" t="n">
+        <v>12.92029732894897</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E464" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F464" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H464" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I464" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J464" t="n">
+        <v>101</v>
+      </c>
+      <c r="K464" t="n">
+        <v>11</v>
+      </c>
+      <c r="L464" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M464" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N464" s="2" t="n">
+        <v>45833.73103450242</v>
+      </c>
+      <c r="O464" t="n">
+        <v>24830</v>
+      </c>
+      <c r="P464" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q464" t="n">
+        <v>2065.92</v>
+      </c>
+      <c r="R464" t="n">
+        <v>12.01885842627014</v>
+      </c>
+      <c r="S464" t="n">
+        <v>2507830</v>
+      </c>
+      <c r="T464" t="n">
+        <v>1213.904701053284</v>
+      </c>
+      <c r="U464" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V464" t="n">
+        <v>0.01231245923026747</v>
+      </c>
+      <c r="W464" t="n">
+        <v>0.00758880482594404</v>
+      </c>
+      <c r="X464" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y464" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z464" t="n">
+        <v>0.4206280708312988</v>
+      </c>
+      <c r="AA464" t="n">
+        <v>10.58742851018906</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E465" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F465" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H465" t="n">
+        <v>1</v>
+      </c>
+      <c r="I465" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J465" t="n">
+        <v>30</v>
+      </c>
+      <c r="K465" t="n">
+        <v>9</v>
+      </c>
+      <c r="L465" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M465" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N465" s="2" t="n">
+        <v>45833.73103450242</v>
+      </c>
+      <c r="O465" t="n">
+        <v>46.14</v>
+      </c>
+      <c r="P465" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q465" t="n">
+        <v>1</v>
+      </c>
+      <c r="R465" t="n">
+        <v>46.14</v>
+      </c>
+      <c r="S465" t="n">
+        <v>1384.2</v>
+      </c>
+      <c r="T465" t="n">
+        <v>1384.2</v>
+      </c>
+      <c r="U465" t="n">
+        <v>41.688</v>
+      </c>
+      <c r="V465" t="n">
+        <v>0.01007005253940463</v>
+      </c>
+      <c r="W465" t="n">
+        <v>0.01007005253940463</v>
+      </c>
+      <c r="X465" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y465" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z465" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="AA465" t="n">
         <v>12.81225872039795</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA465"/>
+  <dimension ref="A1:AA473"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43404,7 +43404,7 @@
         <v>100</v>
       </c>
       <c r="N458" s="2" t="n">
-        <v>45833.73103450242</v>
+        <v>45833.73103450231</v>
       </c>
       <c r="O458" t="n">
         <v>1</v>
@@ -43495,7 +43495,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N459" s="2" t="n">
-        <v>45833.73103450242</v>
+        <v>45833.73103450231</v>
       </c>
       <c r="O459" t="n">
         <v>373.61</v>
@@ -43590,7 +43590,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N460" s="2" t="n">
-        <v>45833.73103450242</v>
+        <v>45833.73103450231</v>
       </c>
       <c r="O460" t="n">
         <v>0.73</v>
@@ -43685,7 +43685,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N461" s="2" t="n">
-        <v>45833.73103450242</v>
+        <v>45833.73103450231</v>
       </c>
       <c r="O461" t="n">
         <v>24.95</v>
@@ -43780,7 +43780,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N462" s="2" t="n">
-        <v>45833.73103450242</v>
+        <v>45833.73103450231</v>
       </c>
       <c r="O462" t="n">
         <v>14.07</v>
@@ -43871,7 +43871,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N463" s="2" t="n">
-        <v>45833.73103450242</v>
+        <v>45833.73103450231</v>
       </c>
       <c r="O463" t="n">
         <v>38.5</v>
@@ -43966,7 +43966,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N464" s="2" t="n">
-        <v>45833.73103450242</v>
+        <v>45833.73103450231</v>
       </c>
       <c r="O464" t="n">
         <v>24830</v>
@@ -44061,7 +44061,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N465" s="2" t="n">
-        <v>45833.73103450242</v>
+        <v>45833.73103450231</v>
       </c>
       <c r="O465" t="n">
         <v>46.14</v>
@@ -44102,6 +44102,760 @@
         <v>0.6434202790260315</v>
       </c>
       <c r="AA465" t="n">
+        <v>12.81225872039795</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F466" t="n">
+        <v>1</v>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H466" t="n">
+        <v>1</v>
+      </c>
+      <c r="I466" t="n">
+        <v>1</v>
+      </c>
+      <c r="J466" t="n">
+        <v>1</v>
+      </c>
+      <c r="K466" t="n">
+        <v>100</v>
+      </c>
+      <c r="L466" t="n">
+        <v>100</v>
+      </c>
+      <c r="M466" t="n">
+        <v>100</v>
+      </c>
+      <c r="N466" s="2" t="n">
+        <v>45833.78023937554</v>
+      </c>
+      <c r="O466" t="n">
+        <v>1</v>
+      </c>
+      <c r="P466" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q466" t="n">
+        <v>1</v>
+      </c>
+      <c r="R466" t="n">
+        <v>1</v>
+      </c>
+      <c r="S466" t="n">
+        <v>0</v>
+      </c>
+      <c r="T466" t="n">
+        <v>45.43580260334033</v>
+      </c>
+      <c r="U466" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V466" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W466" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X466" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y466" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z466" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA466" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr"/>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E467" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F467" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H467" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I467" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J467" t="n">
+        <v>3</v>
+      </c>
+      <c r="K467" t="n">
+        <v>10</v>
+      </c>
+      <c r="L467" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M467" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N467" s="2" t="n">
+        <v>45833.78023937554</v>
+      </c>
+      <c r="O467" t="n">
+        <v>373.61</v>
+      </c>
+      <c r="P467" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q467" t="n">
+        <v>0.85356</v>
+      </c>
+      <c r="R467" t="n">
+        <v>437.7079525750972</v>
+      </c>
+      <c r="S467" t="n">
+        <v>1120.83</v>
+      </c>
+      <c r="T467" t="n">
+        <v>1313.123857725292</v>
+      </c>
+      <c r="U467" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V467" t="n">
+        <v>0.01616684708403837</v>
+      </c>
+      <c r="W467" t="n">
+        <v>0.01629780255662272</v>
+      </c>
+      <c r="X467" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y467" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z467" t="n">
+        <v>0.5092240571975708</v>
+      </c>
+      <c r="AA467" t="n">
+        <v>12.11775493621826</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E468" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F468" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H468" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I468" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J468" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K468" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L468" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M468" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N468" s="2" t="n">
+        <v>45833.78023937554</v>
+      </c>
+      <c r="O468" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="P468" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q468" t="n">
+        <v>1.79125</v>
+      </c>
+      <c r="R468" t="n">
+        <v>0.407536636427076</v>
+      </c>
+      <c r="S468" t="n">
+        <v>2674.72</v>
+      </c>
+      <c r="T468" t="n">
+        <v>1493.214235868807</v>
+      </c>
+      <c r="U468" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="V468" t="n">
+        <v>0.006896551724137945</v>
+      </c>
+      <c r="W468" t="n">
+        <v>-0.002479601511177432</v>
+      </c>
+      <c r="X468" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y468" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z468" t="n">
+        <v>0.5095238089561462</v>
+      </c>
+      <c r="AA468" t="n">
+        <v>11.94347476959229</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E469" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F469" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H469" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I469" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J469" t="n">
+        <v>537</v>
+      </c>
+      <c r="K469" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L469" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M469" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N469" s="2" t="n">
+        <v>45833.78023937554</v>
+      </c>
+      <c r="O469" t="n">
+        <v>24.95</v>
+      </c>
+      <c r="P469" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q469" t="n">
+        <v>9.151770000000001</v>
+      </c>
+      <c r="R469" t="n">
+        <v>2.726248583607324</v>
+      </c>
+      <c r="S469" t="n">
+        <v>13398.15</v>
+      </c>
+      <c r="T469" t="n">
+        <v>1463.995489397133</v>
+      </c>
+      <c r="U469" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V469" t="n">
+        <v>-0.009920634920634885</v>
+      </c>
+      <c r="W469" t="n">
+        <v>-0.02195399325216851</v>
+      </c>
+      <c r="X469" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y469" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z469" t="n">
+        <v>0.5673728585243225</v>
+      </c>
+      <c r="AA469" t="n">
+        <v>11.78222894668579</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E470" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F470" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H470" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I470" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J470" t="n">
+        <v>121</v>
+      </c>
+      <c r="K470" t="n">
+        <v>12</v>
+      </c>
+      <c r="L470" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M470" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N470" s="2" t="n">
+        <v>45833.78023937554</v>
+      </c>
+      <c r="O470" t="n">
+        <v>14.015</v>
+      </c>
+      <c r="P470" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q470" t="n">
+        <v>1.1659088</v>
+      </c>
+      <c r="R470" t="n">
+        <v>12.02066576733961</v>
+      </c>
+      <c r="S470" t="n">
+        <v>1695.815</v>
+      </c>
+      <c r="T470" t="n">
+        <v>1454.500557848093</v>
+      </c>
+      <c r="U470" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V470" t="n">
+        <v>-0.01163610719322983</v>
+      </c>
+      <c r="W470" t="n">
+        <v>-0.02482493074811476</v>
+      </c>
+      <c r="X470" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y470" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z470" t="n">
+        <v>0.5561246275901794</v>
+      </c>
+      <c r="AA470" t="n">
+        <v>14.51355290412903</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr"/>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E471" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F471" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H471" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I471" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J471" t="n">
+        <v>162</v>
+      </c>
+      <c r="K471" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L471" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M471" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N471" s="2" t="n">
+        <v>45833.78023937554</v>
+      </c>
+      <c r="O471" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="P471" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q471" t="n">
+        <v>4.24848</v>
+      </c>
+      <c r="R471" t="n">
+        <v>9.062064550144994</v>
+      </c>
+      <c r="S471" t="n">
+        <v>6237</v>
+      </c>
+      <c r="T471" t="n">
+        <v>1468.054457123489</v>
+      </c>
+      <c r="U471" t="n">
+        <v>8.272543736854324</v>
+      </c>
+      <c r="V471" t="n">
+        <v>-0.0178571428571429</v>
+      </c>
+      <c r="W471" t="n">
+        <v>-0.01410517072324347</v>
+      </c>
+      <c r="X471" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y471" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z471" t="n">
+        <v>0.6009591817855835</v>
+      </c>
+      <c r="AA471" t="n">
+        <v>12.92029732894897</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E472" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F472" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H472" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I472" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J472" t="n">
+        <v>101</v>
+      </c>
+      <c r="K472" t="n">
+        <v>11</v>
+      </c>
+      <c r="L472" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M472" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N472" s="2" t="n">
+        <v>45833.78023937554</v>
+      </c>
+      <c r="O472" t="n">
+        <v>24830</v>
+      </c>
+      <c r="P472" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q472" t="n">
+        <v>2068.92</v>
+      </c>
+      <c r="R472" t="n">
+        <v>12.00143069814203</v>
+      </c>
+      <c r="S472" t="n">
+        <v>2507830</v>
+      </c>
+      <c r="T472" t="n">
+        <v>1212.144500512345</v>
+      </c>
+      <c r="U472" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V472" t="n">
+        <v>0.01231245923026747</v>
+      </c>
+      <c r="W472" t="n">
+        <v>0.006127768916156517</v>
+      </c>
+      <c r="X472" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y472" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z472" t="n">
+        <v>0.4206280708312988</v>
+      </c>
+      <c r="AA472" t="n">
+        <v>10.58742851018906</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E473" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F473" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H473" t="n">
+        <v>1</v>
+      </c>
+      <c r="I473" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J473" t="n">
+        <v>30</v>
+      </c>
+      <c r="K473" t="n">
+        <v>9</v>
+      </c>
+      <c r="L473" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M473" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N473" s="2" t="n">
+        <v>45833.78023937554</v>
+      </c>
+      <c r="O473" t="n">
+        <v>46.14</v>
+      </c>
+      <c r="P473" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q473" t="n">
+        <v>1</v>
+      </c>
+      <c r="R473" t="n">
+        <v>46.14</v>
+      </c>
+      <c r="S473" t="n">
+        <v>1384.2</v>
+      </c>
+      <c r="T473" t="n">
+        <v>1384.2</v>
+      </c>
+      <c r="U473" t="n">
+        <v>41.688</v>
+      </c>
+      <c r="V473" t="n">
+        <v>0.01007005253940463</v>
+      </c>
+      <c r="W473" t="n">
+        <v>0.01007005253940463</v>
+      </c>
+      <c r="X473" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y473" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z473" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="AA473" t="n">
         <v>12.81225872039795</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA473"/>
+  <dimension ref="A1:AA481"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44158,7 +44158,7 @@
         <v>100</v>
       </c>
       <c r="N466" s="2" t="n">
-        <v>45833.78023937554</v>
+        <v>45833.780239375</v>
       </c>
       <c r="O466" t="n">
         <v>1</v>
@@ -44249,7 +44249,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N467" s="2" t="n">
-        <v>45833.78023937554</v>
+        <v>45833.780239375</v>
       </c>
       <c r="O467" t="n">
         <v>373.61</v>
@@ -44344,7 +44344,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N468" s="2" t="n">
-        <v>45833.78023937554</v>
+        <v>45833.780239375</v>
       </c>
       <c r="O468" t="n">
         <v>0.73</v>
@@ -44439,7 +44439,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N469" s="2" t="n">
-        <v>45833.78023937554</v>
+        <v>45833.780239375</v>
       </c>
       <c r="O469" t="n">
         <v>24.95</v>
@@ -44534,7 +44534,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N470" s="2" t="n">
-        <v>45833.78023937554</v>
+        <v>45833.780239375</v>
       </c>
       <c r="O470" t="n">
         <v>14.015</v>
@@ -44625,7 +44625,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N471" s="2" t="n">
-        <v>45833.78023937554</v>
+        <v>45833.780239375</v>
       </c>
       <c r="O471" t="n">
         <v>38.5</v>
@@ -44720,7 +44720,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N472" s="2" t="n">
-        <v>45833.78023937554</v>
+        <v>45833.780239375</v>
       </c>
       <c r="O472" t="n">
         <v>24830</v>
@@ -44815,7 +44815,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N473" s="2" t="n">
-        <v>45833.78023937554</v>
+        <v>45833.780239375</v>
       </c>
       <c r="O473" t="n">
         <v>46.14</v>
@@ -44856,6 +44856,760 @@
         <v>0.6434202790260315</v>
       </c>
       <c r="AA473" t="n">
+        <v>12.81225872039795</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F474" t="n">
+        <v>1</v>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H474" t="n">
+        <v>1</v>
+      </c>
+      <c r="I474" t="n">
+        <v>1</v>
+      </c>
+      <c r="J474" t="n">
+        <v>1</v>
+      </c>
+      <c r="K474" t="n">
+        <v>100</v>
+      </c>
+      <c r="L474" t="n">
+        <v>100</v>
+      </c>
+      <c r="M474" t="n">
+        <v>100</v>
+      </c>
+      <c r="N474" s="2" t="n">
+        <v>45833.80814553177</v>
+      </c>
+      <c r="O474" t="n">
+        <v>1</v>
+      </c>
+      <c r="P474" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q474" t="n">
+        <v>1</v>
+      </c>
+      <c r="R474" t="n">
+        <v>1</v>
+      </c>
+      <c r="S474" t="n">
+        <v>0</v>
+      </c>
+      <c r="T474" t="n">
+        <v>45.43580260334033</v>
+      </c>
+      <c r="U474" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V474" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W474" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X474" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y474" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z474" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA474" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr"/>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E475" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F475" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H475" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I475" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J475" t="n">
+        <v>3</v>
+      </c>
+      <c r="K475" t="n">
+        <v>10</v>
+      </c>
+      <c r="L475" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M475" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N475" s="2" t="n">
+        <v>45833.80814553177</v>
+      </c>
+      <c r="O475" t="n">
+        <v>373.61</v>
+      </c>
+      <c r="P475" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q475" t="n">
+        <v>0.8532999999999999</v>
+      </c>
+      <c r="R475" t="n">
+        <v>437.8413219266378</v>
+      </c>
+      <c r="S475" t="n">
+        <v>1120.83</v>
+      </c>
+      <c r="T475" t="n">
+        <v>1313.523965779913</v>
+      </c>
+      <c r="U475" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V475" t="n">
+        <v>0.01616684708403837</v>
+      </c>
+      <c r="W475" t="n">
+        <v>0.01660746788964151</v>
+      </c>
+      <c r="X475" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y475" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z475" t="n">
+        <v>0.5092240571975708</v>
+      </c>
+      <c r="AA475" t="n">
+        <v>12.11775493621826</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E476" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F476" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H476" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I476" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J476" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K476" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L476" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M476" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N476" s="2" t="n">
+        <v>45833.80814553177</v>
+      </c>
+      <c r="O476" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="P476" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q476" t="n">
+        <v>1.79056</v>
+      </c>
+      <c r="R476" t="n">
+        <v>0.4076936824233759</v>
+      </c>
+      <c r="S476" t="n">
+        <v>2674.72</v>
+      </c>
+      <c r="T476" t="n">
+        <v>1493.789652399249</v>
+      </c>
+      <c r="U476" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="V476" t="n">
+        <v>0.006896551724137945</v>
+      </c>
+      <c r="W476" t="n">
+        <v>-0.002095202733723767</v>
+      </c>
+      <c r="X476" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y476" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z476" t="n">
+        <v>0.5095238089561462</v>
+      </c>
+      <c r="AA476" t="n">
+        <v>11.94347476959229</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E477" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F477" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H477" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I477" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J477" t="n">
+        <v>537</v>
+      </c>
+      <c r="K477" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L477" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M477" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N477" s="2" t="n">
+        <v>45833.80814553177</v>
+      </c>
+      <c r="O477" t="n">
+        <v>24.95</v>
+      </c>
+      <c r="P477" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q477" t="n">
+        <v>9.15512</v>
+      </c>
+      <c r="R477" t="n">
+        <v>2.725251007086745</v>
+      </c>
+      <c r="S477" t="n">
+        <v>13398.15</v>
+      </c>
+      <c r="T477" t="n">
+        <v>1463.459790805582</v>
+      </c>
+      <c r="U477" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V477" t="n">
+        <v>-0.009920634920634885</v>
+      </c>
+      <c r="W477" t="n">
+        <v>-0.02231187541238111</v>
+      </c>
+      <c r="X477" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y477" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z477" t="n">
+        <v>0.5673728585243225</v>
+      </c>
+      <c r="AA477" t="n">
+        <v>11.78222894668579</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E478" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F478" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H478" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I478" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J478" t="n">
+        <v>121</v>
+      </c>
+      <c r="K478" t="n">
+        <v>12</v>
+      </c>
+      <c r="L478" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M478" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N478" s="2" t="n">
+        <v>45833.80814553177</v>
+      </c>
+      <c r="O478" t="n">
+        <v>14.005</v>
+      </c>
+      <c r="P478" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q478" t="n">
+        <v>1.166725</v>
+      </c>
+      <c r="R478" t="n">
+        <v>12.00368553000921</v>
+      </c>
+      <c r="S478" t="n">
+        <v>1694.605</v>
+      </c>
+      <c r="T478" t="n">
+        <v>1452.445949131115</v>
+      </c>
+      <c r="U478" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V478" t="n">
+        <v>-0.01234132581100134</v>
+      </c>
+      <c r="W478" t="n">
+        <v>-0.02620245046583047</v>
+      </c>
+      <c r="X478" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y478" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z478" t="n">
+        <v>0.5561246275901794</v>
+      </c>
+      <c r="AA478" t="n">
+        <v>14.51355290412903</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr"/>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E479" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F479" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H479" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I479" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J479" t="n">
+        <v>162</v>
+      </c>
+      <c r="K479" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L479" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M479" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N479" s="2" t="n">
+        <v>45833.80814553177</v>
+      </c>
+      <c r="O479" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="P479" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q479" t="n">
+        <v>4.2496</v>
+      </c>
+      <c r="R479" t="n">
+        <v>9.059676204819278</v>
+      </c>
+      <c r="S479" t="n">
+        <v>6237</v>
+      </c>
+      <c r="T479" t="n">
+        <v>1467.667545180723</v>
+      </c>
+      <c r="U479" t="n">
+        <v>8.272543736854324</v>
+      </c>
+      <c r="V479" t="n">
+        <v>-0.0178571428571429</v>
+      </c>
+      <c r="W479" t="n">
+        <v>-0.01436500746288727</v>
+      </c>
+      <c r="X479" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y479" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z479" t="n">
+        <v>0.6009591817855835</v>
+      </c>
+      <c r="AA479" t="n">
+        <v>12.92029732894897</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E480" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F480" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H480" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I480" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J480" t="n">
+        <v>101</v>
+      </c>
+      <c r="K480" t="n">
+        <v>11</v>
+      </c>
+      <c r="L480" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M480" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N480" s="2" t="n">
+        <v>45833.80814553177</v>
+      </c>
+      <c r="O480" t="n">
+        <v>24830</v>
+      </c>
+      <c r="P480" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q480" t="n">
+        <v>2068.35</v>
+      </c>
+      <c r="R480" t="n">
+        <v>12.00473807624435</v>
+      </c>
+      <c r="S480" t="n">
+        <v>2507830</v>
+      </c>
+      <c r="T480" t="n">
+        <v>1212.478545700679</v>
+      </c>
+      <c r="U480" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V480" t="n">
+        <v>0.01231245923026747</v>
+      </c>
+      <c r="W480" t="n">
+        <v>0.006405039604522544</v>
+      </c>
+      <c r="X480" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y480" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z480" t="n">
+        <v>0.4206280708312988</v>
+      </c>
+      <c r="AA480" t="n">
+        <v>10.58742851018906</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E481" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F481" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H481" t="n">
+        <v>1</v>
+      </c>
+      <c r="I481" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J481" t="n">
+        <v>30</v>
+      </c>
+      <c r="K481" t="n">
+        <v>9</v>
+      </c>
+      <c r="L481" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M481" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N481" s="2" t="n">
+        <v>45833.80814553177</v>
+      </c>
+      <c r="O481" t="n">
+        <v>46.14</v>
+      </c>
+      <c r="P481" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q481" t="n">
+        <v>1</v>
+      </c>
+      <c r="R481" t="n">
+        <v>46.14</v>
+      </c>
+      <c r="S481" t="n">
+        <v>1384.2</v>
+      </c>
+      <c r="T481" t="n">
+        <v>1384.2</v>
+      </c>
+      <c r="U481" t="n">
+        <v>41.688</v>
+      </c>
+      <c r="V481" t="n">
+        <v>0.01007005253940463</v>
+      </c>
+      <c r="W481" t="n">
+        <v>0.01007005253940463</v>
+      </c>
+      <c r="X481" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y481" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z481" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="AA481" t="n">
         <v>12.81225872039795</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA481"/>
+  <dimension ref="A1:AA489"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44912,7 +44912,7 @@
         <v>100</v>
       </c>
       <c r="N474" s="2" t="n">
-        <v>45833.80814553177</v>
+        <v>45833.80814553241</v>
       </c>
       <c r="O474" t="n">
         <v>1</v>
@@ -45003,7 +45003,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N475" s="2" t="n">
-        <v>45833.80814553177</v>
+        <v>45833.80814553241</v>
       </c>
       <c r="O475" t="n">
         <v>373.61</v>
@@ -45098,7 +45098,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N476" s="2" t="n">
-        <v>45833.80814553177</v>
+        <v>45833.80814553241</v>
       </c>
       <c r="O476" t="n">
         <v>0.73</v>
@@ -45193,7 +45193,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N477" s="2" t="n">
-        <v>45833.80814553177</v>
+        <v>45833.80814553241</v>
       </c>
       <c r="O477" t="n">
         <v>24.95</v>
@@ -45288,7 +45288,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N478" s="2" t="n">
-        <v>45833.80814553177</v>
+        <v>45833.80814553241</v>
       </c>
       <c r="O478" t="n">
         <v>14.005</v>
@@ -45379,7 +45379,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N479" s="2" t="n">
-        <v>45833.80814553177</v>
+        <v>45833.80814553241</v>
       </c>
       <c r="O479" t="n">
         <v>38.5</v>
@@ -45474,7 +45474,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N480" s="2" t="n">
-        <v>45833.80814553177</v>
+        <v>45833.80814553241</v>
       </c>
       <c r="O480" t="n">
         <v>24830</v>
@@ -45569,7 +45569,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N481" s="2" t="n">
-        <v>45833.80814553177</v>
+        <v>45833.80814553241</v>
       </c>
       <c r="O481" t="n">
         <v>46.14</v>
@@ -45610,6 +45610,760 @@
         <v>0.6434202790260315</v>
       </c>
       <c r="AA481" t="n">
+        <v>12.81225872039795</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F482" t="n">
+        <v>1</v>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H482" t="n">
+        <v>1</v>
+      </c>
+      <c r="I482" t="n">
+        <v>1</v>
+      </c>
+      <c r="J482" t="n">
+        <v>1</v>
+      </c>
+      <c r="K482" t="n">
+        <v>100</v>
+      </c>
+      <c r="L482" t="n">
+        <v>100</v>
+      </c>
+      <c r="M482" t="n">
+        <v>100</v>
+      </c>
+      <c r="N482" s="2" t="n">
+        <v>45833.85652001644</v>
+      </c>
+      <c r="O482" t="n">
+        <v>1</v>
+      </c>
+      <c r="P482" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q482" t="n">
+        <v>1</v>
+      </c>
+      <c r="R482" t="n">
+        <v>1</v>
+      </c>
+      <c r="S482" t="n">
+        <v>0</v>
+      </c>
+      <c r="T482" t="n">
+        <v>45.43580260334033</v>
+      </c>
+      <c r="U482" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V482" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W482" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X482" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y482" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z482" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA482" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr"/>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E483" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F483" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H483" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I483" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J483" t="n">
+        <v>3</v>
+      </c>
+      <c r="K483" t="n">
+        <v>10</v>
+      </c>
+      <c r="L483" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M483" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N483" s="2" t="n">
+        <v>45833.85652001644</v>
+      </c>
+      <c r="O483" t="n">
+        <v>373.61</v>
+      </c>
+      <c r="P483" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q483" t="n">
+        <v>0.85282</v>
+      </c>
+      <c r="R483" t="n">
+        <v>438.087755915668</v>
+      </c>
+      <c r="S483" t="n">
+        <v>1120.83</v>
+      </c>
+      <c r="T483" t="n">
+        <v>1314.263267747004</v>
+      </c>
+      <c r="U483" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V483" t="n">
+        <v>0.01616684708403837</v>
+      </c>
+      <c r="W483" t="n">
+        <v>0.01717965379591346</v>
+      </c>
+      <c r="X483" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y483" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z483" t="n">
+        <v>0.5092240571975708</v>
+      </c>
+      <c r="AA483" t="n">
+        <v>12.11775493621826</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E484" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F484" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H484" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I484" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J484" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K484" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L484" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M484" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N484" s="2" t="n">
+        <v>45833.85652001644</v>
+      </c>
+      <c r="O484" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="P484" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q484" t="n">
+        <v>1.79012</v>
+      </c>
+      <c r="R484" t="n">
+        <v>0.4077938909123411</v>
+      </c>
+      <c r="S484" t="n">
+        <v>2674.72</v>
+      </c>
+      <c r="T484" t="n">
+        <v>1494.156816302818</v>
+      </c>
+      <c r="U484" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="V484" t="n">
+        <v>0.006896551724137945</v>
+      </c>
+      <c r="W484" t="n">
+        <v>-0.001849924143016435</v>
+      </c>
+      <c r="X484" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y484" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z484" t="n">
+        <v>0.5095238089561462</v>
+      </c>
+      <c r="AA484" t="n">
+        <v>11.94347476959229</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E485" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F485" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H485" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I485" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J485" t="n">
+        <v>537</v>
+      </c>
+      <c r="K485" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L485" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M485" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N485" s="2" t="n">
+        <v>45833.85652001644</v>
+      </c>
+      <c r="O485" t="n">
+        <v>24.95</v>
+      </c>
+      <c r="P485" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q485" t="n">
+        <v>9.1454</v>
+      </c>
+      <c r="R485" t="n">
+        <v>2.728147483981017</v>
+      </c>
+      <c r="S485" t="n">
+        <v>13398.15</v>
+      </c>
+      <c r="T485" t="n">
+        <v>1465.015198897806</v>
+      </c>
+      <c r="U485" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V485" t="n">
+        <v>-0.009920634920634885</v>
+      </c>
+      <c r="W485" t="n">
+        <v>-0.02127275972897835</v>
+      </c>
+      <c r="X485" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y485" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z485" t="n">
+        <v>0.5673728585243225</v>
+      </c>
+      <c r="AA485" t="n">
+        <v>11.78222894668579</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E486" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F486" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H486" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I486" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J486" t="n">
+        <v>121</v>
+      </c>
+      <c r="K486" t="n">
+        <v>12</v>
+      </c>
+      <c r="L486" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M486" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N486" s="2" t="n">
+        <v>45833.85652001644</v>
+      </c>
+      <c r="O486" t="n">
+        <v>14.02</v>
+      </c>
+      <c r="P486" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q486" t="n">
+        <v>1.165637</v>
+      </c>
+      <c r="R486" t="n">
+        <v>12.02775821289132</v>
+      </c>
+      <c r="S486" t="n">
+        <v>1696.42</v>
+      </c>
+      <c r="T486" t="n">
+        <v>1455.35874375985</v>
+      </c>
+      <c r="U486" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V486" t="n">
+        <v>-0.01128349788434413</v>
+      </c>
+      <c r="W486" t="n">
+        <v>-0.02424955695302544</v>
+      </c>
+      <c r="X486" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y486" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z486" t="n">
+        <v>0.5561246275901794</v>
+      </c>
+      <c r="AA486" t="n">
+        <v>14.51355290412903</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr"/>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E487" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F487" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H487" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I487" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J487" t="n">
+        <v>162</v>
+      </c>
+      <c r="K487" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L487" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M487" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N487" s="2" t="n">
+        <v>45833.85652001644</v>
+      </c>
+      <c r="O487" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="P487" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q487" t="n">
+        <v>4.24986</v>
+      </c>
+      <c r="R487" t="n">
+        <v>9.059121947546508</v>
+      </c>
+      <c r="S487" t="n">
+        <v>6237</v>
+      </c>
+      <c r="T487" t="n">
+        <v>1467.577755502534</v>
+      </c>
+      <c r="U487" t="n">
+        <v>8.272543736854324</v>
+      </c>
+      <c r="V487" t="n">
+        <v>-0.0178571428571429</v>
+      </c>
+      <c r="W487" t="n">
+        <v>-0.01442530711936052</v>
+      </c>
+      <c r="X487" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y487" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z487" t="n">
+        <v>0.6009591817855835</v>
+      </c>
+      <c r="AA487" t="n">
+        <v>12.92029732894897</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E488" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F488" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H488" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I488" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J488" t="n">
+        <v>101</v>
+      </c>
+      <c r="K488" t="n">
+        <v>11</v>
+      </c>
+      <c r="L488" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M488" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N488" s="2" t="n">
+        <v>45833.85652001644</v>
+      </c>
+      <c r="O488" t="n">
+        <v>24830</v>
+      </c>
+      <c r="P488" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q488" t="n">
+        <v>2069.28</v>
+      </c>
+      <c r="R488" t="n">
+        <v>11.99934276656615</v>
+      </c>
+      <c r="S488" t="n">
+        <v>2507830</v>
+      </c>
+      <c r="T488" t="n">
+        <v>1211.933619423181</v>
+      </c>
+      <c r="U488" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V488" t="n">
+        <v>0.01231245923026747</v>
+      </c>
+      <c r="W488" t="n">
+        <v>0.005952729290388037</v>
+      </c>
+      <c r="X488" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y488" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z488" t="n">
+        <v>0.4206280708312988</v>
+      </c>
+      <c r="AA488" t="n">
+        <v>10.58742851018906</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E489" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F489" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H489" t="n">
+        <v>1</v>
+      </c>
+      <c r="I489" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J489" t="n">
+        <v>30</v>
+      </c>
+      <c r="K489" t="n">
+        <v>9</v>
+      </c>
+      <c r="L489" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M489" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N489" s="2" t="n">
+        <v>45833.85652001644</v>
+      </c>
+      <c r="O489" t="n">
+        <v>46.14</v>
+      </c>
+      <c r="P489" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q489" t="n">
+        <v>1</v>
+      </c>
+      <c r="R489" t="n">
+        <v>46.14</v>
+      </c>
+      <c r="S489" t="n">
+        <v>1384.2</v>
+      </c>
+      <c r="T489" t="n">
+        <v>1384.2</v>
+      </c>
+      <c r="U489" t="n">
+        <v>41.688</v>
+      </c>
+      <c r="V489" t="n">
+        <v>0.01007005253940463</v>
+      </c>
+      <c r="W489" t="n">
+        <v>0.01007005253940463</v>
+      </c>
+      <c r="X489" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y489" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z489" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="AA489" t="n">
         <v>12.81225872039795</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA489"/>
+  <dimension ref="A1:AA497"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45666,7 +45666,7 @@
         <v>100</v>
       </c>
       <c r="N482" s="2" t="n">
-        <v>45833.85652001644</v>
+        <v>45833.85652001158</v>
       </c>
       <c r="O482" t="n">
         <v>1</v>
@@ -45757,7 +45757,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N483" s="2" t="n">
-        <v>45833.85652001644</v>
+        <v>45833.85652001158</v>
       </c>
       <c r="O483" t="n">
         <v>373.61</v>
@@ -45852,7 +45852,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N484" s="2" t="n">
-        <v>45833.85652001644</v>
+        <v>45833.85652001158</v>
       </c>
       <c r="O484" t="n">
         <v>0.73</v>
@@ -45947,7 +45947,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N485" s="2" t="n">
-        <v>45833.85652001644</v>
+        <v>45833.85652001158</v>
       </c>
       <c r="O485" t="n">
         <v>24.95</v>
@@ -46042,7 +46042,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N486" s="2" t="n">
-        <v>45833.85652001644</v>
+        <v>45833.85652001158</v>
       </c>
       <c r="O486" t="n">
         <v>14.02</v>
@@ -46133,7 +46133,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N487" s="2" t="n">
-        <v>45833.85652001644</v>
+        <v>45833.85652001158</v>
       </c>
       <c r="O487" t="n">
         <v>38.5</v>
@@ -46228,7 +46228,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N488" s="2" t="n">
-        <v>45833.85652001644</v>
+        <v>45833.85652001158</v>
       </c>
       <c r="O488" t="n">
         <v>24830</v>
@@ -46323,7 +46323,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N489" s="2" t="n">
-        <v>45833.85652001644</v>
+        <v>45833.85652001158</v>
       </c>
       <c r="O489" t="n">
         <v>46.14</v>
@@ -46364,6 +46364,760 @@
         <v>0.6434202790260315</v>
       </c>
       <c r="AA489" t="n">
+        <v>12.81225872039795</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F490" t="n">
+        <v>1</v>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H490" t="n">
+        <v>1</v>
+      </c>
+      <c r="I490" t="n">
+        <v>1</v>
+      </c>
+      <c r="J490" t="n">
+        <v>1</v>
+      </c>
+      <c r="K490" t="n">
+        <v>100</v>
+      </c>
+      <c r="L490" t="n">
+        <v>100</v>
+      </c>
+      <c r="M490" t="n">
+        <v>100</v>
+      </c>
+      <c r="N490" s="2" t="n">
+        <v>45833.89522239442</v>
+      </c>
+      <c r="O490" t="n">
+        <v>1</v>
+      </c>
+      <c r="P490" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q490" t="n">
+        <v>1</v>
+      </c>
+      <c r="R490" t="n">
+        <v>1</v>
+      </c>
+      <c r="S490" t="n">
+        <v>0</v>
+      </c>
+      <c r="T490" t="n">
+        <v>45.43580260334033</v>
+      </c>
+      <c r="U490" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V490" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W490" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X490" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y490" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z490" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA490" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr"/>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E491" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F491" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H491" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I491" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J491" t="n">
+        <v>3</v>
+      </c>
+      <c r="K491" t="n">
+        <v>10</v>
+      </c>
+      <c r="L491" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M491" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N491" s="2" t="n">
+        <v>45833.89522239442</v>
+      </c>
+      <c r="O491" t="n">
+        <v>373.61</v>
+      </c>
+      <c r="P491" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q491" t="n">
+        <v>0.85314</v>
+      </c>
+      <c r="R491" t="n">
+        <v>437.9234357784185</v>
+      </c>
+      <c r="S491" t="n">
+        <v>1120.83</v>
+      </c>
+      <c r="T491" t="n">
+        <v>1313.770307335255</v>
+      </c>
+      <c r="U491" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V491" t="n">
+        <v>0.01616684708403837</v>
+      </c>
+      <c r="W491" t="n">
+        <v>0.01679812498561883</v>
+      </c>
+      <c r="X491" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y491" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z491" t="n">
+        <v>0.5092240571975708</v>
+      </c>
+      <c r="AA491" t="n">
+        <v>12.11775493621826</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E492" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F492" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H492" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I492" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J492" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K492" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L492" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M492" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N492" s="2" t="n">
+        <v>45833.89522239442</v>
+      </c>
+      <c r="O492" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="P492" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q492" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="R492" t="n">
+        <v>0.4078212290502793</v>
+      </c>
+      <c r="S492" t="n">
+        <v>2674.72</v>
+      </c>
+      <c r="T492" t="n">
+        <v>1494.256983240223</v>
+      </c>
+      <c r="U492" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="V492" t="n">
+        <v>0.006896551724137945</v>
+      </c>
+      <c r="W492" t="n">
+        <v>-0.001783009054132201</v>
+      </c>
+      <c r="X492" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y492" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z492" t="n">
+        <v>0.5095238089561462</v>
+      </c>
+      <c r="AA492" t="n">
+        <v>11.94347476959229</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E493" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F493" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H493" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I493" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J493" t="n">
+        <v>537</v>
+      </c>
+      <c r="K493" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L493" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M493" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N493" s="2" t="n">
+        <v>45833.89522239442</v>
+      </c>
+      <c r="O493" t="n">
+        <v>24.95</v>
+      </c>
+      <c r="P493" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q493" t="n">
+        <v>9.1469</v>
+      </c>
+      <c r="R493" t="n">
+        <v>2.727700095114192</v>
+      </c>
+      <c r="S493" t="n">
+        <v>13398.15</v>
+      </c>
+      <c r="T493" t="n">
+        <v>1464.774951076321</v>
+      </c>
+      <c r="U493" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V493" t="n">
+        <v>-0.009920634920634885</v>
+      </c>
+      <c r="W493" t="n">
+        <v>-0.02143326119509315</v>
+      </c>
+      <c r="X493" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y493" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z493" t="n">
+        <v>0.5673728585243225</v>
+      </c>
+      <c r="AA493" t="n">
+        <v>11.78222894668579</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E494" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F494" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H494" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I494" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J494" t="n">
+        <v>121</v>
+      </c>
+      <c r="K494" t="n">
+        <v>12</v>
+      </c>
+      <c r="L494" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M494" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N494" s="2" t="n">
+        <v>45833.89522239442</v>
+      </c>
+      <c r="O494" t="n">
+        <v>14.02</v>
+      </c>
+      <c r="P494" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q494" t="n">
+        <v>1.1655012</v>
+      </c>
+      <c r="R494" t="n">
+        <v>12.02915964393687</v>
+      </c>
+      <c r="S494" t="n">
+        <v>1696.42</v>
+      </c>
+      <c r="T494" t="n">
+        <v>1455.528316916362</v>
+      </c>
+      <c r="U494" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V494" t="n">
+        <v>-0.01128349788434413</v>
+      </c>
+      <c r="W494" t="n">
+        <v>-0.02413586602746842</v>
+      </c>
+      <c r="X494" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y494" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z494" t="n">
+        <v>0.5561246275901794</v>
+      </c>
+      <c r="AA494" t="n">
+        <v>14.51355290412903</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr"/>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E495" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F495" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H495" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I495" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J495" t="n">
+        <v>162</v>
+      </c>
+      <c r="K495" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L495" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M495" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N495" s="2" t="n">
+        <v>45833.89522239442</v>
+      </c>
+      <c r="O495" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="P495" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q495" t="n">
+        <v>4.24695</v>
+      </c>
+      <c r="R495" t="n">
+        <v>9.065329236275444</v>
+      </c>
+      <c r="S495" t="n">
+        <v>6237</v>
+      </c>
+      <c r="T495" t="n">
+        <v>1468.583336276622</v>
+      </c>
+      <c r="U495" t="n">
+        <v>8.272543736854324</v>
+      </c>
+      <c r="V495" t="n">
+        <v>-0.0178571428571429</v>
+      </c>
+      <c r="W495" t="n">
+        <v>-0.01374999369295293</v>
+      </c>
+      <c r="X495" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y495" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z495" t="n">
+        <v>0.6009591817855835</v>
+      </c>
+      <c r="AA495" t="n">
+        <v>12.92029732894897</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E496" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F496" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H496" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I496" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J496" t="n">
+        <v>101</v>
+      </c>
+      <c r="K496" t="n">
+        <v>11</v>
+      </c>
+      <c r="L496" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M496" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N496" s="2" t="n">
+        <v>45833.89522239442</v>
+      </c>
+      <c r="O496" t="n">
+        <v>24830</v>
+      </c>
+      <c r="P496" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q496" t="n">
+        <v>2070.58</v>
+      </c>
+      <c r="R496" t="n">
+        <v>11.99180905833148</v>
+      </c>
+      <c r="S496" t="n">
+        <v>2507830</v>
+      </c>
+      <c r="T496" t="n">
+        <v>1211.17271489148</v>
+      </c>
+      <c r="U496" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V496" t="n">
+        <v>0.01231245923026747</v>
+      </c>
+      <c r="W496" t="n">
+        <v>0.005321148502358986</v>
+      </c>
+      <c r="X496" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y496" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z496" t="n">
+        <v>0.4206280708312988</v>
+      </c>
+      <c r="AA496" t="n">
+        <v>10.58742851018906</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E497" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F497" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H497" t="n">
+        <v>1</v>
+      </c>
+      <c r="I497" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J497" t="n">
+        <v>30</v>
+      </c>
+      <c r="K497" t="n">
+        <v>9</v>
+      </c>
+      <c r="L497" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M497" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N497" s="2" t="n">
+        <v>45833.89522239442</v>
+      </c>
+      <c r="O497" t="n">
+        <v>46.14</v>
+      </c>
+      <c r="P497" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q497" t="n">
+        <v>1</v>
+      </c>
+      <c r="R497" t="n">
+        <v>46.14</v>
+      </c>
+      <c r="S497" t="n">
+        <v>1384.2</v>
+      </c>
+      <c r="T497" t="n">
+        <v>1384.2</v>
+      </c>
+      <c r="U497" t="n">
+        <v>41.688</v>
+      </c>
+      <c r="V497" t="n">
+        <v>0.01007005253940463</v>
+      </c>
+      <c r="W497" t="n">
+        <v>0.01007005253940463</v>
+      </c>
+      <c r="X497" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y497" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z497" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="AA497" t="n">
         <v>12.81225872039795</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA497"/>
+  <dimension ref="A1:AA505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46420,7 +46420,7 @@
         <v>100</v>
       </c>
       <c r="N490" s="2" t="n">
-        <v>45833.89522239442</v>
+        <v>45833.89522239583</v>
       </c>
       <c r="O490" t="n">
         <v>1</v>
@@ -46511,7 +46511,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N491" s="2" t="n">
-        <v>45833.89522239442</v>
+        <v>45833.89522239583</v>
       </c>
       <c r="O491" t="n">
         <v>373.61</v>
@@ -46606,7 +46606,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N492" s="2" t="n">
-        <v>45833.89522239442</v>
+        <v>45833.89522239583</v>
       </c>
       <c r="O492" t="n">
         <v>0.73</v>
@@ -46701,7 +46701,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N493" s="2" t="n">
-        <v>45833.89522239442</v>
+        <v>45833.89522239583</v>
       </c>
       <c r="O493" t="n">
         <v>24.95</v>
@@ -46796,7 +46796,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N494" s="2" t="n">
-        <v>45833.89522239442</v>
+        <v>45833.89522239583</v>
       </c>
       <c r="O494" t="n">
         <v>14.02</v>
@@ -46887,7 +46887,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N495" s="2" t="n">
-        <v>45833.89522239442</v>
+        <v>45833.89522239583</v>
       </c>
       <c r="O495" t="n">
         <v>38.5</v>
@@ -46982,7 +46982,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N496" s="2" t="n">
-        <v>45833.89522239442</v>
+        <v>45833.89522239583</v>
       </c>
       <c r="O496" t="n">
         <v>24830</v>
@@ -47077,7 +47077,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N497" s="2" t="n">
-        <v>45833.89522239442</v>
+        <v>45833.89522239583</v>
       </c>
       <c r="O497" t="n">
         <v>46.14</v>
@@ -47119,6 +47119,760 @@
       </c>
       <c r="AA497" t="n">
         <v>12.81225872039795</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F498" t="n">
+        <v>1</v>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H498" t="n">
+        <v>1</v>
+      </c>
+      <c r="I498" t="n">
+        <v>1</v>
+      </c>
+      <c r="J498" t="n">
+        <v>1</v>
+      </c>
+      <c r="K498" t="n">
+        <v>100</v>
+      </c>
+      <c r="L498" t="n">
+        <v>100</v>
+      </c>
+      <c r="M498" t="n">
+        <v>100</v>
+      </c>
+      <c r="N498" s="2" t="n">
+        <v>45834.31292980131</v>
+      </c>
+      <c r="O498" t="n">
+        <v>1</v>
+      </c>
+      <c r="P498" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q498" t="n">
+        <v>1</v>
+      </c>
+      <c r="R498" t="n">
+        <v>1</v>
+      </c>
+      <c r="S498" t="n">
+        <v>0</v>
+      </c>
+      <c r="T498" t="n">
+        <v>45.43580260334033</v>
+      </c>
+      <c r="U498" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V498" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W498" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X498" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y498" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z498" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA498" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr"/>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E499" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F499" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H499" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I499" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J499" t="n">
+        <v>3</v>
+      </c>
+      <c r="K499" t="n">
+        <v>10</v>
+      </c>
+      <c r="L499" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M499" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N499" s="2" t="n">
+        <v>45834.31292980131</v>
+      </c>
+      <c r="O499" t="n">
+        <v>375</v>
+      </c>
+      <c r="P499" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q499" t="n">
+        <v>0.85241</v>
+      </c>
+      <c r="R499" t="n">
+        <v>439.9291420795157</v>
+      </c>
+      <c r="S499" t="n">
+        <v>1125</v>
+      </c>
+      <c r="T499" t="n">
+        <v>1319.787426238547</v>
+      </c>
+      <c r="U499" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V499" t="n">
+        <v>0.01994745230725714</v>
+      </c>
+      <c r="W499" t="n">
+        <v>0.02145509978899374</v>
+      </c>
+      <c r="X499" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y499" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z499" t="n">
+        <v>0.5015593767166138</v>
+      </c>
+      <c r="AA499" t="n">
+        <v>12.0281548500061</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E500" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F500" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H500" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I500" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J500" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K500" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L500" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M500" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N500" s="2" t="n">
+        <v>45834.31292980131</v>
+      </c>
+      <c r="O500" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="P500" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q500" t="n">
+        <v>1.79099</v>
+      </c>
+      <c r="R500" t="n">
+        <v>0.4048040469237684</v>
+      </c>
+      <c r="S500" t="n">
+        <v>2656.4</v>
+      </c>
+      <c r="T500" t="n">
+        <v>1483.202027928687</v>
+      </c>
+      <c r="U500" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="V500" t="n">
+        <v>0</v>
+      </c>
+      <c r="W500" t="n">
+        <v>-0.009168113724811522</v>
+      </c>
+      <c r="X500" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y500" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z500" t="n">
+        <v>0.4815215170383453</v>
+      </c>
+      <c r="AA500" t="n">
+        <v>11.57751679420471</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E501" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F501" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H501" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I501" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J501" t="n">
+        <v>537</v>
+      </c>
+      <c r="K501" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L501" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M501" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N501" s="2" t="n">
+        <v>45834.31292980131</v>
+      </c>
+      <c r="O501" t="n">
+        <v>25</v>
+      </c>
+      <c r="P501" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q501" t="n">
+        <v>9.1859</v>
+      </c>
+      <c r="R501" t="n">
+        <v>2.721562394539457</v>
+      </c>
+      <c r="S501" t="n">
+        <v>13425</v>
+      </c>
+      <c r="T501" t="n">
+        <v>1461.479005867689</v>
+      </c>
+      <c r="U501" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V501" t="n">
+        <v>-0.007936507936507908</v>
+      </c>
+      <c r="W501" t="n">
+        <v>-0.02363517101866097</v>
+      </c>
+      <c r="X501" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y501" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z501" t="n">
+        <v>0.4985511600971222</v>
+      </c>
+      <c r="AA501" t="n">
+        <v>9.835646152496338</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E502" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F502" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H502" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I502" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J502" t="n">
+        <v>121</v>
+      </c>
+      <c r="K502" t="n">
+        <v>12</v>
+      </c>
+      <c r="L502" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M502" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N502" s="2" t="n">
+        <v>45834.31292980131</v>
+      </c>
+      <c r="O502" t="n">
+        <v>14.02</v>
+      </c>
+      <c r="P502" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q502" t="n">
+        <v>1.1705489</v>
+      </c>
+      <c r="R502" t="n">
+        <v>11.97728689506265</v>
+      </c>
+      <c r="S502" t="n">
+        <v>1696.42</v>
+      </c>
+      <c r="T502" t="n">
+        <v>1449.25171430258</v>
+      </c>
+      <c r="U502" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V502" t="n">
+        <v>-0.01128349788434413</v>
+      </c>
+      <c r="W502" t="n">
+        <v>-0.02834403656101303</v>
+      </c>
+      <c r="X502" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y502" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z502" t="n">
+        <v>0.5161105990409851</v>
+      </c>
+      <c r="AA502" t="n">
+        <v>13.94983839988708</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr"/>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E503" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F503" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H503" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I503" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J503" t="n">
+        <v>162</v>
+      </c>
+      <c r="K503" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L503" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M503" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N503" s="2" t="n">
+        <v>45834.31292980131</v>
+      </c>
+      <c r="O503" t="n">
+        <v>38.45</v>
+      </c>
+      <c r="P503" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q503" t="n">
+        <v>4.24938</v>
+      </c>
+      <c r="R503" t="n">
+        <v>9.048378822322315</v>
+      </c>
+      <c r="S503" t="n">
+        <v>6228.900000000001</v>
+      </c>
+      <c r="T503" t="n">
+        <v>1465.837369216215</v>
+      </c>
+      <c r="U503" t="n">
+        <v>8.272543736854324</v>
+      </c>
+      <c r="V503" t="n">
+        <v>-0.01913265306122447</v>
+      </c>
+      <c r="W503" t="n">
+        <v>-0.01559409062892358</v>
+      </c>
+      <c r="X503" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y503" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z503" t="n">
+        <v>0.5935001373291016</v>
+      </c>
+      <c r="AA503" t="n">
+        <v>12.80392378997803</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E504" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F504" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H504" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I504" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J504" t="n">
+        <v>101</v>
+      </c>
+      <c r="K504" t="n">
+        <v>11</v>
+      </c>
+      <c r="L504" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M504" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N504" s="2" t="n">
+        <v>45834.31292980131</v>
+      </c>
+      <c r="O504" t="n">
+        <v>25008</v>
+      </c>
+      <c r="P504" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q504" t="n">
+        <v>2063.26</v>
+      </c>
+      <c r="R504" t="n">
+        <v>12.12062464255595</v>
+      </c>
+      <c r="S504" t="n">
+        <v>2525808</v>
+      </c>
+      <c r="T504" t="n">
+        <v>1224.183088898151</v>
+      </c>
+      <c r="U504" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V504" t="n">
+        <v>0.01956947162426625</v>
+      </c>
+      <c r="W504" t="n">
+        <v>0.01612027234160784</v>
+      </c>
+      <c r="X504" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y504" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z504" t="n">
+        <v>0.4108201563358307</v>
+      </c>
+      <c r="AA504" t="n">
+        <v>10.51282495260239</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E505" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F505" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H505" t="n">
+        <v>1</v>
+      </c>
+      <c r="I505" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J505" t="n">
+        <v>30</v>
+      </c>
+      <c r="K505" t="n">
+        <v>9</v>
+      </c>
+      <c r="L505" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M505" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N505" s="2" t="n">
+        <v>45834.31292980131</v>
+      </c>
+      <c r="O505" t="n">
+        <v>46.14</v>
+      </c>
+      <c r="P505" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q505" t="n">
+        <v>1</v>
+      </c>
+      <c r="R505" t="n">
+        <v>46.14</v>
+      </c>
+      <c r="S505" t="n">
+        <v>1384.2</v>
+      </c>
+      <c r="T505" t="n">
+        <v>1384.2</v>
+      </c>
+      <c r="U505" t="n">
+        <v>41.688</v>
+      </c>
+      <c r="V505" t="n">
+        <v>0.01007005253940463</v>
+      </c>
+      <c r="W505" t="n">
+        <v>0.01007005253940463</v>
+      </c>
+      <c r="X505" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y505" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z505" t="n">
+        <v>0.5990515947341919</v>
+      </c>
+      <c r="AA505" t="n">
+        <v>12.27674007415771</v>
       </c>
     </row>
   </sheetData>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA505"/>
+  <dimension ref="A1:AA513"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47174,7 +47174,7 @@
         <v>100</v>
       </c>
       <c r="N498" s="2" t="n">
-        <v>45834.31292980131</v>
+        <v>45834.31292980324</v>
       </c>
       <c r="O498" t="n">
         <v>1</v>
@@ -47265,7 +47265,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N499" s="2" t="n">
-        <v>45834.31292980131</v>
+        <v>45834.31292980324</v>
       </c>
       <c r="O499" t="n">
         <v>375</v>
@@ -47360,7 +47360,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N500" s="2" t="n">
-        <v>45834.31292980131</v>
+        <v>45834.31292980324</v>
       </c>
       <c r="O500" t="n">
         <v>0.725</v>
@@ -47455,7 +47455,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N501" s="2" t="n">
-        <v>45834.31292980131</v>
+        <v>45834.31292980324</v>
       </c>
       <c r="O501" t="n">
         <v>25</v>
@@ -47550,7 +47550,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N502" s="2" t="n">
-        <v>45834.31292980131</v>
+        <v>45834.31292980324</v>
       </c>
       <c r="O502" t="n">
         <v>14.02</v>
@@ -47641,7 +47641,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N503" s="2" t="n">
-        <v>45834.31292980131</v>
+        <v>45834.31292980324</v>
       </c>
       <c r="O503" t="n">
         <v>38.45</v>
@@ -47736,7 +47736,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N504" s="2" t="n">
-        <v>45834.31292980131</v>
+        <v>45834.31292980324</v>
       </c>
       <c r="O504" t="n">
         <v>25008</v>
@@ -47831,7 +47831,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N505" s="2" t="n">
-        <v>45834.31292980131</v>
+        <v>45834.31292980324</v>
       </c>
       <c r="O505" t="n">
         <v>46.14</v>
@@ -47872,6 +47872,760 @@
         <v>0.5990515947341919</v>
       </c>
       <c r="AA505" t="n">
+        <v>12.27674007415771</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F506" t="n">
+        <v>1</v>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H506" t="n">
+        <v>1</v>
+      </c>
+      <c r="I506" t="n">
+        <v>1</v>
+      </c>
+      <c r="J506" t="n">
+        <v>1</v>
+      </c>
+      <c r="K506" t="n">
+        <v>100</v>
+      </c>
+      <c r="L506" t="n">
+        <v>100</v>
+      </c>
+      <c r="M506" t="n">
+        <v>100</v>
+      </c>
+      <c r="N506" s="2" t="n">
+        <v>45834.36091549883</v>
+      </c>
+      <c r="O506" t="n">
+        <v>1</v>
+      </c>
+      <c r="P506" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q506" t="n">
+        <v>1</v>
+      </c>
+      <c r="R506" t="n">
+        <v>1</v>
+      </c>
+      <c r="S506" t="n">
+        <v>0</v>
+      </c>
+      <c r="T506" t="n">
+        <v>45.43580260334033</v>
+      </c>
+      <c r="U506" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V506" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W506" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X506" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y506" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z506" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA506" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr"/>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E507" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F507" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H507" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I507" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J507" t="n">
+        <v>3</v>
+      </c>
+      <c r="K507" t="n">
+        <v>10</v>
+      </c>
+      <c r="L507" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M507" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N507" s="2" t="n">
+        <v>45834.36091549883</v>
+      </c>
+      <c r="O507" t="n">
+        <v>374</v>
+      </c>
+      <c r="P507" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q507" t="n">
+        <v>0.85304</v>
+      </c>
+      <c r="R507" t="n">
+        <v>438.4319609865891</v>
+      </c>
+      <c r="S507" t="n">
+        <v>1122</v>
+      </c>
+      <c r="T507" t="n">
+        <v>1315.295882959767</v>
+      </c>
+      <c r="U507" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V507" t="n">
+        <v>0.01722759243443783</v>
+      </c>
+      <c r="W507" t="n">
+        <v>0.01797885073795658</v>
+      </c>
+      <c r="X507" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y507" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z507" t="n">
+        <v>0.5015593767166138</v>
+      </c>
+      <c r="AA507" t="n">
+        <v>12.0281548500061</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E508" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F508" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H508" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I508" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J508" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K508" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L508" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M508" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N508" s="2" t="n">
+        <v>45834.36091549883</v>
+      </c>
+      <c r="O508" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="P508" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q508" t="n">
+        <v>1.79227</v>
+      </c>
+      <c r="R508" t="n">
+        <v>0.4045149447348892</v>
+      </c>
+      <c r="S508" t="n">
+        <v>2656.4</v>
+      </c>
+      <c r="T508" t="n">
+        <v>1482.142757508634</v>
+      </c>
+      <c r="U508" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="V508" t="n">
+        <v>0</v>
+      </c>
+      <c r="W508" t="n">
+        <v>-0.009875744168010514</v>
+      </c>
+      <c r="X508" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y508" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z508" t="n">
+        <v>0.4815215170383453</v>
+      </c>
+      <c r="AA508" t="n">
+        <v>11.57751679420471</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E509" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F509" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H509" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I509" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J509" t="n">
+        <v>537</v>
+      </c>
+      <c r="K509" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L509" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M509" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N509" s="2" t="n">
+        <v>45834.36091549883</v>
+      </c>
+      <c r="O509" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="P509" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q509" t="n">
+        <v>9.213190000000001</v>
+      </c>
+      <c r="R509" t="n">
+        <v>2.729781975624078</v>
+      </c>
+      <c r="S509" t="n">
+        <v>13505.55</v>
+      </c>
+      <c r="T509" t="n">
+        <v>1465.89292091013</v>
+      </c>
+      <c r="U509" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V509" t="n">
+        <v>-0.001984126984126977</v>
+      </c>
+      <c r="W509" t="n">
+        <v>-0.02068638325759931</v>
+      </c>
+      <c r="X509" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y509" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z509" t="n">
+        <v>0.4985511600971222</v>
+      </c>
+      <c r="AA509" t="n">
+        <v>9.835646152496338</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E510" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F510" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H510" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I510" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J510" t="n">
+        <v>121</v>
+      </c>
+      <c r="K510" t="n">
+        <v>12</v>
+      </c>
+      <c r="L510" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M510" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N510" s="2" t="n">
+        <v>45834.36091549883</v>
+      </c>
+      <c r="O510" t="n">
+        <v>14.02</v>
+      </c>
+      <c r="P510" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q510" t="n">
+        <v>1.1741223</v>
+      </c>
+      <c r="R510" t="n">
+        <v>11.94083444288555</v>
+      </c>
+      <c r="S510" t="n">
+        <v>1696.42</v>
+      </c>
+      <c r="T510" t="n">
+        <v>1444.840967589151</v>
+      </c>
+      <c r="U510" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V510" t="n">
+        <v>-0.01128349788434413</v>
+      </c>
+      <c r="W510" t="n">
+        <v>-0.03130123737369916</v>
+      </c>
+      <c r="X510" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y510" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z510" t="n">
+        <v>0.5161105990409851</v>
+      </c>
+      <c r="AA510" t="n">
+        <v>13.94983839988708</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr"/>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E511" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F511" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H511" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I511" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J511" t="n">
+        <v>162</v>
+      </c>
+      <c r="K511" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L511" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M511" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N511" s="2" t="n">
+        <v>45834.36091549883</v>
+      </c>
+      <c r="O511" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="P511" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q511" t="n">
+        <v>4.24452</v>
+      </c>
+      <c r="R511" t="n">
+        <v>9.070519163533215</v>
+      </c>
+      <c r="S511" t="n">
+        <v>6237</v>
+      </c>
+      <c r="T511" t="n">
+        <v>1469.424104492381</v>
+      </c>
+      <c r="U511" t="n">
+        <v>8.272543736854324</v>
+      </c>
+      <c r="V511" t="n">
+        <v>-0.0178571428571429</v>
+      </c>
+      <c r="W511" t="n">
+        <v>-0.0131853627063333</v>
+      </c>
+      <c r="X511" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y511" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z511" t="n">
+        <v>0.5935001373291016</v>
+      </c>
+      <c r="AA511" t="n">
+        <v>12.80392378997803</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E512" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F512" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H512" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I512" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J512" t="n">
+        <v>101</v>
+      </c>
+      <c r="K512" t="n">
+        <v>11</v>
+      </c>
+      <c r="L512" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M512" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N512" s="2" t="n">
+        <v>45834.36091549883</v>
+      </c>
+      <c r="O512" t="n">
+        <v>24923</v>
+      </c>
+      <c r="P512" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q512" t="n">
+        <v>2063.79</v>
+      </c>
+      <c r="R512" t="n">
+        <v>12.07632559514292</v>
+      </c>
+      <c r="S512" t="n">
+        <v>2517223</v>
+      </c>
+      <c r="T512" t="n">
+        <v>1219.708885109435</v>
+      </c>
+      <c r="U512" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V512" t="n">
+        <v>0.01610404435746893</v>
+      </c>
+      <c r="W512" t="n">
+        <v>0.01240650663651666</v>
+      </c>
+      <c r="X512" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y512" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z512" t="n">
+        <v>0.4108201563358307</v>
+      </c>
+      <c r="AA512" t="n">
+        <v>10.51282495260239</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E513" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F513" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H513" t="n">
+        <v>1</v>
+      </c>
+      <c r="I513" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J513" t="n">
+        <v>30</v>
+      </c>
+      <c r="K513" t="n">
+        <v>9</v>
+      </c>
+      <c r="L513" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M513" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N513" s="2" t="n">
+        <v>45834.36091549883</v>
+      </c>
+      <c r="O513" t="n">
+        <v>45.94</v>
+      </c>
+      <c r="P513" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q513" t="n">
+        <v>1</v>
+      </c>
+      <c r="R513" t="n">
+        <v>45.94</v>
+      </c>
+      <c r="S513" t="n">
+        <v>1378.2</v>
+      </c>
+      <c r="T513" t="n">
+        <v>1378.2</v>
+      </c>
+      <c r="U513" t="n">
+        <v>41.688</v>
+      </c>
+      <c r="V513" t="n">
+        <v>0.005691768826619814</v>
+      </c>
+      <c r="W513" t="n">
+        <v>0.005691768826619814</v>
+      </c>
+      <c r="X513" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y513" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z513" t="n">
+        <v>0.5990515947341919</v>
+      </c>
+      <c r="AA513" t="n">
         <v>12.27674007415771</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA513"/>
+  <dimension ref="A1:AA521"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47928,7 +47928,7 @@
         <v>100</v>
       </c>
       <c r="N506" s="2" t="n">
-        <v>45834.36091549883</v>
+        <v>45834.36091549769</v>
       </c>
       <c r="O506" t="n">
         <v>1</v>
@@ -48019,7 +48019,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N507" s="2" t="n">
-        <v>45834.36091549883</v>
+        <v>45834.36091549769</v>
       </c>
       <c r="O507" t="n">
         <v>374</v>
@@ -48114,7 +48114,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N508" s="2" t="n">
-        <v>45834.36091549883</v>
+        <v>45834.36091549769</v>
       </c>
       <c r="O508" t="n">
         <v>0.725</v>
@@ -48209,7 +48209,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N509" s="2" t="n">
-        <v>45834.36091549883</v>
+        <v>45834.36091549769</v>
       </c>
       <c r="O509" t="n">
         <v>25.15</v>
@@ -48304,7 +48304,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N510" s="2" t="n">
-        <v>45834.36091549883</v>
+        <v>45834.36091549769</v>
       </c>
       <c r="O510" t="n">
         <v>14.02</v>
@@ -48395,7 +48395,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N511" s="2" t="n">
-        <v>45834.36091549883</v>
+        <v>45834.36091549769</v>
       </c>
       <c r="O511" t="n">
         <v>38.5</v>
@@ -48490,7 +48490,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N512" s="2" t="n">
-        <v>45834.36091549883</v>
+        <v>45834.36091549769</v>
       </c>
       <c r="O512" t="n">
         <v>24923</v>
@@ -48585,7 +48585,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N513" s="2" t="n">
-        <v>45834.36091549883</v>
+        <v>45834.36091549769</v>
       </c>
       <c r="O513" t="n">
         <v>45.94</v>
@@ -48626,6 +48626,760 @@
         <v>0.5990515947341919</v>
       </c>
       <c r="AA513" t="n">
+        <v>12.27674007415771</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F514" t="n">
+        <v>1</v>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H514" t="n">
+        <v>1</v>
+      </c>
+      <c r="I514" t="n">
+        <v>1</v>
+      </c>
+      <c r="J514" t="n">
+        <v>1</v>
+      </c>
+      <c r="K514" t="n">
+        <v>100</v>
+      </c>
+      <c r="L514" t="n">
+        <v>100</v>
+      </c>
+      <c r="M514" t="n">
+        <v>100</v>
+      </c>
+      <c r="N514" s="2" t="n">
+        <v>45834.39855334348</v>
+      </c>
+      <c r="O514" t="n">
+        <v>1</v>
+      </c>
+      <c r="P514" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q514" t="n">
+        <v>1</v>
+      </c>
+      <c r="R514" t="n">
+        <v>1</v>
+      </c>
+      <c r="S514" t="n">
+        <v>0</v>
+      </c>
+      <c r="T514" t="n">
+        <v>45.43580260334033</v>
+      </c>
+      <c r="U514" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V514" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W514" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X514" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y514" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z514" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA514" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr"/>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E515" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F515" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H515" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I515" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J515" t="n">
+        <v>3</v>
+      </c>
+      <c r="K515" t="n">
+        <v>10</v>
+      </c>
+      <c r="L515" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M515" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N515" s="2" t="n">
+        <v>45834.39855334348</v>
+      </c>
+      <c r="O515" t="n">
+        <v>374.26</v>
+      </c>
+      <c r="P515" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q515" t="n">
+        <v>0.85271</v>
+      </c>
+      <c r="R515" t="n">
+        <v>438.9065450153042</v>
+      </c>
+      <c r="S515" t="n">
+        <v>1122.78</v>
+      </c>
+      <c r="T515" t="n">
+        <v>1316.719635045912</v>
+      </c>
+      <c r="U515" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V515" t="n">
+        <v>0.01793475600137073</v>
+      </c>
+      <c r="W515" t="n">
+        <v>0.01908076972908757</v>
+      </c>
+      <c r="X515" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y515" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z515" t="n">
+        <v>0.5015593767166138</v>
+      </c>
+      <c r="AA515" t="n">
+        <v>12.0281548500061</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E516" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F516" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H516" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I516" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J516" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K516" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L516" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M516" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N516" s="2" t="n">
+        <v>45834.39855334348</v>
+      </c>
+      <c r="O516" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="P516" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q516" t="n">
+        <v>1.79322</v>
+      </c>
+      <c r="R516" t="n">
+        <v>0.4043006435350933</v>
+      </c>
+      <c r="S516" t="n">
+        <v>2656.4</v>
+      </c>
+      <c r="T516" t="n">
+        <v>1481.357557912582</v>
+      </c>
+      <c r="U516" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="V516" t="n">
+        <v>0</v>
+      </c>
+      <c r="W516" t="n">
+        <v>-0.0104002855199028</v>
+      </c>
+      <c r="X516" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y516" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z516" t="n">
+        <v>0.4815215170383453</v>
+      </c>
+      <c r="AA516" t="n">
+        <v>11.57751679420471</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E517" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F517" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H517" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I517" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J517" t="n">
+        <v>537</v>
+      </c>
+      <c r="K517" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L517" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M517" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N517" s="2" t="n">
+        <v>45834.39855334348</v>
+      </c>
+      <c r="O517" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="P517" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q517" t="n">
+        <v>9.200089999999999</v>
+      </c>
+      <c r="R517" t="n">
+        <v>2.733668909760665</v>
+      </c>
+      <c r="S517" t="n">
+        <v>13505.55</v>
+      </c>
+      <c r="T517" t="n">
+        <v>1467.980204541477</v>
+      </c>
+      <c r="U517" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V517" t="n">
+        <v>-0.001984126984126977</v>
+      </c>
+      <c r="W517" t="n">
+        <v>-0.01929193946636176</v>
+      </c>
+      <c r="X517" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y517" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z517" t="n">
+        <v>0.4985511600971222</v>
+      </c>
+      <c r="AA517" t="n">
+        <v>9.835646152496338</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E518" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F518" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H518" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I518" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J518" t="n">
+        <v>121</v>
+      </c>
+      <c r="K518" t="n">
+        <v>12</v>
+      </c>
+      <c r="L518" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M518" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N518" s="2" t="n">
+        <v>45834.39855334348</v>
+      </c>
+      <c r="O518" t="n">
+        <v>14.02</v>
+      </c>
+      <c r="P518" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q518" t="n">
+        <v>1.1724703</v>
+      </c>
+      <c r="R518" t="n">
+        <v>11.95765897012487</v>
+      </c>
+      <c r="S518" t="n">
+        <v>1696.42</v>
+      </c>
+      <c r="T518" t="n">
+        <v>1446.876735385109</v>
+      </c>
+      <c r="U518" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V518" t="n">
+        <v>-0.01128349788434413</v>
+      </c>
+      <c r="W518" t="n">
+        <v>-0.02993634961845404</v>
+      </c>
+      <c r="X518" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y518" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z518" t="n">
+        <v>0.5161105990409851</v>
+      </c>
+      <c r="AA518" t="n">
+        <v>13.94983839988708</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr"/>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E519" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F519" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H519" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I519" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J519" t="n">
+        <v>162</v>
+      </c>
+      <c r="K519" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L519" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M519" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N519" s="2" t="n">
+        <v>45834.39855334348</v>
+      </c>
+      <c r="O519" t="n">
+        <v>38.65</v>
+      </c>
+      <c r="P519" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q519" t="n">
+        <v>4.24597</v>
+      </c>
+      <c r="R519" t="n">
+        <v>9.102749195119136</v>
+      </c>
+      <c r="S519" t="n">
+        <v>6261.3</v>
+      </c>
+      <c r="T519" t="n">
+        <v>1474.6453696093</v>
+      </c>
+      <c r="U519" t="n">
+        <v>8.272543736854324</v>
+      </c>
+      <c r="V519" t="n">
+        <v>-0.0140306122448981</v>
+      </c>
+      <c r="W519" t="n">
+        <v>-0.009678940818455883</v>
+      </c>
+      <c r="X519" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y519" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z519" t="n">
+        <v>0.5935001373291016</v>
+      </c>
+      <c r="AA519" t="n">
+        <v>12.80392378997803</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E520" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F520" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H520" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I520" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J520" t="n">
+        <v>101</v>
+      </c>
+      <c r="K520" t="n">
+        <v>11</v>
+      </c>
+      <c r="L520" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M520" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N520" s="2" t="n">
+        <v>45834.39855334348</v>
+      </c>
+      <c r="O520" t="n">
+        <v>24830</v>
+      </c>
+      <c r="P520" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q520" t="n">
+        <v>2073.04</v>
+      </c>
+      <c r="R520" t="n">
+        <v>11.97757882144098</v>
+      </c>
+      <c r="S520" t="n">
+        <v>2507830</v>
+      </c>
+      <c r="T520" t="n">
+        <v>1209.735460965539</v>
+      </c>
+      <c r="U520" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V520" t="n">
+        <v>0.01231245923026747</v>
+      </c>
+      <c r="W520" t="n">
+        <v>0.004128171027097505</v>
+      </c>
+      <c r="X520" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y520" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z520" t="n">
+        <v>0.4108201563358307</v>
+      </c>
+      <c r="AA520" t="n">
+        <v>10.51282495260239</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E521" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F521" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H521" t="n">
+        <v>1</v>
+      </c>
+      <c r="I521" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J521" t="n">
+        <v>30</v>
+      </c>
+      <c r="K521" t="n">
+        <v>9</v>
+      </c>
+      <c r="L521" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M521" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N521" s="2" t="n">
+        <v>45834.39855334348</v>
+      </c>
+      <c r="O521" t="n">
+        <v>46.08</v>
+      </c>
+      <c r="P521" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q521" t="n">
+        <v>1</v>
+      </c>
+      <c r="R521" t="n">
+        <v>46.08</v>
+      </c>
+      <c r="S521" t="n">
+        <v>1382.4</v>
+      </c>
+      <c r="T521" t="n">
+        <v>1382.4</v>
+      </c>
+      <c r="U521" t="n">
+        <v>41.688</v>
+      </c>
+      <c r="V521" t="n">
+        <v>0.008756567425569184</v>
+      </c>
+      <c r="W521" t="n">
+        <v>0.008756567425569184</v>
+      </c>
+      <c r="X521" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y521" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z521" t="n">
+        <v>0.5990515947341919</v>
+      </c>
+      <c r="AA521" t="n">
         <v>12.27674007415771</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA521"/>
+  <dimension ref="A1:AA529"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48682,7 +48682,7 @@
         <v>100</v>
       </c>
       <c r="N514" s="2" t="n">
-        <v>45834.39855334348</v>
+        <v>45834.39855334491</v>
       </c>
       <c r="O514" t="n">
         <v>1</v>
@@ -48773,7 +48773,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N515" s="2" t="n">
-        <v>45834.39855334348</v>
+        <v>45834.39855334491</v>
       </c>
       <c r="O515" t="n">
         <v>374.26</v>
@@ -48868,7 +48868,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N516" s="2" t="n">
-        <v>45834.39855334348</v>
+        <v>45834.39855334491</v>
       </c>
       <c r="O516" t="n">
         <v>0.725</v>
@@ -48963,7 +48963,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N517" s="2" t="n">
-        <v>45834.39855334348</v>
+        <v>45834.39855334491</v>
       </c>
       <c r="O517" t="n">
         <v>25.15</v>
@@ -49058,7 +49058,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N518" s="2" t="n">
-        <v>45834.39855334348</v>
+        <v>45834.39855334491</v>
       </c>
       <c r="O518" t="n">
         <v>14.02</v>
@@ -49149,7 +49149,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N519" s="2" t="n">
-        <v>45834.39855334348</v>
+        <v>45834.39855334491</v>
       </c>
       <c r="O519" t="n">
         <v>38.65</v>
@@ -49244,7 +49244,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N520" s="2" t="n">
-        <v>45834.39855334348</v>
+        <v>45834.39855334491</v>
       </c>
       <c r="O520" t="n">
         <v>24830</v>
@@ -49339,7 +49339,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N521" s="2" t="n">
-        <v>45834.39855334348</v>
+        <v>45834.39855334491</v>
       </c>
       <c r="O521" t="n">
         <v>46.08</v>
@@ -49380,6 +49380,760 @@
         <v>0.5990515947341919</v>
       </c>
       <c r="AA521" t="n">
+        <v>12.27674007415771</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F522" t="n">
+        <v>1</v>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H522" t="n">
+        <v>1</v>
+      </c>
+      <c r="I522" t="n">
+        <v>1</v>
+      </c>
+      <c r="J522" t="n">
+        <v>1</v>
+      </c>
+      <c r="K522" t="n">
+        <v>100</v>
+      </c>
+      <c r="L522" t="n">
+        <v>100</v>
+      </c>
+      <c r="M522" t="n">
+        <v>100</v>
+      </c>
+      <c r="N522" s="2" t="n">
+        <v>45834.44206475094</v>
+      </c>
+      <c r="O522" t="n">
+        <v>1</v>
+      </c>
+      <c r="P522" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q522" t="n">
+        <v>1</v>
+      </c>
+      <c r="R522" t="n">
+        <v>1</v>
+      </c>
+      <c r="S522" t="n">
+        <v>0</v>
+      </c>
+      <c r="T522" t="n">
+        <v>45.43580260334033</v>
+      </c>
+      <c r="U522" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V522" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W522" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X522" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y522" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z522" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA522" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr"/>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E523" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F523" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H523" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I523" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J523" t="n">
+        <v>3</v>
+      </c>
+      <c r="K523" t="n">
+        <v>10</v>
+      </c>
+      <c r="L523" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M523" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N523" s="2" t="n">
+        <v>45834.44206475094</v>
+      </c>
+      <c r="O523" t="n">
+        <v>376.4</v>
+      </c>
+      <c r="P523" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q523" t="n">
+        <v>0.85282</v>
+      </c>
+      <c r="R523" t="n">
+        <v>441.3592551769423</v>
+      </c>
+      <c r="S523" t="n">
+        <v>1129.2</v>
+      </c>
+      <c r="T523" t="n">
+        <v>1324.077765530827</v>
+      </c>
+      <c r="U523" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V523" t="n">
+        <v>0.02375525612920426</v>
+      </c>
+      <c r="W523" t="n">
+        <v>0.02477562615770945</v>
+      </c>
+      <c r="X523" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y523" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z523" t="n">
+        <v>0.5015593767166138</v>
+      </c>
+      <c r="AA523" t="n">
+        <v>12.0281548500061</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E524" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F524" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H524" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I524" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J524" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K524" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L524" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M524" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N524" s="2" t="n">
+        <v>45834.44206475094</v>
+      </c>
+      <c r="O524" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="P524" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q524" t="n">
+        <v>1.7922</v>
+      </c>
+      <c r="R524" t="n">
+        <v>0.4045307443365695</v>
+      </c>
+      <c r="S524" t="n">
+        <v>2656.4</v>
+      </c>
+      <c r="T524" t="n">
+        <v>1482.200647249191</v>
+      </c>
+      <c r="U524" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="V524" t="n">
+        <v>0</v>
+      </c>
+      <c r="W524" t="n">
+        <v>-0.009837071755384508</v>
+      </c>
+      <c r="X524" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y524" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z524" t="n">
+        <v>0.4815215170383453</v>
+      </c>
+      <c r="AA524" t="n">
+        <v>11.57751679420471</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E525" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F525" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H525" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I525" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J525" t="n">
+        <v>537</v>
+      </c>
+      <c r="K525" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L525" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M525" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N525" s="2" t="n">
+        <v>45834.44206475094</v>
+      </c>
+      <c r="O525" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="P525" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q525" t="n">
+        <v>9.2004</v>
+      </c>
+      <c r="R525" t="n">
+        <v>2.733576801008652</v>
+      </c>
+      <c r="S525" t="n">
+        <v>13505.55</v>
+      </c>
+      <c r="T525" t="n">
+        <v>1467.930742141646</v>
+      </c>
+      <c r="U525" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V525" t="n">
+        <v>-0.001984126984126977</v>
+      </c>
+      <c r="W525" t="n">
+        <v>-0.01932498362735102</v>
+      </c>
+      <c r="X525" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y525" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z525" t="n">
+        <v>0.4985511600971222</v>
+      </c>
+      <c r="AA525" t="n">
+        <v>9.835646152496338</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E526" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F526" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H526" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I526" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J526" t="n">
+        <v>121</v>
+      </c>
+      <c r="K526" t="n">
+        <v>12</v>
+      </c>
+      <c r="L526" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M526" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N526" s="2" t="n">
+        <v>45834.44206475094</v>
+      </c>
+      <c r="O526" t="n">
+        <v>14.02</v>
+      </c>
+      <c r="P526" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q526" t="n">
+        <v>1.1726079</v>
+      </c>
+      <c r="R526" t="n">
+        <v>11.9562557953089</v>
+      </c>
+      <c r="S526" t="n">
+        <v>1696.42</v>
+      </c>
+      <c r="T526" t="n">
+        <v>1446.706951232377</v>
+      </c>
+      <c r="U526" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V526" t="n">
+        <v>-0.01128349788434413</v>
+      </c>
+      <c r="W526" t="n">
+        <v>-0.03005018200717702</v>
+      </c>
+      <c r="X526" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y526" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z526" t="n">
+        <v>0.5161105990409851</v>
+      </c>
+      <c r="AA526" t="n">
+        <v>13.94983839988708</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr"/>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E527" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F527" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H527" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I527" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J527" t="n">
+        <v>162</v>
+      </c>
+      <c r="K527" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L527" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M527" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N527" s="2" t="n">
+        <v>45834.44206475094</v>
+      </c>
+      <c r="O527" t="n">
+        <v>38.85</v>
+      </c>
+      <c r="P527" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q527" t="n">
+        <v>4.24508</v>
+      </c>
+      <c r="R527" t="n">
+        <v>9.15177099135941</v>
+      </c>
+      <c r="S527" t="n">
+        <v>6293.7</v>
+      </c>
+      <c r="T527" t="n">
+        <v>1482.586900600224</v>
+      </c>
+      <c r="U527" t="n">
+        <v>8.272543736854324</v>
+      </c>
+      <c r="V527" t="n">
+        <v>-0.008928571428571508</v>
+      </c>
+      <c r="W527" t="n">
+        <v>-0.004345682026520747</v>
+      </c>
+      <c r="X527" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y527" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z527" t="n">
+        <v>0.5935001373291016</v>
+      </c>
+      <c r="AA527" t="n">
+        <v>12.80392378997803</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E528" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F528" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H528" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I528" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J528" t="n">
+        <v>101</v>
+      </c>
+      <c r="K528" t="n">
+        <v>11</v>
+      </c>
+      <c r="L528" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M528" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N528" s="2" t="n">
+        <v>45834.44206475094</v>
+      </c>
+      <c r="O528" t="n">
+        <v>24781</v>
+      </c>
+      <c r="P528" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q528" t="n">
+        <v>2068.12</v>
+      </c>
+      <c r="R528" t="n">
+        <v>11.98238013268089</v>
+      </c>
+      <c r="S528" t="n">
+        <v>2502881</v>
+      </c>
+      <c r="T528" t="n">
+        <v>1210.22039340077</v>
+      </c>
+      <c r="U528" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V528" t="n">
+        <v>0.01031474233529028</v>
+      </c>
+      <c r="W528" t="n">
+        <v>0.004530684084681269</v>
+      </c>
+      <c r="X528" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y528" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z528" t="n">
+        <v>0.4108201563358307</v>
+      </c>
+      <c r="AA528" t="n">
+        <v>10.51282495260239</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E529" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F529" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H529" t="n">
+        <v>1</v>
+      </c>
+      <c r="I529" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J529" t="n">
+        <v>30</v>
+      </c>
+      <c r="K529" t="n">
+        <v>9</v>
+      </c>
+      <c r="L529" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M529" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N529" s="2" t="n">
+        <v>45834.44206475094</v>
+      </c>
+      <c r="O529" t="n">
+        <v>46.06</v>
+      </c>
+      <c r="P529" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q529" t="n">
+        <v>1</v>
+      </c>
+      <c r="R529" t="n">
+        <v>46.06</v>
+      </c>
+      <c r="S529" t="n">
+        <v>1381.8</v>
+      </c>
+      <c r="T529" t="n">
+        <v>1381.8</v>
+      </c>
+      <c r="U529" t="n">
+        <v>41.688</v>
+      </c>
+      <c r="V529" t="n">
+        <v>0.008318739054290702</v>
+      </c>
+      <c r="W529" t="n">
+        <v>0.008318739054290702</v>
+      </c>
+      <c r="X529" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y529" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z529" t="n">
+        <v>0.5990515947341919</v>
+      </c>
+      <c r="AA529" t="n">
         <v>12.27674007415771</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA529"/>
+  <dimension ref="A1:AA537"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49436,7 +49436,7 @@
         <v>100</v>
       </c>
       <c r="N522" s="2" t="n">
-        <v>45834.44206475094</v>
+        <v>45834.44206474537</v>
       </c>
       <c r="O522" t="n">
         <v>1</v>
@@ -49527,7 +49527,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N523" s="2" t="n">
-        <v>45834.44206475094</v>
+        <v>45834.44206474537</v>
       </c>
       <c r="O523" t="n">
         <v>376.4</v>
@@ -49622,7 +49622,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N524" s="2" t="n">
-        <v>45834.44206475094</v>
+        <v>45834.44206474537</v>
       </c>
       <c r="O524" t="n">
         <v>0.725</v>
@@ -49717,7 +49717,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N525" s="2" t="n">
-        <v>45834.44206475094</v>
+        <v>45834.44206474537</v>
       </c>
       <c r="O525" t="n">
         <v>25.15</v>
@@ -49812,7 +49812,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N526" s="2" t="n">
-        <v>45834.44206475094</v>
+        <v>45834.44206474537</v>
       </c>
       <c r="O526" t="n">
         <v>14.02</v>
@@ -49903,7 +49903,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N527" s="2" t="n">
-        <v>45834.44206475094</v>
+        <v>45834.44206474537</v>
       </c>
       <c r="O527" t="n">
         <v>38.85</v>
@@ -49998,7 +49998,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N528" s="2" t="n">
-        <v>45834.44206475094</v>
+        <v>45834.44206474537</v>
       </c>
       <c r="O528" t="n">
         <v>24781</v>
@@ -50093,7 +50093,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N529" s="2" t="n">
-        <v>45834.44206475094</v>
+        <v>45834.44206474537</v>
       </c>
       <c r="O529" t="n">
         <v>46.06</v>
@@ -50134,6 +50134,760 @@
         <v>0.5990515947341919</v>
       </c>
       <c r="AA529" t="n">
+        <v>12.27674007415771</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F530" t="n">
+        <v>1</v>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H530" t="n">
+        <v>1</v>
+      </c>
+      <c r="I530" t="n">
+        <v>1</v>
+      </c>
+      <c r="J530" t="n">
+        <v>1</v>
+      </c>
+      <c r="K530" t="n">
+        <v>100</v>
+      </c>
+      <c r="L530" t="n">
+        <v>100</v>
+      </c>
+      <c r="M530" t="n">
+        <v>100</v>
+      </c>
+      <c r="N530" s="2" t="n">
+        <v>45834.47701835284</v>
+      </c>
+      <c r="O530" t="n">
+        <v>1</v>
+      </c>
+      <c r="P530" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q530" t="n">
+        <v>1</v>
+      </c>
+      <c r="R530" t="n">
+        <v>1</v>
+      </c>
+      <c r="S530" t="n">
+        <v>0</v>
+      </c>
+      <c r="T530" t="n">
+        <v>45.43580260334033</v>
+      </c>
+      <c r="U530" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V530" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W530" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X530" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y530" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z530" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA530" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr"/>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E531" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F531" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H531" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I531" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J531" t="n">
+        <v>3</v>
+      </c>
+      <c r="K531" t="n">
+        <v>10</v>
+      </c>
+      <c r="L531" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M531" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N531" s="2" t="n">
+        <v>45834.47701835284</v>
+      </c>
+      <c r="O531" t="n">
+        <v>376.5</v>
+      </c>
+      <c r="P531" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q531" t="n">
+        <v>0.85328</v>
+      </c>
+      <c r="R531" t="n">
+        <v>441.2385149071817</v>
+      </c>
+      <c r="S531" t="n">
+        <v>1129.5</v>
+      </c>
+      <c r="T531" t="n">
+        <v>1323.715544721545</v>
+      </c>
+      <c r="U531" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V531" t="n">
+        <v>0.02402724211648621</v>
+      </c>
+      <c r="W531" t="n">
+        <v>0.0244952838195911</v>
+      </c>
+      <c r="X531" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y531" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z531" t="n">
+        <v>0.5015593767166138</v>
+      </c>
+      <c r="AA531" t="n">
+        <v>12.0281548500061</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E532" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F532" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H532" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I532" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J532" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K532" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L532" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M532" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N532" s="2" t="n">
+        <v>45834.47701835284</v>
+      </c>
+      <c r="O532" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="P532" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q532" t="n">
+        <v>1.79064</v>
+      </c>
+      <c r="R532" t="n">
+        <v>0.4048831702631461</v>
+      </c>
+      <c r="S532" t="n">
+        <v>2656.4</v>
+      </c>
+      <c r="T532" t="n">
+        <v>1483.491935844168</v>
+      </c>
+      <c r="U532" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="V532" t="n">
+        <v>0</v>
+      </c>
+      <c r="W532" t="n">
+        <v>-0.00897444489121213</v>
+      </c>
+      <c r="X532" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y532" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z532" t="n">
+        <v>0.4815215170383453</v>
+      </c>
+      <c r="AA532" t="n">
+        <v>11.57751679420471</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E533" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F533" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H533" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I533" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J533" t="n">
+        <v>537</v>
+      </c>
+      <c r="K533" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L533" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M533" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N533" s="2" t="n">
+        <v>45834.47701835284</v>
+      </c>
+      <c r="O533" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="P533" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q533" t="n">
+        <v>9.18186</v>
+      </c>
+      <c r="R533" t="n">
+        <v>2.739096435798411</v>
+      </c>
+      <c r="S533" t="n">
+        <v>13505.55</v>
+      </c>
+      <c r="T533" t="n">
+        <v>1470.894786023747</v>
+      </c>
+      <c r="U533" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V533" t="n">
+        <v>-0.001984126984126977</v>
+      </c>
+      <c r="W533" t="n">
+        <v>-0.01734480588519971</v>
+      </c>
+      <c r="X533" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y533" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z533" t="n">
+        <v>0.4985511600971222</v>
+      </c>
+      <c r="AA533" t="n">
+        <v>9.835646152496338</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E534" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F534" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H534" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I534" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J534" t="n">
+        <v>121</v>
+      </c>
+      <c r="K534" t="n">
+        <v>12</v>
+      </c>
+      <c r="L534" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M534" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N534" s="2" t="n">
+        <v>45834.47701835284</v>
+      </c>
+      <c r="O534" t="n">
+        <v>14.02</v>
+      </c>
+      <c r="P534" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q534" t="n">
+        <v>1.170138</v>
+      </c>
+      <c r="R534" t="n">
+        <v>11.98149278119333</v>
+      </c>
+      <c r="S534" t="n">
+        <v>1696.42</v>
+      </c>
+      <c r="T534" t="n">
+        <v>1449.760626524393</v>
+      </c>
+      <c r="U534" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V534" t="n">
+        <v>-0.01128349788434413</v>
+      </c>
+      <c r="W534" t="n">
+        <v>-0.02800283455289332</v>
+      </c>
+      <c r="X534" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y534" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z534" t="n">
+        <v>0.5161105990409851</v>
+      </c>
+      <c r="AA534" t="n">
+        <v>13.94983839988708</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr"/>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E535" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F535" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H535" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I535" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J535" t="n">
+        <v>162</v>
+      </c>
+      <c r="K535" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L535" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M535" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N535" s="2" t="n">
+        <v>45834.47701835284</v>
+      </c>
+      <c r="O535" t="n">
+        <v>38.85</v>
+      </c>
+      <c r="P535" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q535" t="n">
+        <v>4.2459</v>
+      </c>
+      <c r="R535" t="n">
+        <v>9.150003532819898</v>
+      </c>
+      <c r="S535" t="n">
+        <v>6293.7</v>
+      </c>
+      <c r="T535" t="n">
+        <v>1482.300572316823</v>
+      </c>
+      <c r="U535" t="n">
+        <v>8.272543736854324</v>
+      </c>
+      <c r="V535" t="n">
+        <v>-0.008928571428571508</v>
+      </c>
+      <c r="W535" t="n">
+        <v>-0.004537970243562617</v>
+      </c>
+      <c r="X535" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y535" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z535" t="n">
+        <v>0.5935001373291016</v>
+      </c>
+      <c r="AA535" t="n">
+        <v>12.80392378997803</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E536" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F536" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H536" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I536" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J536" t="n">
+        <v>101</v>
+      </c>
+      <c r="K536" t="n">
+        <v>11</v>
+      </c>
+      <c r="L536" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M536" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N536" s="2" t="n">
+        <v>45834.47701835284</v>
+      </c>
+      <c r="O536" t="n">
+        <v>24871</v>
+      </c>
+      <c r="P536" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q536" t="n">
+        <v>2077.14</v>
+      </c>
+      <c r="R536" t="n">
+        <v>11.97367534205687</v>
+      </c>
+      <c r="S536" t="n">
+        <v>2511971</v>
+      </c>
+      <c r="T536" t="n">
+        <v>1209.341209547744</v>
+      </c>
+      <c r="U536" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V536" t="n">
+        <v>0.01398401826484008</v>
+      </c>
+      <c r="W536" t="n">
+        <v>0.003800926792429049</v>
+      </c>
+      <c r="X536" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y536" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z536" t="n">
+        <v>0.4108201563358307</v>
+      </c>
+      <c r="AA536" t="n">
+        <v>10.51282495260239</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E537" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F537" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H537" t="n">
+        <v>1</v>
+      </c>
+      <c r="I537" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J537" t="n">
+        <v>30</v>
+      </c>
+      <c r="K537" t="n">
+        <v>9</v>
+      </c>
+      <c r="L537" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M537" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N537" s="2" t="n">
+        <v>45834.47701835284</v>
+      </c>
+      <c r="O537" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="P537" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q537" t="n">
+        <v>1</v>
+      </c>
+      <c r="R537" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="S537" t="n">
+        <v>1392</v>
+      </c>
+      <c r="T537" t="n">
+        <v>1392</v>
+      </c>
+      <c r="U537" t="n">
+        <v>41.76</v>
+      </c>
+      <c r="V537" t="n">
+        <v>0.01576182136602444</v>
+      </c>
+      <c r="W537" t="n">
+        <v>0.01576182136602444</v>
+      </c>
+      <c r="X537" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y537" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z537" t="n">
+        <v>0.5990515947341919</v>
+      </c>
+      <c r="AA537" t="n">
         <v>12.27674007415771</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA537"/>
+  <dimension ref="A1:AA545"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50190,7 +50190,7 @@
         <v>100</v>
       </c>
       <c r="N530" s="2" t="n">
-        <v>45834.47701835284</v>
+        <v>45834.47701835648</v>
       </c>
       <c r="O530" t="n">
         <v>1</v>
@@ -50281,7 +50281,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N531" s="2" t="n">
-        <v>45834.47701835284</v>
+        <v>45834.47701835648</v>
       </c>
       <c r="O531" t="n">
         <v>376.5</v>
@@ -50376,7 +50376,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N532" s="2" t="n">
-        <v>45834.47701835284</v>
+        <v>45834.47701835648</v>
       </c>
       <c r="O532" t="n">
         <v>0.725</v>
@@ -50471,7 +50471,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N533" s="2" t="n">
-        <v>45834.47701835284</v>
+        <v>45834.47701835648</v>
       </c>
       <c r="O533" t="n">
         <v>25.15</v>
@@ -50566,7 +50566,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N534" s="2" t="n">
-        <v>45834.47701835284</v>
+        <v>45834.47701835648</v>
       </c>
       <c r="O534" t="n">
         <v>14.02</v>
@@ -50657,7 +50657,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N535" s="2" t="n">
-        <v>45834.47701835284</v>
+        <v>45834.47701835648</v>
       </c>
       <c r="O535" t="n">
         <v>38.85</v>
@@ -50752,7 +50752,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N536" s="2" t="n">
-        <v>45834.47701835284</v>
+        <v>45834.47701835648</v>
       </c>
       <c r="O536" t="n">
         <v>24871</v>
@@ -50847,7 +50847,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N537" s="2" t="n">
-        <v>45834.47701835284</v>
+        <v>45834.47701835648</v>
       </c>
       <c r="O537" t="n">
         <v>46.4</v>
@@ -50888,6 +50888,760 @@
         <v>0.5990515947341919</v>
       </c>
       <c r="AA537" t="n">
+        <v>12.27674007415771</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F538" t="n">
+        <v>1</v>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H538" t="n">
+        <v>1</v>
+      </c>
+      <c r="I538" t="n">
+        <v>1</v>
+      </c>
+      <c r="J538" t="n">
+        <v>1</v>
+      </c>
+      <c r="K538" t="n">
+        <v>100</v>
+      </c>
+      <c r="L538" t="n">
+        <v>100</v>
+      </c>
+      <c r="M538" t="n">
+        <v>100</v>
+      </c>
+      <c r="N538" s="2" t="n">
+        <v>45834.54181311137</v>
+      </c>
+      <c r="O538" t="n">
+        <v>1</v>
+      </c>
+      <c r="P538" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q538" t="n">
+        <v>1</v>
+      </c>
+      <c r="R538" t="n">
+        <v>1</v>
+      </c>
+      <c r="S538" t="n">
+        <v>0</v>
+      </c>
+      <c r="T538" t="n">
+        <v>45.43580260334033</v>
+      </c>
+      <c r="U538" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V538" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W538" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X538" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y538" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z538" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA538" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr"/>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E539" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F539" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H539" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I539" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J539" t="n">
+        <v>3</v>
+      </c>
+      <c r="K539" t="n">
+        <v>10</v>
+      </c>
+      <c r="L539" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M539" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N539" s="2" t="n">
+        <v>45834.54181311137</v>
+      </c>
+      <c r="O539" t="n">
+        <v>375</v>
+      </c>
+      <c r="P539" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q539" t="n">
+        <v>0.8532999999999999</v>
+      </c>
+      <c r="R539" t="n">
+        <v>439.4702918082738</v>
+      </c>
+      <c r="S539" t="n">
+        <v>1125</v>
+      </c>
+      <c r="T539" t="n">
+        <v>1318.410875424821</v>
+      </c>
+      <c r="U539" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V539" t="n">
+        <v>0.01994745230725714</v>
+      </c>
+      <c r="W539" t="n">
+        <v>0.02038971242369181</v>
+      </c>
+      <c r="X539" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y539" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z539" t="n">
+        <v>0.5015593767166138</v>
+      </c>
+      <c r="AA539" t="n">
+        <v>12.0281548500061</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E540" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F540" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H540" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I540" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J540" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K540" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L540" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M540" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N540" s="2" t="n">
+        <v>45834.54181311137</v>
+      </c>
+      <c r="O540" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="P540" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q540" t="n">
+        <v>1.7895</v>
+      </c>
+      <c r="R540" t="n">
+        <v>0.4051411008661637</v>
+      </c>
+      <c r="S540" t="n">
+        <v>2656.4</v>
+      </c>
+      <c r="T540" t="n">
+        <v>1484.436993573624</v>
+      </c>
+      <c r="U540" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="V540" t="n">
+        <v>0</v>
+      </c>
+      <c r="W540" t="n">
+        <v>-0.008343112601285396</v>
+      </c>
+      <c r="X540" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y540" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z540" t="n">
+        <v>0.4815215170383453</v>
+      </c>
+      <c r="AA540" t="n">
+        <v>11.57751679420471</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E541" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F541" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H541" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I541" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J541" t="n">
+        <v>537</v>
+      </c>
+      <c r="K541" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L541" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M541" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N541" s="2" t="n">
+        <v>45834.54181311137</v>
+      </c>
+      <c r="O541" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="P541" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q541" t="n">
+        <v>9.18947</v>
+      </c>
+      <c r="R541" t="n">
+        <v>2.736828130458013</v>
+      </c>
+      <c r="S541" t="n">
+        <v>13505.55</v>
+      </c>
+      <c r="T541" t="n">
+        <v>1469.676706055953</v>
+      </c>
+      <c r="U541" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V541" t="n">
+        <v>-0.001984126984126977</v>
+      </c>
+      <c r="W541" t="n">
+        <v>-0.01815856402655214</v>
+      </c>
+      <c r="X541" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y541" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z541" t="n">
+        <v>0.4985511600971222</v>
+      </c>
+      <c r="AA541" t="n">
+        <v>9.835646152496338</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E542" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F542" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H542" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I542" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J542" t="n">
+        <v>121</v>
+      </c>
+      <c r="K542" t="n">
+        <v>12</v>
+      </c>
+      <c r="L542" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M542" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N542" s="2" t="n">
+        <v>45834.54181311137</v>
+      </c>
+      <c r="O542" t="n">
+        <v>14.02</v>
+      </c>
+      <c r="P542" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q542" t="n">
+        <v>1.1709602</v>
+      </c>
+      <c r="R542" t="n">
+        <v>11.97307987069074</v>
+      </c>
+      <c r="S542" t="n">
+        <v>1696.42</v>
+      </c>
+      <c r="T542" t="n">
+        <v>1448.742664353579</v>
+      </c>
+      <c r="U542" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V542" t="n">
+        <v>-0.01128349788434413</v>
+      </c>
+      <c r="W542" t="n">
+        <v>-0.0286853309088162</v>
+      </c>
+      <c r="X542" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y542" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z542" t="n">
+        <v>0.5161105990409851</v>
+      </c>
+      <c r="AA542" t="n">
+        <v>13.94983839988708</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr"/>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E543" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F543" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H543" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I543" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J543" t="n">
+        <v>162</v>
+      </c>
+      <c r="K543" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L543" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M543" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N543" s="2" t="n">
+        <v>45834.54181311137</v>
+      </c>
+      <c r="O543" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="P543" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q543" t="n">
+        <v>4.24421</v>
+      </c>
+      <c r="R543" t="n">
+        <v>9.118304702170724</v>
+      </c>
+      <c r="S543" t="n">
+        <v>6269.400000000001</v>
+      </c>
+      <c r="T543" t="n">
+        <v>1477.165361751657</v>
+      </c>
+      <c r="U543" t="n">
+        <v>8.272543736854324</v>
+      </c>
+      <c r="V543" t="n">
+        <v>-0.01275510204081631</v>
+      </c>
+      <c r="W543" t="n">
+        <v>-0.007986600857283088</v>
+      </c>
+      <c r="X543" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y543" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z543" t="n">
+        <v>0.5935001373291016</v>
+      </c>
+      <c r="AA543" t="n">
+        <v>12.80392378997803</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E544" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F544" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H544" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I544" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J544" t="n">
+        <v>101</v>
+      </c>
+      <c r="K544" t="n">
+        <v>11</v>
+      </c>
+      <c r="L544" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M544" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N544" s="2" t="n">
+        <v>45834.54181311137</v>
+      </c>
+      <c r="O544" t="n">
+        <v>24609</v>
+      </c>
+      <c r="P544" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q544" t="n">
+        <v>2075.43</v>
+      </c>
+      <c r="R544" t="n">
+        <v>11.85730186033738</v>
+      </c>
+      <c r="S544" t="n">
+        <v>2485509</v>
+      </c>
+      <c r="T544" t="n">
+        <v>1197.587487894075</v>
+      </c>
+      <c r="U544" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V544" t="n">
+        <v>0.003302348336594818</v>
+      </c>
+      <c r="W544" t="n">
+        <v>-0.00595512600397341</v>
+      </c>
+      <c r="X544" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y544" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z544" t="n">
+        <v>0.4108201563358307</v>
+      </c>
+      <c r="AA544" t="n">
+        <v>10.51282495260239</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E545" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F545" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H545" t="n">
+        <v>1</v>
+      </c>
+      <c r="I545" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J545" t="n">
+        <v>30</v>
+      </c>
+      <c r="K545" t="n">
+        <v>9</v>
+      </c>
+      <c r="L545" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M545" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N545" s="2" t="n">
+        <v>45834.54181311137</v>
+      </c>
+      <c r="O545" t="n">
+        <v>46.56</v>
+      </c>
+      <c r="P545" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q545" t="n">
+        <v>1</v>
+      </c>
+      <c r="R545" t="n">
+        <v>46.56</v>
+      </c>
+      <c r="S545" t="n">
+        <v>1396.8</v>
+      </c>
+      <c r="T545" t="n">
+        <v>1396.8</v>
+      </c>
+      <c r="U545" t="n">
+        <v>41.904</v>
+      </c>
+      <c r="V545" t="n">
+        <v>0.01926444833625229</v>
+      </c>
+      <c r="W545" t="n">
+        <v>0.01926444833625229</v>
+      </c>
+      <c r="X545" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y545" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z545" t="n">
+        <v>0.5990515947341919</v>
+      </c>
+      <c r="AA545" t="n">
         <v>12.27674007415771</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA545"/>
+  <dimension ref="A1:AA553"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50944,7 +50944,7 @@
         <v>100</v>
       </c>
       <c r="N538" s="2" t="n">
-        <v>45834.54181311137</v>
+        <v>45834.54181311343</v>
       </c>
       <c r="O538" t="n">
         <v>1</v>
@@ -51035,7 +51035,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N539" s="2" t="n">
-        <v>45834.54181311137</v>
+        <v>45834.54181311343</v>
       </c>
       <c r="O539" t="n">
         <v>375</v>
@@ -51130,7 +51130,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N540" s="2" t="n">
-        <v>45834.54181311137</v>
+        <v>45834.54181311343</v>
       </c>
       <c r="O540" t="n">
         <v>0.725</v>
@@ -51225,7 +51225,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N541" s="2" t="n">
-        <v>45834.54181311137</v>
+        <v>45834.54181311343</v>
       </c>
       <c r="O541" t="n">
         <v>25.15</v>
@@ -51320,7 +51320,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N542" s="2" t="n">
-        <v>45834.54181311137</v>
+        <v>45834.54181311343</v>
       </c>
       <c r="O542" t="n">
         <v>14.02</v>
@@ -51411,7 +51411,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N543" s="2" t="n">
-        <v>45834.54181311137</v>
+        <v>45834.54181311343</v>
       </c>
       <c r="O543" t="n">
         <v>38.7</v>
@@ -51506,7 +51506,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N544" s="2" t="n">
-        <v>45834.54181311137</v>
+        <v>45834.54181311343</v>
       </c>
       <c r="O544" t="n">
         <v>24609</v>
@@ -51601,7 +51601,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N545" s="2" t="n">
-        <v>45834.54181311137</v>
+        <v>45834.54181311343</v>
       </c>
       <c r="O545" t="n">
         <v>46.56</v>
@@ -51642,6 +51642,760 @@
         <v>0.5990515947341919</v>
       </c>
       <c r="AA545" t="n">
+        <v>12.27674007415771</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F546" t="n">
+        <v>1</v>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H546" t="n">
+        <v>1</v>
+      </c>
+      <c r="I546" t="n">
+        <v>1</v>
+      </c>
+      <c r="J546" t="n">
+        <v>1</v>
+      </c>
+      <c r="K546" t="n">
+        <v>100</v>
+      </c>
+      <c r="L546" t="n">
+        <v>100</v>
+      </c>
+      <c r="M546" t="n">
+        <v>100</v>
+      </c>
+      <c r="N546" s="2" t="n">
+        <v>45834.5713877244</v>
+      </c>
+      <c r="O546" t="n">
+        <v>1</v>
+      </c>
+      <c r="P546" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q546" t="n">
+        <v>1</v>
+      </c>
+      <c r="R546" t="n">
+        <v>1</v>
+      </c>
+      <c r="S546" t="n">
+        <v>0</v>
+      </c>
+      <c r="T546" t="n">
+        <v>45.43580260334033</v>
+      </c>
+      <c r="U546" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V546" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W546" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X546" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y546" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z546" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA546" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr"/>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E547" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F547" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H547" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I547" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J547" t="n">
+        <v>3</v>
+      </c>
+      <c r="K547" t="n">
+        <v>10</v>
+      </c>
+      <c r="L547" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M547" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N547" s="2" t="n">
+        <v>45834.5713877244</v>
+      </c>
+      <c r="O547" t="n">
+        <v>372</v>
+      </c>
+      <c r="P547" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q547" t="n">
+        <v>0.85321</v>
+      </c>
+      <c r="R547" t="n">
+        <v>436.0005156995347</v>
+      </c>
+      <c r="S547" t="n">
+        <v>1116</v>
+      </c>
+      <c r="T547" t="n">
+        <v>1308.001547098604</v>
+      </c>
+      <c r="U547" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V547" t="n">
+        <v>0.01178787268879899</v>
+      </c>
+      <c r="W547" t="n">
+        <v>0.01233336843010169</v>
+      </c>
+      <c r="X547" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y547" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z547" t="n">
+        <v>0.5015593767166138</v>
+      </c>
+      <c r="AA547" t="n">
+        <v>12.0281548500061</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E548" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F548" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H548" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I548" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J548" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K548" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L548" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M548" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N548" s="2" t="n">
+        <v>45834.5713877244</v>
+      </c>
+      <c r="O548" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="P548" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q548" t="n">
+        <v>1.79065</v>
+      </c>
+      <c r="R548" t="n">
+        <v>0.4048809091670622</v>
+      </c>
+      <c r="S548" t="n">
+        <v>2656.4</v>
+      </c>
+      <c r="T548" t="n">
+        <v>1483.483651188116</v>
+      </c>
+      <c r="U548" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="V548" t="n">
+        <v>0</v>
+      </c>
+      <c r="W548" t="n">
+        <v>-0.008979979337112254</v>
+      </c>
+      <c r="X548" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y548" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z548" t="n">
+        <v>0.4815215170383453</v>
+      </c>
+      <c r="AA548" t="n">
+        <v>11.57751679420471</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E549" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F549" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H549" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I549" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J549" t="n">
+        <v>537</v>
+      </c>
+      <c r="K549" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L549" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M549" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N549" s="2" t="n">
+        <v>45834.5713877244</v>
+      </c>
+      <c r="O549" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="P549" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q549" t="n">
+        <v>9.19158</v>
+      </c>
+      <c r="R549" t="n">
+        <v>2.736199869880913</v>
+      </c>
+      <c r="S549" t="n">
+        <v>13505.55</v>
+      </c>
+      <c r="T549" t="n">
+        <v>1469.33933012605</v>
+      </c>
+      <c r="U549" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V549" t="n">
+        <v>-0.001984126984126977</v>
+      </c>
+      <c r="W549" t="n">
+        <v>-0.018383953505826</v>
+      </c>
+      <c r="X549" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y549" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z549" t="n">
+        <v>0.4985511600971222</v>
+      </c>
+      <c r="AA549" t="n">
+        <v>9.835646152496338</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E550" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F550" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H550" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I550" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J550" t="n">
+        <v>121</v>
+      </c>
+      <c r="K550" t="n">
+        <v>12</v>
+      </c>
+      <c r="L550" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M550" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N550" s="2" t="n">
+        <v>45834.5713877244</v>
+      </c>
+      <c r="O550" t="n">
+        <v>13.78</v>
+      </c>
+      <c r="P550" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q550" t="n">
+        <v>1.1713717</v>
+      </c>
+      <c r="R550" t="n">
+        <v>11.76398576130873</v>
+      </c>
+      <c r="S550" t="n">
+        <v>1667.38</v>
+      </c>
+      <c r="T550" t="n">
+        <v>1423.442277118356</v>
+      </c>
+      <c r="U550" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V550" t="n">
+        <v>-0.02820874471086043</v>
+      </c>
+      <c r="W550" t="n">
+        <v>-0.04564806546473155</v>
+      </c>
+      <c r="X550" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y550" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z550" t="n">
+        <v>0.5161105990409851</v>
+      </c>
+      <c r="AA550" t="n">
+        <v>13.94983839988708</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr"/>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E551" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F551" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H551" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I551" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J551" t="n">
+        <v>162</v>
+      </c>
+      <c r="K551" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L551" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M551" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N551" s="2" t="n">
+        <v>45834.5713877244</v>
+      </c>
+      <c r="O551" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="P551" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q551" t="n">
+        <v>4.24271</v>
+      </c>
+      <c r="R551" t="n">
+        <v>9.145098298021782</v>
+      </c>
+      <c r="S551" t="n">
+        <v>6285.599999999999</v>
+      </c>
+      <c r="T551" t="n">
+        <v>1481.505924279529</v>
+      </c>
+      <c r="U551" t="n">
+        <v>8.272543736854324</v>
+      </c>
+      <c r="V551" t="n">
+        <v>-0.01020408163265318</v>
+      </c>
+      <c r="W551" t="n">
+        <v>-0.005071628506212456</v>
+      </c>
+      <c r="X551" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y551" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z551" t="n">
+        <v>0.5935001373291016</v>
+      </c>
+      <c r="AA551" t="n">
+        <v>12.80392378997803</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E552" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F552" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H552" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I552" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J552" t="n">
+        <v>101</v>
+      </c>
+      <c r="K552" t="n">
+        <v>11</v>
+      </c>
+      <c r="L552" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M552" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N552" s="2" t="n">
+        <v>45834.5713877244</v>
+      </c>
+      <c r="O552" t="n">
+        <v>24396</v>
+      </c>
+      <c r="P552" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q552" t="n">
+        <v>2077.07</v>
+      </c>
+      <c r="R552" t="n">
+        <v>11.74539134453822</v>
+      </c>
+      <c r="S552" t="n">
+        <v>2463996</v>
+      </c>
+      <c r="T552" t="n">
+        <v>1186.28452579836</v>
+      </c>
+      <c r="U552" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V552" t="n">
+        <v>-0.005381604696673148</v>
+      </c>
+      <c r="W552" t="n">
+        <v>-0.01533703057945823</v>
+      </c>
+      <c r="X552" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y552" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z552" t="n">
+        <v>0.4108201563358307</v>
+      </c>
+      <c r="AA552" t="n">
+        <v>10.51282495260239</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E553" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F553" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H553" t="n">
+        <v>1</v>
+      </c>
+      <c r="I553" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J553" t="n">
+        <v>30</v>
+      </c>
+      <c r="K553" t="n">
+        <v>9</v>
+      </c>
+      <c r="L553" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M553" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N553" s="2" t="n">
+        <v>45834.5713877244</v>
+      </c>
+      <c r="O553" t="n">
+        <v>46.66</v>
+      </c>
+      <c r="P553" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q553" t="n">
+        <v>1</v>
+      </c>
+      <c r="R553" t="n">
+        <v>46.66</v>
+      </c>
+      <c r="S553" t="n">
+        <v>1399.8</v>
+      </c>
+      <c r="T553" t="n">
+        <v>1399.8</v>
+      </c>
+      <c r="U553" t="n">
+        <v>41.994</v>
+      </c>
+      <c r="V553" t="n">
+        <v>0.02145359019264448</v>
+      </c>
+      <c r="W553" t="n">
+        <v>0.02145359019264448</v>
+      </c>
+      <c r="X553" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y553" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z553" t="n">
+        <v>0.5990515947341919</v>
+      </c>
+      <c r="AA553" t="n">
         <v>12.27674007415771</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA553"/>
+  <dimension ref="A1:AA561"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51698,7 +51698,7 @@
         <v>100</v>
       </c>
       <c r="N546" s="2" t="n">
-        <v>45834.5713877244</v>
+        <v>45834.57138771991</v>
       </c>
       <c r="O546" t="n">
         <v>1</v>
@@ -51789,7 +51789,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N547" s="2" t="n">
-        <v>45834.5713877244</v>
+        <v>45834.57138771991</v>
       </c>
       <c r="O547" t="n">
         <v>372</v>
@@ -51884,7 +51884,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N548" s="2" t="n">
-        <v>45834.5713877244</v>
+        <v>45834.57138771991</v>
       </c>
       <c r="O548" t="n">
         <v>0.725</v>
@@ -51979,7 +51979,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N549" s="2" t="n">
-        <v>45834.5713877244</v>
+        <v>45834.57138771991</v>
       </c>
       <c r="O549" t="n">
         <v>25.15</v>
@@ -52074,7 +52074,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N550" s="2" t="n">
-        <v>45834.5713877244</v>
+        <v>45834.57138771991</v>
       </c>
       <c r="O550" t="n">
         <v>13.78</v>
@@ -52165,7 +52165,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N551" s="2" t="n">
-        <v>45834.5713877244</v>
+        <v>45834.57138771991</v>
       </c>
       <c r="O551" t="n">
         <v>38.8</v>
@@ -52260,7 +52260,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N552" s="2" t="n">
-        <v>45834.5713877244</v>
+        <v>45834.57138771991</v>
       </c>
       <c r="O552" t="n">
         <v>24396</v>
@@ -52355,7 +52355,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N553" s="2" t="n">
-        <v>45834.5713877244</v>
+        <v>45834.57138771991</v>
       </c>
       <c r="O553" t="n">
         <v>46.66</v>
@@ -52396,6 +52396,760 @@
         <v>0.5990515947341919</v>
       </c>
       <c r="AA553" t="n">
+        <v>12.27674007415771</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F554" t="n">
+        <v>1</v>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H554" t="n">
+        <v>1</v>
+      </c>
+      <c r="I554" t="n">
+        <v>1</v>
+      </c>
+      <c r="J554" t="n">
+        <v>1</v>
+      </c>
+      <c r="K554" t="n">
+        <v>100</v>
+      </c>
+      <c r="L554" t="n">
+        <v>100</v>
+      </c>
+      <c r="M554" t="n">
+        <v>100</v>
+      </c>
+      <c r="N554" s="2" t="n">
+        <v>45834.60669588256</v>
+      </c>
+      <c r="O554" t="n">
+        <v>1</v>
+      </c>
+      <c r="P554" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q554" t="n">
+        <v>1</v>
+      </c>
+      <c r="R554" t="n">
+        <v>1</v>
+      </c>
+      <c r="S554" t="n">
+        <v>0</v>
+      </c>
+      <c r="T554" t="n">
+        <v>45.43580260334033</v>
+      </c>
+      <c r="U554" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V554" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W554" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X554" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y554" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z554" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA554" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr"/>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E555" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F555" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H555" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I555" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J555" t="n">
+        <v>3</v>
+      </c>
+      <c r="K555" t="n">
+        <v>10</v>
+      </c>
+      <c r="L555" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M555" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N555" s="2" t="n">
+        <v>45834.60669588256</v>
+      </c>
+      <c r="O555" t="n">
+        <v>371.61</v>
+      </c>
+      <c r="P555" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q555" t="n">
+        <v>0.85228</v>
+      </c>
+      <c r="R555" t="n">
+        <v>436.0186793072699</v>
+      </c>
+      <c r="S555" t="n">
+        <v>1114.83</v>
+      </c>
+      <c r="T555" t="n">
+        <v>1308.05603792181</v>
+      </c>
+      <c r="U555" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V555" t="n">
+        <v>0.01072712733839953</v>
+      </c>
+      <c r="W555" t="n">
+        <v>0.01237554183480971</v>
+      </c>
+      <c r="X555" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y555" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z555" t="n">
+        <v>0.5015593767166138</v>
+      </c>
+      <c r="AA555" t="n">
+        <v>12.0281548500061</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E556" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F556" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H556" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I556" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J556" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K556" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L556" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M556" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N556" s="2" t="n">
+        <v>45834.60669588256</v>
+      </c>
+      <c r="O556" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="P556" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q556" t="n">
+        <v>1.78749</v>
+      </c>
+      <c r="R556" t="n">
+        <v>0.4055966746667114</v>
+      </c>
+      <c r="S556" t="n">
+        <v>2656.4</v>
+      </c>
+      <c r="T556" t="n">
+        <v>1486.106215978831</v>
+      </c>
+      <c r="U556" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="V556" t="n">
+        <v>0</v>
+      </c>
+      <c r="W556" t="n">
+        <v>-0.007228012464405409</v>
+      </c>
+      <c r="X556" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y556" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z556" t="n">
+        <v>0.4815215170383453</v>
+      </c>
+      <c r="AA556" t="n">
+        <v>11.57751679420471</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E557" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F557" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H557" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I557" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J557" t="n">
+        <v>537</v>
+      </c>
+      <c r="K557" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L557" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M557" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N557" s="2" t="n">
+        <v>45834.60669588256</v>
+      </c>
+      <c r="O557" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="P557" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q557" t="n">
+        <v>9.19533</v>
+      </c>
+      <c r="R557" t="n">
+        <v>2.735084004597986</v>
+      </c>
+      <c r="S557" t="n">
+        <v>13505.55</v>
+      </c>
+      <c r="T557" t="n">
+        <v>1468.740110469118</v>
+      </c>
+      <c r="U557" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V557" t="n">
+        <v>-0.001984126984126977</v>
+      </c>
+      <c r="W557" t="n">
+        <v>-0.0187842719472906</v>
+      </c>
+      <c r="X557" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y557" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z557" t="n">
+        <v>0.4985511600971222</v>
+      </c>
+      <c r="AA557" t="n">
+        <v>9.835646152496338</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E558" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F558" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H558" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I558" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J558" t="n">
+        <v>121</v>
+      </c>
+      <c r="K558" t="n">
+        <v>12</v>
+      </c>
+      <c r="L558" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M558" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N558" s="2" t="n">
+        <v>45834.60669588256</v>
+      </c>
+      <c r="O558" t="n">
+        <v>13.78</v>
+      </c>
+      <c r="P558" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q558" t="n">
+        <v>1.1719208</v>
+      </c>
+      <c r="R558" t="n">
+        <v>11.75847378082205</v>
+      </c>
+      <c r="S558" t="n">
+        <v>1667.38</v>
+      </c>
+      <c r="T558" t="n">
+        <v>1422.775327479468</v>
+      </c>
+      <c r="U558" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V558" t="n">
+        <v>-0.02820874471086043</v>
+      </c>
+      <c r="W558" t="n">
+        <v>-0.04609522422089796</v>
+      </c>
+      <c r="X558" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y558" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z558" t="n">
+        <v>0.5161105990409851</v>
+      </c>
+      <c r="AA558" t="n">
+        <v>13.94983839988708</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr"/>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E559" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F559" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H559" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I559" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J559" t="n">
+        <v>162</v>
+      </c>
+      <c r="K559" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L559" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M559" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N559" s="2" t="n">
+        <v>45834.60669588256</v>
+      </c>
+      <c r="O559" t="n">
+        <v>38.75</v>
+      </c>
+      <c r="P559" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q559" t="n">
+        <v>4.24059</v>
+      </c>
+      <c r="R559" t="n">
+        <v>9.137879398857235</v>
+      </c>
+      <c r="S559" t="n">
+        <v>6277.5</v>
+      </c>
+      <c r="T559" t="n">
+        <v>1480.336462614872</v>
+      </c>
+      <c r="U559" t="n">
+        <v>8.272543736854324</v>
+      </c>
+      <c r="V559" t="n">
+        <v>-0.01147959183673475</v>
+      </c>
+      <c r="W559" t="n">
+        <v>-0.005856998696417426</v>
+      </c>
+      <c r="X559" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y559" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z559" t="n">
+        <v>0.5935001373291016</v>
+      </c>
+      <c r="AA559" t="n">
+        <v>12.80392378997803</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E560" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F560" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H560" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I560" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J560" t="n">
+        <v>101</v>
+      </c>
+      <c r="K560" t="n">
+        <v>11</v>
+      </c>
+      <c r="L560" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M560" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N560" s="2" t="n">
+        <v>45834.60669588256</v>
+      </c>
+      <c r="O560" t="n">
+        <v>24449</v>
+      </c>
+      <c r="P560" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q560" t="n">
+        <v>2078.17</v>
+      </c>
+      <c r="R560" t="n">
+        <v>11.7646775769066</v>
+      </c>
+      <c r="S560" t="n">
+        <v>2469349</v>
+      </c>
+      <c r="T560" t="n">
+        <v>1188.232435267567</v>
+      </c>
+      <c r="U560" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V560" t="n">
+        <v>-0.003220808871493785</v>
+      </c>
+      <c r="W560" t="n">
+        <v>-0.01372018885186255</v>
+      </c>
+      <c r="X560" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y560" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z560" t="n">
+        <v>0.4108201563358307</v>
+      </c>
+      <c r="AA560" t="n">
+        <v>10.51282495260239</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E561" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F561" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H561" t="n">
+        <v>1</v>
+      </c>
+      <c r="I561" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J561" t="n">
+        <v>30</v>
+      </c>
+      <c r="K561" t="n">
+        <v>9</v>
+      </c>
+      <c r="L561" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M561" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N561" s="2" t="n">
+        <v>45834.60669588256</v>
+      </c>
+      <c r="O561" t="n">
+        <v>46.68</v>
+      </c>
+      <c r="P561" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q561" t="n">
+        <v>1</v>
+      </c>
+      <c r="R561" t="n">
+        <v>46.68</v>
+      </c>
+      <c r="S561" t="n">
+        <v>1400.4</v>
+      </c>
+      <c r="T561" t="n">
+        <v>1400.4</v>
+      </c>
+      <c r="U561" t="n">
+        <v>42.012</v>
+      </c>
+      <c r="V561" t="n">
+        <v>0.02189141856392296</v>
+      </c>
+      <c r="W561" t="n">
+        <v>0.02189141856392296</v>
+      </c>
+      <c r="X561" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y561" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z561" t="n">
+        <v>0.5990515947341919</v>
+      </c>
+      <c r="AA561" t="n">
         <v>12.27674007415771</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA561"/>
+  <dimension ref="A1:AA569"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52452,7 +52452,7 @@
         <v>100</v>
       </c>
       <c r="N554" s="2" t="n">
-        <v>45834.60669588256</v>
+        <v>45834.60669587963</v>
       </c>
       <c r="O554" t="n">
         <v>1</v>
@@ -52543,7 +52543,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N555" s="2" t="n">
-        <v>45834.60669588256</v>
+        <v>45834.60669587963</v>
       </c>
       <c r="O555" t="n">
         <v>371.61</v>
@@ -52638,7 +52638,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N556" s="2" t="n">
-        <v>45834.60669588256</v>
+        <v>45834.60669587963</v>
       </c>
       <c r="O556" t="n">
         <v>0.725</v>
@@ -52733,7 +52733,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N557" s="2" t="n">
-        <v>45834.60669588256</v>
+        <v>45834.60669587963</v>
       </c>
       <c r="O557" t="n">
         <v>25.15</v>
@@ -52828,7 +52828,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N558" s="2" t="n">
-        <v>45834.60669588256</v>
+        <v>45834.60669587963</v>
       </c>
       <c r="O558" t="n">
         <v>13.78</v>
@@ -52919,7 +52919,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N559" s="2" t="n">
-        <v>45834.60669588256</v>
+        <v>45834.60669587963</v>
       </c>
       <c r="O559" t="n">
         <v>38.75</v>
@@ -53014,7 +53014,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N560" s="2" t="n">
-        <v>45834.60669588256</v>
+        <v>45834.60669587963</v>
       </c>
       <c r="O560" t="n">
         <v>24449</v>
@@ -53109,7 +53109,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N561" s="2" t="n">
-        <v>45834.60669588256</v>
+        <v>45834.60669587963</v>
       </c>
       <c r="O561" t="n">
         <v>46.68</v>
@@ -53150,6 +53150,760 @@
         <v>0.5990515947341919</v>
       </c>
       <c r="AA561" t="n">
+        <v>12.27674007415771</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F562" t="n">
+        <v>1</v>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H562" t="n">
+        <v>1</v>
+      </c>
+      <c r="I562" t="n">
+        <v>1</v>
+      </c>
+      <c r="J562" t="n">
+        <v>1</v>
+      </c>
+      <c r="K562" t="n">
+        <v>100</v>
+      </c>
+      <c r="L562" t="n">
+        <v>100</v>
+      </c>
+      <c r="M562" t="n">
+        <v>100</v>
+      </c>
+      <c r="N562" s="2" t="n">
+        <v>45834.64761854877</v>
+      </c>
+      <c r="O562" t="n">
+        <v>1</v>
+      </c>
+      <c r="P562" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q562" t="n">
+        <v>1</v>
+      </c>
+      <c r="R562" t="n">
+        <v>1</v>
+      </c>
+      <c r="S562" t="n">
+        <v>0</v>
+      </c>
+      <c r="T562" t="n">
+        <v>45.43580260334033</v>
+      </c>
+      <c r="U562" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V562" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W562" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X562" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y562" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z562" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA562" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr"/>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E563" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F563" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H563" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I563" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J563" t="n">
+        <v>3</v>
+      </c>
+      <c r="K563" t="n">
+        <v>10</v>
+      </c>
+      <c r="L563" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M563" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N563" s="2" t="n">
+        <v>45834.64761854877</v>
+      </c>
+      <c r="O563" t="n">
+        <v>376.5</v>
+      </c>
+      <c r="P563" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q563" t="n">
+        <v>0.85214</v>
+      </c>
+      <c r="R563" t="n">
+        <v>441.8288074729505</v>
+      </c>
+      <c r="S563" t="n">
+        <v>1129.5</v>
+      </c>
+      <c r="T563" t="n">
+        <v>1325.486422418851</v>
+      </c>
+      <c r="U563" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V563" t="n">
+        <v>0.02402724211648621</v>
+      </c>
+      <c r="W563" t="n">
+        <v>0.02586586215596132</v>
+      </c>
+      <c r="X563" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y563" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z563" t="n">
+        <v>0.5015593767166138</v>
+      </c>
+      <c r="AA563" t="n">
+        <v>12.0281548500061</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E564" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F564" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H564" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I564" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J564" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K564" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L564" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M564" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N564" s="2" t="n">
+        <v>45834.64761854877</v>
+      </c>
+      <c r="O564" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="P564" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q564" t="n">
+        <v>1.78768</v>
+      </c>
+      <c r="R564" t="n">
+        <v>0.4055535666338494</v>
+      </c>
+      <c r="S564" t="n">
+        <v>2656.4</v>
+      </c>
+      <c r="T564" t="n">
+        <v>1485.948268146424</v>
+      </c>
+      <c r="U564" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="V564" t="n">
+        <v>0</v>
+      </c>
+      <c r="W564" t="n">
+        <v>-0.00733352725319969</v>
+      </c>
+      <c r="X564" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y564" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z564" t="n">
+        <v>0.4815215170383453</v>
+      </c>
+      <c r="AA564" t="n">
+        <v>11.57751679420471</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E565" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F565" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H565" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I565" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J565" t="n">
+        <v>537</v>
+      </c>
+      <c r="K565" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L565" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M565" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N565" s="2" t="n">
+        <v>45834.64761854877</v>
+      </c>
+      <c r="O565" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="P565" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q565" t="n">
+        <v>9.185359999999999</v>
+      </c>
+      <c r="R565" t="n">
+        <v>2.738052727383576</v>
+      </c>
+      <c r="S565" t="n">
+        <v>13505.55</v>
+      </c>
+      <c r="T565" t="n">
+        <v>1470.33431460498</v>
+      </c>
+      <c r="U565" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V565" t="n">
+        <v>-0.001984126984126977</v>
+      </c>
+      <c r="W565" t="n">
+        <v>-0.01771923793570196</v>
+      </c>
+      <c r="X565" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y565" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z565" t="n">
+        <v>0.4985511600971222</v>
+      </c>
+      <c r="AA565" t="n">
+        <v>9.835646152496338</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E566" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F566" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H566" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I566" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J566" t="n">
+        <v>121</v>
+      </c>
+      <c r="K566" t="n">
+        <v>12</v>
+      </c>
+      <c r="L566" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M566" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N566" s="2" t="n">
+        <v>45834.64761854877</v>
+      </c>
+      <c r="O566" t="n">
+        <v>13.94</v>
+      </c>
+      <c r="P566" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q566" t="n">
+        <v>1.170275</v>
+      </c>
+      <c r="R566" t="n">
+        <v>11.91173014889663</v>
+      </c>
+      <c r="S566" t="n">
+        <v>1686.74</v>
+      </c>
+      <c r="T566" t="n">
+        <v>1441.319348016492</v>
+      </c>
+      <c r="U566" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V566" t="n">
+        <v>-0.01692524682651619</v>
+      </c>
+      <c r="W566" t="n">
+        <v>-0.03366231973431921</v>
+      </c>
+      <c r="X566" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y566" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z566" t="n">
+        <v>0.5161105990409851</v>
+      </c>
+      <c r="AA566" t="n">
+        <v>13.94983839988708</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr"/>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E567" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F567" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H567" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I567" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J567" t="n">
+        <v>162</v>
+      </c>
+      <c r="K567" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L567" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M567" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N567" s="2" t="n">
+        <v>45834.64761854877</v>
+      </c>
+      <c r="O567" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="P567" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q567" t="n">
+        <v>4.2391</v>
+      </c>
+      <c r="R567" t="n">
+        <v>9.152886225849826</v>
+      </c>
+      <c r="S567" t="n">
+        <v>6285.599999999999</v>
+      </c>
+      <c r="T567" t="n">
+        <v>1482.767568587672</v>
+      </c>
+      <c r="U567" t="n">
+        <v>8.272543736854324</v>
+      </c>
+      <c r="V567" t="n">
+        <v>-0.01020408163265318</v>
+      </c>
+      <c r="W567" t="n">
+        <v>-0.004224351626428313</v>
+      </c>
+      <c r="X567" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y567" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z567" t="n">
+        <v>0.5935001373291016</v>
+      </c>
+      <c r="AA567" t="n">
+        <v>12.80392378997803</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E568" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F568" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H568" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I568" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J568" t="n">
+        <v>101</v>
+      </c>
+      <c r="K568" t="n">
+        <v>11</v>
+      </c>
+      <c r="L568" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M568" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N568" s="2" t="n">
+        <v>45834.64761854877</v>
+      </c>
+      <c r="O568" t="n">
+        <v>24440</v>
+      </c>
+      <c r="P568" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q568" t="n">
+        <v>2081.51</v>
+      </c>
+      <c r="R568" t="n">
+        <v>11.74147613991765</v>
+      </c>
+      <c r="S568" t="n">
+        <v>2468440</v>
+      </c>
+      <c r="T568" t="n">
+        <v>1185.889090131683</v>
+      </c>
+      <c r="U568" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V568" t="n">
+        <v>-0.003587736464448765</v>
+      </c>
+      <c r="W568" t="n">
+        <v>-0.01566525778743166</v>
+      </c>
+      <c r="X568" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y568" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z568" t="n">
+        <v>0.4108201563358307</v>
+      </c>
+      <c r="AA568" t="n">
+        <v>10.51282495260239</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E569" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F569" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H569" t="n">
+        <v>1</v>
+      </c>
+      <c r="I569" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J569" t="n">
+        <v>30</v>
+      </c>
+      <c r="K569" t="n">
+        <v>9</v>
+      </c>
+      <c r="L569" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M569" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N569" s="2" t="n">
+        <v>45834.64761854877</v>
+      </c>
+      <c r="O569" t="n">
+        <v>46.68</v>
+      </c>
+      <c r="P569" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q569" t="n">
+        <v>1</v>
+      </c>
+      <c r="R569" t="n">
+        <v>46.68</v>
+      </c>
+      <c r="S569" t="n">
+        <v>1400.4</v>
+      </c>
+      <c r="T569" t="n">
+        <v>1400.4</v>
+      </c>
+      <c r="U569" t="n">
+        <v>42.012</v>
+      </c>
+      <c r="V569" t="n">
+        <v>0.02189141856392296</v>
+      </c>
+      <c r="W569" t="n">
+        <v>0.02189141856392296</v>
+      </c>
+      <c r="X569" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y569" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z569" t="n">
+        <v>0.5990515947341919</v>
+      </c>
+      <c r="AA569" t="n">
         <v>12.27674007415771</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA569"/>
+  <dimension ref="A1:AA577"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53206,7 +53206,7 @@
         <v>100</v>
       </c>
       <c r="N562" s="2" t="n">
-        <v>45834.64761854877</v>
+        <v>45834.64761855324</v>
       </c>
       <c r="O562" t="n">
         <v>1</v>
@@ -53297,7 +53297,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N563" s="2" t="n">
-        <v>45834.64761854877</v>
+        <v>45834.64761855324</v>
       </c>
       <c r="O563" t="n">
         <v>376.5</v>
@@ -53392,7 +53392,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N564" s="2" t="n">
-        <v>45834.64761854877</v>
+        <v>45834.64761855324</v>
       </c>
       <c r="O564" t="n">
         <v>0.725</v>
@@ -53487,7 +53487,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N565" s="2" t="n">
-        <v>45834.64761854877</v>
+        <v>45834.64761855324</v>
       </c>
       <c r="O565" t="n">
         <v>25.15</v>
@@ -53582,7 +53582,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N566" s="2" t="n">
-        <v>45834.64761854877</v>
+        <v>45834.64761855324</v>
       </c>
       <c r="O566" t="n">
         <v>13.94</v>
@@ -53673,7 +53673,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N567" s="2" t="n">
-        <v>45834.64761854877</v>
+        <v>45834.64761855324</v>
       </c>
       <c r="O567" t="n">
         <v>38.8</v>
@@ -53768,7 +53768,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N568" s="2" t="n">
-        <v>45834.64761854877</v>
+        <v>45834.64761855324</v>
       </c>
       <c r="O568" t="n">
         <v>24440</v>
@@ -53863,7 +53863,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N569" s="2" t="n">
-        <v>45834.64761854877</v>
+        <v>45834.64761855324</v>
       </c>
       <c r="O569" t="n">
         <v>46.68</v>
@@ -53904,6 +53904,760 @@
         <v>0.5990515947341919</v>
       </c>
       <c r="AA569" t="n">
+        <v>12.27674007415771</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F570" t="n">
+        <v>1</v>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H570" t="n">
+        <v>1</v>
+      </c>
+      <c r="I570" t="n">
+        <v>1</v>
+      </c>
+      <c r="J570" t="n">
+        <v>1</v>
+      </c>
+      <c r="K570" t="n">
+        <v>100</v>
+      </c>
+      <c r="L570" t="n">
+        <v>100</v>
+      </c>
+      <c r="M570" t="n">
+        <v>100</v>
+      </c>
+      <c r="N570" s="2" t="n">
+        <v>45834.69310634967</v>
+      </c>
+      <c r="O570" t="n">
+        <v>1</v>
+      </c>
+      <c r="P570" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q570" t="n">
+        <v>1</v>
+      </c>
+      <c r="R570" t="n">
+        <v>1</v>
+      </c>
+      <c r="S570" t="n">
+        <v>0</v>
+      </c>
+      <c r="T570" t="n">
+        <v>45.43580260334033</v>
+      </c>
+      <c r="U570" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V570" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W570" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X570" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y570" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z570" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA570" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr"/>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E571" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F571" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H571" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I571" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J571" t="n">
+        <v>3</v>
+      </c>
+      <c r="K571" t="n">
+        <v>10</v>
+      </c>
+      <c r="L571" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M571" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N571" s="2" t="n">
+        <v>45834.69310634967</v>
+      </c>
+      <c r="O571" t="n">
+        <v>376.5</v>
+      </c>
+      <c r="P571" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q571" t="n">
+        <v>0.8524</v>
+      </c>
+      <c r="R571" t="n">
+        <v>441.6940403566401</v>
+      </c>
+      <c r="S571" t="n">
+        <v>1129.5</v>
+      </c>
+      <c r="T571" t="n">
+        <v>1325.08212106992</v>
+      </c>
+      <c r="U571" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V571" t="n">
+        <v>0.02402724211648621</v>
+      </c>
+      <c r="W571" t="n">
+        <v>0.02555295140495173</v>
+      </c>
+      <c r="X571" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y571" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z571" t="n">
+        <v>0.5015593767166138</v>
+      </c>
+      <c r="AA571" t="n">
+        <v>12.0281548500061</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E572" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F572" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H572" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I572" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J572" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K572" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L572" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M572" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N572" s="2" t="n">
+        <v>45834.69310634967</v>
+      </c>
+      <c r="O572" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="P572" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q572" t="n">
+        <v>1.78907</v>
+      </c>
+      <c r="R572" t="n">
+        <v>0.4052384758561711</v>
+      </c>
+      <c r="S572" t="n">
+        <v>2656.4</v>
+      </c>
+      <c r="T572" t="n">
+        <v>1484.793775537011</v>
+      </c>
+      <c r="U572" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="V572" t="n">
+        <v>0</v>
+      </c>
+      <c r="W572" t="n">
+        <v>-0.008104769517123467</v>
+      </c>
+      <c r="X572" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y572" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z572" t="n">
+        <v>0.4815215170383453</v>
+      </c>
+      <c r="AA572" t="n">
+        <v>11.57751679420471</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E573" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F573" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H573" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I573" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J573" t="n">
+        <v>537</v>
+      </c>
+      <c r="K573" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L573" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M573" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N573" s="2" t="n">
+        <v>45834.69310634967</v>
+      </c>
+      <c r="O573" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="P573" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q573" t="n">
+        <v>9.21001</v>
+      </c>
+      <c r="R573" t="n">
+        <v>2.730724505185119</v>
+      </c>
+      <c r="S573" t="n">
+        <v>13505.55</v>
+      </c>
+      <c r="T573" t="n">
+        <v>1466.399059284409</v>
+      </c>
+      <c r="U573" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V573" t="n">
+        <v>-0.001984126984126977</v>
+      </c>
+      <c r="W573" t="n">
+        <v>-0.02034824928149703</v>
+      </c>
+      <c r="X573" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y573" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z573" t="n">
+        <v>0.4985511600971222</v>
+      </c>
+      <c r="AA573" t="n">
+        <v>9.835646152496338</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E574" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F574" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H574" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I574" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J574" t="n">
+        <v>121</v>
+      </c>
+      <c r="K574" t="n">
+        <v>12</v>
+      </c>
+      <c r="L574" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M574" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N574" s="2" t="n">
+        <v>45834.69310634967</v>
+      </c>
+      <c r="O574" t="n">
+        <v>13.915</v>
+      </c>
+      <c r="P574" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q574" t="n">
+        <v>1.1735711</v>
+      </c>
+      <c r="R574" t="n">
+        <v>11.85697227888451</v>
+      </c>
+      <c r="S574" t="n">
+        <v>1683.715</v>
+      </c>
+      <c r="T574" t="n">
+        <v>1434.693645745026</v>
+      </c>
+      <c r="U574" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V574" t="n">
+        <v>-0.01868829337094502</v>
+      </c>
+      <c r="W574" t="n">
+        <v>-0.03810454537428642</v>
+      </c>
+      <c r="X574" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y574" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z574" t="n">
+        <v>0.5161105990409851</v>
+      </c>
+      <c r="AA574" t="n">
+        <v>13.94983839988708</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr"/>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E575" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F575" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H575" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I575" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J575" t="n">
+        <v>162</v>
+      </c>
+      <c r="K575" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L575" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M575" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N575" s="2" t="n">
+        <v>45834.69310634967</v>
+      </c>
+      <c r="O575" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="P575" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q575" t="n">
+        <v>4.2395</v>
+      </c>
+      <c r="R575" t="n">
+        <v>9.152022644179738</v>
+      </c>
+      <c r="S575" t="n">
+        <v>6285.599999999999</v>
+      </c>
+      <c r="T575" t="n">
+        <v>1482.627668357117</v>
+      </c>
+      <c r="U575" t="n">
+        <v>8.272543736854324</v>
+      </c>
+      <c r="V575" t="n">
+        <v>-0.01020408163265318</v>
+      </c>
+      <c r="W575" t="n">
+        <v>-0.004318303804597856</v>
+      </c>
+      <c r="X575" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y575" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z575" t="n">
+        <v>0.5935001373291016</v>
+      </c>
+      <c r="AA575" t="n">
+        <v>12.80392378997803</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E576" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F576" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H576" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I576" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J576" t="n">
+        <v>101</v>
+      </c>
+      <c r="K576" t="n">
+        <v>11</v>
+      </c>
+      <c r="L576" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M576" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N576" s="2" t="n">
+        <v>45834.69310634967</v>
+      </c>
+      <c r="O576" t="n">
+        <v>24594</v>
+      </c>
+      <c r="P576" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q576" t="n">
+        <v>2085.43</v>
+      </c>
+      <c r="R576" t="n">
+        <v>11.79325127191994</v>
+      </c>
+      <c r="S576" t="n">
+        <v>2483994</v>
+      </c>
+      <c r="T576" t="n">
+        <v>1191.118378463914</v>
+      </c>
+      <c r="U576" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V576" t="n">
+        <v>0.002690802348336518</v>
+      </c>
+      <c r="W576" t="n">
+        <v>-0.01132474211417411</v>
+      </c>
+      <c r="X576" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y576" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z576" t="n">
+        <v>0.4108201563358307</v>
+      </c>
+      <c r="AA576" t="n">
+        <v>10.51282495260239</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E577" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F577" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H577" t="n">
+        <v>1</v>
+      </c>
+      <c r="I577" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J577" t="n">
+        <v>30</v>
+      </c>
+      <c r="K577" t="n">
+        <v>9</v>
+      </c>
+      <c r="L577" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M577" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N577" s="2" t="n">
+        <v>45834.69310634967</v>
+      </c>
+      <c r="O577" t="n">
+        <v>46.68</v>
+      </c>
+      <c r="P577" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q577" t="n">
+        <v>1</v>
+      </c>
+      <c r="R577" t="n">
+        <v>46.68</v>
+      </c>
+      <c r="S577" t="n">
+        <v>1400.4</v>
+      </c>
+      <c r="T577" t="n">
+        <v>1400.4</v>
+      </c>
+      <c r="U577" t="n">
+        <v>42.012</v>
+      </c>
+      <c r="V577" t="n">
+        <v>0.02189141856392296</v>
+      </c>
+      <c r="W577" t="n">
+        <v>0.02189141856392296</v>
+      </c>
+      <c r="X577" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y577" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z577" t="n">
+        <v>0.5990515947341919</v>
+      </c>
+      <c r="AA577" t="n">
         <v>12.27674007415771</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA577"/>
+  <dimension ref="A1:AA585"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53960,7 +53960,7 @@
         <v>100</v>
       </c>
       <c r="N570" s="2" t="n">
-        <v>45834.69310634967</v>
+        <v>45834.69310635416</v>
       </c>
       <c r="O570" t="n">
         <v>1</v>
@@ -54051,7 +54051,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N571" s="2" t="n">
-        <v>45834.69310634967</v>
+        <v>45834.69310635416</v>
       </c>
       <c r="O571" t="n">
         <v>376.5</v>
@@ -54146,7 +54146,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N572" s="2" t="n">
-        <v>45834.69310634967</v>
+        <v>45834.69310635416</v>
       </c>
       <c r="O572" t="n">
         <v>0.725</v>
@@ -54241,7 +54241,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N573" s="2" t="n">
-        <v>45834.69310634967</v>
+        <v>45834.69310635416</v>
       </c>
       <c r="O573" t="n">
         <v>25.15</v>
@@ -54336,7 +54336,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N574" s="2" t="n">
-        <v>45834.69310634967</v>
+        <v>45834.69310635416</v>
       </c>
       <c r="O574" t="n">
         <v>13.915</v>
@@ -54427,7 +54427,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N575" s="2" t="n">
-        <v>45834.69310634967</v>
+        <v>45834.69310635416</v>
       </c>
       <c r="O575" t="n">
         <v>38.8</v>
@@ -54522,7 +54522,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N576" s="2" t="n">
-        <v>45834.69310634967</v>
+        <v>45834.69310635416</v>
       </c>
       <c r="O576" t="n">
         <v>24594</v>
@@ -54617,7 +54617,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N577" s="2" t="n">
-        <v>45834.69310634967</v>
+        <v>45834.69310635416</v>
       </c>
       <c r="O577" t="n">
         <v>46.68</v>
@@ -54658,6 +54658,760 @@
         <v>0.5990515947341919</v>
       </c>
       <c r="AA577" t="n">
+        <v>12.27674007415771</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F578" t="n">
+        <v>1</v>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H578" t="n">
+        <v>1</v>
+      </c>
+      <c r="I578" t="n">
+        <v>1</v>
+      </c>
+      <c r="J578" t="n">
+        <v>1</v>
+      </c>
+      <c r="K578" t="n">
+        <v>100</v>
+      </c>
+      <c r="L578" t="n">
+        <v>100</v>
+      </c>
+      <c r="M578" t="n">
+        <v>100</v>
+      </c>
+      <c r="N578" s="2" t="n">
+        <v>45834.7303631262</v>
+      </c>
+      <c r="O578" t="n">
+        <v>1</v>
+      </c>
+      <c r="P578" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q578" t="n">
+        <v>1</v>
+      </c>
+      <c r="R578" t="n">
+        <v>1</v>
+      </c>
+      <c r="S578" t="n">
+        <v>0</v>
+      </c>
+      <c r="T578" t="n">
+        <v>45.43580260334033</v>
+      </c>
+      <c r="U578" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V578" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W578" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X578" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y578" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z578" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA578" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr"/>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E579" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F579" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H579" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I579" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J579" t="n">
+        <v>3</v>
+      </c>
+      <c r="K579" t="n">
+        <v>10</v>
+      </c>
+      <c r="L579" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M579" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N579" s="2" t="n">
+        <v>45834.7303631262</v>
+      </c>
+      <c r="O579" t="n">
+        <v>376.5</v>
+      </c>
+      <c r="P579" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q579" t="n">
+        <v>0.8522</v>
+      </c>
+      <c r="R579" t="n">
+        <v>441.7977000704061</v>
+      </c>
+      <c r="S579" t="n">
+        <v>1129.5</v>
+      </c>
+      <c r="T579" t="n">
+        <v>1325.393100211218</v>
+      </c>
+      <c r="U579" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V579" t="n">
+        <v>0.02402724211648621</v>
+      </c>
+      <c r="W579" t="n">
+        <v>0.02579363503588472</v>
+      </c>
+      <c r="X579" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y579" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z579" t="n">
+        <v>0.5015593767166138</v>
+      </c>
+      <c r="AA579" t="n">
+        <v>12.0281548500061</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E580" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F580" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H580" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I580" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J580" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K580" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L580" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M580" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N580" s="2" t="n">
+        <v>45834.7303631262</v>
+      </c>
+      <c r="O580" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="P580" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q580" t="n">
+        <v>1.78751</v>
+      </c>
+      <c r="R580" t="n">
+        <v>0.4055921365474878</v>
+      </c>
+      <c r="S580" t="n">
+        <v>2656.4</v>
+      </c>
+      <c r="T580" t="n">
+        <v>1486.089588309996</v>
+      </c>
+      <c r="U580" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="V580" t="n">
+        <v>0</v>
+      </c>
+      <c r="W580" t="n">
+        <v>-0.007239120340585603</v>
+      </c>
+      <c r="X580" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y580" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z580" t="n">
+        <v>0.4815215170383453</v>
+      </c>
+      <c r="AA580" t="n">
+        <v>11.57751679420471</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E581" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F581" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H581" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I581" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J581" t="n">
+        <v>537</v>
+      </c>
+      <c r="K581" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L581" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M581" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N581" s="2" t="n">
+        <v>45834.7303631262</v>
+      </c>
+      <c r="O581" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="P581" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q581" t="n">
+        <v>9.20589</v>
+      </c>
+      <c r="R581" t="n">
+        <v>2.731946612440514</v>
+      </c>
+      <c r="S581" t="n">
+        <v>13505.55</v>
+      </c>
+      <c r="T581" t="n">
+        <v>1467.055330880556</v>
+      </c>
+      <c r="U581" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V581" t="n">
+        <v>-0.001984126984126977</v>
+      </c>
+      <c r="W581" t="n">
+        <v>-0.01990981636377143</v>
+      </c>
+      <c r="X581" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y581" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z581" t="n">
+        <v>0.4985511600971222</v>
+      </c>
+      <c r="AA581" t="n">
+        <v>9.835646152496338</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E582" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F582" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H582" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I582" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J582" t="n">
+        <v>121</v>
+      </c>
+      <c r="K582" t="n">
+        <v>12</v>
+      </c>
+      <c r="L582" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M582" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N582" s="2" t="n">
+        <v>45834.7303631262</v>
+      </c>
+      <c r="O582" t="n">
+        <v>13.88</v>
+      </c>
+      <c r="P582" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q582" t="n">
+        <v>1.1727453</v>
+      </c>
+      <c r="R582" t="n">
+        <v>11.83547697867559</v>
+      </c>
+      <c r="S582" t="n">
+        <v>1679.48</v>
+      </c>
+      <c r="T582" t="n">
+        <v>1432.092714419746</v>
+      </c>
+      <c r="U582" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V582" t="n">
+        <v>-0.02115655853314524</v>
+      </c>
+      <c r="W582" t="n">
+        <v>-0.03984834902672441</v>
+      </c>
+      <c r="X582" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y582" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z582" t="n">
+        <v>0.5161105990409851</v>
+      </c>
+      <c r="AA582" t="n">
+        <v>13.94983839988708</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr"/>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E583" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F583" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H583" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I583" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J583" t="n">
+        <v>162</v>
+      </c>
+      <c r="K583" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L583" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M583" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N583" s="2" t="n">
+        <v>45834.7303631262</v>
+      </c>
+      <c r="O583" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="P583" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q583" t="n">
+        <v>4.23978</v>
+      </c>
+      <c r="R583" t="n">
+        <v>9.15141823396497</v>
+      </c>
+      <c r="S583" t="n">
+        <v>6285.599999999999</v>
+      </c>
+      <c r="T583" t="n">
+        <v>1482.529753902325</v>
+      </c>
+      <c r="U583" t="n">
+        <v>8.272543736854324</v>
+      </c>
+      <c r="V583" t="n">
+        <v>-0.01020408163265318</v>
+      </c>
+      <c r="W583" t="n">
+        <v>-0.004384059781307625</v>
+      </c>
+      <c r="X583" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y583" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z583" t="n">
+        <v>0.5935001373291016</v>
+      </c>
+      <c r="AA583" t="n">
+        <v>12.80392378997803</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E584" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F584" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H584" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I584" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J584" t="n">
+        <v>101</v>
+      </c>
+      <c r="K584" t="n">
+        <v>11</v>
+      </c>
+      <c r="L584" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M584" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N584" s="2" t="n">
+        <v>45834.7303631262</v>
+      </c>
+      <c r="O584" t="n">
+        <v>24594</v>
+      </c>
+      <c r="P584" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q584" t="n">
+        <v>2084.84</v>
+      </c>
+      <c r="R584" t="n">
+        <v>11.79658870704706</v>
+      </c>
+      <c r="S584" t="n">
+        <v>2483994</v>
+      </c>
+      <c r="T584" t="n">
+        <v>1191.455459411753</v>
+      </c>
+      <c r="U584" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V584" t="n">
+        <v>0.002690802348336518</v>
+      </c>
+      <c r="W584" t="n">
+        <v>-0.01104495162562236</v>
+      </c>
+      <c r="X584" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y584" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z584" t="n">
+        <v>0.4108201563358307</v>
+      </c>
+      <c r="AA584" t="n">
+        <v>10.51282495260239</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E585" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F585" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H585" t="n">
+        <v>1</v>
+      </c>
+      <c r="I585" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J585" t="n">
+        <v>30</v>
+      </c>
+      <c r="K585" t="n">
+        <v>9</v>
+      </c>
+      <c r="L585" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M585" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N585" s="2" t="n">
+        <v>45834.7303631262</v>
+      </c>
+      <c r="O585" t="n">
+        <v>46.68</v>
+      </c>
+      <c r="P585" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q585" t="n">
+        <v>1</v>
+      </c>
+      <c r="R585" t="n">
+        <v>46.68</v>
+      </c>
+      <c r="S585" t="n">
+        <v>1400.4</v>
+      </c>
+      <c r="T585" t="n">
+        <v>1400.4</v>
+      </c>
+      <c r="U585" t="n">
+        <v>42.012</v>
+      </c>
+      <c r="V585" t="n">
+        <v>0.02189141856392296</v>
+      </c>
+      <c r="W585" t="n">
+        <v>0.02189141856392296</v>
+      </c>
+      <c r="X585" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y585" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z585" t="n">
+        <v>0.5990515947341919</v>
+      </c>
+      <c r="AA585" t="n">
         <v>12.27674007415771</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA585"/>
+  <dimension ref="A1:AA593"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54714,7 +54714,7 @@
         <v>100</v>
       </c>
       <c r="N578" s="2" t="n">
-        <v>45834.7303631262</v>
+        <v>45834.730363125</v>
       </c>
       <c r="O578" t="n">
         <v>1</v>
@@ -54805,7 +54805,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N579" s="2" t="n">
-        <v>45834.7303631262</v>
+        <v>45834.730363125</v>
       </c>
       <c r="O579" t="n">
         <v>376.5</v>
@@ -54900,7 +54900,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N580" s="2" t="n">
-        <v>45834.7303631262</v>
+        <v>45834.730363125</v>
       </c>
       <c r="O580" t="n">
         <v>0.725</v>
@@ -54995,7 +54995,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N581" s="2" t="n">
-        <v>45834.7303631262</v>
+        <v>45834.730363125</v>
       </c>
       <c r="O581" t="n">
         <v>25.15</v>
@@ -55090,7 +55090,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N582" s="2" t="n">
-        <v>45834.7303631262</v>
+        <v>45834.730363125</v>
       </c>
       <c r="O582" t="n">
         <v>13.88</v>
@@ -55181,7 +55181,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N583" s="2" t="n">
-        <v>45834.7303631262</v>
+        <v>45834.730363125</v>
       </c>
       <c r="O583" t="n">
         <v>38.8</v>
@@ -55276,7 +55276,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N584" s="2" t="n">
-        <v>45834.7303631262</v>
+        <v>45834.730363125</v>
       </c>
       <c r="O584" t="n">
         <v>24594</v>
@@ -55371,7 +55371,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N585" s="2" t="n">
-        <v>45834.7303631262</v>
+        <v>45834.730363125</v>
       </c>
       <c r="O585" t="n">
         <v>46.68</v>
@@ -55412,6 +55412,760 @@
         <v>0.5990515947341919</v>
       </c>
       <c r="AA585" t="n">
+        <v>12.27674007415771</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F586" t="n">
+        <v>1</v>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H586" t="n">
+        <v>1</v>
+      </c>
+      <c r="I586" t="n">
+        <v>1</v>
+      </c>
+      <c r="J586" t="n">
+        <v>1</v>
+      </c>
+      <c r="K586" t="n">
+        <v>100</v>
+      </c>
+      <c r="L586" t="n">
+        <v>100</v>
+      </c>
+      <c r="M586" t="n">
+        <v>100</v>
+      </c>
+      <c r="N586" s="2" t="n">
+        <v>45834.77923869916</v>
+      </c>
+      <c r="O586" t="n">
+        <v>1</v>
+      </c>
+      <c r="P586" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q586" t="n">
+        <v>1</v>
+      </c>
+      <c r="R586" t="n">
+        <v>1</v>
+      </c>
+      <c r="S586" t="n">
+        <v>0</v>
+      </c>
+      <c r="T586" t="n">
+        <v>45.43580260334033</v>
+      </c>
+      <c r="U586" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V586" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W586" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X586" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y586" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z586" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA586" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr"/>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E587" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F587" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H587" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I587" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J587" t="n">
+        <v>3</v>
+      </c>
+      <c r="K587" t="n">
+        <v>10</v>
+      </c>
+      <c r="L587" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M587" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N587" s="2" t="n">
+        <v>45834.77923869916</v>
+      </c>
+      <c r="O587" t="n">
+        <v>376.5</v>
+      </c>
+      <c r="P587" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q587" t="n">
+        <v>0.85232</v>
+      </c>
+      <c r="R587" t="n">
+        <v>441.7354984043552</v>
+      </c>
+      <c r="S587" t="n">
+        <v>1129.5</v>
+      </c>
+      <c r="T587" t="n">
+        <v>1325.206495213066</v>
+      </c>
+      <c r="U587" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V587" t="n">
+        <v>0.02402724211648621</v>
+      </c>
+      <c r="W587" t="n">
+        <v>0.02564921130277464</v>
+      </c>
+      <c r="X587" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y587" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z587" t="n">
+        <v>0.5015593767166138</v>
+      </c>
+      <c r="AA587" t="n">
+        <v>12.0281548500061</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E588" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F588" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H588" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I588" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J588" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K588" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L588" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M588" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N588" s="2" t="n">
+        <v>45834.77923869916</v>
+      </c>
+      <c r="O588" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="P588" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q588" t="n">
+        <v>1.78733</v>
+      </c>
+      <c r="R588" t="n">
+        <v>0.4056329832767312</v>
+      </c>
+      <c r="S588" t="n">
+        <v>2656.4</v>
+      </c>
+      <c r="T588" t="n">
+        <v>1486.239250725943</v>
+      </c>
+      <c r="U588" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="V588" t="n">
+        <v>0</v>
+      </c>
+      <c r="W588" t="n">
+        <v>-0.007139140505670549</v>
+      </c>
+      <c r="X588" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y588" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z588" t="n">
+        <v>0.4815215170383453</v>
+      </c>
+      <c r="AA588" t="n">
+        <v>11.57751679420471</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E589" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F589" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H589" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I589" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J589" t="n">
+        <v>537</v>
+      </c>
+      <c r="K589" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L589" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M589" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N589" s="2" t="n">
+        <v>45834.77923869916</v>
+      </c>
+      <c r="O589" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="P589" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q589" t="n">
+        <v>9.200419999999999</v>
+      </c>
+      <c r="R589" t="n">
+        <v>2.733570858721667</v>
+      </c>
+      <c r="S589" t="n">
+        <v>13505.55</v>
+      </c>
+      <c r="T589" t="n">
+        <v>1467.927551133535</v>
+      </c>
+      <c r="U589" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V589" t="n">
+        <v>-0.001984126984126977</v>
+      </c>
+      <c r="W589" t="n">
+        <v>-0.01932711543223897</v>
+      </c>
+      <c r="X589" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y589" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z589" t="n">
+        <v>0.4985511600971222</v>
+      </c>
+      <c r="AA589" t="n">
+        <v>9.835646152496338</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E590" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F590" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H590" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I590" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J590" t="n">
+        <v>121</v>
+      </c>
+      <c r="K590" t="n">
+        <v>12</v>
+      </c>
+      <c r="L590" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M590" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N590" s="2" t="n">
+        <v>45834.77923869916</v>
+      </c>
+      <c r="O590" t="n">
+        <v>13.815</v>
+      </c>
+      <c r="P590" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q590" t="n">
+        <v>1.1726079</v>
+      </c>
+      <c r="R590" t="n">
+        <v>11.78143179830189</v>
+      </c>
+      <c r="S590" t="n">
+        <v>1671.615</v>
+      </c>
+      <c r="T590" t="n">
+        <v>1425.553247594528</v>
+      </c>
+      <c r="U590" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V590" t="n">
+        <v>-0.0257404795486601</v>
+      </c>
+      <c r="W590" t="n">
+        <v>-0.04423275780521763</v>
+      </c>
+      <c r="X590" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y590" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z590" t="n">
+        <v>0.5161105990409851</v>
+      </c>
+      <c r="AA590" t="n">
+        <v>13.94983839988708</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr"/>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E591" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F591" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H591" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I591" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J591" t="n">
+        <v>162</v>
+      </c>
+      <c r="K591" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L591" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M591" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N591" s="2" t="n">
+        <v>45834.77923869916</v>
+      </c>
+      <c r="O591" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="P591" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q591" t="n">
+        <v>4.2409</v>
+      </c>
+      <c r="R591" t="n">
+        <v>9.149001391214128</v>
+      </c>
+      <c r="S591" t="n">
+        <v>6285.599999999999</v>
+      </c>
+      <c r="T591" t="n">
+        <v>1482.138225376689</v>
+      </c>
+      <c r="U591" t="n">
+        <v>8.272543736854324</v>
+      </c>
+      <c r="V591" t="n">
+        <v>-0.01020408163265318</v>
+      </c>
+      <c r="W591" t="n">
+        <v>-0.004646996859061225</v>
+      </c>
+      <c r="X591" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y591" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z591" t="n">
+        <v>0.5935001373291016</v>
+      </c>
+      <c r="AA591" t="n">
+        <v>12.80392378997803</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E592" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F592" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H592" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I592" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J592" t="n">
+        <v>101</v>
+      </c>
+      <c r="K592" t="n">
+        <v>11</v>
+      </c>
+      <c r="L592" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M592" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N592" s="2" t="n">
+        <v>45834.77923869916</v>
+      </c>
+      <c r="O592" t="n">
+        <v>24594</v>
+      </c>
+      <c r="P592" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q592" t="n">
+        <v>2090.58</v>
+      </c>
+      <c r="R592" t="n">
+        <v>11.76419940877651</v>
+      </c>
+      <c r="S592" t="n">
+        <v>2483994</v>
+      </c>
+      <c r="T592" t="n">
+        <v>1188.184140286428</v>
+      </c>
+      <c r="U592" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V592" t="n">
+        <v>0.002690802348336518</v>
+      </c>
+      <c r="W592" t="n">
+        <v>-0.01376027559201853</v>
+      </c>
+      <c r="X592" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y592" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z592" t="n">
+        <v>0.4108201563358307</v>
+      </c>
+      <c r="AA592" t="n">
+        <v>10.51282495260239</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E593" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F593" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H593" t="n">
+        <v>1</v>
+      </c>
+      <c r="I593" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J593" t="n">
+        <v>30</v>
+      </c>
+      <c r="K593" t="n">
+        <v>9</v>
+      </c>
+      <c r="L593" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M593" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N593" s="2" t="n">
+        <v>45834.77923869916</v>
+      </c>
+      <c r="O593" t="n">
+        <v>46.68</v>
+      </c>
+      <c r="P593" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q593" t="n">
+        <v>1</v>
+      </c>
+      <c r="R593" t="n">
+        <v>46.68</v>
+      </c>
+      <c r="S593" t="n">
+        <v>1400.4</v>
+      </c>
+      <c r="T593" t="n">
+        <v>1400.4</v>
+      </c>
+      <c r="U593" t="n">
+        <v>42.012</v>
+      </c>
+      <c r="V593" t="n">
+        <v>0.02189141856392296</v>
+      </c>
+      <c r="W593" t="n">
+        <v>0.02189141856392296</v>
+      </c>
+      <c r="X593" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y593" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z593" t="n">
+        <v>0.5990515947341919</v>
+      </c>
+      <c r="AA593" t="n">
         <v>12.27674007415771</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA593"/>
+  <dimension ref="A1:AA601"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55468,7 +55468,7 @@
         <v>100</v>
       </c>
       <c r="N586" s="2" t="n">
-        <v>45834.77923869916</v>
+        <v>45834.7792387037</v>
       </c>
       <c r="O586" t="n">
         <v>1</v>
@@ -55559,7 +55559,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N587" s="2" t="n">
-        <v>45834.77923869916</v>
+        <v>45834.7792387037</v>
       </c>
       <c r="O587" t="n">
         <v>376.5</v>
@@ -55654,7 +55654,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N588" s="2" t="n">
-        <v>45834.77923869916</v>
+        <v>45834.7792387037</v>
       </c>
       <c r="O588" t="n">
         <v>0.725</v>
@@ -55749,7 +55749,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N589" s="2" t="n">
-        <v>45834.77923869916</v>
+        <v>45834.7792387037</v>
       </c>
       <c r="O589" t="n">
         <v>25.15</v>
@@ -55844,7 +55844,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N590" s="2" t="n">
-        <v>45834.77923869916</v>
+        <v>45834.7792387037</v>
       </c>
       <c r="O590" t="n">
         <v>13.815</v>
@@ -55935,7 +55935,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N591" s="2" t="n">
-        <v>45834.77923869916</v>
+        <v>45834.7792387037</v>
       </c>
       <c r="O591" t="n">
         <v>38.8</v>
@@ -56030,7 +56030,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N592" s="2" t="n">
-        <v>45834.77923869916</v>
+        <v>45834.7792387037</v>
       </c>
       <c r="O592" t="n">
         <v>24594</v>
@@ -56125,7 +56125,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N593" s="2" t="n">
-        <v>45834.77923869916</v>
+        <v>45834.7792387037</v>
       </c>
       <c r="O593" t="n">
         <v>46.68</v>
@@ -56166,6 +56166,760 @@
         <v>0.5990515947341919</v>
       </c>
       <c r="AA593" t="n">
+        <v>12.27674007415771</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F594" t="n">
+        <v>1</v>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H594" t="n">
+        <v>1</v>
+      </c>
+      <c r="I594" t="n">
+        <v>1</v>
+      </c>
+      <c r="J594" t="n">
+        <v>1</v>
+      </c>
+      <c r="K594" t="n">
+        <v>100</v>
+      </c>
+      <c r="L594" t="n">
+        <v>100</v>
+      </c>
+      <c r="M594" t="n">
+        <v>100</v>
+      </c>
+      <c r="N594" s="2" t="n">
+        <v>45834.80949859742</v>
+      </c>
+      <c r="O594" t="n">
+        <v>1</v>
+      </c>
+      <c r="P594" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q594" t="n">
+        <v>1</v>
+      </c>
+      <c r="R594" t="n">
+        <v>1</v>
+      </c>
+      <c r="S594" t="n">
+        <v>0</v>
+      </c>
+      <c r="T594" t="n">
+        <v>45.43580260334033</v>
+      </c>
+      <c r="U594" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V594" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W594" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X594" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y594" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z594" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA594" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr"/>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E595" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F595" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H595" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I595" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J595" t="n">
+        <v>3</v>
+      </c>
+      <c r="K595" t="n">
+        <v>10</v>
+      </c>
+      <c r="L595" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M595" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N595" s="2" t="n">
+        <v>45834.80949859742</v>
+      </c>
+      <c r="O595" t="n">
+        <v>376.5</v>
+      </c>
+      <c r="P595" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q595" t="n">
+        <v>0.8525199999999999</v>
+      </c>
+      <c r="R595" t="n">
+        <v>441.6318678740675</v>
+      </c>
+      <c r="S595" t="n">
+        <v>1129.5</v>
+      </c>
+      <c r="T595" t="n">
+        <v>1324.895603622203</v>
+      </c>
+      <c r="U595" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V595" t="n">
+        <v>0.02402724211648621</v>
+      </c>
+      <c r="W595" t="n">
+        <v>0.02540859543187346</v>
+      </c>
+      <c r="X595" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y595" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z595" t="n">
+        <v>0.5015593767166138</v>
+      </c>
+      <c r="AA595" t="n">
+        <v>12.0281548500061</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E596" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F596" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H596" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I596" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J596" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K596" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L596" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M596" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N596" s="2" t="n">
+        <v>45834.80949859742</v>
+      </c>
+      <c r="O596" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="P596" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q596" t="n">
+        <v>1.78726</v>
+      </c>
+      <c r="R596" t="n">
+        <v>0.4056488703378355</v>
+      </c>
+      <c r="S596" t="n">
+        <v>2656.4</v>
+      </c>
+      <c r="T596" t="n">
+        <v>1486.29746091783</v>
+      </c>
+      <c r="U596" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="V596" t="n">
+        <v>0</v>
+      </c>
+      <c r="W596" t="n">
+        <v>-0.007100254020120267</v>
+      </c>
+      <c r="X596" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y596" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z596" t="n">
+        <v>0.4815215170383453</v>
+      </c>
+      <c r="AA596" t="n">
+        <v>11.57751679420471</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E597" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F597" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H597" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I597" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J597" t="n">
+        <v>537</v>
+      </c>
+      <c r="K597" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L597" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M597" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N597" s="2" t="n">
+        <v>45834.80949859742</v>
+      </c>
+      <c r="O597" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="P597" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q597" t="n">
+        <v>9.19139</v>
+      </c>
+      <c r="R597" t="n">
+        <v>2.736256431290588</v>
+      </c>
+      <c r="S597" t="n">
+        <v>13505.55</v>
+      </c>
+      <c r="T597" t="n">
+        <v>1469.369703603046</v>
+      </c>
+      <c r="U597" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V597" t="n">
+        <v>-0.001984126984126977</v>
+      </c>
+      <c r="W597" t="n">
+        <v>-0.01836366201032491</v>
+      </c>
+      <c r="X597" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y597" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z597" t="n">
+        <v>0.4985511600971222</v>
+      </c>
+      <c r="AA597" t="n">
+        <v>9.835646152496338</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E598" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F598" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H598" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I598" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J598" t="n">
+        <v>121</v>
+      </c>
+      <c r="K598" t="n">
+        <v>12</v>
+      </c>
+      <c r="L598" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M598" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N598" s="2" t="n">
+        <v>45834.80949859742</v>
+      </c>
+      <c r="O598" t="n">
+        <v>13.838</v>
+      </c>
+      <c r="P598" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q598" t="n">
+        <v>1.1712345</v>
+      </c>
+      <c r="R598" t="n">
+        <v>11.81488420978036</v>
+      </c>
+      <c r="S598" t="n">
+        <v>1674.398</v>
+      </c>
+      <c r="T598" t="n">
+        <v>1429.600989383424</v>
+      </c>
+      <c r="U598" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V598" t="n">
+        <v>-0.02411847672778566</v>
+      </c>
+      <c r="W598" t="n">
+        <v>-0.04151893493454084</v>
+      </c>
+      <c r="X598" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y598" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z598" t="n">
+        <v>0.5161105990409851</v>
+      </c>
+      <c r="AA598" t="n">
+        <v>13.94983839988708</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr"/>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E599" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F599" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H599" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I599" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J599" t="n">
+        <v>162</v>
+      </c>
+      <c r="K599" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L599" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M599" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N599" s="2" t="n">
+        <v>45834.80949859742</v>
+      </c>
+      <c r="O599" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="P599" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q599" t="n">
+        <v>4.23988</v>
+      </c>
+      <c r="R599" t="n">
+        <v>9.151202392520542</v>
+      </c>
+      <c r="S599" t="n">
+        <v>6285.599999999999</v>
+      </c>
+      <c r="T599" t="n">
+        <v>1482.494787588328</v>
+      </c>
+      <c r="U599" t="n">
+        <v>8.272543736854324</v>
+      </c>
+      <c r="V599" t="n">
+        <v>-0.01020408163265318</v>
+      </c>
+      <c r="W599" t="n">
+        <v>-0.004407541953921457</v>
+      </c>
+      <c r="X599" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y599" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z599" t="n">
+        <v>0.5935001373291016</v>
+      </c>
+      <c r="AA599" t="n">
+        <v>12.80392378997803</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E600" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F600" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H600" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I600" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J600" t="n">
+        <v>101</v>
+      </c>
+      <c r="K600" t="n">
+        <v>11</v>
+      </c>
+      <c r="L600" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M600" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N600" s="2" t="n">
+        <v>45834.80949859742</v>
+      </c>
+      <c r="O600" t="n">
+        <v>24594</v>
+      </c>
+      <c r="P600" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q600" t="n">
+        <v>2092.38</v>
+      </c>
+      <c r="R600" t="n">
+        <v>11.75407908697273</v>
+      </c>
+      <c r="S600" t="n">
+        <v>2483994</v>
+      </c>
+      <c r="T600" t="n">
+        <v>1187.161987784246</v>
+      </c>
+      <c r="U600" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V600" t="n">
+        <v>0.002690802348336518</v>
+      </c>
+      <c r="W600" t="n">
+        <v>-0.01460870250488078</v>
+      </c>
+      <c r="X600" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y600" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z600" t="n">
+        <v>0.4108201563358307</v>
+      </c>
+      <c r="AA600" t="n">
+        <v>10.51282495260239</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E601" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F601" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H601" t="n">
+        <v>1</v>
+      </c>
+      <c r="I601" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J601" t="n">
+        <v>30</v>
+      </c>
+      <c r="K601" t="n">
+        <v>9</v>
+      </c>
+      <c r="L601" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M601" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N601" s="2" t="n">
+        <v>45834.80949859742</v>
+      </c>
+      <c r="O601" t="n">
+        <v>46.68</v>
+      </c>
+      <c r="P601" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q601" t="n">
+        <v>1</v>
+      </c>
+      <c r="R601" t="n">
+        <v>46.68</v>
+      </c>
+      <c r="S601" t="n">
+        <v>1400.4</v>
+      </c>
+      <c r="T601" t="n">
+        <v>1400.4</v>
+      </c>
+      <c r="U601" t="n">
+        <v>42.012</v>
+      </c>
+      <c r="V601" t="n">
+        <v>0.02189141856392296</v>
+      </c>
+      <c r="W601" t="n">
+        <v>0.02189141856392296</v>
+      </c>
+      <c r="X601" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y601" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z601" t="n">
+        <v>0.5990515947341919</v>
+      </c>
+      <c r="AA601" t="n">
         <v>12.27674007415771</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA601"/>
+  <dimension ref="A1:AA609"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56222,7 +56222,7 @@
         <v>100</v>
       </c>
       <c r="N594" s="2" t="n">
-        <v>45834.80949859742</v>
+        <v>45834.80949859953</v>
       </c>
       <c r="O594" t="n">
         <v>1</v>
@@ -56313,7 +56313,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N595" s="2" t="n">
-        <v>45834.80949859742</v>
+        <v>45834.80949859953</v>
       </c>
       <c r="O595" t="n">
         <v>376.5</v>
@@ -56408,7 +56408,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N596" s="2" t="n">
-        <v>45834.80949859742</v>
+        <v>45834.80949859953</v>
       </c>
       <c r="O596" t="n">
         <v>0.725</v>
@@ -56503,7 +56503,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N597" s="2" t="n">
-        <v>45834.80949859742</v>
+        <v>45834.80949859953</v>
       </c>
       <c r="O597" t="n">
         <v>25.15</v>
@@ -56598,7 +56598,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N598" s="2" t="n">
-        <v>45834.80949859742</v>
+        <v>45834.80949859953</v>
       </c>
       <c r="O598" t="n">
         <v>13.838</v>
@@ -56689,7 +56689,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N599" s="2" t="n">
-        <v>45834.80949859742</v>
+        <v>45834.80949859953</v>
       </c>
       <c r="O599" t="n">
         <v>38.8</v>
@@ -56784,7 +56784,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N600" s="2" t="n">
-        <v>45834.80949859742</v>
+        <v>45834.80949859953</v>
       </c>
       <c r="O600" t="n">
         <v>24594</v>
@@ -56879,7 +56879,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N601" s="2" t="n">
-        <v>45834.80949859742</v>
+        <v>45834.80949859953</v>
       </c>
       <c r="O601" t="n">
         <v>46.68</v>
@@ -56920,6 +56920,760 @@
         <v>0.5990515947341919</v>
       </c>
       <c r="AA601" t="n">
+        <v>12.27674007415771</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F602" t="n">
+        <v>1</v>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H602" t="n">
+        <v>1</v>
+      </c>
+      <c r="I602" t="n">
+        <v>1</v>
+      </c>
+      <c r="J602" t="n">
+        <v>1</v>
+      </c>
+      <c r="K602" t="n">
+        <v>100</v>
+      </c>
+      <c r="L602" t="n">
+        <v>100</v>
+      </c>
+      <c r="M602" t="n">
+        <v>100</v>
+      </c>
+      <c r="N602" s="2" t="n">
+        <v>45834.85605176295</v>
+      </c>
+      <c r="O602" t="n">
+        <v>1</v>
+      </c>
+      <c r="P602" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q602" t="n">
+        <v>1</v>
+      </c>
+      <c r="R602" t="n">
+        <v>1</v>
+      </c>
+      <c r="S602" t="n">
+        <v>0</v>
+      </c>
+      <c r="T602" t="n">
+        <v>45.43580260334033</v>
+      </c>
+      <c r="U602" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V602" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W602" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X602" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y602" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z602" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA602" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr"/>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E603" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F603" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H603" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I603" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J603" t="n">
+        <v>3</v>
+      </c>
+      <c r="K603" t="n">
+        <v>10</v>
+      </c>
+      <c r="L603" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M603" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N603" s="2" t="n">
+        <v>45834.85605176295</v>
+      </c>
+      <c r="O603" t="n">
+        <v>376.5</v>
+      </c>
+      <c r="P603" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q603" t="n">
+        <v>0.85207</v>
+      </c>
+      <c r="R603" t="n">
+        <v>441.8651049796378</v>
+      </c>
+      <c r="S603" t="n">
+        <v>1129.5</v>
+      </c>
+      <c r="T603" t="n">
+        <v>1325.595314938914</v>
+      </c>
+      <c r="U603" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V603" t="n">
+        <v>0.02402724211648621</v>
+      </c>
+      <c r="W603" t="n">
+        <v>0.02595013998565943</v>
+      </c>
+      <c r="X603" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y603" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z603" t="n">
+        <v>0.5015593767166138</v>
+      </c>
+      <c r="AA603" t="n">
+        <v>12.0281548500061</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E604" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F604" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H604" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I604" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J604" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K604" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L604" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M604" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N604" s="2" t="n">
+        <v>45834.85605176295</v>
+      </c>
+      <c r="O604" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="P604" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q604" t="n">
+        <v>1.78679</v>
+      </c>
+      <c r="R604" t="n">
+        <v>0.4057555728429194</v>
+      </c>
+      <c r="S604" t="n">
+        <v>2656.4</v>
+      </c>
+      <c r="T604" t="n">
+        <v>1486.688418896457</v>
+      </c>
+      <c r="U604" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="V604" t="n">
+        <v>0</v>
+      </c>
+      <c r="W604" t="n">
+        <v>-0.006839080138124842</v>
+      </c>
+      <c r="X604" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y604" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z604" t="n">
+        <v>0.4815215170383453</v>
+      </c>
+      <c r="AA604" t="n">
+        <v>11.57751679420471</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E605" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F605" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H605" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I605" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J605" t="n">
+        <v>537</v>
+      </c>
+      <c r="K605" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L605" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M605" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N605" s="2" t="n">
+        <v>45834.85605176295</v>
+      </c>
+      <c r="O605" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="P605" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q605" t="n">
+        <v>9.179349999999999</v>
+      </c>
+      <c r="R605" t="n">
+        <v>2.739845413890962</v>
+      </c>
+      <c r="S605" t="n">
+        <v>13505.55</v>
+      </c>
+      <c r="T605" t="n">
+        <v>1471.296987259446</v>
+      </c>
+      <c r="U605" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V605" t="n">
+        <v>-0.001984126984126977</v>
+      </c>
+      <c r="W605" t="n">
+        <v>-0.01707610880564303</v>
+      </c>
+      <c r="X605" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y605" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z605" t="n">
+        <v>0.4985511600971222</v>
+      </c>
+      <c r="AA605" t="n">
+        <v>9.835646152496338</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E606" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F606" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H606" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I606" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J606" t="n">
+        <v>121</v>
+      </c>
+      <c r="K606" t="n">
+        <v>12</v>
+      </c>
+      <c r="L606" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M606" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N606" s="2" t="n">
+        <v>45834.85605176295</v>
+      </c>
+      <c r="O606" t="n">
+        <v>13.91</v>
+      </c>
+      <c r="P606" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q606" t="n">
+        <v>1.1698643</v>
+      </c>
+      <c r="R606" t="n">
+        <v>11.89026795671943</v>
+      </c>
+      <c r="S606" t="n">
+        <v>1683.11</v>
+      </c>
+      <c r="T606" t="n">
+        <v>1438.72242276305</v>
+      </c>
+      <c r="U606" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V606" t="n">
+        <v>-0.01904090267983072</v>
+      </c>
+      <c r="W606" t="n">
+        <v>-0.03540343750165331</v>
+      </c>
+      <c r="X606" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y606" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z606" t="n">
+        <v>0.5161105990409851</v>
+      </c>
+      <c r="AA606" t="n">
+        <v>13.94983839988708</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr"/>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E607" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F607" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H607" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I607" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J607" t="n">
+        <v>162</v>
+      </c>
+      <c r="K607" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L607" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M607" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N607" s="2" t="n">
+        <v>45834.85605176295</v>
+      </c>
+      <c r="O607" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="P607" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q607" t="n">
+        <v>4.2393</v>
+      </c>
+      <c r="R607" t="n">
+        <v>9.152454414643927</v>
+      </c>
+      <c r="S607" t="n">
+        <v>6285.599999999999</v>
+      </c>
+      <c r="T607" t="n">
+        <v>1482.697615172316</v>
+      </c>
+      <c r="U607" t="n">
+        <v>8.272543736854324</v>
+      </c>
+      <c r="V607" t="n">
+        <v>-0.01020408163265318</v>
+      </c>
+      <c r="W607" t="n">
+        <v>-0.004271329931732182</v>
+      </c>
+      <c r="X607" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y607" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z607" t="n">
+        <v>0.5935001373291016</v>
+      </c>
+      <c r="AA607" t="n">
+        <v>12.80392378997803</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E608" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F608" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H608" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I608" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J608" t="n">
+        <v>101</v>
+      </c>
+      <c r="K608" t="n">
+        <v>11</v>
+      </c>
+      <c r="L608" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M608" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N608" s="2" t="n">
+        <v>45834.85605176295</v>
+      </c>
+      <c r="O608" t="n">
+        <v>24594</v>
+      </c>
+      <c r="P608" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q608" t="n">
+        <v>2089.28</v>
+      </c>
+      <c r="R608" t="n">
+        <v>11.77151937509572</v>
+      </c>
+      <c r="S608" t="n">
+        <v>2483994</v>
+      </c>
+      <c r="T608" t="n">
+        <v>1188.923456884668</v>
+      </c>
+      <c r="U608" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V608" t="n">
+        <v>0.002690802348336518</v>
+      </c>
+      <c r="W608" t="n">
+        <v>-0.01314661364066216</v>
+      </c>
+      <c r="X608" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y608" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z608" t="n">
+        <v>0.4108201563358307</v>
+      </c>
+      <c r="AA608" t="n">
+        <v>10.51282495260239</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E609" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F609" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H609" t="n">
+        <v>1</v>
+      </c>
+      <c r="I609" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J609" t="n">
+        <v>30</v>
+      </c>
+      <c r="K609" t="n">
+        <v>9</v>
+      </c>
+      <c r="L609" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M609" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N609" s="2" t="n">
+        <v>45834.85605176295</v>
+      </c>
+      <c r="O609" t="n">
+        <v>46.68</v>
+      </c>
+      <c r="P609" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q609" t="n">
+        <v>1</v>
+      </c>
+      <c r="R609" t="n">
+        <v>46.68</v>
+      </c>
+      <c r="S609" t="n">
+        <v>1400.4</v>
+      </c>
+      <c r="T609" t="n">
+        <v>1400.4</v>
+      </c>
+      <c r="U609" t="n">
+        <v>42.012</v>
+      </c>
+      <c r="V609" t="n">
+        <v>0.02189141856392296</v>
+      </c>
+      <c r="W609" t="n">
+        <v>0.02189141856392296</v>
+      </c>
+      <c r="X609" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y609" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z609" t="n">
+        <v>0.5990515947341919</v>
+      </c>
+      <c r="AA609" t="n">
         <v>12.27674007415771</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA609"/>
+  <dimension ref="A1:AA617"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56976,7 +56976,7 @@
         <v>100</v>
       </c>
       <c r="N602" s="2" t="n">
-        <v>45834.85605176295</v>
+        <v>45834.85605175926</v>
       </c>
       <c r="O602" t="n">
         <v>1</v>
@@ -57067,7 +57067,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N603" s="2" t="n">
-        <v>45834.85605176295</v>
+        <v>45834.85605175926</v>
       </c>
       <c r="O603" t="n">
         <v>376.5</v>
@@ -57162,7 +57162,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N604" s="2" t="n">
-        <v>45834.85605176295</v>
+        <v>45834.85605175926</v>
       </c>
       <c r="O604" t="n">
         <v>0.725</v>
@@ -57257,7 +57257,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N605" s="2" t="n">
-        <v>45834.85605176295</v>
+        <v>45834.85605175926</v>
       </c>
       <c r="O605" t="n">
         <v>25.15</v>
@@ -57352,7 +57352,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N606" s="2" t="n">
-        <v>45834.85605176295</v>
+        <v>45834.85605175926</v>
       </c>
       <c r="O606" t="n">
         <v>13.91</v>
@@ -57443,7 +57443,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N607" s="2" t="n">
-        <v>45834.85605176295</v>
+        <v>45834.85605175926</v>
       </c>
       <c r="O607" t="n">
         <v>38.8</v>
@@ -57538,7 +57538,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N608" s="2" t="n">
-        <v>45834.85605176295</v>
+        <v>45834.85605175926</v>
       </c>
       <c r="O608" t="n">
         <v>24594</v>
@@ -57633,7 +57633,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N609" s="2" t="n">
-        <v>45834.85605176295</v>
+        <v>45834.85605175926</v>
       </c>
       <c r="O609" t="n">
         <v>46.68</v>
@@ -57674,6 +57674,760 @@
         <v>0.5990515947341919</v>
       </c>
       <c r="AA609" t="n">
+        <v>12.27674007415771</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F610" t="n">
+        <v>1</v>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H610" t="n">
+        <v>1</v>
+      </c>
+      <c r="I610" t="n">
+        <v>1</v>
+      </c>
+      <c r="J610" t="n">
+        <v>1</v>
+      </c>
+      <c r="K610" t="n">
+        <v>100</v>
+      </c>
+      <c r="L610" t="n">
+        <v>100</v>
+      </c>
+      <c r="M610" t="n">
+        <v>100</v>
+      </c>
+      <c r="N610" s="2" t="n">
+        <v>45834.89518722862</v>
+      </c>
+      <c r="O610" t="n">
+        <v>1</v>
+      </c>
+      <c r="P610" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q610" t="n">
+        <v>1</v>
+      </c>
+      <c r="R610" t="n">
+        <v>1</v>
+      </c>
+      <c r="S610" t="n">
+        <v>0</v>
+      </c>
+      <c r="T610" t="n">
+        <v>45.43580260334033</v>
+      </c>
+      <c r="U610" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V610" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W610" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X610" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y610" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z610" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA610" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr"/>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E611" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F611" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H611" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I611" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J611" t="n">
+        <v>3</v>
+      </c>
+      <c r="K611" t="n">
+        <v>10</v>
+      </c>
+      <c r="L611" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M611" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N611" s="2" t="n">
+        <v>45834.89518722862</v>
+      </c>
+      <c r="O611" t="n">
+        <v>376.5</v>
+      </c>
+      <c r="P611" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q611" t="n">
+        <v>0.85171</v>
+      </c>
+      <c r="R611" t="n">
+        <v>442.0518721160959</v>
+      </c>
+      <c r="S611" t="n">
+        <v>1129.5</v>
+      </c>
+      <c r="T611" t="n">
+        <v>1326.155616348288</v>
+      </c>
+      <c r="U611" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V611" t="n">
+        <v>0.02402724211648621</v>
+      </c>
+      <c r="W611" t="n">
+        <v>0.02638378764788585</v>
+      </c>
+      <c r="X611" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y611" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z611" t="n">
+        <v>0.5015593767166138</v>
+      </c>
+      <c r="AA611" t="n">
+        <v>12.0281548500061</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E612" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F612" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H612" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I612" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J612" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K612" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L612" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M612" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N612" s="2" t="n">
+        <v>45834.89518722862</v>
+      </c>
+      <c r="O612" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="P612" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q612" t="n">
+        <v>1.78585</v>
+      </c>
+      <c r="R612" t="n">
+        <v>0.4059691463448778</v>
+      </c>
+      <c r="S612" t="n">
+        <v>2656.4</v>
+      </c>
+      <c r="T612" t="n">
+        <v>1487.470952207632</v>
+      </c>
+      <c r="U612" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="V612" t="n">
+        <v>0</v>
+      </c>
+      <c r="W612" t="n">
+        <v>-0.00631631995968307</v>
+      </c>
+      <c r="X612" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y612" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z612" t="n">
+        <v>0.4815215170383453</v>
+      </c>
+      <c r="AA612" t="n">
+        <v>11.57751679420471</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E613" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F613" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H613" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I613" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J613" t="n">
+        <v>537</v>
+      </c>
+      <c r="K613" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L613" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M613" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N613" s="2" t="n">
+        <v>45834.89518722862</v>
+      </c>
+      <c r="O613" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="P613" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q613" t="n">
+        <v>9.1807</v>
+      </c>
+      <c r="R613" t="n">
+        <v>2.739442526169028</v>
+      </c>
+      <c r="S613" t="n">
+        <v>13505.55</v>
+      </c>
+      <c r="T613" t="n">
+        <v>1471.080636552768</v>
+      </c>
+      <c r="U613" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V613" t="n">
+        <v>-0.001984126984126977</v>
+      </c>
+      <c r="W613" t="n">
+        <v>-0.01722064541539103</v>
+      </c>
+      <c r="X613" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y613" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z613" t="n">
+        <v>0.4985511600971222</v>
+      </c>
+      <c r="AA613" t="n">
+        <v>9.835646152496338</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E614" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F614" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H614" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I614" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J614" t="n">
+        <v>121</v>
+      </c>
+      <c r="K614" t="n">
+        <v>12</v>
+      </c>
+      <c r="L614" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M614" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N614" s="2" t="n">
+        <v>45834.89518722862</v>
+      </c>
+      <c r="O614" t="n">
+        <v>13.91</v>
+      </c>
+      <c r="P614" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q614" t="n">
+        <v>1.1700011</v>
+      </c>
+      <c r="R614" t="n">
+        <v>11.88887771131155</v>
+      </c>
+      <c r="S614" t="n">
+        <v>1683.11</v>
+      </c>
+      <c r="T614" t="n">
+        <v>1438.554203068698</v>
+      </c>
+      <c r="U614" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V614" t="n">
+        <v>-0.01904090267983072</v>
+      </c>
+      <c r="W614" t="n">
+        <v>-0.03551622099369423</v>
+      </c>
+      <c r="X614" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y614" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z614" t="n">
+        <v>0.5161105990409851</v>
+      </c>
+      <c r="AA614" t="n">
+        <v>13.94983839988708</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr"/>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E615" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F615" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H615" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I615" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J615" t="n">
+        <v>162</v>
+      </c>
+      <c r="K615" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L615" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M615" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N615" s="2" t="n">
+        <v>45834.89518722862</v>
+      </c>
+      <c r="O615" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="P615" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q615" t="n">
+        <v>4.2416</v>
+      </c>
+      <c r="R615" t="n">
+        <v>9.147491512636741</v>
+      </c>
+      <c r="S615" t="n">
+        <v>6285.599999999999</v>
+      </c>
+      <c r="T615" t="n">
+        <v>1481.893625047152</v>
+      </c>
+      <c r="U615" t="n">
+        <v>8.272543736854324</v>
+      </c>
+      <c r="V615" t="n">
+        <v>-0.01020408163265318</v>
+      </c>
+      <c r="W615" t="n">
+        <v>-0.004811262018953322</v>
+      </c>
+      <c r="X615" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y615" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z615" t="n">
+        <v>0.5935001373291016</v>
+      </c>
+      <c r="AA615" t="n">
+        <v>12.80392378997803</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E616" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F616" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H616" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I616" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J616" t="n">
+        <v>101</v>
+      </c>
+      <c r="K616" t="n">
+        <v>11</v>
+      </c>
+      <c r="L616" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M616" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N616" s="2" t="n">
+        <v>45834.89518722862</v>
+      </c>
+      <c r="O616" t="n">
+        <v>24594</v>
+      </c>
+      <c r="P616" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q616" t="n">
+        <v>2086.79</v>
+      </c>
+      <c r="R616" t="n">
+        <v>11.78556538990507</v>
+      </c>
+      <c r="S616" t="n">
+        <v>2483994</v>
+      </c>
+      <c r="T616" t="n">
+        <v>1190.342104380412</v>
+      </c>
+      <c r="U616" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V616" t="n">
+        <v>0.002690802348336518</v>
+      </c>
+      <c r="W616" t="n">
+        <v>-0.01196908023670917</v>
+      </c>
+      <c r="X616" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y616" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z616" t="n">
+        <v>0.4108201563358307</v>
+      </c>
+      <c r="AA616" t="n">
+        <v>10.51282495260239</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E617" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F617" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H617" t="n">
+        <v>1</v>
+      </c>
+      <c r="I617" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J617" t="n">
+        <v>30</v>
+      </c>
+      <c r="K617" t="n">
+        <v>9</v>
+      </c>
+      <c r="L617" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M617" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N617" s="2" t="n">
+        <v>45834.89518722862</v>
+      </c>
+      <c r="O617" t="n">
+        <v>46.68</v>
+      </c>
+      <c r="P617" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q617" t="n">
+        <v>1</v>
+      </c>
+      <c r="R617" t="n">
+        <v>46.68</v>
+      </c>
+      <c r="S617" t="n">
+        <v>1400.4</v>
+      </c>
+      <c r="T617" t="n">
+        <v>1400.4</v>
+      </c>
+      <c r="U617" t="n">
+        <v>42.012</v>
+      </c>
+      <c r="V617" t="n">
+        <v>0.02189141856392296</v>
+      </c>
+      <c r="W617" t="n">
+        <v>0.02189141856392296</v>
+      </c>
+      <c r="X617" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y617" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z617" t="n">
+        <v>0.5990515947341919</v>
+      </c>
+      <c r="AA617" t="n">
         <v>12.27674007415771</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA617"/>
+  <dimension ref="A1:AA625"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57730,7 +57730,7 @@
         <v>100</v>
       </c>
       <c r="N610" s="2" t="n">
-        <v>45834.89518722862</v>
+        <v>45834.89518723379</v>
       </c>
       <c r="O610" t="n">
         <v>1</v>
@@ -57821,7 +57821,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N611" s="2" t="n">
-        <v>45834.89518722862</v>
+        <v>45834.89518723379</v>
       </c>
       <c r="O611" t="n">
         <v>376.5</v>
@@ -57916,7 +57916,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N612" s="2" t="n">
-        <v>45834.89518722862</v>
+        <v>45834.89518723379</v>
       </c>
       <c r="O612" t="n">
         <v>0.725</v>
@@ -58011,7 +58011,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N613" s="2" t="n">
-        <v>45834.89518722862</v>
+        <v>45834.89518723379</v>
       </c>
       <c r="O613" t="n">
         <v>25.15</v>
@@ -58106,7 +58106,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N614" s="2" t="n">
-        <v>45834.89518722862</v>
+        <v>45834.89518723379</v>
       </c>
       <c r="O614" t="n">
         <v>13.91</v>
@@ -58197,7 +58197,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N615" s="2" t="n">
-        <v>45834.89518722862</v>
+        <v>45834.89518723379</v>
       </c>
       <c r="O615" t="n">
         <v>38.8</v>
@@ -58292,7 +58292,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N616" s="2" t="n">
-        <v>45834.89518722862</v>
+        <v>45834.89518723379</v>
       </c>
       <c r="O616" t="n">
         <v>24594</v>
@@ -58387,7 +58387,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N617" s="2" t="n">
-        <v>45834.89518722862</v>
+        <v>45834.89518723379</v>
       </c>
       <c r="O617" t="n">
         <v>46.68</v>
@@ -58428,6 +58428,760 @@
         <v>0.5990515947341919</v>
       </c>
       <c r="AA617" t="n">
+        <v>12.27674007415771</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F618" t="n">
+        <v>1</v>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H618" t="n">
+        <v>1</v>
+      </c>
+      <c r="I618" t="n">
+        <v>1</v>
+      </c>
+      <c r="J618" t="n">
+        <v>1</v>
+      </c>
+      <c r="K618" t="n">
+        <v>100</v>
+      </c>
+      <c r="L618" t="n">
+        <v>100</v>
+      </c>
+      <c r="M618" t="n">
+        <v>100</v>
+      </c>
+      <c r="N618" s="2" t="n">
+        <v>45835.31262064877</v>
+      </c>
+      <c r="O618" t="n">
+        <v>1</v>
+      </c>
+      <c r="P618" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q618" t="n">
+        <v>1</v>
+      </c>
+      <c r="R618" t="n">
+        <v>1</v>
+      </c>
+      <c r="S618" t="n">
+        <v>0</v>
+      </c>
+      <c r="T618" t="n">
+        <v>45.43580260334033</v>
+      </c>
+      <c r="U618" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V618" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W618" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X618" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y618" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z618" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA618" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr"/>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E619" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F619" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H619" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I619" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J619" t="n">
+        <v>3</v>
+      </c>
+      <c r="K619" t="n">
+        <v>10</v>
+      </c>
+      <c r="L619" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M619" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N619" s="2" t="n">
+        <v>45835.31262064877</v>
+      </c>
+      <c r="O619" t="n">
+        <v>375</v>
+      </c>
+      <c r="P619" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q619" t="n">
+        <v>0.85273</v>
+      </c>
+      <c r="R619" t="n">
+        <v>439.7640519273393</v>
+      </c>
+      <c r="S619" t="n">
+        <v>1125</v>
+      </c>
+      <c r="T619" t="n">
+        <v>1319.292155782018</v>
+      </c>
+      <c r="U619" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V619" t="n">
+        <v>0.01994745230725714</v>
+      </c>
+      <c r="W619" t="n">
+        <v>0.02107178310970204</v>
+      </c>
+      <c r="X619" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y619" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z619" t="n">
+        <v>0.5015593767166138</v>
+      </c>
+      <c r="AA619" t="n">
+        <v>12.0281548500061</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E620" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F620" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H620" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I620" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J620" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K620" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L620" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M620" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N620" s="2" t="n">
+        <v>45835.31262064877</v>
+      </c>
+      <c r="O620" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="P620" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q620" t="n">
+        <v>1.78753</v>
+      </c>
+      <c r="R620" t="n">
+        <v>0.4055875985298149</v>
+      </c>
+      <c r="S620" t="n">
+        <v>2656.4</v>
+      </c>
+      <c r="T620" t="n">
+        <v>1486.072961013242</v>
+      </c>
+      <c r="U620" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="V620" t="n">
+        <v>0</v>
+      </c>
+      <c r="W620" t="n">
+        <v>-0.007250227968201961</v>
+      </c>
+      <c r="X620" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y620" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z620" t="n">
+        <v>0.4815215170383453</v>
+      </c>
+      <c r="AA620" t="n">
+        <v>11.57751679420471</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E621" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F621" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H621" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I621" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J621" t="n">
+        <v>537</v>
+      </c>
+      <c r="K621" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L621" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M621" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N621" s="2" t="n">
+        <v>45835.31262064877</v>
+      </c>
+      <c r="O621" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="P621" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q621" t="n">
+        <v>9.194879999999999</v>
+      </c>
+      <c r="R621" t="n">
+        <v>2.664526345096402</v>
+      </c>
+      <c r="S621" t="n">
+        <v>13156.5</v>
+      </c>
+      <c r="T621" t="n">
+        <v>1430.850647316768</v>
+      </c>
+      <c r="U621" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V621" t="n">
+        <v>-0.02777777777777779</v>
+      </c>
+      <c r="W621" t="n">
+        <v>-0.04409694428976896</v>
+      </c>
+      <c r="X621" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y621" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z621" t="n">
+        <v>0.4985511600971222</v>
+      </c>
+      <c r="AA621" t="n">
+        <v>9.835646152496338</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E622" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F622" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H622" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I622" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J622" t="n">
+        <v>121</v>
+      </c>
+      <c r="K622" t="n">
+        <v>12</v>
+      </c>
+      <c r="L622" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M622" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N622" s="2" t="n">
+        <v>45835.31262064877</v>
+      </c>
+      <c r="O622" t="n">
+        <v>13.91</v>
+      </c>
+      <c r="P622" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q622" t="n">
+        <v>1.1716461</v>
+      </c>
+      <c r="R622" t="n">
+        <v>11.87218563694276</v>
+      </c>
+      <c r="S622" t="n">
+        <v>1683.11</v>
+      </c>
+      <c r="T622" t="n">
+        <v>1436.534462070074</v>
+      </c>
+      <c r="U622" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V622" t="n">
+        <v>-0.01904090267983072</v>
+      </c>
+      <c r="W622" t="n">
+        <v>-0.03687036352569717</v>
+      </c>
+      <c r="X622" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y622" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z622" t="n">
+        <v>0.5161105990409851</v>
+      </c>
+      <c r="AA622" t="n">
+        <v>13.94983839988708</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr"/>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E623" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F623" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H623" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I623" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J623" t="n">
+        <v>162</v>
+      </c>
+      <c r="K623" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L623" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M623" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N623" s="2" t="n">
+        <v>45835.31262064877</v>
+      </c>
+      <c r="O623" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="P623" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q623" t="n">
+        <v>4.2379</v>
+      </c>
+      <c r="R623" t="n">
+        <v>9.155477948984167</v>
+      </c>
+      <c r="S623" t="n">
+        <v>6285.599999999999</v>
+      </c>
+      <c r="T623" t="n">
+        <v>1483.187427735435</v>
+      </c>
+      <c r="U623" t="n">
+        <v>8.272543736854324</v>
+      </c>
+      <c r="V623" t="n">
+        <v>-0.01020408163265318</v>
+      </c>
+      <c r="W623" t="n">
+        <v>-0.003942388678258579</v>
+      </c>
+      <c r="X623" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y623" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z623" t="n">
+        <v>0.5935001373291016</v>
+      </c>
+      <c r="AA623" t="n">
+        <v>12.80392378997803</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E624" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F624" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H624" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I624" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J624" t="n">
+        <v>101</v>
+      </c>
+      <c r="K624" t="n">
+        <v>11</v>
+      </c>
+      <c r="L624" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M624" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N624" s="2" t="n">
+        <v>45835.31262064877</v>
+      </c>
+      <c r="O624" t="n">
+        <v>24039</v>
+      </c>
+      <c r="P624" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q624" t="n">
+        <v>2089.05</v>
+      </c>
+      <c r="R624" t="n">
+        <v>11.50714439577798</v>
+      </c>
+      <c r="S624" t="n">
+        <v>2427939</v>
+      </c>
+      <c r="T624" t="n">
+        <v>1162.221583973576</v>
+      </c>
+      <c r="U624" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V624" t="n">
+        <v>-0.01993639921722112</v>
+      </c>
+      <c r="W624" t="n">
+        <v>-0.03531022186275456</v>
+      </c>
+      <c r="X624" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y624" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z624" t="n">
+        <v>0.4108201563358307</v>
+      </c>
+      <c r="AA624" t="n">
+        <v>10.51282495260239</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E625" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F625" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H625" t="n">
+        <v>1</v>
+      </c>
+      <c r="I625" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J625" t="n">
+        <v>30</v>
+      </c>
+      <c r="K625" t="n">
+        <v>9</v>
+      </c>
+      <c r="L625" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M625" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N625" s="2" t="n">
+        <v>45835.31262064877</v>
+      </c>
+      <c r="O625" t="n">
+        <v>46.68</v>
+      </c>
+      <c r="P625" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q625" t="n">
+        <v>1</v>
+      </c>
+      <c r="R625" t="n">
+        <v>46.68</v>
+      </c>
+      <c r="S625" t="n">
+        <v>1400.4</v>
+      </c>
+      <c r="T625" t="n">
+        <v>1400.4</v>
+      </c>
+      <c r="U625" t="n">
+        <v>42.012</v>
+      </c>
+      <c r="V625" t="n">
+        <v>0.02189141856392296</v>
+      </c>
+      <c r="W625" t="n">
+        <v>0.02189141856392296</v>
+      </c>
+      <c r="X625" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y625" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z625" t="n">
+        <v>0.5990515947341919</v>
+      </c>
+      <c r="AA625" t="n">
         <v>12.27674007415771</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA625"/>
+  <dimension ref="A1:AA633"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58484,7 +58484,7 @@
         <v>100</v>
       </c>
       <c r="N618" s="2" t="n">
-        <v>45835.31262064877</v>
+        <v>45835.31262064815</v>
       </c>
       <c r="O618" t="n">
         <v>1</v>
@@ -58575,7 +58575,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N619" s="2" t="n">
-        <v>45835.31262064877</v>
+        <v>45835.31262064815</v>
       </c>
       <c r="O619" t="n">
         <v>375</v>
@@ -58670,7 +58670,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N620" s="2" t="n">
-        <v>45835.31262064877</v>
+        <v>45835.31262064815</v>
       </c>
       <c r="O620" t="n">
         <v>0.725</v>
@@ -58765,7 +58765,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N621" s="2" t="n">
-        <v>45835.31262064877</v>
+        <v>45835.31262064815</v>
       </c>
       <c r="O621" t="n">
         <v>24.5</v>
@@ -58860,7 +58860,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N622" s="2" t="n">
-        <v>45835.31262064877</v>
+        <v>45835.31262064815</v>
       </c>
       <c r="O622" t="n">
         <v>13.91</v>
@@ -58951,7 +58951,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N623" s="2" t="n">
-        <v>45835.31262064877</v>
+        <v>45835.31262064815</v>
       </c>
       <c r="O623" t="n">
         <v>38.8</v>
@@ -59046,7 +59046,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N624" s="2" t="n">
-        <v>45835.31262064877</v>
+        <v>45835.31262064815</v>
       </c>
       <c r="O624" t="n">
         <v>24039</v>
@@ -59141,7 +59141,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N625" s="2" t="n">
-        <v>45835.31262064877</v>
+        <v>45835.31262064815</v>
       </c>
       <c r="O625" t="n">
         <v>46.68</v>
@@ -59182,6 +59182,760 @@
         <v>0.5990515947341919</v>
       </c>
       <c r="AA625" t="n">
+        <v>12.27674007415771</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F626" t="n">
+        <v>1</v>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H626" t="n">
+        <v>1</v>
+      </c>
+      <c r="I626" t="n">
+        <v>1</v>
+      </c>
+      <c r="J626" t="n">
+        <v>1</v>
+      </c>
+      <c r="K626" t="n">
+        <v>100</v>
+      </c>
+      <c r="L626" t="n">
+        <v>100</v>
+      </c>
+      <c r="M626" t="n">
+        <v>100</v>
+      </c>
+      <c r="N626" s="2" t="n">
+        <v>45835.36045668001</v>
+      </c>
+      <c r="O626" t="n">
+        <v>1</v>
+      </c>
+      <c r="P626" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q626" t="n">
+        <v>1</v>
+      </c>
+      <c r="R626" t="n">
+        <v>1</v>
+      </c>
+      <c r="S626" t="n">
+        <v>0</v>
+      </c>
+      <c r="T626" t="n">
+        <v>45.43580260334033</v>
+      </c>
+      <c r="U626" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V626" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W626" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X626" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y626" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z626" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA626" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr"/>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E627" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F627" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H627" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I627" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J627" t="n">
+        <v>3</v>
+      </c>
+      <c r="K627" t="n">
+        <v>10</v>
+      </c>
+      <c r="L627" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M627" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N627" s="2" t="n">
+        <v>45835.36045668001</v>
+      </c>
+      <c r="O627" t="n">
+        <v>376</v>
+      </c>
+      <c r="P627" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q627" t="n">
+        <v>0.8525700000000001</v>
+      </c>
+      <c r="R627" t="n">
+        <v>441.0195057297348</v>
+      </c>
+      <c r="S627" t="n">
+        <v>1128</v>
+      </c>
+      <c r="T627" t="n">
+        <v>1323.058517189204</v>
+      </c>
+      <c r="U627" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V627" t="n">
+        <v>0.02266731218007645</v>
+      </c>
+      <c r="W627" t="n">
+        <v>0.02398677456251797</v>
+      </c>
+      <c r="X627" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y627" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z627" t="n">
+        <v>0.5015593767166138</v>
+      </c>
+      <c r="AA627" t="n">
+        <v>12.0281548500061</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E628" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F628" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H628" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I628" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J628" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K628" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L628" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M628" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N628" s="2" t="n">
+        <v>45835.36045668001</v>
+      </c>
+      <c r="O628" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="P628" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q628" t="n">
+        <v>1.78766</v>
+      </c>
+      <c r="R628" t="n">
+        <v>0.4055581038900014</v>
+      </c>
+      <c r="S628" t="n">
+        <v>2656.4</v>
+      </c>
+      <c r="T628" t="n">
+        <v>1485.964892652965</v>
+      </c>
+      <c r="U628" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="V628" t="n">
+        <v>0</v>
+      </c>
+      <c r="W628" t="n">
+        <v>-0.007322421489545095</v>
+      </c>
+      <c r="X628" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y628" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z628" t="n">
+        <v>0.4815215170383453</v>
+      </c>
+      <c r="AA628" t="n">
+        <v>11.57751679420471</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E629" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F629" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H629" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I629" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J629" t="n">
+        <v>537</v>
+      </c>
+      <c r="K629" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L629" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M629" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N629" s="2" t="n">
+        <v>45835.36045668001</v>
+      </c>
+      <c r="O629" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="P629" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q629" t="n">
+        <v>9.1952</v>
+      </c>
+      <c r="R629" t="n">
+        <v>2.686184096050113</v>
+      </c>
+      <c r="S629" t="n">
+        <v>13263.9</v>
+      </c>
+      <c r="T629" t="n">
+        <v>1442.480859578911</v>
+      </c>
+      <c r="U629" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V629" t="n">
+        <v>-0.01984126984126988</v>
+      </c>
+      <c r="W629" t="n">
+        <v>-0.03632719175774257</v>
+      </c>
+      <c r="X629" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y629" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z629" t="n">
+        <v>0.4985511600971222</v>
+      </c>
+      <c r="AA629" t="n">
+        <v>9.835646152496338</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E630" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F630" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H630" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I630" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J630" t="n">
+        <v>121</v>
+      </c>
+      <c r="K630" t="n">
+        <v>12</v>
+      </c>
+      <c r="L630" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M630" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N630" s="2" t="n">
+        <v>45835.36045668001</v>
+      </c>
+      <c r="O630" t="n">
+        <v>13.91</v>
+      </c>
+      <c r="P630" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q630" t="n">
+        <v>1.1717834</v>
+      </c>
+      <c r="R630" t="n">
+        <v>11.8707945512797</v>
+      </c>
+      <c r="S630" t="n">
+        <v>1683.11</v>
+      </c>
+      <c r="T630" t="n">
+        <v>1436.366140704844</v>
+      </c>
+      <c r="U630" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V630" t="n">
+        <v>-0.01904090267983072</v>
+      </c>
+      <c r="W630" t="n">
+        <v>-0.03698321518333969</v>
+      </c>
+      <c r="X630" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y630" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z630" t="n">
+        <v>0.5161105990409851</v>
+      </c>
+      <c r="AA630" t="n">
+        <v>13.94983839988708</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr"/>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E631" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F631" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H631" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I631" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J631" t="n">
+        <v>162</v>
+      </c>
+      <c r="K631" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L631" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M631" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N631" s="2" t="n">
+        <v>45835.36045668001</v>
+      </c>
+      <c r="O631" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="P631" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q631" t="n">
+        <v>4.23673</v>
+      </c>
+      <c r="R631" t="n">
+        <v>9.181609401590379</v>
+      </c>
+      <c r="S631" t="n">
+        <v>6301.8</v>
+      </c>
+      <c r="T631" t="n">
+        <v>1487.420723057641</v>
+      </c>
+      <c r="U631" t="n">
+        <v>8.272543736854324</v>
+      </c>
+      <c r="V631" t="n">
+        <v>-0.007653061224489943</v>
+      </c>
+      <c r="W631" t="n">
+        <v>-0.001099453289374996</v>
+      </c>
+      <c r="X631" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y631" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z631" t="n">
+        <v>0.5935001373291016</v>
+      </c>
+      <c r="AA631" t="n">
+        <v>12.80392378997803</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E632" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F632" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H632" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I632" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J632" t="n">
+        <v>101</v>
+      </c>
+      <c r="K632" t="n">
+        <v>11</v>
+      </c>
+      <c r="L632" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M632" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N632" s="2" t="n">
+        <v>45835.36045668001</v>
+      </c>
+      <c r="O632" t="n">
+        <v>23920</v>
+      </c>
+      <c r="P632" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q632" t="n">
+        <v>2093.16</v>
+      </c>
+      <c r="R632" t="n">
+        <v>11.42769783485257</v>
+      </c>
+      <c r="S632" t="n">
+        <v>2415920</v>
+      </c>
+      <c r="T632" t="n">
+        <v>1154.197481320109</v>
+      </c>
+      <c r="U632" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V632" t="n">
+        <v>-0.02478799739073712</v>
+      </c>
+      <c r="W632" t="n">
+        <v>-0.04197054371124265</v>
+      </c>
+      <c r="X632" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y632" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z632" t="n">
+        <v>0.4108201563358307</v>
+      </c>
+      <c r="AA632" t="n">
+        <v>10.51282495260239</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E633" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F633" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H633" t="n">
+        <v>1</v>
+      </c>
+      <c r="I633" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J633" t="n">
+        <v>30</v>
+      </c>
+      <c r="K633" t="n">
+        <v>9</v>
+      </c>
+      <c r="L633" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M633" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N633" s="2" t="n">
+        <v>45835.36045668001</v>
+      </c>
+      <c r="O633" t="n">
+        <v>46.62</v>
+      </c>
+      <c r="P633" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q633" t="n">
+        <v>1</v>
+      </c>
+      <c r="R633" t="n">
+        <v>46.62</v>
+      </c>
+      <c r="S633" t="n">
+        <v>1398.6</v>
+      </c>
+      <c r="T633" t="n">
+        <v>1398.6</v>
+      </c>
+      <c r="U633" t="n">
+        <v>42.012</v>
+      </c>
+      <c r="V633" t="n">
+        <v>0.02057793345008752</v>
+      </c>
+      <c r="W633" t="n">
+        <v>0.02057793345008752</v>
+      </c>
+      <c r="X633" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y633" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z633" t="n">
+        <v>0.5990515947341919</v>
+      </c>
+      <c r="AA633" t="n">
         <v>12.27674007415771</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA633"/>
+  <dimension ref="A1:AA641"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59238,7 +59238,7 @@
         <v>100</v>
       </c>
       <c r="N626" s="2" t="n">
-        <v>45835.36045668001</v>
+        <v>45835.36045667824</v>
       </c>
       <c r="O626" t="n">
         <v>1</v>
@@ -59329,7 +59329,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N627" s="2" t="n">
-        <v>45835.36045668001</v>
+        <v>45835.36045667824</v>
       </c>
       <c r="O627" t="n">
         <v>376</v>
@@ -59424,7 +59424,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N628" s="2" t="n">
-        <v>45835.36045668001</v>
+        <v>45835.36045667824</v>
       </c>
       <c r="O628" t="n">
         <v>0.725</v>
@@ -59519,7 +59519,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N629" s="2" t="n">
-        <v>45835.36045668001</v>
+        <v>45835.36045667824</v>
       </c>
       <c r="O629" t="n">
         <v>24.7</v>
@@ -59614,7 +59614,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N630" s="2" t="n">
-        <v>45835.36045668001</v>
+        <v>45835.36045667824</v>
       </c>
       <c r="O630" t="n">
         <v>13.91</v>
@@ -59705,7 +59705,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N631" s="2" t="n">
-        <v>45835.36045668001</v>
+        <v>45835.36045667824</v>
       </c>
       <c r="O631" t="n">
         <v>38.9</v>
@@ -59800,7 +59800,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N632" s="2" t="n">
-        <v>45835.36045668001</v>
+        <v>45835.36045667824</v>
       </c>
       <c r="O632" t="n">
         <v>23920</v>
@@ -59895,7 +59895,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N633" s="2" t="n">
-        <v>45835.36045668001</v>
+        <v>45835.36045667824</v>
       </c>
       <c r="O633" t="n">
         <v>46.62</v>
@@ -59936,6 +59936,760 @@
         <v>0.5990515947341919</v>
       </c>
       <c r="AA633" t="n">
+        <v>12.27674007415771</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F634" t="n">
+        <v>1</v>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H634" t="n">
+        <v>1</v>
+      </c>
+      <c r="I634" t="n">
+        <v>1</v>
+      </c>
+      <c r="J634" t="n">
+        <v>1</v>
+      </c>
+      <c r="K634" t="n">
+        <v>100</v>
+      </c>
+      <c r="L634" t="n">
+        <v>100</v>
+      </c>
+      <c r="M634" t="n">
+        <v>100</v>
+      </c>
+      <c r="N634" s="2" t="n">
+        <v>45835.39751224432</v>
+      </c>
+      <c r="O634" t="n">
+        <v>1</v>
+      </c>
+      <c r="P634" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q634" t="n">
+        <v>1</v>
+      </c>
+      <c r="R634" t="n">
+        <v>1</v>
+      </c>
+      <c r="S634" t="n">
+        <v>0</v>
+      </c>
+      <c r="T634" t="n">
+        <v>45.43580260334033</v>
+      </c>
+      <c r="U634" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V634" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W634" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X634" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y634" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z634" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA634" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr"/>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E635" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F635" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H635" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I635" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J635" t="n">
+        <v>3</v>
+      </c>
+      <c r="K635" t="n">
+        <v>10</v>
+      </c>
+      <c r="L635" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M635" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N635" s="2" t="n">
+        <v>45835.39751224432</v>
+      </c>
+      <c r="O635" t="n">
+        <v>371.11</v>
+      </c>
+      <c r="P635" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q635" t="n">
+        <v>0.8522</v>
+      </c>
+      <c r="R635" t="n">
+        <v>435.472893686928</v>
+      </c>
+      <c r="S635" t="n">
+        <v>1113.33</v>
+      </c>
+      <c r="T635" t="n">
+        <v>1306.418681060784</v>
+      </c>
+      <c r="U635" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V635" t="n">
+        <v>0.009367197401989991</v>
+      </c>
+      <c r="W635" t="n">
+        <v>0.01110830251837225</v>
+      </c>
+      <c r="X635" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y635" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z635" t="n">
+        <v>0.5015593767166138</v>
+      </c>
+      <c r="AA635" t="n">
+        <v>12.0281548500061</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E636" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F636" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H636" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I636" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J636" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K636" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L636" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M636" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N636" s="2" t="n">
+        <v>45835.39751224432</v>
+      </c>
+      <c r="O636" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="P636" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q636" t="n">
+        <v>1.78889</v>
+      </c>
+      <c r="R636" t="n">
+        <v>0.4052792513793469</v>
+      </c>
+      <c r="S636" t="n">
+        <v>2656.4</v>
+      </c>
+      <c r="T636" t="n">
+        <v>1484.943177053927</v>
+      </c>
+      <c r="U636" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="V636" t="n">
+        <v>0</v>
+      </c>
+      <c r="W636" t="n">
+        <v>-0.008004963972072066</v>
+      </c>
+      <c r="X636" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y636" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z636" t="n">
+        <v>0.4815215170383453</v>
+      </c>
+      <c r="AA636" t="n">
+        <v>11.57751679420471</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E637" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F637" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H637" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I637" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J637" t="n">
+        <v>537</v>
+      </c>
+      <c r="K637" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L637" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M637" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N637" s="2" t="n">
+        <v>45835.39751224432</v>
+      </c>
+      <c r="O637" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="P637" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q637" t="n">
+        <v>9.18984</v>
+      </c>
+      <c r="R637" t="n">
+        <v>2.687750820471303</v>
+      </c>
+      <c r="S637" t="n">
+        <v>13263.9</v>
+      </c>
+      <c r="T637" t="n">
+        <v>1443.32219059309</v>
+      </c>
+      <c r="U637" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V637" t="n">
+        <v>-0.01984126984126988</v>
+      </c>
+      <c r="W637" t="n">
+        <v>-0.03576512688477662</v>
+      </c>
+      <c r="X637" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y637" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z637" t="n">
+        <v>0.4985511600971222</v>
+      </c>
+      <c r="AA637" t="n">
+        <v>9.835646152496338</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E638" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F638" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H638" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I638" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J638" t="n">
+        <v>121</v>
+      </c>
+      <c r="K638" t="n">
+        <v>12</v>
+      </c>
+      <c r="L638" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M638" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N638" s="2" t="n">
+        <v>45835.39751224432</v>
+      </c>
+      <c r="O638" t="n">
+        <v>13.91</v>
+      </c>
+      <c r="P638" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q638" t="n">
+        <v>1.1710973</v>
+      </c>
+      <c r="R638" t="n">
+        <v>11.87774918446144</v>
+      </c>
+      <c r="S638" t="n">
+        <v>1683.11</v>
+      </c>
+      <c r="T638" t="n">
+        <v>1437.207651319835</v>
+      </c>
+      <c r="U638" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V638" t="n">
+        <v>-0.01904090267983072</v>
+      </c>
+      <c r="W638" t="n">
+        <v>-0.03641902140024178</v>
+      </c>
+      <c r="X638" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y638" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z638" t="n">
+        <v>0.5161105990409851</v>
+      </c>
+      <c r="AA638" t="n">
+        <v>13.94983839988708</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr"/>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E639" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F639" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H639" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I639" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J639" t="n">
+        <v>162</v>
+      </c>
+      <c r="K639" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L639" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M639" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N639" s="2" t="n">
+        <v>45835.39751224432</v>
+      </c>
+      <c r="O639" t="n">
+        <v>38.75</v>
+      </c>
+      <c r="P639" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q639" t="n">
+        <v>4.2355</v>
+      </c>
+      <c r="R639" t="n">
+        <v>9.14886081926573</v>
+      </c>
+      <c r="S639" t="n">
+        <v>6277.5</v>
+      </c>
+      <c r="T639" t="n">
+        <v>1482.115452721048</v>
+      </c>
+      <c r="U639" t="n">
+        <v>8.272543736854324</v>
+      </c>
+      <c r="V639" t="n">
+        <v>-0.01147959183673475</v>
+      </c>
+      <c r="W639" t="n">
+        <v>-0.004662290190542095</v>
+      </c>
+      <c r="X639" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y639" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z639" t="n">
+        <v>0.5935001373291016</v>
+      </c>
+      <c r="AA639" t="n">
+        <v>12.80392378997803</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E640" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F640" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H640" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I640" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J640" t="n">
+        <v>101</v>
+      </c>
+      <c r="K640" t="n">
+        <v>11</v>
+      </c>
+      <c r="L640" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M640" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N640" s="2" t="n">
+        <v>45835.39751224432</v>
+      </c>
+      <c r="O640" t="n">
+        <v>23867</v>
+      </c>
+      <c r="P640" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q640" t="n">
+        <v>2097.42</v>
+      </c>
+      <c r="R640" t="n">
+        <v>11.37921827769355</v>
+      </c>
+      <c r="S640" t="n">
+        <v>2410567</v>
+      </c>
+      <c r="T640" t="n">
+        <v>1149.301046047048</v>
+      </c>
+      <c r="U640" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V640" t="n">
+        <v>-0.02694879321591648</v>
+      </c>
+      <c r="W640" t="n">
+        <v>-0.0460347782103846</v>
+      </c>
+      <c r="X640" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y640" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z640" t="n">
+        <v>0.4108201563358307</v>
+      </c>
+      <c r="AA640" t="n">
+        <v>10.51282495260239</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E641" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F641" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H641" t="n">
+        <v>1</v>
+      </c>
+      <c r="I641" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J641" t="n">
+        <v>30</v>
+      </c>
+      <c r="K641" t="n">
+        <v>9</v>
+      </c>
+      <c r="L641" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M641" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N641" s="2" t="n">
+        <v>45835.39751224432</v>
+      </c>
+      <c r="O641" t="n">
+        <v>46.86</v>
+      </c>
+      <c r="P641" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q641" t="n">
+        <v>1</v>
+      </c>
+      <c r="R641" t="n">
+        <v>46.86</v>
+      </c>
+      <c r="S641" t="n">
+        <v>1405.8</v>
+      </c>
+      <c r="T641" t="n">
+        <v>1405.8</v>
+      </c>
+      <c r="U641" t="n">
+        <v>42.174</v>
+      </c>
+      <c r="V641" t="n">
+        <v>0.02583187390542907</v>
+      </c>
+      <c r="W641" t="n">
+        <v>0.02583187390542907</v>
+      </c>
+      <c r="X641" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y641" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z641" t="n">
+        <v>0.5990515947341919</v>
+      </c>
+      <c r="AA641" t="n">
         <v>12.27674007415771</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA641"/>
+  <dimension ref="A1:AA649"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59992,7 +59992,7 @@
         <v>100</v>
       </c>
       <c r="N634" s="2" t="n">
-        <v>45835.39751224432</v>
+        <v>45835.39751224537</v>
       </c>
       <c r="O634" t="n">
         <v>1</v>
@@ -60083,7 +60083,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N635" s="2" t="n">
-        <v>45835.39751224432</v>
+        <v>45835.39751224537</v>
       </c>
       <c r="O635" t="n">
         <v>371.11</v>
@@ -60178,7 +60178,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N636" s="2" t="n">
-        <v>45835.39751224432</v>
+        <v>45835.39751224537</v>
       </c>
       <c r="O636" t="n">
         <v>0.725</v>
@@ -60273,7 +60273,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N637" s="2" t="n">
-        <v>45835.39751224432</v>
+        <v>45835.39751224537</v>
       </c>
       <c r="O637" t="n">
         <v>24.7</v>
@@ -60368,7 +60368,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N638" s="2" t="n">
-        <v>45835.39751224432</v>
+        <v>45835.39751224537</v>
       </c>
       <c r="O638" t="n">
         <v>13.91</v>
@@ -60459,7 +60459,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N639" s="2" t="n">
-        <v>45835.39751224432</v>
+        <v>45835.39751224537</v>
       </c>
       <c r="O639" t="n">
         <v>38.75</v>
@@ -60554,7 +60554,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N640" s="2" t="n">
-        <v>45835.39751224432</v>
+        <v>45835.39751224537</v>
       </c>
       <c r="O640" t="n">
         <v>23867</v>
@@ -60649,7 +60649,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N641" s="2" t="n">
-        <v>45835.39751224432</v>
+        <v>45835.39751224537</v>
       </c>
       <c r="O641" t="n">
         <v>46.86</v>
@@ -60690,6 +60690,760 @@
         <v>0.5990515947341919</v>
       </c>
       <c r="AA641" t="n">
+        <v>12.27674007415771</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F642" t="n">
+        <v>1</v>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H642" t="n">
+        <v>1</v>
+      </c>
+      <c r="I642" t="n">
+        <v>1</v>
+      </c>
+      <c r="J642" t="n">
+        <v>1</v>
+      </c>
+      <c r="K642" t="n">
+        <v>100</v>
+      </c>
+      <c r="L642" t="n">
+        <v>100</v>
+      </c>
+      <c r="M642" t="n">
+        <v>100</v>
+      </c>
+      <c r="N642" s="2" t="n">
+        <v>45835.44181357435</v>
+      </c>
+      <c r="O642" t="n">
+        <v>1</v>
+      </c>
+      <c r="P642" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q642" t="n">
+        <v>1</v>
+      </c>
+      <c r="R642" t="n">
+        <v>1</v>
+      </c>
+      <c r="S642" t="n">
+        <v>0</v>
+      </c>
+      <c r="T642" t="n">
+        <v>45.43580260334033</v>
+      </c>
+      <c r="U642" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V642" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W642" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X642" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y642" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z642" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA642" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr"/>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E643" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F643" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H643" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I643" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J643" t="n">
+        <v>3</v>
+      </c>
+      <c r="K643" t="n">
+        <v>10</v>
+      </c>
+      <c r="L643" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M643" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N643" s="2" t="n">
+        <v>45835.44181357435</v>
+      </c>
+      <c r="O643" t="n">
+        <v>370.55</v>
+      </c>
+      <c r="P643" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q643" t="n">
+        <v>0.85279</v>
+      </c>
+      <c r="R643" t="n">
+        <v>434.5149450626766</v>
+      </c>
+      <c r="S643" t="n">
+        <v>1111.65</v>
+      </c>
+      <c r="T643" t="n">
+        <v>1303.54483518803</v>
+      </c>
+      <c r="U643" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V643" t="n">
+        <v>0.007844075873211009</v>
+      </c>
+      <c r="W643" t="n">
+        <v>0.008884077264841306</v>
+      </c>
+      <c r="X643" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y643" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z643" t="n">
+        <v>0.5015593767166138</v>
+      </c>
+      <c r="AA643" t="n">
+        <v>12.0281548500061</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E644" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F644" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H644" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I644" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J644" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K644" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L644" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M644" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N644" s="2" t="n">
+        <v>45835.44181357435</v>
+      </c>
+      <c r="O644" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="P644" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q644" t="n">
+        <v>1.79208</v>
+      </c>
+      <c r="R644" t="n">
+        <v>0.4045578322396322</v>
+      </c>
+      <c r="S644" t="n">
+        <v>2656.4</v>
+      </c>
+      <c r="T644" t="n">
+        <v>1482.299897326012</v>
+      </c>
+      <c r="U644" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="V644" t="n">
+        <v>0</v>
+      </c>
+      <c r="W644" t="n">
+        <v>-0.009770769162090964</v>
+      </c>
+      <c r="X644" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y644" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z644" t="n">
+        <v>0.4815215170383453</v>
+      </c>
+      <c r="AA644" t="n">
+        <v>11.57751679420471</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E645" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F645" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H645" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I645" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J645" t="n">
+        <v>537</v>
+      </c>
+      <c r="K645" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L645" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M645" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N645" s="2" t="n">
+        <v>45835.44181357435</v>
+      </c>
+      <c r="O645" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="P645" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q645" t="n">
+        <v>9.18684</v>
+      </c>
+      <c r="R645" t="n">
+        <v>2.688628516443086</v>
+      </c>
+      <c r="S645" t="n">
+        <v>13263.9</v>
+      </c>
+      <c r="T645" t="n">
+        <v>1443.793513329937</v>
+      </c>
+      <c r="U645" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V645" t="n">
+        <v>-0.01984126984126988</v>
+      </c>
+      <c r="W645" t="n">
+        <v>-0.03545025206173125</v>
+      </c>
+      <c r="X645" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y645" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z645" t="n">
+        <v>0.4985511600971222</v>
+      </c>
+      <c r="AA645" t="n">
+        <v>9.835646152496338</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E646" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F646" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H646" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I646" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J646" t="n">
+        <v>121</v>
+      </c>
+      <c r="K646" t="n">
+        <v>12</v>
+      </c>
+      <c r="L646" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M646" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N646" s="2" t="n">
+        <v>45835.44181357435</v>
+      </c>
+      <c r="O646" t="n">
+        <v>13.91</v>
+      </c>
+      <c r="P646" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q646" t="n">
+        <v>1.170686</v>
+      </c>
+      <c r="R646" t="n">
+        <v>11.88192222338014</v>
+      </c>
+      <c r="S646" t="n">
+        <v>1683.11</v>
+      </c>
+      <c r="T646" t="n">
+        <v>1437.712589028997</v>
+      </c>
+      <c r="U646" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V646" t="n">
+        <v>-0.01904090267983072</v>
+      </c>
+      <c r="W646" t="n">
+        <v>-0.03608048411825659</v>
+      </c>
+      <c r="X646" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y646" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z646" t="n">
+        <v>0.5161105990409851</v>
+      </c>
+      <c r="AA646" t="n">
+        <v>13.94983839988708</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr"/>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E647" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F647" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H647" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I647" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J647" t="n">
+        <v>162</v>
+      </c>
+      <c r="K647" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L647" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M647" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N647" s="2" t="n">
+        <v>45835.44181357435</v>
+      </c>
+      <c r="O647" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="P647" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q647" t="n">
+        <v>4.23548</v>
+      </c>
+      <c r="R647" t="n">
+        <v>9.302369507116076</v>
+      </c>
+      <c r="S647" t="n">
+        <v>6382.8</v>
+      </c>
+      <c r="T647" t="n">
+        <v>1506.983860152804</v>
+      </c>
+      <c r="U647" t="n">
+        <v>8.372132556404468</v>
+      </c>
+      <c r="V647" t="n">
+        <v>0.005102040816326481</v>
+      </c>
+      <c r="W647" t="n">
+        <v>0.01203847603808672</v>
+      </c>
+      <c r="X647" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y647" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z647" t="n">
+        <v>0.5935001373291016</v>
+      </c>
+      <c r="AA647" t="n">
+        <v>12.80392378997803</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E648" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F648" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H648" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I648" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J648" t="n">
+        <v>101</v>
+      </c>
+      <c r="K648" t="n">
+        <v>11</v>
+      </c>
+      <c r="L648" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M648" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N648" s="2" t="n">
+        <v>45835.44181357435</v>
+      </c>
+      <c r="O648" t="n">
+        <v>23970</v>
+      </c>
+      <c r="P648" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q648" t="n">
+        <v>2097.68</v>
+      </c>
+      <c r="R648" t="n">
+        <v>11.4269097288433</v>
+      </c>
+      <c r="S648" t="n">
+        <v>2420970</v>
+      </c>
+      <c r="T648" t="n">
+        <v>1154.117882613173</v>
+      </c>
+      <c r="U648" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V648" t="n">
+        <v>-0.02274951076320941</v>
+      </c>
+      <c r="W648" t="n">
+        <v>-0.04203661377911394</v>
+      </c>
+      <c r="X648" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y648" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z648" t="n">
+        <v>0.4108201563358307</v>
+      </c>
+      <c r="AA648" t="n">
+        <v>10.51282495260239</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E649" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F649" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H649" t="n">
+        <v>1</v>
+      </c>
+      <c r="I649" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J649" t="n">
+        <v>30</v>
+      </c>
+      <c r="K649" t="n">
+        <v>9</v>
+      </c>
+      <c r="L649" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M649" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N649" s="2" t="n">
+        <v>45835.44181357435</v>
+      </c>
+      <c r="O649" t="n">
+        <v>46.56</v>
+      </c>
+      <c r="P649" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q649" t="n">
+        <v>1</v>
+      </c>
+      <c r="R649" t="n">
+        <v>46.56</v>
+      </c>
+      <c r="S649" t="n">
+        <v>1396.8</v>
+      </c>
+      <c r="T649" t="n">
+        <v>1396.8</v>
+      </c>
+      <c r="U649" t="n">
+        <v>42.174</v>
+      </c>
+      <c r="V649" t="n">
+        <v>0.01926444833625229</v>
+      </c>
+      <c r="W649" t="n">
+        <v>0.01926444833625229</v>
+      </c>
+      <c r="X649" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y649" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z649" t="n">
+        <v>0.5990515947341919</v>
+      </c>
+      <c r="AA649" t="n">
         <v>12.27674007415771</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA649"/>
+  <dimension ref="A1:AA657"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60746,7 +60746,7 @@
         <v>100</v>
       </c>
       <c r="N642" s="2" t="n">
-        <v>45835.44181357435</v>
+        <v>45835.44181357639</v>
       </c>
       <c r="O642" t="n">
         <v>1</v>
@@ -60837,7 +60837,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N643" s="2" t="n">
-        <v>45835.44181357435</v>
+        <v>45835.44181357639</v>
       </c>
       <c r="O643" t="n">
         <v>370.55</v>
@@ -60932,7 +60932,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N644" s="2" t="n">
-        <v>45835.44181357435</v>
+        <v>45835.44181357639</v>
       </c>
       <c r="O644" t="n">
         <v>0.725</v>
@@ -61027,7 +61027,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N645" s="2" t="n">
-        <v>45835.44181357435</v>
+        <v>45835.44181357639</v>
       </c>
       <c r="O645" t="n">
         <v>24.7</v>
@@ -61122,7 +61122,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N646" s="2" t="n">
-        <v>45835.44181357435</v>
+        <v>45835.44181357639</v>
       </c>
       <c r="O646" t="n">
         <v>13.91</v>
@@ -61213,7 +61213,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N647" s="2" t="n">
-        <v>45835.44181357435</v>
+        <v>45835.44181357639</v>
       </c>
       <c r="O647" t="n">
         <v>39.4</v>
@@ -61308,7 +61308,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N648" s="2" t="n">
-        <v>45835.44181357435</v>
+        <v>45835.44181357639</v>
       </c>
       <c r="O648" t="n">
         <v>23970</v>
@@ -61403,7 +61403,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N649" s="2" t="n">
-        <v>45835.44181357435</v>
+        <v>45835.44181357639</v>
       </c>
       <c r="O649" t="n">
         <v>46.56</v>
@@ -61444,6 +61444,760 @@
         <v>0.5990515947341919</v>
       </c>
       <c r="AA649" t="n">
+        <v>12.27674007415771</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F650" t="n">
+        <v>1</v>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H650" t="n">
+        <v>1</v>
+      </c>
+      <c r="I650" t="n">
+        <v>1</v>
+      </c>
+      <c r="J650" t="n">
+        <v>1</v>
+      </c>
+      <c r="K650" t="n">
+        <v>100</v>
+      </c>
+      <c r="L650" t="n">
+        <v>100</v>
+      </c>
+      <c r="M650" t="n">
+        <v>100</v>
+      </c>
+      <c r="N650" s="2" t="n">
+        <v>45835.47670557999</v>
+      </c>
+      <c r="O650" t="n">
+        <v>1</v>
+      </c>
+      <c r="P650" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q650" t="n">
+        <v>1</v>
+      </c>
+      <c r="R650" t="n">
+        <v>1</v>
+      </c>
+      <c r="S650" t="n">
+        <v>0</v>
+      </c>
+      <c r="T650" t="n">
+        <v>45.43580260334033</v>
+      </c>
+      <c r="U650" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V650" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W650" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X650" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y650" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z650" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA650" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr"/>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E651" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F651" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H651" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I651" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J651" t="n">
+        <v>3</v>
+      </c>
+      <c r="K651" t="n">
+        <v>10</v>
+      </c>
+      <c r="L651" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M651" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N651" s="2" t="n">
+        <v>45835.47670557999</v>
+      </c>
+      <c r="O651" t="n">
+        <v>370.55</v>
+      </c>
+      <c r="P651" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q651" t="n">
+        <v>0.85337</v>
+      </c>
+      <c r="R651" t="n">
+        <v>434.2196233755581</v>
+      </c>
+      <c r="S651" t="n">
+        <v>1111.65</v>
+      </c>
+      <c r="T651" t="n">
+        <v>1302.658870126674</v>
+      </c>
+      <c r="U651" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V651" t="n">
+        <v>0.007844075873211009</v>
+      </c>
+      <c r="W651" t="n">
+        <v>0.00819838083209401</v>
+      </c>
+      <c r="X651" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y651" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z651" t="n">
+        <v>0.5015593767166138</v>
+      </c>
+      <c r="AA651" t="n">
+        <v>12.0281548500061</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E652" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F652" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H652" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I652" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J652" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K652" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L652" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M652" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N652" s="2" t="n">
+        <v>45835.47670557999</v>
+      </c>
+      <c r="O652" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="P652" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q652" t="n">
+        <v>1.79285</v>
+      </c>
+      <c r="R652" t="n">
+        <v>0.4043840812114789</v>
+      </c>
+      <c r="S652" t="n">
+        <v>2656.4</v>
+      </c>
+      <c r="T652" t="n">
+        <v>1481.663273558859</v>
+      </c>
+      <c r="U652" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="V652" t="n">
+        <v>0</v>
+      </c>
+      <c r="W652" t="n">
+        <v>-0.01019605655799438</v>
+      </c>
+      <c r="X652" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y652" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z652" t="n">
+        <v>0.4815215170383453</v>
+      </c>
+      <c r="AA652" t="n">
+        <v>11.57751679420471</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E653" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F653" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H653" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I653" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J653" t="n">
+        <v>537</v>
+      </c>
+      <c r="K653" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L653" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M653" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N653" s="2" t="n">
+        <v>45835.47670557999</v>
+      </c>
+      <c r="O653" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="P653" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q653" t="n">
+        <v>9.196339999999999</v>
+      </c>
+      <c r="R653" t="n">
+        <v>2.685851110333024</v>
+      </c>
+      <c r="S653" t="n">
+        <v>13263.9</v>
+      </c>
+      <c r="T653" t="n">
+        <v>1442.302046248834</v>
+      </c>
+      <c r="U653" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V653" t="n">
+        <v>-0.01984126984126988</v>
+      </c>
+      <c r="W653" t="n">
+        <v>-0.03644665091229693</v>
+      </c>
+      <c r="X653" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y653" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z653" t="n">
+        <v>0.4985511600971222</v>
+      </c>
+      <c r="AA653" t="n">
+        <v>9.835646152496338</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E654" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F654" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H654" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I654" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J654" t="n">
+        <v>121</v>
+      </c>
+      <c r="K654" t="n">
+        <v>12</v>
+      </c>
+      <c r="L654" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M654" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N654" s="2" t="n">
+        <v>45835.47670557999</v>
+      </c>
+      <c r="O654" t="n">
+        <v>13.91</v>
+      </c>
+      <c r="P654" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q654" t="n">
+        <v>1.1717834</v>
+      </c>
+      <c r="R654" t="n">
+        <v>11.8707945512797</v>
+      </c>
+      <c r="S654" t="n">
+        <v>1683.11</v>
+      </c>
+      <c r="T654" t="n">
+        <v>1436.366140704844</v>
+      </c>
+      <c r="U654" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V654" t="n">
+        <v>-0.01904090267983072</v>
+      </c>
+      <c r="W654" t="n">
+        <v>-0.03698321518333969</v>
+      </c>
+      <c r="X654" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y654" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z654" t="n">
+        <v>0.5161105990409851</v>
+      </c>
+      <c r="AA654" t="n">
+        <v>13.94983839988708</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr"/>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E655" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F655" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H655" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I655" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J655" t="n">
+        <v>162</v>
+      </c>
+      <c r="K655" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L655" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M655" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N655" s="2" t="n">
+        <v>45835.47670557999</v>
+      </c>
+      <c r="O655" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="P655" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q655" t="n">
+        <v>4.23723</v>
+      </c>
+      <c r="R655" t="n">
+        <v>9.298527575798339</v>
+      </c>
+      <c r="S655" t="n">
+        <v>6382.8</v>
+      </c>
+      <c r="T655" t="n">
+        <v>1506.361467279331</v>
+      </c>
+      <c r="U655" t="n">
+        <v>8.372132556404468</v>
+      </c>
+      <c r="V655" t="n">
+        <v>0.005102040816326481</v>
+      </c>
+      <c r="W655" t="n">
+        <v>0.01162049841282986</v>
+      </c>
+      <c r="X655" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y655" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z655" t="n">
+        <v>0.5935001373291016</v>
+      </c>
+      <c r="AA655" t="n">
+        <v>12.80392378997803</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E656" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F656" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H656" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I656" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J656" t="n">
+        <v>101</v>
+      </c>
+      <c r="K656" t="n">
+        <v>11</v>
+      </c>
+      <c r="L656" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M656" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N656" s="2" t="n">
+        <v>45835.47670557999</v>
+      </c>
+      <c r="O656" t="n">
+        <v>23962</v>
+      </c>
+      <c r="P656" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q656" t="n">
+        <v>2096.5</v>
+      </c>
+      <c r="R656" t="n">
+        <v>11.42952539947532</v>
+      </c>
+      <c r="S656" t="n">
+        <v>2420162</v>
+      </c>
+      <c r="T656" t="n">
+        <v>1154.382065347007</v>
+      </c>
+      <c r="U656" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V656" t="n">
+        <v>-0.02307566862361388</v>
+      </c>
+      <c r="W656" t="n">
+        <v>-0.04181733168488644</v>
+      </c>
+      <c r="X656" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y656" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z656" t="n">
+        <v>0.4108201563358307</v>
+      </c>
+      <c r="AA656" t="n">
+        <v>10.51282495260239</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E657" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F657" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G657" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H657" t="n">
+        <v>1</v>
+      </c>
+      <c r="I657" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J657" t="n">
+        <v>30</v>
+      </c>
+      <c r="K657" t="n">
+        <v>9</v>
+      </c>
+      <c r="L657" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M657" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N657" s="2" t="n">
+        <v>45835.47670557999</v>
+      </c>
+      <c r="O657" t="n">
+        <v>46.78</v>
+      </c>
+      <c r="P657" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q657" t="n">
+        <v>1</v>
+      </c>
+      <c r="R657" t="n">
+        <v>46.78</v>
+      </c>
+      <c r="S657" t="n">
+        <v>1403.4</v>
+      </c>
+      <c r="T657" t="n">
+        <v>1403.4</v>
+      </c>
+      <c r="U657" t="n">
+        <v>42.174</v>
+      </c>
+      <c r="V657" t="n">
+        <v>0.02408056042031537</v>
+      </c>
+      <c r="W657" t="n">
+        <v>0.02408056042031537</v>
+      </c>
+      <c r="X657" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y657" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z657" t="n">
+        <v>0.5990515947341919</v>
+      </c>
+      <c r="AA657" t="n">
         <v>12.27674007415771</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA657"/>
+  <dimension ref="A1:AA665"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61500,7 +61500,7 @@
         <v>100</v>
       </c>
       <c r="N650" s="2" t="n">
-        <v>45835.47670557999</v>
+        <v>45835.4767055787</v>
       </c>
       <c r="O650" t="n">
         <v>1</v>
@@ -61591,7 +61591,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N651" s="2" t="n">
-        <v>45835.47670557999</v>
+        <v>45835.4767055787</v>
       </c>
       <c r="O651" t="n">
         <v>370.55</v>
@@ -61686,7 +61686,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N652" s="2" t="n">
-        <v>45835.47670557999</v>
+        <v>45835.4767055787</v>
       </c>
       <c r="O652" t="n">
         <v>0.725</v>
@@ -61781,7 +61781,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N653" s="2" t="n">
-        <v>45835.47670557999</v>
+        <v>45835.4767055787</v>
       </c>
       <c r="O653" t="n">
         <v>24.7</v>
@@ -61876,7 +61876,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N654" s="2" t="n">
-        <v>45835.47670557999</v>
+        <v>45835.4767055787</v>
       </c>
       <c r="O654" t="n">
         <v>13.91</v>
@@ -61967,7 +61967,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N655" s="2" t="n">
-        <v>45835.47670557999</v>
+        <v>45835.4767055787</v>
       </c>
       <c r="O655" t="n">
         <v>39.4</v>
@@ -62062,7 +62062,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N656" s="2" t="n">
-        <v>45835.47670557999</v>
+        <v>45835.4767055787</v>
       </c>
       <c r="O656" t="n">
         <v>23962</v>
@@ -62157,7 +62157,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N657" s="2" t="n">
-        <v>45835.47670557999</v>
+        <v>45835.4767055787</v>
       </c>
       <c r="O657" t="n">
         <v>46.78</v>
@@ -62198,6 +62198,760 @@
         <v>0.5990515947341919</v>
       </c>
       <c r="AA657" t="n">
+        <v>12.27674007415771</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F658" t="n">
+        <v>1</v>
+      </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H658" t="n">
+        <v>1</v>
+      </c>
+      <c r="I658" t="n">
+        <v>1</v>
+      </c>
+      <c r="J658" t="n">
+        <v>1</v>
+      </c>
+      <c r="K658" t="n">
+        <v>100</v>
+      </c>
+      <c r="L658" t="n">
+        <v>100</v>
+      </c>
+      <c r="M658" t="n">
+        <v>100</v>
+      </c>
+      <c r="N658" s="2" t="n">
+        <v>45835.54062481209</v>
+      </c>
+      <c r="O658" t="n">
+        <v>1</v>
+      </c>
+      <c r="P658" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q658" t="n">
+        <v>1</v>
+      </c>
+      <c r="R658" t="n">
+        <v>1</v>
+      </c>
+      <c r="S658" t="n">
+        <v>0</v>
+      </c>
+      <c r="T658" t="n">
+        <v>45.43580260334033</v>
+      </c>
+      <c r="U658" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V658" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W658" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X658" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y658" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z658" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA658" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr"/>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E659" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F659" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H659" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I659" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J659" t="n">
+        <v>3</v>
+      </c>
+      <c r="K659" t="n">
+        <v>10</v>
+      </c>
+      <c r="L659" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M659" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N659" s="2" t="n">
+        <v>45835.54062481209</v>
+      </c>
+      <c r="O659" t="n">
+        <v>370.5</v>
+      </c>
+      <c r="P659" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q659" t="n">
+        <v>0.85485</v>
+      </c>
+      <c r="R659" t="n">
+        <v>433.4093700649237</v>
+      </c>
+      <c r="S659" t="n">
+        <v>1111.5</v>
+      </c>
+      <c r="T659" t="n">
+        <v>1300.228110194771</v>
+      </c>
+      <c r="U659" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V659" t="n">
+        <v>0.007708082879570144</v>
+      </c>
+      <c r="W659" t="n">
+        <v>0.006317083829680881</v>
+      </c>
+      <c r="X659" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y659" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z659" t="n">
+        <v>0.5015593767166138</v>
+      </c>
+      <c r="AA659" t="n">
+        <v>12.0281548500061</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E660" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F660" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H660" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I660" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J660" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K660" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L660" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M660" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N660" s="2" t="n">
+        <v>45835.54062481209</v>
+      </c>
+      <c r="O660" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="P660" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q660" t="n">
+        <v>1.79456</v>
+      </c>
+      <c r="R660" t="n">
+        <v>0.4039987517831669</v>
+      </c>
+      <c r="S660" t="n">
+        <v>2656.4</v>
+      </c>
+      <c r="T660" t="n">
+        <v>1480.251426533524</v>
+      </c>
+      <c r="U660" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="V660" t="n">
+        <v>0</v>
+      </c>
+      <c r="W660" t="n">
+        <v>-0.01113922075606277</v>
+      </c>
+      <c r="X660" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y660" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z660" t="n">
+        <v>0.4815215170383453</v>
+      </c>
+      <c r="AA660" t="n">
+        <v>11.57751679420471</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E661" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F661" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H661" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I661" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J661" t="n">
+        <v>537</v>
+      </c>
+      <c r="K661" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L661" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M661" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N661" s="2" t="n">
+        <v>45835.54062481209</v>
+      </c>
+      <c r="O661" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="P661" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q661" t="n">
+        <v>9.22148</v>
+      </c>
+      <c r="R661" t="n">
+        <v>2.678528826175408</v>
+      </c>
+      <c r="S661" t="n">
+        <v>13263.9</v>
+      </c>
+      <c r="T661" t="n">
+        <v>1438.369979656194</v>
+      </c>
+      <c r="U661" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V661" t="n">
+        <v>-0.01984126984126988</v>
+      </c>
+      <c r="W661" t="n">
+        <v>-0.03907353197651509</v>
+      </c>
+      <c r="X661" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y661" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z661" t="n">
+        <v>0.4985511600971222</v>
+      </c>
+      <c r="AA661" t="n">
+        <v>9.835646152496338</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E662" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F662" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H662" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I662" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J662" t="n">
+        <v>121</v>
+      </c>
+      <c r="K662" t="n">
+        <v>12</v>
+      </c>
+      <c r="L662" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M662" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N662" s="2" t="n">
+        <v>45835.54062481209</v>
+      </c>
+      <c r="O662" t="n">
+        <v>13.91</v>
+      </c>
+      <c r="P662" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q662" t="n">
+        <v>1.1748121</v>
+      </c>
+      <c r="R662" t="n">
+        <v>11.84019129527181</v>
+      </c>
+      <c r="S662" t="n">
+        <v>1683.11</v>
+      </c>
+      <c r="T662" t="n">
+        <v>1432.66314672789</v>
+      </c>
+      <c r="U662" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V662" t="n">
+        <v>-0.01904090267983072</v>
+      </c>
+      <c r="W662" t="n">
+        <v>-0.03946590065804179</v>
+      </c>
+      <c r="X662" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y662" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z662" t="n">
+        <v>0.5161105990409851</v>
+      </c>
+      <c r="AA662" t="n">
+        <v>13.94983839988708</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr"/>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E663" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F663" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H663" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I663" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J663" t="n">
+        <v>162</v>
+      </c>
+      <c r="K663" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L663" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M663" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N663" s="2" t="n">
+        <v>45835.54062481209</v>
+      </c>
+      <c r="O663" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="P663" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q663" t="n">
+        <v>4.23872</v>
+      </c>
+      <c r="R663" t="n">
+        <v>9.271666918314963</v>
+      </c>
+      <c r="S663" t="n">
+        <v>6366.599999999999</v>
+      </c>
+      <c r="T663" t="n">
+        <v>1502.010040767024</v>
+      </c>
+      <c r="U663" t="n">
+        <v>8.372132556404468</v>
+      </c>
+      <c r="V663" t="n">
+        <v>0.002551020408163129</v>
+      </c>
+      <c r="W663" t="n">
+        <v>0.008698230183852074</v>
+      </c>
+      <c r="X663" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y663" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z663" t="n">
+        <v>0.5935001373291016</v>
+      </c>
+      <c r="AA663" t="n">
+        <v>12.80392378997803</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E664" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F664" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H664" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I664" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J664" t="n">
+        <v>101</v>
+      </c>
+      <c r="K664" t="n">
+        <v>11</v>
+      </c>
+      <c r="L664" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M664" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N664" s="2" t="n">
+        <v>45835.54062481209</v>
+      </c>
+      <c r="O664" t="n">
+        <v>23581</v>
+      </c>
+      <c r="P664" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q664" t="n">
+        <v>2087.86</v>
+      </c>
+      <c r="R664" t="n">
+        <v>11.29433965878938</v>
+      </c>
+      <c r="S664" t="n">
+        <v>2381681</v>
+      </c>
+      <c r="T664" t="n">
+        <v>1140.728305537727</v>
+      </c>
+      <c r="U664" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V664" t="n">
+        <v>-0.03860893672537513</v>
+      </c>
+      <c r="W664" t="n">
+        <v>-0.05315049112950787</v>
+      </c>
+      <c r="X664" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y664" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z664" t="n">
+        <v>0.4108201563358307</v>
+      </c>
+      <c r="AA664" t="n">
+        <v>10.51282495260239</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E665" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F665" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H665" t="n">
+        <v>1</v>
+      </c>
+      <c r="I665" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J665" t="n">
+        <v>30</v>
+      </c>
+      <c r="K665" t="n">
+        <v>9</v>
+      </c>
+      <c r="L665" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M665" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N665" s="2" t="n">
+        <v>45835.54062481209</v>
+      </c>
+      <c r="O665" t="n">
+        <v>46.76</v>
+      </c>
+      <c r="P665" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q665" t="n">
+        <v>1</v>
+      </c>
+      <c r="R665" t="n">
+        <v>46.76</v>
+      </c>
+      <c r="S665" t="n">
+        <v>1402.8</v>
+      </c>
+      <c r="T665" t="n">
+        <v>1402.8</v>
+      </c>
+      <c r="U665" t="n">
+        <v>42.174</v>
+      </c>
+      <c r="V665" t="n">
+        <v>0.02364273204903666</v>
+      </c>
+      <c r="W665" t="n">
+        <v>0.02364273204903666</v>
+      </c>
+      <c r="X665" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y665" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z665" t="n">
+        <v>0.5990515947341919</v>
+      </c>
+      <c r="AA665" t="n">
         <v>12.27674007415771</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA665"/>
+  <dimension ref="A1:AA673"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62254,7 +62254,7 @@
         <v>100</v>
       </c>
       <c r="N658" s="2" t="n">
-        <v>45835.54062481209</v>
+        <v>45835.54062481481</v>
       </c>
       <c r="O658" t="n">
         <v>1</v>
@@ -62345,7 +62345,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N659" s="2" t="n">
-        <v>45835.54062481209</v>
+        <v>45835.54062481481</v>
       </c>
       <c r="O659" t="n">
         <v>370.5</v>
@@ -62440,7 +62440,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N660" s="2" t="n">
-        <v>45835.54062481209</v>
+        <v>45835.54062481481</v>
       </c>
       <c r="O660" t="n">
         <v>0.725</v>
@@ -62535,7 +62535,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N661" s="2" t="n">
-        <v>45835.54062481209</v>
+        <v>45835.54062481481</v>
       </c>
       <c r="O661" t="n">
         <v>24.7</v>
@@ -62630,7 +62630,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N662" s="2" t="n">
-        <v>45835.54062481209</v>
+        <v>45835.54062481481</v>
       </c>
       <c r="O662" t="n">
         <v>13.91</v>
@@ -62721,7 +62721,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N663" s="2" t="n">
-        <v>45835.54062481209</v>
+        <v>45835.54062481481</v>
       </c>
       <c r="O663" t="n">
         <v>39.3</v>
@@ -62816,7 +62816,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N664" s="2" t="n">
-        <v>45835.54062481209</v>
+        <v>45835.54062481481</v>
       </c>
       <c r="O664" t="n">
         <v>23581</v>
@@ -62911,7 +62911,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N665" s="2" t="n">
-        <v>45835.54062481209</v>
+        <v>45835.54062481481</v>
       </c>
       <c r="O665" t="n">
         <v>46.76</v>
@@ -62952,6 +62952,760 @@
         <v>0.5990515947341919</v>
       </c>
       <c r="AA665" t="n">
+        <v>12.27674007415771</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F666" t="n">
+        <v>1</v>
+      </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H666" t="n">
+        <v>1</v>
+      </c>
+      <c r="I666" t="n">
+        <v>1</v>
+      </c>
+      <c r="J666" t="n">
+        <v>1</v>
+      </c>
+      <c r="K666" t="n">
+        <v>100</v>
+      </c>
+      <c r="L666" t="n">
+        <v>100</v>
+      </c>
+      <c r="M666" t="n">
+        <v>100</v>
+      </c>
+      <c r="N666" s="2" t="n">
+        <v>45835.56960396613</v>
+      </c>
+      <c r="O666" t="n">
+        <v>1</v>
+      </c>
+      <c r="P666" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q666" t="n">
+        <v>1</v>
+      </c>
+      <c r="R666" t="n">
+        <v>1</v>
+      </c>
+      <c r="S666" t="n">
+        <v>0</v>
+      </c>
+      <c r="T666" t="n">
+        <v>45.43580260334033</v>
+      </c>
+      <c r="U666" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V666" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W666" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X666" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y666" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z666" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA666" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr"/>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E667" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F667" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H667" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I667" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J667" t="n">
+        <v>3</v>
+      </c>
+      <c r="K667" t="n">
+        <v>10</v>
+      </c>
+      <c r="L667" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M667" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N667" s="2" t="n">
+        <v>45835.56960396613</v>
+      </c>
+      <c r="O667" t="n">
+        <v>373.75</v>
+      </c>
+      <c r="P667" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q667" t="n">
+        <v>0.8547</v>
+      </c>
+      <c r="R667" t="n">
+        <v>437.2879372879373</v>
+      </c>
+      <c r="S667" t="n">
+        <v>1121.25</v>
+      </c>
+      <c r="T667" t="n">
+        <v>1311.863811863812</v>
+      </c>
+      <c r="U667" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V667" t="n">
+        <v>0.01654762746623284</v>
+      </c>
+      <c r="W667" t="n">
+        <v>0.01532258469533065</v>
+      </c>
+      <c r="X667" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y667" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z667" t="n">
+        <v>0.5015593767166138</v>
+      </c>
+      <c r="AA667" t="n">
+        <v>12.0281548500061</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E668" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F668" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H668" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I668" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J668" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K668" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L668" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M668" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N668" s="2" t="n">
+        <v>45835.56960396613</v>
+      </c>
+      <c r="O668" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="P668" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q668" t="n">
+        <v>1.79562</v>
+      </c>
+      <c r="R668" t="n">
+        <v>0.4037602610797384</v>
+      </c>
+      <c r="S668" t="n">
+        <v>2656.4</v>
+      </c>
+      <c r="T668" t="n">
+        <v>1479.377596596162</v>
+      </c>
+      <c r="U668" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="V668" t="n">
+        <v>0</v>
+      </c>
+      <c r="W668" t="n">
+        <v>-0.01172297033893588</v>
+      </c>
+      <c r="X668" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y668" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z668" t="n">
+        <v>0.4815215170383453</v>
+      </c>
+      <c r="AA668" t="n">
+        <v>11.57751679420471</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E669" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F669" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H669" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I669" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J669" t="n">
+        <v>537</v>
+      </c>
+      <c r="K669" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L669" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M669" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N669" s="2" t="n">
+        <v>45835.56960396613</v>
+      </c>
+      <c r="O669" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="P669" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q669" t="n">
+        <v>9.207800000000001</v>
+      </c>
+      <c r="R669" t="n">
+        <v>2.682508308173505</v>
+      </c>
+      <c r="S669" t="n">
+        <v>13263.9</v>
+      </c>
+      <c r="T669" t="n">
+        <v>1440.506961489172</v>
+      </c>
+      <c r="U669" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V669" t="n">
+        <v>-0.01984126984126988</v>
+      </c>
+      <c r="W669" t="n">
+        <v>-0.03764588649305967</v>
+      </c>
+      <c r="X669" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y669" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z669" t="n">
+        <v>0.4985511600971222</v>
+      </c>
+      <c r="AA669" t="n">
+        <v>9.835646152496338</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E670" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F670" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H670" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I670" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J670" t="n">
+        <v>121</v>
+      </c>
+      <c r="K670" t="n">
+        <v>12</v>
+      </c>
+      <c r="L670" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M670" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N670" s="2" t="n">
+        <v>45835.56960396613</v>
+      </c>
+      <c r="O670" t="n">
+        <v>13.28</v>
+      </c>
+      <c r="P670" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q670" t="n">
+        <v>1.1734335</v>
+      </c>
+      <c r="R670" t="n">
+        <v>11.31721567519591</v>
+      </c>
+      <c r="S670" t="n">
+        <v>1606.88</v>
+      </c>
+      <c r="T670" t="n">
+        <v>1369.383096698705</v>
+      </c>
+      <c r="U670" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V670" t="n">
+        <v>-0.06346967559943584</v>
+      </c>
+      <c r="W670" t="n">
+        <v>-0.08189223513863508</v>
+      </c>
+      <c r="X670" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y670" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z670" t="n">
+        <v>0.5161105990409851</v>
+      </c>
+      <c r="AA670" t="n">
+        <v>13.94983839988708</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr"/>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E671" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F671" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H671" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I671" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J671" t="n">
+        <v>162</v>
+      </c>
+      <c r="K671" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L671" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M671" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N671" s="2" t="n">
+        <v>45835.56960396613</v>
+      </c>
+      <c r="O671" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="P671" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q671" t="n">
+        <v>4.2386</v>
+      </c>
+      <c r="R671" t="n">
+        <v>9.295522106355872</v>
+      </c>
+      <c r="S671" t="n">
+        <v>6382.8</v>
+      </c>
+      <c r="T671" t="n">
+        <v>1505.874581229651</v>
+      </c>
+      <c r="U671" t="n">
+        <v>8.372132556404468</v>
+      </c>
+      <c r="V671" t="n">
+        <v>0.005102040816326481</v>
+      </c>
+      <c r="W671" t="n">
+        <v>0.01129352250502413</v>
+      </c>
+      <c r="X671" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y671" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z671" t="n">
+        <v>0.5935001373291016</v>
+      </c>
+      <c r="AA671" t="n">
+        <v>12.80392378997803</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E672" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F672" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H672" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I672" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J672" t="n">
+        <v>101</v>
+      </c>
+      <c r="K672" t="n">
+        <v>11</v>
+      </c>
+      <c r="L672" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M672" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N672" s="2" t="n">
+        <v>45835.56960396613</v>
+      </c>
+      <c r="O672" t="n">
+        <v>23569</v>
+      </c>
+      <c r="P672" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q672" t="n">
+        <v>2091.84</v>
+      </c>
+      <c r="R672" t="n">
+        <v>11.26711411962674</v>
+      </c>
+      <c r="S672" t="n">
+        <v>2380469</v>
+      </c>
+      <c r="T672" t="n">
+        <v>1137.978526082301</v>
+      </c>
+      <c r="U672" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V672" t="n">
+        <v>-0.03909817351598177</v>
+      </c>
+      <c r="W672" t="n">
+        <v>-0.05543291658895655</v>
+      </c>
+      <c r="X672" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y672" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z672" t="n">
+        <v>0.4108201563358307</v>
+      </c>
+      <c r="AA672" t="n">
+        <v>10.51282495260239</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E673" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F673" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H673" t="n">
+        <v>1</v>
+      </c>
+      <c r="I673" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J673" t="n">
+        <v>30</v>
+      </c>
+      <c r="K673" t="n">
+        <v>9</v>
+      </c>
+      <c r="L673" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M673" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N673" s="2" t="n">
+        <v>45835.56960396613</v>
+      </c>
+      <c r="O673" t="n">
+        <v>46.66</v>
+      </c>
+      <c r="P673" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q673" t="n">
+        <v>1</v>
+      </c>
+      <c r="R673" t="n">
+        <v>46.66</v>
+      </c>
+      <c r="S673" t="n">
+        <v>1399.8</v>
+      </c>
+      <c r="T673" t="n">
+        <v>1399.8</v>
+      </c>
+      <c r="U673" t="n">
+        <v>42.174</v>
+      </c>
+      <c r="V673" t="n">
+        <v>0.02145359019264448</v>
+      </c>
+      <c r="W673" t="n">
+        <v>0.02145359019264448</v>
+      </c>
+      <c r="X673" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y673" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z673" t="n">
+        <v>0.5990515947341919</v>
+      </c>
+      <c r="AA673" t="n">
         <v>12.27674007415771</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA673"/>
+  <dimension ref="A1:AA681"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63008,7 +63008,7 @@
         <v>100</v>
       </c>
       <c r="N666" s="2" t="n">
-        <v>45835.56960396613</v>
+        <v>45835.56960396991</v>
       </c>
       <c r="O666" t="n">
         <v>1</v>
@@ -63099,7 +63099,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N667" s="2" t="n">
-        <v>45835.56960396613</v>
+        <v>45835.56960396991</v>
       </c>
       <c r="O667" t="n">
         <v>373.75</v>
@@ -63194,7 +63194,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N668" s="2" t="n">
-        <v>45835.56960396613</v>
+        <v>45835.56960396991</v>
       </c>
       <c r="O668" t="n">
         <v>0.725</v>
@@ -63289,7 +63289,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N669" s="2" t="n">
-        <v>45835.56960396613</v>
+        <v>45835.56960396991</v>
       </c>
       <c r="O669" t="n">
         <v>24.7</v>
@@ -63384,7 +63384,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N670" s="2" t="n">
-        <v>45835.56960396613</v>
+        <v>45835.56960396991</v>
       </c>
       <c r="O670" t="n">
         <v>13.28</v>
@@ -63475,7 +63475,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N671" s="2" t="n">
-        <v>45835.56960396613</v>
+        <v>45835.56960396991</v>
       </c>
       <c r="O671" t="n">
         <v>39.4</v>
@@ -63570,7 +63570,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N672" s="2" t="n">
-        <v>45835.56960396613</v>
+        <v>45835.56960396991</v>
       </c>
       <c r="O672" t="n">
         <v>23569</v>
@@ -63665,7 +63665,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N673" s="2" t="n">
-        <v>45835.56960396613</v>
+        <v>45835.56960396991</v>
       </c>
       <c r="O673" t="n">
         <v>46.66</v>
@@ -63706,6 +63706,760 @@
         <v>0.5990515947341919</v>
       </c>
       <c r="AA673" t="n">
+        <v>12.27674007415771</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F674" t="n">
+        <v>1</v>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H674" t="n">
+        <v>1</v>
+      </c>
+      <c r="I674" t="n">
+        <v>1</v>
+      </c>
+      <c r="J674" t="n">
+        <v>1</v>
+      </c>
+      <c r="K674" t="n">
+        <v>100</v>
+      </c>
+      <c r="L674" t="n">
+        <v>100</v>
+      </c>
+      <c r="M674" t="n">
+        <v>100</v>
+      </c>
+      <c r="N674" s="2" t="n">
+        <v>45835.6062320503</v>
+      </c>
+      <c r="O674" t="n">
+        <v>1</v>
+      </c>
+      <c r="P674" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q674" t="n">
+        <v>1</v>
+      </c>
+      <c r="R674" t="n">
+        <v>1</v>
+      </c>
+      <c r="S674" t="n">
+        <v>0</v>
+      </c>
+      <c r="T674" t="n">
+        <v>45.43580260334033</v>
+      </c>
+      <c r="U674" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V674" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W674" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X674" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y674" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z674" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA674" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr"/>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E675" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F675" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H675" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I675" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J675" t="n">
+        <v>3</v>
+      </c>
+      <c r="K675" t="n">
+        <v>10</v>
+      </c>
+      <c r="L675" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M675" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N675" s="2" t="n">
+        <v>45835.6062320503</v>
+      </c>
+      <c r="O675" t="n">
+        <v>373.75</v>
+      </c>
+      <c r="P675" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q675" t="n">
+        <v>0.85477</v>
+      </c>
+      <c r="R675" t="n">
+        <v>437.252126302982</v>
+      </c>
+      <c r="S675" t="n">
+        <v>1121.25</v>
+      </c>
+      <c r="T675" t="n">
+        <v>1311.756378908946</v>
+      </c>
+      <c r="U675" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V675" t="n">
+        <v>0.01654762746623284</v>
+      </c>
+      <c r="W675" t="n">
+        <v>0.01523943650233273</v>
+      </c>
+      <c r="X675" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y675" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z675" t="n">
+        <v>0.5015593767166138</v>
+      </c>
+      <c r="AA675" t="n">
+        <v>12.0281548500061</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E676" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F676" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H676" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I676" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J676" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K676" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L676" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M676" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N676" s="2" t="n">
+        <v>45835.6062320503</v>
+      </c>
+      <c r="O676" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="P676" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q676" t="n">
+        <v>1.79566</v>
+      </c>
+      <c r="R676" t="n">
+        <v>0.4037512669436307</v>
+      </c>
+      <c r="S676" t="n">
+        <v>2656.4</v>
+      </c>
+      <c r="T676" t="n">
+        <v>1479.344642081463</v>
+      </c>
+      <c r="U676" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="V676" t="n">
+        <v>0</v>
+      </c>
+      <c r="W676" t="n">
+        <v>-0.01174498513081546</v>
+      </c>
+      <c r="X676" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y676" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z676" t="n">
+        <v>0.4815215170383453</v>
+      </c>
+      <c r="AA676" t="n">
+        <v>11.57751679420471</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E677" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F677" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H677" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I677" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J677" t="n">
+        <v>537</v>
+      </c>
+      <c r="K677" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L677" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M677" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N677" s="2" t="n">
+        <v>45835.6062320503</v>
+      </c>
+      <c r="O677" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="P677" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q677" t="n">
+        <v>9.201230000000001</v>
+      </c>
+      <c r="R677" t="n">
+        <v>2.684423712916642</v>
+      </c>
+      <c r="S677" t="n">
+        <v>13263.9</v>
+      </c>
+      <c r="T677" t="n">
+        <v>1441.535533836237</v>
+      </c>
+      <c r="U677" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V677" t="n">
+        <v>-0.01984126984126988</v>
+      </c>
+      <c r="W677" t="n">
+        <v>-0.03695873200113409</v>
+      </c>
+      <c r="X677" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y677" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z677" t="n">
+        <v>0.4985511600971222</v>
+      </c>
+      <c r="AA677" t="n">
+        <v>9.835646152496338</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E678" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F678" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G678" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H678" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I678" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J678" t="n">
+        <v>121</v>
+      </c>
+      <c r="K678" t="n">
+        <v>12</v>
+      </c>
+      <c r="L678" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M678" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N678" s="2" t="n">
+        <v>45835.6062320503</v>
+      </c>
+      <c r="O678" t="n">
+        <v>13.43</v>
+      </c>
+      <c r="P678" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q678" t="n">
+        <v>1.1724703</v>
+      </c>
+      <c r="R678" t="n">
+        <v>11.45444792929936</v>
+      </c>
+      <c r="S678" t="n">
+        <v>1625.03</v>
+      </c>
+      <c r="T678" t="n">
+        <v>1385.988199445223</v>
+      </c>
+      <c r="U678" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V678" t="n">
+        <v>-0.05289139633286322</v>
+      </c>
+      <c r="W678" t="n">
+        <v>-0.07075928497687856</v>
+      </c>
+      <c r="X678" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y678" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z678" t="n">
+        <v>0.5161105990409851</v>
+      </c>
+      <c r="AA678" t="n">
+        <v>13.94983839988708</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr"/>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E679" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F679" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H679" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I679" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J679" t="n">
+        <v>162</v>
+      </c>
+      <c r="K679" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L679" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M679" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N679" s="2" t="n">
+        <v>45835.6062320503</v>
+      </c>
+      <c r="O679" t="n">
+        <v>39.45</v>
+      </c>
+      <c r="P679" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q679" t="n">
+        <v>4.24057</v>
+      </c>
+      <c r="R679" t="n">
+        <v>9.302994644587875</v>
+      </c>
+      <c r="S679" t="n">
+        <v>6390.900000000001</v>
+      </c>
+      <c r="T679" t="n">
+        <v>1507.085132423236</v>
+      </c>
+      <c r="U679" t="n">
+        <v>8.372695180129087</v>
+      </c>
+      <c r="V679" t="n">
+        <v>0.006377551020408267</v>
+      </c>
+      <c r="W679" t="n">
+        <v>0.01210648700817218</v>
+      </c>
+      <c r="X679" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y679" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z679" t="n">
+        <v>0.5935001373291016</v>
+      </c>
+      <c r="AA679" t="n">
+        <v>12.80392378997803</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E680" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F680" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G680" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H680" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I680" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J680" t="n">
+        <v>101</v>
+      </c>
+      <c r="K680" t="n">
+        <v>11</v>
+      </c>
+      <c r="L680" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M680" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N680" s="2" t="n">
+        <v>45835.6062320503</v>
+      </c>
+      <c r="O680" t="n">
+        <v>23715</v>
+      </c>
+      <c r="P680" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q680" t="n">
+        <v>2088.52</v>
+      </c>
+      <c r="R680" t="n">
+        <v>11.35493076436903</v>
+      </c>
+      <c r="S680" t="n">
+        <v>2395215</v>
+      </c>
+      <c r="T680" t="n">
+        <v>1146.848007201272</v>
+      </c>
+      <c r="U680" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V680" t="n">
+        <v>-0.03314579256360073</v>
+      </c>
+      <c r="W680" t="n">
+        <v>-0.04807089725388358</v>
+      </c>
+      <c r="X680" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y680" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z680" t="n">
+        <v>0.4108201563358307</v>
+      </c>
+      <c r="AA680" t="n">
+        <v>10.51282495260239</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E681" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F681" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H681" t="n">
+        <v>1</v>
+      </c>
+      <c r="I681" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J681" t="n">
+        <v>30</v>
+      </c>
+      <c r="K681" t="n">
+        <v>9</v>
+      </c>
+      <c r="L681" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M681" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N681" s="2" t="n">
+        <v>45835.6062320503</v>
+      </c>
+      <c r="O681" t="n">
+        <v>46.46</v>
+      </c>
+      <c r="P681" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q681" t="n">
+        <v>1</v>
+      </c>
+      <c r="R681" t="n">
+        <v>46.46</v>
+      </c>
+      <c r="S681" t="n">
+        <v>1393.8</v>
+      </c>
+      <c r="T681" t="n">
+        <v>1393.8</v>
+      </c>
+      <c r="U681" t="n">
+        <v>42.174</v>
+      </c>
+      <c r="V681" t="n">
+        <v>0.01707530647985989</v>
+      </c>
+      <c r="W681" t="n">
+        <v>0.01707530647985989</v>
+      </c>
+      <c r="X681" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y681" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z681" t="n">
+        <v>0.5990515947341919</v>
+      </c>
+      <c r="AA681" t="n">
         <v>12.27674007415771</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA681"/>
+  <dimension ref="A1:AA689"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63762,7 +63762,7 @@
         <v>100</v>
       </c>
       <c r="N674" s="2" t="n">
-        <v>45835.6062320503</v>
+        <v>45835.60623204861</v>
       </c>
       <c r="O674" t="n">
         <v>1</v>
@@ -63853,7 +63853,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N675" s="2" t="n">
-        <v>45835.6062320503</v>
+        <v>45835.60623204861</v>
       </c>
       <c r="O675" t="n">
         <v>373.75</v>
@@ -63948,7 +63948,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N676" s="2" t="n">
-        <v>45835.6062320503</v>
+        <v>45835.60623204861</v>
       </c>
       <c r="O676" t="n">
         <v>0.725</v>
@@ -64043,7 +64043,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N677" s="2" t="n">
-        <v>45835.6062320503</v>
+        <v>45835.60623204861</v>
       </c>
       <c r="O677" t="n">
         <v>24.7</v>
@@ -64138,7 +64138,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N678" s="2" t="n">
-        <v>45835.6062320503</v>
+        <v>45835.60623204861</v>
       </c>
       <c r="O678" t="n">
         <v>13.43</v>
@@ -64229,7 +64229,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N679" s="2" t="n">
-        <v>45835.6062320503</v>
+        <v>45835.60623204861</v>
       </c>
       <c r="O679" t="n">
         <v>39.45</v>
@@ -64324,7 +64324,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N680" s="2" t="n">
-        <v>45835.6062320503</v>
+        <v>45835.60623204861</v>
       </c>
       <c r="O680" t="n">
         <v>23715</v>
@@ -64419,7 +64419,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N681" s="2" t="n">
-        <v>45835.6062320503</v>
+        <v>45835.60623204861</v>
       </c>
       <c r="O681" t="n">
         <v>46.46</v>
@@ -64460,6 +64460,760 @@
         <v>0.5990515947341919</v>
       </c>
       <c r="AA681" t="n">
+        <v>12.27674007415771</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F682" t="n">
+        <v>1</v>
+      </c>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H682" t="n">
+        <v>1</v>
+      </c>
+      <c r="I682" t="n">
+        <v>1</v>
+      </c>
+      <c r="J682" t="n">
+        <v>1</v>
+      </c>
+      <c r="K682" t="n">
+        <v>100</v>
+      </c>
+      <c r="L682" t="n">
+        <v>100</v>
+      </c>
+      <c r="M682" t="n">
+        <v>100</v>
+      </c>
+      <c r="N682" s="2" t="n">
+        <v>45835.64685714407</v>
+      </c>
+      <c r="O682" t="n">
+        <v>1</v>
+      </c>
+      <c r="P682" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q682" t="n">
+        <v>1</v>
+      </c>
+      <c r="R682" t="n">
+        <v>1</v>
+      </c>
+      <c r="S682" t="n">
+        <v>0</v>
+      </c>
+      <c r="T682" t="n">
+        <v>45.43580260334033</v>
+      </c>
+      <c r="U682" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V682" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W682" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X682" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y682" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z682" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA682" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr"/>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E683" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F683" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H683" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I683" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J683" t="n">
+        <v>3</v>
+      </c>
+      <c r="K683" t="n">
+        <v>10</v>
+      </c>
+      <c r="L683" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M683" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N683" s="2" t="n">
+        <v>45835.64685714407</v>
+      </c>
+      <c r="O683" t="n">
+        <v>370.5</v>
+      </c>
+      <c r="P683" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q683" t="n">
+        <v>0.85432</v>
+      </c>
+      <c r="R683" t="n">
+        <v>433.6782470268752</v>
+      </c>
+      <c r="S683" t="n">
+        <v>1111.5</v>
+      </c>
+      <c r="T683" t="n">
+        <v>1301.034741080626</v>
+      </c>
+      <c r="U683" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V683" t="n">
+        <v>0.007708082879570144</v>
+      </c>
+      <c r="W683" t="n">
+        <v>0.006941379239398193</v>
+      </c>
+      <c r="X683" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y683" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z683" t="n">
+        <v>0.5015593767166138</v>
+      </c>
+      <c r="AA683" t="n">
+        <v>12.0281548500061</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E684" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F684" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H684" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I684" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J684" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K684" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L684" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M684" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N684" s="2" t="n">
+        <v>45835.64685714407</v>
+      </c>
+      <c r="O684" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="P684" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q684" t="n">
+        <v>1.7933</v>
+      </c>
+      <c r="R684" t="n">
+        <v>0.4042826074834105</v>
+      </c>
+      <c r="S684" t="n">
+        <v>2656.4</v>
+      </c>
+      <c r="T684" t="n">
+        <v>1481.291473819216</v>
+      </c>
+      <c r="U684" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="V684" t="n">
+        <v>0</v>
+      </c>
+      <c r="W684" t="n">
+        <v>-0.01044443205264034</v>
+      </c>
+      <c r="X684" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y684" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z684" t="n">
+        <v>0.4815215170383453</v>
+      </c>
+      <c r="AA684" t="n">
+        <v>11.57751679420471</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E685" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F685" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H685" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I685" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J685" t="n">
+        <v>537</v>
+      </c>
+      <c r="K685" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L685" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M685" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N685" s="2" t="n">
+        <v>45835.64685714407</v>
+      </c>
+      <c r="O685" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="P685" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q685" t="n">
+        <v>9.196</v>
+      </c>
+      <c r="R685" t="n">
+        <v>2.685950413223141</v>
+      </c>
+      <c r="S685" t="n">
+        <v>13263.9</v>
+      </c>
+      <c r="T685" t="n">
+        <v>1442.355371900826</v>
+      </c>
+      <c r="U685" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V685" t="n">
+        <v>-0.01984126984126988</v>
+      </c>
+      <c r="W685" t="n">
+        <v>-0.03641102584284406</v>
+      </c>
+      <c r="X685" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y685" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z685" t="n">
+        <v>0.4985511600971222</v>
+      </c>
+      <c r="AA685" t="n">
+        <v>9.835646152496338</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E686" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F686" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H686" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I686" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J686" t="n">
+        <v>121</v>
+      </c>
+      <c r="K686" t="n">
+        <v>12</v>
+      </c>
+      <c r="L686" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M686" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N686" s="2" t="n">
+        <v>45835.64685714407</v>
+      </c>
+      <c r="O686" t="n">
+        <v>13.42</v>
+      </c>
+      <c r="P686" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q686" t="n">
+        <v>1.1717834</v>
+      </c>
+      <c r="R686" t="n">
+        <v>11.45262853186007</v>
+      </c>
+      <c r="S686" t="n">
+        <v>1623.82</v>
+      </c>
+      <c r="T686" t="n">
+        <v>1385.768052355068</v>
+      </c>
+      <c r="U686" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V686" t="n">
+        <v>-0.05359661495063472</v>
+      </c>
+      <c r="W686" t="n">
+        <v>-0.07090688337601869</v>
+      </c>
+      <c r="X686" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y686" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z686" t="n">
+        <v>0.5161105990409851</v>
+      </c>
+      <c r="AA686" t="n">
+        <v>13.94983839988708</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr"/>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E687" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F687" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H687" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I687" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J687" t="n">
+        <v>162</v>
+      </c>
+      <c r="K687" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L687" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M687" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N687" s="2" t="n">
+        <v>45835.64685714407</v>
+      </c>
+      <c r="O687" t="n">
+        <v>40</v>
+      </c>
+      <c r="P687" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q687" t="n">
+        <v>4.24009</v>
+      </c>
+      <c r="R687" t="n">
+        <v>9.433762019202423</v>
+      </c>
+      <c r="S687" t="n">
+        <v>6480</v>
+      </c>
+      <c r="T687" t="n">
+        <v>1528.269447110792</v>
+      </c>
+      <c r="U687" t="n">
+        <v>8.490385817282181</v>
+      </c>
+      <c r="V687" t="n">
+        <v>0.02040816326530615</v>
+      </c>
+      <c r="W687" t="n">
+        <v>0.02633314339063175</v>
+      </c>
+      <c r="X687" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y687" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z687" t="n">
+        <v>0.5935001373291016</v>
+      </c>
+      <c r="AA687" t="n">
+        <v>12.80392378997803</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E688" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F688" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H688" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I688" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J688" t="n">
+        <v>101</v>
+      </c>
+      <c r="K688" t="n">
+        <v>11</v>
+      </c>
+      <c r="L688" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M688" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N688" s="2" t="n">
+        <v>45835.64685714407</v>
+      </c>
+      <c r="O688" t="n">
+        <v>23869</v>
+      </c>
+      <c r="P688" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q688" t="n">
+        <v>2087.25</v>
+      </c>
+      <c r="R688" t="n">
+        <v>11.43562103245898</v>
+      </c>
+      <c r="S688" t="n">
+        <v>2410769</v>
+      </c>
+      <c r="T688" t="n">
+        <v>1154.997724278357</v>
+      </c>
+      <c r="U688" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V688" t="n">
+        <v>-0.02686725375081545</v>
+      </c>
+      <c r="W688" t="n">
+        <v>-0.04130631047681232</v>
+      </c>
+      <c r="X688" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y688" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z688" t="n">
+        <v>0.4108201563358307</v>
+      </c>
+      <c r="AA688" t="n">
+        <v>10.51282495260239</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E689" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F689" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H689" t="n">
+        <v>1</v>
+      </c>
+      <c r="I689" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J689" t="n">
+        <v>30</v>
+      </c>
+      <c r="K689" t="n">
+        <v>9</v>
+      </c>
+      <c r="L689" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M689" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N689" s="2" t="n">
+        <v>45835.64685714407</v>
+      </c>
+      <c r="O689" t="n">
+        <v>46.46</v>
+      </c>
+      <c r="P689" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q689" t="n">
+        <v>1</v>
+      </c>
+      <c r="R689" t="n">
+        <v>46.46</v>
+      </c>
+      <c r="S689" t="n">
+        <v>1393.8</v>
+      </c>
+      <c r="T689" t="n">
+        <v>1393.8</v>
+      </c>
+      <c r="U689" t="n">
+        <v>42.174</v>
+      </c>
+      <c r="V689" t="n">
+        <v>0.01707530647985989</v>
+      </c>
+      <c r="W689" t="n">
+        <v>0.01707530647985989</v>
+      </c>
+      <c r="X689" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y689" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z689" t="n">
+        <v>0.5990515947341919</v>
+      </c>
+      <c r="AA689" t="n">
         <v>12.27674007415771</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA689"/>
+  <dimension ref="A1:AA697"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64516,7 +64516,7 @@
         <v>100</v>
       </c>
       <c r="N682" s="2" t="n">
-        <v>45835.64685714407</v>
+        <v>45835.6468571412</v>
       </c>
       <c r="O682" t="n">
         <v>1</v>
@@ -64607,7 +64607,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N683" s="2" t="n">
-        <v>45835.64685714407</v>
+        <v>45835.6468571412</v>
       </c>
       <c r="O683" t="n">
         <v>370.5</v>
@@ -64702,7 +64702,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N684" s="2" t="n">
-        <v>45835.64685714407</v>
+        <v>45835.6468571412</v>
       </c>
       <c r="O684" t="n">
         <v>0.725</v>
@@ -64797,7 +64797,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N685" s="2" t="n">
-        <v>45835.64685714407</v>
+        <v>45835.6468571412</v>
       </c>
       <c r="O685" t="n">
         <v>24.7</v>
@@ -64892,7 +64892,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N686" s="2" t="n">
-        <v>45835.64685714407</v>
+        <v>45835.6468571412</v>
       </c>
       <c r="O686" t="n">
         <v>13.42</v>
@@ -64983,7 +64983,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N687" s="2" t="n">
-        <v>45835.64685714407</v>
+        <v>45835.6468571412</v>
       </c>
       <c r="O687" t="n">
         <v>40</v>
@@ -65078,7 +65078,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N688" s="2" t="n">
-        <v>45835.64685714407</v>
+        <v>45835.6468571412</v>
       </c>
       <c r="O688" t="n">
         <v>23869</v>
@@ -65173,7 +65173,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N689" s="2" t="n">
-        <v>45835.64685714407</v>
+        <v>45835.6468571412</v>
       </c>
       <c r="O689" t="n">
         <v>46.46</v>
@@ -65214,6 +65214,760 @@
         <v>0.5990515947341919</v>
       </c>
       <c r="AA689" t="n">
+        <v>12.27674007415771</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F690" t="n">
+        <v>1</v>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H690" t="n">
+        <v>1</v>
+      </c>
+      <c r="I690" t="n">
+        <v>1</v>
+      </c>
+      <c r="J690" t="n">
+        <v>1</v>
+      </c>
+      <c r="K690" t="n">
+        <v>100</v>
+      </c>
+      <c r="L690" t="n">
+        <v>100</v>
+      </c>
+      <c r="M690" t="n">
+        <v>100</v>
+      </c>
+      <c r="N690" s="2" t="n">
+        <v>45835.69198519247</v>
+      </c>
+      <c r="O690" t="n">
+        <v>1</v>
+      </c>
+      <c r="P690" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q690" t="n">
+        <v>1</v>
+      </c>
+      <c r="R690" t="n">
+        <v>1</v>
+      </c>
+      <c r="S690" t="n">
+        <v>0</v>
+      </c>
+      <c r="T690" t="n">
+        <v>45.43580260334033</v>
+      </c>
+      <c r="U690" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V690" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W690" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X690" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y690" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z690" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA690" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr"/>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E691" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F691" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H691" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I691" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J691" t="n">
+        <v>3</v>
+      </c>
+      <c r="K691" t="n">
+        <v>10</v>
+      </c>
+      <c r="L691" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M691" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N691" s="2" t="n">
+        <v>45835.69198519247</v>
+      </c>
+      <c r="O691" t="n">
+        <v>375</v>
+      </c>
+      <c r="P691" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q691" t="n">
+        <v>0.85494</v>
+      </c>
+      <c r="R691" t="n">
+        <v>438.6272720892694</v>
+      </c>
+      <c r="S691" t="n">
+        <v>1125</v>
+      </c>
+      <c r="T691" t="n">
+        <v>1315.881816267808</v>
+      </c>
+      <c r="U691" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V691" t="n">
+        <v>0.01994745230725714</v>
+      </c>
+      <c r="W691" t="n">
+        <v>0.01843233631732777</v>
+      </c>
+      <c r="X691" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y691" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z691" t="n">
+        <v>0.5015593767166138</v>
+      </c>
+      <c r="AA691" t="n">
+        <v>12.0281548500061</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E692" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F692" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H692" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I692" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J692" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K692" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L692" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M692" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N692" s="2" t="n">
+        <v>45835.69198519247</v>
+      </c>
+      <c r="O692" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="P692" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q692" t="n">
+        <v>1.79361</v>
+      </c>
+      <c r="R692" t="n">
+        <v>0.4042127329798563</v>
+      </c>
+      <c r="S692" t="n">
+        <v>2656.4</v>
+      </c>
+      <c r="T692" t="n">
+        <v>1481.035453638194</v>
+      </c>
+      <c r="U692" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="V692" t="n">
+        <v>0</v>
+      </c>
+      <c r="W692" t="n">
+        <v>-0.01061546267025715</v>
+      </c>
+      <c r="X692" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y692" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z692" t="n">
+        <v>0.4815215170383453</v>
+      </c>
+      <c r="AA692" t="n">
+        <v>11.57751679420471</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E693" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F693" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H693" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I693" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J693" t="n">
+        <v>537</v>
+      </c>
+      <c r="K693" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L693" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M693" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N693" s="2" t="n">
+        <v>45835.69198519247</v>
+      </c>
+      <c r="O693" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="P693" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q693" t="n">
+        <v>9.20219</v>
+      </c>
+      <c r="R693" t="n">
+        <v>2.684143665801293</v>
+      </c>
+      <c r="S693" t="n">
+        <v>13263.9</v>
+      </c>
+      <c r="T693" t="n">
+        <v>1441.385148535294</v>
+      </c>
+      <c r="U693" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V693" t="n">
+        <v>-0.01984126984126988</v>
+      </c>
+      <c r="W693" t="n">
+        <v>-0.03705919934828494</v>
+      </c>
+      <c r="X693" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y693" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z693" t="n">
+        <v>0.4985511600971222</v>
+      </c>
+      <c r="AA693" t="n">
+        <v>9.835646152496338</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E694" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F694" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H694" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I694" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J694" t="n">
+        <v>121</v>
+      </c>
+      <c r="K694" t="n">
+        <v>12</v>
+      </c>
+      <c r="L694" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M694" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N694" s="2" t="n">
+        <v>45835.69198519247</v>
+      </c>
+      <c r="O694" t="n">
+        <v>13.415</v>
+      </c>
+      <c r="P694" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q694" t="n">
+        <v>1.1727453</v>
+      </c>
+      <c r="R694" t="n">
+        <v>11.43897144588855</v>
+      </c>
+      <c r="S694" t="n">
+        <v>1623.215</v>
+      </c>
+      <c r="T694" t="n">
+        <v>1384.115544952514</v>
+      </c>
+      <c r="U694" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V694" t="n">
+        <v>-0.05394922425952053</v>
+      </c>
+      <c r="W694" t="n">
+        <v>-0.07201481283814892</v>
+      </c>
+      <c r="X694" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y694" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z694" t="n">
+        <v>0.5161105990409851</v>
+      </c>
+      <c r="AA694" t="n">
+        <v>13.94983839988708</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr"/>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E695" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F695" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H695" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I695" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J695" t="n">
+        <v>162</v>
+      </c>
+      <c r="K695" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L695" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M695" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N695" s="2" t="n">
+        <v>45835.69198519247</v>
+      </c>
+      <c r="O695" t="n">
+        <v>40</v>
+      </c>
+      <c r="P695" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q695" t="n">
+        <v>4.23911</v>
+      </c>
+      <c r="R695" t="n">
+        <v>9.435942921981265</v>
+      </c>
+      <c r="S695" t="n">
+        <v>6480</v>
+      </c>
+      <c r="T695" t="n">
+        <v>1528.622753360965</v>
+      </c>
+      <c r="U695" t="n">
+        <v>8.492348629783139</v>
+      </c>
+      <c r="V695" t="n">
+        <v>0.02040816326530615</v>
+      </c>
+      <c r="W695" t="n">
+        <v>0.02657041170415098</v>
+      </c>
+      <c r="X695" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y695" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z695" t="n">
+        <v>0.5935001373291016</v>
+      </c>
+      <c r="AA695" t="n">
+        <v>12.80392378997803</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E696" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F696" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H696" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I696" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J696" t="n">
+        <v>101</v>
+      </c>
+      <c r="K696" t="n">
+        <v>11</v>
+      </c>
+      <c r="L696" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M696" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N696" s="2" t="n">
+        <v>45835.69198519247</v>
+      </c>
+      <c r="O696" t="n">
+        <v>23869</v>
+      </c>
+      <c r="P696" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q696" t="n">
+        <v>2090.19</v>
+      </c>
+      <c r="R696" t="n">
+        <v>11.41953602304097</v>
+      </c>
+      <c r="S696" t="n">
+        <v>2410769</v>
+      </c>
+      <c r="T696" t="n">
+        <v>1153.373138327138</v>
+      </c>
+      <c r="U696" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V696" t="n">
+        <v>-0.02686725375081545</v>
+      </c>
+      <c r="W696" t="n">
+        <v>-0.04265478092552666</v>
+      </c>
+      <c r="X696" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y696" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z696" t="n">
+        <v>0.4108201563358307</v>
+      </c>
+      <c r="AA696" t="n">
+        <v>10.51282495260239</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E697" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F697" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H697" t="n">
+        <v>1</v>
+      </c>
+      <c r="I697" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J697" t="n">
+        <v>30</v>
+      </c>
+      <c r="K697" t="n">
+        <v>9</v>
+      </c>
+      <c r="L697" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M697" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N697" s="2" t="n">
+        <v>45835.69198519247</v>
+      </c>
+      <c r="O697" t="n">
+        <v>46.46</v>
+      </c>
+      <c r="P697" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q697" t="n">
+        <v>1</v>
+      </c>
+      <c r="R697" t="n">
+        <v>46.46</v>
+      </c>
+      <c r="S697" t="n">
+        <v>1393.8</v>
+      </c>
+      <c r="T697" t="n">
+        <v>1393.8</v>
+      </c>
+      <c r="U697" t="n">
+        <v>42.174</v>
+      </c>
+      <c r="V697" t="n">
+        <v>0.01707530647985989</v>
+      </c>
+      <c r="W697" t="n">
+        <v>0.01707530647985989</v>
+      </c>
+      <c r="X697" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y697" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z697" t="n">
+        <v>0.5990515947341919</v>
+      </c>
+      <c r="AA697" t="n">
         <v>12.27674007415771</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA697"/>
+  <dimension ref="A1:AA705"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65270,7 +65270,7 @@
         <v>100</v>
       </c>
       <c r="N690" s="2" t="n">
-        <v>45835.69198519247</v>
+        <v>45835.69198519676</v>
       </c>
       <c r="O690" t="n">
         <v>1</v>
@@ -65361,7 +65361,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N691" s="2" t="n">
-        <v>45835.69198519247</v>
+        <v>45835.69198519676</v>
       </c>
       <c r="O691" t="n">
         <v>375</v>
@@ -65456,7 +65456,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N692" s="2" t="n">
-        <v>45835.69198519247</v>
+        <v>45835.69198519676</v>
       </c>
       <c r="O692" t="n">
         <v>0.725</v>
@@ -65551,7 +65551,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N693" s="2" t="n">
-        <v>45835.69198519247</v>
+        <v>45835.69198519676</v>
       </c>
       <c r="O693" t="n">
         <v>24.7</v>
@@ -65646,7 +65646,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N694" s="2" t="n">
-        <v>45835.69198519247</v>
+        <v>45835.69198519676</v>
       </c>
       <c r="O694" t="n">
         <v>13.415</v>
@@ -65737,7 +65737,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N695" s="2" t="n">
-        <v>45835.69198519247</v>
+        <v>45835.69198519676</v>
       </c>
       <c r="O695" t="n">
         <v>40</v>
@@ -65832,7 +65832,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N696" s="2" t="n">
-        <v>45835.69198519247</v>
+        <v>45835.69198519676</v>
       </c>
       <c r="O696" t="n">
         <v>23869</v>
@@ -65927,7 +65927,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N697" s="2" t="n">
-        <v>45835.69198519247</v>
+        <v>45835.69198519676</v>
       </c>
       <c r="O697" t="n">
         <v>46.46</v>
@@ -65968,6 +65968,760 @@
         <v>0.5990515947341919</v>
       </c>
       <c r="AA697" t="n">
+        <v>12.27674007415771</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F698" t="n">
+        <v>1</v>
+      </c>
+      <c r="G698" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H698" t="n">
+        <v>1</v>
+      </c>
+      <c r="I698" t="n">
+        <v>1</v>
+      </c>
+      <c r="J698" t="n">
+        <v>1</v>
+      </c>
+      <c r="K698" t="n">
+        <v>100</v>
+      </c>
+      <c r="L698" t="n">
+        <v>100</v>
+      </c>
+      <c r="M698" t="n">
+        <v>100</v>
+      </c>
+      <c r="N698" s="2" t="n">
+        <v>45835.72964596609</v>
+      </c>
+      <c r="O698" t="n">
+        <v>1</v>
+      </c>
+      <c r="P698" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q698" t="n">
+        <v>1</v>
+      </c>
+      <c r="R698" t="n">
+        <v>1</v>
+      </c>
+      <c r="S698" t="n">
+        <v>0</v>
+      </c>
+      <c r="T698" t="n">
+        <v>45.43580260334033</v>
+      </c>
+      <c r="U698" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V698" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W698" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X698" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y698" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z698" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA698" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr"/>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E699" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F699" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H699" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I699" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J699" t="n">
+        <v>3</v>
+      </c>
+      <c r="K699" t="n">
+        <v>10</v>
+      </c>
+      <c r="L699" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M699" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N699" s="2" t="n">
+        <v>45835.72964596609</v>
+      </c>
+      <c r="O699" t="n">
+        <v>375</v>
+      </c>
+      <c r="P699" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q699" t="n">
+        <v>0.8547</v>
+      </c>
+      <c r="R699" t="n">
+        <v>438.7504387504387</v>
+      </c>
+      <c r="S699" t="n">
+        <v>1125</v>
+      </c>
+      <c r="T699" t="n">
+        <v>1316.251316251316</v>
+      </c>
+      <c r="U699" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V699" t="n">
+        <v>0.01994745230725714</v>
+      </c>
+      <c r="W699" t="n">
+        <v>0.01871831240334165</v>
+      </c>
+      <c r="X699" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y699" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z699" t="n">
+        <v>0.5015593767166138</v>
+      </c>
+      <c r="AA699" t="n">
+        <v>12.0281548500061</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E700" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F700" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H700" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I700" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J700" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K700" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L700" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M700" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N700" s="2" t="n">
+        <v>45835.72964596609</v>
+      </c>
+      <c r="O700" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="P700" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q700" t="n">
+        <v>1.79279</v>
+      </c>
+      <c r="R700" t="n">
+        <v>0.4043976148907568</v>
+      </c>
+      <c r="S700" t="n">
+        <v>2656.4</v>
+      </c>
+      <c r="T700" t="n">
+        <v>1481.712860959733</v>
+      </c>
+      <c r="U700" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="V700" t="n">
+        <v>0</v>
+      </c>
+      <c r="W700" t="n">
+        <v>-0.01016293040456506</v>
+      </c>
+      <c r="X700" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y700" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z700" t="n">
+        <v>0.4815215170383453</v>
+      </c>
+      <c r="AA700" t="n">
+        <v>11.57751679420471</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E701" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F701" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H701" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I701" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J701" t="n">
+        <v>537</v>
+      </c>
+      <c r="K701" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L701" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M701" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N701" s="2" t="n">
+        <v>45835.72964596609</v>
+      </c>
+      <c r="O701" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="P701" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q701" t="n">
+        <v>9.19225</v>
+      </c>
+      <c r="R701" t="n">
+        <v>2.687046153009328</v>
+      </c>
+      <c r="S701" t="n">
+        <v>13263.9</v>
+      </c>
+      <c r="T701" t="n">
+        <v>1442.943784166009</v>
+      </c>
+      <c r="U701" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V701" t="n">
+        <v>-0.01984126984126988</v>
+      </c>
+      <c r="W701" t="n">
+        <v>-0.03601792745527965</v>
+      </c>
+      <c r="X701" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y701" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z701" t="n">
+        <v>0.4985511600971222</v>
+      </c>
+      <c r="AA701" t="n">
+        <v>9.835646152496338</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E702" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F702" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G702" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H702" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I702" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J702" t="n">
+        <v>121</v>
+      </c>
+      <c r="K702" t="n">
+        <v>12</v>
+      </c>
+      <c r="L702" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M702" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N702" s="2" t="n">
+        <v>45835.72964596609</v>
+      </c>
+      <c r="O702" t="n">
+        <v>13.36</v>
+      </c>
+      <c r="P702" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q702" t="n">
+        <v>1.1713717</v>
+      </c>
+      <c r="R702" t="n">
+        <v>11.40543176858379</v>
+      </c>
+      <c r="S702" t="n">
+        <v>1616.56</v>
+      </c>
+      <c r="T702" t="n">
+        <v>1380.057243998639</v>
+      </c>
+      <c r="U702" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V702" t="n">
+        <v>-0.05782792665726377</v>
+      </c>
+      <c r="W702" t="n">
+        <v>-0.07473571513852051</v>
+      </c>
+      <c r="X702" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y702" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z702" t="n">
+        <v>0.5161105990409851</v>
+      </c>
+      <c r="AA702" t="n">
+        <v>13.94983839988708</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr"/>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E703" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F703" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G703" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H703" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I703" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J703" t="n">
+        <v>162</v>
+      </c>
+      <c r="K703" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L703" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M703" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N703" s="2" t="n">
+        <v>45835.72964596609</v>
+      </c>
+      <c r="O703" t="n">
+        <v>40</v>
+      </c>
+      <c r="P703" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q703" t="n">
+        <v>4.2404</v>
+      </c>
+      <c r="R703" t="n">
+        <v>9.433072351664936</v>
+      </c>
+      <c r="S703" t="n">
+        <v>6480</v>
+      </c>
+      <c r="T703" t="n">
+        <v>1528.15772096972</v>
+      </c>
+      <c r="U703" t="n">
+        <v>8.492348629783139</v>
+      </c>
+      <c r="V703" t="n">
+        <v>0.02040816326530615</v>
+      </c>
+      <c r="W703" t="n">
+        <v>0.02625811196094308</v>
+      </c>
+      <c r="X703" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y703" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z703" t="n">
+        <v>0.5935001373291016</v>
+      </c>
+      <c r="AA703" t="n">
+        <v>12.80392378997803</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E704" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F704" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G704" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H704" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I704" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J704" t="n">
+        <v>101</v>
+      </c>
+      <c r="K704" t="n">
+        <v>11</v>
+      </c>
+      <c r="L704" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M704" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N704" s="2" t="n">
+        <v>45835.72964596609</v>
+      </c>
+      <c r="O704" t="n">
+        <v>23869</v>
+      </c>
+      <c r="P704" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q704" t="n">
+        <v>2087.05</v>
+      </c>
+      <c r="R704" t="n">
+        <v>11.43671689705565</v>
+      </c>
+      <c r="S704" t="n">
+        <v>2410769</v>
+      </c>
+      <c r="T704" t="n">
+        <v>1155.108406602621</v>
+      </c>
+      <c r="U704" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V704" t="n">
+        <v>-0.02686725375081545</v>
+      </c>
+      <c r="W704" t="n">
+        <v>-0.04121443977994144</v>
+      </c>
+      <c r="X704" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y704" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z704" t="n">
+        <v>0.4108201563358307</v>
+      </c>
+      <c r="AA704" t="n">
+        <v>10.51282495260239</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E705" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F705" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G705" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H705" t="n">
+        <v>1</v>
+      </c>
+      <c r="I705" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J705" t="n">
+        <v>30</v>
+      </c>
+      <c r="K705" t="n">
+        <v>9</v>
+      </c>
+      <c r="L705" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M705" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N705" s="2" t="n">
+        <v>45835.72964596609</v>
+      </c>
+      <c r="O705" t="n">
+        <v>46.46</v>
+      </c>
+      <c r="P705" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q705" t="n">
+        <v>1</v>
+      </c>
+      <c r="R705" t="n">
+        <v>46.46</v>
+      </c>
+      <c r="S705" t="n">
+        <v>1393.8</v>
+      </c>
+      <c r="T705" t="n">
+        <v>1393.8</v>
+      </c>
+      <c r="U705" t="n">
+        <v>42.174</v>
+      </c>
+      <c r="V705" t="n">
+        <v>0.01707530647985989</v>
+      </c>
+      <c r="W705" t="n">
+        <v>0.01707530647985989</v>
+      </c>
+      <c r="X705" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y705" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z705" t="n">
+        <v>0.5990515947341919</v>
+      </c>
+      <c r="AA705" t="n">
         <v>12.27674007415771</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA705"/>
+  <dimension ref="A1:AA713"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66024,7 +66024,7 @@
         <v>100</v>
       </c>
       <c r="N698" s="2" t="n">
-        <v>45835.72964596609</v>
+        <v>45835.72964596065</v>
       </c>
       <c r="O698" t="n">
         <v>1</v>
@@ -66115,7 +66115,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N699" s="2" t="n">
-        <v>45835.72964596609</v>
+        <v>45835.72964596065</v>
       </c>
       <c r="O699" t="n">
         <v>375</v>
@@ -66210,7 +66210,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N700" s="2" t="n">
-        <v>45835.72964596609</v>
+        <v>45835.72964596065</v>
       </c>
       <c r="O700" t="n">
         <v>0.725</v>
@@ -66305,7 +66305,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N701" s="2" t="n">
-        <v>45835.72964596609</v>
+        <v>45835.72964596065</v>
       </c>
       <c r="O701" t="n">
         <v>24.7</v>
@@ -66400,7 +66400,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N702" s="2" t="n">
-        <v>45835.72964596609</v>
+        <v>45835.72964596065</v>
       </c>
       <c r="O702" t="n">
         <v>13.36</v>
@@ -66491,7 +66491,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N703" s="2" t="n">
-        <v>45835.72964596609</v>
+        <v>45835.72964596065</v>
       </c>
       <c r="O703" t="n">
         <v>40</v>
@@ -66586,7 +66586,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N704" s="2" t="n">
-        <v>45835.72964596609</v>
+        <v>45835.72964596065</v>
       </c>
       <c r="O704" t="n">
         <v>23869</v>
@@ -66681,7 +66681,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N705" s="2" t="n">
-        <v>45835.72964596609</v>
+        <v>45835.72964596065</v>
       </c>
       <c r="O705" t="n">
         <v>46.46</v>
@@ -66722,6 +66722,760 @@
         <v>0.5990515947341919</v>
       </c>
       <c r="AA705" t="n">
+        <v>12.27674007415771</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F706" t="n">
+        <v>1</v>
+      </c>
+      <c r="G706" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H706" t="n">
+        <v>1</v>
+      </c>
+      <c r="I706" t="n">
+        <v>1</v>
+      </c>
+      <c r="J706" t="n">
+        <v>1</v>
+      </c>
+      <c r="K706" t="n">
+        <v>100</v>
+      </c>
+      <c r="L706" t="n">
+        <v>100</v>
+      </c>
+      <c r="M706" t="n">
+        <v>100</v>
+      </c>
+      <c r="N706" s="2" t="n">
+        <v>45835.77815953759</v>
+      </c>
+      <c r="O706" t="n">
+        <v>1</v>
+      </c>
+      <c r="P706" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q706" t="n">
+        <v>1</v>
+      </c>
+      <c r="R706" t="n">
+        <v>1</v>
+      </c>
+      <c r="S706" t="n">
+        <v>0</v>
+      </c>
+      <c r="T706" t="n">
+        <v>45.43580260334033</v>
+      </c>
+      <c r="U706" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V706" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W706" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X706" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y706" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z706" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA706" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr"/>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E707" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F707" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G707" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H707" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I707" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J707" t="n">
+        <v>3</v>
+      </c>
+      <c r="K707" t="n">
+        <v>10</v>
+      </c>
+      <c r="L707" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M707" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N707" s="2" t="n">
+        <v>45835.77815953759</v>
+      </c>
+      <c r="O707" t="n">
+        <v>375</v>
+      </c>
+      <c r="P707" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q707" t="n">
+        <v>0.8541</v>
+      </c>
+      <c r="R707" t="n">
+        <v>439.0586582367404</v>
+      </c>
+      <c r="S707" t="n">
+        <v>1125</v>
+      </c>
+      <c r="T707" t="n">
+        <v>1317.175974710221</v>
+      </c>
+      <c r="U707" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V707" t="n">
+        <v>0.01994745230725714</v>
+      </c>
+      <c r="W707" t="n">
+        <v>0.01943395575592577</v>
+      </c>
+      <c r="X707" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y707" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z707" t="n">
+        <v>0.5015593767166138</v>
+      </c>
+      <c r="AA707" t="n">
+        <v>12.0281548500061</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E708" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F708" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G708" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H708" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I708" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J708" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K708" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L708" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M708" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N708" s="2" t="n">
+        <v>45835.77815953759</v>
+      </c>
+      <c r="O708" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="P708" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q708" t="n">
+        <v>1.79557</v>
+      </c>
+      <c r="R708" t="n">
+        <v>0.4037715043133935</v>
+      </c>
+      <c r="S708" t="n">
+        <v>2656.4</v>
+      </c>
+      <c r="T708" t="n">
+        <v>1479.418791804274</v>
+      </c>
+      <c r="U708" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="V708" t="n">
+        <v>0</v>
+      </c>
+      <c r="W708" t="n">
+        <v>-0.01169545046976739</v>
+      </c>
+      <c r="X708" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y708" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z708" t="n">
+        <v>0.4815215170383453</v>
+      </c>
+      <c r="AA708" t="n">
+        <v>11.57751679420471</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E709" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F709" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G709" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H709" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I709" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J709" t="n">
+        <v>537</v>
+      </c>
+      <c r="K709" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L709" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M709" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N709" s="2" t="n">
+        <v>45835.77815953759</v>
+      </c>
+      <c r="O709" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="P709" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q709" t="n">
+        <v>9.17534</v>
+      </c>
+      <c r="R709" t="n">
+        <v>2.691998334666617</v>
+      </c>
+      <c r="S709" t="n">
+        <v>13263.9</v>
+      </c>
+      <c r="T709" t="n">
+        <v>1445.603105715973</v>
+      </c>
+      <c r="U709" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V709" t="n">
+        <v>-0.01984126984126988</v>
+      </c>
+      <c r="W709" t="n">
+        <v>-0.03424132442512151</v>
+      </c>
+      <c r="X709" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y709" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z709" t="n">
+        <v>0.4985511600971222</v>
+      </c>
+      <c r="AA709" t="n">
+        <v>9.835646152496338</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E710" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F710" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G710" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H710" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I710" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J710" t="n">
+        <v>121</v>
+      </c>
+      <c r="K710" t="n">
+        <v>12</v>
+      </c>
+      <c r="L710" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M710" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N710" s="2" t="n">
+        <v>45835.77815953759</v>
+      </c>
+      <c r="O710" t="n">
+        <v>13.35</v>
+      </c>
+      <c r="P710" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q710" t="n">
+        <v>1.1691804</v>
+      </c>
+      <c r="R710" t="n">
+        <v>11.41825504430283</v>
+      </c>
+      <c r="S710" t="n">
+        <v>1615.35</v>
+      </c>
+      <c r="T710" t="n">
+        <v>1381.608860360642</v>
+      </c>
+      <c r="U710" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V710" t="n">
+        <v>-0.05853314527503528</v>
+      </c>
+      <c r="W710" t="n">
+        <v>-0.07369542843315968</v>
+      </c>
+      <c r="X710" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y710" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z710" t="n">
+        <v>0.5161105990409851</v>
+      </c>
+      <c r="AA710" t="n">
+        <v>13.94983839988708</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr"/>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E711" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F711" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G711" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H711" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I711" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J711" t="n">
+        <v>162</v>
+      </c>
+      <c r="K711" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L711" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M711" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N711" s="2" t="n">
+        <v>45835.77815953759</v>
+      </c>
+      <c r="O711" t="n">
+        <v>40</v>
+      </c>
+      <c r="P711" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q711" t="n">
+        <v>4.23984</v>
+      </c>
+      <c r="R711" t="n">
+        <v>9.434318276161365</v>
+      </c>
+      <c r="S711" t="n">
+        <v>6480</v>
+      </c>
+      <c r="T711" t="n">
+        <v>1528.359560738141</v>
+      </c>
+      <c r="U711" t="n">
+        <v>8.492348629783139</v>
+      </c>
+      <c r="V711" t="n">
+        <v>0.02040816326530615</v>
+      </c>
+      <c r="W711" t="n">
+        <v>0.02639366060020754</v>
+      </c>
+      <c r="X711" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y711" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z711" t="n">
+        <v>0.5935001373291016</v>
+      </c>
+      <c r="AA711" t="n">
+        <v>12.80392378997803</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E712" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F712" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G712" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H712" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I712" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J712" t="n">
+        <v>101</v>
+      </c>
+      <c r="K712" t="n">
+        <v>11</v>
+      </c>
+      <c r="L712" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M712" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N712" s="2" t="n">
+        <v>45835.77815953759</v>
+      </c>
+      <c r="O712" t="n">
+        <v>23869</v>
+      </c>
+      <c r="P712" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q712" t="n">
+        <v>2087.79</v>
+      </c>
+      <c r="R712" t="n">
+        <v>11.43266324678248</v>
+      </c>
+      <c r="S712" t="n">
+        <v>2410769</v>
+      </c>
+      <c r="T712" t="n">
+        <v>1154.698987925031</v>
+      </c>
+      <c r="U712" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V712" t="n">
+        <v>-0.02686725375081545</v>
+      </c>
+      <c r="W712" t="n">
+        <v>-0.04155427343876861</v>
+      </c>
+      <c r="X712" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y712" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z712" t="n">
+        <v>0.4108201563358307</v>
+      </c>
+      <c r="AA712" t="n">
+        <v>10.51282495260239</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E713" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F713" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G713" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H713" t="n">
+        <v>1</v>
+      </c>
+      <c r="I713" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J713" t="n">
+        <v>30</v>
+      </c>
+      <c r="K713" t="n">
+        <v>9</v>
+      </c>
+      <c r="L713" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M713" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N713" s="2" t="n">
+        <v>45835.77815953759</v>
+      </c>
+      <c r="O713" t="n">
+        <v>46.46</v>
+      </c>
+      <c r="P713" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q713" t="n">
+        <v>1</v>
+      </c>
+      <c r="R713" t="n">
+        <v>46.46</v>
+      </c>
+      <c r="S713" t="n">
+        <v>1393.8</v>
+      </c>
+      <c r="T713" t="n">
+        <v>1393.8</v>
+      </c>
+      <c r="U713" t="n">
+        <v>42.174</v>
+      </c>
+      <c r="V713" t="n">
+        <v>0.01707530647985989</v>
+      </c>
+      <c r="W713" t="n">
+        <v>0.01707530647985989</v>
+      </c>
+      <c r="X713" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y713" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z713" t="n">
+        <v>0.5990515947341919</v>
+      </c>
+      <c r="AA713" t="n">
         <v>12.27674007415771</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA713"/>
+  <dimension ref="A1:AA721"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66778,7 +66778,7 @@
         <v>100</v>
       </c>
       <c r="N706" s="2" t="n">
-        <v>45835.77815953759</v>
+        <v>45835.77815953704</v>
       </c>
       <c r="O706" t="n">
         <v>1</v>
@@ -66869,7 +66869,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N707" s="2" t="n">
-        <v>45835.77815953759</v>
+        <v>45835.77815953704</v>
       </c>
       <c r="O707" t="n">
         <v>375</v>
@@ -66964,7 +66964,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N708" s="2" t="n">
-        <v>45835.77815953759</v>
+        <v>45835.77815953704</v>
       </c>
       <c r="O708" t="n">
         <v>0.725</v>
@@ -67059,7 +67059,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N709" s="2" t="n">
-        <v>45835.77815953759</v>
+        <v>45835.77815953704</v>
       </c>
       <c r="O709" t="n">
         <v>24.7</v>
@@ -67154,7 +67154,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N710" s="2" t="n">
-        <v>45835.77815953759</v>
+        <v>45835.77815953704</v>
       </c>
       <c r="O710" t="n">
         <v>13.35</v>
@@ -67245,7 +67245,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N711" s="2" t="n">
-        <v>45835.77815953759</v>
+        <v>45835.77815953704</v>
       </c>
       <c r="O711" t="n">
         <v>40</v>
@@ -67340,7 +67340,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N712" s="2" t="n">
-        <v>45835.77815953759</v>
+        <v>45835.77815953704</v>
       </c>
       <c r="O712" t="n">
         <v>23869</v>
@@ -67435,7 +67435,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N713" s="2" t="n">
-        <v>45835.77815953759</v>
+        <v>45835.77815953704</v>
       </c>
       <c r="O713" t="n">
         <v>46.46</v>
@@ -67476,6 +67476,760 @@
         <v>0.5990515947341919</v>
       </c>
       <c r="AA713" t="n">
+        <v>12.27674007415771</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F714" t="n">
+        <v>1</v>
+      </c>
+      <c r="G714" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H714" t="n">
+        <v>1</v>
+      </c>
+      <c r="I714" t="n">
+        <v>1</v>
+      </c>
+      <c r="J714" t="n">
+        <v>1</v>
+      </c>
+      <c r="K714" t="n">
+        <v>100</v>
+      </c>
+      <c r="L714" t="n">
+        <v>100</v>
+      </c>
+      <c r="M714" t="n">
+        <v>100</v>
+      </c>
+      <c r="N714" s="2" t="n">
+        <v>45835.80769185778</v>
+      </c>
+      <c r="O714" t="n">
+        <v>1</v>
+      </c>
+      <c r="P714" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q714" t="n">
+        <v>1</v>
+      </c>
+      <c r="R714" t="n">
+        <v>1</v>
+      </c>
+      <c r="S714" t="n">
+        <v>0</v>
+      </c>
+      <c r="T714" t="n">
+        <v>45.43580260334033</v>
+      </c>
+      <c r="U714" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V714" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W714" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X714" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y714" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z714" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA714" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr"/>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E715" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F715" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G715" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H715" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I715" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J715" t="n">
+        <v>3</v>
+      </c>
+      <c r="K715" t="n">
+        <v>10</v>
+      </c>
+      <c r="L715" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M715" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N715" s="2" t="n">
+        <v>45835.80769185778</v>
+      </c>
+      <c r="O715" t="n">
+        <v>375</v>
+      </c>
+      <c r="P715" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q715" t="n">
+        <v>0.85425</v>
+      </c>
+      <c r="R715" t="n">
+        <v>438.9815627743635</v>
+      </c>
+      <c r="S715" t="n">
+        <v>1125</v>
+      </c>
+      <c r="T715" t="n">
+        <v>1316.944688323091</v>
+      </c>
+      <c r="U715" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V715" t="n">
+        <v>0.01994745230725714</v>
+      </c>
+      <c r="W715" t="n">
+        <v>0.01925495067150873</v>
+      </c>
+      <c r="X715" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y715" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z715" t="n">
+        <v>0.5015593767166138</v>
+      </c>
+      <c r="AA715" t="n">
+        <v>12.0281548500061</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E716" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F716" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G716" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H716" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I716" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J716" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K716" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L716" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M716" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N716" s="2" t="n">
+        <v>45835.80769185778</v>
+      </c>
+      <c r="O716" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="P716" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q716" t="n">
+        <v>1.79492</v>
+      </c>
+      <c r="R716" t="n">
+        <v>0.4039177233525728</v>
+      </c>
+      <c r="S716" t="n">
+        <v>2656.4</v>
+      </c>
+      <c r="T716" t="n">
+        <v>1479.954538363827</v>
+      </c>
+      <c r="U716" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="V716" t="n">
+        <v>0</v>
+      </c>
+      <c r="W716" t="n">
+        <v>-0.01133755264858605</v>
+      </c>
+      <c r="X716" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y716" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z716" t="n">
+        <v>0.4815215170383453</v>
+      </c>
+      <c r="AA716" t="n">
+        <v>11.57751679420471</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E717" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F717" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G717" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H717" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I717" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J717" t="n">
+        <v>537</v>
+      </c>
+      <c r="K717" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L717" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M717" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N717" s="2" t="n">
+        <v>45835.80769185778</v>
+      </c>
+      <c r="O717" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="P717" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q717" t="n">
+        <v>9.1873</v>
+      </c>
+      <c r="R717" t="n">
+        <v>2.688493899186921</v>
+      </c>
+      <c r="S717" t="n">
+        <v>13263.9</v>
+      </c>
+      <c r="T717" t="n">
+        <v>1443.721223863377</v>
+      </c>
+      <c r="U717" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V717" t="n">
+        <v>-0.01984126984126988</v>
+      </c>
+      <c r="W717" t="n">
+        <v>-0.03549854621605864</v>
+      </c>
+      <c r="X717" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y717" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z717" t="n">
+        <v>0.4985511600971222</v>
+      </c>
+      <c r="AA717" t="n">
+        <v>9.835646152496338</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E718" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F718" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G718" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H718" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I718" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J718" t="n">
+        <v>121</v>
+      </c>
+      <c r="K718" t="n">
+        <v>12</v>
+      </c>
+      <c r="L718" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M718" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N718" s="2" t="n">
+        <v>45835.80769185778</v>
+      </c>
+      <c r="O718" t="n">
+        <v>13.38</v>
+      </c>
+      <c r="P718" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q718" t="n">
+        <v>1.1705489</v>
+      </c>
+      <c r="R718" t="n">
+        <v>11.43053485420387</v>
+      </c>
+      <c r="S718" t="n">
+        <v>1618.98</v>
+      </c>
+      <c r="T718" t="n">
+        <v>1383.094717358668</v>
+      </c>
+      <c r="U718" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V718" t="n">
+        <v>-0.05641748942172065</v>
+      </c>
+      <c r="W718" t="n">
+        <v>-0.07269923032712933</v>
+      </c>
+      <c r="X718" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y718" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z718" t="n">
+        <v>0.5161105990409851</v>
+      </c>
+      <c r="AA718" t="n">
+        <v>13.94983839988708</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr"/>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E719" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F719" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G719" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H719" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I719" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J719" t="n">
+        <v>162</v>
+      </c>
+      <c r="K719" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L719" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M719" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N719" s="2" t="n">
+        <v>45835.80769185778</v>
+      </c>
+      <c r="O719" t="n">
+        <v>40</v>
+      </c>
+      <c r="P719" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q719" t="n">
+        <v>4.23934</v>
+      </c>
+      <c r="R719" t="n">
+        <v>9.435430986898904</v>
+      </c>
+      <c r="S719" t="n">
+        <v>6480</v>
+      </c>
+      <c r="T719" t="n">
+        <v>1528.539819877622</v>
+      </c>
+      <c r="U719" t="n">
+        <v>8.492348629783139</v>
+      </c>
+      <c r="V719" t="n">
+        <v>0.02040816326530615</v>
+      </c>
+      <c r="W719" t="n">
+        <v>0.02651471643208225</v>
+      </c>
+      <c r="X719" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y719" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z719" t="n">
+        <v>0.5935001373291016</v>
+      </c>
+      <c r="AA719" t="n">
+        <v>12.80392378997803</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E720" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F720" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G720" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H720" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I720" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J720" t="n">
+        <v>101</v>
+      </c>
+      <c r="K720" t="n">
+        <v>11</v>
+      </c>
+      <c r="L720" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M720" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N720" s="2" t="n">
+        <v>45835.80769185778</v>
+      </c>
+      <c r="O720" t="n">
+        <v>23869</v>
+      </c>
+      <c r="P720" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q720" t="n">
+        <v>2091.51</v>
+      </c>
+      <c r="R720" t="n">
+        <v>11.41232889156638</v>
+      </c>
+      <c r="S720" t="n">
+        <v>2410769</v>
+      </c>
+      <c r="T720" t="n">
+        <v>1152.645218048204</v>
+      </c>
+      <c r="U720" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V720" t="n">
+        <v>-0.02686725375081545</v>
+      </c>
+      <c r="W720" t="n">
+        <v>-0.04325898348213819</v>
+      </c>
+      <c r="X720" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y720" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z720" t="n">
+        <v>0.4108201563358307</v>
+      </c>
+      <c r="AA720" t="n">
+        <v>10.51282495260239</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E721" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F721" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G721" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H721" t="n">
+        <v>1</v>
+      </c>
+      <c r="I721" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J721" t="n">
+        <v>30</v>
+      </c>
+      <c r="K721" t="n">
+        <v>9</v>
+      </c>
+      <c r="L721" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M721" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N721" s="2" t="n">
+        <v>45835.80769185778</v>
+      </c>
+      <c r="O721" t="n">
+        <v>46.46</v>
+      </c>
+      <c r="P721" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q721" t="n">
+        <v>1</v>
+      </c>
+      <c r="R721" t="n">
+        <v>46.46</v>
+      </c>
+      <c r="S721" t="n">
+        <v>1393.8</v>
+      </c>
+      <c r="T721" t="n">
+        <v>1393.8</v>
+      </c>
+      <c r="U721" t="n">
+        <v>42.174</v>
+      </c>
+      <c r="V721" t="n">
+        <v>0.01707530647985989</v>
+      </c>
+      <c r="W721" t="n">
+        <v>0.01707530647985989</v>
+      </c>
+      <c r="X721" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y721" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z721" t="n">
+        <v>0.5990515947341919</v>
+      </c>
+      <c r="AA721" t="n">
         <v>12.27674007415771</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA721"/>
+  <dimension ref="A1:AA729"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67532,7 +67532,7 @@
         <v>100</v>
       </c>
       <c r="N714" s="2" t="n">
-        <v>45835.80769185778</v>
+        <v>45835.80769186343</v>
       </c>
       <c r="O714" t="n">
         <v>1</v>
@@ -67623,7 +67623,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N715" s="2" t="n">
-        <v>45835.80769185778</v>
+        <v>45835.80769186343</v>
       </c>
       <c r="O715" t="n">
         <v>375</v>
@@ -67718,7 +67718,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N716" s="2" t="n">
-        <v>45835.80769185778</v>
+        <v>45835.80769186343</v>
       </c>
       <c r="O716" t="n">
         <v>0.725</v>
@@ -67813,7 +67813,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N717" s="2" t="n">
-        <v>45835.80769185778</v>
+        <v>45835.80769186343</v>
       </c>
       <c r="O717" t="n">
         <v>24.7</v>
@@ -67908,7 +67908,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N718" s="2" t="n">
-        <v>45835.80769185778</v>
+        <v>45835.80769186343</v>
       </c>
       <c r="O718" t="n">
         <v>13.38</v>
@@ -67999,7 +67999,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N719" s="2" t="n">
-        <v>45835.80769185778</v>
+        <v>45835.80769186343</v>
       </c>
       <c r="O719" t="n">
         <v>40</v>
@@ -68094,7 +68094,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N720" s="2" t="n">
-        <v>45835.80769185778</v>
+        <v>45835.80769186343</v>
       </c>
       <c r="O720" t="n">
         <v>23869</v>
@@ -68189,7 +68189,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N721" s="2" t="n">
-        <v>45835.80769185778</v>
+        <v>45835.80769186343</v>
       </c>
       <c r="O721" t="n">
         <v>46.46</v>
@@ -68230,6 +68230,760 @@
         <v>0.5990515947341919</v>
       </c>
       <c r="AA721" t="n">
+        <v>12.27674007415771</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F722" t="n">
+        <v>1</v>
+      </c>
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H722" t="n">
+        <v>1</v>
+      </c>
+      <c r="I722" t="n">
+        <v>1</v>
+      </c>
+      <c r="J722" t="n">
+        <v>1</v>
+      </c>
+      <c r="K722" t="n">
+        <v>100</v>
+      </c>
+      <c r="L722" t="n">
+        <v>100</v>
+      </c>
+      <c r="M722" t="n">
+        <v>100</v>
+      </c>
+      <c r="N722" s="2" t="n">
+        <v>45835.85558274058</v>
+      </c>
+      <c r="O722" t="n">
+        <v>1</v>
+      </c>
+      <c r="P722" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q722" t="n">
+        <v>1</v>
+      </c>
+      <c r="R722" t="n">
+        <v>1</v>
+      </c>
+      <c r="S722" t="n">
+        <v>0</v>
+      </c>
+      <c r="T722" t="n">
+        <v>45.43580260334033</v>
+      </c>
+      <c r="U722" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V722" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W722" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X722" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y722" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z722" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA722" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr"/>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E723" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F723" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G723" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H723" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I723" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J723" t="n">
+        <v>3</v>
+      </c>
+      <c r="K723" t="n">
+        <v>10</v>
+      </c>
+      <c r="L723" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M723" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N723" s="2" t="n">
+        <v>45835.85558274058</v>
+      </c>
+      <c r="O723" t="n">
+        <v>375</v>
+      </c>
+      <c r="P723" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q723" t="n">
+        <v>0.85409</v>
+      </c>
+      <c r="R723" t="n">
+        <v>439.0637988970717</v>
+      </c>
+      <c r="S723" t="n">
+        <v>1125</v>
+      </c>
+      <c r="T723" t="n">
+        <v>1317.191396691215</v>
+      </c>
+      <c r="U723" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V723" t="n">
+        <v>0.01994745230725714</v>
+      </c>
+      <c r="W723" t="n">
+        <v>0.0194458916638014</v>
+      </c>
+      <c r="X723" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y723" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z723" t="n">
+        <v>0.5015593767166138</v>
+      </c>
+      <c r="AA723" t="n">
+        <v>12.0281548500061</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E724" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F724" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H724" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I724" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J724" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K724" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L724" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M724" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N724" s="2" t="n">
+        <v>45835.85558274058</v>
+      </c>
+      <c r="O724" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="P724" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q724" t="n">
+        <v>1.79402</v>
+      </c>
+      <c r="R724" t="n">
+        <v>0.4041203554029498</v>
+      </c>
+      <c r="S724" t="n">
+        <v>2656.4</v>
+      </c>
+      <c r="T724" t="n">
+        <v>1480.696982196408</v>
+      </c>
+      <c r="U724" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="V724" t="n">
+        <v>0</v>
+      </c>
+      <c r="W724" t="n">
+        <v>-0.01084157367253424</v>
+      </c>
+      <c r="X724" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y724" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z724" t="n">
+        <v>0.4815215170383453</v>
+      </c>
+      <c r="AA724" t="n">
+        <v>11.57751679420471</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E725" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F725" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H725" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I725" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J725" t="n">
+        <v>537</v>
+      </c>
+      <c r="K725" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L725" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M725" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N725" s="2" t="n">
+        <v>45835.85558274058</v>
+      </c>
+      <c r="O725" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="P725" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q725" t="n">
+        <v>9.195309999999999</v>
+      </c>
+      <c r="R725" t="n">
+        <v>2.686151962250321</v>
+      </c>
+      <c r="S725" t="n">
+        <v>13263.9</v>
+      </c>
+      <c r="T725" t="n">
+        <v>1442.463603728422</v>
+      </c>
+      <c r="U725" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V725" t="n">
+        <v>-0.01984126984126988</v>
+      </c>
+      <c r="W725" t="n">
+        <v>-0.03633871980942383</v>
+      </c>
+      <c r="X725" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y725" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z725" t="n">
+        <v>0.4985511600971222</v>
+      </c>
+      <c r="AA725" t="n">
+        <v>9.835646152496338</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E726" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F726" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G726" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H726" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I726" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J726" t="n">
+        <v>121</v>
+      </c>
+      <c r="K726" t="n">
+        <v>12</v>
+      </c>
+      <c r="L726" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M726" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N726" s="2" t="n">
+        <v>45835.85558274058</v>
+      </c>
+      <c r="O726" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="P726" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q726" t="n">
+        <v>1.1719208</v>
+      </c>
+      <c r="R726" t="n">
+        <v>11.43421978686614</v>
+      </c>
+      <c r="S726" t="n">
+        <v>1621.4</v>
+      </c>
+      <c r="T726" t="n">
+        <v>1383.540594210803</v>
+      </c>
+      <c r="U726" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V726" t="n">
+        <v>-0.05500705218617763</v>
+      </c>
+      <c r="W726" t="n">
+        <v>-0.07240029060667863</v>
+      </c>
+      <c r="X726" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y726" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z726" t="n">
+        <v>0.5161105990409851</v>
+      </c>
+      <c r="AA726" t="n">
+        <v>13.94983839988708</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr"/>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E727" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F727" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H727" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I727" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J727" t="n">
+        <v>162</v>
+      </c>
+      <c r="K727" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L727" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M727" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N727" s="2" t="n">
+        <v>45835.85558274058</v>
+      </c>
+      <c r="O727" t="n">
+        <v>40</v>
+      </c>
+      <c r="P727" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q727" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="R727" t="n">
+        <v>9.433962264150942</v>
+      </c>
+      <c r="S727" t="n">
+        <v>6480</v>
+      </c>
+      <c r="T727" t="n">
+        <v>1528.301886792453</v>
+      </c>
+      <c r="U727" t="n">
+        <v>8.492348629783139</v>
+      </c>
+      <c r="V727" t="n">
+        <v>0.02040816326530615</v>
+      </c>
+      <c r="W727" t="n">
+        <v>0.02635492876395817</v>
+      </c>
+      <c r="X727" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y727" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z727" t="n">
+        <v>0.5935001373291016</v>
+      </c>
+      <c r="AA727" t="n">
+        <v>12.80392378997803</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E728" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F728" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G728" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H728" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I728" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J728" t="n">
+        <v>101</v>
+      </c>
+      <c r="K728" t="n">
+        <v>11</v>
+      </c>
+      <c r="L728" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M728" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N728" s="2" t="n">
+        <v>45835.85558274058</v>
+      </c>
+      <c r="O728" t="n">
+        <v>23869</v>
+      </c>
+      <c r="P728" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q728" t="n">
+        <v>2089.88</v>
+      </c>
+      <c r="R728" t="n">
+        <v>11.42122992707715</v>
+      </c>
+      <c r="S728" t="n">
+        <v>2410769</v>
+      </c>
+      <c r="T728" t="n">
+        <v>1153.544222634792</v>
+      </c>
+      <c r="U728" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V728" t="n">
+        <v>-0.02686725375081545</v>
+      </c>
+      <c r="W728" t="n">
+        <v>-0.04251277419886634</v>
+      </c>
+      <c r="X728" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y728" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z728" t="n">
+        <v>0.4108201563358307</v>
+      </c>
+      <c r="AA728" t="n">
+        <v>10.51282495260239</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E729" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F729" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G729" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H729" t="n">
+        <v>1</v>
+      </c>
+      <c r="I729" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J729" t="n">
+        <v>30</v>
+      </c>
+      <c r="K729" t="n">
+        <v>9</v>
+      </c>
+      <c r="L729" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M729" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N729" s="2" t="n">
+        <v>45835.85558274058</v>
+      </c>
+      <c r="O729" t="n">
+        <v>46.46</v>
+      </c>
+      <c r="P729" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q729" t="n">
+        <v>1</v>
+      </c>
+      <c r="R729" t="n">
+        <v>46.46</v>
+      </c>
+      <c r="S729" t="n">
+        <v>1393.8</v>
+      </c>
+      <c r="T729" t="n">
+        <v>1393.8</v>
+      </c>
+      <c r="U729" t="n">
+        <v>42.174</v>
+      </c>
+      <c r="V729" t="n">
+        <v>0.01707530647985989</v>
+      </c>
+      <c r="W729" t="n">
+        <v>0.01707530647985989</v>
+      </c>
+      <c r="X729" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y729" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z729" t="n">
+        <v>0.5990515947341919</v>
+      </c>
+      <c r="AA729" t="n">
         <v>12.27674007415771</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA729"/>
+  <dimension ref="A1:AA737"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68286,7 +68286,7 @@
         <v>100</v>
       </c>
       <c r="N722" s="2" t="n">
-        <v>45835.85558274058</v>
+        <v>45835.85558274305</v>
       </c>
       <c r="O722" t="n">
         <v>1</v>
@@ -68377,7 +68377,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N723" s="2" t="n">
-        <v>45835.85558274058</v>
+        <v>45835.85558274305</v>
       </c>
       <c r="O723" t="n">
         <v>375</v>
@@ -68472,7 +68472,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N724" s="2" t="n">
-        <v>45835.85558274058</v>
+        <v>45835.85558274305</v>
       </c>
       <c r="O724" t="n">
         <v>0.725</v>
@@ -68567,7 +68567,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N725" s="2" t="n">
-        <v>45835.85558274058</v>
+        <v>45835.85558274305</v>
       </c>
       <c r="O725" t="n">
         <v>24.7</v>
@@ -68662,7 +68662,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N726" s="2" t="n">
-        <v>45835.85558274058</v>
+        <v>45835.85558274305</v>
       </c>
       <c r="O726" t="n">
         <v>13.4</v>
@@ -68753,7 +68753,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N727" s="2" t="n">
-        <v>45835.85558274058</v>
+        <v>45835.85558274305</v>
       </c>
       <c r="O727" t="n">
         <v>40</v>
@@ -68848,7 +68848,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N728" s="2" t="n">
-        <v>45835.85558274058</v>
+        <v>45835.85558274305</v>
       </c>
       <c r="O728" t="n">
         <v>23869</v>
@@ -68943,7 +68943,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N729" s="2" t="n">
-        <v>45835.85558274058</v>
+        <v>45835.85558274305</v>
       </c>
       <c r="O729" t="n">
         <v>46.46</v>
@@ -68984,6 +68984,760 @@
         <v>0.5990515947341919</v>
       </c>
       <c r="AA729" t="n">
+        <v>12.27674007415771</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F730" t="n">
+        <v>1</v>
+      </c>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H730" t="n">
+        <v>1</v>
+      </c>
+      <c r="I730" t="n">
+        <v>1</v>
+      </c>
+      <c r="J730" t="n">
+        <v>1</v>
+      </c>
+      <c r="K730" t="n">
+        <v>100</v>
+      </c>
+      <c r="L730" t="n">
+        <v>100</v>
+      </c>
+      <c r="M730" t="n">
+        <v>100</v>
+      </c>
+      <c r="N730" s="2" t="n">
+        <v>45835.89427517669</v>
+      </c>
+      <c r="O730" t="n">
+        <v>1</v>
+      </c>
+      <c r="P730" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q730" t="n">
+        <v>1</v>
+      </c>
+      <c r="R730" t="n">
+        <v>1</v>
+      </c>
+      <c r="S730" t="n">
+        <v>0</v>
+      </c>
+      <c r="T730" t="n">
+        <v>45.43580260334033</v>
+      </c>
+      <c r="U730" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V730" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W730" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X730" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y730" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z730" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA730" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr"/>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E731" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F731" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H731" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I731" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J731" t="n">
+        <v>3</v>
+      </c>
+      <c r="K731" t="n">
+        <v>10</v>
+      </c>
+      <c r="L731" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M731" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N731" s="2" t="n">
+        <v>45835.89427517669</v>
+      </c>
+      <c r="O731" t="n">
+        <v>375</v>
+      </c>
+      <c r="P731" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q731" t="n">
+        <v>0.85424</v>
+      </c>
+      <c r="R731" t="n">
+        <v>438.9867016295186</v>
+      </c>
+      <c r="S731" t="n">
+        <v>1125</v>
+      </c>
+      <c r="T731" t="n">
+        <v>1316.960104888556</v>
+      </c>
+      <c r="U731" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V731" t="n">
+        <v>0.01994745230725714</v>
+      </c>
+      <c r="W731" t="n">
+        <v>0.01926688238801288</v>
+      </c>
+      <c r="X731" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y731" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z731" t="n">
+        <v>0.5015593767166138</v>
+      </c>
+      <c r="AA731" t="n">
+        <v>12.0281548500061</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="E732" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F732" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G732" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="H732" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="I732" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="J732" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K732" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L732" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="M732" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="N732" s="2" t="n">
+        <v>45835.89427517669</v>
+      </c>
+      <c r="O732" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="P732" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="Q732" t="n">
+        <v>1.794</v>
+      </c>
+      <c r="R732" t="n">
+        <v>0.4041248606465997</v>
+      </c>
+      <c r="S732" t="n">
+        <v>2656.4</v>
+      </c>
+      <c r="T732" t="n">
+        <v>1480.713489409142</v>
+      </c>
+      <c r="U732" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="V732" t="n">
+        <v>0</v>
+      </c>
+      <c r="W732" t="n">
+        <v>-0.01083054626532898</v>
+      </c>
+      <c r="X732" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y732" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z732" t="n">
+        <v>0.4815215170383453</v>
+      </c>
+      <c r="AA732" t="n">
+        <v>11.57751679420471</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="E733" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="F733" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H733" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="I733" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="J733" t="n">
+        <v>537</v>
+      </c>
+      <c r="K733" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L733" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="M733" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="N733" s="2" t="n">
+        <v>45835.89427517669</v>
+      </c>
+      <c r="O733" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="P733" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="Q733" t="n">
+        <v>9.1989</v>
+      </c>
+      <c r="R733" t="n">
+        <v>2.685103653697725</v>
+      </c>
+      <c r="S733" t="n">
+        <v>13263.9</v>
+      </c>
+      <c r="T733" t="n">
+        <v>1441.900662035678</v>
+      </c>
+      <c r="U733" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="V733" t="n">
+        <v>-0.01984126984126988</v>
+      </c>
+      <c r="W733" t="n">
+        <v>-0.03671480216664968</v>
+      </c>
+      <c r="X733" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y733" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z733" t="n">
+        <v>0.4985511600971222</v>
+      </c>
+      <c r="AA733" t="n">
+        <v>9.835646152496338</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E734" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F734" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H734" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I734" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J734" t="n">
+        <v>121</v>
+      </c>
+      <c r="K734" t="n">
+        <v>12</v>
+      </c>
+      <c r="L734" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M734" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N734" s="2" t="n">
+        <v>45835.89427517669</v>
+      </c>
+      <c r="O734" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="P734" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q734" t="n">
+        <v>1.1719208</v>
+      </c>
+      <c r="R734" t="n">
+        <v>11.43421978686614</v>
+      </c>
+      <c r="S734" t="n">
+        <v>1621.4</v>
+      </c>
+      <c r="T734" t="n">
+        <v>1383.540594210803</v>
+      </c>
+      <c r="U734" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V734" t="n">
+        <v>-0.05500705218617763</v>
+      </c>
+      <c r="W734" t="n">
+        <v>-0.07240029060667863</v>
+      </c>
+      <c r="X734" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y734" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z734" t="n">
+        <v>0.5161105990409851</v>
+      </c>
+      <c r="AA734" t="n">
+        <v>13.94983839988708</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr"/>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E735" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F735" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G735" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H735" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I735" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J735" t="n">
+        <v>162</v>
+      </c>
+      <c r="K735" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L735" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M735" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N735" s="2" t="n">
+        <v>45835.89427517669</v>
+      </c>
+      <c r="O735" t="n">
+        <v>40</v>
+      </c>
+      <c r="P735" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q735" t="n">
+        <v>4.2377</v>
+      </c>
+      <c r="R735" t="n">
+        <v>9.439082521178941</v>
+      </c>
+      <c r="S735" t="n">
+        <v>6480</v>
+      </c>
+      <c r="T735" t="n">
+        <v>1529.131368430988</v>
+      </c>
+      <c r="U735" t="n">
+        <v>8.495174269061048</v>
+      </c>
+      <c r="V735" t="n">
+        <v>0.02040816326530615</v>
+      </c>
+      <c r="W735" t="n">
+        <v>0.02691198007390394</v>
+      </c>
+      <c r="X735" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y735" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="Z735" t="n">
+        <v>0.5935001373291016</v>
+      </c>
+      <c r="AA735" t="n">
+        <v>12.80392378997803</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E736" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F736" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G736" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H736" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I736" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J736" t="n">
+        <v>101</v>
+      </c>
+      <c r="K736" t="n">
+        <v>11</v>
+      </c>
+      <c r="L736" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M736" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N736" s="2" t="n">
+        <v>45835.89427517669</v>
+      </c>
+      <c r="O736" t="n">
+        <v>23869</v>
+      </c>
+      <c r="P736" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q736" t="n">
+        <v>2086.57</v>
+      </c>
+      <c r="R736" t="n">
+        <v>11.43934782921253</v>
+      </c>
+      <c r="S736" t="n">
+        <v>2410769</v>
+      </c>
+      <c r="T736" t="n">
+        <v>1155.374130750466</v>
+      </c>
+      <c r="U736" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V736" t="n">
+        <v>-0.02686725375081545</v>
+      </c>
+      <c r="W736" t="n">
+        <v>-0.04099387825125766</v>
+      </c>
+      <c r="X736" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y736" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z736" t="n">
+        <v>0.4108201563358307</v>
+      </c>
+      <c r="AA736" t="n">
+        <v>10.51282495260239</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E737" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F737" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G737" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H737" t="n">
+        <v>1</v>
+      </c>
+      <c r="I737" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J737" t="n">
+        <v>30</v>
+      </c>
+      <c r="K737" t="n">
+        <v>9</v>
+      </c>
+      <c r="L737" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M737" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N737" s="2" t="n">
+        <v>45835.89427517669</v>
+      </c>
+      <c r="O737" t="n">
+        <v>46.46</v>
+      </c>
+      <c r="P737" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q737" t="n">
+        <v>1</v>
+      </c>
+      <c r="R737" t="n">
+        <v>46.46</v>
+      </c>
+      <c r="S737" t="n">
+        <v>1393.8</v>
+      </c>
+      <c r="T737" t="n">
+        <v>1393.8</v>
+      </c>
+      <c r="U737" t="n">
+        <v>42.174</v>
+      </c>
+      <c r="V737" t="n">
+        <v>0.01707530647985989</v>
+      </c>
+      <c r="W737" t="n">
+        <v>0.01707530647985989</v>
+      </c>
+      <c r="X737" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y737" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z737" t="n">
+        <v>0.5990515947341919</v>
+      </c>
+      <c r="AA737" t="n">
         <v>12.27674007415771</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA737"/>
+  <dimension ref="A1:AA745"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69040,7 +69040,7 @@
         <v>100</v>
       </c>
       <c r="N730" s="2" t="n">
-        <v>45835.89427517669</v>
+        <v>45835.89427517361</v>
       </c>
       <c r="O730" t="n">
         <v>1</v>
@@ -69131,7 +69131,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N731" s="2" t="n">
-        <v>45835.89427517669</v>
+        <v>45835.89427517361</v>
       </c>
       <c r="O731" t="n">
         <v>375</v>
@@ -69226,7 +69226,7 @@
         <v>11.50223774147034</v>
       </c>
       <c r="N732" s="2" t="n">
-        <v>45835.89427517669</v>
+        <v>45835.89427517361</v>
       </c>
       <c r="O732" t="n">
         <v>0.725</v>
@@ -69321,7 +69321,7 @@
         <v>12.54904908370972</v>
       </c>
       <c r="N733" s="2" t="n">
-        <v>45835.89427517669</v>
+        <v>45835.89427517361</v>
       </c>
       <c r="O733" t="n">
         <v>24.7</v>
@@ -69416,7 +69416,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N734" s="2" t="n">
-        <v>45835.89427517669</v>
+        <v>45835.89427517361</v>
       </c>
       <c r="O734" t="n">
         <v>13.4</v>
@@ -69507,7 +69507,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N735" s="2" t="n">
-        <v>45835.89427517669</v>
+        <v>45835.89427517361</v>
       </c>
       <c r="O735" t="n">
         <v>40</v>
@@ -69602,7 +69602,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N736" s="2" t="n">
-        <v>45835.89427517669</v>
+        <v>45835.89427517361</v>
       </c>
       <c r="O736" t="n">
         <v>23869</v>
@@ -69697,7 +69697,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N737" s="2" t="n">
-        <v>45835.89427517669</v>
+        <v>45835.89427517361</v>
       </c>
       <c r="O737" t="n">
         <v>46.46</v>
@@ -69739,6 +69739,760 @@
       </c>
       <c r="AA737" t="n">
         <v>12.27674007415771</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F738" t="n">
+        <v>1</v>
+      </c>
+      <c r="G738" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H738" t="n">
+        <v>1</v>
+      </c>
+      <c r="I738" t="n">
+        <v>1</v>
+      </c>
+      <c r="J738" t="n">
+        <v>1</v>
+      </c>
+      <c r="K738" t="n">
+        <v>100</v>
+      </c>
+      <c r="L738" t="n">
+        <v>100</v>
+      </c>
+      <c r="M738" t="n">
+        <v>100</v>
+      </c>
+      <c r="N738" s="2" t="n">
+        <v>45838.31344841498</v>
+      </c>
+      <c r="O738" t="n">
+        <v>1</v>
+      </c>
+      <c r="P738" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q738" t="n">
+        <v>1</v>
+      </c>
+      <c r="R738" t="n">
+        <v>1</v>
+      </c>
+      <c r="S738" t="n">
+        <v>0</v>
+      </c>
+      <c r="T738" t="n">
+        <v>6.22133174009582</v>
+      </c>
+      <c r="U738" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V738" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W738" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X738" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y738" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z738" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA738" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr"/>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E739" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F739" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G739" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H739" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I739" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J739" t="n">
+        <v>3</v>
+      </c>
+      <c r="K739" t="n">
+        <v>10</v>
+      </c>
+      <c r="L739" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M739" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N739" s="2" t="n">
+        <v>45838.31344841498</v>
+      </c>
+      <c r="O739" t="n">
+        <v>375</v>
+      </c>
+      <c r="P739" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q739" t="n">
+        <v>0.8555</v>
+      </c>
+      <c r="R739" t="n">
+        <v>438.3401519579193</v>
+      </c>
+      <c r="S739" t="n">
+        <v>1125</v>
+      </c>
+      <c r="T739" t="n">
+        <v>1315.020455873758</v>
+      </c>
+      <c r="U739" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V739" t="n">
+        <v>0.01994745230725714</v>
+      </c>
+      <c r="W739" t="n">
+        <v>0.01776568277163793</v>
+      </c>
+      <c r="X739" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y739" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z739" t="n">
+        <v>0.5365895628929138</v>
+      </c>
+      <c r="AA739" t="n">
+        <v>11.5371036529541</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E740" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F740" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G740" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H740" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I740" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J740" t="n">
+        <v>121</v>
+      </c>
+      <c r="K740" t="n">
+        <v>12</v>
+      </c>
+      <c r="L740" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M740" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N740" s="2" t="n">
+        <v>45838.31344841498</v>
+      </c>
+      <c r="O740" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="P740" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q740" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="R740" t="n">
+        <v>11.42483947674235</v>
+      </c>
+      <c r="S740" t="n">
+        <v>1621.4</v>
+      </c>
+      <c r="T740" t="n">
+        <v>1382.405576685825</v>
+      </c>
+      <c r="U740" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V740" t="n">
+        <v>-0.05500705218617763</v>
+      </c>
+      <c r="W740" t="n">
+        <v>-0.07316126714089233</v>
+      </c>
+      <c r="X740" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y740" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z740" t="n">
+        <v>0.5561246275901794</v>
+      </c>
+      <c r="AA740" t="n">
+        <v>12.51355290412903</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr"/>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E741" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F741" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H741" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I741" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J741" t="n">
+        <v>162</v>
+      </c>
+      <c r="K741" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L741" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M741" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N741" s="2" t="n">
+        <v>45838.31344841498</v>
+      </c>
+      <c r="O741" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="P741" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q741" t="n">
+        <v>4.23888</v>
+      </c>
+      <c r="R741" t="n">
+        <v>9.271316951647604</v>
+      </c>
+      <c r="S741" t="n">
+        <v>6366.599999999999</v>
+      </c>
+      <c r="T741" t="n">
+        <v>1501.953346166912</v>
+      </c>
+      <c r="U741" t="n">
+        <v>8.495174269061048</v>
+      </c>
+      <c r="V741" t="n">
+        <v>0.002551020408163129</v>
+      </c>
+      <c r="W741" t="n">
+        <v>0.008660156042373801</v>
+      </c>
+      <c r="X741" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y741" t="n">
+        <v>10.667</v>
+      </c>
+      <c r="Z741" t="n">
+        <v>0.6009591817855835</v>
+      </c>
+      <c r="AA741" t="n">
+        <v>13.92029732894897</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E742" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F742" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G742" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H742" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I742" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J742" t="n">
+        <v>101</v>
+      </c>
+      <c r="K742" t="n">
+        <v>11</v>
+      </c>
+      <c r="L742" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M742" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N742" s="2" t="n">
+        <v>45838.31344841498</v>
+      </c>
+      <c r="O742" t="n">
+        <v>24386</v>
+      </c>
+      <c r="P742" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q742" t="n">
+        <v>2082.99</v>
+      </c>
+      <c r="R742" t="n">
+        <v>11.70720934810057</v>
+      </c>
+      <c r="S742" t="n">
+        <v>2462986</v>
+      </c>
+      <c r="T742" t="n">
+        <v>1182.428144158157</v>
+      </c>
+      <c r="U742" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V742" t="n">
+        <v>-0.005789302022178755</v>
+      </c>
+      <c r="W742" t="n">
+        <v>-0.01853797952086444</v>
+      </c>
+      <c r="X742" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y742" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z742" t="n">
+        <v>0.4416439533233643</v>
+      </c>
+      <c r="AA742" t="n">
+        <v>9.998224020004272</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E743" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F743" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G743" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H743" t="n">
+        <v>1</v>
+      </c>
+      <c r="I743" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J743" t="n">
+        <v>30</v>
+      </c>
+      <c r="K743" t="n">
+        <v>9</v>
+      </c>
+      <c r="L743" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M743" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N743" s="2" t="n">
+        <v>45838.31344841498</v>
+      </c>
+      <c r="O743" t="n">
+        <v>46.46</v>
+      </c>
+      <c r="P743" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q743" t="n">
+        <v>1</v>
+      </c>
+      <c r="R743" t="n">
+        <v>46.46</v>
+      </c>
+      <c r="S743" t="n">
+        <v>1393.8</v>
+      </c>
+      <c r="T743" t="n">
+        <v>1393.8</v>
+      </c>
+      <c r="U743" t="n">
+        <v>42.174</v>
+      </c>
+      <c r="V743" t="n">
+        <v>0.01707530647985989</v>
+      </c>
+      <c r="W743" t="n">
+        <v>0.01707530647985989</v>
+      </c>
+      <c r="X743" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y743" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z743" t="n">
+        <v>0.56679368019104</v>
+      </c>
+      <c r="AA743" t="n">
+        <v>10.87115383148193</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>MHY271836006</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>GLOBAL SHIP LEA. A DL-,01</t>
+        </is>
+      </c>
+      <c r="E744" s="2" t="n">
+        <v>45838.31344841498</v>
+      </c>
+      <c r="F744" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="G744" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H744" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="I744" t="n">
+        <v>22.64505496285648</v>
+      </c>
+      <c r="J744" t="n">
+        <v>66</v>
+      </c>
+      <c r="K744" t="n">
+        <v>10</v>
+      </c>
+      <c r="L744" t="n">
+        <v>0.5395355224609375</v>
+      </c>
+      <c r="M744" t="n">
+        <v>12.45218944549561</v>
+      </c>
+      <c r="N744" s="2" t="n">
+        <v>45838.31344841498</v>
+      </c>
+      <c r="O744" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="P744" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q744" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="R744" t="n">
+        <v>22.64505496285648</v>
+      </c>
+      <c r="S744" t="n">
+        <v>1752.96</v>
+      </c>
+      <c r="T744" t="n">
+        <v>1494.573627548528</v>
+      </c>
+      <c r="U744" t="n">
+        <v>20.38054946657084</v>
+      </c>
+      <c r="V744" t="n">
+        <v>0</v>
+      </c>
+      <c r="W744" t="n">
+        <v>0</v>
+      </c>
+      <c r="X744" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y744" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z744" t="n">
+        <v>0.5395355224609375</v>
+      </c>
+      <c r="AA744" t="n">
+        <v>12.45218944549561</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>US74767N1072</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>QSG</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>QSG</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>QUANTASING GRP  ADR/3CL.A</t>
+        </is>
+      </c>
+      <c r="E745" s="2" t="n">
+        <v>45838.31344841498</v>
+      </c>
+      <c r="F745" t="n">
+        <v>8</v>
+      </c>
+      <c r="G745" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H745" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="I745" t="n">
+        <v>6.820799687607375</v>
+      </c>
+      <c r="J745" t="n">
+        <v>214</v>
+      </c>
+      <c r="K745" t="n">
+        <v>9</v>
+      </c>
+      <c r="L745" t="n">
+        <v>0.6086904406547546</v>
+      </c>
+      <c r="M745" t="n">
+        <v>12.26600360870361</v>
+      </c>
+      <c r="N745" s="2" t="n">
+        <v>45838.31344841498</v>
+      </c>
+      <c r="O745" t="n">
+        <v>8</v>
+      </c>
+      <c r="P745" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q745" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="R745" t="n">
+        <v>6.820799687607375</v>
+      </c>
+      <c r="S745" t="n">
+        <v>1712</v>
+      </c>
+      <c r="T745" t="n">
+        <v>1459.651133147978</v>
+      </c>
+      <c r="U745" t="n">
+        <v>6.138719718846637</v>
+      </c>
+      <c r="V745" t="n">
+        <v>0</v>
+      </c>
+      <c r="W745" t="n">
+        <v>0</v>
+      </c>
+      <c r="X745" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y745" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z745" t="n">
+        <v>0.6086904406547546</v>
+      </c>
+      <c r="AA745" t="n">
+        <v>12.26600360870361</v>
       </c>
     </row>
   </sheetData>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA745"/>
+  <dimension ref="A1:AA753"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69794,7 +69794,7 @@
         <v>100</v>
       </c>
       <c r="N738" s="2" t="n">
-        <v>45838.31344841498</v>
+        <v>45838.31344841435</v>
       </c>
       <c r="O738" t="n">
         <v>1</v>
@@ -69885,7 +69885,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N739" s="2" t="n">
-        <v>45838.31344841498</v>
+        <v>45838.31344841435</v>
       </c>
       <c r="O739" t="n">
         <v>375</v>
@@ -69980,7 +69980,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N740" s="2" t="n">
-        <v>45838.31344841498</v>
+        <v>45838.31344841435</v>
       </c>
       <c r="O740" t="n">
         <v>13.4</v>
@@ -70071,7 +70071,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N741" s="2" t="n">
-        <v>45838.31344841498</v>
+        <v>45838.31344841435</v>
       </c>
       <c r="O741" t="n">
         <v>39.3</v>
@@ -70166,7 +70166,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N742" s="2" t="n">
-        <v>45838.31344841498</v>
+        <v>45838.31344841435</v>
       </c>
       <c r="O742" t="n">
         <v>24386</v>
@@ -70261,7 +70261,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N743" s="2" t="n">
-        <v>45838.31344841498</v>
+        <v>45838.31344841435</v>
       </c>
       <c r="O743" t="n">
         <v>46.46</v>
@@ -70327,7 +70327,7 @@
         </is>
       </c>
       <c r="E744" s="2" t="n">
-        <v>45838.31344841498</v>
+        <v>45838.31344841435</v>
       </c>
       <c r="F744" t="n">
         <v>26.56</v>
@@ -70356,7 +70356,7 @@
         <v>12.45218944549561</v>
       </c>
       <c r="N744" s="2" t="n">
-        <v>45838.31344841498</v>
+        <v>45838.31344841435</v>
       </c>
       <c r="O744" t="n">
         <v>26.56</v>
@@ -70422,7 +70422,7 @@
         </is>
       </c>
       <c r="E745" s="2" t="n">
-        <v>45838.31344841498</v>
+        <v>45838.31344841435</v>
       </c>
       <c r="F745" t="n">
         <v>8</v>
@@ -70451,7 +70451,7 @@
         <v>12.26600360870361</v>
       </c>
       <c r="N745" s="2" t="n">
-        <v>45838.31344841498</v>
+        <v>45838.31344841435</v>
       </c>
       <c r="O745" t="n">
         <v>8</v>
@@ -70492,6 +70492,760 @@
         <v>0.6086904406547546</v>
       </c>
       <c r="AA745" t="n">
+        <v>12.26600360870361</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F746" t="n">
+        <v>1</v>
+      </c>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H746" t="n">
+        <v>1</v>
+      </c>
+      <c r="I746" t="n">
+        <v>1</v>
+      </c>
+      <c r="J746" t="n">
+        <v>1</v>
+      </c>
+      <c r="K746" t="n">
+        <v>100</v>
+      </c>
+      <c r="L746" t="n">
+        <v>100</v>
+      </c>
+      <c r="M746" t="n">
+        <v>100</v>
+      </c>
+      <c r="N746" s="2" t="n">
+        <v>45838.3618508462</v>
+      </c>
+      <c r="O746" t="n">
+        <v>1</v>
+      </c>
+      <c r="P746" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q746" t="n">
+        <v>1</v>
+      </c>
+      <c r="R746" t="n">
+        <v>1</v>
+      </c>
+      <c r="S746" t="n">
+        <v>0</v>
+      </c>
+      <c r="T746" t="n">
+        <v>6.22133174009582</v>
+      </c>
+      <c r="U746" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V746" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W746" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X746" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y746" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z746" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA746" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr"/>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E747" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F747" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H747" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I747" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J747" t="n">
+        <v>3</v>
+      </c>
+      <c r="K747" t="n">
+        <v>10</v>
+      </c>
+      <c r="L747" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M747" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N747" s="2" t="n">
+        <v>45838.3618508462</v>
+      </c>
+      <c r="O747" t="n">
+        <v>370.8</v>
+      </c>
+      <c r="P747" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q747" t="n">
+        <v>0.8557399999999999</v>
+      </c>
+      <c r="R747" t="n">
+        <v>433.3091826956787</v>
+      </c>
+      <c r="S747" t="n">
+        <v>1112.4</v>
+      </c>
+      <c r="T747" t="n">
+        <v>1299.927548087036</v>
+      </c>
+      <c r="U747" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V747" t="n">
+        <v>0.008524040841415781</v>
+      </c>
+      <c r="W747" t="n">
+        <v>0.006084462506242172</v>
+      </c>
+      <c r="X747" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y747" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z747" t="n">
+        <v>0.5365895628929138</v>
+      </c>
+      <c r="AA747" t="n">
+        <v>11.5371036529541</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E748" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F748" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H748" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I748" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J748" t="n">
+        <v>121</v>
+      </c>
+      <c r="K748" t="n">
+        <v>12</v>
+      </c>
+      <c r="L748" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M748" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N748" s="2" t="n">
+        <v>45838.3618508462</v>
+      </c>
+      <c r="O748" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="P748" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q748" t="n">
+        <v>1.1727453</v>
+      </c>
+      <c r="R748" t="n">
+        <v>11.4261809448309</v>
+      </c>
+      <c r="S748" t="n">
+        <v>1621.4</v>
+      </c>
+      <c r="T748" t="n">
+        <v>1382.567894324539</v>
+      </c>
+      <c r="U748" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V748" t="n">
+        <v>-0.05500705218617763</v>
+      </c>
+      <c r="W748" t="n">
+        <v>-0.07305244070303352</v>
+      </c>
+      <c r="X748" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y748" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z748" t="n">
+        <v>0.5561246275901794</v>
+      </c>
+      <c r="AA748" t="n">
+        <v>12.51355290412903</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr"/>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E749" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F749" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G749" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H749" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I749" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J749" t="n">
+        <v>162</v>
+      </c>
+      <c r="K749" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L749" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M749" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N749" s="2" t="n">
+        <v>45838.3618508462</v>
+      </c>
+      <c r="O749" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="P749" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q749" t="n">
+        <v>4.24059</v>
+      </c>
+      <c r="R749" t="n">
+        <v>9.361904829280832</v>
+      </c>
+      <c r="S749" t="n">
+        <v>6431.400000000001</v>
+      </c>
+      <c r="T749" t="n">
+        <v>1516.628582343495</v>
+      </c>
+      <c r="U749" t="n">
+        <v>8.495174269061048</v>
+      </c>
+      <c r="V749" t="n">
+        <v>0.01275510204081631</v>
+      </c>
+      <c r="W749" t="n">
+        <v>0.01851553940005757</v>
+      </c>
+      <c r="X749" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y749" t="n">
+        <v>10.667</v>
+      </c>
+      <c r="Z749" t="n">
+        <v>0.6009591817855835</v>
+      </c>
+      <c r="AA749" t="n">
+        <v>13.92029732894897</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E750" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F750" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G750" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H750" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I750" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J750" t="n">
+        <v>101</v>
+      </c>
+      <c r="K750" t="n">
+        <v>11</v>
+      </c>
+      <c r="L750" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M750" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N750" s="2" t="n">
+        <v>45838.3618508462</v>
+      </c>
+      <c r="O750" t="n">
+        <v>24457</v>
+      </c>
+      <c r="P750" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q750" t="n">
+        <v>2085.8</v>
+      </c>
+      <c r="R750" t="n">
+        <v>11.72547703519033</v>
+      </c>
+      <c r="S750" t="n">
+        <v>2470157</v>
+      </c>
+      <c r="T750" t="n">
+        <v>1184.273180554224</v>
+      </c>
+      <c r="U750" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V750" t="n">
+        <v>-0.002894651011089322</v>
+      </c>
+      <c r="W750" t="n">
+        <v>-0.01700652650353962</v>
+      </c>
+      <c r="X750" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y750" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z750" t="n">
+        <v>0.4416439533233643</v>
+      </c>
+      <c r="AA750" t="n">
+        <v>9.998224020004272</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E751" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F751" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G751" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H751" t="n">
+        <v>1</v>
+      </c>
+      <c r="I751" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J751" t="n">
+        <v>30</v>
+      </c>
+      <c r="K751" t="n">
+        <v>9</v>
+      </c>
+      <c r="L751" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M751" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N751" s="2" t="n">
+        <v>45838.3618508462</v>
+      </c>
+      <c r="O751" t="n">
+        <v>45.98</v>
+      </c>
+      <c r="P751" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q751" t="n">
+        <v>1</v>
+      </c>
+      <c r="R751" t="n">
+        <v>45.98</v>
+      </c>
+      <c r="S751" t="n">
+        <v>1379.4</v>
+      </c>
+      <c r="T751" t="n">
+        <v>1379.4</v>
+      </c>
+      <c r="U751" t="n">
+        <v>42.174</v>
+      </c>
+      <c r="V751" t="n">
+        <v>0.006567425569176777</v>
+      </c>
+      <c r="W751" t="n">
+        <v>0.006567425569176777</v>
+      </c>
+      <c r="X751" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y751" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z751" t="n">
+        <v>0.56679368019104</v>
+      </c>
+      <c r="AA751" t="n">
+        <v>10.87115383148193</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>MHY271836006</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>GLOBAL SHIP LEA. A DL-,01</t>
+        </is>
+      </c>
+      <c r="E752" s="2" t="n">
+        <v>45838.31344841435</v>
+      </c>
+      <c r="F752" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="G752" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H752" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="I752" t="n">
+        <v>22.64505496285648</v>
+      </c>
+      <c r="J752" t="n">
+        <v>66</v>
+      </c>
+      <c r="K752" t="n">
+        <v>10</v>
+      </c>
+      <c r="L752" t="n">
+        <v>0.5395355224609375</v>
+      </c>
+      <c r="M752" t="n">
+        <v>12.45218944549561</v>
+      </c>
+      <c r="N752" s="2" t="n">
+        <v>45838.3618508462</v>
+      </c>
+      <c r="O752" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="P752" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q752" t="n">
+        <v>1.1727453</v>
+      </c>
+      <c r="R752" t="n">
+        <v>22.64771387273946</v>
+      </c>
+      <c r="S752" t="n">
+        <v>1752.96</v>
+      </c>
+      <c r="T752" t="n">
+        <v>1494.749115600804</v>
+      </c>
+      <c r="U752" t="n">
+        <v>20.38294248546551</v>
+      </c>
+      <c r="V752" t="n">
+        <v>0</v>
+      </c>
+      <c r="W752" t="n">
+        <v>0.0001174167997088915</v>
+      </c>
+      <c r="X752" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y752" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z752" t="n">
+        <v>0.5395355224609375</v>
+      </c>
+      <c r="AA752" t="n">
+        <v>12.45218944549561</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>US74767N1072</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>QSG</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>QSG</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>QUANTASING GRP  ADR/3CL.A</t>
+        </is>
+      </c>
+      <c r="E753" s="2" t="n">
+        <v>45838.31344841435</v>
+      </c>
+      <c r="F753" t="n">
+        <v>8</v>
+      </c>
+      <c r="G753" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H753" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="I753" t="n">
+        <v>6.820799687607375</v>
+      </c>
+      <c r="J753" t="n">
+        <v>214</v>
+      </c>
+      <c r="K753" t="n">
+        <v>9</v>
+      </c>
+      <c r="L753" t="n">
+        <v>0.6086904406547546</v>
+      </c>
+      <c r="M753" t="n">
+        <v>12.26600360870361</v>
+      </c>
+      <c r="N753" s="2" t="n">
+        <v>45838.3618508462</v>
+      </c>
+      <c r="O753" t="n">
+        <v>8</v>
+      </c>
+      <c r="P753" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q753" t="n">
+        <v>1.1727453</v>
+      </c>
+      <c r="R753" t="n">
+        <v>6.82160056407815</v>
+      </c>
+      <c r="S753" t="n">
+        <v>1712</v>
+      </c>
+      <c r="T753" t="n">
+        <v>1459.822520712724</v>
+      </c>
+      <c r="U753" t="n">
+        <v>6.139440507670335</v>
+      </c>
+      <c r="V753" t="n">
+        <v>0</v>
+      </c>
+      <c r="W753" t="n">
+        <v>0.0001174167997088915</v>
+      </c>
+      <c r="X753" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y753" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z753" t="n">
+        <v>0.6086904406547546</v>
+      </c>
+      <c r="AA753" t="n">
         <v>12.26600360870361</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA753"/>
+  <dimension ref="A1:AA761"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70548,7 +70548,7 @@
         <v>100</v>
       </c>
       <c r="N746" s="2" t="n">
-        <v>45838.3618508462</v>
+        <v>45838.36185084491</v>
       </c>
       <c r="O746" t="n">
         <v>1</v>
@@ -70639,7 +70639,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N747" s="2" t="n">
-        <v>45838.3618508462</v>
+        <v>45838.36185084491</v>
       </c>
       <c r="O747" t="n">
         <v>370.8</v>
@@ -70734,7 +70734,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N748" s="2" t="n">
-        <v>45838.3618508462</v>
+        <v>45838.36185084491</v>
       </c>
       <c r="O748" t="n">
         <v>13.4</v>
@@ -70825,7 +70825,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N749" s="2" t="n">
-        <v>45838.3618508462</v>
+        <v>45838.36185084491</v>
       </c>
       <c r="O749" t="n">
         <v>39.7</v>
@@ -70920,7 +70920,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N750" s="2" t="n">
-        <v>45838.3618508462</v>
+        <v>45838.36185084491</v>
       </c>
       <c r="O750" t="n">
         <v>24457</v>
@@ -71015,7 +71015,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N751" s="2" t="n">
-        <v>45838.3618508462</v>
+        <v>45838.36185084491</v>
       </c>
       <c r="O751" t="n">
         <v>45.98</v>
@@ -71110,7 +71110,7 @@
         <v>12.45218944549561</v>
       </c>
       <c r="N752" s="2" t="n">
-        <v>45838.3618508462</v>
+        <v>45838.36185084491</v>
       </c>
       <c r="O752" t="n">
         <v>26.56</v>
@@ -71205,7 +71205,7 @@
         <v>12.26600360870361</v>
       </c>
       <c r="N753" s="2" t="n">
-        <v>45838.3618508462</v>
+        <v>45838.36185084491</v>
       </c>
       <c r="O753" t="n">
         <v>8</v>
@@ -71246,6 +71246,760 @@
         <v>0.6086904406547546</v>
       </c>
       <c r="AA753" t="n">
+        <v>12.26600360870361</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E754" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F754" t="n">
+        <v>1</v>
+      </c>
+      <c r="G754" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H754" t="n">
+        <v>1</v>
+      </c>
+      <c r="I754" t="n">
+        <v>1</v>
+      </c>
+      <c r="J754" t="n">
+        <v>1</v>
+      </c>
+      <c r="K754" t="n">
+        <v>100</v>
+      </c>
+      <c r="L754" t="n">
+        <v>100</v>
+      </c>
+      <c r="M754" t="n">
+        <v>100</v>
+      </c>
+      <c r="N754" s="2" t="n">
+        <v>45838.39947125121</v>
+      </c>
+      <c r="O754" t="n">
+        <v>1</v>
+      </c>
+      <c r="P754" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q754" t="n">
+        <v>1</v>
+      </c>
+      <c r="R754" t="n">
+        <v>1</v>
+      </c>
+      <c r="S754" t="n">
+        <v>0</v>
+      </c>
+      <c r="T754" t="n">
+        <v>6.22133174009582</v>
+      </c>
+      <c r="U754" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V754" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W754" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X754" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y754" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z754" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA754" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr"/>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E755" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F755" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G755" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H755" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I755" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J755" t="n">
+        <v>3</v>
+      </c>
+      <c r="K755" t="n">
+        <v>10</v>
+      </c>
+      <c r="L755" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M755" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N755" s="2" t="n">
+        <v>45838.39947125121</v>
+      </c>
+      <c r="O755" t="n">
+        <v>370.888</v>
+      </c>
+      <c r="P755" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q755" t="n">
+        <v>0.85611</v>
+      </c>
+      <c r="R755" t="n">
+        <v>433.2247024330985</v>
+      </c>
+      <c r="S755" t="n">
+        <v>1112.664</v>
+      </c>
+      <c r="T755" t="n">
+        <v>1299.674107299296</v>
+      </c>
+      <c r="U755" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V755" t="n">
+        <v>0.008763388510223846</v>
+      </c>
+      <c r="W755" t="n">
+        <v>0.005888310929113016</v>
+      </c>
+      <c r="X755" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y755" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z755" t="n">
+        <v>0.5365895628929138</v>
+      </c>
+      <c r="AA755" t="n">
+        <v>11.5371036529541</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E756" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F756" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G756" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H756" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I756" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J756" t="n">
+        <v>121</v>
+      </c>
+      <c r="K756" t="n">
+        <v>12</v>
+      </c>
+      <c r="L756" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M756" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N756" s="2" t="n">
+        <v>45838.39947125121</v>
+      </c>
+      <c r="O756" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="P756" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q756" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="R756" t="n">
+        <v>11.42483947674235</v>
+      </c>
+      <c r="S756" t="n">
+        <v>1621.4</v>
+      </c>
+      <c r="T756" t="n">
+        <v>1382.405576685825</v>
+      </c>
+      <c r="U756" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V756" t="n">
+        <v>-0.05500705218617763</v>
+      </c>
+      <c r="W756" t="n">
+        <v>-0.07316126714089233</v>
+      </c>
+      <c r="X756" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y756" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z756" t="n">
+        <v>0.5561246275901794</v>
+      </c>
+      <c r="AA756" t="n">
+        <v>12.51355290412903</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr"/>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E757" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F757" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G757" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H757" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I757" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J757" t="n">
+        <v>162</v>
+      </c>
+      <c r="K757" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L757" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M757" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N757" s="2" t="n">
+        <v>45838.39947125121</v>
+      </c>
+      <c r="O757" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="P757" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q757" t="n">
+        <v>4.23891</v>
+      </c>
+      <c r="R757" t="n">
+        <v>9.365615217119496</v>
+      </c>
+      <c r="S757" t="n">
+        <v>6431.400000000001</v>
+      </c>
+      <c r="T757" t="n">
+        <v>1517.229665173358</v>
+      </c>
+      <c r="U757" t="n">
+        <v>8.495174269061048</v>
+      </c>
+      <c r="V757" t="n">
+        <v>0.01275510204081631</v>
+      </c>
+      <c r="W757" t="n">
+        <v>0.01891920593371643</v>
+      </c>
+      <c r="X757" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y757" t="n">
+        <v>10.667</v>
+      </c>
+      <c r="Z757" t="n">
+        <v>0.6009591817855835</v>
+      </c>
+      <c r="AA757" t="n">
+        <v>13.92029732894897</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E758" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F758" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G758" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H758" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I758" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J758" t="n">
+        <v>101</v>
+      </c>
+      <c r="K758" t="n">
+        <v>11</v>
+      </c>
+      <c r="L758" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M758" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N758" s="2" t="n">
+        <v>45838.39947125121</v>
+      </c>
+      <c r="O758" t="n">
+        <v>24241</v>
+      </c>
+      <c r="P758" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q758" t="n">
+        <v>2085.23</v>
+      </c>
+      <c r="R758" t="n">
+        <v>11.62509651213535</v>
+      </c>
+      <c r="S758" t="n">
+        <v>2448341</v>
+      </c>
+      <c r="T758" t="n">
+        <v>1174.134747725671</v>
+      </c>
+      <c r="U758" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V758" t="n">
+        <v>-0.01170091324200917</v>
+      </c>
+      <c r="W758" t="n">
+        <v>-0.02542182583277552</v>
+      </c>
+      <c r="X758" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y758" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z758" t="n">
+        <v>0.4416439533233643</v>
+      </c>
+      <c r="AA758" t="n">
+        <v>9.998224020004272</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E759" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F759" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G759" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H759" t="n">
+        <v>1</v>
+      </c>
+      <c r="I759" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J759" t="n">
+        <v>30</v>
+      </c>
+      <c r="K759" t="n">
+        <v>9</v>
+      </c>
+      <c r="L759" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M759" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N759" s="2" t="n">
+        <v>45838.39947125121</v>
+      </c>
+      <c r="O759" t="n">
+        <v>45.86</v>
+      </c>
+      <c r="P759" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q759" t="n">
+        <v>1</v>
+      </c>
+      <c r="R759" t="n">
+        <v>45.86</v>
+      </c>
+      <c r="S759" t="n">
+        <v>1375.8</v>
+      </c>
+      <c r="T759" t="n">
+        <v>1375.8</v>
+      </c>
+      <c r="U759" t="n">
+        <v>42.174</v>
+      </c>
+      <c r="V759" t="n">
+        <v>0.003940455341506111</v>
+      </c>
+      <c r="W759" t="n">
+        <v>0.003940455341506111</v>
+      </c>
+      <c r="X759" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y759" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z759" t="n">
+        <v>0.56679368019104</v>
+      </c>
+      <c r="AA759" t="n">
+        <v>10.87115383148193</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>MHY271836006</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>GLOBAL SHIP LEA. A DL-,01</t>
+        </is>
+      </c>
+      <c r="E760" s="2" t="n">
+        <v>45838.31344841435</v>
+      </c>
+      <c r="F760" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="G760" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H760" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="I760" t="n">
+        <v>22.64505496285648</v>
+      </c>
+      <c r="J760" t="n">
+        <v>66</v>
+      </c>
+      <c r="K760" t="n">
+        <v>10</v>
+      </c>
+      <c r="L760" t="n">
+        <v>0.5395355224609375</v>
+      </c>
+      <c r="M760" t="n">
+        <v>12.45218944549561</v>
+      </c>
+      <c r="N760" s="2" t="n">
+        <v>45838.39947125121</v>
+      </c>
+      <c r="O760" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="P760" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q760" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="R760" t="n">
+        <v>22.64505496285648</v>
+      </c>
+      <c r="S760" t="n">
+        <v>1752.96</v>
+      </c>
+      <c r="T760" t="n">
+        <v>1494.573627548528</v>
+      </c>
+      <c r="U760" t="n">
+        <v>20.38294248546551</v>
+      </c>
+      <c r="V760" t="n">
+        <v>0</v>
+      </c>
+      <c r="W760" t="n">
+        <v>0</v>
+      </c>
+      <c r="X760" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y760" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z760" t="n">
+        <v>0.5395355224609375</v>
+      </c>
+      <c r="AA760" t="n">
+        <v>12.45218944549561</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>US74767N1072</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>QSG</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>QSG</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>QUANTASING GRP  ADR/3CL.A</t>
+        </is>
+      </c>
+      <c r="E761" s="2" t="n">
+        <v>45838.31344841435</v>
+      </c>
+      <c r="F761" t="n">
+        <v>8</v>
+      </c>
+      <c r="G761" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H761" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="I761" t="n">
+        <v>6.820799687607375</v>
+      </c>
+      <c r="J761" t="n">
+        <v>214</v>
+      </c>
+      <c r="K761" t="n">
+        <v>9</v>
+      </c>
+      <c r="L761" t="n">
+        <v>0.6086904406547546</v>
+      </c>
+      <c r="M761" t="n">
+        <v>12.26600360870361</v>
+      </c>
+      <c r="N761" s="2" t="n">
+        <v>45838.39947125121</v>
+      </c>
+      <c r="O761" t="n">
+        <v>8</v>
+      </c>
+      <c r="P761" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q761" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="R761" t="n">
+        <v>6.820799687607375</v>
+      </c>
+      <c r="S761" t="n">
+        <v>1712</v>
+      </c>
+      <c r="T761" t="n">
+        <v>1459.651133147978</v>
+      </c>
+      <c r="U761" t="n">
+        <v>6.139440507670335</v>
+      </c>
+      <c r="V761" t="n">
+        <v>0</v>
+      </c>
+      <c r="W761" t="n">
+        <v>0</v>
+      </c>
+      <c r="X761" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y761" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z761" t="n">
+        <v>0.6086904406547546</v>
+      </c>
+      <c r="AA761" t="n">
         <v>12.26600360870361</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA761"/>
+  <dimension ref="A1:AA769"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71302,7 +71302,7 @@
         <v>100</v>
       </c>
       <c r="N754" s="2" t="n">
-        <v>45838.39947125121</v>
+        <v>45838.39947125</v>
       </c>
       <c r="O754" t="n">
         <v>1</v>
@@ -71393,7 +71393,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N755" s="2" t="n">
-        <v>45838.39947125121</v>
+        <v>45838.39947125</v>
       </c>
       <c r="O755" t="n">
         <v>370.888</v>
@@ -71488,7 +71488,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N756" s="2" t="n">
-        <v>45838.39947125121</v>
+        <v>45838.39947125</v>
       </c>
       <c r="O756" t="n">
         <v>13.4</v>
@@ -71579,7 +71579,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N757" s="2" t="n">
-        <v>45838.39947125121</v>
+        <v>45838.39947125</v>
       </c>
       <c r="O757" t="n">
         <v>39.7</v>
@@ -71674,7 +71674,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N758" s="2" t="n">
-        <v>45838.39947125121</v>
+        <v>45838.39947125</v>
       </c>
       <c r="O758" t="n">
         <v>24241</v>
@@ -71769,7 +71769,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N759" s="2" t="n">
-        <v>45838.39947125121</v>
+        <v>45838.39947125</v>
       </c>
       <c r="O759" t="n">
         <v>45.86</v>
@@ -71864,7 +71864,7 @@
         <v>12.45218944549561</v>
       </c>
       <c r="N760" s="2" t="n">
-        <v>45838.39947125121</v>
+        <v>45838.39947125</v>
       </c>
       <c r="O760" t="n">
         <v>26.56</v>
@@ -71959,7 +71959,7 @@
         <v>12.26600360870361</v>
       </c>
       <c r="N761" s="2" t="n">
-        <v>45838.39947125121</v>
+        <v>45838.39947125</v>
       </c>
       <c r="O761" t="n">
         <v>8</v>
@@ -72000,6 +72000,760 @@
         <v>0.6086904406547546</v>
       </c>
       <c r="AA761" t="n">
+        <v>12.26600360870361</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E762" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F762" t="n">
+        <v>1</v>
+      </c>
+      <c r="G762" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H762" t="n">
+        <v>1</v>
+      </c>
+      <c r="I762" t="n">
+        <v>1</v>
+      </c>
+      <c r="J762" t="n">
+        <v>1</v>
+      </c>
+      <c r="K762" t="n">
+        <v>100</v>
+      </c>
+      <c r="L762" t="n">
+        <v>100</v>
+      </c>
+      <c r="M762" t="n">
+        <v>100</v>
+      </c>
+      <c r="N762" s="2" t="n">
+        <v>45838.44238600003</v>
+      </c>
+      <c r="O762" t="n">
+        <v>1</v>
+      </c>
+      <c r="P762" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q762" t="n">
+        <v>1</v>
+      </c>
+      <c r="R762" t="n">
+        <v>1</v>
+      </c>
+      <c r="S762" t="n">
+        <v>0</v>
+      </c>
+      <c r="T762" t="n">
+        <v>6.22133174009582</v>
+      </c>
+      <c r="U762" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V762" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W762" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X762" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y762" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z762" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA762" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr"/>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E763" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F763" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G763" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H763" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I763" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J763" t="n">
+        <v>3</v>
+      </c>
+      <c r="K763" t="n">
+        <v>10</v>
+      </c>
+      <c r="L763" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M763" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N763" s="2" t="n">
+        <v>45838.44238600003</v>
+      </c>
+      <c r="O763" t="n">
+        <v>368</v>
+      </c>
+      <c r="P763" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q763" t="n">
+        <v>0.85576</v>
+      </c>
+      <c r="R763" t="n">
+        <v>430.0271104047864</v>
+      </c>
+      <c r="S763" t="n">
+        <v>1104</v>
+      </c>
+      <c r="T763" t="n">
+        <v>1290.081331214359</v>
+      </c>
+      <c r="U763" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V763" t="n">
+        <v>0.000908433197521763</v>
+      </c>
+      <c r="W763" t="n">
+        <v>-0.0015360589794704</v>
+      </c>
+      <c r="X763" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y763" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z763" t="n">
+        <v>0.5365895628929138</v>
+      </c>
+      <c r="AA763" t="n">
+        <v>11.5371036529541</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E764" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F764" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G764" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H764" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I764" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J764" t="n">
+        <v>121</v>
+      </c>
+      <c r="K764" t="n">
+        <v>12</v>
+      </c>
+      <c r="L764" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M764" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N764" s="2" t="n">
+        <v>45838.44238600003</v>
+      </c>
+      <c r="O764" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="P764" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q764" t="n">
+        <v>1.1724703</v>
+      </c>
+      <c r="R764" t="n">
+        <v>11.42886092722349</v>
+      </c>
+      <c r="S764" t="n">
+        <v>1621.4</v>
+      </c>
+      <c r="T764" t="n">
+        <v>1382.892172194042</v>
+      </c>
+      <c r="U764" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V764" t="n">
+        <v>-0.05500705218617763</v>
+      </c>
+      <c r="W764" t="n">
+        <v>-0.07283502745273063</v>
+      </c>
+      <c r="X764" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y764" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z764" t="n">
+        <v>0.5561246275901794</v>
+      </c>
+      <c r="AA764" t="n">
+        <v>12.51355290412903</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr"/>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E765" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F765" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G765" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H765" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I765" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J765" t="n">
+        <v>162</v>
+      </c>
+      <c r="K765" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L765" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M765" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N765" s="2" t="n">
+        <v>45838.44238600003</v>
+      </c>
+      <c r="O765" t="n">
+        <v>39.45</v>
+      </c>
+      <c r="P765" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q765" t="n">
+        <v>4.24022</v>
+      </c>
+      <c r="R765" t="n">
+        <v>9.303762540622893</v>
+      </c>
+      <c r="S765" t="n">
+        <v>6390.900000000001</v>
+      </c>
+      <c r="T765" t="n">
+        <v>1507.209531580909</v>
+      </c>
+      <c r="U765" t="n">
+        <v>8.495174269061048</v>
+      </c>
+      <c r="V765" t="n">
+        <v>0.006377551020408267</v>
+      </c>
+      <c r="W765" t="n">
+        <v>0.01219002919948609</v>
+      </c>
+      <c r="X765" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y765" t="n">
+        <v>10.667</v>
+      </c>
+      <c r="Z765" t="n">
+        <v>0.6009591817855835</v>
+      </c>
+      <c r="AA765" t="n">
+        <v>13.92029732894897</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E766" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F766" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G766" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H766" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I766" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J766" t="n">
+        <v>101</v>
+      </c>
+      <c r="K766" t="n">
+        <v>11</v>
+      </c>
+      <c r="L766" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M766" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N766" s="2" t="n">
+        <v>45838.44238600003</v>
+      </c>
+      <c r="O766" t="n">
+        <v>24273</v>
+      </c>
+      <c r="P766" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q766" t="n">
+        <v>2082.55</v>
+      </c>
+      <c r="R766" t="n">
+        <v>11.655422438837</v>
+      </c>
+      <c r="S766" t="n">
+        <v>2451573</v>
+      </c>
+      <c r="T766" t="n">
+        <v>1177.197666322537</v>
+      </c>
+      <c r="U766" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V766" t="n">
+        <v>-0.01039628180039143</v>
+      </c>
+      <c r="W766" t="n">
+        <v>-0.02287948252887506</v>
+      </c>
+      <c r="X766" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y766" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z766" t="n">
+        <v>0.4416439533233643</v>
+      </c>
+      <c r="AA766" t="n">
+        <v>9.998224020004272</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E767" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F767" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G767" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H767" t="n">
+        <v>1</v>
+      </c>
+      <c r="I767" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J767" t="n">
+        <v>30</v>
+      </c>
+      <c r="K767" t="n">
+        <v>9</v>
+      </c>
+      <c r="L767" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M767" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N767" s="2" t="n">
+        <v>45838.44238600003</v>
+      </c>
+      <c r="O767" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="P767" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q767" t="n">
+        <v>1</v>
+      </c>
+      <c r="R767" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="S767" t="n">
+        <v>1371</v>
+      </c>
+      <c r="T767" t="n">
+        <v>1371</v>
+      </c>
+      <c r="U767" t="n">
+        <v>42.174</v>
+      </c>
+      <c r="V767" t="n">
+        <v>0.0004378283712784814</v>
+      </c>
+      <c r="W767" t="n">
+        <v>0.0004378283712784814</v>
+      </c>
+      <c r="X767" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y767" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z767" t="n">
+        <v>0.56679368019104</v>
+      </c>
+      <c r="AA767" t="n">
+        <v>10.87115383148193</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>MHY271836006</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>GLOBAL SHIP LEA. A DL-,01</t>
+        </is>
+      </c>
+      <c r="E768" s="2" t="n">
+        <v>45838.31344841435</v>
+      </c>
+      <c r="F768" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="G768" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H768" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="I768" t="n">
+        <v>22.64505496285648</v>
+      </c>
+      <c r="J768" t="n">
+        <v>66</v>
+      </c>
+      <c r="K768" t="n">
+        <v>10</v>
+      </c>
+      <c r="L768" t="n">
+        <v>0.5395355224609375</v>
+      </c>
+      <c r="M768" t="n">
+        <v>12.45218944549561</v>
+      </c>
+      <c r="N768" s="2" t="n">
+        <v>45838.44238600003</v>
+      </c>
+      <c r="O768" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="P768" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q768" t="n">
+        <v>1.1724703</v>
+      </c>
+      <c r="R768" t="n">
+        <v>22.65302583783998</v>
+      </c>
+      <c r="S768" t="n">
+        <v>1752.96</v>
+      </c>
+      <c r="T768" t="n">
+        <v>1495.099705297439</v>
+      </c>
+      <c r="U768" t="n">
+        <v>20.38772325405598</v>
+      </c>
+      <c r="V768" t="n">
+        <v>0</v>
+      </c>
+      <c r="W768" t="n">
+        <v>0.0003519918585568327</v>
+      </c>
+      <c r="X768" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y768" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z768" t="n">
+        <v>0.5395355224609375</v>
+      </c>
+      <c r="AA768" t="n">
+        <v>12.45218944549561</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>US74767N1072</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>QSG</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>QSG</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>QUANTASING GRP  ADR/3CL.A</t>
+        </is>
+      </c>
+      <c r="E769" s="2" t="n">
+        <v>45838.31344841435</v>
+      </c>
+      <c r="F769" t="n">
+        <v>8</v>
+      </c>
+      <c r="G769" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H769" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="I769" t="n">
+        <v>6.820799687607375</v>
+      </c>
+      <c r="J769" t="n">
+        <v>214</v>
+      </c>
+      <c r="K769" t="n">
+        <v>9</v>
+      </c>
+      <c r="L769" t="n">
+        <v>0.6086904406547546</v>
+      </c>
+      <c r="M769" t="n">
+        <v>12.26600360870361</v>
+      </c>
+      <c r="N769" s="2" t="n">
+        <v>45838.44238600003</v>
+      </c>
+      <c r="O769" t="n">
+        <v>8</v>
+      </c>
+      <c r="P769" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q769" t="n">
+        <v>1.1724703</v>
+      </c>
+      <c r="R769" t="n">
+        <v>6.82320055356626</v>
+      </c>
+      <c r="S769" t="n">
+        <v>1712</v>
+      </c>
+      <c r="T769" t="n">
+        <v>1460.16491846318</v>
+      </c>
+      <c r="U769" t="n">
+        <v>6.140880498209635</v>
+      </c>
+      <c r="V769" t="n">
+        <v>0</v>
+      </c>
+      <c r="W769" t="n">
+        <v>0.0003519918585570547</v>
+      </c>
+      <c r="X769" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y769" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z769" t="n">
+        <v>0.6086904406547546</v>
+      </c>
+      <c r="AA769" t="n">
         <v>12.26600360870361</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA769"/>
+  <dimension ref="A1:AA777"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72056,7 +72056,7 @@
         <v>100</v>
       </c>
       <c r="N762" s="2" t="n">
-        <v>45838.44238600003</v>
+        <v>45838.44238599537</v>
       </c>
       <c r="O762" t="n">
         <v>1</v>
@@ -72147,7 +72147,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N763" s="2" t="n">
-        <v>45838.44238600003</v>
+        <v>45838.44238599537</v>
       </c>
       <c r="O763" t="n">
         <v>368</v>
@@ -72242,7 +72242,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N764" s="2" t="n">
-        <v>45838.44238600003</v>
+        <v>45838.44238599537</v>
       </c>
       <c r="O764" t="n">
         <v>13.4</v>
@@ -72333,7 +72333,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N765" s="2" t="n">
-        <v>45838.44238600003</v>
+        <v>45838.44238599537</v>
       </c>
       <c r="O765" t="n">
         <v>39.45</v>
@@ -72428,7 +72428,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N766" s="2" t="n">
-        <v>45838.44238600003</v>
+        <v>45838.44238599537</v>
       </c>
       <c r="O766" t="n">
         <v>24273</v>
@@ -72523,7 +72523,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N767" s="2" t="n">
-        <v>45838.44238600003</v>
+        <v>45838.44238599537</v>
       </c>
       <c r="O767" t="n">
         <v>45.7</v>
@@ -72618,7 +72618,7 @@
         <v>12.45218944549561</v>
       </c>
       <c r="N768" s="2" t="n">
-        <v>45838.44238600003</v>
+        <v>45838.44238599537</v>
       </c>
       <c r="O768" t="n">
         <v>26.56</v>
@@ -72713,7 +72713,7 @@
         <v>12.26600360870361</v>
       </c>
       <c r="N769" s="2" t="n">
-        <v>45838.44238600003</v>
+        <v>45838.44238599537</v>
       </c>
       <c r="O769" t="n">
         <v>8</v>
@@ -72754,6 +72754,760 @@
         <v>0.6086904406547546</v>
       </c>
       <c r="AA769" t="n">
+        <v>12.26600360870361</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E770" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F770" t="n">
+        <v>1</v>
+      </c>
+      <c r="G770" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H770" t="n">
+        <v>1</v>
+      </c>
+      <c r="I770" t="n">
+        <v>1</v>
+      </c>
+      <c r="J770" t="n">
+        <v>1</v>
+      </c>
+      <c r="K770" t="n">
+        <v>100</v>
+      </c>
+      <c r="L770" t="n">
+        <v>100</v>
+      </c>
+      <c r="M770" t="n">
+        <v>100</v>
+      </c>
+      <c r="N770" s="2" t="n">
+        <v>45838.47687138714</v>
+      </c>
+      <c r="O770" t="n">
+        <v>1</v>
+      </c>
+      <c r="P770" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q770" t="n">
+        <v>1</v>
+      </c>
+      <c r="R770" t="n">
+        <v>1</v>
+      </c>
+      <c r="S770" t="n">
+        <v>0</v>
+      </c>
+      <c r="T770" t="n">
+        <v>6.22133174009582</v>
+      </c>
+      <c r="U770" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V770" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W770" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X770" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y770" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z770" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA770" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr"/>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E771" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F771" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G771" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H771" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I771" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J771" t="n">
+        <v>3</v>
+      </c>
+      <c r="K771" t="n">
+        <v>10</v>
+      </c>
+      <c r="L771" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M771" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N771" s="2" t="n">
+        <v>45838.47687138714</v>
+      </c>
+      <c r="O771" t="n">
+        <v>374.4</v>
+      </c>
+      <c r="P771" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q771" t="n">
+        <v>0.8555</v>
+      </c>
+      <c r="R771" t="n">
+        <v>437.6388077147867</v>
+      </c>
+      <c r="S771" t="n">
+        <v>1123.2</v>
+      </c>
+      <c r="T771" t="n">
+        <v>1312.91642314436</v>
+      </c>
+      <c r="U771" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V771" t="n">
+        <v>0.01831553638356542</v>
+      </c>
+      <c r="W771" t="n">
+        <v>0.01613725767920315</v>
+      </c>
+      <c r="X771" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y771" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z771" t="n">
+        <v>0.5365895628929138</v>
+      </c>
+      <c r="AA771" t="n">
+        <v>11.5371036529541</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E772" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F772" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G772" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H772" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I772" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J772" t="n">
+        <v>121</v>
+      </c>
+      <c r="K772" t="n">
+        <v>12</v>
+      </c>
+      <c r="L772" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M772" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N772" s="2" t="n">
+        <v>45838.47687138714</v>
+      </c>
+      <c r="O772" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="P772" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q772" t="n">
+        <v>1.1732959</v>
+      </c>
+      <c r="R772" t="n">
+        <v>11.42081890851234</v>
+      </c>
+      <c r="S772" t="n">
+        <v>1621.4</v>
+      </c>
+      <c r="T772" t="n">
+        <v>1381.919087929993</v>
+      </c>
+      <c r="U772" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V772" t="n">
+        <v>-0.05500705218617763</v>
+      </c>
+      <c r="W772" t="n">
+        <v>-0.07348743525653789</v>
+      </c>
+      <c r="X772" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y772" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z772" t="n">
+        <v>0.5561246275901794</v>
+      </c>
+      <c r="AA772" t="n">
+        <v>12.51355290412903</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr"/>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E773" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F773" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G773" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H773" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I773" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J773" t="n">
+        <v>162</v>
+      </c>
+      <c r="K773" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L773" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M773" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N773" s="2" t="n">
+        <v>45838.47687138714</v>
+      </c>
+      <c r="O773" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="P773" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q773" t="n">
+        <v>4.24059</v>
+      </c>
+      <c r="R773" t="n">
+        <v>9.291159956515484</v>
+      </c>
+      <c r="S773" t="n">
+        <v>6382.8</v>
+      </c>
+      <c r="T773" t="n">
+        <v>1505.167912955509</v>
+      </c>
+      <c r="U773" t="n">
+        <v>8.495174269061048</v>
+      </c>
+      <c r="V773" t="n">
+        <v>0.005102040816326481</v>
+      </c>
+      <c r="W773" t="n">
+        <v>0.0108189484222232</v>
+      </c>
+      <c r="X773" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y773" t="n">
+        <v>10.667</v>
+      </c>
+      <c r="Z773" t="n">
+        <v>0.6009591817855835</v>
+      </c>
+      <c r="AA773" t="n">
+        <v>13.92029732894897</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E774" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F774" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G774" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H774" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I774" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J774" t="n">
+        <v>101</v>
+      </c>
+      <c r="K774" t="n">
+        <v>11</v>
+      </c>
+      <c r="L774" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M774" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N774" s="2" t="n">
+        <v>45838.47687138714</v>
+      </c>
+      <c r="O774" t="n">
+        <v>24126</v>
+      </c>
+      <c r="P774" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q774" t="n">
+        <v>2083.15</v>
+      </c>
+      <c r="R774" t="n">
+        <v>11.58149917192713</v>
+      </c>
+      <c r="S774" t="n">
+        <v>2436726</v>
+      </c>
+      <c r="T774" t="n">
+        <v>1169.73141636464</v>
+      </c>
+      <c r="U774" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V774" t="n">
+        <v>-0.01638943248532287</v>
+      </c>
+      <c r="W774" t="n">
+        <v>-0.02907676462612852</v>
+      </c>
+      <c r="X774" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y774" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z774" t="n">
+        <v>0.4416439533233643</v>
+      </c>
+      <c r="AA774" t="n">
+        <v>9.998224020004272</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E775" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F775" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G775" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H775" t="n">
+        <v>1</v>
+      </c>
+      <c r="I775" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J775" t="n">
+        <v>30</v>
+      </c>
+      <c r="K775" t="n">
+        <v>9</v>
+      </c>
+      <c r="L775" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M775" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N775" s="2" t="n">
+        <v>45838.47687138714</v>
+      </c>
+      <c r="O775" t="n">
+        <v>45.78</v>
+      </c>
+      <c r="P775" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q775" t="n">
+        <v>1</v>
+      </c>
+      <c r="R775" t="n">
+        <v>45.78</v>
+      </c>
+      <c r="S775" t="n">
+        <v>1373.4</v>
+      </c>
+      <c r="T775" t="n">
+        <v>1373.4</v>
+      </c>
+      <c r="U775" t="n">
+        <v>42.174</v>
+      </c>
+      <c r="V775" t="n">
+        <v>0.002189141856392407</v>
+      </c>
+      <c r="W775" t="n">
+        <v>0.002189141856392407</v>
+      </c>
+      <c r="X775" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y775" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z775" t="n">
+        <v>0.56679368019104</v>
+      </c>
+      <c r="AA775" t="n">
+        <v>10.87115383148193</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>MHY271836006</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>GLOBAL SHIP LEA. A DL-,01</t>
+        </is>
+      </c>
+      <c r="E776" s="2" t="n">
+        <v>45838.31344841435</v>
+      </c>
+      <c r="F776" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="G776" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H776" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="I776" t="n">
+        <v>22.64505496285648</v>
+      </c>
+      <c r="J776" t="n">
+        <v>66</v>
+      </c>
+      <c r="K776" t="n">
+        <v>10</v>
+      </c>
+      <c r="L776" t="n">
+        <v>0.5395355224609375</v>
+      </c>
+      <c r="M776" t="n">
+        <v>12.45218944549561</v>
+      </c>
+      <c r="N776" s="2" t="n">
+        <v>45838.47687138714</v>
+      </c>
+      <c r="O776" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="P776" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q776" t="n">
+        <v>1.1732959</v>
+      </c>
+      <c r="R776" t="n">
+        <v>22.6370858365737</v>
+      </c>
+      <c r="S776" t="n">
+        <v>1752.96</v>
+      </c>
+      <c r="T776" t="n">
+        <v>1494.047665213864</v>
+      </c>
+      <c r="U776" t="n">
+        <v>20.38772325405598</v>
+      </c>
+      <c r="V776" t="n">
+        <v>0</v>
+      </c>
+      <c r="W776" t="n">
+        <v>-0.000351914636367745</v>
+      </c>
+      <c r="X776" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y776" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z776" t="n">
+        <v>0.5395355224609375</v>
+      </c>
+      <c r="AA776" t="n">
+        <v>12.45218944549561</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>US74767N1072</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>QSG</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>QSG</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>QUANTASING GRP  ADR/3CL.A</t>
+        </is>
+      </c>
+      <c r="E777" s="2" t="n">
+        <v>45838.31344841435</v>
+      </c>
+      <c r="F777" t="n">
+        <v>8</v>
+      </c>
+      <c r="G777" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H777" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="I777" t="n">
+        <v>6.820799687607375</v>
+      </c>
+      <c r="J777" t="n">
+        <v>214</v>
+      </c>
+      <c r="K777" t="n">
+        <v>9</v>
+      </c>
+      <c r="L777" t="n">
+        <v>0.6086904406547546</v>
+      </c>
+      <c r="M777" t="n">
+        <v>12.26600360870361</v>
+      </c>
+      <c r="N777" s="2" t="n">
+        <v>45838.47687138714</v>
+      </c>
+      <c r="O777" t="n">
+        <v>8</v>
+      </c>
+      <c r="P777" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q777" t="n">
+        <v>1.1732959</v>
+      </c>
+      <c r="R777" t="n">
+        <v>6.818399348365574</v>
+      </c>
+      <c r="S777" t="n">
+        <v>1712</v>
+      </c>
+      <c r="T777" t="n">
+        <v>1459.137460550233</v>
+      </c>
+      <c r="U777" t="n">
+        <v>6.140880498209635</v>
+      </c>
+      <c r="V777" t="n">
+        <v>0</v>
+      </c>
+      <c r="W777" t="n">
+        <v>-0.000351914636367634</v>
+      </c>
+      <c r="X777" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y777" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z777" t="n">
+        <v>0.6086904406547546</v>
+      </c>
+      <c r="AA777" t="n">
         <v>12.26600360870361</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA777"/>
+  <dimension ref="A1:AA785"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72810,7 +72810,7 @@
         <v>100</v>
       </c>
       <c r="N770" s="2" t="n">
-        <v>45838.47687138714</v>
+        <v>45838.47687138889</v>
       </c>
       <c r="O770" t="n">
         <v>1</v>
@@ -72901,7 +72901,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N771" s="2" t="n">
-        <v>45838.47687138714</v>
+        <v>45838.47687138889</v>
       </c>
       <c r="O771" t="n">
         <v>374.4</v>
@@ -72996,7 +72996,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N772" s="2" t="n">
-        <v>45838.47687138714</v>
+        <v>45838.47687138889</v>
       </c>
       <c r="O772" t="n">
         <v>13.4</v>
@@ -73087,7 +73087,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N773" s="2" t="n">
-        <v>45838.47687138714</v>
+        <v>45838.47687138889</v>
       </c>
       <c r="O773" t="n">
         <v>39.4</v>
@@ -73182,7 +73182,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N774" s="2" t="n">
-        <v>45838.47687138714</v>
+        <v>45838.47687138889</v>
       </c>
       <c r="O774" t="n">
         <v>24126</v>
@@ -73277,7 +73277,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N775" s="2" t="n">
-        <v>45838.47687138714</v>
+        <v>45838.47687138889</v>
       </c>
       <c r="O775" t="n">
         <v>45.78</v>
@@ -73372,7 +73372,7 @@
         <v>12.45218944549561</v>
       </c>
       <c r="N776" s="2" t="n">
-        <v>45838.47687138714</v>
+        <v>45838.47687138889</v>
       </c>
       <c r="O776" t="n">
         <v>26.56</v>
@@ -73467,7 +73467,7 @@
         <v>12.26600360870361</v>
       </c>
       <c r="N777" s="2" t="n">
-        <v>45838.47687138714</v>
+        <v>45838.47687138889</v>
       </c>
       <c r="O777" t="n">
         <v>8</v>
@@ -73508,6 +73508,760 @@
         <v>0.6086904406547546</v>
       </c>
       <c r="AA777" t="n">
+        <v>12.26600360870361</v>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E778" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F778" t="n">
+        <v>1</v>
+      </c>
+      <c r="G778" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H778" t="n">
+        <v>1</v>
+      </c>
+      <c r="I778" t="n">
+        <v>1</v>
+      </c>
+      <c r="J778" t="n">
+        <v>1</v>
+      </c>
+      <c r="K778" t="n">
+        <v>100</v>
+      </c>
+      <c r="L778" t="n">
+        <v>100</v>
+      </c>
+      <c r="M778" t="n">
+        <v>100</v>
+      </c>
+      <c r="N778" s="2" t="n">
+        <v>45838.54183967479</v>
+      </c>
+      <c r="O778" t="n">
+        <v>1</v>
+      </c>
+      <c r="P778" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q778" t="n">
+        <v>1</v>
+      </c>
+      <c r="R778" t="n">
+        <v>1</v>
+      </c>
+      <c r="S778" t="n">
+        <v>0</v>
+      </c>
+      <c r="T778" t="n">
+        <v>6.22133174009582</v>
+      </c>
+      <c r="U778" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V778" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W778" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X778" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y778" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z778" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA778" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr"/>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E779" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F779" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G779" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H779" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I779" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J779" t="n">
+        <v>3</v>
+      </c>
+      <c r="K779" t="n">
+        <v>10</v>
+      </c>
+      <c r="L779" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M779" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N779" s="2" t="n">
+        <v>45838.54183967479</v>
+      </c>
+      <c r="O779" t="n">
+        <v>366.5</v>
+      </c>
+      <c r="P779" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q779" t="n">
+        <v>0.85539</v>
+      </c>
+      <c r="R779" t="n">
+        <v>428.4595330784788</v>
+      </c>
+      <c r="S779" t="n">
+        <v>1099.5</v>
+      </c>
+      <c r="T779" t="n">
+        <v>1285.378599235436</v>
+      </c>
+      <c r="U779" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V779" t="n">
+        <v>-0.00317135661170731</v>
+      </c>
+      <c r="W779" t="n">
+        <v>-0.005175758424480259</v>
+      </c>
+      <c r="X779" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y779" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z779" t="n">
+        <v>0.5365895628929138</v>
+      </c>
+      <c r="AA779" t="n">
+        <v>11.5371036529541</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E780" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F780" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G780" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H780" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I780" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J780" t="n">
+        <v>121</v>
+      </c>
+      <c r="K780" t="n">
+        <v>12</v>
+      </c>
+      <c r="L780" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M780" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N780" s="2" t="n">
+        <v>45838.54183967479</v>
+      </c>
+      <c r="O780" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="P780" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q780" t="n">
+        <v>1.1716461</v>
+      </c>
+      <c r="R780" t="n">
+        <v>11.43690061358972</v>
+      </c>
+      <c r="S780" t="n">
+        <v>1621.4</v>
+      </c>
+      <c r="T780" t="n">
+        <v>1383.864974244356</v>
+      </c>
+      <c r="U780" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V780" t="n">
+        <v>-0.05500705218617763</v>
+      </c>
+      <c r="W780" t="n">
+        <v>-0.0721828088601254</v>
+      </c>
+      <c r="X780" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y780" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z780" t="n">
+        <v>0.5561246275901794</v>
+      </c>
+      <c r="AA780" t="n">
+        <v>12.51355290412903</v>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr"/>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E781" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F781" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G781" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H781" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I781" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J781" t="n">
+        <v>162</v>
+      </c>
+      <c r="K781" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L781" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M781" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N781" s="2" t="n">
+        <v>45838.54183967479</v>
+      </c>
+      <c r="O781" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="P781" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q781" t="n">
+        <v>4.24043</v>
+      </c>
+      <c r="R781" t="n">
+        <v>9.291510530771644</v>
+      </c>
+      <c r="S781" t="n">
+        <v>6382.8</v>
+      </c>
+      <c r="T781" t="n">
+        <v>1505.224705985006</v>
+      </c>
+      <c r="U781" t="n">
+        <v>8.495174269061048</v>
+      </c>
+      <c r="V781" t="n">
+        <v>0.005102040816326481</v>
+      </c>
+      <c r="W781" t="n">
+        <v>0.01085708866548818</v>
+      </c>
+      <c r="X781" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y781" t="n">
+        <v>10.667</v>
+      </c>
+      <c r="Z781" t="n">
+        <v>0.6009591817855835</v>
+      </c>
+      <c r="AA781" t="n">
+        <v>13.92029732894897</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E782" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F782" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G782" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H782" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I782" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J782" t="n">
+        <v>101</v>
+      </c>
+      <c r="K782" t="n">
+        <v>11</v>
+      </c>
+      <c r="L782" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M782" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N782" s="2" t="n">
+        <v>45838.54183967479</v>
+      </c>
+      <c r="O782" t="n">
+        <v>24249</v>
+      </c>
+      <c r="P782" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q782" t="n">
+        <v>2082.35</v>
+      </c>
+      <c r="R782" t="n">
+        <v>11.64501644776334</v>
+      </c>
+      <c r="S782" t="n">
+        <v>2449149</v>
+      </c>
+      <c r="T782" t="n">
+        <v>1176.146661224098</v>
+      </c>
+      <c r="U782" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V782" t="n">
+        <v>-0.01137475538160471</v>
+      </c>
+      <c r="W782" t="n">
+        <v>-0.02375185823520831</v>
+      </c>
+      <c r="X782" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y782" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z782" t="n">
+        <v>0.4416439533233643</v>
+      </c>
+      <c r="AA782" t="n">
+        <v>9.998224020004272</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E783" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F783" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G783" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H783" t="n">
+        <v>1</v>
+      </c>
+      <c r="I783" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J783" t="n">
+        <v>30</v>
+      </c>
+      <c r="K783" t="n">
+        <v>9</v>
+      </c>
+      <c r="L783" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M783" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N783" s="2" t="n">
+        <v>45838.54183967479</v>
+      </c>
+      <c r="O783" t="n">
+        <v>45.66</v>
+      </c>
+      <c r="P783" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q783" t="n">
+        <v>1</v>
+      </c>
+      <c r="R783" t="n">
+        <v>45.66</v>
+      </c>
+      <c r="S783" t="n">
+        <v>1369.8</v>
+      </c>
+      <c r="T783" t="n">
+        <v>1369.8</v>
+      </c>
+      <c r="U783" t="n">
+        <v>42.174</v>
+      </c>
+      <c r="V783" t="n">
+        <v>-0.0004378283712784814</v>
+      </c>
+      <c r="W783" t="n">
+        <v>-0.0004378283712784814</v>
+      </c>
+      <c r="X783" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y783" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z783" t="n">
+        <v>0.56679368019104</v>
+      </c>
+      <c r="AA783" t="n">
+        <v>10.87115383148193</v>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>MHY271836006</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>GLOBAL SHIP LEA. A DL-,01</t>
+        </is>
+      </c>
+      <c r="E784" s="2" t="n">
+        <v>45838.31344841435</v>
+      </c>
+      <c r="F784" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="G784" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H784" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="I784" t="n">
+        <v>22.64505496285648</v>
+      </c>
+      <c r="J784" t="n">
+        <v>66</v>
+      </c>
+      <c r="K784" t="n">
+        <v>10</v>
+      </c>
+      <c r="L784" t="n">
+        <v>0.5395355224609375</v>
+      </c>
+      <c r="M784" t="n">
+        <v>12.45218944549561</v>
+      </c>
+      <c r="N784" s="2" t="n">
+        <v>45838.54183967479</v>
+      </c>
+      <c r="O784" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="P784" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q784" t="n">
+        <v>1.1716461</v>
+      </c>
+      <c r="R784" t="n">
+        <v>22.66896121618977</v>
+      </c>
+      <c r="S784" t="n">
+        <v>1752.96</v>
+      </c>
+      <c r="T784" t="n">
+        <v>1496.151440268525</v>
+      </c>
+      <c r="U784" t="n">
+        <v>20.40206509457079</v>
+      </c>
+      <c r="V784" t="n">
+        <v>0</v>
+      </c>
+      <c r="W784" t="n">
+        <v>0.001055694206637758</v>
+      </c>
+      <c r="X784" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y784" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z784" t="n">
+        <v>0.5395355224609375</v>
+      </c>
+      <c r="AA784" t="n">
+        <v>12.45218944549561</v>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>US74767N1072</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>QSG</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>QSG</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>QUANTASING GRP  ADR/3CL.A</t>
+        </is>
+      </c>
+      <c r="E785" s="2" t="n">
+        <v>45838.31344841435</v>
+      </c>
+      <c r="F785" t="n">
+        <v>8</v>
+      </c>
+      <c r="G785" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H785" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="I785" t="n">
+        <v>6.820799687607375</v>
+      </c>
+      <c r="J785" t="n">
+        <v>214</v>
+      </c>
+      <c r="K785" t="n">
+        <v>9</v>
+      </c>
+      <c r="L785" t="n">
+        <v>0.6086904406547546</v>
+      </c>
+      <c r="M785" t="n">
+        <v>12.26600360870361</v>
+      </c>
+      <c r="N785" s="2" t="n">
+        <v>45838.54183967479</v>
+      </c>
+      <c r="O785" t="n">
+        <v>8</v>
+      </c>
+      <c r="P785" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q785" t="n">
+        <v>1.1716461</v>
+      </c>
+      <c r="R785" t="n">
+        <v>6.828000366322219</v>
+      </c>
+      <c r="S785" t="n">
+        <v>1712</v>
+      </c>
+      <c r="T785" t="n">
+        <v>1461.192078392955</v>
+      </c>
+      <c r="U785" t="n">
+        <v>6.145200329689997</v>
+      </c>
+      <c r="V785" t="n">
+        <v>0</v>
+      </c>
+      <c r="W785" t="n">
+        <v>0.001055694206637758</v>
+      </c>
+      <c r="X785" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y785" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z785" t="n">
+        <v>0.6086904406547546</v>
+      </c>
+      <c r="AA785" t="n">
         <v>12.26600360870361</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA785"/>
+  <dimension ref="A1:AA793"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73564,7 +73564,7 @@
         <v>100</v>
       </c>
       <c r="N778" s="2" t="n">
-        <v>45838.54183967479</v>
+        <v>45838.54183967593</v>
       </c>
       <c r="O778" t="n">
         <v>1</v>
@@ -73655,7 +73655,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N779" s="2" t="n">
-        <v>45838.54183967479</v>
+        <v>45838.54183967593</v>
       </c>
       <c r="O779" t="n">
         <v>366.5</v>
@@ -73750,7 +73750,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N780" s="2" t="n">
-        <v>45838.54183967479</v>
+        <v>45838.54183967593</v>
       </c>
       <c r="O780" t="n">
         <v>13.4</v>
@@ -73841,7 +73841,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N781" s="2" t="n">
-        <v>45838.54183967479</v>
+        <v>45838.54183967593</v>
       </c>
       <c r="O781" t="n">
         <v>39.4</v>
@@ -73936,7 +73936,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N782" s="2" t="n">
-        <v>45838.54183967479</v>
+        <v>45838.54183967593</v>
       </c>
       <c r="O782" t="n">
         <v>24249</v>
@@ -74031,7 +74031,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N783" s="2" t="n">
-        <v>45838.54183967479</v>
+        <v>45838.54183967593</v>
       </c>
       <c r="O783" t="n">
         <v>45.66</v>
@@ -74126,7 +74126,7 @@
         <v>12.45218944549561</v>
       </c>
       <c r="N784" s="2" t="n">
-        <v>45838.54183967479</v>
+        <v>45838.54183967593</v>
       </c>
       <c r="O784" t="n">
         <v>26.56</v>
@@ -74221,7 +74221,7 @@
         <v>12.26600360870361</v>
       </c>
       <c r="N785" s="2" t="n">
-        <v>45838.54183967479</v>
+        <v>45838.54183967593</v>
       </c>
       <c r="O785" t="n">
         <v>8</v>
@@ -74262,6 +74262,760 @@
         <v>0.6086904406547546</v>
       </c>
       <c r="AA785" t="n">
+        <v>12.26600360870361</v>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E786" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F786" t="n">
+        <v>1</v>
+      </c>
+      <c r="G786" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H786" t="n">
+        <v>1</v>
+      </c>
+      <c r="I786" t="n">
+        <v>1</v>
+      </c>
+      <c r="J786" t="n">
+        <v>1</v>
+      </c>
+      <c r="K786" t="n">
+        <v>100</v>
+      </c>
+      <c r="L786" t="n">
+        <v>100</v>
+      </c>
+      <c r="M786" t="n">
+        <v>100</v>
+      </c>
+      <c r="N786" s="2" t="n">
+        <v>45838.5717768878</v>
+      </c>
+      <c r="O786" t="n">
+        <v>1</v>
+      </c>
+      <c r="P786" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q786" t="n">
+        <v>1</v>
+      </c>
+      <c r="R786" t="n">
+        <v>1</v>
+      </c>
+      <c r="S786" t="n">
+        <v>0</v>
+      </c>
+      <c r="T786" t="n">
+        <v>6.22133174009582</v>
+      </c>
+      <c r="U786" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V786" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W786" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X786" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y786" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z786" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA786" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr"/>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E787" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F787" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G787" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H787" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I787" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J787" t="n">
+        <v>3</v>
+      </c>
+      <c r="K787" t="n">
+        <v>10</v>
+      </c>
+      <c r="L787" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M787" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N787" s="2" t="n">
+        <v>45838.5717768878</v>
+      </c>
+      <c r="O787" t="n">
+        <v>372.845</v>
+      </c>
+      <c r="P787" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q787" t="n">
+        <v>0.85623</v>
+      </c>
+      <c r="R787" t="n">
+        <v>435.4495871436413</v>
+      </c>
+      <c r="S787" t="n">
+        <v>1118.535</v>
+      </c>
+      <c r="T787" t="n">
+        <v>1306.348761430924</v>
+      </c>
+      <c r="U787" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V787" t="n">
+        <v>0.01408615428133153</v>
+      </c>
+      <c r="W787" t="n">
+        <v>0.01105418792303969</v>
+      </c>
+      <c r="X787" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y787" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z787" t="n">
+        <v>0.5365895628929138</v>
+      </c>
+      <c r="AA787" t="n">
+        <v>11.5371036529541</v>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E788" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F788" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G788" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H788" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I788" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J788" t="n">
+        <v>121</v>
+      </c>
+      <c r="K788" t="n">
+        <v>12</v>
+      </c>
+      <c r="L788" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M788" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N788" s="2" t="n">
+        <v>45838.5717768878</v>
+      </c>
+      <c r="O788" t="n">
+        <v>13.625</v>
+      </c>
+      <c r="P788" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q788" t="n">
+        <v>1.1721956</v>
+      </c>
+      <c r="R788" t="n">
+        <v>11.62348672866542</v>
+      </c>
+      <c r="S788" t="n">
+        <v>1648.625</v>
+      </c>
+      <c r="T788" t="n">
+        <v>1406.441894168516</v>
+      </c>
+      <c r="U788" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V788" t="n">
+        <v>-0.03913963328631875</v>
+      </c>
+      <c r="W788" t="n">
+        <v>-0.0570460326438893</v>
+      </c>
+      <c r="X788" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y788" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z788" t="n">
+        <v>0.5561246275901794</v>
+      </c>
+      <c r="AA788" t="n">
+        <v>12.51355290412903</v>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr"/>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E789" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F789" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G789" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H789" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I789" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J789" t="n">
+        <v>162</v>
+      </c>
+      <c r="K789" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L789" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M789" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N789" s="2" t="n">
+        <v>45838.5717768878</v>
+      </c>
+      <c r="O789" t="n">
+        <v>39.45</v>
+      </c>
+      <c r="P789" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q789" t="n">
+        <v>4.23987</v>
+      </c>
+      <c r="R789" t="n">
+        <v>9.304530563437087</v>
+      </c>
+      <c r="S789" t="n">
+        <v>6390.900000000001</v>
+      </c>
+      <c r="T789" t="n">
+        <v>1507.333951276808</v>
+      </c>
+      <c r="U789" t="n">
+        <v>8.495174269061048</v>
+      </c>
+      <c r="V789" t="n">
+        <v>0.006377551020408267</v>
+      </c>
+      <c r="W789" t="n">
+        <v>0.0122735851835658</v>
+      </c>
+      <c r="X789" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y789" t="n">
+        <v>10.667</v>
+      </c>
+      <c r="Z789" t="n">
+        <v>0.6009591817855835</v>
+      </c>
+      <c r="AA789" t="n">
+        <v>13.92029732894897</v>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E790" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F790" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G790" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H790" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I790" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J790" t="n">
+        <v>101</v>
+      </c>
+      <c r="K790" t="n">
+        <v>11</v>
+      </c>
+      <c r="L790" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M790" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N790" s="2" t="n">
+        <v>45838.5717768878</v>
+      </c>
+      <c r="O790" t="n">
+        <v>24136</v>
+      </c>
+      <c r="P790" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q790" t="n">
+        <v>2083.29</v>
+      </c>
+      <c r="R790" t="n">
+        <v>11.58552097883636</v>
+      </c>
+      <c r="S790" t="n">
+        <v>2437736</v>
+      </c>
+      <c r="T790" t="n">
+        <v>1170.137618862472</v>
+      </c>
+      <c r="U790" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V790" t="n">
+        <v>-0.01598173515981738</v>
+      </c>
+      <c r="W790" t="n">
+        <v>-0.02873960052341684</v>
+      </c>
+      <c r="X790" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y790" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z790" t="n">
+        <v>0.4416439533233643</v>
+      </c>
+      <c r="AA790" t="n">
+        <v>9.998224020004272</v>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E791" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F791" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G791" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H791" t="n">
+        <v>1</v>
+      </c>
+      <c r="I791" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J791" t="n">
+        <v>30</v>
+      </c>
+      <c r="K791" t="n">
+        <v>9</v>
+      </c>
+      <c r="L791" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M791" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N791" s="2" t="n">
+        <v>45838.5717768878</v>
+      </c>
+      <c r="O791" t="n">
+        <v>45.56</v>
+      </c>
+      <c r="P791" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q791" t="n">
+        <v>1</v>
+      </c>
+      <c r="R791" t="n">
+        <v>45.56</v>
+      </c>
+      <c r="S791" t="n">
+        <v>1366.8</v>
+      </c>
+      <c r="T791" t="n">
+        <v>1366.8</v>
+      </c>
+      <c r="U791" t="n">
+        <v>42.174</v>
+      </c>
+      <c r="V791" t="n">
+        <v>-0.002626970227670666</v>
+      </c>
+      <c r="W791" t="n">
+        <v>-0.002626970227670666</v>
+      </c>
+      <c r="X791" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y791" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z791" t="n">
+        <v>0.56679368019104</v>
+      </c>
+      <c r="AA791" t="n">
+        <v>10.87115383148193</v>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>MHY271836006</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>GLOBAL SHIP LEA. A DL-,01</t>
+        </is>
+      </c>
+      <c r="E792" s="2" t="n">
+        <v>45838.31344841435</v>
+      </c>
+      <c r="F792" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="G792" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H792" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="I792" t="n">
+        <v>22.64505496285648</v>
+      </c>
+      <c r="J792" t="n">
+        <v>66</v>
+      </c>
+      <c r="K792" t="n">
+        <v>10</v>
+      </c>
+      <c r="L792" t="n">
+        <v>0.5395355224609375</v>
+      </c>
+      <c r="M792" t="n">
+        <v>12.45218944549561</v>
+      </c>
+      <c r="N792" s="2" t="n">
+        <v>45838.5717768878</v>
+      </c>
+      <c r="O792" t="n">
+        <v>26.48</v>
+      </c>
+      <c r="P792" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q792" t="n">
+        <v>1.1721956</v>
+      </c>
+      <c r="R792" t="n">
+        <v>22.59008650092186</v>
+      </c>
+      <c r="S792" t="n">
+        <v>1747.68</v>
+      </c>
+      <c r="T792" t="n">
+        <v>1490.945709060843</v>
+      </c>
+      <c r="U792" t="n">
+        <v>20.40206509457079</v>
+      </c>
+      <c r="V792" t="n">
+        <v>-0.003012048192771011</v>
+      </c>
+      <c r="W792" t="n">
+        <v>-0.002427393619701346</v>
+      </c>
+      <c r="X792" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y792" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z792" t="n">
+        <v>0.5395355224609375</v>
+      </c>
+      <c r="AA792" t="n">
+        <v>12.45218944549561</v>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>US74767N1072</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>QSG</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>QSG</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>QUANTASING GRP  ADR/3CL.A</t>
+        </is>
+      </c>
+      <c r="E793" s="2" t="n">
+        <v>45838.31344841435</v>
+      </c>
+      <c r="F793" t="n">
+        <v>8</v>
+      </c>
+      <c r="G793" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H793" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="I793" t="n">
+        <v>6.820799687607375</v>
+      </c>
+      <c r="J793" t="n">
+        <v>214</v>
+      </c>
+      <c r="K793" t="n">
+        <v>9</v>
+      </c>
+      <c r="L793" t="n">
+        <v>0.6086904406547546</v>
+      </c>
+      <c r="M793" t="n">
+        <v>12.26600360870361</v>
+      </c>
+      <c r="N793" s="2" t="n">
+        <v>45838.5717768878</v>
+      </c>
+      <c r="O793" t="n">
+        <v>8.74</v>
+      </c>
+      <c r="P793" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q793" t="n">
+        <v>1.1721956</v>
+      </c>
+      <c r="R793" t="n">
+        <v>7.456093505213635</v>
+      </c>
+      <c r="S793" t="n">
+        <v>1870.36</v>
+      </c>
+      <c r="T793" t="n">
+        <v>1595.604010115718</v>
+      </c>
+      <c r="U793" t="n">
+        <v>6.710484154692272</v>
+      </c>
+      <c r="V793" t="n">
+        <v>0.09250000000000003</v>
+      </c>
+      <c r="W793" t="n">
+        <v>0.0931406648344355</v>
+      </c>
+      <c r="X793" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y793" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z793" t="n">
+        <v>0.6086904406547546</v>
+      </c>
+      <c r="AA793" t="n">
         <v>12.26600360870361</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA793"/>
+  <dimension ref="A1:AA801"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74318,7 +74318,7 @@
         <v>100</v>
       </c>
       <c r="N786" s="2" t="n">
-        <v>45838.5717768878</v>
+        <v>45838.57177688657</v>
       </c>
       <c r="O786" t="n">
         <v>1</v>
@@ -74409,7 +74409,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N787" s="2" t="n">
-        <v>45838.5717768878</v>
+        <v>45838.57177688657</v>
       </c>
       <c r="O787" t="n">
         <v>372.845</v>
@@ -74504,7 +74504,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N788" s="2" t="n">
-        <v>45838.5717768878</v>
+        <v>45838.57177688657</v>
       </c>
       <c r="O788" t="n">
         <v>13.625</v>
@@ -74595,7 +74595,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N789" s="2" t="n">
-        <v>45838.5717768878</v>
+        <v>45838.57177688657</v>
       </c>
       <c r="O789" t="n">
         <v>39.45</v>
@@ -74690,7 +74690,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N790" s="2" t="n">
-        <v>45838.5717768878</v>
+        <v>45838.57177688657</v>
       </c>
       <c r="O790" t="n">
         <v>24136</v>
@@ -74785,7 +74785,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N791" s="2" t="n">
-        <v>45838.5717768878</v>
+        <v>45838.57177688657</v>
       </c>
       <c r="O791" t="n">
         <v>45.56</v>
@@ -74880,7 +74880,7 @@
         <v>12.45218944549561</v>
       </c>
       <c r="N792" s="2" t="n">
-        <v>45838.5717768878</v>
+        <v>45838.57177688657</v>
       </c>
       <c r="O792" t="n">
         <v>26.48</v>
@@ -74975,7 +74975,7 @@
         <v>12.26600360870361</v>
       </c>
       <c r="N793" s="2" t="n">
-        <v>45838.5717768878</v>
+        <v>45838.57177688657</v>
       </c>
       <c r="O793" t="n">
         <v>8.74</v>
@@ -75016,6 +75016,760 @@
         <v>0.6086904406547546</v>
       </c>
       <c r="AA793" t="n">
+        <v>12.26600360870361</v>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E794" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F794" t="n">
+        <v>1</v>
+      </c>
+      <c r="G794" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H794" t="n">
+        <v>1</v>
+      </c>
+      <c r="I794" t="n">
+        <v>1</v>
+      </c>
+      <c r="J794" t="n">
+        <v>1</v>
+      </c>
+      <c r="K794" t="n">
+        <v>100</v>
+      </c>
+      <c r="L794" t="n">
+        <v>100</v>
+      </c>
+      <c r="M794" t="n">
+        <v>100</v>
+      </c>
+      <c r="N794" s="2" t="n">
+        <v>45838.60707810448</v>
+      </c>
+      <c r="O794" t="n">
+        <v>1</v>
+      </c>
+      <c r="P794" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q794" t="n">
+        <v>1</v>
+      </c>
+      <c r="R794" t="n">
+        <v>1</v>
+      </c>
+      <c r="S794" t="n">
+        <v>0</v>
+      </c>
+      <c r="T794" t="n">
+        <v>6.22133174009582</v>
+      </c>
+      <c r="U794" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V794" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W794" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X794" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y794" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z794" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA794" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr"/>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E795" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F795" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G795" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H795" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I795" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J795" t="n">
+        <v>3</v>
+      </c>
+      <c r="K795" t="n">
+        <v>10</v>
+      </c>
+      <c r="L795" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M795" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N795" s="2" t="n">
+        <v>45838.60707810448</v>
+      </c>
+      <c r="O795" t="n">
+        <v>365.126</v>
+      </c>
+      <c r="P795" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q795" t="n">
+        <v>0.85658</v>
+      </c>
+      <c r="R795" t="n">
+        <v>426.2602442270424</v>
+      </c>
+      <c r="S795" t="n">
+        <v>1095.378</v>
+      </c>
+      <c r="T795" t="n">
+        <v>1278.780732681127</v>
+      </c>
+      <c r="U795" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V795" t="n">
+        <v>-0.006908444076961229</v>
+      </c>
+      <c r="W795" t="n">
+        <v>-0.01028220534588653</v>
+      </c>
+      <c r="X795" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y795" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z795" t="n">
+        <v>0.5365895628929138</v>
+      </c>
+      <c r="AA795" t="n">
+        <v>11.5371036529541</v>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E796" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F796" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G796" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H796" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I796" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J796" t="n">
+        <v>121</v>
+      </c>
+      <c r="K796" t="n">
+        <v>12</v>
+      </c>
+      <c r="L796" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M796" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N796" s="2" t="n">
+        <v>45838.60707810448</v>
+      </c>
+      <c r="O796" t="n">
+        <v>13.805</v>
+      </c>
+      <c r="P796" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q796" t="n">
+        <v>1.1739845</v>
+      </c>
+      <c r="R796" t="n">
+        <v>11.75909903410139</v>
+      </c>
+      <c r="S796" t="n">
+        <v>1670.405</v>
+      </c>
+      <c r="T796" t="n">
+        <v>1422.850983126268</v>
+      </c>
+      <c r="U796" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V796" t="n">
+        <v>-0.02644569816643161</v>
+      </c>
+      <c r="W796" t="n">
+        <v>-0.04604450062357135</v>
+      </c>
+      <c r="X796" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y796" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z796" t="n">
+        <v>0.5561246275901794</v>
+      </c>
+      <c r="AA796" t="n">
+        <v>12.51355290412903</v>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr"/>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E797" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F797" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G797" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H797" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I797" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J797" t="n">
+        <v>162</v>
+      </c>
+      <c r="K797" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L797" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M797" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N797" s="2" t="n">
+        <v>45838.60707810448</v>
+      </c>
+      <c r="O797" t="n">
+        <v>39.35</v>
+      </c>
+      <c r="P797" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q797" t="n">
+        <v>4.24057</v>
+      </c>
+      <c r="R797" t="n">
+        <v>9.279412909113633</v>
+      </c>
+      <c r="S797" t="n">
+        <v>6374.7</v>
+      </c>
+      <c r="T797" t="n">
+        <v>1503.264891276409</v>
+      </c>
+      <c r="U797" t="n">
+        <v>8.495174269061048</v>
+      </c>
+      <c r="V797" t="n">
+        <v>0.003826530612244916</v>
+      </c>
+      <c r="W797" t="n">
+        <v>0.009540944582295818</v>
+      </c>
+      <c r="X797" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y797" t="n">
+        <v>10.667</v>
+      </c>
+      <c r="Z797" t="n">
+        <v>0.6009591817855835</v>
+      </c>
+      <c r="AA797" t="n">
+        <v>13.92029732894897</v>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E798" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F798" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G798" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H798" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I798" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J798" t="n">
+        <v>101</v>
+      </c>
+      <c r="K798" t="n">
+        <v>11</v>
+      </c>
+      <c r="L798" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M798" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N798" s="2" t="n">
+        <v>45838.60707810448</v>
+      </c>
+      <c r="O798" t="n">
+        <v>24377</v>
+      </c>
+      <c r="P798" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q798" t="n">
+        <v>2086.07</v>
+      </c>
+      <c r="R798" t="n">
+        <v>11.68560978298907</v>
+      </c>
+      <c r="S798" t="n">
+        <v>2462077</v>
+      </c>
+      <c r="T798" t="n">
+        <v>1180.246588081895</v>
+      </c>
+      <c r="U798" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V798" t="n">
+        <v>-0.006156229615133735</v>
+      </c>
+      <c r="W798" t="n">
+        <v>-0.02034875715244799</v>
+      </c>
+      <c r="X798" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y798" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z798" t="n">
+        <v>0.4416439533233643</v>
+      </c>
+      <c r="AA798" t="n">
+        <v>9.998224020004272</v>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E799" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F799" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G799" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H799" t="n">
+        <v>1</v>
+      </c>
+      <c r="I799" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J799" t="n">
+        <v>30</v>
+      </c>
+      <c r="K799" t="n">
+        <v>9</v>
+      </c>
+      <c r="L799" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M799" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N799" s="2" t="n">
+        <v>45838.60707810448</v>
+      </c>
+      <c r="O799" t="n">
+        <v>46.02</v>
+      </c>
+      <c r="P799" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q799" t="n">
+        <v>1</v>
+      </c>
+      <c r="R799" t="n">
+        <v>46.02</v>
+      </c>
+      <c r="S799" t="n">
+        <v>1380.6</v>
+      </c>
+      <c r="T799" t="n">
+        <v>1380.6</v>
+      </c>
+      <c r="U799" t="n">
+        <v>42.174</v>
+      </c>
+      <c r="V799" t="n">
+        <v>0.007443082311733962</v>
+      </c>
+      <c r="W799" t="n">
+        <v>0.007443082311733962</v>
+      </c>
+      <c r="X799" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y799" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z799" t="n">
+        <v>0.56679368019104</v>
+      </c>
+      <c r="AA799" t="n">
+        <v>10.87115383148193</v>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>MHY271836006</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>GLOBAL SHIP LEA. A DL-,01</t>
+        </is>
+      </c>
+      <c r="E800" s="2" t="n">
+        <v>45838.31344841435</v>
+      </c>
+      <c r="F800" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="G800" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H800" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="I800" t="n">
+        <v>22.64505496285648</v>
+      </c>
+      <c r="J800" t="n">
+        <v>66</v>
+      </c>
+      <c r="K800" t="n">
+        <v>10</v>
+      </c>
+      <c r="L800" t="n">
+        <v>0.5395355224609375</v>
+      </c>
+      <c r="M800" t="n">
+        <v>12.45218944549561</v>
+      </c>
+      <c r="N800" s="2" t="n">
+        <v>45838.60707810448</v>
+      </c>
+      <c r="O800" t="n">
+        <v>26.36</v>
+      </c>
+      <c r="P800" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q800" t="n">
+        <v>1.1739845</v>
+      </c>
+      <c r="R800" t="n">
+        <v>22.453448065115</v>
+      </c>
+      <c r="S800" t="n">
+        <v>1739.76</v>
+      </c>
+      <c r="T800" t="n">
+        <v>1481.92757229759</v>
+      </c>
+      <c r="U800" t="n">
+        <v>20.40206509457079</v>
+      </c>
+      <c r="V800" t="n">
+        <v>-0.007530120481927693</v>
+      </c>
+      <c r="W800" t="n">
+        <v>-0.008461312991104197</v>
+      </c>
+      <c r="X800" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y800" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z800" t="n">
+        <v>0.5395355224609375</v>
+      </c>
+      <c r="AA800" t="n">
+        <v>12.45218944549561</v>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>US74767N1072</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>QSG</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>QSG</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>QUANTASING GRP  ADR/3CL.A</t>
+        </is>
+      </c>
+      <c r="E801" s="2" t="n">
+        <v>45838.31344841435</v>
+      </c>
+      <c r="F801" t="n">
+        <v>8</v>
+      </c>
+      <c r="G801" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H801" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="I801" t="n">
+        <v>6.820799687607375</v>
+      </c>
+      <c r="J801" t="n">
+        <v>214</v>
+      </c>
+      <c r="K801" t="n">
+        <v>9</v>
+      </c>
+      <c r="L801" t="n">
+        <v>0.6086904406547546</v>
+      </c>
+      <c r="M801" t="n">
+        <v>12.26600360870361</v>
+      </c>
+      <c r="N801" s="2" t="n">
+        <v>45838.60707810448</v>
+      </c>
+      <c r="O801" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="P801" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q801" t="n">
+        <v>1.1739845</v>
+      </c>
+      <c r="R801" t="n">
+        <v>7.572502021960257</v>
+      </c>
+      <c r="S801" t="n">
+        <v>1902.46</v>
+      </c>
+      <c r="T801" t="n">
+        <v>1620.515432699495</v>
+      </c>
+      <c r="U801" t="n">
+        <v>6.815251819764232</v>
+      </c>
+      <c r="V801" t="n">
+        <v>0.1112500000000001</v>
+      </c>
+      <c r="W801" t="n">
+        <v>0.1102073611278513</v>
+      </c>
+      <c r="X801" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y801" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z801" t="n">
+        <v>0.6086904406547546</v>
+      </c>
+      <c r="AA801" t="n">
         <v>12.26600360870361</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA801"/>
+  <dimension ref="A1:AA809"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75072,7 +75072,7 @@
         <v>100</v>
       </c>
       <c r="N794" s="2" t="n">
-        <v>45838.60707810448</v>
+        <v>45838.60707810185</v>
       </c>
       <c r="O794" t="n">
         <v>1</v>
@@ -75163,7 +75163,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N795" s="2" t="n">
-        <v>45838.60707810448</v>
+        <v>45838.60707810185</v>
       </c>
       <c r="O795" t="n">
         <v>365.126</v>
@@ -75258,7 +75258,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N796" s="2" t="n">
-        <v>45838.60707810448</v>
+        <v>45838.60707810185</v>
       </c>
       <c r="O796" t="n">
         <v>13.805</v>
@@ -75349,7 +75349,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N797" s="2" t="n">
-        <v>45838.60707810448</v>
+        <v>45838.60707810185</v>
       </c>
       <c r="O797" t="n">
         <v>39.35</v>
@@ -75444,7 +75444,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N798" s="2" t="n">
-        <v>45838.60707810448</v>
+        <v>45838.60707810185</v>
       </c>
       <c r="O798" t="n">
         <v>24377</v>
@@ -75539,7 +75539,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N799" s="2" t="n">
-        <v>45838.60707810448</v>
+        <v>45838.60707810185</v>
       </c>
       <c r="O799" t="n">
         <v>46.02</v>
@@ -75634,7 +75634,7 @@
         <v>12.45218944549561</v>
       </c>
       <c r="N800" s="2" t="n">
-        <v>45838.60707810448</v>
+        <v>45838.60707810185</v>
       </c>
       <c r="O800" t="n">
         <v>26.36</v>
@@ -75729,7 +75729,7 @@
         <v>12.26600360870361</v>
       </c>
       <c r="N801" s="2" t="n">
-        <v>45838.60707810448</v>
+        <v>45838.60707810185</v>
       </c>
       <c r="O801" t="n">
         <v>8.890000000000001</v>
@@ -75770,6 +75770,760 @@
         <v>0.6086904406547546</v>
       </c>
       <c r="AA801" t="n">
+        <v>12.26600360870361</v>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E802" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F802" t="n">
+        <v>1</v>
+      </c>
+      <c r="G802" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H802" t="n">
+        <v>1</v>
+      </c>
+      <c r="I802" t="n">
+        <v>1</v>
+      </c>
+      <c r="J802" t="n">
+        <v>1</v>
+      </c>
+      <c r="K802" t="n">
+        <v>100</v>
+      </c>
+      <c r="L802" t="n">
+        <v>100</v>
+      </c>
+      <c r="M802" t="n">
+        <v>100</v>
+      </c>
+      <c r="N802" s="2" t="n">
+        <v>45838.64790813495</v>
+      </c>
+      <c r="O802" t="n">
+        <v>1</v>
+      </c>
+      <c r="P802" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q802" t="n">
+        <v>1</v>
+      </c>
+      <c r="R802" t="n">
+        <v>1</v>
+      </c>
+      <c r="S802" t="n">
+        <v>0</v>
+      </c>
+      <c r="T802" t="n">
+        <v>6.22133174009582</v>
+      </c>
+      <c r="U802" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V802" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W802" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X802" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y802" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z802" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA802" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr"/>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E803" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F803" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G803" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H803" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I803" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J803" t="n">
+        <v>3</v>
+      </c>
+      <c r="K803" t="n">
+        <v>10</v>
+      </c>
+      <c r="L803" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M803" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N803" s="2" t="n">
+        <v>45838.64790813495</v>
+      </c>
+      <c r="O803" t="n">
+        <v>366</v>
+      </c>
+      <c r="P803" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q803" t="n">
+        <v>0.85724</v>
+      </c>
+      <c r="R803" t="n">
+        <v>426.9516121506229</v>
+      </c>
+      <c r="S803" t="n">
+        <v>1098</v>
+      </c>
+      <c r="T803" t="n">
+        <v>1280.854836451869</v>
+      </c>
+      <c r="U803" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V803" t="n">
+        <v>-0.004531286548117075</v>
+      </c>
+      <c r="W803" t="n">
+        <v>-0.008676943898477729</v>
+      </c>
+      <c r="X803" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y803" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z803" t="n">
+        <v>0.5365895628929138</v>
+      </c>
+      <c r="AA803" t="n">
+        <v>11.5371036529541</v>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E804" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F804" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G804" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H804" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I804" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J804" t="n">
+        <v>121</v>
+      </c>
+      <c r="K804" t="n">
+        <v>12</v>
+      </c>
+      <c r="L804" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M804" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N804" s="2" t="n">
+        <v>45838.64790813495</v>
+      </c>
+      <c r="O804" t="n">
+        <v>13.845</v>
+      </c>
+      <c r="P804" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q804" t="n">
+        <v>1.1752262</v>
+      </c>
+      <c r="R804" t="n">
+        <v>11.78071081124638</v>
+      </c>
+      <c r="S804" t="n">
+        <v>1675.245</v>
+      </c>
+      <c r="T804" t="n">
+        <v>1425.466008160812</v>
+      </c>
+      <c r="U804" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V804" t="n">
+        <v>-0.02362482369534546</v>
+      </c>
+      <c r="W804" t="n">
+        <v>-0.04429124779365856</v>
+      </c>
+      <c r="X804" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y804" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z804" t="n">
+        <v>0.5561246275901794</v>
+      </c>
+      <c r="AA804" t="n">
+        <v>12.51355290412903</v>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr"/>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E805" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F805" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G805" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H805" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I805" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J805" t="n">
+        <v>162</v>
+      </c>
+      <c r="K805" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L805" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M805" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N805" s="2" t="n">
+        <v>45838.64790813495</v>
+      </c>
+      <c r="O805" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="P805" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q805" t="n">
+        <v>4.2418</v>
+      </c>
+      <c r="R805" t="n">
+        <v>9.217784902635675</v>
+      </c>
+      <c r="S805" t="n">
+        <v>6334.2</v>
+      </c>
+      <c r="T805" t="n">
+        <v>1493.281154226979</v>
+      </c>
+      <c r="U805" t="n">
+        <v>8.495174269061048</v>
+      </c>
+      <c r="V805" t="n">
+        <v>-0.002551020408163351</v>
+      </c>
+      <c r="W805" t="n">
+        <v>0.00283621051324956</v>
+      </c>
+      <c r="X805" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y805" t="n">
+        <v>10.667</v>
+      </c>
+      <c r="Z805" t="n">
+        <v>0.6009591817855835</v>
+      </c>
+      <c r="AA805" t="n">
+        <v>13.92029732894897</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E806" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F806" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G806" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H806" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I806" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J806" t="n">
+        <v>101</v>
+      </c>
+      <c r="K806" t="n">
+        <v>11</v>
+      </c>
+      <c r="L806" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M806" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N806" s="2" t="n">
+        <v>45838.64790813495</v>
+      </c>
+      <c r="O806" t="n">
+        <v>24481</v>
+      </c>
+      <c r="P806" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q806" t="n">
+        <v>2085.44</v>
+      </c>
+      <c r="R806" t="n">
+        <v>11.73900951357987</v>
+      </c>
+      <c r="S806" t="n">
+        <v>2472581</v>
+      </c>
+      <c r="T806" t="n">
+        <v>1185.639960871567</v>
+      </c>
+      <c r="U806" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V806" t="n">
+        <v>-0.001916177429876043</v>
+      </c>
+      <c r="W806" t="n">
+        <v>-0.01587204490443528</v>
+      </c>
+      <c r="X806" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y806" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z806" t="n">
+        <v>0.4416439533233643</v>
+      </c>
+      <c r="AA806" t="n">
+        <v>9.998224020004272</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E807" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F807" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G807" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H807" t="n">
+        <v>1</v>
+      </c>
+      <c r="I807" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J807" t="n">
+        <v>30</v>
+      </c>
+      <c r="K807" t="n">
+        <v>9</v>
+      </c>
+      <c r="L807" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M807" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N807" s="2" t="n">
+        <v>45838.64790813495</v>
+      </c>
+      <c r="O807" t="n">
+        <v>46.02</v>
+      </c>
+      <c r="P807" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q807" t="n">
+        <v>1</v>
+      </c>
+      <c r="R807" t="n">
+        <v>46.02</v>
+      </c>
+      <c r="S807" t="n">
+        <v>1380.6</v>
+      </c>
+      <c r="T807" t="n">
+        <v>1380.6</v>
+      </c>
+      <c r="U807" t="n">
+        <v>42.174</v>
+      </c>
+      <c r="V807" t="n">
+        <v>0.007443082311733962</v>
+      </c>
+      <c r="W807" t="n">
+        <v>0.007443082311733962</v>
+      </c>
+      <c r="X807" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y807" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z807" t="n">
+        <v>0.56679368019104</v>
+      </c>
+      <c r="AA807" t="n">
+        <v>10.87115383148193</v>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>MHY271836006</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>GLOBAL SHIP LEA. A DL-,01</t>
+        </is>
+      </c>
+      <c r="E808" s="2" t="n">
+        <v>45838.31344841435</v>
+      </c>
+      <c r="F808" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="G808" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H808" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="I808" t="n">
+        <v>22.64505496285648</v>
+      </c>
+      <c r="J808" t="n">
+        <v>66</v>
+      </c>
+      <c r="K808" t="n">
+        <v>10</v>
+      </c>
+      <c r="L808" t="n">
+        <v>0.5395355224609375</v>
+      </c>
+      <c r="M808" t="n">
+        <v>12.45218944549561</v>
+      </c>
+      <c r="N808" s="2" t="n">
+        <v>45838.64790813495</v>
+      </c>
+      <c r="O808" t="n">
+        <v>26.27</v>
+      </c>
+      <c r="P808" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q808" t="n">
+        <v>1.1752262</v>
+      </c>
+      <c r="R808" t="n">
+        <v>22.35314359057005</v>
+      </c>
+      <c r="S808" t="n">
+        <v>1733.82</v>
+      </c>
+      <c r="T808" t="n">
+        <v>1475.307476977624</v>
+      </c>
+      <c r="U808" t="n">
+        <v>20.40206509457079</v>
+      </c>
+      <c r="V808" t="n">
+        <v>-0.01091867469879515</v>
+      </c>
+      <c r="W808" t="n">
+        <v>-0.01289073366195126</v>
+      </c>
+      <c r="X808" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y808" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z808" t="n">
+        <v>0.5395355224609375</v>
+      </c>
+      <c r="AA808" t="n">
+        <v>12.45218944549561</v>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>US74767N1072</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>QSG</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>QSG</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>QUANTASING GRP  ADR/3CL.A</t>
+        </is>
+      </c>
+      <c r="E809" s="2" t="n">
+        <v>45838.31344841435</v>
+      </c>
+      <c r="F809" t="n">
+        <v>8</v>
+      </c>
+      <c r="G809" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H809" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="I809" t="n">
+        <v>6.820799687607375</v>
+      </c>
+      <c r="J809" t="n">
+        <v>214</v>
+      </c>
+      <c r="K809" t="n">
+        <v>9</v>
+      </c>
+      <c r="L809" t="n">
+        <v>0.6086904406547546</v>
+      </c>
+      <c r="M809" t="n">
+        <v>12.26600360870361</v>
+      </c>
+      <c r="N809" s="2" t="n">
+        <v>45838.64790813495</v>
+      </c>
+      <c r="O809" t="n">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="P809" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q809" t="n">
+        <v>1.1752262</v>
+      </c>
+      <c r="R809" t="n">
+        <v>7.836789207047971</v>
+      </c>
+      <c r="S809" t="n">
+        <v>1970.94</v>
+      </c>
+      <c r="T809" t="n">
+        <v>1677.072890308266</v>
+      </c>
+      <c r="U809" t="n">
+        <v>7.053110286343174</v>
+      </c>
+      <c r="V809" t="n">
+        <v>0.1512500000000001</v>
+      </c>
+      <c r="W809" t="n">
+        <v>0.1489546044412557</v>
+      </c>
+      <c r="X809" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y809" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z809" t="n">
+        <v>0.6086904406547546</v>
+      </c>
+      <c r="AA809" t="n">
         <v>12.26600360870361</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA809"/>
+  <dimension ref="A1:AA817"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75826,7 +75826,7 @@
         <v>100</v>
       </c>
       <c r="N802" s="2" t="n">
-        <v>45838.64790813495</v>
+        <v>45838.64790813658</v>
       </c>
       <c r="O802" t="n">
         <v>1</v>
@@ -75917,7 +75917,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N803" s="2" t="n">
-        <v>45838.64790813495</v>
+        <v>45838.64790813658</v>
       </c>
       <c r="O803" t="n">
         <v>366</v>
@@ -76012,7 +76012,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N804" s="2" t="n">
-        <v>45838.64790813495</v>
+        <v>45838.64790813658</v>
       </c>
       <c r="O804" t="n">
         <v>13.845</v>
@@ -76103,7 +76103,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N805" s="2" t="n">
-        <v>45838.64790813495</v>
+        <v>45838.64790813658</v>
       </c>
       <c r="O805" t="n">
         <v>39.1</v>
@@ -76198,7 +76198,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N806" s="2" t="n">
-        <v>45838.64790813495</v>
+        <v>45838.64790813658</v>
       </c>
       <c r="O806" t="n">
         <v>24481</v>
@@ -76293,7 +76293,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N807" s="2" t="n">
-        <v>45838.64790813495</v>
+        <v>45838.64790813658</v>
       </c>
       <c r="O807" t="n">
         <v>46.02</v>
@@ -76388,7 +76388,7 @@
         <v>12.45218944549561</v>
       </c>
       <c r="N808" s="2" t="n">
-        <v>45838.64790813495</v>
+        <v>45838.64790813658</v>
       </c>
       <c r="O808" t="n">
         <v>26.27</v>
@@ -76483,7 +76483,7 @@
         <v>12.26600360870361</v>
       </c>
       <c r="N809" s="2" t="n">
-        <v>45838.64790813495</v>
+        <v>45838.64790813658</v>
       </c>
       <c r="O809" t="n">
         <v>9.210000000000001</v>
@@ -76524,6 +76524,760 @@
         <v>0.6086904406547546</v>
       </c>
       <c r="AA809" t="n">
+        <v>12.26600360870361</v>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E810" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F810" t="n">
+        <v>1</v>
+      </c>
+      <c r="G810" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H810" t="n">
+        <v>1</v>
+      </c>
+      <c r="I810" t="n">
+        <v>1</v>
+      </c>
+      <c r="J810" t="n">
+        <v>1</v>
+      </c>
+      <c r="K810" t="n">
+        <v>100</v>
+      </c>
+      <c r="L810" t="n">
+        <v>100</v>
+      </c>
+      <c r="M810" t="n">
+        <v>100</v>
+      </c>
+      <c r="N810" s="2" t="n">
+        <v>45838.69360276566</v>
+      </c>
+      <c r="O810" t="n">
+        <v>1</v>
+      </c>
+      <c r="P810" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q810" t="n">
+        <v>1</v>
+      </c>
+      <c r="R810" t="n">
+        <v>1</v>
+      </c>
+      <c r="S810" t="n">
+        <v>0</v>
+      </c>
+      <c r="T810" t="n">
+        <v>6.22133174009582</v>
+      </c>
+      <c r="U810" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V810" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W810" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X810" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y810" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z810" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA810" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr"/>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E811" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F811" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G811" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H811" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I811" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J811" t="n">
+        <v>3</v>
+      </c>
+      <c r="K811" t="n">
+        <v>10</v>
+      </c>
+      <c r="L811" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M811" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N811" s="2" t="n">
+        <v>45838.69360276566</v>
+      </c>
+      <c r="O811" t="n">
+        <v>372.5</v>
+      </c>
+      <c r="P811" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q811" t="n">
+        <v>0.8577399999999999</v>
+      </c>
+      <c r="R811" t="n">
+        <v>434.2807843868771</v>
+      </c>
+      <c r="S811" t="n">
+        <v>1117.5</v>
+      </c>
+      <c r="T811" t="n">
+        <v>1302.842353160632</v>
+      </c>
+      <c r="U811" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V811" t="n">
+        <v>0.01314780262520876</v>
+      </c>
+      <c r="W811" t="n">
+        <v>0.008340388307717994</v>
+      </c>
+      <c r="X811" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y811" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z811" t="n">
+        <v>0.5365895628929138</v>
+      </c>
+      <c r="AA811" t="n">
+        <v>11.5371036529541</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E812" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F812" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G812" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H812" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I812" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J812" t="n">
+        <v>121</v>
+      </c>
+      <c r="K812" t="n">
+        <v>12</v>
+      </c>
+      <c r="L812" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M812" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N812" s="2" t="n">
+        <v>45838.69360276566</v>
+      </c>
+      <c r="O812" t="n">
+        <v>13.855</v>
+      </c>
+      <c r="P812" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q812" t="n">
+        <v>1.1755025</v>
+      </c>
+      <c r="R812" t="n">
+        <v>11.78644877403494</v>
+      </c>
+      <c r="S812" t="n">
+        <v>1676.455</v>
+      </c>
+      <c r="T812" t="n">
+        <v>1426.160301658227</v>
+      </c>
+      <c r="U812" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V812" t="n">
+        <v>-0.02291960507757396</v>
+      </c>
+      <c r="W812" t="n">
+        <v>-0.04382575625034502</v>
+      </c>
+      <c r="X812" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y812" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z812" t="n">
+        <v>0.5561246275901794</v>
+      </c>
+      <c r="AA812" t="n">
+        <v>12.51355290412903</v>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr"/>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E813" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F813" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G813" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H813" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I813" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J813" t="n">
+        <v>162</v>
+      </c>
+      <c r="K813" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L813" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M813" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N813" s="2" t="n">
+        <v>45838.69360276566</v>
+      </c>
+      <c r="O813" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="P813" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q813" t="n">
+        <v>4.2449</v>
+      </c>
+      <c r="R813" t="n">
+        <v>9.2110532639167</v>
+      </c>
+      <c r="S813" t="n">
+        <v>6334.2</v>
+      </c>
+      <c r="T813" t="n">
+        <v>1492.190628754505</v>
+      </c>
+      <c r="U813" t="n">
+        <v>8.495174269061048</v>
+      </c>
+      <c r="V813" t="n">
+        <v>-0.002551020408163351</v>
+      </c>
+      <c r="W813" t="n">
+        <v>0.002103851151994629</v>
+      </c>
+      <c r="X813" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y813" t="n">
+        <v>10.667</v>
+      </c>
+      <c r="Z813" t="n">
+        <v>0.6009591817855835</v>
+      </c>
+      <c r="AA813" t="n">
+        <v>13.92029732894897</v>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E814" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F814" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G814" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H814" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I814" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J814" t="n">
+        <v>101</v>
+      </c>
+      <c r="K814" t="n">
+        <v>11</v>
+      </c>
+      <c r="L814" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M814" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N814" s="2" t="n">
+        <v>45838.69360276566</v>
+      </c>
+      <c r="O814" t="n">
+        <v>24481</v>
+      </c>
+      <c r="P814" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q814" t="n">
+        <v>2083.91</v>
+      </c>
+      <c r="R814" t="n">
+        <v>11.7476282564986</v>
+      </c>
+      <c r="S814" t="n">
+        <v>2472581</v>
+      </c>
+      <c r="T814" t="n">
+        <v>1186.510453906359</v>
+      </c>
+      <c r="U814" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V814" t="n">
+        <v>-0.001916177429876043</v>
+      </c>
+      <c r="W814" t="n">
+        <v>-0.01514950133427317</v>
+      </c>
+      <c r="X814" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y814" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z814" t="n">
+        <v>0.4416439533233643</v>
+      </c>
+      <c r="AA814" t="n">
+        <v>9.998224020004272</v>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E815" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F815" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G815" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H815" t="n">
+        <v>1</v>
+      </c>
+      <c r="I815" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J815" t="n">
+        <v>30</v>
+      </c>
+      <c r="K815" t="n">
+        <v>9</v>
+      </c>
+      <c r="L815" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M815" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N815" s="2" t="n">
+        <v>45838.69360276566</v>
+      </c>
+      <c r="O815" t="n">
+        <v>46.02</v>
+      </c>
+      <c r="P815" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q815" t="n">
+        <v>1</v>
+      </c>
+      <c r="R815" t="n">
+        <v>46.02</v>
+      </c>
+      <c r="S815" t="n">
+        <v>1380.6</v>
+      </c>
+      <c r="T815" t="n">
+        <v>1380.6</v>
+      </c>
+      <c r="U815" t="n">
+        <v>42.174</v>
+      </c>
+      <c r="V815" t="n">
+        <v>0.007443082311733962</v>
+      </c>
+      <c r="W815" t="n">
+        <v>0.007443082311733962</v>
+      </c>
+      <c r="X815" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y815" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z815" t="n">
+        <v>0.56679368019104</v>
+      </c>
+      <c r="AA815" t="n">
+        <v>10.87115383148193</v>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>MHY271836006</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>GLOBAL SHIP LEA. A DL-,01</t>
+        </is>
+      </c>
+      <c r="E816" s="2" t="n">
+        <v>45838.31344841435</v>
+      </c>
+      <c r="F816" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="G816" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H816" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="I816" t="n">
+        <v>22.64505496285648</v>
+      </c>
+      <c r="J816" t="n">
+        <v>66</v>
+      </c>
+      <c r="K816" t="n">
+        <v>10</v>
+      </c>
+      <c r="L816" t="n">
+        <v>0.5395355224609375</v>
+      </c>
+      <c r="M816" t="n">
+        <v>12.45218944549561</v>
+      </c>
+      <c r="N816" s="2" t="n">
+        <v>45838.69360276566</v>
+      </c>
+      <c r="O816" t="n">
+        <v>26.07</v>
+      </c>
+      <c r="P816" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q816" t="n">
+        <v>1.1755025</v>
+      </c>
+      <c r="R816" t="n">
+        <v>22.17774951563268</v>
+      </c>
+      <c r="S816" t="n">
+        <v>1720.62</v>
+      </c>
+      <c r="T816" t="n">
+        <v>1463.731468031757</v>
+      </c>
+      <c r="U816" t="n">
+        <v>20.40206509457079</v>
+      </c>
+      <c r="V816" t="n">
+        <v>-0.01844879518072284</v>
+      </c>
+      <c r="W816" t="n">
+        <v>-0.02063609242681463</v>
+      </c>
+      <c r="X816" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y816" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z816" t="n">
+        <v>0.5395355224609375</v>
+      </c>
+      <c r="AA816" t="n">
+        <v>12.45218944549561</v>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>US74767N1072</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>QSG</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>QSG</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>QUANTASING GRP  ADR/3CL.A</t>
+        </is>
+      </c>
+      <c r="E817" s="2" t="n">
+        <v>45838.31344841435</v>
+      </c>
+      <c r="F817" t="n">
+        <v>8</v>
+      </c>
+      <c r="G817" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H817" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="I817" t="n">
+        <v>6.820799687607375</v>
+      </c>
+      <c r="J817" t="n">
+        <v>214</v>
+      </c>
+      <c r="K817" t="n">
+        <v>9</v>
+      </c>
+      <c r="L817" t="n">
+        <v>0.6086904406547546</v>
+      </c>
+      <c r="M817" t="n">
+        <v>12.26600360870361</v>
+      </c>
+      <c r="N817" s="2" t="n">
+        <v>45838.69360276566</v>
+      </c>
+      <c r="O817" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="P817" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q817" t="n">
+        <v>1.1755025</v>
+      </c>
+      <c r="R817" t="n">
+        <v>7.792412181173584</v>
+      </c>
+      <c r="S817" t="n">
+        <v>1960.24</v>
+      </c>
+      <c r="T817" t="n">
+        <v>1667.576206771147</v>
+      </c>
+      <c r="U817" t="n">
+        <v>7.053110286343174</v>
+      </c>
+      <c r="V817" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="W817" t="n">
+        <v>0.142448472036427</v>
+      </c>
+      <c r="X817" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y817" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z817" t="n">
+        <v>0.6086904406547546</v>
+      </c>
+      <c r="AA817" t="n">
         <v>12.26600360870361</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA817"/>
+  <dimension ref="A1:AA825"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76580,7 +76580,7 @@
         <v>100</v>
       </c>
       <c r="N810" s="2" t="n">
-        <v>45838.69360276566</v>
+        <v>45838.6936027662</v>
       </c>
       <c r="O810" t="n">
         <v>1</v>
@@ -76671,7 +76671,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N811" s="2" t="n">
-        <v>45838.69360276566</v>
+        <v>45838.6936027662</v>
       </c>
       <c r="O811" t="n">
         <v>372.5</v>
@@ -76766,7 +76766,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N812" s="2" t="n">
-        <v>45838.69360276566</v>
+        <v>45838.6936027662</v>
       </c>
       <c r="O812" t="n">
         <v>13.855</v>
@@ -76857,7 +76857,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N813" s="2" t="n">
-        <v>45838.69360276566</v>
+        <v>45838.6936027662</v>
       </c>
       <c r="O813" t="n">
         <v>39.1</v>
@@ -76952,7 +76952,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N814" s="2" t="n">
-        <v>45838.69360276566</v>
+        <v>45838.6936027662</v>
       </c>
       <c r="O814" t="n">
         <v>24481</v>
@@ -77047,7 +77047,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N815" s="2" t="n">
-        <v>45838.69360276566</v>
+        <v>45838.6936027662</v>
       </c>
       <c r="O815" t="n">
         <v>46.02</v>
@@ -77142,7 +77142,7 @@
         <v>12.45218944549561</v>
       </c>
       <c r="N816" s="2" t="n">
-        <v>45838.69360276566</v>
+        <v>45838.6936027662</v>
       </c>
       <c r="O816" t="n">
         <v>26.07</v>
@@ -77237,7 +77237,7 @@
         <v>12.26600360870361</v>
       </c>
       <c r="N817" s="2" t="n">
-        <v>45838.69360276566</v>
+        <v>45838.6936027662</v>
       </c>
       <c r="O817" t="n">
         <v>9.16</v>
@@ -77278,6 +77278,760 @@
         <v>0.6086904406547546</v>
       </c>
       <c r="AA817" t="n">
+        <v>12.26600360870361</v>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E818" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F818" t="n">
+        <v>1</v>
+      </c>
+      <c r="G818" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H818" t="n">
+        <v>1</v>
+      </c>
+      <c r="I818" t="n">
+        <v>1</v>
+      </c>
+      <c r="J818" t="n">
+        <v>1</v>
+      </c>
+      <c r="K818" t="n">
+        <v>100</v>
+      </c>
+      <c r="L818" t="n">
+        <v>100</v>
+      </c>
+      <c r="M818" t="n">
+        <v>100</v>
+      </c>
+      <c r="N818" s="2" t="n">
+        <v>45838.72979800656</v>
+      </c>
+      <c r="O818" t="n">
+        <v>1</v>
+      </c>
+      <c r="P818" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q818" t="n">
+        <v>1</v>
+      </c>
+      <c r="R818" t="n">
+        <v>1</v>
+      </c>
+      <c r="S818" t="n">
+        <v>0</v>
+      </c>
+      <c r="T818" t="n">
+        <v>6.22133174009582</v>
+      </c>
+      <c r="U818" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V818" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W818" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X818" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y818" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z818" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA818" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr"/>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E819" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F819" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G819" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H819" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I819" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J819" t="n">
+        <v>3</v>
+      </c>
+      <c r="K819" t="n">
+        <v>10</v>
+      </c>
+      <c r="L819" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M819" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N819" s="2" t="n">
+        <v>45838.72979800656</v>
+      </c>
+      <c r="O819" t="n">
+        <v>372.5</v>
+      </c>
+      <c r="P819" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q819" t="n">
+        <v>0.85807</v>
+      </c>
+      <c r="R819" t="n">
+        <v>434.113766942091</v>
+      </c>
+      <c r="S819" t="n">
+        <v>1117.5</v>
+      </c>
+      <c r="T819" t="n">
+        <v>1302.341300826273</v>
+      </c>
+      <c r="U819" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V819" t="n">
+        <v>0.01314780262520876</v>
+      </c>
+      <c r="W819" t="n">
+        <v>0.007952596719454252</v>
+      </c>
+      <c r="X819" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y819" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z819" t="n">
+        <v>0.5365895628929138</v>
+      </c>
+      <c r="AA819" t="n">
+        <v>11.5371036529541</v>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E820" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F820" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G820" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H820" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I820" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J820" t="n">
+        <v>121</v>
+      </c>
+      <c r="K820" t="n">
+        <v>12</v>
+      </c>
+      <c r="L820" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M820" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N820" s="2" t="n">
+        <v>45838.72979800656</v>
+      </c>
+      <c r="O820" t="n">
+        <v>13.865</v>
+      </c>
+      <c r="P820" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q820" t="n">
+        <v>1.177163</v>
+      </c>
+      <c r="R820" t="n">
+        <v>11.77831787101701</v>
+      </c>
+      <c r="S820" t="n">
+        <v>1677.665</v>
+      </c>
+      <c r="T820" t="n">
+        <v>1425.176462393059</v>
+      </c>
+      <c r="U820" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V820" t="n">
+        <v>-0.02221438645980245</v>
+      </c>
+      <c r="W820" t="n">
+        <v>-0.04448537478288306</v>
+      </c>
+      <c r="X820" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y820" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z820" t="n">
+        <v>0.5561246275901794</v>
+      </c>
+      <c r="AA820" t="n">
+        <v>12.51355290412903</v>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr"/>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E821" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F821" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G821" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H821" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I821" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J821" t="n">
+        <v>162</v>
+      </c>
+      <c r="K821" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L821" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M821" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N821" s="2" t="n">
+        <v>45838.72979800656</v>
+      </c>
+      <c r="O821" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="P821" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q821" t="n">
+        <v>4.24557</v>
+      </c>
+      <c r="R821" t="n">
+        <v>9.209599653285661</v>
+      </c>
+      <c r="S821" t="n">
+        <v>6334.2</v>
+      </c>
+      <c r="T821" t="n">
+        <v>1491.955143832277</v>
+      </c>
+      <c r="U821" t="n">
+        <v>8.495174269061048</v>
+      </c>
+      <c r="V821" t="n">
+        <v>-0.002551020408163351</v>
+      </c>
+      <c r="W821" t="n">
+        <v>0.001945707585813583</v>
+      </c>
+      <c r="X821" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y821" t="n">
+        <v>10.667</v>
+      </c>
+      <c r="Z821" t="n">
+        <v>0.6009591817855835</v>
+      </c>
+      <c r="AA821" t="n">
+        <v>13.92029732894897</v>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E822" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F822" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G822" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H822" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I822" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J822" t="n">
+        <v>101</v>
+      </c>
+      <c r="K822" t="n">
+        <v>11</v>
+      </c>
+      <c r="L822" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M822" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N822" s="2" t="n">
+        <v>45838.72979800656</v>
+      </c>
+      <c r="O822" t="n">
+        <v>24481</v>
+      </c>
+      <c r="P822" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q822" t="n">
+        <v>2084.86</v>
+      </c>
+      <c r="R822" t="n">
+        <v>11.74227526068897</v>
+      </c>
+      <c r="S822" t="n">
+        <v>2472581</v>
+      </c>
+      <c r="T822" t="n">
+        <v>1185.969801329586</v>
+      </c>
+      <c r="U822" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V822" t="n">
+        <v>-0.001916177429876043</v>
+      </c>
+      <c r="W822" t="n">
+        <v>-0.01559826430815769</v>
+      </c>
+      <c r="X822" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y822" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z822" t="n">
+        <v>0.4416439533233643</v>
+      </c>
+      <c r="AA822" t="n">
+        <v>9.998224020004272</v>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E823" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F823" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G823" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H823" t="n">
+        <v>1</v>
+      </c>
+      <c r="I823" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J823" t="n">
+        <v>30</v>
+      </c>
+      <c r="K823" t="n">
+        <v>9</v>
+      </c>
+      <c r="L823" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M823" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N823" s="2" t="n">
+        <v>45838.72979800656</v>
+      </c>
+      <c r="O823" t="n">
+        <v>46.02</v>
+      </c>
+      <c r="P823" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q823" t="n">
+        <v>1</v>
+      </c>
+      <c r="R823" t="n">
+        <v>46.02</v>
+      </c>
+      <c r="S823" t="n">
+        <v>1380.6</v>
+      </c>
+      <c r="T823" t="n">
+        <v>1380.6</v>
+      </c>
+      <c r="U823" t="n">
+        <v>42.174</v>
+      </c>
+      <c r="V823" t="n">
+        <v>0.007443082311733962</v>
+      </c>
+      <c r="W823" t="n">
+        <v>0.007443082311733962</v>
+      </c>
+      <c r="X823" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y823" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z823" t="n">
+        <v>0.56679368019104</v>
+      </c>
+      <c r="AA823" t="n">
+        <v>10.87115383148193</v>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>MHY271836006</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>GLOBAL SHIP LEA. A DL-,01</t>
+        </is>
+      </c>
+      <c r="E824" s="2" t="n">
+        <v>45838.31344841435</v>
+      </c>
+      <c r="F824" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="G824" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H824" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="I824" t="n">
+        <v>22.64505496285648</v>
+      </c>
+      <c r="J824" t="n">
+        <v>66</v>
+      </c>
+      <c r="K824" t="n">
+        <v>10</v>
+      </c>
+      <c r="L824" t="n">
+        <v>0.5395355224609375</v>
+      </c>
+      <c r="M824" t="n">
+        <v>12.45218944549561</v>
+      </c>
+      <c r="N824" s="2" t="n">
+        <v>45838.72979800656</v>
+      </c>
+      <c r="O824" t="n">
+        <v>26.199</v>
+      </c>
+      <c r="P824" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q824" t="n">
+        <v>1.177163</v>
+      </c>
+      <c r="R824" t="n">
+        <v>22.25605120106561</v>
+      </c>
+      <c r="S824" t="n">
+        <v>1729.134</v>
+      </c>
+      <c r="T824" t="n">
+        <v>1468.89937927033</v>
+      </c>
+      <c r="U824" t="n">
+        <v>20.40206509457079</v>
+      </c>
+      <c r="V824" t="n">
+        <v>-0.01359186746987939</v>
+      </c>
+      <c r="W824" t="n">
+        <v>-0.01717830945559351</v>
+      </c>
+      <c r="X824" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y824" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z824" t="n">
+        <v>0.5395355224609375</v>
+      </c>
+      <c r="AA824" t="n">
+        <v>12.45218944549561</v>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>US74767N1072</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>QSG</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>QSG</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>QUANTASING GRP  ADR/3CL.A</t>
+        </is>
+      </c>
+      <c r="E825" s="2" t="n">
+        <v>45838.31344841435</v>
+      </c>
+      <c r="F825" t="n">
+        <v>8</v>
+      </c>
+      <c r="G825" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H825" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="I825" t="n">
+        <v>6.820799687607375</v>
+      </c>
+      <c r="J825" t="n">
+        <v>214</v>
+      </c>
+      <c r="K825" t="n">
+        <v>9</v>
+      </c>
+      <c r="L825" t="n">
+        <v>0.6086904406547546</v>
+      </c>
+      <c r="M825" t="n">
+        <v>12.26600360870361</v>
+      </c>
+      <c r="N825" s="2" t="n">
+        <v>45838.72979800656</v>
+      </c>
+      <c r="O825" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="P825" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q825" t="n">
+        <v>1.177163</v>
+      </c>
+      <c r="R825" t="n">
+        <v>8.29961526143788</v>
+      </c>
+      <c r="S825" t="n">
+        <v>2090.78</v>
+      </c>
+      <c r="T825" t="n">
+        <v>1776.117665947706</v>
+      </c>
+      <c r="U825" t="n">
+        <v>7.469653735294092</v>
+      </c>
+      <c r="V825" t="n">
+        <v>0.2212499999999999</v>
+      </c>
+      <c r="W825" t="n">
+        <v>0.2168097058351306</v>
+      </c>
+      <c r="X825" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y825" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z825" t="n">
+        <v>0.6086904406547546</v>
+      </c>
+      <c r="AA825" t="n">
         <v>12.26600360870361</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA825"/>
+  <dimension ref="A1:AA833"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77334,7 +77334,7 @@
         <v>100</v>
       </c>
       <c r="N818" s="2" t="n">
-        <v>45838.72979800656</v>
+        <v>45838.72979800926</v>
       </c>
       <c r="O818" t="n">
         <v>1</v>
@@ -77425,7 +77425,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N819" s="2" t="n">
-        <v>45838.72979800656</v>
+        <v>45838.72979800926</v>
       </c>
       <c r="O819" t="n">
         <v>372.5</v>
@@ -77520,7 +77520,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N820" s="2" t="n">
-        <v>45838.72979800656</v>
+        <v>45838.72979800926</v>
       </c>
       <c r="O820" t="n">
         <v>13.865</v>
@@ -77611,7 +77611,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N821" s="2" t="n">
-        <v>45838.72979800656</v>
+        <v>45838.72979800926</v>
       </c>
       <c r="O821" t="n">
         <v>39.1</v>
@@ -77706,7 +77706,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N822" s="2" t="n">
-        <v>45838.72979800656</v>
+        <v>45838.72979800926</v>
       </c>
       <c r="O822" t="n">
         <v>24481</v>
@@ -77801,7 +77801,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N823" s="2" t="n">
-        <v>45838.72979800656</v>
+        <v>45838.72979800926</v>
       </c>
       <c r="O823" t="n">
         <v>46.02</v>
@@ -77896,7 +77896,7 @@
         <v>12.45218944549561</v>
       </c>
       <c r="N824" s="2" t="n">
-        <v>45838.72979800656</v>
+        <v>45838.72979800926</v>
       </c>
       <c r="O824" t="n">
         <v>26.199</v>
@@ -77991,7 +77991,7 @@
         <v>12.26600360870361</v>
       </c>
       <c r="N825" s="2" t="n">
-        <v>45838.72979800656</v>
+        <v>45838.72979800926</v>
       </c>
       <c r="O825" t="n">
         <v>9.77</v>
@@ -78032,6 +78032,760 @@
         <v>0.6086904406547546</v>
       </c>
       <c r="AA825" t="n">
+        <v>12.26600360870361</v>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E826" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F826" t="n">
+        <v>1</v>
+      </c>
+      <c r="G826" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H826" t="n">
+        <v>1</v>
+      </c>
+      <c r="I826" t="n">
+        <v>1</v>
+      </c>
+      <c r="J826" t="n">
+        <v>1</v>
+      </c>
+      <c r="K826" t="n">
+        <v>100</v>
+      </c>
+      <c r="L826" t="n">
+        <v>100</v>
+      </c>
+      <c r="M826" t="n">
+        <v>100</v>
+      </c>
+      <c r="N826" s="2" t="n">
+        <v>45838.77897949814</v>
+      </c>
+      <c r="O826" t="n">
+        <v>1</v>
+      </c>
+      <c r="P826" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q826" t="n">
+        <v>1</v>
+      </c>
+      <c r="R826" t="n">
+        <v>1</v>
+      </c>
+      <c r="S826" t="n">
+        <v>0</v>
+      </c>
+      <c r="T826" t="n">
+        <v>6.22133174009582</v>
+      </c>
+      <c r="U826" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V826" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W826" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X826" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y826" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z826" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA826" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr"/>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E827" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F827" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G827" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H827" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I827" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J827" t="n">
+        <v>3</v>
+      </c>
+      <c r="K827" t="n">
+        <v>10</v>
+      </c>
+      <c r="L827" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M827" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N827" s="2" t="n">
+        <v>45838.77897949814</v>
+      </c>
+      <c r="O827" t="n">
+        <v>372.5</v>
+      </c>
+      <c r="P827" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q827" t="n">
+        <v>0.85847</v>
+      </c>
+      <c r="R827" t="n">
+        <v>433.9114937039151</v>
+      </c>
+      <c r="S827" t="n">
+        <v>1117.5</v>
+      </c>
+      <c r="T827" t="n">
+        <v>1301.734481111745</v>
+      </c>
+      <c r="U827" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V827" t="n">
+        <v>0.01314780262520876</v>
+      </c>
+      <c r="W827" t="n">
+        <v>0.007482946016823089</v>
+      </c>
+      <c r="X827" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y827" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z827" t="n">
+        <v>0.5365895628929138</v>
+      </c>
+      <c r="AA827" t="n">
+        <v>11.5371036529541</v>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E828" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F828" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G828" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H828" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I828" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J828" t="n">
+        <v>121</v>
+      </c>
+      <c r="K828" t="n">
+        <v>12</v>
+      </c>
+      <c r="L828" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M828" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N828" s="2" t="n">
+        <v>45838.77897949814</v>
+      </c>
+      <c r="O828" t="n">
+        <v>13.91</v>
+      </c>
+      <c r="P828" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q828" t="n">
+        <v>1.1778563</v>
+      </c>
+      <c r="R828" t="n">
+        <v>11.80959001535247</v>
+      </c>
+      <c r="S828" t="n">
+        <v>1683.11</v>
+      </c>
+      <c r="T828" t="n">
+        <v>1428.960391857649</v>
+      </c>
+      <c r="U828" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V828" t="n">
+        <v>-0.01904090267983072</v>
+      </c>
+      <c r="W828" t="n">
+        <v>-0.04194842582279801</v>
+      </c>
+      <c r="X828" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y828" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z828" t="n">
+        <v>0.5561246275901794</v>
+      </c>
+      <c r="AA828" t="n">
+        <v>12.51355290412903</v>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr"/>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E829" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F829" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G829" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H829" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I829" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J829" t="n">
+        <v>162</v>
+      </c>
+      <c r="K829" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L829" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M829" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N829" s="2" t="n">
+        <v>45838.77897949814</v>
+      </c>
+      <c r="O829" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="P829" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q829" t="n">
+        <v>4.24491</v>
+      </c>
+      <c r="R829" t="n">
+        <v>9.211031564862388</v>
+      </c>
+      <c r="S829" t="n">
+        <v>6334.2</v>
+      </c>
+      <c r="T829" t="n">
+        <v>1492.187113507707</v>
+      </c>
+      <c r="U829" t="n">
+        <v>8.495174269061048</v>
+      </c>
+      <c r="V829" t="n">
+        <v>-0.002551020408163351</v>
+      </c>
+      <c r="W829" t="n">
+        <v>0.002101490433272346</v>
+      </c>
+      <c r="X829" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y829" t="n">
+        <v>10.667</v>
+      </c>
+      <c r="Z829" t="n">
+        <v>0.6009591817855835</v>
+      </c>
+      <c r="AA829" t="n">
+        <v>13.92029732894897</v>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E830" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F830" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G830" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H830" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I830" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J830" t="n">
+        <v>101</v>
+      </c>
+      <c r="K830" t="n">
+        <v>11</v>
+      </c>
+      <c r="L830" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M830" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N830" s="2" t="n">
+        <v>45838.77897949814</v>
+      </c>
+      <c r="O830" t="n">
+        <v>24481</v>
+      </c>
+      <c r="P830" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q830" t="n">
+        <v>2084.87</v>
+      </c>
+      <c r="R830" t="n">
+        <v>11.74221893931037</v>
+      </c>
+      <c r="S830" t="n">
+        <v>2472581</v>
+      </c>
+      <c r="T830" t="n">
+        <v>1185.964112870347</v>
+      </c>
+      <c r="U830" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V830" t="n">
+        <v>-0.001916177429876043</v>
+      </c>
+      <c r="W830" t="n">
+        <v>-0.01560298595380305</v>
+      </c>
+      <c r="X830" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y830" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z830" t="n">
+        <v>0.4416439533233643</v>
+      </c>
+      <c r="AA830" t="n">
+        <v>9.998224020004272</v>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E831" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F831" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G831" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H831" t="n">
+        <v>1</v>
+      </c>
+      <c r="I831" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J831" t="n">
+        <v>30</v>
+      </c>
+      <c r="K831" t="n">
+        <v>9</v>
+      </c>
+      <c r="L831" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M831" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N831" s="2" t="n">
+        <v>45838.77897949814</v>
+      </c>
+      <c r="O831" t="n">
+        <v>46.02</v>
+      </c>
+      <c r="P831" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q831" t="n">
+        <v>1</v>
+      </c>
+      <c r="R831" t="n">
+        <v>46.02</v>
+      </c>
+      <c r="S831" t="n">
+        <v>1380.6</v>
+      </c>
+      <c r="T831" t="n">
+        <v>1380.6</v>
+      </c>
+      <c r="U831" t="n">
+        <v>42.174</v>
+      </c>
+      <c r="V831" t="n">
+        <v>0.007443082311733962</v>
+      </c>
+      <c r="W831" t="n">
+        <v>0.007443082311733962</v>
+      </c>
+      <c r="X831" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y831" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z831" t="n">
+        <v>0.56679368019104</v>
+      </c>
+      <c r="AA831" t="n">
+        <v>10.87115383148193</v>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>MHY271836006</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>GLOBAL SHIP LEA. A DL-,01</t>
+        </is>
+      </c>
+      <c r="E832" s="2" t="n">
+        <v>45838.31344841435</v>
+      </c>
+      <c r="F832" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="G832" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H832" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="I832" t="n">
+        <v>22.64505496285648</v>
+      </c>
+      <c r="J832" t="n">
+        <v>66</v>
+      </c>
+      <c r="K832" t="n">
+        <v>10</v>
+      </c>
+      <c r="L832" t="n">
+        <v>0.5395355224609375</v>
+      </c>
+      <c r="M832" t="n">
+        <v>12.45218944549561</v>
+      </c>
+      <c r="N832" s="2" t="n">
+        <v>45838.77897949814</v>
+      </c>
+      <c r="O832" t="n">
+        <v>26.22</v>
+      </c>
+      <c r="P832" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q832" t="n">
+        <v>1.1778563</v>
+      </c>
+      <c r="R832" t="n">
+        <v>22.26078002893901</v>
+      </c>
+      <c r="S832" t="n">
+        <v>1730.52</v>
+      </c>
+      <c r="T832" t="n">
+        <v>1469.211481909975</v>
+      </c>
+      <c r="U832" t="n">
+        <v>20.40206509457079</v>
+      </c>
+      <c r="V832" t="n">
+        <v>-0.01280120481927716</v>
+      </c>
+      <c r="W832" t="n">
+        <v>-0.01696948559178935</v>
+      </c>
+      <c r="X832" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y832" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z832" t="n">
+        <v>0.5395355224609375</v>
+      </c>
+      <c r="AA832" t="n">
+        <v>12.45218944549561</v>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>US74767N1072</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>QSG</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>QSG</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>QUANTASING GRP  ADR/3CL.A</t>
+        </is>
+      </c>
+      <c r="E833" s="2" t="n">
+        <v>45838.31344841435</v>
+      </c>
+      <c r="F833" t="n">
+        <v>8</v>
+      </c>
+      <c r="G833" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H833" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="I833" t="n">
+        <v>6.820799687607375</v>
+      </c>
+      <c r="J833" t="n">
+        <v>214</v>
+      </c>
+      <c r="K833" t="n">
+        <v>9</v>
+      </c>
+      <c r="L833" t="n">
+        <v>0.6086904406547546</v>
+      </c>
+      <c r="M833" t="n">
+        <v>12.26600360870361</v>
+      </c>
+      <c r="N833" s="2" t="n">
+        <v>45838.77897949814</v>
+      </c>
+      <c r="O833" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="P833" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q833" t="n">
+        <v>1.1778563</v>
+      </c>
+      <c r="R833" t="n">
+        <v>8.209830010672778</v>
+      </c>
+      <c r="S833" t="n">
+        <v>2069.38</v>
+      </c>
+      <c r="T833" t="n">
+        <v>1756.903622283975</v>
+      </c>
+      <c r="U833" t="n">
+        <v>7.469653735294092</v>
+      </c>
+      <c r="V833" t="n">
+        <v>0.20875</v>
+      </c>
+      <c r="W833" t="n">
+        <v>0.20364625655099</v>
+      </c>
+      <c r="X833" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y833" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z833" t="n">
+        <v>0.6086904406547546</v>
+      </c>
+      <c r="AA833" t="n">
         <v>12.26600360870361</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA833"/>
+  <dimension ref="A1:AA841"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78088,7 +78088,7 @@
         <v>100</v>
       </c>
       <c r="N826" s="2" t="n">
-        <v>45838.77897949814</v>
+        <v>45838.77897950231</v>
       </c>
       <c r="O826" t="n">
         <v>1</v>
@@ -78179,7 +78179,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N827" s="2" t="n">
-        <v>45838.77897949814</v>
+        <v>45838.77897950231</v>
       </c>
       <c r="O827" t="n">
         <v>372.5</v>
@@ -78274,7 +78274,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N828" s="2" t="n">
-        <v>45838.77897949814</v>
+        <v>45838.77897950231</v>
       </c>
       <c r="O828" t="n">
         <v>13.91</v>
@@ -78365,7 +78365,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N829" s="2" t="n">
-        <v>45838.77897949814</v>
+        <v>45838.77897950231</v>
       </c>
       <c r="O829" t="n">
         <v>39.1</v>
@@ -78460,7 +78460,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N830" s="2" t="n">
-        <v>45838.77897949814</v>
+        <v>45838.77897950231</v>
       </c>
       <c r="O830" t="n">
         <v>24481</v>
@@ -78555,7 +78555,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N831" s="2" t="n">
-        <v>45838.77897949814</v>
+        <v>45838.77897950231</v>
       </c>
       <c r="O831" t="n">
         <v>46.02</v>
@@ -78650,7 +78650,7 @@
         <v>12.45218944549561</v>
       </c>
       <c r="N832" s="2" t="n">
-        <v>45838.77897949814</v>
+        <v>45838.77897950231</v>
       </c>
       <c r="O832" t="n">
         <v>26.22</v>
@@ -78745,7 +78745,7 @@
         <v>12.26600360870361</v>
       </c>
       <c r="N833" s="2" t="n">
-        <v>45838.77897949814</v>
+        <v>45838.77897950231</v>
       </c>
       <c r="O833" t="n">
         <v>9.67</v>
@@ -78786,6 +78786,760 @@
         <v>0.6086904406547546</v>
       </c>
       <c r="AA833" t="n">
+        <v>12.26600360870361</v>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E834" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F834" t="n">
+        <v>1</v>
+      </c>
+      <c r="G834" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H834" t="n">
+        <v>1</v>
+      </c>
+      <c r="I834" t="n">
+        <v>1</v>
+      </c>
+      <c r="J834" t="n">
+        <v>1</v>
+      </c>
+      <c r="K834" t="n">
+        <v>100</v>
+      </c>
+      <c r="L834" t="n">
+        <v>100</v>
+      </c>
+      <c r="M834" t="n">
+        <v>100</v>
+      </c>
+      <c r="N834" s="2" t="n">
+        <v>45838.80867745714</v>
+      </c>
+      <c r="O834" t="n">
+        <v>1</v>
+      </c>
+      <c r="P834" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q834" t="n">
+        <v>1</v>
+      </c>
+      <c r="R834" t="n">
+        <v>1</v>
+      </c>
+      <c r="S834" t="n">
+        <v>0</v>
+      </c>
+      <c r="T834" t="n">
+        <v>6.22133174009582</v>
+      </c>
+      <c r="U834" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V834" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W834" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X834" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y834" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z834" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA834" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr"/>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E835" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F835" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G835" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H835" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I835" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J835" t="n">
+        <v>3</v>
+      </c>
+      <c r="K835" t="n">
+        <v>10</v>
+      </c>
+      <c r="L835" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M835" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N835" s="2" t="n">
+        <v>45838.80867745714</v>
+      </c>
+      <c r="O835" t="n">
+        <v>372.5</v>
+      </c>
+      <c r="P835" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q835" t="n">
+        <v>0.85824</v>
+      </c>
+      <c r="R835" t="n">
+        <v>434.0277777777778</v>
+      </c>
+      <c r="S835" t="n">
+        <v>1117.5</v>
+      </c>
+      <c r="T835" t="n">
+        <v>1302.083333333333</v>
+      </c>
+      <c r="U835" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V835" t="n">
+        <v>0.01314780262520876</v>
+      </c>
+      <c r="W835" t="n">
+        <v>0.007752941679555869</v>
+      </c>
+      <c r="X835" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y835" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z835" t="n">
+        <v>0.5365895628929138</v>
+      </c>
+      <c r="AA835" t="n">
+        <v>11.5371036529541</v>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E836" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F836" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G836" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H836" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I836" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J836" t="n">
+        <v>121</v>
+      </c>
+      <c r="K836" t="n">
+        <v>12</v>
+      </c>
+      <c r="L836" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M836" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N836" s="2" t="n">
+        <v>45838.80867745714</v>
+      </c>
+      <c r="O836" t="n">
+        <v>13.93</v>
+      </c>
+      <c r="P836" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q836" t="n">
+        <v>1.1781338</v>
+      </c>
+      <c r="R836" t="n">
+        <v>11.82378436133485</v>
+      </c>
+      <c r="S836" t="n">
+        <v>1685.53</v>
+      </c>
+      <c r="T836" t="n">
+        <v>1430.677907721517</v>
+      </c>
+      <c r="U836" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V836" t="n">
+        <v>-0.0176304654442877</v>
+      </c>
+      <c r="W836" t="n">
+        <v>-0.04079691120669704</v>
+      </c>
+      <c r="X836" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y836" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z836" t="n">
+        <v>0.5561246275901794</v>
+      </c>
+      <c r="AA836" t="n">
+        <v>12.51355290412903</v>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr"/>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E837" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F837" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G837" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H837" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I837" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J837" t="n">
+        <v>162</v>
+      </c>
+      <c r="K837" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L837" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M837" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N837" s="2" t="n">
+        <v>45838.80867745714</v>
+      </c>
+      <c r="O837" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="P837" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q837" t="n">
+        <v>4.2443</v>
+      </c>
+      <c r="R837" t="n">
+        <v>9.212355394293523</v>
+      </c>
+      <c r="S837" t="n">
+        <v>6334.2</v>
+      </c>
+      <c r="T837" t="n">
+        <v>1492.401573875551</v>
+      </c>
+      <c r="U837" t="n">
+        <v>8.495174269061048</v>
+      </c>
+      <c r="V837" t="n">
+        <v>-0.002551020408163351</v>
+      </c>
+      <c r="W837" t="n">
+        <v>0.002245514632589929</v>
+      </c>
+      <c r="X837" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y837" t="n">
+        <v>10.667</v>
+      </c>
+      <c r="Z837" t="n">
+        <v>0.6009591817855835</v>
+      </c>
+      <c r="AA837" t="n">
+        <v>13.92029732894897</v>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E838" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F838" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G838" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H838" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I838" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J838" t="n">
+        <v>101</v>
+      </c>
+      <c r="K838" t="n">
+        <v>11</v>
+      </c>
+      <c r="L838" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M838" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N838" s="2" t="n">
+        <v>45838.80867745714</v>
+      </c>
+      <c r="O838" t="n">
+        <v>24481</v>
+      </c>
+      <c r="P838" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q838" t="n">
+        <v>2084.47</v>
+      </c>
+      <c r="R838" t="n">
+        <v>11.74447221595897</v>
+      </c>
+      <c r="S838" t="n">
+        <v>2472581</v>
+      </c>
+      <c r="T838" t="n">
+        <v>1186.191693811856</v>
+      </c>
+      <c r="U838" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V838" t="n">
+        <v>-0.001916177429876043</v>
+      </c>
+      <c r="W838" t="n">
+        <v>-0.01541408479158024</v>
+      </c>
+      <c r="X838" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y838" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z838" t="n">
+        <v>0.4416439533233643</v>
+      </c>
+      <c r="AA838" t="n">
+        <v>9.998224020004272</v>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E839" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F839" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G839" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H839" t="n">
+        <v>1</v>
+      </c>
+      <c r="I839" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J839" t="n">
+        <v>30</v>
+      </c>
+      <c r="K839" t="n">
+        <v>9</v>
+      </c>
+      <c r="L839" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M839" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N839" s="2" t="n">
+        <v>45838.80867745714</v>
+      </c>
+      <c r="O839" t="n">
+        <v>46.02</v>
+      </c>
+      <c r="P839" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q839" t="n">
+        <v>1</v>
+      </c>
+      <c r="R839" t="n">
+        <v>46.02</v>
+      </c>
+      <c r="S839" t="n">
+        <v>1380.6</v>
+      </c>
+      <c r="T839" t="n">
+        <v>1380.6</v>
+      </c>
+      <c r="U839" t="n">
+        <v>42.174</v>
+      </c>
+      <c r="V839" t="n">
+        <v>0.007443082311733962</v>
+      </c>
+      <c r="W839" t="n">
+        <v>0.007443082311733962</v>
+      </c>
+      <c r="X839" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y839" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z839" t="n">
+        <v>0.56679368019104</v>
+      </c>
+      <c r="AA839" t="n">
+        <v>10.87115383148193</v>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>MHY271836006</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>GLOBAL SHIP LEA. A DL-,01</t>
+        </is>
+      </c>
+      <c r="E840" s="2" t="n">
+        <v>45838.31344841435</v>
+      </c>
+      <c r="F840" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="G840" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H840" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="I840" t="n">
+        <v>22.64505496285648</v>
+      </c>
+      <c r="J840" t="n">
+        <v>66</v>
+      </c>
+      <c r="K840" t="n">
+        <v>10</v>
+      </c>
+      <c r="L840" t="n">
+        <v>0.5395355224609375</v>
+      </c>
+      <c r="M840" t="n">
+        <v>12.45218944549561</v>
+      </c>
+      <c r="N840" s="2" t="n">
+        <v>45838.80867745714</v>
+      </c>
+      <c r="O840" t="n">
+        <v>26.285</v>
+      </c>
+      <c r="P840" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q840" t="n">
+        <v>1.1781338</v>
+      </c>
+      <c r="R840" t="n">
+        <v>22.31070868181526</v>
+      </c>
+      <c r="S840" t="n">
+        <v>1734.81</v>
+      </c>
+      <c r="T840" t="n">
+        <v>1472.506772999807</v>
+      </c>
+      <c r="U840" t="n">
+        <v>20.40206509457079</v>
+      </c>
+      <c r="V840" t="n">
+        <v>-0.01035391566265054</v>
+      </c>
+      <c r="W840" t="n">
+        <v>-0.01476464868774374</v>
+      </c>
+      <c r="X840" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y840" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z840" t="n">
+        <v>0.5395355224609375</v>
+      </c>
+      <c r="AA840" t="n">
+        <v>12.45218944549561</v>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>US74767N1072</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>QSG</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>QSG</t>
+        </is>
+      </c>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>QUANTASING GRP  ADR/3CL.A</t>
+        </is>
+      </c>
+      <c r="E841" s="2" t="n">
+        <v>45838.31344841435</v>
+      </c>
+      <c r="F841" t="n">
+        <v>8</v>
+      </c>
+      <c r="G841" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H841" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="I841" t="n">
+        <v>6.820799687607375</v>
+      </c>
+      <c r="J841" t="n">
+        <v>214</v>
+      </c>
+      <c r="K841" t="n">
+        <v>9</v>
+      </c>
+      <c r="L841" t="n">
+        <v>0.6086904406547546</v>
+      </c>
+      <c r="M841" t="n">
+        <v>12.26600360870361</v>
+      </c>
+      <c r="N841" s="2" t="n">
+        <v>45838.80867745714</v>
+      </c>
+      <c r="O841" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="P841" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q841" t="n">
+        <v>1.1781338</v>
+      </c>
+      <c r="R841" t="n">
+        <v>8.123016248239377</v>
+      </c>
+      <c r="S841" t="n">
+        <v>2047.98</v>
+      </c>
+      <c r="T841" t="n">
+        <v>1738.325477123227</v>
+      </c>
+      <c r="U841" t="n">
+        <v>7.469653735294092</v>
+      </c>
+      <c r="V841" t="n">
+        <v>0.19625</v>
+      </c>
+      <c r="W841" t="n">
+        <v>0.1909184582854682</v>
+      </c>
+      <c r="X841" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y841" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z841" t="n">
+        <v>0.6086904406547546</v>
+      </c>
+      <c r="AA841" t="n">
         <v>12.26600360870361</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA841"/>
+  <dimension ref="A1:AA849"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78842,7 +78842,7 @@
         <v>100</v>
       </c>
       <c r="N834" s="2" t="n">
-        <v>45838.80867745714</v>
+        <v>45838.8086774537</v>
       </c>
       <c r="O834" t="n">
         <v>1</v>
@@ -78933,7 +78933,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N835" s="2" t="n">
-        <v>45838.80867745714</v>
+        <v>45838.8086774537</v>
       </c>
       <c r="O835" t="n">
         <v>372.5</v>
@@ -79028,7 +79028,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N836" s="2" t="n">
-        <v>45838.80867745714</v>
+        <v>45838.8086774537</v>
       </c>
       <c r="O836" t="n">
         <v>13.93</v>
@@ -79119,7 +79119,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N837" s="2" t="n">
-        <v>45838.80867745714</v>
+        <v>45838.8086774537</v>
       </c>
       <c r="O837" t="n">
         <v>39.1</v>
@@ -79214,7 +79214,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N838" s="2" t="n">
-        <v>45838.80867745714</v>
+        <v>45838.8086774537</v>
       </c>
       <c r="O838" t="n">
         <v>24481</v>
@@ -79309,7 +79309,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N839" s="2" t="n">
-        <v>45838.80867745714</v>
+        <v>45838.8086774537</v>
       </c>
       <c r="O839" t="n">
         <v>46.02</v>
@@ -79404,7 +79404,7 @@
         <v>12.45218944549561</v>
       </c>
       <c r="N840" s="2" t="n">
-        <v>45838.80867745714</v>
+        <v>45838.8086774537</v>
       </c>
       <c r="O840" t="n">
         <v>26.285</v>
@@ -79499,7 +79499,7 @@
         <v>12.26600360870361</v>
       </c>
       <c r="N841" s="2" t="n">
-        <v>45838.80867745714</v>
+        <v>45838.8086774537</v>
       </c>
       <c r="O841" t="n">
         <v>9.57</v>
@@ -79540,6 +79540,760 @@
         <v>0.6086904406547546</v>
       </c>
       <c r="AA841" t="n">
+        <v>12.26600360870361</v>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E842" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F842" t="n">
+        <v>1</v>
+      </c>
+      <c r="G842" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H842" t="n">
+        <v>1</v>
+      </c>
+      <c r="I842" t="n">
+        <v>1</v>
+      </c>
+      <c r="J842" t="n">
+        <v>1</v>
+      </c>
+      <c r="K842" t="n">
+        <v>100</v>
+      </c>
+      <c r="L842" t="n">
+        <v>100</v>
+      </c>
+      <c r="M842" t="n">
+        <v>100</v>
+      </c>
+      <c r="N842" s="2" t="n">
+        <v>45838.85538100046</v>
+      </c>
+      <c r="O842" t="n">
+        <v>1</v>
+      </c>
+      <c r="P842" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q842" t="n">
+        <v>1</v>
+      </c>
+      <c r="R842" t="n">
+        <v>1</v>
+      </c>
+      <c r="S842" t="n">
+        <v>0</v>
+      </c>
+      <c r="T842" t="n">
+        <v>6.22133174009582</v>
+      </c>
+      <c r="U842" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V842" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W842" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X842" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y842" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z842" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA842" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr"/>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E843" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F843" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G843" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H843" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I843" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J843" t="n">
+        <v>3</v>
+      </c>
+      <c r="K843" t="n">
+        <v>10</v>
+      </c>
+      <c r="L843" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M843" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N843" s="2" t="n">
+        <v>45838.85538100046</v>
+      </c>
+      <c r="O843" t="n">
+        <v>372.5</v>
+      </c>
+      <c r="P843" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q843" t="n">
+        <v>0.85803</v>
+      </c>
+      <c r="R843" t="n">
+        <v>434.1340046385325</v>
+      </c>
+      <c r="S843" t="n">
+        <v>1117.5</v>
+      </c>
+      <c r="T843" t="n">
+        <v>1302.402013915597</v>
+      </c>
+      <c r="U843" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V843" t="n">
+        <v>0.01314780262520876</v>
+      </c>
+      <c r="W843" t="n">
+        <v>0.007999585873526671</v>
+      </c>
+      <c r="X843" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y843" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z843" t="n">
+        <v>0.5365895628929138</v>
+      </c>
+      <c r="AA843" t="n">
+        <v>11.5371036529541</v>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E844" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F844" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G844" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H844" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I844" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J844" t="n">
+        <v>121</v>
+      </c>
+      <c r="K844" t="n">
+        <v>12</v>
+      </c>
+      <c r="L844" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M844" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N844" s="2" t="n">
+        <v>45838.85538100046</v>
+      </c>
+      <c r="O844" t="n">
+        <v>13.97</v>
+      </c>
+      <c r="P844" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q844" t="n">
+        <v>1.1788282</v>
+      </c>
+      <c r="R844" t="n">
+        <v>11.85075144961751</v>
+      </c>
+      <c r="S844" t="n">
+        <v>1690.37</v>
+      </c>
+      <c r="T844" t="n">
+        <v>1433.940925403719</v>
+      </c>
+      <c r="U844" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V844" t="n">
+        <v>-0.01480959097320167</v>
+      </c>
+      <c r="W844" t="n">
+        <v>-0.03860920940277413</v>
+      </c>
+      <c r="X844" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y844" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z844" t="n">
+        <v>0.5561246275901794</v>
+      </c>
+      <c r="AA844" t="n">
+        <v>12.51355290412903</v>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr"/>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E845" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F845" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G845" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H845" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I845" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J845" t="n">
+        <v>162</v>
+      </c>
+      <c r="K845" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L845" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M845" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N845" s="2" t="n">
+        <v>45838.85538100046</v>
+      </c>
+      <c r="O845" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="P845" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q845" t="n">
+        <v>4.24464</v>
+      </c>
+      <c r="R845" t="n">
+        <v>9.211617475215801</v>
+      </c>
+      <c r="S845" t="n">
+        <v>6334.2</v>
+      </c>
+      <c r="T845" t="n">
+        <v>1492.28203098496</v>
+      </c>
+      <c r="U845" t="n">
+        <v>8.495174269061048</v>
+      </c>
+      <c r="V845" t="n">
+        <v>-0.002551020408163351</v>
+      </c>
+      <c r="W845" t="n">
+        <v>0.002165233743050443</v>
+      </c>
+      <c r="X845" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y845" t="n">
+        <v>10.667</v>
+      </c>
+      <c r="Z845" t="n">
+        <v>0.6009591817855835</v>
+      </c>
+      <c r="AA845" t="n">
+        <v>13.92029732894897</v>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E846" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F846" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G846" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H846" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I846" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J846" t="n">
+        <v>101</v>
+      </c>
+      <c r="K846" t="n">
+        <v>11</v>
+      </c>
+      <c r="L846" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M846" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N846" s="2" t="n">
+        <v>45838.85538100046</v>
+      </c>
+      <c r="O846" t="n">
+        <v>24481</v>
+      </c>
+      <c r="P846" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q846" t="n">
+        <v>2086.14</v>
+      </c>
+      <c r="R846" t="n">
+        <v>11.73507051300488</v>
+      </c>
+      <c r="S846" t="n">
+        <v>2472581</v>
+      </c>
+      <c r="T846" t="n">
+        <v>1185.242121813493</v>
+      </c>
+      <c r="U846" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V846" t="n">
+        <v>-0.001916177429876043</v>
+      </c>
+      <c r="W846" t="n">
+        <v>-0.01620226702211047</v>
+      </c>
+      <c r="X846" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y846" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z846" t="n">
+        <v>0.4416439533233643</v>
+      </c>
+      <c r="AA846" t="n">
+        <v>9.998224020004272</v>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E847" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F847" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G847" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H847" t="n">
+        <v>1</v>
+      </c>
+      <c r="I847" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J847" t="n">
+        <v>30</v>
+      </c>
+      <c r="K847" t="n">
+        <v>9</v>
+      </c>
+      <c r="L847" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M847" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N847" s="2" t="n">
+        <v>45838.85538100046</v>
+      </c>
+      <c r="O847" t="n">
+        <v>46.02</v>
+      </c>
+      <c r="P847" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q847" t="n">
+        <v>1</v>
+      </c>
+      <c r="R847" t="n">
+        <v>46.02</v>
+      </c>
+      <c r="S847" t="n">
+        <v>1380.6</v>
+      </c>
+      <c r="T847" t="n">
+        <v>1380.6</v>
+      </c>
+      <c r="U847" t="n">
+        <v>42.174</v>
+      </c>
+      <c r="V847" t="n">
+        <v>0.007443082311733962</v>
+      </c>
+      <c r="W847" t="n">
+        <v>0.007443082311733962</v>
+      </c>
+      <c r="X847" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y847" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z847" t="n">
+        <v>0.56679368019104</v>
+      </c>
+      <c r="AA847" t="n">
+        <v>10.87115383148193</v>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>MHY271836006</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="D848" t="inlineStr">
+        <is>
+          <t>GLOBAL SHIP LEA. A DL-,01</t>
+        </is>
+      </c>
+      <c r="E848" s="2" t="n">
+        <v>45838.31344841435</v>
+      </c>
+      <c r="F848" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="G848" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H848" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="I848" t="n">
+        <v>22.64505496285648</v>
+      </c>
+      <c r="J848" t="n">
+        <v>66</v>
+      </c>
+      <c r="K848" t="n">
+        <v>10</v>
+      </c>
+      <c r="L848" t="n">
+        <v>0.5395355224609375</v>
+      </c>
+      <c r="M848" t="n">
+        <v>12.45218944549561</v>
+      </c>
+      <c r="N848" s="2" t="n">
+        <v>45838.85538100046</v>
+      </c>
+      <c r="O848" t="n">
+        <v>26.31</v>
+      </c>
+      <c r="P848" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q848" t="n">
+        <v>1.1788282</v>
+      </c>
+      <c r="R848" t="n">
+        <v>22.31877384677428</v>
+      </c>
+      <c r="S848" t="n">
+        <v>1736.46</v>
+      </c>
+      <c r="T848" t="n">
+        <v>1473.039073887102</v>
+      </c>
+      <c r="U848" t="n">
+        <v>20.40206509457079</v>
+      </c>
+      <c r="V848" t="n">
+        <v>-0.009412650602409589</v>
+      </c>
+      <c r="W848" t="n">
+        <v>-0.01440849300729841</v>
+      </c>
+      <c r="X848" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y848" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z848" t="n">
+        <v>0.5395355224609375</v>
+      </c>
+      <c r="AA848" t="n">
+        <v>12.45218944549561</v>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>US74767N1072</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>QSG</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>QSG</t>
+        </is>
+      </c>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>QUANTASING GRP  ADR/3CL.A</t>
+        </is>
+      </c>
+      <c r="E849" s="2" t="n">
+        <v>45838.31344841435</v>
+      </c>
+      <c r="F849" t="n">
+        <v>8</v>
+      </c>
+      <c r="G849" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H849" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="I849" t="n">
+        <v>6.820799687607375</v>
+      </c>
+      <c r="J849" t="n">
+        <v>214</v>
+      </c>
+      <c r="K849" t="n">
+        <v>9</v>
+      </c>
+      <c r="L849" t="n">
+        <v>0.6086904406547546</v>
+      </c>
+      <c r="M849" t="n">
+        <v>12.26600360870361</v>
+      </c>
+      <c r="N849" s="2" t="n">
+        <v>45838.85538100046</v>
+      </c>
+      <c r="O849" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="P849" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q849" t="n">
+        <v>1.1788282</v>
+      </c>
+      <c r="R849" t="n">
+        <v>8.016435304143554</v>
+      </c>
+      <c r="S849" t="n">
+        <v>2022.3</v>
+      </c>
+      <c r="T849" t="n">
+        <v>1715.517155086721</v>
+      </c>
+      <c r="U849" t="n">
+        <v>7.469653735294092</v>
+      </c>
+      <c r="V849" t="n">
+        <v>0.1812499999999999</v>
+      </c>
+      <c r="W849" t="n">
+        <v>0.1752925861037256</v>
+      </c>
+      <c r="X849" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y849" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z849" t="n">
+        <v>0.6086904406547546</v>
+      </c>
+      <c r="AA849" t="n">
         <v>12.26600360870361</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA849"/>
+  <dimension ref="A1:AA857"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79596,7 +79596,7 @@
         <v>100</v>
       </c>
       <c r="N842" s="2" t="n">
-        <v>45838.85538100046</v>
+        <v>45838.85538099537</v>
       </c>
       <c r="O842" t="n">
         <v>1</v>
@@ -79687,7 +79687,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N843" s="2" t="n">
-        <v>45838.85538100046</v>
+        <v>45838.85538099537</v>
       </c>
       <c r="O843" t="n">
         <v>372.5</v>
@@ -79782,7 +79782,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N844" s="2" t="n">
-        <v>45838.85538100046</v>
+        <v>45838.85538099537</v>
       </c>
       <c r="O844" t="n">
         <v>13.97</v>
@@ -79873,7 +79873,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N845" s="2" t="n">
-        <v>45838.85538100046</v>
+        <v>45838.85538099537</v>
       </c>
       <c r="O845" t="n">
         <v>39.1</v>
@@ -79968,7 +79968,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N846" s="2" t="n">
-        <v>45838.85538100046</v>
+        <v>45838.85538099537</v>
       </c>
       <c r="O846" t="n">
         <v>24481</v>
@@ -80063,7 +80063,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N847" s="2" t="n">
-        <v>45838.85538100046</v>
+        <v>45838.85538099537</v>
       </c>
       <c r="O847" t="n">
         <v>46.02</v>
@@ -80158,7 +80158,7 @@
         <v>12.45218944549561</v>
       </c>
       <c r="N848" s="2" t="n">
-        <v>45838.85538100046</v>
+        <v>45838.85538099537</v>
       </c>
       <c r="O848" t="n">
         <v>26.31</v>
@@ -80253,7 +80253,7 @@
         <v>12.26600360870361</v>
       </c>
       <c r="N849" s="2" t="n">
-        <v>45838.85538100046</v>
+        <v>45838.85538099537</v>
       </c>
       <c r="O849" t="n">
         <v>9.449999999999999</v>
@@ -80294,6 +80294,760 @@
         <v>0.6086904406547546</v>
       </c>
       <c r="AA849" t="n">
+        <v>12.26600360870361</v>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E850" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F850" t="n">
+        <v>1</v>
+      </c>
+      <c r="G850" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H850" t="n">
+        <v>1</v>
+      </c>
+      <c r="I850" t="n">
+        <v>1</v>
+      </c>
+      <c r="J850" t="n">
+        <v>1</v>
+      </c>
+      <c r="K850" t="n">
+        <v>100</v>
+      </c>
+      <c r="L850" t="n">
+        <v>100</v>
+      </c>
+      <c r="M850" t="n">
+        <v>100</v>
+      </c>
+      <c r="N850" s="2" t="n">
+        <v>45838.89479244837</v>
+      </c>
+      <c r="O850" t="n">
+        <v>1</v>
+      </c>
+      <c r="P850" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q850" t="n">
+        <v>1</v>
+      </c>
+      <c r="R850" t="n">
+        <v>1</v>
+      </c>
+      <c r="S850" t="n">
+        <v>0</v>
+      </c>
+      <c r="T850" t="n">
+        <v>6.22133174009582</v>
+      </c>
+      <c r="U850" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V850" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W850" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X850" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y850" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z850" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA850" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr"/>
+      <c r="D851" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E851" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F851" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G851" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H851" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I851" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J851" t="n">
+        <v>3</v>
+      </c>
+      <c r="K851" t="n">
+        <v>10</v>
+      </c>
+      <c r="L851" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M851" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N851" s="2" t="n">
+        <v>45838.89479244837</v>
+      </c>
+      <c r="O851" t="n">
+        <v>372.5</v>
+      </c>
+      <c r="P851" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q851" t="n">
+        <v>0.85792</v>
+      </c>
+      <c r="R851" t="n">
+        <v>434.1896680343156</v>
+      </c>
+      <c r="S851" t="n">
+        <v>1117.5</v>
+      </c>
+      <c r="T851" t="n">
+        <v>1302.569004102947</v>
+      </c>
+      <c r="U851" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V851" t="n">
+        <v>0.01314780262520876</v>
+      </c>
+      <c r="W851" t="n">
+        <v>0.008128828640271868</v>
+      </c>
+      <c r="X851" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y851" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z851" t="n">
+        <v>0.5365895628929138</v>
+      </c>
+      <c r="AA851" t="n">
+        <v>11.5371036529541</v>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D852" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E852" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F852" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G852" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H852" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I852" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J852" t="n">
+        <v>121</v>
+      </c>
+      <c r="K852" t="n">
+        <v>12</v>
+      </c>
+      <c r="L852" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M852" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N852" s="2" t="n">
+        <v>45838.89479244837</v>
+      </c>
+      <c r="O852" t="n">
+        <v>13.97</v>
+      </c>
+      <c r="P852" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q852" t="n">
+        <v>1.1785504</v>
+      </c>
+      <c r="R852" t="n">
+        <v>11.85354482930896</v>
+      </c>
+      <c r="S852" t="n">
+        <v>1690.37</v>
+      </c>
+      <c r="T852" t="n">
+        <v>1434.278924346384</v>
+      </c>
+      <c r="U852" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V852" t="n">
+        <v>-0.01480959097320167</v>
+      </c>
+      <c r="W852" t="n">
+        <v>-0.03838259681019607</v>
+      </c>
+      <c r="X852" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y852" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z852" t="n">
+        <v>0.5561246275901794</v>
+      </c>
+      <c r="AA852" t="n">
+        <v>12.51355290412903</v>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr"/>
+      <c r="D853" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E853" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F853" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G853" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H853" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I853" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J853" t="n">
+        <v>162</v>
+      </c>
+      <c r="K853" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L853" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M853" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N853" s="2" t="n">
+        <v>45838.89479244837</v>
+      </c>
+      <c r="O853" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="P853" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q853" t="n">
+        <v>4.2409</v>
+      </c>
+      <c r="R853" t="n">
+        <v>9.219741092692589</v>
+      </c>
+      <c r="S853" t="n">
+        <v>6334.2</v>
+      </c>
+      <c r="T853" t="n">
+        <v>1493.598057016199</v>
+      </c>
+      <c r="U853" t="n">
+        <v>8.495174269061048</v>
+      </c>
+      <c r="V853" t="n">
+        <v>-0.002551020408163351</v>
+      </c>
+      <c r="W853" t="n">
+        <v>0.003049031515739875</v>
+      </c>
+      <c r="X853" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y853" t="n">
+        <v>10.667</v>
+      </c>
+      <c r="Z853" t="n">
+        <v>0.6009591817855835</v>
+      </c>
+      <c r="AA853" t="n">
+        <v>13.92029732894897</v>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="D854" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="E854" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F854" t="n">
+        <v>24528</v>
+      </c>
+      <c r="G854" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="H854" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="I854" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="J854" t="n">
+        <v>101</v>
+      </c>
+      <c r="K854" t="n">
+        <v>11</v>
+      </c>
+      <c r="L854" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="M854" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="N854" s="2" t="n">
+        <v>45838.89479244837</v>
+      </c>
+      <c r="O854" t="n">
+        <v>24481</v>
+      </c>
+      <c r="P854" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="Q854" t="n">
+        <v>2089.83</v>
+      </c>
+      <c r="R854" t="n">
+        <v>11.71434997105028</v>
+      </c>
+      <c r="S854" t="n">
+        <v>2472581</v>
+      </c>
+      <c r="T854" t="n">
+        <v>1183.149347076078</v>
+      </c>
+      <c r="U854" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="V854" t="n">
+        <v>-0.001916177429876043</v>
+      </c>
+      <c r="W854" t="n">
+        <v>-0.01793935263897328</v>
+      </c>
+      <c r="X854" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y854" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z854" t="n">
+        <v>0.4416439533233643</v>
+      </c>
+      <c r="AA854" t="n">
+        <v>9.998224020004272</v>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E855" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F855" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G855" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H855" t="n">
+        <v>1</v>
+      </c>
+      <c r="I855" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J855" t="n">
+        <v>30</v>
+      </c>
+      <c r="K855" t="n">
+        <v>9</v>
+      </c>
+      <c r="L855" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M855" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N855" s="2" t="n">
+        <v>45838.89479244837</v>
+      </c>
+      <c r="O855" t="n">
+        <v>46.02</v>
+      </c>
+      <c r="P855" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q855" t="n">
+        <v>1</v>
+      </c>
+      <c r="R855" t="n">
+        <v>46.02</v>
+      </c>
+      <c r="S855" t="n">
+        <v>1380.6</v>
+      </c>
+      <c r="T855" t="n">
+        <v>1380.6</v>
+      </c>
+      <c r="U855" t="n">
+        <v>42.174</v>
+      </c>
+      <c r="V855" t="n">
+        <v>0.007443082311733962</v>
+      </c>
+      <c r="W855" t="n">
+        <v>0.007443082311733962</v>
+      </c>
+      <c r="X855" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y855" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z855" t="n">
+        <v>0.56679368019104</v>
+      </c>
+      <c r="AA855" t="n">
+        <v>10.87115383148193</v>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>MHY271836006</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="D856" t="inlineStr">
+        <is>
+          <t>GLOBAL SHIP LEA. A DL-,01</t>
+        </is>
+      </c>
+      <c r="E856" s="2" t="n">
+        <v>45838.31344841435</v>
+      </c>
+      <c r="F856" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="G856" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H856" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="I856" t="n">
+        <v>22.64505496285648</v>
+      </c>
+      <c r="J856" t="n">
+        <v>66</v>
+      </c>
+      <c r="K856" t="n">
+        <v>10</v>
+      </c>
+      <c r="L856" t="n">
+        <v>0.5395355224609375</v>
+      </c>
+      <c r="M856" t="n">
+        <v>12.45218944549561</v>
+      </c>
+      <c r="N856" s="2" t="n">
+        <v>45838.89479244837</v>
+      </c>
+      <c r="O856" t="n">
+        <v>26.31</v>
+      </c>
+      <c r="P856" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q856" t="n">
+        <v>1.1785504</v>
+      </c>
+      <c r="R856" t="n">
+        <v>22.3240346785339</v>
+      </c>
+      <c r="S856" t="n">
+        <v>1736.46</v>
+      </c>
+      <c r="T856" t="n">
+        <v>1473.386288783237</v>
+      </c>
+      <c r="U856" t="n">
+        <v>20.40206509457079</v>
+      </c>
+      <c r="V856" t="n">
+        <v>-0.009412650602409589</v>
+      </c>
+      <c r="W856" t="n">
+        <v>-0.01417617598407861</v>
+      </c>
+      <c r="X856" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y856" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z856" t="n">
+        <v>0.5395355224609375</v>
+      </c>
+      <c r="AA856" t="n">
+        <v>12.45218944549561</v>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>US74767N1072</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>QSG</t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>QSG</t>
+        </is>
+      </c>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>QUANTASING GRP  ADR/3CL.A</t>
+        </is>
+      </c>
+      <c r="E857" s="2" t="n">
+        <v>45838.31344841435</v>
+      </c>
+      <c r="F857" t="n">
+        <v>8</v>
+      </c>
+      <c r="G857" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H857" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="I857" t="n">
+        <v>6.820799687607375</v>
+      </c>
+      <c r="J857" t="n">
+        <v>214</v>
+      </c>
+      <c r="K857" t="n">
+        <v>9</v>
+      </c>
+      <c r="L857" t="n">
+        <v>0.6086904406547546</v>
+      </c>
+      <c r="M857" t="n">
+        <v>12.26600360870361</v>
+      </c>
+      <c r="N857" s="2" t="n">
+        <v>45838.89479244837</v>
+      </c>
+      <c r="O857" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="P857" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q857" t="n">
+        <v>1.1785504</v>
+      </c>
+      <c r="R857" t="n">
+        <v>8.018324884536121</v>
+      </c>
+      <c r="S857" t="n">
+        <v>2022.3</v>
+      </c>
+      <c r="T857" t="n">
+        <v>1715.92152529073</v>
+      </c>
+      <c r="U857" t="n">
+        <v>7.469653735294092</v>
+      </c>
+      <c r="V857" t="n">
+        <v>0.1812499999999999</v>
+      </c>
+      <c r="W857" t="n">
+        <v>0.1755696181936723</v>
+      </c>
+      <c r="X857" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y857" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z857" t="n">
+        <v>0.6086904406547546</v>
+      </c>
+      <c r="AA857" t="n">
         <v>12.26600360870361</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA857"/>
+  <dimension ref="A1:AA864"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80350,7 +80350,7 @@
         <v>100</v>
       </c>
       <c r="N850" s="2" t="n">
-        <v>45838.89479244837</v>
+        <v>45838.89479245371</v>
       </c>
       <c r="O850" t="n">
         <v>1</v>
@@ -80441,7 +80441,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N851" s="2" t="n">
-        <v>45838.89479244837</v>
+        <v>45838.89479245371</v>
       </c>
       <c r="O851" t="n">
         <v>372.5</v>
@@ -80536,7 +80536,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N852" s="2" t="n">
-        <v>45838.89479244837</v>
+        <v>45838.89479245371</v>
       </c>
       <c r="O852" t="n">
         <v>13.97</v>
@@ -80627,7 +80627,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N853" s="2" t="n">
-        <v>45838.89479244837</v>
+        <v>45838.89479245371</v>
       </c>
       <c r="O853" t="n">
         <v>39.1</v>
@@ -80722,7 +80722,7 @@
         <v>12.66160106658936</v>
       </c>
       <c r="N854" s="2" t="n">
-        <v>45838.89479244837</v>
+        <v>45838.89479245371</v>
       </c>
       <c r="O854" t="n">
         <v>24481</v>
@@ -80817,7 +80817,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N855" s="2" t="n">
-        <v>45838.89479244837</v>
+        <v>45838.89479245371</v>
       </c>
       <c r="O855" t="n">
         <v>46.02</v>
@@ -80912,7 +80912,7 @@
         <v>12.45218944549561</v>
       </c>
       <c r="N856" s="2" t="n">
-        <v>45838.89479244837</v>
+        <v>45838.89479245371</v>
       </c>
       <c r="O856" t="n">
         <v>26.31</v>
@@ -81007,7 +81007,7 @@
         <v>12.26600360870361</v>
       </c>
       <c r="N857" s="2" t="n">
-        <v>45838.89479244837</v>
+        <v>45838.89479245371</v>
       </c>
       <c r="O857" t="n">
         <v>9.449999999999999</v>
@@ -81049,6 +81049,665 @@
       </c>
       <c r="AA857" t="n">
         <v>12.26600360870361</v>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D858" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E858" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F858" t="n">
+        <v>1</v>
+      </c>
+      <c r="G858" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H858" t="n">
+        <v>1</v>
+      </c>
+      <c r="I858" t="n">
+        <v>1</v>
+      </c>
+      <c r="J858" t="n">
+        <v>1</v>
+      </c>
+      <c r="K858" t="n">
+        <v>100</v>
+      </c>
+      <c r="L858" t="n">
+        <v>100</v>
+      </c>
+      <c r="M858" t="n">
+        <v>100</v>
+      </c>
+      <c r="N858" s="2" t="n">
+        <v>45839.31381714748</v>
+      </c>
+      <c r="O858" t="n">
+        <v>1</v>
+      </c>
+      <c r="P858" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q858" t="n">
+        <v>1</v>
+      </c>
+      <c r="R858" t="n">
+        <v>1</v>
+      </c>
+      <c r="S858" t="n">
+        <v>0</v>
+      </c>
+      <c r="T858" t="n">
+        <v>1414.591526256027</v>
+      </c>
+      <c r="U858" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V858" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W858" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X858" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y858" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z858" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA858" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr"/>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E859" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F859" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G859" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H859" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I859" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J859" t="n">
+        <v>3</v>
+      </c>
+      <c r="K859" t="n">
+        <v>10</v>
+      </c>
+      <c r="L859" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M859" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N859" s="2" t="n">
+        <v>45839.31381714748</v>
+      </c>
+      <c r="O859" t="n">
+        <v>371.45</v>
+      </c>
+      <c r="P859" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q859" t="n">
+        <v>0.85673</v>
+      </c>
+      <c r="R859" t="n">
+        <v>433.5671681860096</v>
+      </c>
+      <c r="S859" t="n">
+        <v>1114.35</v>
+      </c>
+      <c r="T859" t="n">
+        <v>1300.701504558029</v>
+      </c>
+      <c r="U859" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V859" t="n">
+        <v>0.01029194975874836</v>
+      </c>
+      <c r="W859" t="n">
+        <v>0.006683469413410137</v>
+      </c>
+      <c r="X859" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y859" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z859" t="n">
+        <v>0.4370984435081482</v>
+      </c>
+      <c r="AA859" t="n">
+        <v>10.20819354057312</v>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D860" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E860" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F860" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G860" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H860" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I860" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J860" t="n">
+        <v>121</v>
+      </c>
+      <c r="K860" t="n">
+        <v>12</v>
+      </c>
+      <c r="L860" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M860" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N860" s="2" t="n">
+        <v>45839.31381714748</v>
+      </c>
+      <c r="O860" t="n">
+        <v>13.97</v>
+      </c>
+      <c r="P860" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q860" t="n">
+        <v>1.1788282</v>
+      </c>
+      <c r="R860" t="n">
+        <v>11.85075144961751</v>
+      </c>
+      <c r="S860" t="n">
+        <v>1690.37</v>
+      </c>
+      <c r="T860" t="n">
+        <v>1433.940925403719</v>
+      </c>
+      <c r="U860" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V860" t="n">
+        <v>-0.01480959097320167</v>
+      </c>
+      <c r="W860" t="n">
+        <v>-0.03860920940277413</v>
+      </c>
+      <c r="X860" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y860" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z860" t="n">
+        <v>0.3516944050788879</v>
+      </c>
+      <c r="AA860" t="n">
+        <v>9.560202062129974</v>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr"/>
+      <c r="D861" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E861" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F861" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G861" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H861" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I861" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J861" t="n">
+        <v>162</v>
+      </c>
+      <c r="K861" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L861" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M861" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N861" s="2" t="n">
+        <v>45839.31381714748</v>
+      </c>
+      <c r="O861" t="n">
+        <v>39.45</v>
+      </c>
+      <c r="P861" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q861" t="n">
+        <v>4.23944</v>
+      </c>
+      <c r="R861" t="n">
+        <v>9.305474307927463</v>
+      </c>
+      <c r="S861" t="n">
+        <v>6390.900000000001</v>
+      </c>
+      <c r="T861" t="n">
+        <v>1507.486837884249</v>
+      </c>
+      <c r="U861" t="n">
+        <v>8.495174269061048</v>
+      </c>
+      <c r="V861" t="n">
+        <v>0.006377551020408267</v>
+      </c>
+      <c r="W861" t="n">
+        <v>0.01237625856533997</v>
+      </c>
+      <c r="X861" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y861" t="n">
+        <v>10.667</v>
+      </c>
+      <c r="Z861" t="n">
+        <v>0.4341856837272644</v>
+      </c>
+      <c r="AA861" t="n">
+        <v>11.63437480163574</v>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D862" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E862" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F862" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G862" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H862" t="n">
+        <v>1</v>
+      </c>
+      <c r="I862" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J862" t="n">
+        <v>30</v>
+      </c>
+      <c r="K862" t="n">
+        <v>9</v>
+      </c>
+      <c r="L862" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M862" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N862" s="2" t="n">
+        <v>45839.31381714748</v>
+      </c>
+      <c r="O862" t="n">
+        <v>46.02</v>
+      </c>
+      <c r="P862" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q862" t="n">
+        <v>1</v>
+      </c>
+      <c r="R862" t="n">
+        <v>46.02</v>
+      </c>
+      <c r="S862" t="n">
+        <v>1380.6</v>
+      </c>
+      <c r="T862" t="n">
+        <v>1380.6</v>
+      </c>
+      <c r="U862" t="n">
+        <v>42.174</v>
+      </c>
+      <c r="V862" t="n">
+        <v>0.007443082311733962</v>
+      </c>
+      <c r="W862" t="n">
+        <v>0.007443082311733962</v>
+      </c>
+      <c r="X862" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y862" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z862" t="n">
+        <v>0.468702644109726</v>
+      </c>
+      <c r="AA862" t="n">
+        <v>9.620825290679932</v>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>MHY271836006</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t>GLOBAL SHIP LEA. A DL-,01</t>
+        </is>
+      </c>
+      <c r="E863" s="2" t="n">
+        <v>45838.31344841435</v>
+      </c>
+      <c r="F863" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="G863" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H863" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="I863" t="n">
+        <v>22.64505496285648</v>
+      </c>
+      <c r="J863" t="n">
+        <v>66</v>
+      </c>
+      <c r="K863" t="n">
+        <v>10</v>
+      </c>
+      <c r="L863" t="n">
+        <v>0.5395355224609375</v>
+      </c>
+      <c r="M863" t="n">
+        <v>12.45218944549561</v>
+      </c>
+      <c r="N863" s="2" t="n">
+        <v>45839.31381714748</v>
+      </c>
+      <c r="O863" t="n">
+        <v>26.31</v>
+      </c>
+      <c r="P863" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q863" t="n">
+        <v>1.1788282</v>
+      </c>
+      <c r="R863" t="n">
+        <v>22.31877384677428</v>
+      </c>
+      <c r="S863" t="n">
+        <v>1736.46</v>
+      </c>
+      <c r="T863" t="n">
+        <v>1473.039073887102</v>
+      </c>
+      <c r="U863" t="n">
+        <v>20.40206509457079</v>
+      </c>
+      <c r="V863" t="n">
+        <v>-0.009412650602409589</v>
+      </c>
+      <c r="W863" t="n">
+        <v>-0.01440849300729841</v>
+      </c>
+      <c r="X863" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y863" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z863" t="n">
+        <v>0.358627051115036</v>
+      </c>
+      <c r="AA863" t="n">
+        <v>9.922716617584229</v>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>PAP310761054</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="D864" t="inlineStr">
+        <is>
+          <t>COPA HOLDINGS CL.A O.N.</t>
+        </is>
+      </c>
+      <c r="E864" s="2" t="n">
+        <v>45839.31381714748</v>
+      </c>
+      <c r="F864" t="n">
+        <v>109.97</v>
+      </c>
+      <c r="G864" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H864" t="n">
+        <v>1.1788282</v>
+      </c>
+      <c r="I864" t="n">
+        <v>93.2875545393298</v>
+      </c>
+      <c r="J864" t="n">
+        <v>16</v>
+      </c>
+      <c r="K864" t="n">
+        <v>10</v>
+      </c>
+      <c r="L864" t="n">
+        <v>0.4318655133247375</v>
+      </c>
+      <c r="M864" t="n">
+        <v>11.16087436676025</v>
+      </c>
+      <c r="N864" s="2" t="n">
+        <v>45839.31381714748</v>
+      </c>
+      <c r="O864" t="n">
+        <v>109.97</v>
+      </c>
+      <c r="P864" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q864" t="n">
+        <v>1.1788282</v>
+      </c>
+      <c r="R864" t="n">
+        <v>93.2875545393298</v>
+      </c>
+      <c r="S864" t="n">
+        <v>1759.52</v>
+      </c>
+      <c r="T864" t="n">
+        <v>1492.600872629277</v>
+      </c>
+      <c r="U864" t="n">
+        <v>83.95879908539682</v>
+      </c>
+      <c r="V864" t="n">
+        <v>0</v>
+      </c>
+      <c r="W864" t="n">
+        <v>0</v>
+      </c>
+      <c r="X864" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y864" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z864" t="n">
+        <v>0.4318655133247375</v>
+      </c>
+      <c r="AA864" t="n">
+        <v>11.16087436676025</v>
       </c>
     </row>
   </sheetData>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA864"/>
+  <dimension ref="A1:AA871"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81104,7 +81104,7 @@
         <v>100</v>
       </c>
       <c r="N858" s="2" t="n">
-        <v>45839.31381714748</v>
+        <v>45839.31381715278</v>
       </c>
       <c r="O858" t="n">
         <v>1</v>
@@ -81195,7 +81195,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N859" s="2" t="n">
-        <v>45839.31381714748</v>
+        <v>45839.31381715278</v>
       </c>
       <c r="O859" t="n">
         <v>371.45</v>
@@ -81290,7 +81290,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N860" s="2" t="n">
-        <v>45839.31381714748</v>
+        <v>45839.31381715278</v>
       </c>
       <c r="O860" t="n">
         <v>13.97</v>
@@ -81381,7 +81381,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N861" s="2" t="n">
-        <v>45839.31381714748</v>
+        <v>45839.31381715278</v>
       </c>
       <c r="O861" t="n">
         <v>39.45</v>
@@ -81476,7 +81476,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N862" s="2" t="n">
-        <v>45839.31381714748</v>
+        <v>45839.31381715278</v>
       </c>
       <c r="O862" t="n">
         <v>46.02</v>
@@ -81571,7 +81571,7 @@
         <v>12.45218944549561</v>
       </c>
       <c r="N863" s="2" t="n">
-        <v>45839.31381714748</v>
+        <v>45839.31381715278</v>
       </c>
       <c r="O863" t="n">
         <v>26.31</v>
@@ -81637,7 +81637,7 @@
         </is>
       </c>
       <c r="E864" s="2" t="n">
-        <v>45839.31381714748</v>
+        <v>45839.31381715278</v>
       </c>
       <c r="F864" t="n">
         <v>109.97</v>
@@ -81666,7 +81666,7 @@
         <v>11.16087436676025</v>
       </c>
       <c r="N864" s="2" t="n">
-        <v>45839.31381714748</v>
+        <v>45839.31381715278</v>
       </c>
       <c r="O864" t="n">
         <v>109.97</v>
@@ -81707,6 +81707,665 @@
         <v>0.4318655133247375</v>
       </c>
       <c r="AA864" t="n">
+        <v>11.16087436676025</v>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D865" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E865" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F865" t="n">
+        <v>1</v>
+      </c>
+      <c r="G865" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H865" t="n">
+        <v>1</v>
+      </c>
+      <c r="I865" t="n">
+        <v>1</v>
+      </c>
+      <c r="J865" t="n">
+        <v>1</v>
+      </c>
+      <c r="K865" t="n">
+        <v>100</v>
+      </c>
+      <c r="L865" t="n">
+        <v>100</v>
+      </c>
+      <c r="M865" t="n">
+        <v>100</v>
+      </c>
+      <c r="N865" s="2" t="n">
+        <v>45839.36131964176</v>
+      </c>
+      <c r="O865" t="n">
+        <v>1</v>
+      </c>
+      <c r="P865" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q865" t="n">
+        <v>1</v>
+      </c>
+      <c r="R865" t="n">
+        <v>1</v>
+      </c>
+      <c r="S865" t="n">
+        <v>0</v>
+      </c>
+      <c r="T865" t="n">
+        <v>1414.591526256027</v>
+      </c>
+      <c r="U865" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V865" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W865" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X865" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y865" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z865" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA865" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr"/>
+      <c r="D866" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E866" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F866" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G866" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H866" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I866" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J866" t="n">
+        <v>3</v>
+      </c>
+      <c r="K866" t="n">
+        <v>10</v>
+      </c>
+      <c r="L866" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M866" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N866" s="2" t="n">
+        <v>45839.36131964176</v>
+      </c>
+      <c r="O866" t="n">
+        <v>365.55</v>
+      </c>
+      <c r="P866" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q866" t="n">
+        <v>0.8565</v>
+      </c>
+      <c r="R866" t="n">
+        <v>426.7950963222416</v>
+      </c>
+      <c r="S866" t="n">
+        <v>1096.65</v>
+      </c>
+      <c r="T866" t="n">
+        <v>1280.385288966725</v>
+      </c>
+      <c r="U866" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V866" t="n">
+        <v>-0.005755223490885752</v>
+      </c>
+      <c r="W866" t="n">
+        <v>-0.00904035217450605</v>
+      </c>
+      <c r="X866" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y866" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z866" t="n">
+        <v>0.4370984435081482</v>
+      </c>
+      <c r="AA866" t="n">
+        <v>10.20819354057312</v>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E867" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F867" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G867" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H867" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I867" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J867" t="n">
+        <v>121</v>
+      </c>
+      <c r="K867" t="n">
+        <v>12</v>
+      </c>
+      <c r="L867" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M867" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N867" s="2" t="n">
+        <v>45839.36131964176</v>
+      </c>
+      <c r="O867" t="n">
+        <v>13.97</v>
+      </c>
+      <c r="P867" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q867" t="n">
+        <v>1.1800802</v>
+      </c>
+      <c r="R867" t="n">
+        <v>11.83817845600664</v>
+      </c>
+      <c r="S867" t="n">
+        <v>1690.37</v>
+      </c>
+      <c r="T867" t="n">
+        <v>1432.419593176803</v>
+      </c>
+      <c r="U867" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V867" t="n">
+        <v>-0.01480959097320167</v>
+      </c>
+      <c r="W867" t="n">
+        <v>-0.03962919200211568</v>
+      </c>
+      <c r="X867" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y867" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z867" t="n">
+        <v>0.3516944050788879</v>
+      </c>
+      <c r="AA867" t="n">
+        <v>9.560202062129974</v>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr"/>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E868" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F868" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G868" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H868" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I868" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J868" t="n">
+        <v>162</v>
+      </c>
+      <c r="K868" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L868" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M868" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N868" s="2" t="n">
+        <v>45839.36131964176</v>
+      </c>
+      <c r="O868" t="n">
+        <v>39.35</v>
+      </c>
+      <c r="P868" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q868" t="n">
+        <v>4.2396</v>
+      </c>
+      <c r="R868" t="n">
+        <v>9.281535993961695</v>
+      </c>
+      <c r="S868" t="n">
+        <v>6374.7</v>
+      </c>
+      <c r="T868" t="n">
+        <v>1503.608831021794</v>
+      </c>
+      <c r="U868" t="n">
+        <v>8.495174269061048</v>
+      </c>
+      <c r="V868" t="n">
+        <v>0.003826530612244916</v>
+      </c>
+      <c r="W868" t="n">
+        <v>0.009771922673683209</v>
+      </c>
+      <c r="X868" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y868" t="n">
+        <v>10.667</v>
+      </c>
+      <c r="Z868" t="n">
+        <v>0.4341856837272644</v>
+      </c>
+      <c r="AA868" t="n">
+        <v>11.63437480163574</v>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D869" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E869" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F869" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G869" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H869" t="n">
+        <v>1</v>
+      </c>
+      <c r="I869" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J869" t="n">
+        <v>30</v>
+      </c>
+      <c r="K869" t="n">
+        <v>9</v>
+      </c>
+      <c r="L869" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M869" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N869" s="2" t="n">
+        <v>45839.36131964176</v>
+      </c>
+      <c r="O869" t="n">
+        <v>45.18</v>
+      </c>
+      <c r="P869" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q869" t="n">
+        <v>1</v>
+      </c>
+      <c r="R869" t="n">
+        <v>45.18</v>
+      </c>
+      <c r="S869" t="n">
+        <v>1355.4</v>
+      </c>
+      <c r="T869" t="n">
+        <v>1355.4</v>
+      </c>
+      <c r="U869" t="n">
+        <v>42.174</v>
+      </c>
+      <c r="V869" t="n">
+        <v>-0.01094570928196148</v>
+      </c>
+      <c r="W869" t="n">
+        <v>-0.01094570928196148</v>
+      </c>
+      <c r="X869" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y869" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z869" t="n">
+        <v>0.468702644109726</v>
+      </c>
+      <c r="AA869" t="n">
+        <v>9.620825290679932</v>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>MHY271836006</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="D870" t="inlineStr">
+        <is>
+          <t>GLOBAL SHIP LEA. A DL-,01</t>
+        </is>
+      </c>
+      <c r="E870" s="2" t="n">
+        <v>45838.31344841435</v>
+      </c>
+      <c r="F870" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="G870" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H870" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="I870" t="n">
+        <v>22.64505496285648</v>
+      </c>
+      <c r="J870" t="n">
+        <v>66</v>
+      </c>
+      <c r="K870" t="n">
+        <v>10</v>
+      </c>
+      <c r="L870" t="n">
+        <v>0.5395355224609375</v>
+      </c>
+      <c r="M870" t="n">
+        <v>12.45218944549561</v>
+      </c>
+      <c r="N870" s="2" t="n">
+        <v>45839.36131964176</v>
+      </c>
+      <c r="O870" t="n">
+        <v>26.31</v>
+      </c>
+      <c r="P870" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q870" t="n">
+        <v>1.1800802</v>
+      </c>
+      <c r="R870" t="n">
+        <v>22.29509485880705</v>
+      </c>
+      <c r="S870" t="n">
+        <v>1736.46</v>
+      </c>
+      <c r="T870" t="n">
+        <v>1471.476260681266</v>
+      </c>
+      <c r="U870" t="n">
+        <v>20.40206509457079</v>
+      </c>
+      <c r="V870" t="n">
+        <v>-0.009412650602409589</v>
+      </c>
+      <c r="W870" t="n">
+        <v>-0.01545415123184513</v>
+      </c>
+      <c r="X870" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y870" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z870" t="n">
+        <v>0.358627051115036</v>
+      </c>
+      <c r="AA870" t="n">
+        <v>9.922716617584229</v>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>PAP310761054</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>COPA HOLDINGS CL.A O.N.</t>
+        </is>
+      </c>
+      <c r="E871" s="2" t="n">
+        <v>45839.31381715278</v>
+      </c>
+      <c r="F871" t="n">
+        <v>109.97</v>
+      </c>
+      <c r="G871" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H871" t="n">
+        <v>1.1788282</v>
+      </c>
+      <c r="I871" t="n">
+        <v>93.2875545393298</v>
+      </c>
+      <c r="J871" t="n">
+        <v>16</v>
+      </c>
+      <c r="K871" t="n">
+        <v>10</v>
+      </c>
+      <c r="L871" t="n">
+        <v>0.4318655133247375</v>
+      </c>
+      <c r="M871" t="n">
+        <v>11.16087436676025</v>
+      </c>
+      <c r="N871" s="2" t="n">
+        <v>45839.36131964176</v>
+      </c>
+      <c r="O871" t="n">
+        <v>109.97</v>
+      </c>
+      <c r="P871" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q871" t="n">
+        <v>1.1800802</v>
+      </c>
+      <c r="R871" t="n">
+        <v>93.18858158962416</v>
+      </c>
+      <c r="S871" t="n">
+        <v>1759.52</v>
+      </c>
+      <c r="T871" t="n">
+        <v>1491.017305433987</v>
+      </c>
+      <c r="U871" t="n">
+        <v>83.95879908539682</v>
+      </c>
+      <c r="V871" t="n">
+        <v>0</v>
+      </c>
+      <c r="W871" t="n">
+        <v>-0.001060944840867384</v>
+      </c>
+      <c r="X871" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y871" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z871" t="n">
+        <v>0.4318655133247375</v>
+      </c>
+      <c r="AA871" t="n">
         <v>11.16087436676025</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA871"/>
+  <dimension ref="A1:AA878"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81763,7 +81763,7 @@
         <v>100</v>
       </c>
       <c r="N865" s="2" t="n">
-        <v>45839.36131964176</v>
+        <v>45839.3613196412</v>
       </c>
       <c r="O865" t="n">
         <v>1</v>
@@ -81854,7 +81854,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N866" s="2" t="n">
-        <v>45839.36131964176</v>
+        <v>45839.3613196412</v>
       </c>
       <c r="O866" t="n">
         <v>365.55</v>
@@ -81949,7 +81949,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N867" s="2" t="n">
-        <v>45839.36131964176</v>
+        <v>45839.3613196412</v>
       </c>
       <c r="O867" t="n">
         <v>13.97</v>
@@ -82040,7 +82040,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N868" s="2" t="n">
-        <v>45839.36131964176</v>
+        <v>45839.3613196412</v>
       </c>
       <c r="O868" t="n">
         <v>39.35</v>
@@ -82135,7 +82135,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N869" s="2" t="n">
-        <v>45839.36131964176</v>
+        <v>45839.3613196412</v>
       </c>
       <c r="O869" t="n">
         <v>45.18</v>
@@ -82230,7 +82230,7 @@
         <v>12.45218944549561</v>
       </c>
       <c r="N870" s="2" t="n">
-        <v>45839.36131964176</v>
+        <v>45839.3613196412</v>
       </c>
       <c r="O870" t="n">
         <v>26.31</v>
@@ -82325,7 +82325,7 @@
         <v>11.16087436676025</v>
       </c>
       <c r="N871" s="2" t="n">
-        <v>45839.36131964176</v>
+        <v>45839.3613196412</v>
       </c>
       <c r="O871" t="n">
         <v>109.97</v>
@@ -82366,6 +82366,665 @@
         <v>0.4318655133247375</v>
       </c>
       <c r="AA871" t="n">
+        <v>11.16087436676025</v>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D872" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E872" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F872" t="n">
+        <v>1</v>
+      </c>
+      <c r="G872" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H872" t="n">
+        <v>1</v>
+      </c>
+      <c r="I872" t="n">
+        <v>1</v>
+      </c>
+      <c r="J872" t="n">
+        <v>1</v>
+      </c>
+      <c r="K872" t="n">
+        <v>100</v>
+      </c>
+      <c r="L872" t="n">
+        <v>100</v>
+      </c>
+      <c r="M872" t="n">
+        <v>100</v>
+      </c>
+      <c r="N872" s="2" t="n">
+        <v>45839.3990298189</v>
+      </c>
+      <c r="O872" t="n">
+        <v>1</v>
+      </c>
+      <c r="P872" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q872" t="n">
+        <v>1</v>
+      </c>
+      <c r="R872" t="n">
+        <v>1</v>
+      </c>
+      <c r="S872" t="n">
+        <v>0</v>
+      </c>
+      <c r="T872" t="n">
+        <v>1414.591526256027</v>
+      </c>
+      <c r="U872" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V872" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W872" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X872" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y872" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z872" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA872" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr"/>
+      <c r="D873" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E873" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F873" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G873" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H873" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I873" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J873" t="n">
+        <v>3</v>
+      </c>
+      <c r="K873" t="n">
+        <v>10</v>
+      </c>
+      <c r="L873" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M873" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N873" s="2" t="n">
+        <v>45839.3990298189</v>
+      </c>
+      <c r="O873" t="n">
+        <v>365.55</v>
+      </c>
+      <c r="P873" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q873" t="n">
+        <v>0.85831</v>
+      </c>
+      <c r="R873" t="n">
+        <v>425.8950728757675</v>
+      </c>
+      <c r="S873" t="n">
+        <v>1096.65</v>
+      </c>
+      <c r="T873" t="n">
+        <v>1277.685218627303</v>
+      </c>
+      <c r="U873" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V873" t="n">
+        <v>-0.005755223490885752</v>
+      </c>
+      <c r="W873" t="n">
+        <v>-0.01113008311386843</v>
+      </c>
+      <c r="X873" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y873" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z873" t="n">
+        <v>0.4370984435081482</v>
+      </c>
+      <c r="AA873" t="n">
+        <v>10.20819354057312</v>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E874" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F874" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G874" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H874" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I874" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J874" t="n">
+        <v>121</v>
+      </c>
+      <c r="K874" t="n">
+        <v>12</v>
+      </c>
+      <c r="L874" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M874" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N874" s="2" t="n">
+        <v>45839.3990298189</v>
+      </c>
+      <c r="O874" t="n">
+        <v>13.97</v>
+      </c>
+      <c r="P874" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q874" t="n">
+        <v>1.183152</v>
+      </c>
+      <c r="R874" t="n">
+        <v>11.807443168756</v>
+      </c>
+      <c r="S874" t="n">
+        <v>1690.37</v>
+      </c>
+      <c r="T874" t="n">
+        <v>1428.700623419476</v>
+      </c>
+      <c r="U874" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V874" t="n">
+        <v>-0.01480959097320167</v>
+      </c>
+      <c r="W874" t="n">
+        <v>-0.04212258849555695</v>
+      </c>
+      <c r="X874" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y874" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z874" t="n">
+        <v>0.3516944050788879</v>
+      </c>
+      <c r="AA874" t="n">
+        <v>9.560202062129974</v>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr"/>
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E875" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F875" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G875" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H875" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I875" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J875" t="n">
+        <v>162</v>
+      </c>
+      <c r="K875" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L875" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M875" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N875" s="2" t="n">
+        <v>45839.3990298189</v>
+      </c>
+      <c r="O875" t="n">
+        <v>39.35</v>
+      </c>
+      <c r="P875" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q875" t="n">
+        <v>4.23964</v>
+      </c>
+      <c r="R875" t="n">
+        <v>9.281448424866264</v>
+      </c>
+      <c r="S875" t="n">
+        <v>6374.7</v>
+      </c>
+      <c r="T875" t="n">
+        <v>1503.594644828335</v>
+      </c>
+      <c r="U875" t="n">
+        <v>8.495174269061048</v>
+      </c>
+      <c r="V875" t="n">
+        <v>0.003826530612244916</v>
+      </c>
+      <c r="W875" t="n">
+        <v>0.009762395714576488</v>
+      </c>
+      <c r="X875" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y875" t="n">
+        <v>10.667</v>
+      </c>
+      <c r="Z875" t="n">
+        <v>0.4341856837272644</v>
+      </c>
+      <c r="AA875" t="n">
+        <v>11.63437480163574</v>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E876" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F876" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G876" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H876" t="n">
+        <v>1</v>
+      </c>
+      <c r="I876" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J876" t="n">
+        <v>30</v>
+      </c>
+      <c r="K876" t="n">
+        <v>9</v>
+      </c>
+      <c r="L876" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M876" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N876" s="2" t="n">
+        <v>45839.3990298189</v>
+      </c>
+      <c r="O876" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="P876" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q876" t="n">
+        <v>1</v>
+      </c>
+      <c r="R876" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="S876" t="n">
+        <v>1359</v>
+      </c>
+      <c r="T876" t="n">
+        <v>1359</v>
+      </c>
+      <c r="U876" t="n">
+        <v>42.174</v>
+      </c>
+      <c r="V876" t="n">
+        <v>-0.008318739054290814</v>
+      </c>
+      <c r="W876" t="n">
+        <v>-0.008318739054290814</v>
+      </c>
+      <c r="X876" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y876" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z876" t="n">
+        <v>0.468702644109726</v>
+      </c>
+      <c r="AA876" t="n">
+        <v>9.620825290679932</v>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>MHY271836006</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="D877" t="inlineStr">
+        <is>
+          <t>GLOBAL SHIP LEA. A DL-,01</t>
+        </is>
+      </c>
+      <c r="E877" s="2" t="n">
+        <v>45838.31344841435</v>
+      </c>
+      <c r="F877" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="G877" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H877" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="I877" t="n">
+        <v>22.64505496285648</v>
+      </c>
+      <c r="J877" t="n">
+        <v>66</v>
+      </c>
+      <c r="K877" t="n">
+        <v>10</v>
+      </c>
+      <c r="L877" t="n">
+        <v>0.5395355224609375</v>
+      </c>
+      <c r="M877" t="n">
+        <v>12.45218944549561</v>
+      </c>
+      <c r="N877" s="2" t="n">
+        <v>45839.3990298189</v>
+      </c>
+      <c r="O877" t="n">
+        <v>26.31</v>
+      </c>
+      <c r="P877" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q877" t="n">
+        <v>1.183152</v>
+      </c>
+      <c r="R877" t="n">
+        <v>22.23721043450038</v>
+      </c>
+      <c r="S877" t="n">
+        <v>1736.46</v>
+      </c>
+      <c r="T877" t="n">
+        <v>1467.655888677025</v>
+      </c>
+      <c r="U877" t="n">
+        <v>20.40206509457079</v>
+      </c>
+      <c r="V877" t="n">
+        <v>-0.009412650602409589</v>
+      </c>
+      <c r="W877" t="n">
+        <v>-0.01801031302529699</v>
+      </c>
+      <c r="X877" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y877" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z877" t="n">
+        <v>0.358627051115036</v>
+      </c>
+      <c r="AA877" t="n">
+        <v>9.922716617584229</v>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>PAP310761054</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>COPA HOLDINGS CL.A O.N.</t>
+        </is>
+      </c>
+      <c r="E878" s="2" t="n">
+        <v>45839.31381715278</v>
+      </c>
+      <c r="F878" t="n">
+        <v>109.97</v>
+      </c>
+      <c r="G878" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H878" t="n">
+        <v>1.1788282</v>
+      </c>
+      <c r="I878" t="n">
+        <v>93.2875545393298</v>
+      </c>
+      <c r="J878" t="n">
+        <v>16</v>
+      </c>
+      <c r="K878" t="n">
+        <v>10</v>
+      </c>
+      <c r="L878" t="n">
+        <v>0.4318655133247375</v>
+      </c>
+      <c r="M878" t="n">
+        <v>11.16087436676025</v>
+      </c>
+      <c r="N878" s="2" t="n">
+        <v>45839.3990298189</v>
+      </c>
+      <c r="O878" t="n">
+        <v>109.97</v>
+      </c>
+      <c r="P878" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q878" t="n">
+        <v>1.183152</v>
+      </c>
+      <c r="R878" t="n">
+        <v>92.94663745655673</v>
+      </c>
+      <c r="S878" t="n">
+        <v>1759.52</v>
+      </c>
+      <c r="T878" t="n">
+        <v>1487.146199304908</v>
+      </c>
+      <c r="U878" t="n">
+        <v>83.95879908539682</v>
+      </c>
+      <c r="V878" t="n">
+        <v>0</v>
+      </c>
+      <c r="W878" t="n">
+        <v>-0.003654475502724686</v>
+      </c>
+      <c r="X878" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y878" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z878" t="n">
+        <v>0.4318655133247375</v>
+      </c>
+      <c r="AA878" t="n">
         <v>11.16087436676025</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA878"/>
+  <dimension ref="A1:AA885"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82422,7 +82422,7 @@
         <v>100</v>
       </c>
       <c r="N872" s="2" t="n">
-        <v>45839.3990298189</v>
+        <v>45839.39902981481</v>
       </c>
       <c r="O872" t="n">
         <v>1</v>
@@ -82513,7 +82513,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N873" s="2" t="n">
-        <v>45839.3990298189</v>
+        <v>45839.39902981481</v>
       </c>
       <c r="O873" t="n">
         <v>365.55</v>
@@ -82608,7 +82608,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N874" s="2" t="n">
-        <v>45839.3990298189</v>
+        <v>45839.39902981481</v>
       </c>
       <c r="O874" t="n">
         <v>13.97</v>
@@ -82699,7 +82699,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N875" s="2" t="n">
-        <v>45839.3990298189</v>
+        <v>45839.39902981481</v>
       </c>
       <c r="O875" t="n">
         <v>39.35</v>
@@ -82794,7 +82794,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N876" s="2" t="n">
-        <v>45839.3990298189</v>
+        <v>45839.39902981481</v>
       </c>
       <c r="O876" t="n">
         <v>45.3</v>
@@ -82889,7 +82889,7 @@
         <v>12.45218944549561</v>
       </c>
       <c r="N877" s="2" t="n">
-        <v>45839.3990298189</v>
+        <v>45839.39902981481</v>
       </c>
       <c r="O877" t="n">
         <v>26.31</v>
@@ -82984,7 +82984,7 @@
         <v>11.16087436676025</v>
       </c>
       <c r="N878" s="2" t="n">
-        <v>45839.3990298189</v>
+        <v>45839.39902981481</v>
       </c>
       <c r="O878" t="n">
         <v>109.97</v>
@@ -83025,6 +83025,665 @@
         <v>0.4318655133247375</v>
       </c>
       <c r="AA878" t="n">
+        <v>11.16087436676025</v>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E879" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F879" t="n">
+        <v>1</v>
+      </c>
+      <c r="G879" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H879" t="n">
+        <v>1</v>
+      </c>
+      <c r="I879" t="n">
+        <v>1</v>
+      </c>
+      <c r="J879" t="n">
+        <v>1</v>
+      </c>
+      <c r="K879" t="n">
+        <v>100</v>
+      </c>
+      <c r="L879" t="n">
+        <v>100</v>
+      </c>
+      <c r="M879" t="n">
+        <v>100</v>
+      </c>
+      <c r="N879" s="2" t="n">
+        <v>45839.44242867827</v>
+      </c>
+      <c r="O879" t="n">
+        <v>1</v>
+      </c>
+      <c r="P879" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q879" t="n">
+        <v>1</v>
+      </c>
+      <c r="R879" t="n">
+        <v>1</v>
+      </c>
+      <c r="S879" t="n">
+        <v>0</v>
+      </c>
+      <c r="T879" t="n">
+        <v>1414.591526256027</v>
+      </c>
+      <c r="U879" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V879" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W879" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X879" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y879" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z879" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA879" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr"/>
+      <c r="D880" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E880" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F880" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G880" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H880" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I880" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J880" t="n">
+        <v>3</v>
+      </c>
+      <c r="K880" t="n">
+        <v>10</v>
+      </c>
+      <c r="L880" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M880" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N880" s="2" t="n">
+        <v>45839.44242867827</v>
+      </c>
+      <c r="O880" t="n">
+        <v>380</v>
+      </c>
+      <c r="P880" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q880" t="n">
+        <v>0.8575199999999999</v>
+      </c>
+      <c r="R880" t="n">
+        <v>443.1383524582517</v>
+      </c>
+      <c r="S880" t="n">
+        <v>1140</v>
+      </c>
+      <c r="T880" t="n">
+        <v>1329.415057374755</v>
+      </c>
+      <c r="U880" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V880" t="n">
+        <v>0.0335467516713539</v>
+      </c>
+      <c r="W880" t="n">
+        <v>0.02890644591296399</v>
+      </c>
+      <c r="X880" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y880" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z880" t="n">
+        <v>0.4370984435081482</v>
+      </c>
+      <c r="AA880" t="n">
+        <v>10.20819354057312</v>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E881" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F881" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G881" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H881" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I881" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J881" t="n">
+        <v>121</v>
+      </c>
+      <c r="K881" t="n">
+        <v>12</v>
+      </c>
+      <c r="L881" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M881" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N881" s="2" t="n">
+        <v>45839.44242867827</v>
+      </c>
+      <c r="O881" t="n">
+        <v>13.97</v>
+      </c>
+      <c r="P881" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q881" t="n">
+        <v>1.1820331</v>
+      </c>
+      <c r="R881" t="n">
+        <v>11.81861996927159</v>
+      </c>
+      <c r="S881" t="n">
+        <v>1690.37</v>
+      </c>
+      <c r="T881" t="n">
+        <v>1430.053016281862</v>
+      </c>
+      <c r="U881" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V881" t="n">
+        <v>-0.01480959097320167</v>
+      </c>
+      <c r="W881" t="n">
+        <v>-0.04121587189368492</v>
+      </c>
+      <c r="X881" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y881" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z881" t="n">
+        <v>0.3516944050788879</v>
+      </c>
+      <c r="AA881" t="n">
+        <v>9.560202062129974</v>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr"/>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E882" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F882" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G882" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H882" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I882" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J882" t="n">
+        <v>162</v>
+      </c>
+      <c r="K882" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L882" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M882" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N882" s="2" t="n">
+        <v>45839.44242867827</v>
+      </c>
+      <c r="O882" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="P882" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q882" t="n">
+        <v>4.241</v>
+      </c>
+      <c r="R882" t="n">
+        <v>9.290261730723886</v>
+      </c>
+      <c r="S882" t="n">
+        <v>6382.8</v>
+      </c>
+      <c r="T882" t="n">
+        <v>1505.02240037727</v>
+      </c>
+      <c r="U882" t="n">
+        <v>8.495174269061048</v>
+      </c>
+      <c r="V882" t="n">
+        <v>0.005102040816326481</v>
+      </c>
+      <c r="W882" t="n">
+        <v>0.01072122718457802</v>
+      </c>
+      <c r="X882" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y882" t="n">
+        <v>10.667</v>
+      </c>
+      <c r="Z882" t="n">
+        <v>0.4341856837272644</v>
+      </c>
+      <c r="AA882" t="n">
+        <v>11.63437480163574</v>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D883" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E883" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F883" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G883" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H883" t="n">
+        <v>1</v>
+      </c>
+      <c r="I883" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J883" t="n">
+        <v>30</v>
+      </c>
+      <c r="K883" t="n">
+        <v>9</v>
+      </c>
+      <c r="L883" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M883" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N883" s="2" t="n">
+        <v>45839.44242867827</v>
+      </c>
+      <c r="O883" t="n">
+        <v>45.36</v>
+      </c>
+      <c r="P883" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q883" t="n">
+        <v>1</v>
+      </c>
+      <c r="R883" t="n">
+        <v>45.36</v>
+      </c>
+      <c r="S883" t="n">
+        <v>1360.8</v>
+      </c>
+      <c r="T883" t="n">
+        <v>1360.8</v>
+      </c>
+      <c r="U883" t="n">
+        <v>42.174</v>
+      </c>
+      <c r="V883" t="n">
+        <v>-0.007005253940455369</v>
+      </c>
+      <c r="W883" t="n">
+        <v>-0.007005253940455369</v>
+      </c>
+      <c r="X883" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y883" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z883" t="n">
+        <v>0.468702644109726</v>
+      </c>
+      <c r="AA883" t="n">
+        <v>9.620825290679932</v>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>MHY271836006</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>GLOBAL SHIP LEA. A DL-,01</t>
+        </is>
+      </c>
+      <c r="E884" s="2" t="n">
+        <v>45838.31344841435</v>
+      </c>
+      <c r="F884" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="G884" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H884" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="I884" t="n">
+        <v>22.64505496285648</v>
+      </c>
+      <c r="J884" t="n">
+        <v>66</v>
+      </c>
+      <c r="K884" t="n">
+        <v>10</v>
+      </c>
+      <c r="L884" t="n">
+        <v>0.5395355224609375</v>
+      </c>
+      <c r="M884" t="n">
+        <v>12.45218944549561</v>
+      </c>
+      <c r="N884" s="2" t="n">
+        <v>45839.44242867827</v>
+      </c>
+      <c r="O884" t="n">
+        <v>26.31</v>
+      </c>
+      <c r="P884" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q884" t="n">
+        <v>1.1820331</v>
+      </c>
+      <c r="R884" t="n">
+        <v>22.25825994212853</v>
+      </c>
+      <c r="S884" t="n">
+        <v>1736.46</v>
+      </c>
+      <c r="T884" t="n">
+        <v>1469.045156180483</v>
+      </c>
+      <c r="U884" t="n">
+        <v>20.40206509457079</v>
+      </c>
+      <c r="V884" t="n">
+        <v>-0.009412650602409589</v>
+      </c>
+      <c r="W884" t="n">
+        <v>-0.01708077199911406</v>
+      </c>
+      <c r="X884" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y884" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z884" t="n">
+        <v>0.358627051115036</v>
+      </c>
+      <c r="AA884" t="n">
+        <v>9.922716617584229</v>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>PAP310761054</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>COPA HOLDINGS CL.A O.N.</t>
+        </is>
+      </c>
+      <c r="E885" s="2" t="n">
+        <v>45839.31381715278</v>
+      </c>
+      <c r="F885" t="n">
+        <v>109.97</v>
+      </c>
+      <c r="G885" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H885" t="n">
+        <v>1.1788282</v>
+      </c>
+      <c r="I885" t="n">
+        <v>93.2875545393298</v>
+      </c>
+      <c r="J885" t="n">
+        <v>16</v>
+      </c>
+      <c r="K885" t="n">
+        <v>10</v>
+      </c>
+      <c r="L885" t="n">
+        <v>0.4318655133247375</v>
+      </c>
+      <c r="M885" t="n">
+        <v>11.16087436676025</v>
+      </c>
+      <c r="N885" s="2" t="n">
+        <v>45839.44242867827</v>
+      </c>
+      <c r="O885" t="n">
+        <v>109.97</v>
+      </c>
+      <c r="P885" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q885" t="n">
+        <v>1.1820331</v>
+      </c>
+      <c r="R885" t="n">
+        <v>93.03461975811</v>
+      </c>
+      <c r="S885" t="n">
+        <v>1759.52</v>
+      </c>
+      <c r="T885" t="n">
+        <v>1488.55391612976</v>
+      </c>
+      <c r="U885" t="n">
+        <v>83.95879908539682</v>
+      </c>
+      <c r="V885" t="n">
+        <v>0</v>
+      </c>
+      <c r="W885" t="n">
+        <v>-0.00271134539295026</v>
+      </c>
+      <c r="X885" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y885" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z885" t="n">
+        <v>0.4318655133247375</v>
+      </c>
+      <c r="AA885" t="n">
         <v>11.16087436676025</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA885"/>
+  <dimension ref="A1:AA892"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83081,7 +83081,7 @@
         <v>100</v>
       </c>
       <c r="N879" s="2" t="n">
-        <v>45839.44242867827</v>
+        <v>45839.44242868056</v>
       </c>
       <c r="O879" t="n">
         <v>1</v>
@@ -83172,7 +83172,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N880" s="2" t="n">
-        <v>45839.44242867827</v>
+        <v>45839.44242868056</v>
       </c>
       <c r="O880" t="n">
         <v>380</v>
@@ -83267,7 +83267,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N881" s="2" t="n">
-        <v>45839.44242867827</v>
+        <v>45839.44242868056</v>
       </c>
       <c r="O881" t="n">
         <v>13.97</v>
@@ -83358,7 +83358,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N882" s="2" t="n">
-        <v>45839.44242867827</v>
+        <v>45839.44242868056</v>
       </c>
       <c r="O882" t="n">
         <v>39.4</v>
@@ -83453,7 +83453,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N883" s="2" t="n">
-        <v>45839.44242867827</v>
+        <v>45839.44242868056</v>
       </c>
       <c r="O883" t="n">
         <v>45.36</v>
@@ -83548,7 +83548,7 @@
         <v>12.45218944549561</v>
       </c>
       <c r="N884" s="2" t="n">
-        <v>45839.44242867827</v>
+        <v>45839.44242868056</v>
       </c>
       <c r="O884" t="n">
         <v>26.31</v>
@@ -83643,7 +83643,7 @@
         <v>11.16087436676025</v>
       </c>
       <c r="N885" s="2" t="n">
-        <v>45839.44242867827</v>
+        <v>45839.44242868056</v>
       </c>
       <c r="O885" t="n">
         <v>109.97</v>
@@ -83684,6 +83684,665 @@
         <v>0.4318655133247375</v>
       </c>
       <c r="AA885" t="n">
+        <v>11.16087436676025</v>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E886" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F886" t="n">
+        <v>1</v>
+      </c>
+      <c r="G886" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H886" t="n">
+        <v>1</v>
+      </c>
+      <c r="I886" t="n">
+        <v>1</v>
+      </c>
+      <c r="J886" t="n">
+        <v>1</v>
+      </c>
+      <c r="K886" t="n">
+        <v>100</v>
+      </c>
+      <c r="L886" t="n">
+        <v>100</v>
+      </c>
+      <c r="M886" t="n">
+        <v>100</v>
+      </c>
+      <c r="N886" s="2" t="n">
+        <v>45839.47699291607</v>
+      </c>
+      <c r="O886" t="n">
+        <v>1</v>
+      </c>
+      <c r="P886" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q886" t="n">
+        <v>1</v>
+      </c>
+      <c r="R886" t="n">
+        <v>1</v>
+      </c>
+      <c r="S886" t="n">
+        <v>0</v>
+      </c>
+      <c r="T886" t="n">
+        <v>1414.591526256027</v>
+      </c>
+      <c r="U886" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V886" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W886" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X886" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y886" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z886" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA886" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr"/>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E887" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F887" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G887" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H887" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I887" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J887" t="n">
+        <v>3</v>
+      </c>
+      <c r="K887" t="n">
+        <v>10</v>
+      </c>
+      <c r="L887" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M887" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N887" s="2" t="n">
+        <v>45839.47699291607</v>
+      </c>
+      <c r="O887" t="n">
+        <v>380</v>
+      </c>
+      <c r="P887" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q887" t="n">
+        <v>0.85763</v>
+      </c>
+      <c r="R887" t="n">
+        <v>443.0815153387825</v>
+      </c>
+      <c r="S887" t="n">
+        <v>1140</v>
+      </c>
+      <c r="T887" t="n">
+        <v>1329.244546016347</v>
+      </c>
+      <c r="U887" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V887" t="n">
+        <v>0.0335467516713539</v>
+      </c>
+      <c r="W887" t="n">
+        <v>0.0287744779208805</v>
+      </c>
+      <c r="X887" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y887" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z887" t="n">
+        <v>0.4370984435081482</v>
+      </c>
+      <c r="AA887" t="n">
+        <v>10.20819354057312</v>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E888" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F888" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G888" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H888" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I888" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J888" t="n">
+        <v>121</v>
+      </c>
+      <c r="K888" t="n">
+        <v>12</v>
+      </c>
+      <c r="L888" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M888" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N888" s="2" t="n">
+        <v>45839.47699291607</v>
+      </c>
+      <c r="O888" t="n">
+        <v>13.97</v>
+      </c>
+      <c r="P888" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q888" t="n">
+        <v>1.1811954</v>
+      </c>
+      <c r="R888" t="n">
+        <v>11.82700169675568</v>
+      </c>
+      <c r="S888" t="n">
+        <v>1690.37</v>
+      </c>
+      <c r="T888" t="n">
+        <v>1431.067205307437</v>
+      </c>
+      <c r="U888" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V888" t="n">
+        <v>-0.01480959097320167</v>
+      </c>
+      <c r="W888" t="n">
+        <v>-0.04053590525639983</v>
+      </c>
+      <c r="X888" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y888" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z888" t="n">
+        <v>0.3516944050788879</v>
+      </c>
+      <c r="AA888" t="n">
+        <v>9.560202062129974</v>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C889" t="inlineStr"/>
+      <c r="D889" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E889" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F889" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G889" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H889" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I889" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J889" t="n">
+        <v>162</v>
+      </c>
+      <c r="K889" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L889" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M889" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N889" s="2" t="n">
+        <v>45839.47699291607</v>
+      </c>
+      <c r="O889" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="P889" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q889" t="n">
+        <v>4.24132</v>
+      </c>
+      <c r="R889" t="n">
+        <v>9.289560797110333</v>
+      </c>
+      <c r="S889" t="n">
+        <v>6382.8</v>
+      </c>
+      <c r="T889" t="n">
+        <v>1504.908849131874</v>
+      </c>
+      <c r="U889" t="n">
+        <v>8.495174269061048</v>
+      </c>
+      <c r="V889" t="n">
+        <v>0.005102040816326481</v>
+      </c>
+      <c r="W889" t="n">
+        <v>0.01064497007766341</v>
+      </c>
+      <c r="X889" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y889" t="n">
+        <v>10.667</v>
+      </c>
+      <c r="Z889" t="n">
+        <v>0.4341856837272644</v>
+      </c>
+      <c r="AA889" t="n">
+        <v>11.63437480163574</v>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E890" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F890" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G890" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H890" t="n">
+        <v>1</v>
+      </c>
+      <c r="I890" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J890" t="n">
+        <v>30</v>
+      </c>
+      <c r="K890" t="n">
+        <v>9</v>
+      </c>
+      <c r="L890" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M890" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N890" s="2" t="n">
+        <v>45839.47699291607</v>
+      </c>
+      <c r="O890" t="n">
+        <v>45.36</v>
+      </c>
+      <c r="P890" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q890" t="n">
+        <v>1</v>
+      </c>
+      <c r="R890" t="n">
+        <v>45.36</v>
+      </c>
+      <c r="S890" t="n">
+        <v>1360.8</v>
+      </c>
+      <c r="T890" t="n">
+        <v>1360.8</v>
+      </c>
+      <c r="U890" t="n">
+        <v>42.174</v>
+      </c>
+      <c r="V890" t="n">
+        <v>-0.007005253940455369</v>
+      </c>
+      <c r="W890" t="n">
+        <v>-0.007005253940455369</v>
+      </c>
+      <c r="X890" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y890" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z890" t="n">
+        <v>0.468702644109726</v>
+      </c>
+      <c r="AA890" t="n">
+        <v>9.620825290679932</v>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>MHY271836006</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="C891" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>GLOBAL SHIP LEA. A DL-,01</t>
+        </is>
+      </c>
+      <c r="E891" s="2" t="n">
+        <v>45838.31344841435</v>
+      </c>
+      <c r="F891" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="G891" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H891" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="I891" t="n">
+        <v>22.64505496285648</v>
+      </c>
+      <c r="J891" t="n">
+        <v>66</v>
+      </c>
+      <c r="K891" t="n">
+        <v>10</v>
+      </c>
+      <c r="L891" t="n">
+        <v>0.5395355224609375</v>
+      </c>
+      <c r="M891" t="n">
+        <v>12.45218944549561</v>
+      </c>
+      <c r="N891" s="2" t="n">
+        <v>45839.47699291607</v>
+      </c>
+      <c r="O891" t="n">
+        <v>26.31</v>
+      </c>
+      <c r="P891" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q891" t="n">
+        <v>1.1811954</v>
+      </c>
+      <c r="R891" t="n">
+        <v>22.27404542889347</v>
+      </c>
+      <c r="S891" t="n">
+        <v>1736.46</v>
+      </c>
+      <c r="T891" t="n">
+        <v>1470.086998306969</v>
+      </c>
+      <c r="U891" t="n">
+        <v>20.40206509457079</v>
+      </c>
+      <c r="V891" t="n">
+        <v>-0.009412650602409589</v>
+      </c>
+      <c r="W891" t="n">
+        <v>-0.01638368882617236</v>
+      </c>
+      <c r="X891" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y891" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z891" t="n">
+        <v>0.358627051115036</v>
+      </c>
+      <c r="AA891" t="n">
+        <v>9.922716617584229</v>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>PAP310761054</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="D892" t="inlineStr">
+        <is>
+          <t>COPA HOLDINGS CL.A O.N.</t>
+        </is>
+      </c>
+      <c r="E892" s="2" t="n">
+        <v>45839.31381715278</v>
+      </c>
+      <c r="F892" t="n">
+        <v>109.97</v>
+      </c>
+      <c r="G892" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H892" t="n">
+        <v>1.1788282</v>
+      </c>
+      <c r="I892" t="n">
+        <v>93.2875545393298</v>
+      </c>
+      <c r="J892" t="n">
+        <v>16</v>
+      </c>
+      <c r="K892" t="n">
+        <v>10</v>
+      </c>
+      <c r="L892" t="n">
+        <v>0.4318655133247375</v>
+      </c>
+      <c r="M892" t="n">
+        <v>11.16087436676025</v>
+      </c>
+      <c r="N892" s="2" t="n">
+        <v>45839.47699291607</v>
+      </c>
+      <c r="O892" t="n">
+        <v>109.97</v>
+      </c>
+      <c r="P892" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q892" t="n">
+        <v>1.1811954</v>
+      </c>
+      <c r="R892" t="n">
+        <v>93.10059961290062</v>
+      </c>
+      <c r="S892" t="n">
+        <v>1759.52</v>
+      </c>
+      <c r="T892" t="n">
+        <v>1489.60959380641</v>
+      </c>
+      <c r="U892" t="n">
+        <v>83.95879908539682</v>
+      </c>
+      <c r="V892" t="n">
+        <v>0</v>
+      </c>
+      <c r="W892" t="n">
+        <v>-0.002004071468615476</v>
+      </c>
+      <c r="X892" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y892" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z892" t="n">
+        <v>0.4318655133247375</v>
+      </c>
+      <c r="AA892" t="n">
         <v>11.16087436676025</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA892"/>
+  <dimension ref="A1:AA899"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83740,7 +83740,7 @@
         <v>100</v>
       </c>
       <c r="N886" s="2" t="n">
-        <v>45839.47699291607</v>
+        <v>45839.47699291667</v>
       </c>
       <c r="O886" t="n">
         <v>1</v>
@@ -83831,7 +83831,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N887" s="2" t="n">
-        <v>45839.47699291607</v>
+        <v>45839.47699291667</v>
       </c>
       <c r="O887" t="n">
         <v>380</v>
@@ -83926,7 +83926,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N888" s="2" t="n">
-        <v>45839.47699291607</v>
+        <v>45839.47699291667</v>
       </c>
       <c r="O888" t="n">
         <v>13.97</v>
@@ -84017,7 +84017,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N889" s="2" t="n">
-        <v>45839.47699291607</v>
+        <v>45839.47699291667</v>
       </c>
       <c r="O889" t="n">
         <v>39.4</v>
@@ -84112,7 +84112,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N890" s="2" t="n">
-        <v>45839.47699291607</v>
+        <v>45839.47699291667</v>
       </c>
       <c r="O890" t="n">
         <v>45.36</v>
@@ -84207,7 +84207,7 @@
         <v>12.45218944549561</v>
       </c>
       <c r="N891" s="2" t="n">
-        <v>45839.47699291607</v>
+        <v>45839.47699291667</v>
       </c>
       <c r="O891" t="n">
         <v>26.31</v>
@@ -84302,7 +84302,7 @@
         <v>11.16087436676025</v>
       </c>
       <c r="N892" s="2" t="n">
-        <v>45839.47699291607</v>
+        <v>45839.47699291667</v>
       </c>
       <c r="O892" t="n">
         <v>109.97</v>
@@ -84343,6 +84343,665 @@
         <v>0.4318655133247375</v>
       </c>
       <c r="AA892" t="n">
+        <v>11.16087436676025</v>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E893" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F893" t="n">
+        <v>1</v>
+      </c>
+      <c r="G893" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H893" t="n">
+        <v>1</v>
+      </c>
+      <c r="I893" t="n">
+        <v>1</v>
+      </c>
+      <c r="J893" t="n">
+        <v>1</v>
+      </c>
+      <c r="K893" t="n">
+        <v>100</v>
+      </c>
+      <c r="L893" t="n">
+        <v>100</v>
+      </c>
+      <c r="M893" t="n">
+        <v>100</v>
+      </c>
+      <c r="N893" s="2" t="n">
+        <v>45839.54189306686</v>
+      </c>
+      <c r="O893" t="n">
+        <v>1</v>
+      </c>
+      <c r="P893" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q893" t="n">
+        <v>1</v>
+      </c>
+      <c r="R893" t="n">
+        <v>1</v>
+      </c>
+      <c r="S893" t="n">
+        <v>0</v>
+      </c>
+      <c r="T893" t="n">
+        <v>1414.591526256027</v>
+      </c>
+      <c r="U893" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V893" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W893" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X893" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y893" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z893" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA893" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr"/>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E894" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F894" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G894" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H894" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I894" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J894" t="n">
+        <v>3</v>
+      </c>
+      <c r="K894" t="n">
+        <v>10</v>
+      </c>
+      <c r="L894" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M894" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N894" s="2" t="n">
+        <v>45839.54189306686</v>
+      </c>
+      <c r="O894" t="n">
+        <v>380</v>
+      </c>
+      <c r="P894" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q894" t="n">
+        <v>0.85892</v>
+      </c>
+      <c r="R894" t="n">
+        <v>442.4160573743771</v>
+      </c>
+      <c r="S894" t="n">
+        <v>1140</v>
+      </c>
+      <c r="T894" t="n">
+        <v>1327.248172123131</v>
+      </c>
+      <c r="U894" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V894" t="n">
+        <v>0.0335467516713539</v>
+      </c>
+      <c r="W894" t="n">
+        <v>0.02722937584325047</v>
+      </c>
+      <c r="X894" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y894" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z894" t="n">
+        <v>0.4370984435081482</v>
+      </c>
+      <c r="AA894" t="n">
+        <v>10.20819354057312</v>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E895" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F895" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G895" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H895" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I895" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J895" t="n">
+        <v>121</v>
+      </c>
+      <c r="K895" t="n">
+        <v>12</v>
+      </c>
+      <c r="L895" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M895" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N895" s="2" t="n">
+        <v>45839.54189306686</v>
+      </c>
+      <c r="O895" t="n">
+        <v>13.97</v>
+      </c>
+      <c r="P895" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q895" t="n">
+        <v>1.1806376</v>
+      </c>
+      <c r="R895" t="n">
+        <v>11.83258944150178</v>
+      </c>
+      <c r="S895" t="n">
+        <v>1690.37</v>
+      </c>
+      <c r="T895" t="n">
+        <v>1431.743322421715</v>
+      </c>
+      <c r="U895" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V895" t="n">
+        <v>-0.01480959097320167</v>
+      </c>
+      <c r="W895" t="n">
+        <v>-0.0400826001337713</v>
+      </c>
+      <c r="X895" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y895" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z895" t="n">
+        <v>0.3516944050788879</v>
+      </c>
+      <c r="AA895" t="n">
+        <v>9.560202062129974</v>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C896" t="inlineStr"/>
+      <c r="D896" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E896" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F896" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G896" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H896" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I896" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J896" t="n">
+        <v>162</v>
+      </c>
+      <c r="K896" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L896" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M896" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N896" s="2" t="n">
+        <v>45839.54189306686</v>
+      </c>
+      <c r="O896" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="P896" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q896" t="n">
+        <v>4.24194</v>
+      </c>
+      <c r="R896" t="n">
+        <v>9.264628919786702</v>
+      </c>
+      <c r="S896" t="n">
+        <v>6366.599999999999</v>
+      </c>
+      <c r="T896" t="n">
+        <v>1500.869885005446</v>
+      </c>
+      <c r="U896" t="n">
+        <v>8.495174269061048</v>
+      </c>
+      <c r="V896" t="n">
+        <v>0.002551020408163129</v>
+      </c>
+      <c r="W896" t="n">
+        <v>0.007932540829171941</v>
+      </c>
+      <c r="X896" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y896" t="n">
+        <v>10.667</v>
+      </c>
+      <c r="Z896" t="n">
+        <v>0.4341856837272644</v>
+      </c>
+      <c r="AA896" t="n">
+        <v>11.63437480163574</v>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D897" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E897" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F897" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G897" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H897" t="n">
+        <v>1</v>
+      </c>
+      <c r="I897" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J897" t="n">
+        <v>30</v>
+      </c>
+      <c r="K897" t="n">
+        <v>9</v>
+      </c>
+      <c r="L897" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M897" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N897" s="2" t="n">
+        <v>45839.54189306686</v>
+      </c>
+      <c r="O897" t="n">
+        <v>45.38</v>
+      </c>
+      <c r="P897" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q897" t="n">
+        <v>1</v>
+      </c>
+      <c r="R897" t="n">
+        <v>45.38</v>
+      </c>
+      <c r="S897" t="n">
+        <v>1361.4</v>
+      </c>
+      <c r="T897" t="n">
+        <v>1361.4</v>
+      </c>
+      <c r="U897" t="n">
+        <v>42.174</v>
+      </c>
+      <c r="V897" t="n">
+        <v>-0.006567425569176777</v>
+      </c>
+      <c r="W897" t="n">
+        <v>-0.006567425569176777</v>
+      </c>
+      <c r="X897" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y897" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z897" t="n">
+        <v>0.468702644109726</v>
+      </c>
+      <c r="AA897" t="n">
+        <v>9.620825290679932</v>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>MHY271836006</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>GLOBAL SHIP LEA. A DL-,01</t>
+        </is>
+      </c>
+      <c r="E898" s="2" t="n">
+        <v>45838.31344841435</v>
+      </c>
+      <c r="F898" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="G898" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H898" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="I898" t="n">
+        <v>22.64505496285648</v>
+      </c>
+      <c r="J898" t="n">
+        <v>66</v>
+      </c>
+      <c r="K898" t="n">
+        <v>10</v>
+      </c>
+      <c r="L898" t="n">
+        <v>0.5395355224609375</v>
+      </c>
+      <c r="M898" t="n">
+        <v>12.45218944549561</v>
+      </c>
+      <c r="N898" s="2" t="n">
+        <v>45839.54189306686</v>
+      </c>
+      <c r="O898" t="n">
+        <v>26.31</v>
+      </c>
+      <c r="P898" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q898" t="n">
+        <v>1.1806376</v>
+      </c>
+      <c r="R898" t="n">
+        <v>22.28456894816834</v>
+      </c>
+      <c r="S898" t="n">
+        <v>1736.46</v>
+      </c>
+      <c r="T898" t="n">
+        <v>1470.781550579111</v>
+      </c>
+      <c r="U898" t="n">
+        <v>20.40206509457079</v>
+      </c>
+      <c r="V898" t="n">
+        <v>-0.009412650602409589</v>
+      </c>
+      <c r="W898" t="n">
+        <v>-0.0159189728300253</v>
+      </c>
+      <c r="X898" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y898" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z898" t="n">
+        <v>0.358627051115036</v>
+      </c>
+      <c r="AA898" t="n">
+        <v>9.922716617584229</v>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>PAP310761054</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>COPA HOLDINGS CL.A O.N.</t>
+        </is>
+      </c>
+      <c r="E899" s="2" t="n">
+        <v>45839.31381715278</v>
+      </c>
+      <c r="F899" t="n">
+        <v>109.97</v>
+      </c>
+      <c r="G899" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H899" t="n">
+        <v>1.1788282</v>
+      </c>
+      <c r="I899" t="n">
+        <v>93.2875545393298</v>
+      </c>
+      <c r="J899" t="n">
+        <v>16</v>
+      </c>
+      <c r="K899" t="n">
+        <v>10</v>
+      </c>
+      <c r="L899" t="n">
+        <v>0.4318655133247375</v>
+      </c>
+      <c r="M899" t="n">
+        <v>11.16087436676025</v>
+      </c>
+      <c r="N899" s="2" t="n">
+        <v>45839.54189306686</v>
+      </c>
+      <c r="O899" t="n">
+        <v>109.97</v>
+      </c>
+      <c r="P899" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q899" t="n">
+        <v>1.1806376</v>
+      </c>
+      <c r="R899" t="n">
+        <v>93.14458560357555</v>
+      </c>
+      <c r="S899" t="n">
+        <v>1759.52</v>
+      </c>
+      <c r="T899" t="n">
+        <v>1490.313369657209</v>
+      </c>
+      <c r="U899" t="n">
+        <v>83.95879908539682</v>
+      </c>
+      <c r="V899" t="n">
+        <v>0</v>
+      </c>
+      <c r="W899" t="n">
+        <v>-0.001532561727663029</v>
+      </c>
+      <c r="X899" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y899" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z899" t="n">
+        <v>0.4318655133247375</v>
+      </c>
+      <c r="AA899" t="n">
         <v>11.16087436676025</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA899"/>
+  <dimension ref="A1:AA906"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84399,7 +84399,7 @@
         <v>100</v>
       </c>
       <c r="N893" s="2" t="n">
-        <v>45839.54189306686</v>
+        <v>45839.54189306713</v>
       </c>
       <c r="O893" t="n">
         <v>1</v>
@@ -84490,7 +84490,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N894" s="2" t="n">
-        <v>45839.54189306686</v>
+        <v>45839.54189306713</v>
       </c>
       <c r="O894" t="n">
         <v>380</v>
@@ -84585,7 +84585,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N895" s="2" t="n">
-        <v>45839.54189306686</v>
+        <v>45839.54189306713</v>
       </c>
       <c r="O895" t="n">
         <v>13.97</v>
@@ -84676,7 +84676,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N896" s="2" t="n">
-        <v>45839.54189306686</v>
+        <v>45839.54189306713</v>
       </c>
       <c r="O896" t="n">
         <v>39.3</v>
@@ -84771,7 +84771,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N897" s="2" t="n">
-        <v>45839.54189306686</v>
+        <v>45839.54189306713</v>
       </c>
       <c r="O897" t="n">
         <v>45.38</v>
@@ -84866,7 +84866,7 @@
         <v>12.45218944549561</v>
       </c>
       <c r="N898" s="2" t="n">
-        <v>45839.54189306686</v>
+        <v>45839.54189306713</v>
       </c>
       <c r="O898" t="n">
         <v>26.31</v>
@@ -84961,7 +84961,7 @@
         <v>11.16087436676025</v>
       </c>
       <c r="N899" s="2" t="n">
-        <v>45839.54189306686</v>
+        <v>45839.54189306713</v>
       </c>
       <c r="O899" t="n">
         <v>109.97</v>
@@ -85002,6 +85002,665 @@
         <v>0.4318655133247375</v>
       </c>
       <c r="AA899" t="n">
+        <v>11.16087436676025</v>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E900" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F900" t="n">
+        <v>1</v>
+      </c>
+      <c r="G900" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H900" t="n">
+        <v>1</v>
+      </c>
+      <c r="I900" t="n">
+        <v>1</v>
+      </c>
+      <c r="J900" t="n">
+        <v>1</v>
+      </c>
+      <c r="K900" t="n">
+        <v>100</v>
+      </c>
+      <c r="L900" t="n">
+        <v>100</v>
+      </c>
+      <c r="M900" t="n">
+        <v>100</v>
+      </c>
+      <c r="N900" s="2" t="n">
+        <v>45839.57170062756</v>
+      </c>
+      <c r="O900" t="n">
+        <v>1</v>
+      </c>
+      <c r="P900" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q900" t="n">
+        <v>1</v>
+      </c>
+      <c r="R900" t="n">
+        <v>1</v>
+      </c>
+      <c r="S900" t="n">
+        <v>0</v>
+      </c>
+      <c r="T900" t="n">
+        <v>1414.591526256027</v>
+      </c>
+      <c r="U900" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V900" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W900" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X900" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y900" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z900" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA900" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr"/>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E901" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F901" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G901" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H901" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I901" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J901" t="n">
+        <v>3</v>
+      </c>
+      <c r="K901" t="n">
+        <v>10</v>
+      </c>
+      <c r="L901" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M901" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N901" s="2" t="n">
+        <v>45839.57170062756</v>
+      </c>
+      <c r="O901" t="n">
+        <v>365.75</v>
+      </c>
+      <c r="P901" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q901" t="n">
+        <v>0.85914</v>
+      </c>
+      <c r="R901" t="n">
+        <v>425.7164140885071</v>
+      </c>
+      <c r="S901" t="n">
+        <v>1097.25</v>
+      </c>
+      <c r="T901" t="n">
+        <v>1277.149242265521</v>
+      </c>
+      <c r="U901" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V901" t="n">
+        <v>-0.005211251516321846</v>
+      </c>
+      <c r="W901" t="n">
+        <v>-0.01154490430190469</v>
+      </c>
+      <c r="X901" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y901" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z901" t="n">
+        <v>0.4370984435081482</v>
+      </c>
+      <c r="AA901" t="n">
+        <v>10.20819354057312</v>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D902" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E902" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F902" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G902" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H902" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I902" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J902" t="n">
+        <v>121</v>
+      </c>
+      <c r="K902" t="n">
+        <v>12</v>
+      </c>
+      <c r="L902" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M902" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N902" s="2" t="n">
+        <v>45839.57170062756</v>
+      </c>
+      <c r="O902" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="P902" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q902" t="n">
+        <v>1.1806376</v>
+      </c>
+      <c r="R902" t="n">
+        <v>12.11209942830891</v>
+      </c>
+      <c r="S902" t="n">
+        <v>1730.3</v>
+      </c>
+      <c r="T902" t="n">
+        <v>1465.564030825378</v>
+      </c>
+      <c r="U902" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V902" t="n">
+        <v>0.008462623413258097</v>
+      </c>
+      <c r="W902" t="n">
+        <v>-0.01740738596370284</v>
+      </c>
+      <c r="X902" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y902" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z902" t="n">
+        <v>0.3516944050788879</v>
+      </c>
+      <c r="AA902" t="n">
+        <v>9.560202062129974</v>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C903" t="inlineStr"/>
+      <c r="D903" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E903" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F903" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G903" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H903" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I903" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J903" t="n">
+        <v>162</v>
+      </c>
+      <c r="K903" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L903" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M903" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N903" s="2" t="n">
+        <v>45839.57170062756</v>
+      </c>
+      <c r="O903" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="P903" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q903" t="n">
+        <v>4.24366</v>
+      </c>
+      <c r="R903" t="n">
+        <v>9.237309303761377</v>
+      </c>
+      <c r="S903" t="n">
+        <v>6350.400000000001</v>
+      </c>
+      <c r="T903" t="n">
+        <v>1496.444107209343</v>
+      </c>
+      <c r="U903" t="n">
+        <v>8.495174269061048</v>
+      </c>
+      <c r="V903" t="n">
+        <v>0</v>
+      </c>
+      <c r="W903" t="n">
+        <v>0.004960340837861787</v>
+      </c>
+      <c r="X903" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y903" t="n">
+        <v>10.667</v>
+      </c>
+      <c r="Z903" t="n">
+        <v>0.4341856837272644</v>
+      </c>
+      <c r="AA903" t="n">
+        <v>11.63437480163574</v>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D904" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E904" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F904" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G904" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H904" t="n">
+        <v>1</v>
+      </c>
+      <c r="I904" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J904" t="n">
+        <v>30</v>
+      </c>
+      <c r="K904" t="n">
+        <v>9</v>
+      </c>
+      <c r="L904" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M904" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N904" s="2" t="n">
+        <v>45839.57170062756</v>
+      </c>
+      <c r="O904" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="P904" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q904" t="n">
+        <v>1</v>
+      </c>
+      <c r="R904" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="S904" t="n">
+        <v>1362</v>
+      </c>
+      <c r="T904" t="n">
+        <v>1362</v>
+      </c>
+      <c r="U904" t="n">
+        <v>42.174</v>
+      </c>
+      <c r="V904" t="n">
+        <v>-0.006129597197898407</v>
+      </c>
+      <c r="W904" t="n">
+        <v>-0.006129597197898407</v>
+      </c>
+      <c r="X904" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y904" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z904" t="n">
+        <v>0.468702644109726</v>
+      </c>
+      <c r="AA904" t="n">
+        <v>9.620825290679932</v>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>MHY271836006</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="D905" t="inlineStr">
+        <is>
+          <t>GLOBAL SHIP LEA. A DL-,01</t>
+        </is>
+      </c>
+      <c r="E905" s="2" t="n">
+        <v>45838.31344841435</v>
+      </c>
+      <c r="F905" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="G905" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H905" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="I905" t="n">
+        <v>22.64505496285648</v>
+      </c>
+      <c r="J905" t="n">
+        <v>66</v>
+      </c>
+      <c r="K905" t="n">
+        <v>10</v>
+      </c>
+      <c r="L905" t="n">
+        <v>0.5395355224609375</v>
+      </c>
+      <c r="M905" t="n">
+        <v>12.45218944549561</v>
+      </c>
+      <c r="N905" s="2" t="n">
+        <v>45839.57170062756</v>
+      </c>
+      <c r="O905" t="n">
+        <v>26.31</v>
+      </c>
+      <c r="P905" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q905" t="n">
+        <v>1.1806376</v>
+      </c>
+      <c r="R905" t="n">
+        <v>22.28456894816834</v>
+      </c>
+      <c r="S905" t="n">
+        <v>1736.46</v>
+      </c>
+      <c r="T905" t="n">
+        <v>1470.781550579111</v>
+      </c>
+      <c r="U905" t="n">
+        <v>20.40206509457079</v>
+      </c>
+      <c r="V905" t="n">
+        <v>-0.009412650602409589</v>
+      </c>
+      <c r="W905" t="n">
+        <v>-0.0159189728300253</v>
+      </c>
+      <c r="X905" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y905" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z905" t="n">
+        <v>0.358627051115036</v>
+      </c>
+      <c r="AA905" t="n">
+        <v>9.922716617584229</v>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>PAP310761054</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>COPA HOLDINGS CL.A O.N.</t>
+        </is>
+      </c>
+      <c r="E906" s="2" t="n">
+        <v>45839.31381715278</v>
+      </c>
+      <c r="F906" t="n">
+        <v>109.97</v>
+      </c>
+      <c r="G906" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H906" t="n">
+        <v>1.1788282</v>
+      </c>
+      <c r="I906" t="n">
+        <v>93.2875545393298</v>
+      </c>
+      <c r="J906" t="n">
+        <v>16</v>
+      </c>
+      <c r="K906" t="n">
+        <v>10</v>
+      </c>
+      <c r="L906" t="n">
+        <v>0.4318655133247375</v>
+      </c>
+      <c r="M906" t="n">
+        <v>11.16087436676025</v>
+      </c>
+      <c r="N906" s="2" t="n">
+        <v>45839.57170062756</v>
+      </c>
+      <c r="O906" t="n">
+        <v>109.97</v>
+      </c>
+      <c r="P906" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q906" t="n">
+        <v>1.1806376</v>
+      </c>
+      <c r="R906" t="n">
+        <v>93.14458560357555</v>
+      </c>
+      <c r="S906" t="n">
+        <v>1759.52</v>
+      </c>
+      <c r="T906" t="n">
+        <v>1490.313369657209</v>
+      </c>
+      <c r="U906" t="n">
+        <v>83.95879908539682</v>
+      </c>
+      <c r="V906" t="n">
+        <v>0</v>
+      </c>
+      <c r="W906" t="n">
+        <v>-0.001532561727663029</v>
+      </c>
+      <c r="X906" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y906" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z906" t="n">
+        <v>0.4318655133247375</v>
+      </c>
+      <c r="AA906" t="n">
         <v>11.16087436676025</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA906"/>
+  <dimension ref="A1:AA913"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85058,7 +85058,7 @@
         <v>100</v>
       </c>
       <c r="N900" s="2" t="n">
-        <v>45839.57170062756</v>
+        <v>45839.571700625</v>
       </c>
       <c r="O900" t="n">
         <v>1</v>
@@ -85149,7 +85149,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N901" s="2" t="n">
-        <v>45839.57170062756</v>
+        <v>45839.571700625</v>
       </c>
       <c r="O901" t="n">
         <v>365.75</v>
@@ -85244,7 +85244,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N902" s="2" t="n">
-        <v>45839.57170062756</v>
+        <v>45839.571700625</v>
       </c>
       <c r="O902" t="n">
         <v>14.3</v>
@@ -85335,7 +85335,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N903" s="2" t="n">
-        <v>45839.57170062756</v>
+        <v>45839.571700625</v>
       </c>
       <c r="O903" t="n">
         <v>39.2</v>
@@ -85430,7 +85430,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N904" s="2" t="n">
-        <v>45839.57170062756</v>
+        <v>45839.571700625</v>
       </c>
       <c r="O904" t="n">
         <v>45.4</v>
@@ -85525,7 +85525,7 @@
         <v>12.45218944549561</v>
       </c>
       <c r="N905" s="2" t="n">
-        <v>45839.57170062756</v>
+        <v>45839.571700625</v>
       </c>
       <c r="O905" t="n">
         <v>26.31</v>
@@ -85620,7 +85620,7 @@
         <v>11.16087436676025</v>
       </c>
       <c r="N906" s="2" t="n">
-        <v>45839.57170062756</v>
+        <v>45839.571700625</v>
       </c>
       <c r="O906" t="n">
         <v>109.97</v>
@@ -85661,6 +85661,665 @@
         <v>0.4318655133247375</v>
       </c>
       <c r="AA906" t="n">
+        <v>11.16087436676025</v>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E907" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F907" t="n">
+        <v>1</v>
+      </c>
+      <c r="G907" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H907" t="n">
+        <v>1</v>
+      </c>
+      <c r="I907" t="n">
+        <v>1</v>
+      </c>
+      <c r="J907" t="n">
+        <v>1</v>
+      </c>
+      <c r="K907" t="n">
+        <v>100</v>
+      </c>
+      <c r="L907" t="n">
+        <v>100</v>
+      </c>
+      <c r="M907" t="n">
+        <v>100</v>
+      </c>
+      <c r="N907" s="2" t="n">
+        <v>45839.60593738992</v>
+      </c>
+      <c r="O907" t="n">
+        <v>1</v>
+      </c>
+      <c r="P907" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q907" t="n">
+        <v>1</v>
+      </c>
+      <c r="R907" t="n">
+        <v>1</v>
+      </c>
+      <c r="S907" t="n">
+        <v>0</v>
+      </c>
+      <c r="T907" t="n">
+        <v>1414.591526256027</v>
+      </c>
+      <c r="U907" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V907" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W907" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X907" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y907" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z907" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA907" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr"/>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E908" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F908" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G908" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H908" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I908" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J908" t="n">
+        <v>3</v>
+      </c>
+      <c r="K908" t="n">
+        <v>10</v>
+      </c>
+      <c r="L908" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M908" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N908" s="2" t="n">
+        <v>45839.60593738992</v>
+      </c>
+      <c r="O908" t="n">
+        <v>369.5</v>
+      </c>
+      <c r="P908" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q908" t="n">
+        <v>0.85919</v>
+      </c>
+      <c r="R908" t="n">
+        <v>430.0562157380789</v>
+      </c>
+      <c r="S908" t="n">
+        <v>1108.5</v>
+      </c>
+      <c r="T908" t="n">
+        <v>1290.168647214237</v>
+      </c>
+      <c r="U908" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V908" t="n">
+        <v>0.004988223006750614</v>
+      </c>
+      <c r="W908" t="n">
+        <v>-0.001468480389468119</v>
+      </c>
+      <c r="X908" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y908" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z908" t="n">
+        <v>0.4370984435081482</v>
+      </c>
+      <c r="AA908" t="n">
+        <v>10.20819354057312</v>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E909" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F909" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G909" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H909" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I909" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J909" t="n">
+        <v>121</v>
+      </c>
+      <c r="K909" t="n">
+        <v>12</v>
+      </c>
+      <c r="L909" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M909" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N909" s="2" t="n">
+        <v>45839.60593738992</v>
+      </c>
+      <c r="O909" t="n">
+        <v>14.225</v>
+      </c>
+      <c r="P909" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q909" t="n">
+        <v>1.1796626</v>
+      </c>
+      <c r="R909" t="n">
+        <v>12.05853266857829</v>
+      </c>
+      <c r="S909" t="n">
+        <v>1721.225</v>
+      </c>
+      <c r="T909" t="n">
+        <v>1459.082452897973</v>
+      </c>
+      <c r="U909" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V909" t="n">
+        <v>0.003173483779971731</v>
+      </c>
+      <c r="W909" t="n">
+        <v>-0.02175298292488237</v>
+      </c>
+      <c r="X909" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y909" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z909" t="n">
+        <v>0.3516944050788879</v>
+      </c>
+      <c r="AA909" t="n">
+        <v>9.560202062129974</v>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr"/>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E910" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F910" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G910" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H910" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I910" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J910" t="n">
+        <v>162</v>
+      </c>
+      <c r="K910" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L910" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M910" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N910" s="2" t="n">
+        <v>45839.60593738992</v>
+      </c>
+      <c r="O910" t="n">
+        <v>39.35</v>
+      </c>
+      <c r="P910" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q910" t="n">
+        <v>4.24698</v>
+      </c>
+      <c r="R910" t="n">
+        <v>9.265407418918857</v>
+      </c>
+      <c r="S910" t="n">
+        <v>6374.7</v>
+      </c>
+      <c r="T910" t="n">
+        <v>1500.996001864855</v>
+      </c>
+      <c r="U910" t="n">
+        <v>8.495174269061048</v>
+      </c>
+      <c r="V910" t="n">
+        <v>0.003826530612244916</v>
+      </c>
+      <c r="W910" t="n">
+        <v>0.008017236569832553</v>
+      </c>
+      <c r="X910" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y910" t="n">
+        <v>10.667</v>
+      </c>
+      <c r="Z910" t="n">
+        <v>0.4341856837272644</v>
+      </c>
+      <c r="AA910" t="n">
+        <v>11.63437480163574</v>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D911" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E911" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F911" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G911" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H911" t="n">
+        <v>1</v>
+      </c>
+      <c r="I911" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J911" t="n">
+        <v>30</v>
+      </c>
+      <c r="K911" t="n">
+        <v>9</v>
+      </c>
+      <c r="L911" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M911" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N911" s="2" t="n">
+        <v>45839.60593738992</v>
+      </c>
+      <c r="O911" t="n">
+        <v>45.54</v>
+      </c>
+      <c r="P911" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q911" t="n">
+        <v>1</v>
+      </c>
+      <c r="R911" t="n">
+        <v>45.54</v>
+      </c>
+      <c r="S911" t="n">
+        <v>1366.2</v>
+      </c>
+      <c r="T911" t="n">
+        <v>1366.2</v>
+      </c>
+      <c r="U911" t="n">
+        <v>42.174</v>
+      </c>
+      <c r="V911" t="n">
+        <v>-0.003064798598949259</v>
+      </c>
+      <c r="W911" t="n">
+        <v>-0.003064798598949259</v>
+      </c>
+      <c r="X911" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y911" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z911" t="n">
+        <v>0.468702644109726</v>
+      </c>
+      <c r="AA911" t="n">
+        <v>9.620825290679932</v>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>MHY271836006</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="D912" t="inlineStr">
+        <is>
+          <t>GLOBAL SHIP LEA. A DL-,01</t>
+        </is>
+      </c>
+      <c r="E912" s="2" t="n">
+        <v>45838.31344841435</v>
+      </c>
+      <c r="F912" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="G912" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H912" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="I912" t="n">
+        <v>22.64505496285648</v>
+      </c>
+      <c r="J912" t="n">
+        <v>66</v>
+      </c>
+      <c r="K912" t="n">
+        <v>10</v>
+      </c>
+      <c r="L912" t="n">
+        <v>0.5395355224609375</v>
+      </c>
+      <c r="M912" t="n">
+        <v>12.45218944549561</v>
+      </c>
+      <c r="N912" s="2" t="n">
+        <v>45839.60593738992</v>
+      </c>
+      <c r="O912" t="n">
+        <v>26.12</v>
+      </c>
+      <c r="P912" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q912" t="n">
+        <v>1.1796626</v>
+      </c>
+      <c r="R912" t="n">
+        <v>22.14192430954411</v>
+      </c>
+      <c r="S912" t="n">
+        <v>1723.92</v>
+      </c>
+      <c r="T912" t="n">
+        <v>1461.367004429911</v>
+      </c>
+      <c r="U912" t="n">
+        <v>20.40206509457079</v>
+      </c>
+      <c r="V912" t="n">
+        <v>-0.01656626506024084</v>
+      </c>
+      <c r="W912" t="n">
+        <v>-0.02221812462533823</v>
+      </c>
+      <c r="X912" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y912" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z912" t="n">
+        <v>0.358627051115036</v>
+      </c>
+      <c r="AA912" t="n">
+        <v>9.922716617584229</v>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>PAP310761054</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="D913" t="inlineStr">
+        <is>
+          <t>COPA HOLDINGS CL.A O.N.</t>
+        </is>
+      </c>
+      <c r="E913" s="2" t="n">
+        <v>45839.31381715278</v>
+      </c>
+      <c r="F913" t="n">
+        <v>109.97</v>
+      </c>
+      <c r="G913" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H913" t="n">
+        <v>1.1788282</v>
+      </c>
+      <c r="I913" t="n">
+        <v>93.2875545393298</v>
+      </c>
+      <c r="J913" t="n">
+        <v>16</v>
+      </c>
+      <c r="K913" t="n">
+        <v>10</v>
+      </c>
+      <c r="L913" t="n">
+        <v>0.4318655133247375</v>
+      </c>
+      <c r="M913" t="n">
+        <v>11.16087436676025</v>
+      </c>
+      <c r="N913" s="2" t="n">
+        <v>45839.60593738992</v>
+      </c>
+      <c r="O913" t="n">
+        <v>109.665</v>
+      </c>
+      <c r="P913" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q913" t="n">
+        <v>1.1796626</v>
+      </c>
+      <c r="R913" t="n">
+        <v>92.96302179962306</v>
+      </c>
+      <c r="S913" t="n">
+        <v>1754.64</v>
+      </c>
+      <c r="T913" t="n">
+        <v>1487.408348793969</v>
+      </c>
+      <c r="U913" t="n">
+        <v>83.95879908539682</v>
+      </c>
+      <c r="V913" t="n">
+        <v>-0.002773483677366517</v>
+      </c>
+      <c r="W913" t="n">
+        <v>-0.003478842824311768</v>
+      </c>
+      <c r="X913" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y913" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z913" t="n">
+        <v>0.4318655133247375</v>
+      </c>
+      <c r="AA913" t="n">
         <v>11.16087436676025</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA913"/>
+  <dimension ref="A1:AA920"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85717,7 +85717,7 @@
         <v>100</v>
       </c>
       <c r="N907" s="2" t="n">
-        <v>45839.60593738992</v>
+        <v>45839.60593738426</v>
       </c>
       <c r="O907" t="n">
         <v>1</v>
@@ -85808,7 +85808,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N908" s="2" t="n">
-        <v>45839.60593738992</v>
+        <v>45839.60593738426</v>
       </c>
       <c r="O908" t="n">
         <v>369.5</v>
@@ -85903,7 +85903,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N909" s="2" t="n">
-        <v>45839.60593738992</v>
+        <v>45839.60593738426</v>
       </c>
       <c r="O909" t="n">
         <v>14.225</v>
@@ -85994,7 +85994,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N910" s="2" t="n">
-        <v>45839.60593738992</v>
+        <v>45839.60593738426</v>
       </c>
       <c r="O910" t="n">
         <v>39.35</v>
@@ -86089,7 +86089,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N911" s="2" t="n">
-        <v>45839.60593738992</v>
+        <v>45839.60593738426</v>
       </c>
       <c r="O911" t="n">
         <v>45.54</v>
@@ -86184,7 +86184,7 @@
         <v>12.45218944549561</v>
       </c>
       <c r="N912" s="2" t="n">
-        <v>45839.60593738992</v>
+        <v>45839.60593738426</v>
       </c>
       <c r="O912" t="n">
         <v>26.12</v>
@@ -86279,7 +86279,7 @@
         <v>11.16087436676025</v>
       </c>
       <c r="N913" s="2" t="n">
-        <v>45839.60593738992</v>
+        <v>45839.60593738426</v>
       </c>
       <c r="O913" t="n">
         <v>109.665</v>
@@ -86320,6 +86320,665 @@
         <v>0.4318655133247375</v>
       </c>
       <c r="AA913" t="n">
+        <v>11.16087436676025</v>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D914" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E914" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F914" t="n">
+        <v>1</v>
+      </c>
+      <c r="G914" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H914" t="n">
+        <v>1</v>
+      </c>
+      <c r="I914" t="n">
+        <v>1</v>
+      </c>
+      <c r="J914" t="n">
+        <v>1</v>
+      </c>
+      <c r="K914" t="n">
+        <v>100</v>
+      </c>
+      <c r="L914" t="n">
+        <v>100</v>
+      </c>
+      <c r="M914" t="n">
+        <v>100</v>
+      </c>
+      <c r="N914" s="2" t="n">
+        <v>45839.64758943042</v>
+      </c>
+      <c r="O914" t="n">
+        <v>1</v>
+      </c>
+      <c r="P914" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q914" t="n">
+        <v>1</v>
+      </c>
+      <c r="R914" t="n">
+        <v>1</v>
+      </c>
+      <c r="S914" t="n">
+        <v>0</v>
+      </c>
+      <c r="T914" t="n">
+        <v>1414.591526256027</v>
+      </c>
+      <c r="U914" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V914" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W914" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X914" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y914" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z914" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA914" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr"/>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E915" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F915" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G915" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H915" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I915" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J915" t="n">
+        <v>3</v>
+      </c>
+      <c r="K915" t="n">
+        <v>10</v>
+      </c>
+      <c r="L915" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M915" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N915" s="2" t="n">
+        <v>45839.64758943042</v>
+      </c>
+      <c r="O915" t="n">
+        <v>365</v>
+      </c>
+      <c r="P915" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q915" t="n">
+        <v>0.85884</v>
+      </c>
+      <c r="R915" t="n">
+        <v>424.99184947138</v>
+      </c>
+      <c r="S915" t="n">
+        <v>1095</v>
+      </c>
+      <c r="T915" t="n">
+        <v>1274.97554841414</v>
+      </c>
+      <c r="U915" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V915" t="n">
+        <v>-0.007251146420936383</v>
+      </c>
+      <c r="W915" t="n">
+        <v>-0.01322724391639984</v>
+      </c>
+      <c r="X915" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y915" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z915" t="n">
+        <v>0.4370984435081482</v>
+      </c>
+      <c r="AA915" t="n">
+        <v>10.20819354057312</v>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E916" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F916" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G916" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H916" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I916" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J916" t="n">
+        <v>121</v>
+      </c>
+      <c r="K916" t="n">
+        <v>12</v>
+      </c>
+      <c r="L916" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M916" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N916" s="2" t="n">
+        <v>45839.64758943042</v>
+      </c>
+      <c r="O916" t="n">
+        <v>14.085</v>
+      </c>
+      <c r="P916" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q916" t="n">
+        <v>1.1777176</v>
+      </c>
+      <c r="R916" t="n">
+        <v>11.95957333065244</v>
+      </c>
+      <c r="S916" t="n">
+        <v>1704.285</v>
+      </c>
+      <c r="T916" t="n">
+        <v>1447.108373008945</v>
+      </c>
+      <c r="U916" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V916" t="n">
+        <v>-0.006699576868829271</v>
+      </c>
+      <c r="W916" t="n">
+        <v>-0.02978104735016218</v>
+      </c>
+      <c r="X916" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y916" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z916" t="n">
+        <v>0.3516944050788879</v>
+      </c>
+      <c r="AA916" t="n">
+        <v>9.560202062129974</v>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr"/>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E917" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F917" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G917" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H917" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I917" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J917" t="n">
+        <v>162</v>
+      </c>
+      <c r="K917" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L917" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M917" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N917" s="2" t="n">
+        <v>45839.64758943042</v>
+      </c>
+      <c r="O917" t="n">
+        <v>39.05</v>
+      </c>
+      <c r="P917" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q917" t="n">
+        <v>4.25075</v>
+      </c>
+      <c r="R917" t="n">
+        <v>9.186614126918778</v>
+      </c>
+      <c r="S917" t="n">
+        <v>6326.099999999999</v>
+      </c>
+      <c r="T917" t="n">
+        <v>1488.231488560842</v>
+      </c>
+      <c r="U917" t="n">
+        <v>8.495174269061048</v>
+      </c>
+      <c r="V917" t="n">
+        <v>-0.003826530612245027</v>
+      </c>
+      <c r="W917" t="n">
+        <v>-0.0005549710915362382</v>
+      </c>
+      <c r="X917" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y917" t="n">
+        <v>10.667</v>
+      </c>
+      <c r="Z917" t="n">
+        <v>0.4341856837272644</v>
+      </c>
+      <c r="AA917" t="n">
+        <v>11.63437480163574</v>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D918" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E918" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F918" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G918" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H918" t="n">
+        <v>1</v>
+      </c>
+      <c r="I918" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J918" t="n">
+        <v>30</v>
+      </c>
+      <c r="K918" t="n">
+        <v>9</v>
+      </c>
+      <c r="L918" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M918" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N918" s="2" t="n">
+        <v>45839.64758943042</v>
+      </c>
+      <c r="O918" t="n">
+        <v>45.54</v>
+      </c>
+      <c r="P918" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q918" t="n">
+        <v>1</v>
+      </c>
+      <c r="R918" t="n">
+        <v>45.54</v>
+      </c>
+      <c r="S918" t="n">
+        <v>1366.2</v>
+      </c>
+      <c r="T918" t="n">
+        <v>1366.2</v>
+      </c>
+      <c r="U918" t="n">
+        <v>42.174</v>
+      </c>
+      <c r="V918" t="n">
+        <v>-0.003064798598949259</v>
+      </c>
+      <c r="W918" t="n">
+        <v>-0.003064798598949259</v>
+      </c>
+      <c r="X918" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y918" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z918" t="n">
+        <v>0.468702644109726</v>
+      </c>
+      <c r="AA918" t="n">
+        <v>9.620825290679932</v>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>MHY271836006</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="D919" t="inlineStr">
+        <is>
+          <t>GLOBAL SHIP LEA. A DL-,01</t>
+        </is>
+      </c>
+      <c r="E919" s="2" t="n">
+        <v>45838.31344841435</v>
+      </c>
+      <c r="F919" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="G919" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H919" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="I919" t="n">
+        <v>22.64505496285648</v>
+      </c>
+      <c r="J919" t="n">
+        <v>66</v>
+      </c>
+      <c r="K919" t="n">
+        <v>10</v>
+      </c>
+      <c r="L919" t="n">
+        <v>0.5395355224609375</v>
+      </c>
+      <c r="M919" t="n">
+        <v>12.45218944549561</v>
+      </c>
+      <c r="N919" s="2" t="n">
+        <v>45839.64758943042</v>
+      </c>
+      <c r="O919" t="n">
+        <v>26.1832</v>
+      </c>
+      <c r="P919" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q919" t="n">
+        <v>1.1777176</v>
+      </c>
+      <c r="R919" t="n">
+        <v>22.23215480519269</v>
+      </c>
+      <c r="S919" t="n">
+        <v>1728.0912</v>
+      </c>
+      <c r="T919" t="n">
+        <v>1467.322217142717</v>
+      </c>
+      <c r="U919" t="n">
+        <v>20.40206509457079</v>
+      </c>
+      <c r="V919" t="n">
+        <v>-0.01418674698795175</v>
+      </c>
+      <c r="W919" t="n">
+        <v>-0.01823356835923151</v>
+      </c>
+      <c r="X919" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y919" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z919" t="n">
+        <v>0.358627051115036</v>
+      </c>
+      <c r="AA919" t="n">
+        <v>9.922716617584229</v>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>PAP310761054</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="D920" t="inlineStr">
+        <is>
+          <t>COPA HOLDINGS CL.A O.N.</t>
+        </is>
+      </c>
+      <c r="E920" s="2" t="n">
+        <v>45839.31381715278</v>
+      </c>
+      <c r="F920" t="n">
+        <v>109.97</v>
+      </c>
+      <c r="G920" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H920" t="n">
+        <v>1.1788282</v>
+      </c>
+      <c r="I920" t="n">
+        <v>93.2875545393298</v>
+      </c>
+      <c r="J920" t="n">
+        <v>16</v>
+      </c>
+      <c r="K920" t="n">
+        <v>10</v>
+      </c>
+      <c r="L920" t="n">
+        <v>0.4318655133247375</v>
+      </c>
+      <c r="M920" t="n">
+        <v>11.16087436676025</v>
+      </c>
+      <c r="N920" s="2" t="n">
+        <v>45839.64758943042</v>
+      </c>
+      <c r="O920" t="n">
+        <v>109.02</v>
+      </c>
+      <c r="P920" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q920" t="n">
+        <v>1.1777176</v>
+      </c>
+      <c r="R920" t="n">
+        <v>92.56888068922464</v>
+      </c>
+      <c r="S920" t="n">
+        <v>1744.32</v>
+      </c>
+      <c r="T920" t="n">
+        <v>1481.102091027594</v>
+      </c>
+      <c r="U920" t="n">
+        <v>83.95879908539682</v>
+      </c>
+      <c r="V920" t="n">
+        <v>-0.008638719650813864</v>
+      </c>
+      <c r="W920" t="n">
+        <v>-0.007703855607043231</v>
+      </c>
+      <c r="X920" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y920" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z920" t="n">
+        <v>0.4318655133247375</v>
+      </c>
+      <c r="AA920" t="n">
         <v>11.16087436676025</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA920"/>
+  <dimension ref="A1:AA927"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86376,7 +86376,7 @@
         <v>100</v>
       </c>
       <c r="N914" s="2" t="n">
-        <v>45839.64758943042</v>
+        <v>45839.64758943287</v>
       </c>
       <c r="O914" t="n">
         <v>1</v>
@@ -86467,7 +86467,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N915" s="2" t="n">
-        <v>45839.64758943042</v>
+        <v>45839.64758943287</v>
       </c>
       <c r="O915" t="n">
         <v>365</v>
@@ -86562,7 +86562,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N916" s="2" t="n">
-        <v>45839.64758943042</v>
+        <v>45839.64758943287</v>
       </c>
       <c r="O916" t="n">
         <v>14.085</v>
@@ -86653,7 +86653,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N917" s="2" t="n">
-        <v>45839.64758943042</v>
+        <v>45839.64758943287</v>
       </c>
       <c r="O917" t="n">
         <v>39.05</v>
@@ -86748,7 +86748,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N918" s="2" t="n">
-        <v>45839.64758943042</v>
+        <v>45839.64758943287</v>
       </c>
       <c r="O918" t="n">
         <v>45.54</v>
@@ -86843,7 +86843,7 @@
         <v>12.45218944549561</v>
       </c>
       <c r="N919" s="2" t="n">
-        <v>45839.64758943042</v>
+        <v>45839.64758943287</v>
       </c>
       <c r="O919" t="n">
         <v>26.1832</v>
@@ -86938,7 +86938,7 @@
         <v>11.16087436676025</v>
       </c>
       <c r="N920" s="2" t="n">
-        <v>45839.64758943042</v>
+        <v>45839.64758943287</v>
       </c>
       <c r="O920" t="n">
         <v>109.02</v>
@@ -86979,6 +86979,665 @@
         <v>0.4318655133247375</v>
       </c>
       <c r="AA920" t="n">
+        <v>11.16087436676025</v>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D921" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E921" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F921" t="n">
+        <v>1</v>
+      </c>
+      <c r="G921" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H921" t="n">
+        <v>1</v>
+      </c>
+      <c r="I921" t="n">
+        <v>1</v>
+      </c>
+      <c r="J921" t="n">
+        <v>1</v>
+      </c>
+      <c r="K921" t="n">
+        <v>100</v>
+      </c>
+      <c r="L921" t="n">
+        <v>100</v>
+      </c>
+      <c r="M921" t="n">
+        <v>100</v>
+      </c>
+      <c r="N921" s="2" t="n">
+        <v>45839.69351045909</v>
+      </c>
+      <c r="O921" t="n">
+        <v>1</v>
+      </c>
+      <c r="P921" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q921" t="n">
+        <v>1</v>
+      </c>
+      <c r="R921" t="n">
+        <v>1</v>
+      </c>
+      <c r="S921" t="n">
+        <v>0</v>
+      </c>
+      <c r="T921" t="n">
+        <v>1414.591526256027</v>
+      </c>
+      <c r="U921" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V921" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W921" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X921" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y921" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z921" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA921" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr"/>
+      <c r="D922" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E922" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F922" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G922" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H922" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I922" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J922" t="n">
+        <v>3</v>
+      </c>
+      <c r="K922" t="n">
+        <v>10</v>
+      </c>
+      <c r="L922" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M922" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N922" s="2" t="n">
+        <v>45839.69351045909</v>
+      </c>
+      <c r="O922" t="n">
+        <v>370</v>
+      </c>
+      <c r="P922" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q922" t="n">
+        <v>0.85761</v>
+      </c>
+      <c r="R922" t="n">
+        <v>431.4315364792855</v>
+      </c>
+      <c r="S922" t="n">
+        <v>1110</v>
+      </c>
+      <c r="T922" t="n">
+        <v>1294.294609437856</v>
+      </c>
+      <c r="U922" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V922" t="n">
+        <v>0.006348152943160379</v>
+      </c>
+      <c r="W922" t="n">
+        <v>0.001724825646841621</v>
+      </c>
+      <c r="X922" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y922" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z922" t="n">
+        <v>0.4370984435081482</v>
+      </c>
+      <c r="AA922" t="n">
+        <v>10.20819354057312</v>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D923" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E923" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F923" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G923" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H923" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I923" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J923" t="n">
+        <v>121</v>
+      </c>
+      <c r="K923" t="n">
+        <v>12</v>
+      </c>
+      <c r="L923" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M923" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N923" s="2" t="n">
+        <v>45839.69351045909</v>
+      </c>
+      <c r="O923" t="n">
+        <v>14.08</v>
+      </c>
+      <c r="P923" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q923" t="n">
+        <v>1.176886</v>
+      </c>
+      <c r="R923" t="n">
+        <v>11.96377559083887</v>
+      </c>
+      <c r="S923" t="n">
+        <v>1703.68</v>
+      </c>
+      <c r="T923" t="n">
+        <v>1447.616846491504</v>
+      </c>
+      <c r="U923" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V923" t="n">
+        <v>-0.007052186177715081</v>
+      </c>
+      <c r="W923" t="n">
+        <v>-0.02944013949633495</v>
+      </c>
+      <c r="X923" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y923" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z923" t="n">
+        <v>0.3516944050788879</v>
+      </c>
+      <c r="AA923" t="n">
+        <v>9.560202062129974</v>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C924" t="inlineStr"/>
+      <c r="D924" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E924" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F924" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G924" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H924" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I924" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J924" t="n">
+        <v>162</v>
+      </c>
+      <c r="K924" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L924" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M924" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N924" s="2" t="n">
+        <v>45839.69351045909</v>
+      </c>
+      <c r="O924" t="n">
+        <v>39.05</v>
+      </c>
+      <c r="P924" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q924" t="n">
+        <v>4.2541</v>
+      </c>
+      <c r="R924" t="n">
+        <v>9.179379892339155</v>
+      </c>
+      <c r="S924" t="n">
+        <v>6326.099999999999</v>
+      </c>
+      <c r="T924" t="n">
+        <v>1487.059542558943</v>
+      </c>
+      <c r="U924" t="n">
+        <v>8.495174269061048</v>
+      </c>
+      <c r="V924" t="n">
+        <v>-0.003826530612245027</v>
+      </c>
+      <c r="W924" t="n">
+        <v>-0.001342009677099187</v>
+      </c>
+      <c r="X924" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y924" t="n">
+        <v>10.667</v>
+      </c>
+      <c r="Z924" t="n">
+        <v>0.4341856837272644</v>
+      </c>
+      <c r="AA924" t="n">
+        <v>11.63437480163574</v>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C925" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D925" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E925" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F925" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G925" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H925" t="n">
+        <v>1</v>
+      </c>
+      <c r="I925" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J925" t="n">
+        <v>30</v>
+      </c>
+      <c r="K925" t="n">
+        <v>9</v>
+      </c>
+      <c r="L925" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M925" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N925" s="2" t="n">
+        <v>45839.69351045909</v>
+      </c>
+      <c r="O925" t="n">
+        <v>45.54</v>
+      </c>
+      <c r="P925" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q925" t="n">
+        <v>1</v>
+      </c>
+      <c r="R925" t="n">
+        <v>45.54</v>
+      </c>
+      <c r="S925" t="n">
+        <v>1366.2</v>
+      </c>
+      <c r="T925" t="n">
+        <v>1366.2</v>
+      </c>
+      <c r="U925" t="n">
+        <v>42.174</v>
+      </c>
+      <c r="V925" t="n">
+        <v>-0.003064798598949259</v>
+      </c>
+      <c r="W925" t="n">
+        <v>-0.003064798598949259</v>
+      </c>
+      <c r="X925" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y925" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z925" t="n">
+        <v>0.468702644109726</v>
+      </c>
+      <c r="AA925" t="n">
+        <v>9.620825290679932</v>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>MHY271836006</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="D926" t="inlineStr">
+        <is>
+          <t>GLOBAL SHIP LEA. A DL-,01</t>
+        </is>
+      </c>
+      <c r="E926" s="2" t="n">
+        <v>45838.31344841435</v>
+      </c>
+      <c r="F926" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="G926" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H926" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="I926" t="n">
+        <v>22.64505496285648</v>
+      </c>
+      <c r="J926" t="n">
+        <v>66</v>
+      </c>
+      <c r="K926" t="n">
+        <v>10</v>
+      </c>
+      <c r="L926" t="n">
+        <v>0.5395355224609375</v>
+      </c>
+      <c r="M926" t="n">
+        <v>12.45218944549561</v>
+      </c>
+      <c r="N926" s="2" t="n">
+        <v>45839.69351045909</v>
+      </c>
+      <c r="O926" t="n">
+        <v>26.41</v>
+      </c>
+      <c r="P926" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q926" t="n">
+        <v>1.176886</v>
+      </c>
+      <c r="R926" t="n">
+        <v>22.44057623253229</v>
+      </c>
+      <c r="S926" t="n">
+        <v>1743.06</v>
+      </c>
+      <c r="T926" t="n">
+        <v>1481.078031347131</v>
+      </c>
+      <c r="U926" t="n">
+        <v>20.40206509457079</v>
+      </c>
+      <c r="V926" t="n">
+        <v>-0.005647590361445687</v>
+      </c>
+      <c r="W926" t="n">
+        <v>-0.009029729919383667</v>
+      </c>
+      <c r="X926" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y926" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z926" t="n">
+        <v>0.358627051115036</v>
+      </c>
+      <c r="AA926" t="n">
+        <v>9.922716617584229</v>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>PAP310761054</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="D927" t="inlineStr">
+        <is>
+          <t>COPA HOLDINGS CL.A O.N.</t>
+        </is>
+      </c>
+      <c r="E927" s="2" t="n">
+        <v>45839.31381715278</v>
+      </c>
+      <c r="F927" t="n">
+        <v>109.97</v>
+      </c>
+      <c r="G927" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H927" t="n">
+        <v>1.1788282</v>
+      </c>
+      <c r="I927" t="n">
+        <v>93.2875545393298</v>
+      </c>
+      <c r="J927" t="n">
+        <v>16</v>
+      </c>
+      <c r="K927" t="n">
+        <v>10</v>
+      </c>
+      <c r="L927" t="n">
+        <v>0.4318655133247375</v>
+      </c>
+      <c r="M927" t="n">
+        <v>11.16087436676025</v>
+      </c>
+      <c r="N927" s="2" t="n">
+        <v>45839.69351045909</v>
+      </c>
+      <c r="O927" t="n">
+        <v>109.82</v>
+      </c>
+      <c r="P927" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q927" t="n">
+        <v>1.176886</v>
+      </c>
+      <c r="R927" t="n">
+        <v>93.31405080865945</v>
+      </c>
+      <c r="S927" t="n">
+        <v>1757.12</v>
+      </c>
+      <c r="T927" t="n">
+        <v>1493.024812938551</v>
+      </c>
+      <c r="U927" t="n">
+        <v>83.9826457277935</v>
+      </c>
+      <c r="V927" t="n">
+        <v>-0.00136400836591799</v>
+      </c>
+      <c r="W927" t="n">
+        <v>0.0002840279119811218</v>
+      </c>
+      <c r="X927" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y927" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z927" t="n">
+        <v>0.4318655133247375</v>
+      </c>
+      <c r="AA927" t="n">
         <v>11.16087436676025</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA927"/>
+  <dimension ref="A1:AA934"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87035,7 +87035,7 @@
         <v>100</v>
       </c>
       <c r="N921" s="2" t="n">
-        <v>45839.69351045909</v>
+        <v>45839.69351046297</v>
       </c>
       <c r="O921" t="n">
         <v>1</v>
@@ -87126,7 +87126,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N922" s="2" t="n">
-        <v>45839.69351045909</v>
+        <v>45839.69351046297</v>
       </c>
       <c r="O922" t="n">
         <v>370</v>
@@ -87221,7 +87221,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N923" s="2" t="n">
-        <v>45839.69351045909</v>
+        <v>45839.69351046297</v>
       </c>
       <c r="O923" t="n">
         <v>14.08</v>
@@ -87312,7 +87312,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N924" s="2" t="n">
-        <v>45839.69351045909</v>
+        <v>45839.69351046297</v>
       </c>
       <c r="O924" t="n">
         <v>39.05</v>
@@ -87407,7 +87407,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N925" s="2" t="n">
-        <v>45839.69351045909</v>
+        <v>45839.69351046297</v>
       </c>
       <c r="O925" t="n">
         <v>45.54</v>
@@ -87502,7 +87502,7 @@
         <v>12.45218944549561</v>
       </c>
       <c r="N926" s="2" t="n">
-        <v>45839.69351045909</v>
+        <v>45839.69351046297</v>
       </c>
       <c r="O926" t="n">
         <v>26.41</v>
@@ -87597,7 +87597,7 @@
         <v>11.16087436676025</v>
       </c>
       <c r="N927" s="2" t="n">
-        <v>45839.69351045909</v>
+        <v>45839.69351046297</v>
       </c>
       <c r="O927" t="n">
         <v>109.82</v>
@@ -87638,6 +87638,665 @@
         <v>0.4318655133247375</v>
       </c>
       <c r="AA927" t="n">
+        <v>11.16087436676025</v>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D928" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E928" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F928" t="n">
+        <v>1</v>
+      </c>
+      <c r="G928" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H928" t="n">
+        <v>1</v>
+      </c>
+      <c r="I928" t="n">
+        <v>1</v>
+      </c>
+      <c r="J928" t="n">
+        <v>1</v>
+      </c>
+      <c r="K928" t="n">
+        <v>100</v>
+      </c>
+      <c r="L928" t="n">
+        <v>100</v>
+      </c>
+      <c r="M928" t="n">
+        <v>100</v>
+      </c>
+      <c r="N928" s="2" t="n">
+        <v>45839.73144538394</v>
+      </c>
+      <c r="O928" t="n">
+        <v>1</v>
+      </c>
+      <c r="P928" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q928" t="n">
+        <v>1</v>
+      </c>
+      <c r="R928" t="n">
+        <v>1</v>
+      </c>
+      <c r="S928" t="n">
+        <v>0</v>
+      </c>
+      <c r="T928" t="n">
+        <v>1414.591526256027</v>
+      </c>
+      <c r="U928" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V928" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W928" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X928" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y928" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z928" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA928" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr"/>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E929" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F929" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G929" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H929" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I929" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J929" t="n">
+        <v>3</v>
+      </c>
+      <c r="K929" t="n">
+        <v>10</v>
+      </c>
+      <c r="L929" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M929" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N929" s="2" t="n">
+        <v>45839.73144538394</v>
+      </c>
+      <c r="O929" t="n">
+        <v>370</v>
+      </c>
+      <c r="P929" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q929" t="n">
+        <v>0.85766</v>
+      </c>
+      <c r="R929" t="n">
+        <v>431.4063848144953</v>
+      </c>
+      <c r="S929" t="n">
+        <v>1110</v>
+      </c>
+      <c r="T929" t="n">
+        <v>1294.219154443486</v>
+      </c>
+      <c r="U929" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V929" t="n">
+        <v>0.006348152943160379</v>
+      </c>
+      <c r="W929" t="n">
+        <v>0.001666426932569687</v>
+      </c>
+      <c r="X929" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y929" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z929" t="n">
+        <v>0.4370984435081482</v>
+      </c>
+      <c r="AA929" t="n">
+        <v>10.20819354057312</v>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D930" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E930" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F930" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G930" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H930" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I930" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J930" t="n">
+        <v>121</v>
+      </c>
+      <c r="K930" t="n">
+        <v>12</v>
+      </c>
+      <c r="L930" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M930" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N930" s="2" t="n">
+        <v>45839.73144538394</v>
+      </c>
+      <c r="O930" t="n">
+        <v>14.065</v>
+      </c>
+      <c r="P930" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q930" t="n">
+        <v>1.1784115</v>
+      </c>
+      <c r="R930" t="n">
+        <v>11.93555901312912</v>
+      </c>
+      <c r="S930" t="n">
+        <v>1701.865</v>
+      </c>
+      <c r="T930" t="n">
+        <v>1444.202640588623</v>
+      </c>
+      <c r="U930" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V930" t="n">
+        <v>-0.008110014104372398</v>
+      </c>
+      <c r="W930" t="n">
+        <v>-0.03172920598023354</v>
+      </c>
+      <c r="X930" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y930" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z930" t="n">
+        <v>0.3516944050788879</v>
+      </c>
+      <c r="AA930" t="n">
+        <v>9.560202062129974</v>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C931" t="inlineStr"/>
+      <c r="D931" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E931" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F931" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G931" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H931" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I931" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J931" t="n">
+        <v>162</v>
+      </c>
+      <c r="K931" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L931" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M931" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N931" s="2" t="n">
+        <v>45839.73144538394</v>
+      </c>
+      <c r="O931" t="n">
+        <v>39.05</v>
+      </c>
+      <c r="P931" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q931" t="n">
+        <v>4.25008</v>
+      </c>
+      <c r="R931" t="n">
+        <v>9.188062342355909</v>
+      </c>
+      <c r="S931" t="n">
+        <v>6326.099999999999</v>
+      </c>
+      <c r="T931" t="n">
+        <v>1488.466099461657</v>
+      </c>
+      <c r="U931" t="n">
+        <v>8.495174269061048</v>
+      </c>
+      <c r="V931" t="n">
+        <v>-0.003826530612245027</v>
+      </c>
+      <c r="W931" t="n">
+        <v>-0.000397414488044201</v>
+      </c>
+      <c r="X931" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y931" t="n">
+        <v>10.667</v>
+      </c>
+      <c r="Z931" t="n">
+        <v>0.4341856837272644</v>
+      </c>
+      <c r="AA931" t="n">
+        <v>11.63437480163574</v>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D932" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E932" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F932" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G932" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H932" t="n">
+        <v>1</v>
+      </c>
+      <c r="I932" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J932" t="n">
+        <v>30</v>
+      </c>
+      <c r="K932" t="n">
+        <v>9</v>
+      </c>
+      <c r="L932" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M932" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N932" s="2" t="n">
+        <v>45839.73144538394</v>
+      </c>
+      <c r="O932" t="n">
+        <v>45.54</v>
+      </c>
+      <c r="P932" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q932" t="n">
+        <v>1</v>
+      </c>
+      <c r="R932" t="n">
+        <v>45.54</v>
+      </c>
+      <c r="S932" t="n">
+        <v>1366.2</v>
+      </c>
+      <c r="T932" t="n">
+        <v>1366.2</v>
+      </c>
+      <c r="U932" t="n">
+        <v>42.174</v>
+      </c>
+      <c r="V932" t="n">
+        <v>-0.003064798598949259</v>
+      </c>
+      <c r="W932" t="n">
+        <v>-0.003064798598949259</v>
+      </c>
+      <c r="X932" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y932" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z932" t="n">
+        <v>0.468702644109726</v>
+      </c>
+      <c r="AA932" t="n">
+        <v>9.620825290679932</v>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>MHY271836006</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="D933" t="inlineStr">
+        <is>
+          <t>GLOBAL SHIP LEA. A DL-,01</t>
+        </is>
+      </c>
+      <c r="E933" s="2" t="n">
+        <v>45838.31344841435</v>
+      </c>
+      <c r="F933" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="G933" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H933" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="I933" t="n">
+        <v>22.64505496285648</v>
+      </c>
+      <c r="J933" t="n">
+        <v>66</v>
+      </c>
+      <c r="K933" t="n">
+        <v>10</v>
+      </c>
+      <c r="L933" t="n">
+        <v>0.5395355224609375</v>
+      </c>
+      <c r="M933" t="n">
+        <v>12.45218944549561</v>
+      </c>
+      <c r="N933" s="2" t="n">
+        <v>45839.73144538394</v>
+      </c>
+      <c r="O933" t="n">
+        <v>26.44</v>
+      </c>
+      <c r="P933" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q933" t="n">
+        <v>1.1784115</v>
+      </c>
+      <c r="R933" t="n">
+        <v>22.43698402468068</v>
+      </c>
+      <c r="S933" t="n">
+        <v>1745.04</v>
+      </c>
+      <c r="T933" t="n">
+        <v>1480.840945628925</v>
+      </c>
+      <c r="U933" t="n">
+        <v>20.40206509457079</v>
+      </c>
+      <c r="V933" t="n">
+        <v>-0.004518072289156572</v>
+      </c>
+      <c r="W933" t="n">
+        <v>-0.009188360925468708</v>
+      </c>
+      <c r="X933" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y933" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z933" t="n">
+        <v>0.358627051115036</v>
+      </c>
+      <c r="AA933" t="n">
+        <v>9.922716617584229</v>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>PAP310761054</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="D934" t="inlineStr">
+        <is>
+          <t>COPA HOLDINGS CL.A O.N.</t>
+        </is>
+      </c>
+      <c r="E934" s="2" t="n">
+        <v>45839.31381715278</v>
+      </c>
+      <c r="F934" t="n">
+        <v>109.97</v>
+      </c>
+      <c r="G934" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H934" t="n">
+        <v>1.1788282</v>
+      </c>
+      <c r="I934" t="n">
+        <v>93.2875545393298</v>
+      </c>
+      <c r="J934" t="n">
+        <v>16</v>
+      </c>
+      <c r="K934" t="n">
+        <v>10</v>
+      </c>
+      <c r="L934" t="n">
+        <v>0.4318655133247375</v>
+      </c>
+      <c r="M934" t="n">
+        <v>11.16087436676025</v>
+      </c>
+      <c r="N934" s="2" t="n">
+        <v>45839.73144538394</v>
+      </c>
+      <c r="O934" t="n">
+        <v>109.195</v>
+      </c>
+      <c r="P934" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q934" t="n">
+        <v>1.1784115</v>
+      </c>
+      <c r="R934" t="n">
+        <v>92.66287710192917</v>
+      </c>
+      <c r="S934" t="n">
+        <v>1747.12</v>
+      </c>
+      <c r="T934" t="n">
+        <v>1482.606033630867</v>
+      </c>
+      <c r="U934" t="n">
+        <v>83.9826457277935</v>
+      </c>
+      <c r="V934" t="n">
+        <v>-0.007047376557242968</v>
+      </c>
+      <c r="W934" t="n">
+        <v>-0.006696256971097547</v>
+      </c>
+      <c r="X934" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y934" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z934" t="n">
+        <v>0.4318655133247375</v>
+      </c>
+      <c r="AA934" t="n">
         <v>11.16087436676025</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA934"/>
+  <dimension ref="A1:AA941"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87694,7 +87694,7 @@
         <v>100</v>
       </c>
       <c r="N928" s="2" t="n">
-        <v>45839.73144538394</v>
+        <v>45839.73144538194</v>
       </c>
       <c r="O928" t="n">
         <v>1</v>
@@ -87785,7 +87785,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N929" s="2" t="n">
-        <v>45839.73144538394</v>
+        <v>45839.73144538194</v>
       </c>
       <c r="O929" t="n">
         <v>370</v>
@@ -87880,7 +87880,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N930" s="2" t="n">
-        <v>45839.73144538394</v>
+        <v>45839.73144538194</v>
       </c>
       <c r="O930" t="n">
         <v>14.065</v>
@@ -87971,7 +87971,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N931" s="2" t="n">
-        <v>45839.73144538394</v>
+        <v>45839.73144538194</v>
       </c>
       <c r="O931" t="n">
         <v>39.05</v>
@@ -88066,7 +88066,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N932" s="2" t="n">
-        <v>45839.73144538394</v>
+        <v>45839.73144538194</v>
       </c>
       <c r="O932" t="n">
         <v>45.54</v>
@@ -88161,7 +88161,7 @@
         <v>12.45218944549561</v>
       </c>
       <c r="N933" s="2" t="n">
-        <v>45839.73144538394</v>
+        <v>45839.73144538194</v>
       </c>
       <c r="O933" t="n">
         <v>26.44</v>
@@ -88256,7 +88256,7 @@
         <v>11.16087436676025</v>
       </c>
       <c r="N934" s="2" t="n">
-        <v>45839.73144538394</v>
+        <v>45839.73144538194</v>
       </c>
       <c r="O934" t="n">
         <v>109.195</v>
@@ -88297,6 +88297,665 @@
         <v>0.4318655133247375</v>
       </c>
       <c r="AA934" t="n">
+        <v>11.16087436676025</v>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D935" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E935" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F935" t="n">
+        <v>1</v>
+      </c>
+      <c r="G935" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H935" t="n">
+        <v>1</v>
+      </c>
+      <c r="I935" t="n">
+        <v>1</v>
+      </c>
+      <c r="J935" t="n">
+        <v>1</v>
+      </c>
+      <c r="K935" t="n">
+        <v>100</v>
+      </c>
+      <c r="L935" t="n">
+        <v>100</v>
+      </c>
+      <c r="M935" t="n">
+        <v>100</v>
+      </c>
+      <c r="N935" s="2" t="n">
+        <v>45839.7787284242</v>
+      </c>
+      <c r="O935" t="n">
+        <v>1</v>
+      </c>
+      <c r="P935" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q935" t="n">
+        <v>1</v>
+      </c>
+      <c r="R935" t="n">
+        <v>1</v>
+      </c>
+      <c r="S935" t="n">
+        <v>0</v>
+      </c>
+      <c r="T935" t="n">
+        <v>1414.591526256027</v>
+      </c>
+      <c r="U935" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V935" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W935" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X935" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y935" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z935" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA935" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr"/>
+      <c r="D936" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E936" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F936" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G936" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H936" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I936" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J936" t="n">
+        <v>3</v>
+      </c>
+      <c r="K936" t="n">
+        <v>10</v>
+      </c>
+      <c r="L936" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M936" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N936" s="2" t="n">
+        <v>45839.7787284242</v>
+      </c>
+      <c r="O936" t="n">
+        <v>370</v>
+      </c>
+      <c r="P936" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q936" t="n">
+        <v>0.85743</v>
+      </c>
+      <c r="R936" t="n">
+        <v>431.5221067609017</v>
+      </c>
+      <c r="S936" t="n">
+        <v>1110</v>
+      </c>
+      <c r="T936" t="n">
+        <v>1294.566320282705</v>
+      </c>
+      <c r="U936" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V936" t="n">
+        <v>0.006348152943160379</v>
+      </c>
+      <c r="W936" t="n">
+        <v>0.001935117412485754</v>
+      </c>
+      <c r="X936" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y936" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z936" t="n">
+        <v>0.4370984435081482</v>
+      </c>
+      <c r="AA936" t="n">
+        <v>10.20819354057312</v>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D937" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E937" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F937" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G937" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H937" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I937" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J937" t="n">
+        <v>121</v>
+      </c>
+      <c r="K937" t="n">
+        <v>12</v>
+      </c>
+      <c r="L937" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M937" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N937" s="2" t="n">
+        <v>45839.7787284242</v>
+      </c>
+      <c r="O937" t="n">
+        <v>14.0318</v>
+      </c>
+      <c r="P937" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q937" t="n">
+        <v>1.1781338</v>
+      </c>
+      <c r="R937" t="n">
+        <v>11.91019220397548</v>
+      </c>
+      <c r="S937" t="n">
+        <v>1697.8478</v>
+      </c>
+      <c r="T937" t="n">
+        <v>1441.133256681032</v>
+      </c>
+      <c r="U937" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V937" t="n">
+        <v>-0.01045133991537373</v>
+      </c>
+      <c r="W937" t="n">
+        <v>-0.03378708533166774</v>
+      </c>
+      <c r="X937" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y937" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z937" t="n">
+        <v>0.3516944050788879</v>
+      </c>
+      <c r="AA937" t="n">
+        <v>9.560202062129974</v>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr"/>
+      <c r="D938" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E938" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F938" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G938" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H938" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I938" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J938" t="n">
+        <v>162</v>
+      </c>
+      <c r="K938" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L938" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M938" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N938" s="2" t="n">
+        <v>45839.7787284242</v>
+      </c>
+      <c r="O938" t="n">
+        <v>39.05</v>
+      </c>
+      <c r="P938" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q938" t="n">
+        <v>4.2493</v>
+      </c>
+      <c r="R938" t="n">
+        <v>9.189748899818794</v>
+      </c>
+      <c r="S938" t="n">
+        <v>6326.099999999999</v>
+      </c>
+      <c r="T938" t="n">
+        <v>1488.739321770644</v>
+      </c>
+      <c r="U938" t="n">
+        <v>8.495174269061048</v>
+      </c>
+      <c r="V938" t="n">
+        <v>-0.003826530612245027</v>
+      </c>
+      <c r="W938" t="n">
+        <v>-0.0002139277921886507</v>
+      </c>
+      <c r="X938" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y938" t="n">
+        <v>10.667</v>
+      </c>
+      <c r="Z938" t="n">
+        <v>0.4341856837272644</v>
+      </c>
+      <c r="AA938" t="n">
+        <v>11.63437480163574</v>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D939" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E939" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F939" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G939" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H939" t="n">
+        <v>1</v>
+      </c>
+      <c r="I939" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J939" t="n">
+        <v>30</v>
+      </c>
+      <c r="K939" t="n">
+        <v>9</v>
+      </c>
+      <c r="L939" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M939" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N939" s="2" t="n">
+        <v>45839.7787284242</v>
+      </c>
+      <c r="O939" t="n">
+        <v>45.54</v>
+      </c>
+      <c r="P939" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q939" t="n">
+        <v>1</v>
+      </c>
+      <c r="R939" t="n">
+        <v>45.54</v>
+      </c>
+      <c r="S939" t="n">
+        <v>1366.2</v>
+      </c>
+      <c r="T939" t="n">
+        <v>1366.2</v>
+      </c>
+      <c r="U939" t="n">
+        <v>42.174</v>
+      </c>
+      <c r="V939" t="n">
+        <v>-0.003064798598949259</v>
+      </c>
+      <c r="W939" t="n">
+        <v>-0.003064798598949259</v>
+      </c>
+      <c r="X939" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y939" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z939" t="n">
+        <v>0.468702644109726</v>
+      </c>
+      <c r="AA939" t="n">
+        <v>9.620825290679932</v>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>MHY271836006</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="D940" t="inlineStr">
+        <is>
+          <t>GLOBAL SHIP LEA. A DL-,01</t>
+        </is>
+      </c>
+      <c r="E940" s="2" t="n">
+        <v>45838.31344841435</v>
+      </c>
+      <c r="F940" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="G940" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H940" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="I940" t="n">
+        <v>22.64505496285648</v>
+      </c>
+      <c r="J940" t="n">
+        <v>66</v>
+      </c>
+      <c r="K940" t="n">
+        <v>10</v>
+      </c>
+      <c r="L940" t="n">
+        <v>0.5395355224609375</v>
+      </c>
+      <c r="M940" t="n">
+        <v>12.45218944549561</v>
+      </c>
+      <c r="N940" s="2" t="n">
+        <v>45839.7787284242</v>
+      </c>
+      <c r="O940" t="n">
+        <v>26.26</v>
+      </c>
+      <c r="P940" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q940" t="n">
+        <v>1.1781338</v>
+      </c>
+      <c r="R940" t="n">
+        <v>22.28948868116678</v>
+      </c>
+      <c r="S940" t="n">
+        <v>1733.16</v>
+      </c>
+      <c r="T940" t="n">
+        <v>1471.106252957007</v>
+      </c>
+      <c r="U940" t="n">
+        <v>20.40206509457079</v>
+      </c>
+      <c r="V940" t="n">
+        <v>-0.01129518072289148</v>
+      </c>
+      <c r="W940" t="n">
+        <v>-0.01570171864333847</v>
+      </c>
+      <c r="X940" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y940" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z940" t="n">
+        <v>0.358627051115036</v>
+      </c>
+      <c r="AA940" t="n">
+        <v>9.922716617584229</v>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>PAP310761054</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="D941" t="inlineStr">
+        <is>
+          <t>COPA HOLDINGS CL.A O.N.</t>
+        </is>
+      </c>
+      <c r="E941" s="2" t="n">
+        <v>45839.31381715278</v>
+      </c>
+      <c r="F941" t="n">
+        <v>109.97</v>
+      </c>
+      <c r="G941" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H941" t="n">
+        <v>1.1788282</v>
+      </c>
+      <c r="I941" t="n">
+        <v>93.2875545393298</v>
+      </c>
+      <c r="J941" t="n">
+        <v>16</v>
+      </c>
+      <c r="K941" t="n">
+        <v>10</v>
+      </c>
+      <c r="L941" t="n">
+        <v>0.4318655133247375</v>
+      </c>
+      <c r="M941" t="n">
+        <v>11.16087436676025</v>
+      </c>
+      <c r="N941" s="2" t="n">
+        <v>45839.7787284242</v>
+      </c>
+      <c r="O941" t="n">
+        <v>108.925</v>
+      </c>
+      <c r="P941" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q941" t="n">
+        <v>1.1781338</v>
+      </c>
+      <c r="R941" t="n">
+        <v>92.4555428254414</v>
+      </c>
+      <c r="S941" t="n">
+        <v>1742.8</v>
+      </c>
+      <c r="T941" t="n">
+        <v>1479.288685207062</v>
+      </c>
+      <c r="U941" t="n">
+        <v>83.9826457277935</v>
+      </c>
+      <c r="V941" t="n">
+        <v>-0.009502591615895284</v>
+      </c>
+      <c r="W941" t="n">
+        <v>-0.008918785769409743</v>
+      </c>
+      <c r="X941" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y941" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z941" t="n">
+        <v>0.4318655133247375</v>
+      </c>
+      <c r="AA941" t="n">
         <v>11.16087436676025</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA941"/>
+  <dimension ref="A1:AA948"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88353,7 +88353,7 @@
         <v>100</v>
       </c>
       <c r="N935" s="2" t="n">
-        <v>45839.7787284242</v>
+        <v>45839.77872842592</v>
       </c>
       <c r="O935" t="n">
         <v>1</v>
@@ -88444,7 +88444,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N936" s="2" t="n">
-        <v>45839.7787284242</v>
+        <v>45839.77872842592</v>
       </c>
       <c r="O936" t="n">
         <v>370</v>
@@ -88539,7 +88539,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N937" s="2" t="n">
-        <v>45839.7787284242</v>
+        <v>45839.77872842592</v>
       </c>
       <c r="O937" t="n">
         <v>14.0318</v>
@@ -88630,7 +88630,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N938" s="2" t="n">
-        <v>45839.7787284242</v>
+        <v>45839.77872842592</v>
       </c>
       <c r="O938" t="n">
         <v>39.05</v>
@@ -88725,7 +88725,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N939" s="2" t="n">
-        <v>45839.7787284242</v>
+        <v>45839.77872842592</v>
       </c>
       <c r="O939" t="n">
         <v>45.54</v>
@@ -88820,7 +88820,7 @@
         <v>12.45218944549561</v>
       </c>
       <c r="N940" s="2" t="n">
-        <v>45839.7787284242</v>
+        <v>45839.77872842592</v>
       </c>
       <c r="O940" t="n">
         <v>26.26</v>
@@ -88915,7 +88915,7 @@
         <v>11.16087436676025</v>
       </c>
       <c r="N941" s="2" t="n">
-        <v>45839.7787284242</v>
+        <v>45839.77872842592</v>
       </c>
       <c r="O941" t="n">
         <v>108.925</v>
@@ -88956,6 +88956,665 @@
         <v>0.4318655133247375</v>
       </c>
       <c r="AA941" t="n">
+        <v>11.16087436676025</v>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D942" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E942" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F942" t="n">
+        <v>1</v>
+      </c>
+      <c r="G942" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H942" t="n">
+        <v>1</v>
+      </c>
+      <c r="I942" t="n">
+        <v>1</v>
+      </c>
+      <c r="J942" t="n">
+        <v>1</v>
+      </c>
+      <c r="K942" t="n">
+        <v>100</v>
+      </c>
+      <c r="L942" t="n">
+        <v>100</v>
+      </c>
+      <c r="M942" t="n">
+        <v>100</v>
+      </c>
+      <c r="N942" s="2" t="n">
+        <v>45839.80891699749</v>
+      </c>
+      <c r="O942" t="n">
+        <v>1</v>
+      </c>
+      <c r="P942" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q942" t="n">
+        <v>1</v>
+      </c>
+      <c r="R942" t="n">
+        <v>1</v>
+      </c>
+      <c r="S942" t="n">
+        <v>0</v>
+      </c>
+      <c r="T942" t="n">
+        <v>1414.591526256027</v>
+      </c>
+      <c r="U942" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V942" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W942" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X942" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y942" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z942" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA942" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr"/>
+      <c r="D943" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E943" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F943" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G943" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H943" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I943" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J943" t="n">
+        <v>3</v>
+      </c>
+      <c r="K943" t="n">
+        <v>10</v>
+      </c>
+      <c r="L943" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M943" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N943" s="2" t="n">
+        <v>45839.80891699749</v>
+      </c>
+      <c r="O943" t="n">
+        <v>370</v>
+      </c>
+      <c r="P943" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q943" t="n">
+        <v>0.85787</v>
+      </c>
+      <c r="R943" t="n">
+        <v>431.3007798384371</v>
+      </c>
+      <c r="S943" t="n">
+        <v>1110</v>
+      </c>
+      <c r="T943" t="n">
+        <v>1293.902339515311</v>
+      </c>
+      <c r="U943" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V943" t="n">
+        <v>0.006348152943160379</v>
+      </c>
+      <c r="W943" t="n">
+        <v>0.001421226669527709</v>
+      </c>
+      <c r="X943" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y943" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z943" t="n">
+        <v>0.4370984435081482</v>
+      </c>
+      <c r="AA943" t="n">
+        <v>10.20819354057312</v>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D944" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E944" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F944" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G944" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H944" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I944" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J944" t="n">
+        <v>121</v>
+      </c>
+      <c r="K944" t="n">
+        <v>12</v>
+      </c>
+      <c r="L944" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M944" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N944" s="2" t="n">
+        <v>45839.80891699749</v>
+      </c>
+      <c r="O944" t="n">
+        <v>13.995</v>
+      </c>
+      <c r="P944" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q944" t="n">
+        <v>1.1789672</v>
+      </c>
+      <c r="R944" t="n">
+        <v>11.87055924880692</v>
+      </c>
+      <c r="S944" t="n">
+        <v>1693.395</v>
+      </c>
+      <c r="T944" t="n">
+        <v>1436.337669105638</v>
+      </c>
+      <c r="U944" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V944" t="n">
+        <v>-0.01304654442877295</v>
+      </c>
+      <c r="W944" t="n">
+        <v>-0.03700230406823402</v>
+      </c>
+      <c r="X944" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y944" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z944" t="n">
+        <v>0.3516944050788879</v>
+      </c>
+      <c r="AA944" t="n">
+        <v>9.560202062129974</v>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr"/>
+      <c r="D945" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E945" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F945" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G945" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H945" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I945" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J945" t="n">
+        <v>162</v>
+      </c>
+      <c r="K945" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L945" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M945" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N945" s="2" t="n">
+        <v>45839.80891699749</v>
+      </c>
+      <c r="O945" t="n">
+        <v>39.05</v>
+      </c>
+      <c r="P945" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q945" t="n">
+        <v>4.24667</v>
+      </c>
+      <c r="R945" t="n">
+        <v>9.195440191962172</v>
+      </c>
+      <c r="S945" t="n">
+        <v>6326.099999999999</v>
+      </c>
+      <c r="T945" t="n">
+        <v>1489.661311097872</v>
+      </c>
+      <c r="U945" t="n">
+        <v>8.495174269061048</v>
+      </c>
+      <c r="V945" t="n">
+        <v>-0.003826530612245027</v>
+      </c>
+      <c r="W945" t="n">
+        <v>0.0004052484965049175</v>
+      </c>
+      <c r="X945" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y945" t="n">
+        <v>10.667</v>
+      </c>
+      <c r="Z945" t="n">
+        <v>0.4341856837272644</v>
+      </c>
+      <c r="AA945" t="n">
+        <v>11.63437480163574</v>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D946" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E946" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F946" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G946" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H946" t="n">
+        <v>1</v>
+      </c>
+      <c r="I946" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J946" t="n">
+        <v>30</v>
+      </c>
+      <c r="K946" t="n">
+        <v>9</v>
+      </c>
+      <c r="L946" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M946" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N946" s="2" t="n">
+        <v>45839.80891699749</v>
+      </c>
+      <c r="O946" t="n">
+        <v>45.54</v>
+      </c>
+      <c r="P946" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q946" t="n">
+        <v>1</v>
+      </c>
+      <c r="R946" t="n">
+        <v>45.54</v>
+      </c>
+      <c r="S946" t="n">
+        <v>1366.2</v>
+      </c>
+      <c r="T946" t="n">
+        <v>1366.2</v>
+      </c>
+      <c r="U946" t="n">
+        <v>42.174</v>
+      </c>
+      <c r="V946" t="n">
+        <v>-0.003064798598949259</v>
+      </c>
+      <c r="W946" t="n">
+        <v>-0.003064798598949259</v>
+      </c>
+      <c r="X946" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y946" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z946" t="n">
+        <v>0.468702644109726</v>
+      </c>
+      <c r="AA946" t="n">
+        <v>9.620825290679932</v>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>MHY271836006</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="D947" t="inlineStr">
+        <is>
+          <t>GLOBAL SHIP LEA. A DL-,01</t>
+        </is>
+      </c>
+      <c r="E947" s="2" t="n">
+        <v>45838.31344841435</v>
+      </c>
+      <c r="F947" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="G947" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H947" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="I947" t="n">
+        <v>22.64505496285648</v>
+      </c>
+      <c r="J947" t="n">
+        <v>66</v>
+      </c>
+      <c r="K947" t="n">
+        <v>10</v>
+      </c>
+      <c r="L947" t="n">
+        <v>0.5395355224609375</v>
+      </c>
+      <c r="M947" t="n">
+        <v>12.45218944549561</v>
+      </c>
+      <c r="N947" s="2" t="n">
+        <v>45839.80891699749</v>
+      </c>
+      <c r="O947" t="n">
+        <v>26.19</v>
+      </c>
+      <c r="P947" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q947" t="n">
+        <v>1.1789672</v>
+      </c>
+      <c r="R947" t="n">
+        <v>22.21435846561295</v>
+      </c>
+      <c r="S947" t="n">
+        <v>1728.54</v>
+      </c>
+      <c r="T947" t="n">
+        <v>1466.147658730455</v>
+      </c>
+      <c r="U947" t="n">
+        <v>20.40206509457079</v>
+      </c>
+      <c r="V947" t="n">
+        <v>-0.01393072289156616</v>
+      </c>
+      <c r="W947" t="n">
+        <v>-0.01901945029278929</v>
+      </c>
+      <c r="X947" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y947" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z947" t="n">
+        <v>0.358627051115036</v>
+      </c>
+      <c r="AA947" t="n">
+        <v>9.922716617584229</v>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>PAP310761054</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>COPA HOLDINGS CL.A O.N.</t>
+        </is>
+      </c>
+      <c r="E948" s="2" t="n">
+        <v>45839.31381715278</v>
+      </c>
+      <c r="F948" t="n">
+        <v>109.97</v>
+      </c>
+      <c r="G948" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H948" t="n">
+        <v>1.1788282</v>
+      </c>
+      <c r="I948" t="n">
+        <v>93.2875545393298</v>
+      </c>
+      <c r="J948" t="n">
+        <v>16</v>
+      </c>
+      <c r="K948" t="n">
+        <v>10</v>
+      </c>
+      <c r="L948" t="n">
+        <v>0.4318655133247375</v>
+      </c>
+      <c r="M948" t="n">
+        <v>11.16087436676025</v>
+      </c>
+      <c r="N948" s="2" t="n">
+        <v>45839.80891699749</v>
+      </c>
+      <c r="O948" t="n">
+        <v>109.095</v>
+      </c>
+      <c r="P948" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q948" t="n">
+        <v>1.1789672</v>
+      </c>
+      <c r="R948" t="n">
+        <v>92.53438093952063</v>
+      </c>
+      <c r="S948" t="n">
+        <v>1745.52</v>
+      </c>
+      <c r="T948" t="n">
+        <v>1480.55009503233</v>
+      </c>
+      <c r="U948" t="n">
+        <v>83.9826457277935</v>
+      </c>
+      <c r="V948" t="n">
+        <v>-0.007956715467854925</v>
+      </c>
+      <c r="W948" t="n">
+        <v>-0.008073677175143845</v>
+      </c>
+      <c r="X948" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y948" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z948" t="n">
+        <v>0.4318655133247375</v>
+      </c>
+      <c r="AA948" t="n">
         <v>11.16087436676025</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA948"/>
+  <dimension ref="A1:AA955"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -89012,7 +89012,7 @@
         <v>100</v>
       </c>
       <c r="N942" s="2" t="n">
-        <v>45839.80891699749</v>
+        <v>45839.80891700232</v>
       </c>
       <c r="O942" t="n">
         <v>1</v>
@@ -89103,7 +89103,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N943" s="2" t="n">
-        <v>45839.80891699749</v>
+        <v>45839.80891700232</v>
       </c>
       <c r="O943" t="n">
         <v>370</v>
@@ -89198,7 +89198,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N944" s="2" t="n">
-        <v>45839.80891699749</v>
+        <v>45839.80891700232</v>
       </c>
       <c r="O944" t="n">
         <v>13.995</v>
@@ -89289,7 +89289,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N945" s="2" t="n">
-        <v>45839.80891699749</v>
+        <v>45839.80891700232</v>
       </c>
       <c r="O945" t="n">
         <v>39.05</v>
@@ -89384,7 +89384,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N946" s="2" t="n">
-        <v>45839.80891699749</v>
+        <v>45839.80891700232</v>
       </c>
       <c r="O946" t="n">
         <v>45.54</v>
@@ -89479,7 +89479,7 @@
         <v>12.45218944549561</v>
       </c>
       <c r="N947" s="2" t="n">
-        <v>45839.80891699749</v>
+        <v>45839.80891700232</v>
       </c>
       <c r="O947" t="n">
         <v>26.19</v>
@@ -89574,7 +89574,7 @@
         <v>11.16087436676025</v>
       </c>
       <c r="N948" s="2" t="n">
-        <v>45839.80891699749</v>
+        <v>45839.80891700232</v>
       </c>
       <c r="O948" t="n">
         <v>109.095</v>
@@ -89615,6 +89615,665 @@
         <v>0.4318655133247375</v>
       </c>
       <c r="AA948" t="n">
+        <v>11.16087436676025</v>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E949" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F949" t="n">
+        <v>1</v>
+      </c>
+      <c r="G949" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H949" t="n">
+        <v>1</v>
+      </c>
+      <c r="I949" t="n">
+        <v>1</v>
+      </c>
+      <c r="J949" t="n">
+        <v>1</v>
+      </c>
+      <c r="K949" t="n">
+        <v>100</v>
+      </c>
+      <c r="L949" t="n">
+        <v>100</v>
+      </c>
+      <c r="M949" t="n">
+        <v>100</v>
+      </c>
+      <c r="N949" s="2" t="n">
+        <v>45839.85629020934</v>
+      </c>
+      <c r="O949" t="n">
+        <v>1</v>
+      </c>
+      <c r="P949" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q949" t="n">
+        <v>1</v>
+      </c>
+      <c r="R949" t="n">
+        <v>1</v>
+      </c>
+      <c r="S949" t="n">
+        <v>0</v>
+      </c>
+      <c r="T949" t="n">
+        <v>1414.591526256027</v>
+      </c>
+      <c r="U949" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V949" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W949" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X949" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y949" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z949" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA949" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr"/>
+      <c r="D950" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E950" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F950" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G950" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H950" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I950" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J950" t="n">
+        <v>3</v>
+      </c>
+      <c r="K950" t="n">
+        <v>10</v>
+      </c>
+      <c r="L950" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M950" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N950" s="2" t="n">
+        <v>45839.85629020934</v>
+      </c>
+      <c r="O950" t="n">
+        <v>370</v>
+      </c>
+      <c r="P950" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q950" t="n">
+        <v>0.8584000000000001</v>
+      </c>
+      <c r="R950" t="n">
+        <v>431.0344827586206</v>
+      </c>
+      <c r="S950" t="n">
+        <v>1110</v>
+      </c>
+      <c r="T950" t="n">
+        <v>1293.103448275862</v>
+      </c>
+      <c r="U950" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V950" t="n">
+        <v>0.006348152943160379</v>
+      </c>
+      <c r="W950" t="n">
+        <v>0.0008029213921105782</v>
+      </c>
+      <c r="X950" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y950" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z950" t="n">
+        <v>0.4370984435081482</v>
+      </c>
+      <c r="AA950" t="n">
+        <v>10.20819354057312</v>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D951" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E951" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F951" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G951" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H951" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I951" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J951" t="n">
+        <v>121</v>
+      </c>
+      <c r="K951" t="n">
+        <v>12</v>
+      </c>
+      <c r="L951" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M951" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N951" s="2" t="n">
+        <v>45839.85629020934</v>
+      </c>
+      <c r="O951" t="n">
+        <v>13.98</v>
+      </c>
+      <c r="P951" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q951" t="n">
+        <v>1.180777</v>
+      </c>
+      <c r="R951" t="n">
+        <v>11.83966151102198</v>
+      </c>
+      <c r="S951" t="n">
+        <v>1691.58</v>
+      </c>
+      <c r="T951" t="n">
+        <v>1432.59904283366</v>
+      </c>
+      <c r="U951" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V951" t="n">
+        <v>-0.01410437235543016</v>
+      </c>
+      <c r="W951" t="n">
+        <v>-0.03950887934179526</v>
+      </c>
+      <c r="X951" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y951" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z951" t="n">
+        <v>0.3516944050788879</v>
+      </c>
+      <c r="AA951" t="n">
+        <v>9.560202062129974</v>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr"/>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E952" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F952" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G952" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H952" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I952" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J952" t="n">
+        <v>162</v>
+      </c>
+      <c r="K952" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L952" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M952" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N952" s="2" t="n">
+        <v>45839.85629020934</v>
+      </c>
+      <c r="O952" t="n">
+        <v>39.05</v>
+      </c>
+      <c r="P952" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q952" t="n">
+        <v>4.24926</v>
+      </c>
+      <c r="R952" t="n">
+        <v>9.189835406635508</v>
+      </c>
+      <c r="S952" t="n">
+        <v>6326.099999999999</v>
+      </c>
+      <c r="T952" t="n">
+        <v>1488.753335874952</v>
+      </c>
+      <c r="U952" t="n">
+        <v>8.495174269061048</v>
+      </c>
+      <c r="V952" t="n">
+        <v>-0.003826530612245027</v>
+      </c>
+      <c r="W952" t="n">
+        <v>-0.0002045164022317358</v>
+      </c>
+      <c r="X952" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y952" t="n">
+        <v>10.667</v>
+      </c>
+      <c r="Z952" t="n">
+        <v>0.4341856837272644</v>
+      </c>
+      <c r="AA952" t="n">
+        <v>11.63437480163574</v>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E953" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F953" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G953" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H953" t="n">
+        <v>1</v>
+      </c>
+      <c r="I953" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J953" t="n">
+        <v>30</v>
+      </c>
+      <c r="K953" t="n">
+        <v>9</v>
+      </c>
+      <c r="L953" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M953" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N953" s="2" t="n">
+        <v>45839.85629020934</v>
+      </c>
+      <c r="O953" t="n">
+        <v>45.54</v>
+      </c>
+      <c r="P953" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q953" t="n">
+        <v>1</v>
+      </c>
+      <c r="R953" t="n">
+        <v>45.54</v>
+      </c>
+      <c r="S953" t="n">
+        <v>1366.2</v>
+      </c>
+      <c r="T953" t="n">
+        <v>1366.2</v>
+      </c>
+      <c r="U953" t="n">
+        <v>42.174</v>
+      </c>
+      <c r="V953" t="n">
+        <v>-0.003064798598949259</v>
+      </c>
+      <c r="W953" t="n">
+        <v>-0.003064798598949259</v>
+      </c>
+      <c r="X953" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y953" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z953" t="n">
+        <v>0.468702644109726</v>
+      </c>
+      <c r="AA953" t="n">
+        <v>9.620825290679932</v>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>MHY271836006</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="D954" t="inlineStr">
+        <is>
+          <t>GLOBAL SHIP LEA. A DL-,01</t>
+        </is>
+      </c>
+      <c r="E954" s="2" t="n">
+        <v>45838.31344841435</v>
+      </c>
+      <c r="F954" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="G954" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H954" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="I954" t="n">
+        <v>22.64505496285648</v>
+      </c>
+      <c r="J954" t="n">
+        <v>66</v>
+      </c>
+      <c r="K954" t="n">
+        <v>10</v>
+      </c>
+      <c r="L954" t="n">
+        <v>0.5395355224609375</v>
+      </c>
+      <c r="M954" t="n">
+        <v>12.45218944549561</v>
+      </c>
+      <c r="N954" s="2" t="n">
+        <v>45839.85629020934</v>
+      </c>
+      <c r="O954" t="n">
+        <v>26.17</v>
+      </c>
+      <c r="P954" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q954" t="n">
+        <v>1.180777</v>
+      </c>
+      <c r="R954" t="n">
+        <v>22.16337208465274</v>
+      </c>
+      <c r="S954" t="n">
+        <v>1727.22</v>
+      </c>
+      <c r="T954" t="n">
+        <v>1462.78255758708</v>
+      </c>
+      <c r="U954" t="n">
+        <v>20.40206509457079</v>
+      </c>
+      <c r="V954" t="n">
+        <v>-0.01468373493975894</v>
+      </c>
+      <c r="W954" t="n">
+        <v>-0.021270996206184</v>
+      </c>
+      <c r="X954" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y954" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z954" t="n">
+        <v>0.358627051115036</v>
+      </c>
+      <c r="AA954" t="n">
+        <v>9.922716617584229</v>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>PAP310761054</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>COPA HOLDINGS CL.A O.N.</t>
+        </is>
+      </c>
+      <c r="E955" s="2" t="n">
+        <v>45839.31381715278</v>
+      </c>
+      <c r="F955" t="n">
+        <v>109.97</v>
+      </c>
+      <c r="G955" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H955" t="n">
+        <v>1.1788282</v>
+      </c>
+      <c r="I955" t="n">
+        <v>93.2875545393298</v>
+      </c>
+      <c r="J955" t="n">
+        <v>16</v>
+      </c>
+      <c r="K955" t="n">
+        <v>10</v>
+      </c>
+      <c r="L955" t="n">
+        <v>0.4318655133247375</v>
+      </c>
+      <c r="M955" t="n">
+        <v>11.16087436676025</v>
+      </c>
+      <c r="N955" s="2" t="n">
+        <v>45839.85629020934</v>
+      </c>
+      <c r="O955" t="n">
+        <v>109.1</v>
+      </c>
+      <c r="P955" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q955" t="n">
+        <v>1.180777</v>
+      </c>
+      <c r="R955" t="n">
+        <v>92.39678618401273</v>
+      </c>
+      <c r="S955" t="n">
+        <v>1745.6</v>
+      </c>
+      <c r="T955" t="n">
+        <v>1478.348578944204</v>
+      </c>
+      <c r="U955" t="n">
+        <v>83.9826457277935</v>
+      </c>
+      <c r="V955" t="n">
+        <v>-0.007911248522324277</v>
+      </c>
+      <c r="W955" t="n">
+        <v>-0.009548630143815462</v>
+      </c>
+      <c r="X955" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y955" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z955" t="n">
+        <v>0.4318655133247375</v>
+      </c>
+      <c r="AA955" t="n">
         <v>11.16087436676025</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA955"/>
+  <dimension ref="A1:AA962"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -89671,7 +89671,7 @@
         <v>100</v>
       </c>
       <c r="N949" s="2" t="n">
-        <v>45839.85629020934</v>
+        <v>45839.85629020834</v>
       </c>
       <c r="O949" t="n">
         <v>1</v>
@@ -89762,7 +89762,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N950" s="2" t="n">
-        <v>45839.85629020934</v>
+        <v>45839.85629020834</v>
       </c>
       <c r="O950" t="n">
         <v>370</v>
@@ -89857,7 +89857,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N951" s="2" t="n">
-        <v>45839.85629020934</v>
+        <v>45839.85629020834</v>
       </c>
       <c r="O951" t="n">
         <v>13.98</v>
@@ -89948,7 +89948,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N952" s="2" t="n">
-        <v>45839.85629020934</v>
+        <v>45839.85629020834</v>
       </c>
       <c r="O952" t="n">
         <v>39.05</v>
@@ -90043,7 +90043,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N953" s="2" t="n">
-        <v>45839.85629020934</v>
+        <v>45839.85629020834</v>
       </c>
       <c r="O953" t="n">
         <v>45.54</v>
@@ -90138,7 +90138,7 @@
         <v>12.45218944549561</v>
       </c>
       <c r="N954" s="2" t="n">
-        <v>45839.85629020934</v>
+        <v>45839.85629020834</v>
       </c>
       <c r="O954" t="n">
         <v>26.17</v>
@@ -90233,7 +90233,7 @@
         <v>11.16087436676025</v>
       </c>
       <c r="N955" s="2" t="n">
-        <v>45839.85629020934</v>
+        <v>45839.85629020834</v>
       </c>
       <c r="O955" t="n">
         <v>109.1</v>
@@ -90274,6 +90274,665 @@
         <v>0.4318655133247375</v>
       </c>
       <c r="AA955" t="n">
+        <v>11.16087436676025</v>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D956" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E956" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F956" t="n">
+        <v>1</v>
+      </c>
+      <c r="G956" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H956" t="n">
+        <v>1</v>
+      </c>
+      <c r="I956" t="n">
+        <v>1</v>
+      </c>
+      <c r="J956" t="n">
+        <v>1</v>
+      </c>
+      <c r="K956" t="n">
+        <v>100</v>
+      </c>
+      <c r="L956" t="n">
+        <v>100</v>
+      </c>
+      <c r="M956" t="n">
+        <v>100</v>
+      </c>
+      <c r="N956" s="2" t="n">
+        <v>45839.89511715126</v>
+      </c>
+      <c r="O956" t="n">
+        <v>1</v>
+      </c>
+      <c r="P956" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q956" t="n">
+        <v>1</v>
+      </c>
+      <c r="R956" t="n">
+        <v>1</v>
+      </c>
+      <c r="S956" t="n">
+        <v>0</v>
+      </c>
+      <c r="T956" t="n">
+        <v>1414.591526256027</v>
+      </c>
+      <c r="U956" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V956" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W956" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X956" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y956" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z956" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA956" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr"/>
+      <c r="D957" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E957" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F957" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G957" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H957" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I957" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J957" t="n">
+        <v>3</v>
+      </c>
+      <c r="K957" t="n">
+        <v>10</v>
+      </c>
+      <c r="L957" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M957" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N957" s="2" t="n">
+        <v>45839.89511715126</v>
+      </c>
+      <c r="O957" t="n">
+        <v>370</v>
+      </c>
+      <c r="P957" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q957" t="n">
+        <v>0.85829</v>
+      </c>
+      <c r="R957" t="n">
+        <v>431.0897249181512</v>
+      </c>
+      <c r="S957" t="n">
+        <v>1110</v>
+      </c>
+      <c r="T957" t="n">
+        <v>1293.269174754454</v>
+      </c>
+      <c r="U957" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V957" t="n">
+        <v>0.006348152943160379</v>
+      </c>
+      <c r="W957" t="n">
+        <v>0.0009311861060803395</v>
+      </c>
+      <c r="X957" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y957" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z957" t="n">
+        <v>0.4370984435081482</v>
+      </c>
+      <c r="AA957" t="n">
+        <v>10.20819354057312</v>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D958" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E958" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F958" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G958" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H958" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I958" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J958" t="n">
+        <v>121</v>
+      </c>
+      <c r="K958" t="n">
+        <v>12</v>
+      </c>
+      <c r="L958" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M958" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N958" s="2" t="n">
+        <v>45839.89511715126</v>
+      </c>
+      <c r="O958" t="n">
+        <v>13.98</v>
+      </c>
+      <c r="P958" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q958" t="n">
+        <v>1.1804981</v>
+      </c>
+      <c r="R958" t="n">
+        <v>11.84245870450787</v>
+      </c>
+      <c r="S958" t="n">
+        <v>1691.58</v>
+      </c>
+      <c r="T958" t="n">
+        <v>1432.937503245452</v>
+      </c>
+      <c r="U958" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V958" t="n">
+        <v>-0.01410437235543016</v>
+      </c>
+      <c r="W958" t="n">
+        <v>-0.03928195735560014</v>
+      </c>
+      <c r="X958" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y958" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z958" t="n">
+        <v>0.3516944050788879</v>
+      </c>
+      <c r="AA958" t="n">
+        <v>9.560202062129974</v>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr"/>
+      <c r="D959" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E959" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F959" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G959" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H959" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I959" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J959" t="n">
+        <v>162</v>
+      </c>
+      <c r="K959" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L959" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M959" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N959" s="2" t="n">
+        <v>45839.89511715126</v>
+      </c>
+      <c r="O959" t="n">
+        <v>39.05</v>
+      </c>
+      <c r="P959" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q959" t="n">
+        <v>4.2458</v>
+      </c>
+      <c r="R959" t="n">
+        <v>9.197324414715718</v>
+      </c>
+      <c r="S959" t="n">
+        <v>6326.099999999999</v>
+      </c>
+      <c r="T959" t="n">
+        <v>1489.966555183946</v>
+      </c>
+      <c r="U959" t="n">
+        <v>8.495174269061048</v>
+      </c>
+      <c r="V959" t="n">
+        <v>-0.003826530612245027</v>
+      </c>
+      <c r="W959" t="n">
+        <v>0.0006102399153640192</v>
+      </c>
+      <c r="X959" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y959" t="n">
+        <v>10.667</v>
+      </c>
+      <c r="Z959" t="n">
+        <v>0.4341856837272644</v>
+      </c>
+      <c r="AA959" t="n">
+        <v>11.63437480163574</v>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D960" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E960" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F960" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G960" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H960" t="n">
+        <v>1</v>
+      </c>
+      <c r="I960" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J960" t="n">
+        <v>30</v>
+      </c>
+      <c r="K960" t="n">
+        <v>9</v>
+      </c>
+      <c r="L960" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M960" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N960" s="2" t="n">
+        <v>45839.89511715126</v>
+      </c>
+      <c r="O960" t="n">
+        <v>45.54</v>
+      </c>
+      <c r="P960" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q960" t="n">
+        <v>1</v>
+      </c>
+      <c r="R960" t="n">
+        <v>45.54</v>
+      </c>
+      <c r="S960" t="n">
+        <v>1366.2</v>
+      </c>
+      <c r="T960" t="n">
+        <v>1366.2</v>
+      </c>
+      <c r="U960" t="n">
+        <v>42.174</v>
+      </c>
+      <c r="V960" t="n">
+        <v>-0.003064798598949259</v>
+      </c>
+      <c r="W960" t="n">
+        <v>-0.003064798598949259</v>
+      </c>
+      <c r="X960" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y960" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z960" t="n">
+        <v>0.468702644109726</v>
+      </c>
+      <c r="AA960" t="n">
+        <v>9.620825290679932</v>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>MHY271836006</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="D961" t="inlineStr">
+        <is>
+          <t>GLOBAL SHIP LEA. A DL-,01</t>
+        </is>
+      </c>
+      <c r="E961" s="2" t="n">
+        <v>45838.31344841435</v>
+      </c>
+      <c r="F961" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="G961" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H961" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="I961" t="n">
+        <v>22.64505496285648</v>
+      </c>
+      <c r="J961" t="n">
+        <v>66</v>
+      </c>
+      <c r="K961" t="n">
+        <v>10</v>
+      </c>
+      <c r="L961" t="n">
+        <v>0.5395355224609375</v>
+      </c>
+      <c r="M961" t="n">
+        <v>12.45218944549561</v>
+      </c>
+      <c r="N961" s="2" t="n">
+        <v>45839.89511715126</v>
+      </c>
+      <c r="O961" t="n">
+        <v>26.17</v>
+      </c>
+      <c r="P961" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q961" t="n">
+        <v>1.1804981</v>
+      </c>
+      <c r="R961" t="n">
+        <v>22.16860831881051</v>
+      </c>
+      <c r="S961" t="n">
+        <v>1727.22</v>
+      </c>
+      <c r="T961" t="n">
+        <v>1463.128149041494</v>
+      </c>
+      <c r="U961" t="n">
+        <v>20.40206509457079</v>
+      </c>
+      <c r="V961" t="n">
+        <v>-0.01468373493975894</v>
+      </c>
+      <c r="W961" t="n">
+        <v>-0.02103976540694941</v>
+      </c>
+      <c r="X961" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y961" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z961" t="n">
+        <v>0.358627051115036</v>
+      </c>
+      <c r="AA961" t="n">
+        <v>9.922716617584229</v>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>PAP310761054</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="D962" t="inlineStr">
+        <is>
+          <t>COPA HOLDINGS CL.A O.N.</t>
+        </is>
+      </c>
+      <c r="E962" s="2" t="n">
+        <v>45839.31381715278</v>
+      </c>
+      <c r="F962" t="n">
+        <v>109.97</v>
+      </c>
+      <c r="G962" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H962" t="n">
+        <v>1.1788282</v>
+      </c>
+      <c r="I962" t="n">
+        <v>93.2875545393298</v>
+      </c>
+      <c r="J962" t="n">
+        <v>16</v>
+      </c>
+      <c r="K962" t="n">
+        <v>10</v>
+      </c>
+      <c r="L962" t="n">
+        <v>0.4318655133247375</v>
+      </c>
+      <c r="M962" t="n">
+        <v>11.16087436676025</v>
+      </c>
+      <c r="N962" s="2" t="n">
+        <v>45839.89511715126</v>
+      </c>
+      <c r="O962" t="n">
+        <v>109.1</v>
+      </c>
+      <c r="P962" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q962" t="n">
+        <v>1.1804981</v>
+      </c>
+      <c r="R962" t="n">
+        <v>92.41861549798342</v>
+      </c>
+      <c r="S962" t="n">
+        <v>1745.6</v>
+      </c>
+      <c r="T962" t="n">
+        <v>1478.697847967735</v>
+      </c>
+      <c r="U962" t="n">
+        <v>83.9826457277935</v>
+      </c>
+      <c r="V962" t="n">
+        <v>-0.007911248522324277</v>
+      </c>
+      <c r="W962" t="n">
+        <v>-0.009314629862872459</v>
+      </c>
+      <c r="X962" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y962" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z962" t="n">
+        <v>0.4318655133247375</v>
+      </c>
+      <c r="AA962" t="n">
         <v>11.16087436676025</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA962"/>
+  <dimension ref="A1:AA969"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -90330,7 +90330,7 @@
         <v>100</v>
       </c>
       <c r="N956" s="2" t="n">
-        <v>45839.89511715126</v>
+        <v>45839.89511715278</v>
       </c>
       <c r="O956" t="n">
         <v>1</v>
@@ -90421,7 +90421,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N957" s="2" t="n">
-        <v>45839.89511715126</v>
+        <v>45839.89511715278</v>
       </c>
       <c r="O957" t="n">
         <v>370</v>
@@ -90516,7 +90516,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N958" s="2" t="n">
-        <v>45839.89511715126</v>
+        <v>45839.89511715278</v>
       </c>
       <c r="O958" t="n">
         <v>13.98</v>
@@ -90607,7 +90607,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N959" s="2" t="n">
-        <v>45839.89511715126</v>
+        <v>45839.89511715278</v>
       </c>
       <c r="O959" t="n">
         <v>39.05</v>
@@ -90702,7 +90702,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N960" s="2" t="n">
-        <v>45839.89511715126</v>
+        <v>45839.89511715278</v>
       </c>
       <c r="O960" t="n">
         <v>45.54</v>
@@ -90797,7 +90797,7 @@
         <v>12.45218944549561</v>
       </c>
       <c r="N961" s="2" t="n">
-        <v>45839.89511715126</v>
+        <v>45839.89511715278</v>
       </c>
       <c r="O961" t="n">
         <v>26.17</v>
@@ -90892,7 +90892,7 @@
         <v>11.16087436676025</v>
       </c>
       <c r="N962" s="2" t="n">
-        <v>45839.89511715126</v>
+        <v>45839.89511715278</v>
       </c>
       <c r="O962" t="n">
         <v>109.1</v>
@@ -90934,6 +90934,665 @@
       </c>
       <c r="AA962" t="n">
         <v>11.16087436676025</v>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D963" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E963" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F963" t="n">
+        <v>1</v>
+      </c>
+      <c r="G963" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H963" t="n">
+        <v>1</v>
+      </c>
+      <c r="I963" t="n">
+        <v>1</v>
+      </c>
+      <c r="J963" t="n">
+        <v>1</v>
+      </c>
+      <c r="K963" t="n">
+        <v>100</v>
+      </c>
+      <c r="L963" t="n">
+        <v>100</v>
+      </c>
+      <c r="M963" t="n">
+        <v>100</v>
+      </c>
+      <c r="N963" s="2" t="n">
+        <v>45840.31280041537</v>
+      </c>
+      <c r="O963" t="n">
+        <v>1</v>
+      </c>
+      <c r="P963" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q963" t="n">
+        <v>1</v>
+      </c>
+      <c r="R963" t="n">
+        <v>1</v>
+      </c>
+      <c r="S963" t="n">
+        <v>0</v>
+      </c>
+      <c r="T963" t="n">
+        <v>1414.591526256027</v>
+      </c>
+      <c r="U963" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V963" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W963" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X963" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y963" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z963" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA963" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr"/>
+      <c r="D964" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E964" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F964" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G964" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H964" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I964" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J964" t="n">
+        <v>3</v>
+      </c>
+      <c r="K964" t="n">
+        <v>10</v>
+      </c>
+      <c r="L964" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M964" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N964" s="2" t="n">
+        <v>45840.31280041537</v>
+      </c>
+      <c r="O964" t="n">
+        <v>365</v>
+      </c>
+      <c r="P964" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q964" t="n">
+        <v>0.85864</v>
+      </c>
+      <c r="R964" t="n">
+        <v>425.0908413304761</v>
+      </c>
+      <c r="S964" t="n">
+        <v>1095</v>
+      </c>
+      <c r="T964" t="n">
+        <v>1275.272523991428</v>
+      </c>
+      <c r="U964" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V964" t="n">
+        <v>-0.007251146420936383</v>
+      </c>
+      <c r="W964" t="n">
+        <v>-0.01299739840347613</v>
+      </c>
+      <c r="X964" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y964" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z964" t="n">
+        <v>0.4170325100421906</v>
+      </c>
+      <c r="AA964" t="n">
+        <v>9.962165534496307</v>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D965" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E965" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F965" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G965" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H965" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I965" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J965" t="n">
+        <v>121</v>
+      </c>
+      <c r="K965" t="n">
+        <v>12</v>
+      </c>
+      <c r="L965" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M965" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N965" s="2" t="n">
+        <v>45840.31280041537</v>
+      </c>
+      <c r="O965" t="n">
+        <v>13.98</v>
+      </c>
+      <c r="P965" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q965" t="n">
+        <v>1.1781338</v>
+      </c>
+      <c r="R965" t="n">
+        <v>11.86622436263182</v>
+      </c>
+      <c r="S965" t="n">
+        <v>1691.58</v>
+      </c>
+      <c r="T965" t="n">
+        <v>1435.81314787845</v>
+      </c>
+      <c r="U965" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V965" t="n">
+        <v>-0.01410437235543016</v>
+      </c>
+      <c r="W965" t="n">
+        <v>-0.03735397118949202</v>
+      </c>
+      <c r="X965" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y965" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z965" t="n">
+        <v>0.323738694190979</v>
+      </c>
+      <c r="AA965" t="n">
+        <v>9.174263775348663</v>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr"/>
+      <c r="D966" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E966" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F966" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G966" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H966" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I966" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J966" t="n">
+        <v>162</v>
+      </c>
+      <c r="K966" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L966" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M966" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N966" s="2" t="n">
+        <v>45840.31280041537</v>
+      </c>
+      <c r="O966" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="P966" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q966" t="n">
+        <v>4.25572</v>
+      </c>
+      <c r="R966" t="n">
+        <v>9.234630097844782</v>
+      </c>
+      <c r="S966" t="n">
+        <v>6366.599999999999</v>
+      </c>
+      <c r="T966" t="n">
+        <v>1496.010075850855</v>
+      </c>
+      <c r="U966" t="n">
+        <v>8.495174269061048</v>
+      </c>
+      <c r="V966" t="n">
+        <v>0.002551020408163129</v>
+      </c>
+      <c r="W966" t="n">
+        <v>0.00466886032090863</v>
+      </c>
+      <c r="X966" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y966" t="n">
+        <v>10.667</v>
+      </c>
+      <c r="Z966" t="n">
+        <v>0.3741045594215393</v>
+      </c>
+      <c r="AA966" t="n">
+        <v>10.81489402484894</v>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D967" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E967" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F967" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G967" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H967" t="n">
+        <v>1</v>
+      </c>
+      <c r="I967" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J967" t="n">
+        <v>30</v>
+      </c>
+      <c r="K967" t="n">
+        <v>9</v>
+      </c>
+      <c r="L967" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M967" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N967" s="2" t="n">
+        <v>45840.31280041537</v>
+      </c>
+      <c r="O967" t="n">
+        <v>45.54</v>
+      </c>
+      <c r="P967" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q967" t="n">
+        <v>1</v>
+      </c>
+      <c r="R967" t="n">
+        <v>45.54</v>
+      </c>
+      <c r="S967" t="n">
+        <v>1366.2</v>
+      </c>
+      <c r="T967" t="n">
+        <v>1366.2</v>
+      </c>
+      <c r="U967" t="n">
+        <v>42.174</v>
+      </c>
+      <c r="V967" t="n">
+        <v>-0.003064798598949259</v>
+      </c>
+      <c r="W967" t="n">
+        <v>-0.003064798598949259</v>
+      </c>
+      <c r="X967" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y967" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z967" t="n">
+        <v>0.4272054731845856</v>
+      </c>
+      <c r="AA967" t="n">
+        <v>10.09143114089966</v>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>MHY271836006</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="D968" t="inlineStr">
+        <is>
+          <t>GLOBAL SHIP LEA. A DL-,01</t>
+        </is>
+      </c>
+      <c r="E968" s="2" t="n">
+        <v>45838.31344841435</v>
+      </c>
+      <c r="F968" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="G968" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H968" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="I968" t="n">
+        <v>22.64505496285648</v>
+      </c>
+      <c r="J968" t="n">
+        <v>66</v>
+      </c>
+      <c r="K968" t="n">
+        <v>10</v>
+      </c>
+      <c r="L968" t="n">
+        <v>0.5395355224609375</v>
+      </c>
+      <c r="M968" t="n">
+        <v>12.45218944549561</v>
+      </c>
+      <c r="N968" s="2" t="n">
+        <v>45840.31280041537</v>
+      </c>
+      <c r="O968" t="n">
+        <v>26.17</v>
+      </c>
+      <c r="P968" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q968" t="n">
+        <v>1.1781338</v>
+      </c>
+      <c r="R968" t="n">
+        <v>22.21309667883224</v>
+      </c>
+      <c r="S968" t="n">
+        <v>1727.22</v>
+      </c>
+      <c r="T968" t="n">
+        <v>1466.064380802928</v>
+      </c>
+      <c r="U968" t="n">
+        <v>20.40206509457079</v>
+      </c>
+      <c r="V968" t="n">
+        <v>-0.01468373493975894</v>
+      </c>
+      <c r="W968" t="n">
+        <v>-0.0190751704834794</v>
+      </c>
+      <c r="X968" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y968" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z968" t="n">
+        <v>0.3208521902561188</v>
+      </c>
+      <c r="AA968" t="n">
+        <v>9.439456224441528</v>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>PAP310761054</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="D969" t="inlineStr">
+        <is>
+          <t>COPA HOLDINGS CL.A O.N.</t>
+        </is>
+      </c>
+      <c r="E969" s="2" t="n">
+        <v>45839.31381715278</v>
+      </c>
+      <c r="F969" t="n">
+        <v>109.97</v>
+      </c>
+      <c r="G969" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H969" t="n">
+        <v>1.1788282</v>
+      </c>
+      <c r="I969" t="n">
+        <v>93.2875545393298</v>
+      </c>
+      <c r="J969" t="n">
+        <v>16</v>
+      </c>
+      <c r="K969" t="n">
+        <v>10</v>
+      </c>
+      <c r="L969" t="n">
+        <v>0.4318655133247375</v>
+      </c>
+      <c r="M969" t="n">
+        <v>11.16087436676025</v>
+      </c>
+      <c r="N969" s="2" t="n">
+        <v>45840.31280041537</v>
+      </c>
+      <c r="O969" t="n">
+        <v>109.1</v>
+      </c>
+      <c r="P969" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q969" t="n">
+        <v>1.1781338</v>
+      </c>
+      <c r="R969" t="n">
+        <v>92.60408282998077</v>
+      </c>
+      <c r="S969" t="n">
+        <v>1745.6</v>
+      </c>
+      <c r="T969" t="n">
+        <v>1481.665325279692</v>
+      </c>
+      <c r="U969" t="n">
+        <v>83.9826457277935</v>
+      </c>
+      <c r="V969" t="n">
+        <v>-0.007911248522324277</v>
+      </c>
+      <c r="W969" t="n">
+        <v>-0.007326504727496963</v>
+      </c>
+      <c r="X969" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y969" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z969" t="n">
+        <v>0.4244736433029175</v>
+      </c>
+      <c r="AA969" t="n">
+        <v>11.11160755157471</v>
       </c>
     </row>
   </sheetData>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA969"/>
+  <dimension ref="A1:AA976"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -90989,7 +90989,7 @@
         <v>100</v>
       </c>
       <c r="N963" s="2" t="n">
-        <v>45840.31280041537</v>
+        <v>45840.31280041666</v>
       </c>
       <c r="O963" t="n">
         <v>1</v>
@@ -91080,7 +91080,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N964" s="2" t="n">
-        <v>45840.31280041537</v>
+        <v>45840.31280041666</v>
       </c>
       <c r="O964" t="n">
         <v>365</v>
@@ -91175,7 +91175,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N965" s="2" t="n">
-        <v>45840.31280041537</v>
+        <v>45840.31280041666</v>
       </c>
       <c r="O965" t="n">
         <v>13.98</v>
@@ -91266,7 +91266,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N966" s="2" t="n">
-        <v>45840.31280041537</v>
+        <v>45840.31280041666</v>
       </c>
       <c r="O966" t="n">
         <v>39.3</v>
@@ -91361,7 +91361,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N967" s="2" t="n">
-        <v>45840.31280041537</v>
+        <v>45840.31280041666</v>
       </c>
       <c r="O967" t="n">
         <v>45.54</v>
@@ -91456,7 +91456,7 @@
         <v>12.45218944549561</v>
       </c>
       <c r="N968" s="2" t="n">
-        <v>45840.31280041537</v>
+        <v>45840.31280041666</v>
       </c>
       <c r="O968" t="n">
         <v>26.17</v>
@@ -91551,7 +91551,7 @@
         <v>11.16087436676025</v>
       </c>
       <c r="N969" s="2" t="n">
-        <v>45840.31280041537</v>
+        <v>45840.31280041666</v>
       </c>
       <c r="O969" t="n">
         <v>109.1</v>
@@ -91592,6 +91592,665 @@
         <v>0.4244736433029175</v>
       </c>
       <c r="AA969" t="n">
+        <v>11.11160755157471</v>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D970" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E970" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F970" t="n">
+        <v>1</v>
+      </c>
+      <c r="G970" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H970" t="n">
+        <v>1</v>
+      </c>
+      <c r="I970" t="n">
+        <v>1</v>
+      </c>
+      <c r="J970" t="n">
+        <v>1</v>
+      </c>
+      <c r="K970" t="n">
+        <v>100</v>
+      </c>
+      <c r="L970" t="n">
+        <v>100</v>
+      </c>
+      <c r="M970" t="n">
+        <v>100</v>
+      </c>
+      <c r="N970" s="2" t="n">
+        <v>45840.36099544726</v>
+      </c>
+      <c r="O970" t="n">
+        <v>1</v>
+      </c>
+      <c r="P970" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q970" t="n">
+        <v>1</v>
+      </c>
+      <c r="R970" t="n">
+        <v>1</v>
+      </c>
+      <c r="S970" t="n">
+        <v>0</v>
+      </c>
+      <c r="T970" t="n">
+        <v>1414.591526256027</v>
+      </c>
+      <c r="U970" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V970" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W970" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X970" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y970" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z970" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA970" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr"/>
+      <c r="D971" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E971" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F971" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G971" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H971" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I971" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J971" t="n">
+        <v>3</v>
+      </c>
+      <c r="K971" t="n">
+        <v>10</v>
+      </c>
+      <c r="L971" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M971" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N971" s="2" t="n">
+        <v>45840.36099544726</v>
+      </c>
+      <c r="O971" t="n">
+        <v>365.1</v>
+      </c>
+      <c r="P971" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q971" t="n">
+        <v>0.85954</v>
+      </c>
+      <c r="R971" t="n">
+        <v>424.762082043884</v>
+      </c>
+      <c r="S971" t="n">
+        <v>1095.3</v>
+      </c>
+      <c r="T971" t="n">
+        <v>1274.286246131652</v>
+      </c>
+      <c r="U971" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V971" t="n">
+        <v>-0.00697916043365443</v>
+      </c>
+      <c r="W971" t="n">
+        <v>-0.01376073235381448</v>
+      </c>
+      <c r="X971" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y971" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z971" t="n">
+        <v>0.4170325100421906</v>
+      </c>
+      <c r="AA971" t="n">
+        <v>9.962165534496307</v>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D972" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E972" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F972" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G972" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H972" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I972" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J972" t="n">
+        <v>121</v>
+      </c>
+      <c r="K972" t="n">
+        <v>12</v>
+      </c>
+      <c r="L972" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M972" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N972" s="2" t="n">
+        <v>45840.36099544726</v>
+      </c>
+      <c r="O972" t="n">
+        <v>13.98</v>
+      </c>
+      <c r="P972" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q972" t="n">
+        <v>1.177995</v>
+      </c>
+      <c r="R972" t="n">
+        <v>11.8676225281092</v>
+      </c>
+      <c r="S972" t="n">
+        <v>1691.58</v>
+      </c>
+      <c r="T972" t="n">
+        <v>1435.982325901214</v>
+      </c>
+      <c r="U972" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V972" t="n">
+        <v>-0.01410437235543016</v>
+      </c>
+      <c r="W972" t="n">
+        <v>-0.03724054518276132</v>
+      </c>
+      <c r="X972" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y972" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z972" t="n">
+        <v>0.323738694190979</v>
+      </c>
+      <c r="AA972" t="n">
+        <v>9.174263775348663</v>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr"/>
+      <c r="D973" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E973" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F973" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G973" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H973" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I973" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J973" t="n">
+        <v>162</v>
+      </c>
+      <c r="K973" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L973" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M973" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N973" s="2" t="n">
+        <v>45840.36099544726</v>
+      </c>
+      <c r="O973" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="P973" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q973" t="n">
+        <v>4.25183</v>
+      </c>
+      <c r="R973" t="n">
+        <v>9.149001723963563</v>
+      </c>
+      <c r="S973" t="n">
+        <v>6301.8</v>
+      </c>
+      <c r="T973" t="n">
+        <v>1482.138279282097</v>
+      </c>
+      <c r="U973" t="n">
+        <v>8.495174269061048</v>
+      </c>
+      <c r="V973" t="n">
+        <v>-0.007653061224489943</v>
+      </c>
+      <c r="W973" t="n">
+        <v>-0.004646960658044819</v>
+      </c>
+      <c r="X973" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y973" t="n">
+        <v>10.667</v>
+      </c>
+      <c r="Z973" t="n">
+        <v>0.3741045594215393</v>
+      </c>
+      <c r="AA973" t="n">
+        <v>10.81489402484894</v>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D974" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E974" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F974" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G974" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H974" t="n">
+        <v>1</v>
+      </c>
+      <c r="I974" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J974" t="n">
+        <v>30</v>
+      </c>
+      <c r="K974" t="n">
+        <v>9</v>
+      </c>
+      <c r="L974" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M974" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N974" s="2" t="n">
+        <v>45840.36099544726</v>
+      </c>
+      <c r="O974" t="n">
+        <v>45.18</v>
+      </c>
+      <c r="P974" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q974" t="n">
+        <v>1</v>
+      </c>
+      <c r="R974" t="n">
+        <v>45.18</v>
+      </c>
+      <c r="S974" t="n">
+        <v>1355.4</v>
+      </c>
+      <c r="T974" t="n">
+        <v>1355.4</v>
+      </c>
+      <c r="U974" t="n">
+        <v>42.174</v>
+      </c>
+      <c r="V974" t="n">
+        <v>-0.01094570928196148</v>
+      </c>
+      <c r="W974" t="n">
+        <v>-0.01094570928196148</v>
+      </c>
+      <c r="X974" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y974" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z974" t="n">
+        <v>0.4272054731845856</v>
+      </c>
+      <c r="AA974" t="n">
+        <v>10.09143114089966</v>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>MHY271836006</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="D975" t="inlineStr">
+        <is>
+          <t>GLOBAL SHIP LEA. A DL-,01</t>
+        </is>
+      </c>
+      <c r="E975" s="2" t="n">
+        <v>45838.31344841435</v>
+      </c>
+      <c r="F975" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="G975" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H975" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="I975" t="n">
+        <v>22.64505496285648</v>
+      </c>
+      <c r="J975" t="n">
+        <v>66</v>
+      </c>
+      <c r="K975" t="n">
+        <v>10</v>
+      </c>
+      <c r="L975" t="n">
+        <v>0.5395355224609375</v>
+      </c>
+      <c r="M975" t="n">
+        <v>12.45218944549561</v>
+      </c>
+      <c r="N975" s="2" t="n">
+        <v>45840.36099544726</v>
+      </c>
+      <c r="O975" t="n">
+        <v>26.17</v>
+      </c>
+      <c r="P975" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q975" t="n">
+        <v>1.177995</v>
+      </c>
+      <c r="R975" t="n">
+        <v>22.21571398859928</v>
+      </c>
+      <c r="S975" t="n">
+        <v>1727.22</v>
+      </c>
+      <c r="T975" t="n">
+        <v>1466.237123247552</v>
+      </c>
+      <c r="U975" t="n">
+        <v>20.40206509457079</v>
+      </c>
+      <c r="V975" t="n">
+        <v>-0.01468373493975894</v>
+      </c>
+      <c r="W975" t="n">
+        <v>-0.01895959073455256</v>
+      </c>
+      <c r="X975" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y975" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z975" t="n">
+        <v>0.3208521902561188</v>
+      </c>
+      <c r="AA975" t="n">
+        <v>9.439456224441528</v>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>PAP310761054</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="D976" t="inlineStr">
+        <is>
+          <t>COPA HOLDINGS CL.A O.N.</t>
+        </is>
+      </c>
+      <c r="E976" s="2" t="n">
+        <v>45839.31381715278</v>
+      </c>
+      <c r="F976" t="n">
+        <v>109.97</v>
+      </c>
+      <c r="G976" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H976" t="n">
+        <v>1.1788282</v>
+      </c>
+      <c r="I976" t="n">
+        <v>93.2875545393298</v>
+      </c>
+      <c r="J976" t="n">
+        <v>16</v>
+      </c>
+      <c r="K976" t="n">
+        <v>10</v>
+      </c>
+      <c r="L976" t="n">
+        <v>0.4318655133247375</v>
+      </c>
+      <c r="M976" t="n">
+        <v>11.16087436676025</v>
+      </c>
+      <c r="N976" s="2" t="n">
+        <v>45840.36099544726</v>
+      </c>
+      <c r="O976" t="n">
+        <v>109.1</v>
+      </c>
+      <c r="P976" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q976" t="n">
+        <v>1.177995</v>
+      </c>
+      <c r="R976" t="n">
+        <v>92.61499412136725</v>
+      </c>
+      <c r="S976" t="n">
+        <v>1745.6</v>
+      </c>
+      <c r="T976" t="n">
+        <v>1481.839905941876</v>
+      </c>
+      <c r="U976" t="n">
+        <v>83.9826457277935</v>
+      </c>
+      <c r="V976" t="n">
+        <v>-0.007911248522324277</v>
+      </c>
+      <c r="W976" t="n">
+        <v>-0.007209540664709024</v>
+      </c>
+      <c r="X976" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y976" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z976" t="n">
+        <v>0.4244736433029175</v>
+      </c>
+      <c r="AA976" t="n">
         <v>11.11160755157471</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA976"/>
+  <dimension ref="A1:AA983"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -91648,7 +91648,7 @@
         <v>100</v>
       </c>
       <c r="N970" s="2" t="n">
-        <v>45840.36099544726</v>
+        <v>45840.36099545139</v>
       </c>
       <c r="O970" t="n">
         <v>1</v>
@@ -91739,7 +91739,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N971" s="2" t="n">
-        <v>45840.36099544726</v>
+        <v>45840.36099545139</v>
       </c>
       <c r="O971" t="n">
         <v>365.1</v>
@@ -91834,7 +91834,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N972" s="2" t="n">
-        <v>45840.36099544726</v>
+        <v>45840.36099545139</v>
       </c>
       <c r="O972" t="n">
         <v>13.98</v>
@@ -91925,7 +91925,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N973" s="2" t="n">
-        <v>45840.36099544726</v>
+        <v>45840.36099545139</v>
       </c>
       <c r="O973" t="n">
         <v>38.9</v>
@@ -92020,7 +92020,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N974" s="2" t="n">
-        <v>45840.36099544726</v>
+        <v>45840.36099545139</v>
       </c>
       <c r="O974" t="n">
         <v>45.18</v>
@@ -92115,7 +92115,7 @@
         <v>12.45218944549561</v>
       </c>
       <c r="N975" s="2" t="n">
-        <v>45840.36099544726</v>
+        <v>45840.36099545139</v>
       </c>
       <c r="O975" t="n">
         <v>26.17</v>
@@ -92210,7 +92210,7 @@
         <v>11.16087436676025</v>
       </c>
       <c r="N976" s="2" t="n">
-        <v>45840.36099544726</v>
+        <v>45840.36099545139</v>
       </c>
       <c r="O976" t="n">
         <v>109.1</v>
@@ -92251,6 +92251,665 @@
         <v>0.4244736433029175</v>
       </c>
       <c r="AA976" t="n">
+        <v>11.11160755157471</v>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D977" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E977" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F977" t="n">
+        <v>1</v>
+      </c>
+      <c r="G977" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H977" t="n">
+        <v>1</v>
+      </c>
+      <c r="I977" t="n">
+        <v>1</v>
+      </c>
+      <c r="J977" t="n">
+        <v>1</v>
+      </c>
+      <c r="K977" t="n">
+        <v>100</v>
+      </c>
+      <c r="L977" t="n">
+        <v>100</v>
+      </c>
+      <c r="M977" t="n">
+        <v>100</v>
+      </c>
+      <c r="N977" s="2" t="n">
+        <v>45840.39921379081</v>
+      </c>
+      <c r="O977" t="n">
+        <v>1</v>
+      </c>
+      <c r="P977" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q977" t="n">
+        <v>1</v>
+      </c>
+      <c r="R977" t="n">
+        <v>1</v>
+      </c>
+      <c r="S977" t="n">
+        <v>0</v>
+      </c>
+      <c r="T977" t="n">
+        <v>1414.591526256027</v>
+      </c>
+      <c r="U977" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V977" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W977" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X977" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y977" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z977" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA977" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C978" t="inlineStr"/>
+      <c r="D978" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E978" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F978" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G978" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H978" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I978" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J978" t="n">
+        <v>3</v>
+      </c>
+      <c r="K978" t="n">
+        <v>10</v>
+      </c>
+      <c r="L978" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M978" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N978" s="2" t="n">
+        <v>45840.39921379081</v>
+      </c>
+      <c r="O978" t="n">
+        <v>365.1</v>
+      </c>
+      <c r="P978" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q978" t="n">
+        <v>0.85933</v>
+      </c>
+      <c r="R978" t="n">
+        <v>424.8658838862835</v>
+      </c>
+      <c r="S978" t="n">
+        <v>1095.3</v>
+      </c>
+      <c r="T978" t="n">
+        <v>1274.597651658851</v>
+      </c>
+      <c r="U978" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V978" t="n">
+        <v>-0.00697916043365443</v>
+      </c>
+      <c r="W978" t="n">
+        <v>-0.0135197187196977</v>
+      </c>
+      <c r="X978" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y978" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z978" t="n">
+        <v>0.4170325100421906</v>
+      </c>
+      <c r="AA978" t="n">
+        <v>9.962165534496307</v>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D979" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E979" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F979" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G979" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H979" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I979" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J979" t="n">
+        <v>121</v>
+      </c>
+      <c r="K979" t="n">
+        <v>12</v>
+      </c>
+      <c r="L979" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M979" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N979" s="2" t="n">
+        <v>45840.39921379081</v>
+      </c>
+      <c r="O979" t="n">
+        <v>13.98</v>
+      </c>
+      <c r="P979" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q979" t="n">
+        <v>1.1775789</v>
+      </c>
+      <c r="R979" t="n">
+        <v>11.87181597768098</v>
+      </c>
+      <c r="S979" t="n">
+        <v>1691.58</v>
+      </c>
+      <c r="T979" t="n">
+        <v>1436.489733299399</v>
+      </c>
+      <c r="U979" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V979" t="n">
+        <v>-0.01410437235543016</v>
+      </c>
+      <c r="W979" t="n">
+        <v>-0.03690035208899134</v>
+      </c>
+      <c r="X979" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y979" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z979" t="n">
+        <v>0.323738694190979</v>
+      </c>
+      <c r="AA979" t="n">
+        <v>9.174263775348663</v>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C980" t="inlineStr"/>
+      <c r="D980" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E980" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F980" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G980" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H980" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I980" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J980" t="n">
+        <v>162</v>
+      </c>
+      <c r="K980" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L980" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M980" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N980" s="2" t="n">
+        <v>45840.39921379081</v>
+      </c>
+      <c r="O980" t="n">
+        <v>39</v>
+      </c>
+      <c r="P980" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q980" t="n">
+        <v>4.25165</v>
+      </c>
+      <c r="R980" t="n">
+        <v>9.172909341079347</v>
+      </c>
+      <c r="S980" t="n">
+        <v>6318</v>
+      </c>
+      <c r="T980" t="n">
+        <v>1486.011313254854</v>
+      </c>
+      <c r="U980" t="n">
+        <v>8.495174269061048</v>
+      </c>
+      <c r="V980" t="n">
+        <v>-0.005102040816326592</v>
+      </c>
+      <c r="W980" t="n">
+        <v>-0.002045964387895505</v>
+      </c>
+      <c r="X980" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y980" t="n">
+        <v>10.667</v>
+      </c>
+      <c r="Z980" t="n">
+        <v>0.3741045594215393</v>
+      </c>
+      <c r="AA980" t="n">
+        <v>10.81489402484894</v>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D981" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E981" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F981" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G981" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H981" t="n">
+        <v>1</v>
+      </c>
+      <c r="I981" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J981" t="n">
+        <v>30</v>
+      </c>
+      <c r="K981" t="n">
+        <v>9</v>
+      </c>
+      <c r="L981" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M981" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N981" s="2" t="n">
+        <v>45840.39921379081</v>
+      </c>
+      <c r="O981" t="n">
+        <v>45</v>
+      </c>
+      <c r="P981" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q981" t="n">
+        <v>1</v>
+      </c>
+      <c r="R981" t="n">
+        <v>45</v>
+      </c>
+      <c r="S981" t="n">
+        <v>1350</v>
+      </c>
+      <c r="T981" t="n">
+        <v>1350</v>
+      </c>
+      <c r="U981" t="n">
+        <v>42.174</v>
+      </c>
+      <c r="V981" t="n">
+        <v>-0.01488616462346759</v>
+      </c>
+      <c r="W981" t="n">
+        <v>-0.01488616462346759</v>
+      </c>
+      <c r="X981" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y981" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z981" t="n">
+        <v>0.4272054731845856</v>
+      </c>
+      <c r="AA981" t="n">
+        <v>10.09143114089966</v>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>MHY271836006</t>
+        </is>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="D982" t="inlineStr">
+        <is>
+          <t>GLOBAL SHIP LEA. A DL-,01</t>
+        </is>
+      </c>
+      <c r="E982" s="2" t="n">
+        <v>45838.31344841435</v>
+      </c>
+      <c r="F982" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="G982" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H982" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="I982" t="n">
+        <v>22.64505496285648</v>
+      </c>
+      <c r="J982" t="n">
+        <v>66</v>
+      </c>
+      <c r="K982" t="n">
+        <v>10</v>
+      </c>
+      <c r="L982" t="n">
+        <v>0.5395355224609375</v>
+      </c>
+      <c r="M982" t="n">
+        <v>12.45218944549561</v>
+      </c>
+      <c r="N982" s="2" t="n">
+        <v>45840.39921379081</v>
+      </c>
+      <c r="O982" t="n">
+        <v>26.17</v>
+      </c>
+      <c r="P982" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q982" t="n">
+        <v>1.1775789</v>
+      </c>
+      <c r="R982" t="n">
+        <v>22.2235639582197</v>
+      </c>
+      <c r="S982" t="n">
+        <v>1727.22</v>
+      </c>
+      <c r="T982" t="n">
+        <v>1466.7552212425</v>
+      </c>
+      <c r="U982" t="n">
+        <v>20.40206509457079</v>
+      </c>
+      <c r="V982" t="n">
+        <v>-0.01468373493975894</v>
+      </c>
+      <c r="W982" t="n">
+        <v>-0.01861293802678488</v>
+      </c>
+      <c r="X982" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y982" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z982" t="n">
+        <v>0.3208521902561188</v>
+      </c>
+      <c r="AA982" t="n">
+        <v>9.439456224441528</v>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>PAP310761054</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="D983" t="inlineStr">
+        <is>
+          <t>COPA HOLDINGS CL.A O.N.</t>
+        </is>
+      </c>
+      <c r="E983" s="2" t="n">
+        <v>45839.31381715278</v>
+      </c>
+      <c r="F983" t="n">
+        <v>109.97</v>
+      </c>
+      <c r="G983" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H983" t="n">
+        <v>1.1788282</v>
+      </c>
+      <c r="I983" t="n">
+        <v>93.2875545393298</v>
+      </c>
+      <c r="J983" t="n">
+        <v>16</v>
+      </c>
+      <c r="K983" t="n">
+        <v>10</v>
+      </c>
+      <c r="L983" t="n">
+        <v>0.4318655133247375</v>
+      </c>
+      <c r="M983" t="n">
+        <v>11.16087436676025</v>
+      </c>
+      <c r="N983" s="2" t="n">
+        <v>45840.39921379081</v>
+      </c>
+      <c r="O983" t="n">
+        <v>109.1</v>
+      </c>
+      <c r="P983" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q983" t="n">
+        <v>1.1775789</v>
+      </c>
+      <c r="R983" t="n">
+        <v>92.64771982582228</v>
+      </c>
+      <c r="S983" t="n">
+        <v>1745.6</v>
+      </c>
+      <c r="T983" t="n">
+        <v>1482.363517213156</v>
+      </c>
+      <c r="U983" t="n">
+        <v>83.9826457277935</v>
+      </c>
+      <c r="V983" t="n">
+        <v>-0.007911248522324277</v>
+      </c>
+      <c r="W983" t="n">
+        <v>-0.006858736051846837</v>
+      </c>
+      <c r="X983" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y983" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z983" t="n">
+        <v>0.4244736433029175</v>
+      </c>
+      <c r="AA983" t="n">
         <v>11.11160755157471</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA983"/>
+  <dimension ref="A1:AA990"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92307,7 +92307,7 @@
         <v>100</v>
       </c>
       <c r="N977" s="2" t="n">
-        <v>45840.39921379081</v>
+        <v>45840.3992137963</v>
       </c>
       <c r="O977" t="n">
         <v>1</v>
@@ -92398,7 +92398,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N978" s="2" t="n">
-        <v>45840.39921379081</v>
+        <v>45840.3992137963</v>
       </c>
       <c r="O978" t="n">
         <v>365.1</v>
@@ -92493,7 +92493,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N979" s="2" t="n">
-        <v>45840.39921379081</v>
+        <v>45840.3992137963</v>
       </c>
       <c r="O979" t="n">
         <v>13.98</v>
@@ -92584,7 +92584,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N980" s="2" t="n">
-        <v>45840.39921379081</v>
+        <v>45840.3992137963</v>
       </c>
       <c r="O980" t="n">
         <v>39</v>
@@ -92679,7 +92679,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N981" s="2" t="n">
-        <v>45840.39921379081</v>
+        <v>45840.3992137963</v>
       </c>
       <c r="O981" t="n">
         <v>45</v>
@@ -92774,7 +92774,7 @@
         <v>12.45218944549561</v>
       </c>
       <c r="N982" s="2" t="n">
-        <v>45840.39921379081</v>
+        <v>45840.3992137963</v>
       </c>
       <c r="O982" t="n">
         <v>26.17</v>
@@ -92869,7 +92869,7 @@
         <v>11.16087436676025</v>
       </c>
       <c r="N983" s="2" t="n">
-        <v>45840.39921379081</v>
+        <v>45840.3992137963</v>
       </c>
       <c r="O983" t="n">
         <v>109.1</v>
@@ -92910,6 +92910,665 @@
         <v>0.4244736433029175</v>
       </c>
       <c r="AA983" t="n">
+        <v>11.11160755157471</v>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D984" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E984" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F984" t="n">
+        <v>1</v>
+      </c>
+      <c r="G984" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H984" t="n">
+        <v>1</v>
+      </c>
+      <c r="I984" t="n">
+        <v>1</v>
+      </c>
+      <c r="J984" t="n">
+        <v>1</v>
+      </c>
+      <c r="K984" t="n">
+        <v>100</v>
+      </c>
+      <c r="L984" t="n">
+        <v>100</v>
+      </c>
+      <c r="M984" t="n">
+        <v>100</v>
+      </c>
+      <c r="N984" s="2" t="n">
+        <v>45840.44242256984</v>
+      </c>
+      <c r="O984" t="n">
+        <v>1</v>
+      </c>
+      <c r="P984" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q984" t="n">
+        <v>1</v>
+      </c>
+      <c r="R984" t="n">
+        <v>1</v>
+      </c>
+      <c r="S984" t="n">
+        <v>0</v>
+      </c>
+      <c r="T984" t="n">
+        <v>1414.591526256027</v>
+      </c>
+      <c r="U984" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V984" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W984" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X984" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y984" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z984" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA984" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C985" t="inlineStr"/>
+      <c r="D985" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E985" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F985" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G985" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H985" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I985" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J985" t="n">
+        <v>3</v>
+      </c>
+      <c r="K985" t="n">
+        <v>10</v>
+      </c>
+      <c r="L985" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M985" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N985" s="2" t="n">
+        <v>45840.44242256984</v>
+      </c>
+      <c r="O985" t="n">
+        <v>365</v>
+      </c>
+      <c r="P985" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q985" t="n">
+        <v>0.85921</v>
+      </c>
+      <c r="R985" t="n">
+        <v>424.8088360237893</v>
+      </c>
+      <c r="S985" t="n">
+        <v>1095</v>
+      </c>
+      <c r="T985" t="n">
+        <v>1274.426508071368</v>
+      </c>
+      <c r="U985" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V985" t="n">
+        <v>-0.007251146420936383</v>
+      </c>
+      <c r="W985" t="n">
+        <v>-0.01365217602816626</v>
+      </c>
+      <c r="X985" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y985" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z985" t="n">
+        <v>0.4170325100421906</v>
+      </c>
+      <c r="AA985" t="n">
+        <v>9.962165534496307</v>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D986" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E986" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F986" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G986" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H986" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I986" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J986" t="n">
+        <v>121</v>
+      </c>
+      <c r="K986" t="n">
+        <v>12</v>
+      </c>
+      <c r="L986" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M986" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N986" s="2" t="n">
+        <v>45840.44242256984</v>
+      </c>
+      <c r="O986" t="n">
+        <v>13.98</v>
+      </c>
+      <c r="P986" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q986" t="n">
+        <v>1.1778563</v>
+      </c>
+      <c r="R986" t="n">
+        <v>11.86902001542973</v>
+      </c>
+      <c r="S986" t="n">
+        <v>1691.58</v>
+      </c>
+      <c r="T986" t="n">
+        <v>1436.151421866997</v>
+      </c>
+      <c r="U986" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V986" t="n">
+        <v>-0.01410437235543016</v>
+      </c>
+      <c r="W986" t="n">
+        <v>-0.03712717419142475</v>
+      </c>
+      <c r="X986" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y986" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z986" t="n">
+        <v>0.323738694190979</v>
+      </c>
+      <c r="AA986" t="n">
+        <v>9.174263775348663</v>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C987" t="inlineStr"/>
+      <c r="D987" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E987" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F987" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G987" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H987" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I987" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J987" t="n">
+        <v>162</v>
+      </c>
+      <c r="K987" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L987" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M987" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N987" s="2" t="n">
+        <v>45840.44242256984</v>
+      </c>
+      <c r="O987" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="P987" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q987" t="n">
+        <v>4.25094</v>
+      </c>
+      <c r="R987" t="n">
+        <v>9.197965626426155</v>
+      </c>
+      <c r="S987" t="n">
+        <v>6334.2</v>
+      </c>
+      <c r="T987" t="n">
+        <v>1490.070431481037</v>
+      </c>
+      <c r="U987" t="n">
+        <v>8.495174269061048</v>
+      </c>
+      <c r="V987" t="n">
+        <v>-0.002551020408163351</v>
+      </c>
+      <c r="W987" t="n">
+        <v>0.0006799996600992397</v>
+      </c>
+      <c r="X987" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y987" t="n">
+        <v>10.667</v>
+      </c>
+      <c r="Z987" t="n">
+        <v>0.3741045594215393</v>
+      </c>
+      <c r="AA987" t="n">
+        <v>10.81489402484894</v>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D988" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E988" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F988" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G988" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H988" t="n">
+        <v>1</v>
+      </c>
+      <c r="I988" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J988" t="n">
+        <v>30</v>
+      </c>
+      <c r="K988" t="n">
+        <v>9</v>
+      </c>
+      <c r="L988" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M988" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N988" s="2" t="n">
+        <v>45840.44242256984</v>
+      </c>
+      <c r="O988" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="P988" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q988" t="n">
+        <v>1</v>
+      </c>
+      <c r="R988" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="S988" t="n">
+        <v>1347</v>
+      </c>
+      <c r="T988" t="n">
+        <v>1347</v>
+      </c>
+      <c r="U988" t="n">
+        <v>42.174</v>
+      </c>
+      <c r="V988" t="n">
+        <v>-0.01707530647985989</v>
+      </c>
+      <c r="W988" t="n">
+        <v>-0.01707530647985989</v>
+      </c>
+      <c r="X988" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y988" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z988" t="n">
+        <v>0.4272054731845856</v>
+      </c>
+      <c r="AA988" t="n">
+        <v>10.09143114089966</v>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>MHY271836006</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="D989" t="inlineStr">
+        <is>
+          <t>GLOBAL SHIP LEA. A DL-,01</t>
+        </is>
+      </c>
+      <c r="E989" s="2" t="n">
+        <v>45838.31344841435</v>
+      </c>
+      <c r="F989" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="G989" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H989" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="I989" t="n">
+        <v>22.64505496285648</v>
+      </c>
+      <c r="J989" t="n">
+        <v>66</v>
+      </c>
+      <c r="K989" t="n">
+        <v>10</v>
+      </c>
+      <c r="L989" t="n">
+        <v>0.5395355224609375</v>
+      </c>
+      <c r="M989" t="n">
+        <v>12.45218944549561</v>
+      </c>
+      <c r="N989" s="2" t="n">
+        <v>45840.44242256984</v>
+      </c>
+      <c r="O989" t="n">
+        <v>26.17</v>
+      </c>
+      <c r="P989" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q989" t="n">
+        <v>1.1778563</v>
+      </c>
+      <c r="R989" t="n">
+        <v>22.21833002888383</v>
+      </c>
+      <c r="S989" t="n">
+        <v>1727.22</v>
+      </c>
+      <c r="T989" t="n">
+        <v>1466.409781906333</v>
+      </c>
+      <c r="U989" t="n">
+        <v>20.40206509457079</v>
+      </c>
+      <c r="V989" t="n">
+        <v>-0.01468373493975894</v>
+      </c>
+      <c r="W989" t="n">
+        <v>-0.01884406704565689</v>
+      </c>
+      <c r="X989" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y989" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z989" t="n">
+        <v>0.3208521902561188</v>
+      </c>
+      <c r="AA989" t="n">
+        <v>9.439456224441528</v>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>PAP310761054</t>
+        </is>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="D990" t="inlineStr">
+        <is>
+          <t>COPA HOLDINGS CL.A O.N.</t>
+        </is>
+      </c>
+      <c r="E990" s="2" t="n">
+        <v>45839.31381715278</v>
+      </c>
+      <c r="F990" t="n">
+        <v>109.97</v>
+      </c>
+      <c r="G990" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H990" t="n">
+        <v>1.1788282</v>
+      </c>
+      <c r="I990" t="n">
+        <v>93.2875545393298</v>
+      </c>
+      <c r="J990" t="n">
+        <v>16</v>
+      </c>
+      <c r="K990" t="n">
+        <v>10</v>
+      </c>
+      <c r="L990" t="n">
+        <v>0.4318655133247375</v>
+      </c>
+      <c r="M990" t="n">
+        <v>11.16087436676025</v>
+      </c>
+      <c r="N990" s="2" t="n">
+        <v>45840.44242256984</v>
+      </c>
+      <c r="O990" t="n">
+        <v>109.1</v>
+      </c>
+      <c r="P990" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q990" t="n">
+        <v>1.1778563</v>
+      </c>
+      <c r="R990" t="n">
+        <v>92.62590012041366</v>
+      </c>
+      <c r="S990" t="n">
+        <v>1745.6</v>
+      </c>
+      <c r="T990" t="n">
+        <v>1482.014401926619</v>
+      </c>
+      <c r="U990" t="n">
+        <v>83.9826457277935</v>
+      </c>
+      <c r="V990" t="n">
+        <v>-0.007911248522324277</v>
+      </c>
+      <c r="W990" t="n">
+        <v>-0.007092633333390608</v>
+      </c>
+      <c r="X990" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y990" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z990" t="n">
+        <v>0.4244736433029175</v>
+      </c>
+      <c r="AA990" t="n">
         <v>11.11160755157471</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA990"/>
+  <dimension ref="A1:AA997"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92966,7 +92966,7 @@
         <v>100</v>
       </c>
       <c r="N984" s="2" t="n">
-        <v>45840.44242256984</v>
+        <v>45840.44242256945</v>
       </c>
       <c r="O984" t="n">
         <v>1</v>
@@ -93057,7 +93057,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N985" s="2" t="n">
-        <v>45840.44242256984</v>
+        <v>45840.44242256945</v>
       </c>
       <c r="O985" t="n">
         <v>365</v>
@@ -93152,7 +93152,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N986" s="2" t="n">
-        <v>45840.44242256984</v>
+        <v>45840.44242256945</v>
       </c>
       <c r="O986" t="n">
         <v>13.98</v>
@@ -93243,7 +93243,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N987" s="2" t="n">
-        <v>45840.44242256984</v>
+        <v>45840.44242256945</v>
       </c>
       <c r="O987" t="n">
         <v>39.1</v>
@@ -93338,7 +93338,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N988" s="2" t="n">
-        <v>45840.44242256984</v>
+        <v>45840.44242256945</v>
       </c>
       <c r="O988" t="n">
         <v>44.9</v>
@@ -93433,7 +93433,7 @@
         <v>12.45218944549561</v>
       </c>
       <c r="N989" s="2" t="n">
-        <v>45840.44242256984</v>
+        <v>45840.44242256945</v>
       </c>
       <c r="O989" t="n">
         <v>26.17</v>
@@ -93528,7 +93528,7 @@
         <v>11.16087436676025</v>
       </c>
       <c r="N990" s="2" t="n">
-        <v>45840.44242256984</v>
+        <v>45840.44242256945</v>
       </c>
       <c r="O990" t="n">
         <v>109.1</v>
@@ -93569,6 +93569,665 @@
         <v>0.4244736433029175</v>
       </c>
       <c r="AA990" t="n">
+        <v>11.11160755157471</v>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D991" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E991" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F991" t="n">
+        <v>1</v>
+      </c>
+      <c r="G991" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H991" t="n">
+        <v>1</v>
+      </c>
+      <c r="I991" t="n">
+        <v>1</v>
+      </c>
+      <c r="J991" t="n">
+        <v>1</v>
+      </c>
+      <c r="K991" t="n">
+        <v>100</v>
+      </c>
+      <c r="L991" t="n">
+        <v>100</v>
+      </c>
+      <c r="M991" t="n">
+        <v>100</v>
+      </c>
+      <c r="N991" s="2" t="n">
+        <v>45840.4769741096</v>
+      </c>
+      <c r="O991" t="n">
+        <v>1</v>
+      </c>
+      <c r="P991" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q991" t="n">
+        <v>1</v>
+      </c>
+      <c r="R991" t="n">
+        <v>1</v>
+      </c>
+      <c r="S991" t="n">
+        <v>0</v>
+      </c>
+      <c r="T991" t="n">
+        <v>1414.591526256027</v>
+      </c>
+      <c r="U991" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V991" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W991" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X991" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y991" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z991" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA991" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C992" t="inlineStr"/>
+      <c r="D992" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E992" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F992" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G992" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H992" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I992" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J992" t="n">
+        <v>3</v>
+      </c>
+      <c r="K992" t="n">
+        <v>10</v>
+      </c>
+      <c r="L992" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M992" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N992" s="2" t="n">
+        <v>45840.4769741096</v>
+      </c>
+      <c r="O992" t="n">
+        <v>365.1</v>
+      </c>
+      <c r="P992" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q992" t="n">
+        <v>0.8581299999999999</v>
+      </c>
+      <c r="R992" t="n">
+        <v>425.460011886311</v>
+      </c>
+      <c r="S992" t="n">
+        <v>1095.3</v>
+      </c>
+      <c r="T992" t="n">
+        <v>1276.380035658933</v>
+      </c>
+      <c r="U992" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V992" t="n">
+        <v>-0.00697916043365443</v>
+      </c>
+      <c r="W992" t="n">
+        <v>-0.01214023503128614</v>
+      </c>
+      <c r="X992" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y992" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z992" t="n">
+        <v>0.4170325100421906</v>
+      </c>
+      <c r="AA992" t="n">
+        <v>9.962165534496307</v>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D993" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E993" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F993" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G993" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H993" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I993" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J993" t="n">
+        <v>121</v>
+      </c>
+      <c r="K993" t="n">
+        <v>12</v>
+      </c>
+      <c r="L993" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M993" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="N993" s="2" t="n">
+        <v>45840.4769741096</v>
+      </c>
+      <c r="O993" t="n">
+        <v>13.98</v>
+      </c>
+      <c r="P993" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q993" t="n">
+        <v>1.176886</v>
+      </c>
+      <c r="R993" t="n">
+        <v>11.87880559374485</v>
+      </c>
+      <c r="S993" t="n">
+        <v>1691.58</v>
+      </c>
+      <c r="T993" t="n">
+        <v>1437.335476843127</v>
+      </c>
+      <c r="U993" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="V993" t="n">
+        <v>-0.01410437235543016</v>
+      </c>
+      <c r="W993" t="n">
+        <v>-0.03633332032377556</v>
+      </c>
+      <c r="X993" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y993" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z993" t="n">
+        <v>0.323738694190979</v>
+      </c>
+      <c r="AA993" t="n">
+        <v>9.174263775348663</v>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="C994" t="inlineStr"/>
+      <c r="D994" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="E994" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="F994" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G994" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H994" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="I994" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="J994" t="n">
+        <v>162</v>
+      </c>
+      <c r="K994" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="L994" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="M994" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="N994" s="2" t="n">
+        <v>45840.4769741096</v>
+      </c>
+      <c r="O994" t="n">
+        <v>39.15</v>
+      </c>
+      <c r="P994" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="Q994" t="n">
+        <v>4.24854</v>
+      </c>
+      <c r="R994" t="n">
+        <v>9.214930305469643</v>
+      </c>
+      <c r="S994" t="n">
+        <v>6342.3</v>
+      </c>
+      <c r="T994" t="n">
+        <v>1492.818709486082</v>
+      </c>
+      <c r="U994" t="n">
+        <v>8.495174269061048</v>
+      </c>
+      <c r="V994" t="n">
+        <v>-0.001275510204081787</v>
+      </c>
+      <c r="W994" t="n">
+        <v>0.002525648546924497</v>
+      </c>
+      <c r="X994" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y994" t="n">
+        <v>10.667</v>
+      </c>
+      <c r="Z994" t="n">
+        <v>0.3741045594215393</v>
+      </c>
+      <c r="AA994" t="n">
+        <v>10.81489402484894</v>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="D995" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="E995" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="F995" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G995" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H995" t="n">
+        <v>1</v>
+      </c>
+      <c r="I995" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="J995" t="n">
+        <v>30</v>
+      </c>
+      <c r="K995" t="n">
+        <v>9</v>
+      </c>
+      <c r="L995" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="M995" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="N995" s="2" t="n">
+        <v>45840.4769741096</v>
+      </c>
+      <c r="O995" t="n">
+        <v>44.98</v>
+      </c>
+      <c r="P995" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q995" t="n">
+        <v>1</v>
+      </c>
+      <c r="R995" t="n">
+        <v>44.98</v>
+      </c>
+      <c r="S995" t="n">
+        <v>1349.4</v>
+      </c>
+      <c r="T995" t="n">
+        <v>1349.4</v>
+      </c>
+      <c r="U995" t="n">
+        <v>42.174</v>
+      </c>
+      <c r="V995" t="n">
+        <v>-0.01532399299474607</v>
+      </c>
+      <c r="W995" t="n">
+        <v>-0.01532399299474607</v>
+      </c>
+      <c r="X995" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y995" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z995" t="n">
+        <v>0.4272054731845856</v>
+      </c>
+      <c r="AA995" t="n">
+        <v>10.09143114089966</v>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>MHY271836006</t>
+        </is>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="D996" t="inlineStr">
+        <is>
+          <t>GLOBAL SHIP LEA. A DL-,01</t>
+        </is>
+      </c>
+      <c r="E996" s="2" t="n">
+        <v>45838.31344841435</v>
+      </c>
+      <c r="F996" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="G996" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H996" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="I996" t="n">
+        <v>22.64505496285648</v>
+      </c>
+      <c r="J996" t="n">
+        <v>66</v>
+      </c>
+      <c r="K996" t="n">
+        <v>10</v>
+      </c>
+      <c r="L996" t="n">
+        <v>0.5395355224609375</v>
+      </c>
+      <c r="M996" t="n">
+        <v>12.45218944549561</v>
+      </c>
+      <c r="N996" s="2" t="n">
+        <v>45840.4769741096</v>
+      </c>
+      <c r="O996" t="n">
+        <v>26.17</v>
+      </c>
+      <c r="P996" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q996" t="n">
+        <v>1.176886</v>
+      </c>
+      <c r="R996" t="n">
+        <v>22.23664823950663</v>
+      </c>
+      <c r="S996" t="n">
+        <v>1727.22</v>
+      </c>
+      <c r="T996" t="n">
+        <v>1467.618783807437</v>
+      </c>
+      <c r="U996" t="n">
+        <v>20.40206509457079</v>
+      </c>
+      <c r="V996" t="n">
+        <v>-0.01468373493975894</v>
+      </c>
+      <c r="W996" t="n">
+        <v>-0.01803513941651913</v>
+      </c>
+      <c r="X996" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y996" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z996" t="n">
+        <v>0.3208521902561188</v>
+      </c>
+      <c r="AA996" t="n">
+        <v>9.439456224441528</v>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>PAP310761054</t>
+        </is>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="D997" t="inlineStr">
+        <is>
+          <t>COPA HOLDINGS CL.A O.N.</t>
+        </is>
+      </c>
+      <c r="E997" s="2" t="n">
+        <v>45839.31381715278</v>
+      </c>
+      <c r="F997" t="n">
+        <v>109.97</v>
+      </c>
+      <c r="G997" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H997" t="n">
+        <v>1.1788282</v>
+      </c>
+      <c r="I997" t="n">
+        <v>93.2875545393298</v>
+      </c>
+      <c r="J997" t="n">
+        <v>16</v>
+      </c>
+      <c r="K997" t="n">
+        <v>10</v>
+      </c>
+      <c r="L997" t="n">
+        <v>0.4318655133247375</v>
+      </c>
+      <c r="M997" t="n">
+        <v>11.16087436676025</v>
+      </c>
+      <c r="N997" s="2" t="n">
+        <v>45840.4769741096</v>
+      </c>
+      <c r="O997" t="n">
+        <v>109.1</v>
+      </c>
+      <c r="P997" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q997" t="n">
+        <v>1.176886</v>
+      </c>
+      <c r="R997" t="n">
+        <v>92.70226682958246</v>
+      </c>
+      <c r="S997" t="n">
+        <v>1745.6</v>
+      </c>
+      <c r="T997" t="n">
+        <v>1483.236269273319</v>
+      </c>
+      <c r="U997" t="n">
+        <v>83.9826457277935</v>
+      </c>
+      <c r="V997" t="n">
+        <v>-0.007911248522324277</v>
+      </c>
+      <c r="W997" t="n">
+        <v>-0.006274017071597582</v>
+      </c>
+      <c r="X997" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y997" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z997" t="n">
+        <v>0.4244736433029175</v>
+      </c>
+      <c r="AA997" t="n">
         <v>11.11160755157471</v>
       </c>
     </row>

--- a/data/depot_hist.xlsx
+++ b/data/depot_hist.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA997"/>
+  <dimension ref="A1:AA1004"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -93625,7 +93625,7 @@
         <v>100</v>
       </c>
       <c r="N991" s="2" t="n">
-        <v>45840.4769741096</v>
+        <v>45840.47697410879</v>
       </c>
       <c r="O991" t="n">
         <v>1</v>
@@ -93716,7 +93716,7 @@
         <v>11.58161377906799</v>
       </c>
       <c r="N992" s="2" t="n">
-        <v>45840.4769741096</v>
+        <v>45840.47697410879</v>
       </c>
       <c r="O992" t="n">
         <v>365.1</v>
@@ -93811,7 +93811,7 @@
         <v>14.27337956428528</v>
       </c>
       <c r="N993" s="2" t="n">
-        <v>45840.4769741096</v>
+        <v>45840.47697410879</v>
       </c>
       <c r="O993" t="n">
         <v>13.98</v>
@@ -93902,7 +93902,7 @@
         <v>12.85747975540161</v>
       </c>
       <c r="N994" s="2" t="n">
-        <v>45840.4769741096</v>
+        <v>45840.47697410879</v>
       </c>
       <c r="O994" t="n">
         <v>39.15</v>
@@ -93997,7 +93997,7 @@
         <v>12.81225872039795</v>
       </c>
       <c r="N995" s="2" t="n">
-        <v>45840.4769741096</v>
+        <v>45840.47697410879</v>
       </c>
       <c r="O995" t="n">
         <v>44.98</v>
@@ -94092,7 +94092,7 @@
         <v>12.45218944549561</v>
       </c>
       <c r="N996" s="2" t="n">
-        <v>45840.4769741096</v>
+        <v>45840.47697410879</v>
       </c>
       <c r="O996" t="n">
         <v>26.17</v>
@@ -94187,7 +94187,7 @@
         <v>11.16087436676025</v>
       </c>
       <c r="N997" s="2" t="n">
-        <v>45840.4769741096</v>
+        <v>45840.47697410879</v>
       </c>
       <c r="O997" t="n">
         <v>109.1</v>
@@ -94228,6 +94228,665 @@
         <v>0.4244736433029175</v>
       </c>
       <c r="AA997" t="n">
+        <v>11.11160755157471</v>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D998" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="E998" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="F998" t="n">
+        <v>1</v>
+      </c>
+      <c r="G998" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H998" t="n">
+        <v>1</v>
+      </c>
+      <c r="I998" t="n">
+        <v>1</v>
+      </c>
+      <c r="J998" t="n">
+        <v>1</v>
+      </c>
+      <c r="K998" t="n">
+        <v>100</v>
+      </c>
+      <c r="L998" t="n">
+        <v>100</v>
+      </c>
+      <c r="M998" t="n">
+        <v>100</v>
+      </c>
+      <c r="N998" s="2" t="n">
+        <v>45840.54168296391</v>
+      </c>
+      <c r="O998" t="n">
+        <v>1</v>
+      </c>
+      <c r="P998" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Q998" t="n">
+        <v>1</v>
+      </c>
+      <c r="R998" t="n">
+        <v>1</v>
+      </c>
+      <c r="S998" t="n">
+        <v>0</v>
+      </c>
+      <c r="T998" t="n">
+        <v>1414.591526256027</v>
+      </c>
+      <c r="U998" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V998" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="W998" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="X998" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y998" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z998" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA998" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="C999" t="inlineStr"/>
+      <c r="D999" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="E999" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="F999" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="G999" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="H999" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="I999" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="J999" t="n">
+        <v>3</v>
+      </c>
+      <c r="K999" t="n">
+        <v>10</v>
+      </c>
+      <c r="L999" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="M999" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="N999" s="2" t="n">
+        <v>45840.54168296391</v>
+      </c>
+      <c r="O999" t="n">
+        <v>375</v>
+      </c>
+      <c r="P999" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="Q999" t="n">
+        <v>0.86391</v>
+      </c>
+      <c r="R999" t="n">
+        <v>434.0729937146231</v>
+      </c>
+      <c r="S999" t="n">
+        <v>1125</v>
+      </c>
+      <c r="T999" t="n">
+        <v>1302.218981143869</v>
+      </c>
+      <c r="U999" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="V999" t="n">
+        <v>0.01994745230725714</v>
+      </c>
+      <c r="W999" t="n">
+        <v>0.007857926880272537</v>
+      </c>
+      <c r="X999" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y999" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z999" t="n">
+        <v>0.4170325100421906</v>
+      </c>
+      <c r="AA999" t="n">
+        <v>9.962165534496307</v>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D1000" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="E1000" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="F1000" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G1000" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H1000" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="I1000" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="J1000" t="n">
+        <v>121</v>
+      </c>
+      <c r="K1000" t="n">
+        <v>12</v>
+      </c>
+      <c r="L1000" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="M1000" t="n">
+        <v>14.27337956428528</v>
